--- a/database/conference_coverage_matrix.xlsx
+++ b/database/conference_coverage_matrix.xlsx
@@ -42,7 +42,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -86,6 +86,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="0093C47D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="006AA84F"/>
       </patternFill>
     </fill>
@@ -121,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -132,7 +137,8 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -142,7 +148,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -155,6 +161,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1090,7 +1099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1200,7 +1209,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Abstract book in hand and ingestable. Only extraction remains.</t>
+          <t>Abstract book in hand, nothing extracted into the database yet.</t>
         </is>
       </c>
       <c r="C8" s="8" t="n"/>
@@ -1208,12 +1217,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ingested</t>
+          <t>Extracted</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Full abstracts ingested into the database.</t>
+          <t>Abstracts are in the database, but from the regex parsers (or extracted and not yet merged). Titles and author lists are weak; full re-extraction is queued.</t>
         </is>
       </c>
       <c r="C9" s="9" t="n"/>
@@ -1221,68 +1230,81 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>- 'ASIH/JMIH' = the American joint meeting (ASIH pre-1997, JMIH from 1997). ASIH/JMIH/HL/SSAR/NIA share one source book, collapsed to this column to remove duplicates.</t>
-        </is>
-      </c>
+          <t>Ingested</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fully extracted and merged into the database. Done.</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>- 'AES' (American Elasmobranch Society, founded 1983) kept separate — cell shows elasmo-abstract count where ingested. Pre-1983 = no conference (blank).</t>
+          <t>- 'ASIH/JMIH' = the American joint meeting (ASIH pre-1997, JMIH from 1997). ASIH/JMIH/HL/SSAR/NIA share one source book, collapsed to this column to remove duplicates.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>- Host cities 1916-2025 from github.com/SimonDedman/AESconfLocations; 2026 = New Orleans.</t>
+          <t>- 'AES' (American Elasmobranch Society, founded 1983) kept separate — cell shows elasmo-abstract count where ingested. Pre-1983 = no conference (blank).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>- 'OCR' = degraded 1997-2004 JMIH phone-photo scans (all needs_review); Carylanne's flatbed re-scans would upgrade the non-AES content.</t>
+          <t>- Host cities 1916-2025 from github.com/SimonDedman/AESconfLocations; 2026 = New Orleans.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>- AES 1985-2005: full abstracts harvested from elasmo.org/meetings/abstracts/abst&lt;YYYY&gt;/ (1,305 abstracts, 2026-08-25); JMIH-book copies of the same AES talks were removed. No AES source found for 1983-84 or 2006+ online.</t>
+          <t>- 'OCR' = degraded 1997-2004 JMIH phone-photo scans (all needs_review); Carylanne's flatbed re-scans would upgrade the non-AES content.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>- ASIH/JMIH pre-1992: Carylanne's archive starts 1992 → host city shown but 'Missing'.</t>
+          <t>- AES 1985-2005: full abstracts harvested from elasmo.org/meetings/abstracts/abst&lt;YYYY&gt;/ (1,305 abstracts, 2026-08-25); JMIH-book copies of the same AES talks were removed. No AES source found for 1983-84 or 2006+ online.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>- EEA from Cat Gordon (Shark Trust). 2004-2019 + 2023 ingested via Fable and merged 2026-08-25. Received 2026-08-27: 2002 Cardiff booklet, a clean 2024 Thessaloniki book, and the full SI2022 Valencia abstract book (all queued for extraction). 2025 Rotterdam abstract book is still a corrupt file. Cat holds hardcopies of 2010/2012/2015/2017 but has no scanning capacity, so those are being sought digitally from the host groups; Ali Hood is searching her paperwork for 2003-2009. EEA began in 1997 (2002 Cardiff was the 6th).</t>
+          <t>- ASIH/JMIH pre-1992: Carylanne's archive starts 1992 → host city shown but 'Missing'.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>- OCS (Oceania Chondrichthyan Soc, ~2011+, biennial): Brit Finucci collating, pending council — years/locations TBC.</t>
+          <t>- EEA from Cat Gordon (Shark Trust). 2004-2019 + 2023 ingested via Fable and merged 2026-08-25. Received 2026-08-27: 2002 Cardiff booklet, a clean 2024 Thessaloniki book, and the full SI2022 Valencia abstract book (all queued for extraction). 2025 Rotterdam abstract book is still a corrupt file. Cat holds hardcopies of 2010/2012/2015/2017 but has no scanning capacity, so those are being sought digitally from the host groups; Ali Hood is searching her paperwork for 2003-2009. EEA began in 1997 (2002 Cardiff was the 6th).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>- Blank/unshaded cell = no conference that year for that series.</t>
+          <t>- OCS (Oceania Chondrichthyan Soc, ~2011+, biennial): Brit Finucci collating, pending council — years/locations TBC.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
+        <is>
+          <t>- Blank/unshaded cell = no conference that year for that series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>- Per-society counts &amp; trends: see the Dashboard tab.</t>
         </is>
@@ -1311,1934 +1333,1934 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>ASIH/JMIH</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>AES</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>EEA</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>OCS</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="n">
+      <c r="A2" s="12" t="n">
         <v>1916</v>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>New York, NY; Missing</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr"/>
-      <c r="D2" s="13" t="inlineStr"/>
-      <c r="E2" s="13" t="inlineStr"/>
-      <c r="F2" s="13" t="inlineStr"/>
+      <c r="C2" s="14" t="inlineStr"/>
+      <c r="D2" s="14" t="inlineStr"/>
+      <c r="E2" s="14" t="inlineStr"/>
+      <c r="F2" s="14" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="n">
+      <c r="A3" s="12" t="n">
         <v>1917</v>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Cambridge, MA; Missing</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr"/>
-      <c r="D3" s="13" t="inlineStr"/>
-      <c r="E3" s="13" t="inlineStr"/>
-      <c r="F3" s="13" t="inlineStr"/>
+      <c r="C3" s="14" t="inlineStr"/>
+      <c r="D3" s="14" t="inlineStr"/>
+      <c r="E3" s="14" t="inlineStr"/>
+      <c r="F3" s="14" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="n">
+      <c r="A4" s="12" t="n">
         <v>1918</v>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Brooklyn, NY; Missing</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr"/>
-      <c r="D4" s="13" t="inlineStr"/>
-      <c r="E4" s="13" t="inlineStr"/>
-      <c r="F4" s="13" t="inlineStr"/>
+      <c r="C4" s="14" t="inlineStr"/>
+      <c r="D4" s="14" t="inlineStr"/>
+      <c r="E4" s="14" t="inlineStr"/>
+      <c r="F4" s="14" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="n">
+      <c r="A5" s="12" t="n">
         <v>1919</v>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>?; Missing</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr"/>
-      <c r="D5" s="13" t="inlineStr"/>
-      <c r="E5" s="13" t="inlineStr"/>
-      <c r="F5" s="13" t="inlineStr"/>
+      <c r="C5" s="14" t="inlineStr"/>
+      <c r="D5" s="14" t="inlineStr"/>
+      <c r="E5" s="14" t="inlineStr"/>
+      <c r="F5" s="14" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="n">
+      <c r="A6" s="12" t="n">
         <v>1920</v>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Washington, DC; Missing</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr"/>
-      <c r="D6" s="13" t="inlineStr"/>
-      <c r="E6" s="13" t="inlineStr"/>
-      <c r="F6" s="13" t="inlineStr"/>
+      <c r="C6" s="14" t="inlineStr"/>
+      <c r="D6" s="14" t="inlineStr"/>
+      <c r="E6" s="14" t="inlineStr"/>
+      <c r="F6" s="14" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="n">
+      <c r="A7" s="12" t="n">
         <v>1921</v>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Philadelphia, PA; Missing</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr"/>
-      <c r="D7" s="13" t="inlineStr"/>
-      <c r="E7" s="13" t="inlineStr"/>
-      <c r="F7" s="13" t="inlineStr"/>
+      <c r="C7" s="14" t="inlineStr"/>
+      <c r="D7" s="14" t="inlineStr"/>
+      <c r="E7" s="14" t="inlineStr"/>
+      <c r="F7" s="14" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n">
+      <c r="A8" s="12" t="n">
         <v>1922</v>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Chicago, IL; Missing</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr"/>
-      <c r="D8" s="13" t="inlineStr"/>
-      <c r="E8" s="13" t="inlineStr"/>
-      <c r="F8" s="13" t="inlineStr"/>
+      <c r="C8" s="14" t="inlineStr"/>
+      <c r="D8" s="14" t="inlineStr"/>
+      <c r="E8" s="14" t="inlineStr"/>
+      <c r="F8" s="14" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="n">
+      <c r="A9" s="12" t="n">
         <v>1923</v>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Cambridge, MA; Missing</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr"/>
-      <c r="D9" s="13" t="inlineStr"/>
-      <c r="E9" s="13" t="inlineStr"/>
-      <c r="F9" s="13" t="inlineStr"/>
+      <c r="C9" s="14" t="inlineStr"/>
+      <c r="D9" s="14" t="inlineStr"/>
+      <c r="E9" s="14" t="inlineStr"/>
+      <c r="F9" s="14" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n">
+      <c r="A10" s="12" t="n">
         <v>1924</v>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Northhampton, MA; Missing</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr"/>
-      <c r="D10" s="13" t="inlineStr"/>
-      <c r="E10" s="13" t="inlineStr"/>
-      <c r="F10" s="13" t="inlineStr"/>
+      <c r="C10" s="14" t="inlineStr"/>
+      <c r="D10" s="14" t="inlineStr"/>
+      <c r="E10" s="14" t="inlineStr"/>
+      <c r="F10" s="14" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n">
+      <c r="A11" s="12" t="n">
         <v>1925</v>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>?; Missing</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr"/>
-      <c r="D11" s="13" t="inlineStr"/>
-      <c r="E11" s="13" t="inlineStr"/>
-      <c r="F11" s="13" t="inlineStr"/>
+      <c r="C11" s="14" t="inlineStr"/>
+      <c r="D11" s="14" t="inlineStr"/>
+      <c r="E11" s="14" t="inlineStr"/>
+      <c r="F11" s="14" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n">
+      <c r="A12" s="12" t="n">
         <v>1926</v>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>Philadelphia, PA; Missing</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr"/>
-      <c r="D12" s="13" t="inlineStr"/>
-      <c r="E12" s="13" t="inlineStr"/>
-      <c r="F12" s="13" t="inlineStr"/>
+      <c r="C12" s="14" t="inlineStr"/>
+      <c r="D12" s="14" t="inlineStr"/>
+      <c r="E12" s="14" t="inlineStr"/>
+      <c r="F12" s="14" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n">
+      <c r="A13" s="12" t="n">
         <v>1927</v>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Philadelphia, PA; Missing</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr"/>
-      <c r="D13" s="13" t="inlineStr"/>
-      <c r="E13" s="13" t="inlineStr"/>
-      <c r="F13" s="13" t="inlineStr"/>
+      <c r="C13" s="14" t="inlineStr"/>
+      <c r="D13" s="14" t="inlineStr"/>
+      <c r="E13" s="14" t="inlineStr"/>
+      <c r="F13" s="14" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n">
+      <c r="A14" s="12" t="n">
         <v>1928</v>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>Washington, DC; Missing</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr"/>
-      <c r="D14" s="13" t="inlineStr"/>
-      <c r="E14" s="13" t="inlineStr"/>
-      <c r="F14" s="13" t="inlineStr"/>
+      <c r="C14" s="14" t="inlineStr"/>
+      <c r="D14" s="14" t="inlineStr"/>
+      <c r="E14" s="14" t="inlineStr"/>
+      <c r="F14" s="14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="n">
+      <c r="A15" s="12" t="n">
         <v>1929</v>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>Ann Arbor, MI; Missing</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr"/>
-      <c r="D15" s="13" t="inlineStr"/>
-      <c r="E15" s="13" t="inlineStr"/>
-      <c r="F15" s="13" t="inlineStr"/>
+      <c r="C15" s="14" t="inlineStr"/>
+      <c r="D15" s="14" t="inlineStr"/>
+      <c r="E15" s="14" t="inlineStr"/>
+      <c r="F15" s="14" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n">
+      <c r="A16" s="12" t="n">
         <v>1930</v>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>New York, NY; Missing</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr"/>
-      <c r="D16" s="13" t="inlineStr"/>
-      <c r="E16" s="13" t="inlineStr"/>
-      <c r="F16" s="13" t="inlineStr"/>
+      <c r="C16" s="14" t="inlineStr"/>
+      <c r="D16" s="14" t="inlineStr"/>
+      <c r="E16" s="14" t="inlineStr"/>
+      <c r="F16" s="14" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="n">
+      <c r="A17" s="12" t="n">
         <v>1931</v>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>Philadelphia, PA; Missing</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr"/>
-      <c r="D17" s="13" t="inlineStr"/>
-      <c r="E17" s="13" t="inlineStr"/>
-      <c r="F17" s="13" t="inlineStr"/>
+      <c r="C17" s="14" t="inlineStr"/>
+      <c r="D17" s="14" t="inlineStr"/>
+      <c r="E17" s="14" t="inlineStr"/>
+      <c r="F17" s="14" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n">
+      <c r="A18" s="12" t="n">
         <v>1932</v>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>Washington, DC; Missing</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr"/>
-      <c r="D18" s="13" t="inlineStr"/>
-      <c r="E18" s="13" t="inlineStr"/>
-      <c r="F18" s="13" t="inlineStr"/>
+      <c r="C18" s="14" t="inlineStr"/>
+      <c r="D18" s="14" t="inlineStr"/>
+      <c r="E18" s="14" t="inlineStr"/>
+      <c r="F18" s="14" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="n">
+      <c r="A19" s="12" t="n">
         <v>1933</v>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>Cambridge, MA; Missing</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr"/>
-      <c r="D19" s="13" t="inlineStr"/>
-      <c r="E19" s="13" t="inlineStr"/>
-      <c r="F19" s="13" t="inlineStr"/>
+      <c r="C19" s="14" t="inlineStr"/>
+      <c r="D19" s="14" t="inlineStr"/>
+      <c r="E19" s="14" t="inlineStr"/>
+      <c r="F19" s="14" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="n">
+      <c r="A20" s="12" t="n">
         <v>1934</v>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>New York, NY; Missing</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr"/>
-      <c r="D20" s="13" t="inlineStr"/>
-      <c r="E20" s="13" t="inlineStr"/>
-      <c r="F20" s="13" t="inlineStr"/>
+      <c r="C20" s="14" t="inlineStr"/>
+      <c r="D20" s="14" t="inlineStr"/>
+      <c r="E20" s="14" t="inlineStr"/>
+      <c r="F20" s="14" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="n">
+      <c r="A21" s="12" t="n">
         <v>1935</v>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>Pittsburgh, PA; Missing</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr"/>
-      <c r="D21" s="13" t="inlineStr"/>
-      <c r="E21" s="13" t="inlineStr"/>
-      <c r="F21" s="13" t="inlineStr"/>
+      <c r="C21" s="14" t="inlineStr"/>
+      <c r="D21" s="14" t="inlineStr"/>
+      <c r="E21" s="14" t="inlineStr"/>
+      <c r="F21" s="14" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="n">
+      <c r="A22" s="12" t="n">
         <v>1936</v>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>Ann Arbor, MI; Missing</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr"/>
-      <c r="D22" s="13" t="inlineStr"/>
-      <c r="E22" s="13" t="inlineStr"/>
-      <c r="F22" s="13" t="inlineStr"/>
+      <c r="C22" s="14" t="inlineStr"/>
+      <c r="D22" s="14" t="inlineStr"/>
+      <c r="E22" s="14" t="inlineStr"/>
+      <c r="F22" s="14" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="n">
+      <c r="A23" s="12" t="n">
         <v>1937</v>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>Washington, DC; Missing</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr"/>
-      <c r="D23" s="13" t="inlineStr"/>
-      <c r="E23" s="13" t="inlineStr"/>
-      <c r="F23" s="13" t="inlineStr"/>
+      <c r="C23" s="14" t="inlineStr"/>
+      <c r="D23" s="14" t="inlineStr"/>
+      <c r="E23" s="14" t="inlineStr"/>
+      <c r="F23" s="14" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="n">
+      <c r="A24" s="12" t="n">
         <v>1938</v>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>Berkeley, CA; Missing</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr"/>
-      <c r="D24" s="13" t="inlineStr"/>
-      <c r="E24" s="13" t="inlineStr"/>
-      <c r="F24" s="13" t="inlineStr"/>
+      <c r="C24" s="14" t="inlineStr"/>
+      <c r="D24" s="14" t="inlineStr"/>
+      <c r="E24" s="14" t="inlineStr"/>
+      <c r="F24" s="14" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n">
+      <c r="A25" s="12" t="n">
         <v>1939</v>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>Chicago, IL; Missing</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr"/>
-      <c r="D25" s="13" t="inlineStr"/>
-      <c r="E25" s="13" t="inlineStr"/>
-      <c r="F25" s="13" t="inlineStr"/>
+      <c r="C25" s="14" t="inlineStr"/>
+      <c r="D25" s="14" t="inlineStr"/>
+      <c r="E25" s="14" t="inlineStr"/>
+      <c r="F25" s="14" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="n">
+      <c r="A26" s="12" t="n">
         <v>1940</v>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>Toronto, ON; Missing</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr"/>
-      <c r="D26" s="13" t="inlineStr"/>
-      <c r="E26" s="13" t="inlineStr"/>
-      <c r="F26" s="13" t="inlineStr"/>
+      <c r="C26" s="14" t="inlineStr"/>
+      <c r="D26" s="14" t="inlineStr"/>
+      <c r="E26" s="14" t="inlineStr"/>
+      <c r="F26" s="14" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="n">
+      <c r="A27" s="12" t="n">
         <v>1941</v>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>Gainesville, FL; Missing</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr"/>
-      <c r="D27" s="13" t="inlineStr"/>
-      <c r="E27" s="13" t="inlineStr"/>
-      <c r="F27" s="13" t="inlineStr"/>
+      <c r="C27" s="14" t="inlineStr"/>
+      <c r="D27" s="14" t="inlineStr"/>
+      <c r="E27" s="14" t="inlineStr"/>
+      <c r="F27" s="14" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="n">
+      <c r="A28" s="12" t="n">
         <v>1942</v>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>New York, NY; Missing</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr"/>
-      <c r="D28" s="13" t="inlineStr"/>
-      <c r="E28" s="13" t="inlineStr"/>
-      <c r="F28" s="13" t="inlineStr"/>
+      <c r="C28" s="14" t="inlineStr"/>
+      <c r="D28" s="14" t="inlineStr"/>
+      <c r="E28" s="14" t="inlineStr"/>
+      <c r="F28" s="14" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="n">
+      <c r="A29" s="12" t="n">
         <v>1943</v>
       </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>?; Missing</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr"/>
-      <c r="D29" s="13" t="inlineStr"/>
-      <c r="E29" s="13" t="inlineStr"/>
-      <c r="F29" s="13" t="inlineStr"/>
+      <c r="C29" s="14" t="inlineStr"/>
+      <c r="D29" s="14" t="inlineStr"/>
+      <c r="E29" s="14" t="inlineStr"/>
+      <c r="F29" s="14" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="n">
+      <c r="A30" s="12" t="n">
         <v>1944</v>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B30" s="13" t="inlineStr">
         <is>
           <t>?; Missing</t>
         </is>
       </c>
-      <c r="C30" s="13" t="inlineStr"/>
-      <c r="D30" s="13" t="inlineStr"/>
-      <c r="E30" s="13" t="inlineStr"/>
-      <c r="F30" s="13" t="inlineStr"/>
+      <c r="C30" s="14" t="inlineStr"/>
+      <c r="D30" s="14" t="inlineStr"/>
+      <c r="E30" s="14" t="inlineStr"/>
+      <c r="F30" s="14" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="n">
+      <c r="A31" s="12" t="n">
         <v>1945</v>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>?; Missing</t>
         </is>
       </c>
-      <c r="C31" s="13" t="inlineStr"/>
-      <c r="D31" s="13" t="inlineStr"/>
-      <c r="E31" s="13" t="inlineStr"/>
-      <c r="F31" s="13" t="inlineStr"/>
+      <c r="C31" s="14" t="inlineStr"/>
+      <c r="D31" s="14" t="inlineStr"/>
+      <c r="E31" s="14" t="inlineStr"/>
+      <c r="F31" s="14" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="n">
+      <c r="A32" s="12" t="n">
         <v>1946</v>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="13" t="inlineStr">
         <is>
           <t>Pittsburgh, PA; Missing</t>
         </is>
       </c>
-      <c r="C32" s="13" t="inlineStr"/>
-      <c r="D32" s="13" t="inlineStr"/>
-      <c r="E32" s="13" t="inlineStr"/>
-      <c r="F32" s="13" t="inlineStr"/>
+      <c r="C32" s="14" t="inlineStr"/>
+      <c r="D32" s="14" t="inlineStr"/>
+      <c r="E32" s="14" t="inlineStr"/>
+      <c r="F32" s="14" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="n">
+      <c r="A33" s="12" t="n">
         <v>1947</v>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>Higgins Lake, MI; Missing</t>
         </is>
       </c>
-      <c r="C33" s="13" t="inlineStr"/>
-      <c r="D33" s="13" t="inlineStr"/>
-      <c r="E33" s="13" t="inlineStr"/>
-      <c r="F33" s="13" t="inlineStr"/>
+      <c r="C33" s="14" t="inlineStr"/>
+      <c r="D33" s="14" t="inlineStr"/>
+      <c r="E33" s="14" t="inlineStr"/>
+      <c r="F33" s="14" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="n">
+      <c r="A34" s="12" t="n">
         <v>1948</v>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t>New Orleans, LA; Missing</t>
         </is>
       </c>
-      <c r="C34" s="13" t="inlineStr"/>
-      <c r="D34" s="13" t="inlineStr"/>
-      <c r="E34" s="13" t="inlineStr"/>
-      <c r="F34" s="13" t="inlineStr"/>
+      <c r="C34" s="14" t="inlineStr"/>
+      <c r="D34" s="14" t="inlineStr"/>
+      <c r="E34" s="14" t="inlineStr"/>
+      <c r="F34" s="14" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="n">
+      <c r="A35" s="12" t="n">
         <v>1949</v>
       </c>
-      <c r="B35" s="12" t="inlineStr">
+      <c r="B35" s="13" t="inlineStr">
         <is>
           <t>Washington, DC; Missing</t>
         </is>
       </c>
-      <c r="C35" s="13" t="inlineStr"/>
-      <c r="D35" s="13" t="inlineStr"/>
-      <c r="E35" s="13" t="inlineStr"/>
-      <c r="F35" s="13" t="inlineStr"/>
+      <c r="C35" s="14" t="inlineStr"/>
+      <c r="D35" s="14" t="inlineStr"/>
+      <c r="E35" s="14" t="inlineStr"/>
+      <c r="F35" s="14" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="n">
+      <c r="A36" s="12" t="n">
         <v>1950</v>
       </c>
-      <c r="B36" s="12" t="inlineStr">
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>Salt Lake City, UT; Missing</t>
         </is>
       </c>
-      <c r="C36" s="13" t="inlineStr"/>
-      <c r="D36" s="13" t="inlineStr"/>
-      <c r="E36" s="13" t="inlineStr"/>
-      <c r="F36" s="13" t="inlineStr"/>
+      <c r="C36" s="14" t="inlineStr"/>
+      <c r="D36" s="14" t="inlineStr"/>
+      <c r="E36" s="14" t="inlineStr"/>
+      <c r="F36" s="14" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="n">
+      <c r="A37" s="12" t="n">
         <v>1951</v>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B37" s="13" t="inlineStr">
         <is>
           <t>Chicago, IL; Missing</t>
         </is>
       </c>
-      <c r="C37" s="13" t="inlineStr"/>
-      <c r="D37" s="13" t="inlineStr"/>
-      <c r="E37" s="13" t="inlineStr"/>
-      <c r="F37" s="13" t="inlineStr"/>
+      <c r="C37" s="14" t="inlineStr"/>
+      <c r="D37" s="14" t="inlineStr"/>
+      <c r="E37" s="14" t="inlineStr"/>
+      <c r="F37" s="14" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="n">
+      <c r="A38" s="12" t="n">
         <v>1952</v>
       </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="B38" s="13" t="inlineStr">
         <is>
           <t>Austin, TX; Missing</t>
         </is>
       </c>
-      <c r="C38" s="13" t="inlineStr"/>
-      <c r="D38" s="13" t="inlineStr"/>
-      <c r="E38" s="13" t="inlineStr"/>
-      <c r="F38" s="13" t="inlineStr"/>
+      <c r="C38" s="14" t="inlineStr"/>
+      <c r="D38" s="14" t="inlineStr"/>
+      <c r="E38" s="14" t="inlineStr"/>
+      <c r="F38" s="14" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="n">
+      <c r="A39" s="12" t="n">
         <v>1953</v>
       </c>
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B39" s="13" t="inlineStr">
         <is>
           <t>New York, NY; Missing</t>
         </is>
       </c>
-      <c r="C39" s="13" t="inlineStr"/>
-      <c r="D39" s="13" t="inlineStr"/>
-      <c r="E39" s="13" t="inlineStr"/>
-      <c r="F39" s="13" t="inlineStr"/>
+      <c r="C39" s="14" t="inlineStr"/>
+      <c r="D39" s="14" t="inlineStr"/>
+      <c r="E39" s="14" t="inlineStr"/>
+      <c r="F39" s="14" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="n">
+      <c r="A40" s="12" t="n">
         <v>1954</v>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B40" s="13" t="inlineStr">
         <is>
           <t>Gainesville, FL; Missing</t>
         </is>
       </c>
-      <c r="C40" s="13" t="inlineStr"/>
-      <c r="D40" s="13" t="inlineStr"/>
-      <c r="E40" s="13" t="inlineStr"/>
-      <c r="F40" s="13" t="inlineStr"/>
+      <c r="C40" s="14" t="inlineStr"/>
+      <c r="D40" s="14" t="inlineStr"/>
+      <c r="E40" s="14" t="inlineStr"/>
+      <c r="F40" s="14" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="n">
+      <c r="A41" s="12" t="n">
         <v>1955</v>
       </c>
-      <c r="B41" s="12" t="inlineStr">
+      <c r="B41" s="13" t="inlineStr">
         <is>
           <t>San Francisco, CA; Missing</t>
         </is>
       </c>
-      <c r="C41" s="13" t="inlineStr"/>
-      <c r="D41" s="13" t="inlineStr"/>
-      <c r="E41" s="13" t="inlineStr"/>
-      <c r="F41" s="13" t="inlineStr"/>
+      <c r="C41" s="14" t="inlineStr"/>
+      <c r="D41" s="14" t="inlineStr"/>
+      <c r="E41" s="14" t="inlineStr"/>
+      <c r="F41" s="14" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="n">
+      <c r="A42" s="12" t="n">
         <v>1956</v>
       </c>
-      <c r="B42" s="12" t="inlineStr">
+      <c r="B42" s="13" t="inlineStr">
         <is>
           <t>Higgins Lake, MI; Missing</t>
         </is>
       </c>
-      <c r="C42" s="13" t="inlineStr"/>
-      <c r="D42" s="13" t="inlineStr"/>
-      <c r="E42" s="13" t="inlineStr"/>
-      <c r="F42" s="13" t="inlineStr"/>
+      <c r="C42" s="14" t="inlineStr"/>
+      <c r="D42" s="14" t="inlineStr"/>
+      <c r="E42" s="14" t="inlineStr"/>
+      <c r="F42" s="14" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="n">
+      <c r="A43" s="12" t="n">
         <v>1957</v>
       </c>
-      <c r="B43" s="12" t="inlineStr">
+      <c r="B43" s="13" t="inlineStr">
         <is>
           <t>New Orleans, LA; Missing</t>
         </is>
       </c>
-      <c r="C43" s="13" t="inlineStr"/>
-      <c r="D43" s="13" t="inlineStr"/>
-      <c r="E43" s="13" t="inlineStr"/>
-      <c r="F43" s="13" t="inlineStr"/>
+      <c r="C43" s="14" t="inlineStr"/>
+      <c r="D43" s="14" t="inlineStr"/>
+      <c r="E43" s="14" t="inlineStr"/>
+      <c r="F43" s="14" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="11" t="n">
+      <c r="A44" s="12" t="n">
         <v>1958</v>
       </c>
-      <c r="B44" s="12" t="inlineStr">
+      <c r="B44" s="13" t="inlineStr">
         <is>
           <t>Bloomington, IN; Missing</t>
         </is>
       </c>
-      <c r="C44" s="13" t="inlineStr"/>
-      <c r="D44" s="13" t="inlineStr"/>
-      <c r="E44" s="13" t="inlineStr"/>
-      <c r="F44" s="13" t="inlineStr"/>
+      <c r="C44" s="14" t="inlineStr"/>
+      <c r="D44" s="14" t="inlineStr"/>
+      <c r="E44" s="14" t="inlineStr"/>
+      <c r="F44" s="14" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="11" t="n">
+      <c r="A45" s="12" t="n">
         <v>1959</v>
       </c>
-      <c r="B45" s="12" t="inlineStr">
+      <c r="B45" s="13" t="inlineStr">
         <is>
           <t>San Diego, CA; Missing</t>
         </is>
       </c>
-      <c r="C45" s="13" t="inlineStr"/>
-      <c r="D45" s="13" t="inlineStr"/>
-      <c r="E45" s="13" t="inlineStr"/>
-      <c r="F45" s="13" t="inlineStr"/>
+      <c r="C45" s="14" t="inlineStr"/>
+      <c r="D45" s="14" t="inlineStr"/>
+      <c r="E45" s="14" t="inlineStr"/>
+      <c r="F45" s="14" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="11" t="n">
+      <c r="A46" s="12" t="n">
         <v>1960</v>
       </c>
-      <c r="B46" s="12" t="inlineStr">
+      <c r="B46" s="13" t="inlineStr">
         <is>
           <t>Chicago, IL; Missing</t>
         </is>
       </c>
-      <c r="C46" s="13" t="inlineStr"/>
-      <c r="D46" s="13" t="inlineStr"/>
-      <c r="E46" s="13" t="inlineStr"/>
-      <c r="F46" s="13" t="inlineStr"/>
+      <c r="C46" s="14" t="inlineStr"/>
+      <c r="D46" s="14" t="inlineStr"/>
+      <c r="E46" s="14" t="inlineStr"/>
+      <c r="F46" s="14" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="11" t="n">
+      <c r="A47" s="12" t="n">
         <v>1961</v>
       </c>
-      <c r="B47" s="12" t="inlineStr">
+      <c r="B47" s="13" t="inlineStr">
         <is>
           <t>Austin, TX; Missing</t>
         </is>
       </c>
-      <c r="C47" s="13" t="inlineStr"/>
-      <c r="D47" s="13" t="inlineStr"/>
-      <c r="E47" s="13" t="inlineStr"/>
-      <c r="F47" s="13" t="inlineStr"/>
+      <c r="C47" s="14" t="inlineStr"/>
+      <c r="D47" s="14" t="inlineStr"/>
+      <c r="E47" s="14" t="inlineStr"/>
+      <c r="F47" s="14" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="11" t="n">
+      <c r="A48" s="12" t="n">
         <v>1962</v>
       </c>
-      <c r="B48" s="12" t="inlineStr">
+      <c r="B48" s="13" t="inlineStr">
         <is>
           <t>Washington, DC; Missing</t>
         </is>
       </c>
-      <c r="C48" s="13" t="inlineStr"/>
-      <c r="D48" s="13" t="inlineStr"/>
-      <c r="E48" s="13" t="inlineStr"/>
-      <c r="F48" s="13" t="inlineStr"/>
+      <c r="C48" s="14" t="inlineStr"/>
+      <c r="D48" s="14" t="inlineStr"/>
+      <c r="E48" s="14" t="inlineStr"/>
+      <c r="F48" s="14" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="11" t="n">
+      <c r="A49" s="12" t="n">
         <v>1963</v>
       </c>
-      <c r="B49" s="12" t="inlineStr">
+      <c r="B49" s="13" t="inlineStr">
         <is>
           <t>Vancouver, BC; Missing</t>
         </is>
       </c>
-      <c r="C49" s="13" t="inlineStr"/>
-      <c r="D49" s="13" t="inlineStr"/>
-      <c r="E49" s="13" t="inlineStr"/>
-      <c r="F49" s="13" t="inlineStr"/>
+      <c r="C49" s="14" t="inlineStr"/>
+      <c r="D49" s="14" t="inlineStr"/>
+      <c r="E49" s="14" t="inlineStr"/>
+      <c r="F49" s="14" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="11" t="n">
+      <c r="A50" s="12" t="n">
         <v>1964</v>
       </c>
-      <c r="B50" s="12" t="inlineStr">
+      <c r="B50" s="13" t="inlineStr">
         <is>
           <t>Morehead City, NC; Missing</t>
         </is>
       </c>
-      <c r="C50" s="13" t="inlineStr"/>
-      <c r="D50" s="13" t="inlineStr"/>
-      <c r="E50" s="13" t="inlineStr"/>
-      <c r="F50" s="13" t="inlineStr"/>
+      <c r="C50" s="14" t="inlineStr"/>
+      <c r="D50" s="14" t="inlineStr"/>
+      <c r="E50" s="14" t="inlineStr"/>
+      <c r="F50" s="14" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="11" t="n">
+      <c r="A51" s="12" t="n">
         <v>1965</v>
       </c>
-      <c r="B51" s="12" t="inlineStr">
+      <c r="B51" s="13" t="inlineStr">
         <is>
           <t>Lawrence, KS; Missing</t>
         </is>
       </c>
-      <c r="C51" s="13" t="inlineStr"/>
-      <c r="D51" s="13" t="inlineStr"/>
-      <c r="E51" s="13" t="inlineStr"/>
-      <c r="F51" s="13" t="inlineStr"/>
+      <c r="C51" s="14" t="inlineStr"/>
+      <c r="D51" s="14" t="inlineStr"/>
+      <c r="E51" s="14" t="inlineStr"/>
+      <c r="F51" s="14" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="11" t="n">
+      <c r="A52" s="12" t="n">
         <v>1966</v>
       </c>
-      <c r="B52" s="12" t="inlineStr">
+      <c r="B52" s="13" t="inlineStr">
         <is>
           <t>Miami, FL; Missing</t>
         </is>
       </c>
-      <c r="C52" s="13" t="inlineStr"/>
-      <c r="D52" s="13" t="inlineStr"/>
-      <c r="E52" s="13" t="inlineStr"/>
-      <c r="F52" s="13" t="inlineStr"/>
+      <c r="C52" s="14" t="inlineStr"/>
+      <c r="D52" s="14" t="inlineStr"/>
+      <c r="E52" s="14" t="inlineStr"/>
+      <c r="F52" s="14" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="11" t="n">
+      <c r="A53" s="12" t="n">
         <v>1967</v>
       </c>
-      <c r="B53" s="12" t="inlineStr">
+      <c r="B53" s="13" t="inlineStr">
         <is>
           <t>San Francisco, CA; Missing</t>
         </is>
       </c>
-      <c r="C53" s="13" t="inlineStr"/>
-      <c r="D53" s="13" t="inlineStr"/>
-      <c r="E53" s="13" t="inlineStr"/>
-      <c r="F53" s="13" t="inlineStr"/>
+      <c r="C53" s="14" t="inlineStr"/>
+      <c r="D53" s="14" t="inlineStr"/>
+      <c r="E53" s="14" t="inlineStr"/>
+      <c r="F53" s="14" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="11" t="n">
+      <c r="A54" s="12" t="n">
         <v>1968</v>
       </c>
-      <c r="B54" s="12" t="inlineStr">
+      <c r="B54" s="13" t="inlineStr">
         <is>
           <t>Ann Arbor, MI; Missing</t>
         </is>
       </c>
-      <c r="C54" s="13" t="inlineStr"/>
-      <c r="D54" s="13" t="inlineStr"/>
-      <c r="E54" s="13" t="inlineStr"/>
-      <c r="F54" s="13" t="inlineStr"/>
+      <c r="C54" s="14" t="inlineStr"/>
+      <c r="D54" s="14" t="inlineStr"/>
+      <c r="E54" s="14" t="inlineStr"/>
+      <c r="F54" s="14" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="11" t="n">
+      <c r="A55" s="12" t="n">
         <v>1969</v>
       </c>
-      <c r="B55" s="12" t="inlineStr">
+      <c r="B55" s="13" t="inlineStr">
         <is>
           <t>New York, NY; Missing</t>
         </is>
       </c>
-      <c r="C55" s="13" t="inlineStr"/>
-      <c r="D55" s="13" t="inlineStr"/>
-      <c r="E55" s="13" t="inlineStr"/>
-      <c r="F55" s="13" t="inlineStr"/>
+      <c r="C55" s="14" t="inlineStr"/>
+      <c r="D55" s="14" t="inlineStr"/>
+      <c r="E55" s="14" t="inlineStr"/>
+      <c r="F55" s="14" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="11" t="n">
+      <c r="A56" s="12" t="n">
         <v>1970</v>
       </c>
-      <c r="B56" s="12" t="inlineStr">
+      <c r="B56" s="13" t="inlineStr">
         <is>
           <t>New Orleans, LA; Missing</t>
         </is>
       </c>
-      <c r="C56" s="13" t="inlineStr"/>
-      <c r="D56" s="13" t="inlineStr"/>
-      <c r="E56" s="13" t="inlineStr"/>
-      <c r="F56" s="13" t="inlineStr"/>
+      <c r="C56" s="14" t="inlineStr"/>
+      <c r="D56" s="14" t="inlineStr"/>
+      <c r="E56" s="14" t="inlineStr"/>
+      <c r="F56" s="14" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="11" t="n">
+      <c r="A57" s="12" t="n">
         <v>1971</v>
       </c>
-      <c r="B57" s="12" t="inlineStr">
+      <c r="B57" s="13" t="inlineStr">
         <is>
           <t>Los Angeles, CA; Missing</t>
         </is>
       </c>
-      <c r="C57" s="13" t="inlineStr"/>
-      <c r="D57" s="13" t="inlineStr"/>
-      <c r="E57" s="13" t="inlineStr"/>
-      <c r="F57" s="13" t="inlineStr"/>
+      <c r="C57" s="14" t="inlineStr"/>
+      <c r="D57" s="14" t="inlineStr"/>
+      <c r="E57" s="14" t="inlineStr"/>
+      <c r="F57" s="14" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="11" t="n">
+      <c r="A58" s="12" t="n">
         <v>1972</v>
       </c>
-      <c r="B58" s="12" t="inlineStr">
+      <c r="B58" s="13" t="inlineStr">
         <is>
           <t>Boston, MA; Missing</t>
         </is>
       </c>
-      <c r="C58" s="13" t="inlineStr"/>
-      <c r="D58" s="13" t="inlineStr"/>
-      <c r="E58" s="13" t="inlineStr"/>
-      <c r="F58" s="13" t="inlineStr"/>
+      <c r="C58" s="14" t="inlineStr"/>
+      <c r="D58" s="14" t="inlineStr"/>
+      <c r="E58" s="14" t="inlineStr"/>
+      <c r="F58" s="14" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="11" t="n">
+      <c r="A59" s="12" t="n">
         <v>1973</v>
       </c>
-      <c r="B59" s="12" t="inlineStr">
+      <c r="B59" s="13" t="inlineStr">
         <is>
           <t>San Jose, Costa Rica; Missing</t>
         </is>
       </c>
-      <c r="C59" s="13" t="inlineStr"/>
-      <c r="D59" s="13" t="inlineStr"/>
-      <c r="E59" s="13" t="inlineStr"/>
-      <c r="F59" s="13" t="inlineStr"/>
+      <c r="C59" s="14" t="inlineStr"/>
+      <c r="D59" s="14" t="inlineStr"/>
+      <c r="E59" s="14" t="inlineStr"/>
+      <c r="F59" s="14" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="11" t="n">
+      <c r="A60" s="12" t="n">
         <v>1974</v>
       </c>
-      <c r="B60" s="12" t="inlineStr">
+      <c r="B60" s="13" t="inlineStr">
         <is>
           <t>Ottawa, ON; Missing</t>
         </is>
       </c>
-      <c r="C60" s="13" t="inlineStr"/>
-      <c r="D60" s="13" t="inlineStr"/>
-      <c r="E60" s="13" t="inlineStr"/>
-      <c r="F60" s="13" t="inlineStr"/>
+      <c r="C60" s="14" t="inlineStr"/>
+      <c r="D60" s="14" t="inlineStr"/>
+      <c r="E60" s="14" t="inlineStr"/>
+      <c r="F60" s="14" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="11" t="n">
+      <c r="A61" s="12" t="n">
         <v>1975</v>
       </c>
-      <c r="B61" s="12" t="inlineStr">
+      <c r="B61" s="13" t="inlineStr">
         <is>
           <t>Williamsburg, VA; Missing</t>
         </is>
       </c>
-      <c r="C61" s="13" t="inlineStr"/>
-      <c r="D61" s="13" t="inlineStr"/>
-      <c r="E61" s="13" t="inlineStr"/>
-      <c r="F61" s="13" t="inlineStr"/>
+      <c r="C61" s="14" t="inlineStr"/>
+      <c r="D61" s="14" t="inlineStr"/>
+      <c r="E61" s="14" t="inlineStr"/>
+      <c r="F61" s="14" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="11" t="n">
+      <c r="A62" s="12" t="n">
         <v>1976</v>
       </c>
-      <c r="B62" s="12" t="inlineStr">
+      <c r="B62" s="13" t="inlineStr">
         <is>
           <t>Fairbanks, AK; Missing</t>
         </is>
       </c>
-      <c r="C62" s="13" t="inlineStr"/>
-      <c r="D62" s="13" t="inlineStr"/>
-      <c r="E62" s="13" t="inlineStr"/>
-      <c r="F62" s="13" t="inlineStr"/>
+      <c r="C62" s="14" t="inlineStr"/>
+      <c r="D62" s="14" t="inlineStr"/>
+      <c r="E62" s="14" t="inlineStr"/>
+      <c r="F62" s="14" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="11" t="n">
+      <c r="A63" s="12" t="n">
         <v>1977</v>
       </c>
-      <c r="B63" s="12" t="inlineStr">
+      <c r="B63" s="13" t="inlineStr">
         <is>
           <t>Gainesville, FL; Missing</t>
         </is>
       </c>
-      <c r="C63" s="13" t="inlineStr"/>
-      <c r="D63" s="13" t="inlineStr"/>
-      <c r="E63" s="13" t="inlineStr"/>
-      <c r="F63" s="13" t="inlineStr"/>
+      <c r="C63" s="14" t="inlineStr"/>
+      <c r="D63" s="14" t="inlineStr"/>
+      <c r="E63" s="14" t="inlineStr"/>
+      <c r="F63" s="14" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="11" t="n">
+      <c r="A64" s="12" t="n">
         <v>1978</v>
       </c>
-      <c r="B64" s="12" t="inlineStr">
+      <c r="B64" s="13" t="inlineStr">
         <is>
           <t>Tempe, AZ; Missing</t>
         </is>
       </c>
-      <c r="C64" s="13" t="inlineStr"/>
-      <c r="D64" s="13" t="inlineStr"/>
-      <c r="E64" s="13" t="inlineStr"/>
-      <c r="F64" s="13" t="inlineStr"/>
+      <c r="C64" s="14" t="inlineStr"/>
+      <c r="D64" s="14" t="inlineStr"/>
+      <c r="E64" s="14" t="inlineStr"/>
+      <c r="F64" s="14" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="11" t="n">
+      <c r="A65" s="12" t="n">
         <v>1979</v>
       </c>
-      <c r="B65" s="12" t="inlineStr">
+      <c r="B65" s="13" t="inlineStr">
         <is>
           <t>Orono, ME; Missing</t>
         </is>
       </c>
-      <c r="C65" s="13" t="inlineStr"/>
-      <c r="D65" s="13" t="inlineStr"/>
-      <c r="E65" s="13" t="inlineStr"/>
-      <c r="F65" s="13" t="inlineStr"/>
+      <c r="C65" s="14" t="inlineStr"/>
+      <c r="D65" s="14" t="inlineStr"/>
+      <c r="E65" s="14" t="inlineStr"/>
+      <c r="F65" s="14" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="11" t="n">
+      <c r="A66" s="12" t="n">
         <v>1980</v>
       </c>
-      <c r="B66" s="12" t="inlineStr">
+      <c r="B66" s="13" t="inlineStr">
         <is>
           <t>Fort Worth, TX; Missing</t>
         </is>
       </c>
-      <c r="C66" s="13" t="inlineStr"/>
-      <c r="D66" s="13" t="inlineStr"/>
-      <c r="E66" s="13" t="inlineStr"/>
-      <c r="F66" s="13" t="inlineStr"/>
+      <c r="C66" s="14" t="inlineStr"/>
+      <c r="D66" s="14" t="inlineStr"/>
+      <c r="E66" s="14" t="inlineStr"/>
+      <c r="F66" s="14" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="11" t="n">
+      <c r="A67" s="12" t="n">
         <v>1981</v>
       </c>
-      <c r="B67" s="12" t="inlineStr">
+      <c r="B67" s="13" t="inlineStr">
         <is>
           <t>Corvallis, OR; Missing</t>
         </is>
       </c>
-      <c r="C67" s="13" t="inlineStr"/>
-      <c r="D67" s="13" t="inlineStr"/>
-      <c r="E67" s="13" t="inlineStr"/>
-      <c r="F67" s="13" t="inlineStr"/>
+      <c r="C67" s="14" t="inlineStr"/>
+      <c r="D67" s="14" t="inlineStr"/>
+      <c r="E67" s="14" t="inlineStr"/>
+      <c r="F67" s="14" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="11" t="n">
+      <c r="A68" s="12" t="n">
         <v>1982</v>
       </c>
-      <c r="B68" s="12" t="inlineStr">
+      <c r="B68" s="13" t="inlineStr">
         <is>
           <t>DeKalb, IL; Missing</t>
         </is>
       </c>
-      <c r="C68" s="13" t="inlineStr"/>
-      <c r="D68" s="13" t="inlineStr"/>
-      <c r="E68" s="13" t="inlineStr"/>
-      <c r="F68" s="13" t="inlineStr"/>
+      <c r="C68" s="14" t="inlineStr"/>
+      <c r="D68" s="14" t="inlineStr"/>
+      <c r="E68" s="14" t="inlineStr"/>
+      <c r="F68" s="14" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="11" t="n">
+      <c r="A69" s="12" t="n">
         <v>1983</v>
       </c>
-      <c r="B69" s="12" t="inlineStr">
+      <c r="B69" s="13" t="inlineStr">
         <is>
           <t>Tallahasee, FL; Missing</t>
         </is>
       </c>
-      <c r="C69" s="12" t="inlineStr">
+      <c r="C69" s="13" t="inlineStr">
         <is>
           <t>Tallahasee, FL; Missing</t>
         </is>
       </c>
-      <c r="D69" s="13" t="inlineStr"/>
-      <c r="E69" s="13" t="inlineStr"/>
-      <c r="F69" s="13" t="inlineStr"/>
+      <c r="D69" s="14" t="inlineStr"/>
+      <c r="E69" s="14" t="inlineStr"/>
+      <c r="F69" s="14" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="11" t="n">
+      <c r="A70" s="12" t="n">
         <v>1984</v>
       </c>
-      <c r="B70" s="12" t="inlineStr">
+      <c r="B70" s="13" t="inlineStr">
         <is>
           <t>Norman, OK; Missing</t>
         </is>
       </c>
-      <c r="C70" s="12" t="inlineStr">
+      <c r="C70" s="13" t="inlineStr">
         <is>
           <t>Norman, OK; Missing</t>
         </is>
       </c>
-      <c r="D70" s="13" t="inlineStr"/>
-      <c r="E70" s="13" t="inlineStr"/>
-      <c r="F70" s="13" t="inlineStr"/>
+      <c r="D70" s="14" t="inlineStr"/>
+      <c r="E70" s="14" t="inlineStr"/>
+      <c r="F70" s="14" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="11" t="n">
+      <c r="A71" s="12" t="n">
         <v>1985</v>
       </c>
-      <c r="B71" s="12" t="inlineStr">
+      <c r="B71" s="13" t="inlineStr">
         <is>
           <t>Knoxville, TN; Missing</t>
         </is>
       </c>
-      <c r="C71" s="14" t="inlineStr">
+      <c r="C71" s="15" t="inlineStr">
         <is>
           <t>Knoxville, TN (26); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D71" s="13" t="inlineStr"/>
-      <c r="E71" s="13" t="inlineStr"/>
-      <c r="F71" s="13" t="inlineStr"/>
+      <c r="D71" s="14" t="inlineStr"/>
+      <c r="E71" s="14" t="inlineStr"/>
+      <c r="F71" s="14" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="11" t="n">
+      <c r="A72" s="12" t="n">
         <v>1986</v>
       </c>
-      <c r="B72" s="12" t="inlineStr">
+      <c r="B72" s="13" t="inlineStr">
         <is>
           <t>Victoria, BC; Missing</t>
         </is>
       </c>
-      <c r="C72" s="14" t="inlineStr">
+      <c r="C72" s="15" t="inlineStr">
         <is>
           <t>Victoria, BC (35); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D72" s="13" t="inlineStr"/>
-      <c r="E72" s="13" t="inlineStr"/>
-      <c r="F72" s="13" t="inlineStr"/>
+      <c r="D72" s="14" t="inlineStr"/>
+      <c r="E72" s="14" t="inlineStr"/>
+      <c r="F72" s="14" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="11" t="n">
+      <c r="A73" s="12" t="n">
         <v>1987</v>
       </c>
-      <c r="B73" s="12" t="inlineStr">
+      <c r="B73" s="13" t="inlineStr">
         <is>
           <t>Albany, NY; Missing</t>
         </is>
       </c>
-      <c r="C73" s="14" t="inlineStr">
+      <c r="C73" s="15" t="inlineStr">
         <is>
           <t>Albany, NY (33); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D73" s="13" t="inlineStr"/>
-      <c r="E73" s="13" t="inlineStr"/>
-      <c r="F73" s="13" t="inlineStr"/>
+      <c r="D73" s="14" t="inlineStr"/>
+      <c r="E73" s="14" t="inlineStr"/>
+      <c r="F73" s="14" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="11" t="n">
+      <c r="A74" s="12" t="n">
         <v>1988</v>
       </c>
-      <c r="B74" s="12" t="inlineStr">
+      <c r="B74" s="13" t="inlineStr">
         <is>
           <t>Ann Arbor, MI; Missing</t>
         </is>
       </c>
-      <c r="C74" s="14" t="inlineStr">
+      <c r="C74" s="15" t="inlineStr">
         <is>
           <t>Ann Arbor, MI (34); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D74" s="13" t="inlineStr"/>
-      <c r="E74" s="13" t="inlineStr"/>
-      <c r="F74" s="13" t="inlineStr"/>
+      <c r="D74" s="14" t="inlineStr"/>
+      <c r="E74" s="14" t="inlineStr"/>
+      <c r="F74" s="14" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="11" t="n">
+      <c r="A75" s="12" t="n">
         <v>1989</v>
       </c>
-      <c r="B75" s="12" t="inlineStr">
+      <c r="B75" s="13" t="inlineStr">
         <is>
           <t>San Francisco, CA; Missing</t>
         </is>
       </c>
-      <c r="C75" s="14" t="inlineStr">
+      <c r="C75" s="15" t="inlineStr">
         <is>
           <t>San Francisco, CA (63); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D75" s="13" t="inlineStr"/>
-      <c r="E75" s="13" t="inlineStr"/>
-      <c r="F75" s="13" t="inlineStr"/>
+      <c r="D75" s="14" t="inlineStr"/>
+      <c r="E75" s="14" t="inlineStr"/>
+      <c r="F75" s="14" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="11" t="n">
+      <c r="A76" s="12" t="n">
         <v>1990</v>
       </c>
-      <c r="B76" s="12" t="inlineStr">
+      <c r="B76" s="13" t="inlineStr">
         <is>
           <t>Charleston, SC; Missing</t>
         </is>
       </c>
-      <c r="C76" s="14" t="inlineStr">
+      <c r="C76" s="15" t="inlineStr">
         <is>
           <t>Charleston, SC (47); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D76" s="13" t="inlineStr"/>
-      <c r="E76" s="13" t="inlineStr"/>
-      <c r="F76" s="13" t="inlineStr"/>
+      <c r="D76" s="14" t="inlineStr"/>
+      <c r="E76" s="14" t="inlineStr"/>
+      <c r="F76" s="14" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="11" t="n">
+      <c r="A77" s="12" t="n">
         <v>1991</v>
       </c>
-      <c r="B77" s="12" t="inlineStr">
+      <c r="B77" s="13" t="inlineStr">
         <is>
           <t>New York, NY; Missing</t>
         </is>
       </c>
-      <c r="C77" s="14" t="inlineStr">
+      <c r="C77" s="15" t="inlineStr">
         <is>
           <t>New York, NY (34); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D77" s="13" t="inlineStr"/>
-      <c r="E77" s="13" t="inlineStr"/>
-      <c r="F77" s="13" t="inlineStr"/>
+      <c r="D77" s="14" t="inlineStr"/>
+      <c r="E77" s="14" t="inlineStr"/>
+      <c r="F77" s="14" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="11" t="n">
+      <c r="A78" s="12" t="n">
         <v>1992</v>
       </c>
-      <c r="B78" s="15" t="inlineStr">
+      <c r="B78" s="16" t="inlineStr">
         <is>
           <t>Champaign-Urbana, IL; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C78" s="14" t="inlineStr">
+      <c r="C78" s="15" t="inlineStr">
         <is>
           <t>Champaign-Urbana, IL (41); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D78" s="13" t="inlineStr"/>
-      <c r="E78" s="13" t="inlineStr"/>
-      <c r="F78" s="13" t="inlineStr"/>
+      <c r="D78" s="14" t="inlineStr"/>
+      <c r="E78" s="14" t="inlineStr"/>
+      <c r="F78" s="14" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="11" t="n">
+      <c r="A79" s="12" t="n">
         <v>1993</v>
       </c>
-      <c r="B79" s="15" t="inlineStr">
+      <c r="B79" s="16" t="inlineStr">
         <is>
           <t>Austin, TX; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C79" s="14" t="inlineStr">
+      <c r="C79" s="15" t="inlineStr">
         <is>
           <t>Austin, TX (45); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D79" s="13" t="inlineStr"/>
-      <c r="E79" s="13" t="inlineStr"/>
-      <c r="F79" s="13" t="inlineStr"/>
+      <c r="D79" s="14" t="inlineStr"/>
+      <c r="E79" s="14" t="inlineStr"/>
+      <c r="F79" s="14" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="11" t="n">
+      <c r="A80" s="12" t="n">
         <v>1994</v>
       </c>
-      <c r="B80" s="15" t="inlineStr">
+      <c r="B80" s="16" t="inlineStr">
         <is>
           <t>Los Angeles, CA; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C80" s="14" t="inlineStr">
+      <c r="C80" s="15" t="inlineStr">
         <is>
           <t>Los Angeles, CA (50); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D80" s="13" t="inlineStr"/>
-      <c r="E80" s="13" t="inlineStr"/>
-      <c r="F80" s="13" t="inlineStr"/>
+      <c r="D80" s="14" t="inlineStr"/>
+      <c r="E80" s="14" t="inlineStr"/>
+      <c r="F80" s="14" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="11" t="n">
+      <c r="A81" s="12" t="n">
         <v>1995</v>
       </c>
-      <c r="B81" s="15" t="inlineStr">
+      <c r="B81" s="16" t="inlineStr">
         <is>
           <t>Edmonton, AB; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C81" s="14" t="inlineStr">
+      <c r="C81" s="15" t="inlineStr">
         <is>
           <t>Edmonton, AB (46); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D81" s="13" t="inlineStr"/>
-      <c r="E81" s="13" t="inlineStr"/>
-      <c r="F81" s="13" t="inlineStr"/>
+      <c r="D81" s="14" t="inlineStr"/>
+      <c r="E81" s="14" t="inlineStr"/>
+      <c r="F81" s="14" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="11" t="n">
+      <c r="A82" s="12" t="n">
         <v>1996</v>
       </c>
-      <c r="B82" s="15" t="inlineStr">
+      <c r="B82" s="16" t="inlineStr">
         <is>
           <t>New Orleans, LA; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C82" s="14" t="inlineStr">
+      <c r="C82" s="15" t="inlineStr">
         <is>
           <t>New Orleans, LA (98); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D82" s="13" t="inlineStr"/>
-      <c r="E82" s="13" t="inlineStr"/>
-      <c r="F82" s="13" t="inlineStr"/>
+      <c r="D82" s="14" t="inlineStr"/>
+      <c r="E82" s="14" t="inlineStr"/>
+      <c r="F82" s="14" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="11" t="n">
+      <c r="A83" s="12" t="n">
         <v>1997</v>
       </c>
-      <c r="B83" s="16" t="inlineStr">
+      <c r="B83" s="17" t="inlineStr">
         <is>
           <t>Seattle, WA; OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
         </is>
       </c>
-      <c r="C83" s="14" t="inlineStr">
+      <c r="C83" s="15" t="inlineStr">
         <is>
           <t>Seattle, WA (68); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D83" s="12" t="inlineStr">
+      <c r="D83" s="13" t="inlineStr">
         <is>
           <t>?; Missing — 1st EEA; no known abstract source; host city also unknown</t>
         </is>
       </c>
-      <c r="E83" s="13" t="inlineStr"/>
-      <c r="F83" s="13" t="inlineStr"/>
+      <c r="E83" s="14" t="inlineStr"/>
+      <c r="F83" s="14" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="11" t="n">
+      <c r="A84" s="12" t="n">
         <v>1998</v>
       </c>
-      <c r="B84" s="16" t="inlineStr">
+      <c r="B84" s="17" t="inlineStr">
         <is>
           <t>Guelph, ON; OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
         </is>
       </c>
-      <c r="C84" s="14" t="inlineStr">
+      <c r="C84" s="15" t="inlineStr">
         <is>
           <t>Guelph, ON (63); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D84" s="12" t="inlineStr">
+      <c r="D84" s="13" t="inlineStr">
         <is>
           <t>Lisbon; Missing — 2nd EEA; no known abstract source</t>
         </is>
       </c>
-      <c r="E84" s="13" t="inlineStr"/>
-      <c r="F84" s="13" t="inlineStr"/>
+      <c r="E84" s="14" t="inlineStr"/>
+      <c r="F84" s="14" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="11" t="n">
+      <c r="A85" s="12" t="n">
         <v>1999</v>
       </c>
-      <c r="B85" s="16" t="inlineStr">
+      <c r="B85" s="17" t="inlineStr">
         <is>
           <t>University Park, PA; OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
         </is>
       </c>
-      <c r="C85" s="14" t="inlineStr">
+      <c r="C85" s="15" t="inlineStr">
         <is>
           <t>University Park, PA (78); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D85" s="12" t="inlineStr">
+      <c r="D85" s="13" t="inlineStr">
         <is>
           <t>?; Missing — 3rd EEA; no known abstract source; host city also unknown</t>
         </is>
       </c>
-      <c r="E85" s="13" t="inlineStr"/>
-      <c r="F85" s="13" t="inlineStr"/>
+      <c r="E85" s="14" t="inlineStr"/>
+      <c r="F85" s="14" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="11" t="n">
+      <c r="A86" s="12" t="n">
         <v>2000</v>
       </c>
-      <c r="B86" s="16" t="inlineStr">
+      <c r="B86" s="17" t="inlineStr">
         <is>
           <t>La Paz, Mexico; OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
         </is>
       </c>
-      <c r="C86" s="14" t="inlineStr">
+      <c r="C86" s="15" t="inlineStr">
         <is>
           <t>La Paz, Mexico (134); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D86" s="12" t="inlineStr">
+      <c r="D86" s="13" t="inlineStr">
         <is>
           <t>?; Missing — 4th EEA; no known abstract source; host city also unknown</t>
         </is>
       </c>
-      <c r="E86" s="13" t="inlineStr"/>
-      <c r="F86" s="13" t="inlineStr"/>
+      <c r="E86" s="14" t="inlineStr"/>
+      <c r="F86" s="14" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="11" t="n">
+      <c r="A87" s="12" t="n">
         <v>2001</v>
       </c>
-      <c r="B87" s="16" t="inlineStr">
+      <c r="B87" s="17" t="inlineStr">
         <is>
           <t>University Park, PA; OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
         </is>
       </c>
-      <c r="C87" s="14" t="inlineStr">
+      <c r="C87" s="15" t="inlineStr">
         <is>
           <t>University Park, PA (84); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D87" s="12" t="inlineStr">
+      <c r="D87" s="13" t="inlineStr">
         <is>
           <t>?; Missing — 5th EEA; no known abstract source; host city also unknown</t>
         </is>
       </c>
-      <c r="E87" s="13" t="inlineStr"/>
-      <c r="F87" s="13" t="inlineStr"/>
+      <c r="E87" s="14" t="inlineStr"/>
+      <c r="F87" s="14" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="11" t="n">
+      <c r="A88" s="12" t="n">
         <v>2002</v>
       </c>
-      <c r="B88" s="15" t="inlineStr">
+      <c r="B88" s="16" t="inlineStr">
         <is>
           <t>Kansas City, MO; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C88" s="14" t="inlineStr">
+      <c r="C88" s="15" t="inlineStr">
         <is>
           <t>Kansas City, MO (27); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D88" s="17" t="inlineStr">
+      <c r="D88" s="18" t="inlineStr">
         <is>
           <t>Cardiff; Digital — abstract booklet (Word) found by Ali Hood 2026-08-27; queued for extraction</t>
         </is>
       </c>
-      <c r="E88" s="13" t="inlineStr"/>
-      <c r="F88" s="13" t="inlineStr"/>
+      <c r="E88" s="14" t="inlineStr"/>
+      <c r="F88" s="14" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="11" t="n">
+      <c r="A89" s="12" t="n">
         <v>2003</v>
       </c>
-      <c r="B89" s="16" t="inlineStr">
+      <c r="B89" s="17" t="inlineStr">
         <is>
           <t>Manaus, Brazil; OCR — degraded phone scan — 0 abstracts recovered — flatbed re-scan needed (Carylanne)</t>
         </is>
       </c>
-      <c r="C89" s="14" t="inlineStr">
+      <c r="C89" s="15" t="inlineStr">
         <is>
           <t>Manaus, Brazil (82); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D89" s="18" t="inlineStr">
+      <c r="D89" s="19" t="inlineStr">
         <is>
           <t>San Marino; Pending — 7th EEA; Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
-      <c r="E89" s="13" t="inlineStr"/>
-      <c r="F89" s="13" t="inlineStr"/>
+      <c r="E89" s="14" t="inlineStr"/>
+      <c r="F89" s="14" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="11" t="n">
+      <c r="A90" s="12" t="n">
         <v>2004</v>
       </c>
-      <c r="B90" s="16" t="inlineStr">
+      <c r="B90" s="17" t="inlineStr">
         <is>
           <t>Norman, OK; OCR — degraded phone scan — 0 abstracts recovered — flatbed re-scan needed (Carylanne)</t>
         </is>
       </c>
-      <c r="C90" s="14" t="inlineStr">
+      <c r="C90" s="15" t="inlineStr">
         <is>
           <t>Norman, OK (59); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D90" s="14" t="inlineStr">
+      <c r="D90" s="15" t="inlineStr">
         <is>
           <t>London; Ingested — 55 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E90" s="13" t="inlineStr"/>
-      <c r="F90" s="13" t="inlineStr"/>
+      <c r="E90" s="14" t="inlineStr"/>
+      <c r="F90" s="14" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="11" t="n">
+      <c r="A91" s="12" t="n">
         <v>2005</v>
       </c>
-      <c r="B91" s="14" t="inlineStr">
+      <c r="B91" s="15" t="inlineStr">
         <is>
           <t>Tampa, FL; Ingested</t>
         </is>
       </c>
-      <c r="C91" s="14" t="inlineStr">
+      <c r="C91" s="15" t="inlineStr">
         <is>
           <t>Tampa, FL (158); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D91" s="18" t="inlineStr">
+      <c r="D91" s="19" t="inlineStr">
         <is>
           <t>Monaco; Pending — 9th EEA; Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
-      <c r="E91" s="13" t="inlineStr"/>
-      <c r="F91" s="13" t="inlineStr"/>
+      <c r="E91" s="14" t="inlineStr"/>
+      <c r="F91" s="14" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="11" t="n">
+      <c r="A92" s="12" t="n">
         <v>2006</v>
       </c>
-      <c r="B92" s="15" t="inlineStr">
+      <c r="B92" s="16" t="inlineStr">
         <is>
           <t>New Orleans, LA; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C92" s="15" t="inlineStr">
+      <c r="C92" s="16" t="inlineStr">
         <is>
           <t>New Orleans, LA; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="D92" s="18" t="inlineStr">
+      <c r="D92" s="19" t="inlineStr">
         <is>
           <t>Hamburg; Pending — 10th EEA; Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
-      <c r="E92" s="13" t="inlineStr"/>
-      <c r="F92" s="13" t="inlineStr"/>
+      <c r="E92" s="14" t="inlineStr"/>
+      <c r="F92" s="14" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="11" t="n">
+      <c r="A93" s="12" t="n">
         <v>2007</v>
       </c>
-      <c r="B93" s="14" t="inlineStr">
-        <is>
-          <t>St. Louis, MO; Ingested</t>
-        </is>
-      </c>
-      <c r="C93" s="14" t="inlineStr">
-        <is>
-          <t>St. Louis, MO (155); Ingested</t>
-        </is>
-      </c>
-      <c r="D93" s="18" t="inlineStr">
+      <c r="B93" s="20" t="inlineStr">
+        <is>
+          <t>St. Louis, MO; Extracted — regex-parsed; Fable re-extraction part-done (229 so far)</t>
+        </is>
+      </c>
+      <c r="C93" s="20" t="inlineStr">
+        <is>
+          <t>St. Louis, MO (155); Extracted — regex-parsed; Fable re-extraction part-done (229 so far)</t>
+        </is>
+      </c>
+      <c r="D93" s="19" t="inlineStr">
         <is>
           <t>Brest; Pending — 11th EEA; Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
-      <c r="E93" s="13" t="inlineStr"/>
-      <c r="F93" s="13" t="inlineStr"/>
+      <c r="E93" s="14" t="inlineStr"/>
+      <c r="F93" s="14" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="11" t="n">
+      <c r="A94" s="12" t="n">
         <v>2008</v>
       </c>
-      <c r="B94" s="14" t="inlineStr">
-        <is>
-          <t>Montreal, PQ; Ingested</t>
-        </is>
-      </c>
-      <c r="C94" s="14" t="inlineStr">
-        <is>
-          <t>Montreal, PQ (193); Ingested</t>
-        </is>
-      </c>
-      <c r="D94" s="18" t="inlineStr">
+      <c r="B94" s="20" t="inlineStr">
+        <is>
+          <t>Montreal, PQ; Extracted — regex-parsed; Fable re-extraction part-done (684 so far)</t>
+        </is>
+      </c>
+      <c r="C94" s="20" t="inlineStr">
+        <is>
+          <t>Montreal, PQ (193); Extracted — regex-parsed; Fable re-extraction part-done (684 so far)</t>
+        </is>
+      </c>
+      <c r="D94" s="19" t="inlineStr">
         <is>
           <t>Lisbon; Pending — 12th EEA; Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
-      <c r="E94" s="13" t="inlineStr"/>
-      <c r="F94" s="13" t="inlineStr"/>
+      <c r="E94" s="14" t="inlineStr"/>
+      <c r="F94" s="14" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="11" t="n">
+      <c r="A95" s="12" t="n">
         <v>2009</v>
       </c>
-      <c r="B95" s="14" t="inlineStr">
-        <is>
-          <t>Portland, OR; Ingested</t>
-        </is>
-      </c>
-      <c r="C95" s="14" t="inlineStr">
-        <is>
-          <t>Portland, OR (149); Ingested</t>
-        </is>
-      </c>
-      <c r="D95" s="18" t="inlineStr">
+      <c r="B95" s="20" t="inlineStr">
+        <is>
+          <t>Portland, OR; Extracted — regex-parsed; Fable re-extraction queued</t>
+        </is>
+      </c>
+      <c r="C95" s="20" t="inlineStr">
+        <is>
+          <t>Portland, OR (149); Extracted — regex-parsed; Fable re-extraction queued</t>
+        </is>
+      </c>
+      <c r="D95" s="19" t="inlineStr">
         <is>
           <t>Palma de Majorca; Pending — 13th EEA; Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
-      <c r="E95" s="13" t="inlineStr"/>
-      <c r="F95" s="13" t="inlineStr"/>
+      <c r="E95" s="14" t="inlineStr"/>
+      <c r="F95" s="14" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="11" t="n">
+      <c r="A96" s="12" t="n">
         <v>2010</v>
       </c>
-      <c r="B96" s="15" t="inlineStr">
+      <c r="B96" s="16" t="inlineStr">
         <is>
           <t>Providence, RI; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C96" s="15" t="inlineStr">
+      <c r="C96" s="16" t="inlineStr">
         <is>
           <t>Providence, RI; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="D96" s="15" t="inlineStr">
+      <c r="D96" s="16" t="inlineStr">
         <is>
           <t>Galway; Hardcopy — Cat holds a hardcopy but has no scanning capacity; digital copy needed from IEG (Ireland)</t>
         </is>
       </c>
-      <c r="E96" s="13" t="inlineStr"/>
-      <c r="F96" s="12" t="inlineStr">
+      <c r="E96" s="14" t="inlineStr"/>
+      <c r="F96" s="13" t="inlineStr">
         <is>
           <t>Cairns; Missing — find source</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="11" t="n">
+      <c r="A97" s="12" t="n">
         <v>2011</v>
       </c>
-      <c r="B97" s="15" t="inlineStr">
+      <c r="B97" s="16" t="inlineStr">
         <is>
           <t>Minneapolis, MN; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C97" s="15" t="inlineStr">
+      <c r="C97" s="16" t="inlineStr">
         <is>
           <t>Minneapolis, MN; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="D97" s="14" t="inlineStr">
+      <c r="D97" s="15" t="inlineStr">
         <is>
           <t>Berlin; Ingested — 58 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E97" s="13" t="inlineStr"/>
-      <c r="F97" s="13" t="inlineStr"/>
+      <c r="E97" s="14" t="inlineStr"/>
+      <c r="F97" s="14" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="11" t="n">
+      <c r="A98" s="12" t="n">
         <v>2012</v>
       </c>
-      <c r="B98" s="14" t="inlineStr">
-        <is>
-          <t>Vancouver, BC; Ingested</t>
-        </is>
-      </c>
-      <c r="C98" s="14" t="inlineStr">
-        <is>
-          <t>Vancouver, BC (65); Ingested</t>
-        </is>
-      </c>
-      <c r="D98" s="15" t="inlineStr">
+      <c r="B98" s="20" t="inlineStr">
+        <is>
+          <t>Vancouver, BC; Extracted — regex-parsed; Fable re-extraction queued</t>
+        </is>
+      </c>
+      <c r="C98" s="20" t="inlineStr">
+        <is>
+          <t>Vancouver, BC (65); Extracted — regex-parsed; Fable re-extraction queued</t>
+        </is>
+      </c>
+      <c r="D98" s="16" t="inlineStr">
         <is>
           <t>Milan; Hardcopy — Cat holds a hardcopy but has no scanning capacity; digital copy needed from GRIS (Italy)</t>
         </is>
       </c>
-      <c r="E98" s="18" t="inlineStr">
+      <c r="E98" s="19" t="inlineStr">
         <is>
           <t>Adelaide; Pending — joint with ASFB; Brit Finucci confirming</t>
         </is>
       </c>
-      <c r="F98" s="13" t="inlineStr"/>
+      <c r="F98" s="14" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="11" t="n">
+      <c r="A99" s="12" t="n">
         <v>2013</v>
       </c>
-      <c r="B99" s="15" t="inlineStr">
+      <c r="B99" s="16" t="inlineStr">
         <is>
           <t>Albuquerque, NM; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C99" s="15" t="inlineStr">
+      <c r="C99" s="16" t="inlineStr">
         <is>
           <t>Albuquerque, NM; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="D99" s="14" t="inlineStr">
+      <c r="D99" s="15" t="inlineStr">
         <is>
           <t>Plymouth; Ingested — 93 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E99" s="13" t="inlineStr"/>
-      <c r="F99" s="13" t="inlineStr"/>
+      <c r="E99" s="14" t="inlineStr"/>
+      <c r="F99" s="14" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="11" t="n">
+      <c r="A100" s="12" t="n">
         <v>2014</v>
       </c>
-      <c r="B100" s="15" t="inlineStr">
+      <c r="B100" s="16" t="inlineStr">
         <is>
           <t>Chattanooga, TN; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C100" s="15" t="inlineStr">
+      <c r="C100" s="16" t="inlineStr">
         <is>
           <t>Chattanooga, TN; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="D100" s="14" t="inlineStr">
+      <c r="D100" s="15" t="inlineStr">
         <is>
           <t>Leeuwarden; Ingested — 61 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E100" s="18" t="inlineStr">
+      <c r="E100" s="19" t="inlineStr">
         <is>
           <t>?; Pending — Brit Finucci collating; year/location to confirm</t>
         </is>
       </c>
-      <c r="F100" s="12" t="inlineStr">
+      <c r="F100" s="13" t="inlineStr">
         <is>
           <t>Durban; Missing — find source</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="11" t="n">
+      <c r="A101" s="12" t="n">
         <v>2015</v>
       </c>
-      <c r="B101" s="14" t="inlineStr">
+      <c r="B101" s="15" t="inlineStr">
         <is>
           <t>Reno, NV; Ingested</t>
         </is>
       </c>
-      <c r="C101" s="14" t="inlineStr">
+      <c r="C101" s="15" t="inlineStr">
         <is>
           <t>Reno, NV (128); Ingested</t>
         </is>
       </c>
-      <c r="D101" s="17" t="inlineStr">
+      <c r="D101" s="18" t="inlineStr">
         <is>
           <t>Peniche; Digital — 19th EEA Book of Abstracts (99pp, born-digital) held by Simon all along; queued for extraction</t>
         </is>
       </c>
-      <c r="E101" s="13" t="inlineStr"/>
-      <c r="F101" s="13" t="inlineStr"/>
+      <c r="E101" s="14" t="inlineStr"/>
+      <c r="F101" s="14" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="11" t="n">
+      <c r="A102" s="12" t="n">
         <v>2016</v>
       </c>
-      <c r="B102" s="14" t="inlineStr">
+      <c r="B102" s="15" t="inlineStr">
         <is>
           <t>New Orleans, LA; Ingested</t>
         </is>
       </c>
-      <c r="C102" s="14" t="inlineStr">
+      <c r="C102" s="15" t="inlineStr">
         <is>
           <t>New Orleans, LA (251); Ingested</t>
         </is>
       </c>
-      <c r="D102" s="14" t="inlineStr">
+      <c r="D102" s="15" t="inlineStr">
         <is>
           <t>Bristol; Ingested — 93 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E102" s="18" t="inlineStr">
+      <c r="E102" s="19" t="inlineStr">
         <is>
           <t>?; Pending — Brit Finucci collating; year/location to confirm</t>
         </is>
       </c>
-      <c r="F102" s="13" t="inlineStr"/>
+      <c r="F102" s="14" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="11" t="n">
+      <c r="A103" s="12" t="n">
         <v>2017</v>
       </c>
-      <c r="B103" s="19" t="inlineStr">
+      <c r="B103" s="21" t="inlineStr">
         <is>
           <t>Austin, TX; Programme — grid programme only — abstract book needed (Carylanne)</t>
         </is>
       </c>
-      <c r="C103" s="19" t="inlineStr">
+      <c r="C103" s="21" t="inlineStr">
         <is>
           <t>Austin, TX; Programme — grid programme only — abstract book needed (Carylanne)</t>
         </is>
       </c>
-      <c r="D103" s="20" t="inlineStr">
+      <c r="D103" s="22" t="inlineStr">
         <is>
           <t>Amsterdam; Schedule — 62 talks ingested, NO abstract bodies; Cat holds a hardcopy but has no scanning capacity; abstract book needed from NEV</t>
         </is>
       </c>
-      <c r="E103" s="13" t="inlineStr"/>
-      <c r="F103" s="13" t="inlineStr"/>
+      <c r="E103" s="14" t="inlineStr"/>
+      <c r="F103" s="14" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="11" t="n">
+      <c r="A104" s="12" t="n">
         <v>2018</v>
       </c>
-      <c r="B104" s="15" t="inlineStr">
+      <c r="B104" s="16" t="inlineStr">
         <is>
           <t>Rochester, NY; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C104" s="15" t="inlineStr">
+      <c r="C104" s="16" t="inlineStr">
         <is>
           <t>Rochester, NY; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="D104" s="14" t="inlineStr">
+      <c r="D104" s="15" t="inlineStr">
         <is>
           <t>Peniche; Ingested — 75 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E104" s="18" t="inlineStr">
+      <c r="E104" s="19" t="inlineStr">
         <is>
           <t>North Stradbroke Is.; Pending — Moreton Bay Research Station; Brit Finucci confirming</t>
         </is>
       </c>
-      <c r="F104" s="14" t="inlineStr">
+      <c r="F104" s="15" t="inlineStr">
         <is>
           <t>Joao Pessoa; Ingested</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="11" t="n">
+      <c r="A105" s="12" t="n">
         <v>2019</v>
       </c>
-      <c r="B105" s="19" t="inlineStr">
+      <c r="B105" s="21" t="inlineStr">
         <is>
           <t>Snowbird, UT; Programme — grid programme only — abstract book needed (Carylanne)</t>
         </is>
       </c>
-      <c r="C105" s="19" t="inlineStr">
+      <c r="C105" s="21" t="inlineStr">
         <is>
           <t>Snowbird, UT; Programme — grid programme only — abstract book needed (Carylanne)</t>
         </is>
       </c>
-      <c r="D105" s="14" t="inlineStr">
+      <c r="D105" s="15" t="inlineStr">
         <is>
           <t>Rende; Ingested — 136 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E105" s="13" t="inlineStr"/>
-      <c r="F105" s="13" t="inlineStr"/>
+      <c r="E105" s="14" t="inlineStr"/>
+      <c r="F105" s="14" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="11" t="n">
+      <c r="A106" s="12" t="n">
         <v>2020</v>
       </c>
-      <c r="B106" s="15" t="inlineStr">
+      <c r="B106" s="16" t="inlineStr">
         <is>
           <t>?; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C106" s="15" t="inlineStr">
+      <c r="C106" s="16" t="inlineStr">
         <is>
           <t>?; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="D106" s="12" t="inlineStr">
+      <c r="D106" s="13" t="inlineStr">
         <is>
           <t>?; Missing — unknown whether a meeting was held: Cat thinks it was online for covid but was on maternity leave and is unsure; organiser unknown; abstracts unknown</t>
         </is>
       </c>
-      <c r="E106" s="18" t="inlineStr">
+      <c r="E106" s="19" t="inlineStr">
         <is>
           <t>?; Pending — Brit Finucci collating; year/location to confirm</t>
         </is>
       </c>
-      <c r="F106" s="13" t="inlineStr"/>
+      <c r="F106" s="14" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="11" t="n">
+      <c r="A107" s="12" t="n">
         <v>2021</v>
       </c>
-      <c r="B107" s="20" t="inlineStr">
+      <c r="B107" s="22" t="inlineStr">
         <is>
           <t>Phoenix, AZ; Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="C107" s="20" t="inlineStr">
+      <c r="C107" s="22" t="inlineStr">
         <is>
           <t>Phoenix, AZ (46); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="D107" s="19" t="inlineStr">
+      <c r="D107" s="21" t="inlineStr">
         <is>
           <t>Leiden; Programme — programme only; abstract book needed from NEV</t>
         </is>
       </c>
-      <c r="E107" s="13" t="inlineStr"/>
-      <c r="F107" s="13" t="inlineStr"/>
+      <c r="E107" s="14" t="inlineStr"/>
+      <c r="F107" s="14" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="11" t="n">
+      <c r="A108" s="12" t="n">
         <v>2022</v>
       </c>
-      <c r="B108" s="20" t="inlineStr">
+      <c r="B108" s="22" t="inlineStr">
         <is>
           <t>Spokane, WA; Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="C108" s="20" t="inlineStr">
+      <c r="C108" s="22" t="inlineStr">
         <is>
           <t>Spokane, WA (69); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="D108" s="17" t="inlineStr">
+      <c r="D108" s="18" t="inlineStr">
         <is>
           <t>Valencia (=SI2022); Digital — full SI2022 abstract book received 2026-08-27; queued for extraction</t>
         </is>
       </c>
-      <c r="E108" s="18" t="inlineStr">
+      <c r="E108" s="19" t="inlineStr">
         <is>
           <t>?; Pending — Brit Finucci collating; year/location to confirm</t>
         </is>
       </c>
-      <c r="F108" s="17" t="inlineStr">
+      <c r="F108" s="18" t="inlineStr">
         <is>
           <t>Valencia; Digital — full abstract book received 2026-08-27; queued (schedule already ingested)</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="11" t="n">
+      <c r="A109" s="12" t="n">
         <v>2023</v>
       </c>
-      <c r="B109" s="20" t="inlineStr">
+      <c r="B109" s="22" t="inlineStr">
         <is>
           <t>Norfolk, VA; Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="C109" s="20" t="inlineStr">
+      <c r="C109" s="22" t="inlineStr">
         <is>
           <t>Norfolk, VA (87); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="D109" s="14" t="inlineStr">
+      <c r="D109" s="15" t="inlineStr">
         <is>
           <t>Brighton; Ingested — oral 64 + poster 34 = 98 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E109" s="13" t="inlineStr"/>
-      <c r="F109" s="13" t="inlineStr"/>
+      <c r="E109" s="14" t="inlineStr"/>
+      <c r="F109" s="14" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="11" t="n">
+      <c r="A110" s="12" t="n">
         <v>2024</v>
       </c>
-      <c r="B110" s="20" t="inlineStr">
+      <c r="B110" s="22" t="inlineStr">
         <is>
           <t>Pittsburgh, PA; Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="C110" s="20" t="inlineStr">
+      <c r="C110" s="22" t="inlineStr">
         <is>
           <t>Pittsburgh, PA (97); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="D110" s="17" t="inlineStr">
+      <c r="D110" s="18" t="inlineStr">
         <is>
           <t>Thessaloniki; Digital — clean abstract book received from Cat 2026-08-27; queued for extraction</t>
         </is>
       </c>
-      <c r="E110" s="18" t="inlineStr">
+      <c r="E110" s="19" t="inlineStr">
         <is>
           <t>Geelong; Pending — Brit Finucci confirming</t>
         </is>
       </c>
-      <c r="F110" s="13" t="inlineStr"/>
+      <c r="F110" s="14" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="11" t="n">
+      <c r="A111" s="12" t="n">
         <v>2025</v>
       </c>
-      <c r="B111" s="20" t="inlineStr">
+      <c r="B111" s="22" t="inlineStr">
         <is>
           <t>St. Paul, MN; Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="C111" s="20" t="inlineStr">
+      <c r="C111" s="22" t="inlineStr">
         <is>
           <t>St. Paul, MN (68); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="D111" s="19" t="inlineStr">
+      <c r="D111" s="21" t="inlineStr">
         <is>
           <t>Rotterdam; Programme — agenda only; Cat has no abstract book and is unsure one was produced; NEV/Irene to confirm whether it exists</t>
         </is>
       </c>
-      <c r="E111" s="13" t="inlineStr"/>
-      <c r="F111" s="13" t="inlineStr"/>
+      <c r="E111" s="14" t="inlineStr"/>
+      <c r="F111" s="14" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="11" t="n">
+      <c r="A112" s="12" t="n">
         <v>2026</v>
       </c>
-      <c r="B112" s="20" t="inlineStr">
+      <c r="B112" s="22" t="inlineStr">
         <is>
           <t>New Orleans, LA; Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="C112" s="20" t="inlineStr">
+      <c r="C112" s="22" t="inlineStr">
         <is>
           <t>New Orleans, LA (61); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="D112" s="18" t="inlineStr">
+      <c r="D112" s="19" t="inlineStr">
         <is>
           <t>online; Pending — will be digital (Shark Trust hosting)</t>
         </is>
       </c>
-      <c r="E112" s="18" t="inlineStr">
+      <c r="E112" s="19" t="inlineStr">
         <is>
           <t>?; Pending — Brit Finucci collating; year/location to confirm</t>
         </is>
       </c>
-      <c r="F112" s="14" t="inlineStr">
+      <c r="F112" s="15" t="inlineStr">
         <is>
           <t>Colombo; Ingested</t>
         </is>
@@ -3262,7 +3284,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Conference abstract coverage — dashboard</t>
         </is>
@@ -4277,13 +4299,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C43" t="n">
         <v>44</v>
       </c>
       <c r="D43" t="n">
-        <v>61.4</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="44">

--- a/database/conference_coverage_matrix.xlsx
+++ b/database/conference_coverage_matrix.xlsx
@@ -166,10 +166,10 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2690,9 +2690,9 @@
       <c r="A89" s="12" t="n">
         <v>2003</v>
       </c>
-      <c r="B89" s="17" t="inlineStr">
-        <is>
-          <t>Manaus, Brazil; OCR — degraded phone scan — 0 abstracts recovered — flatbed re-scan needed (Carylanne)</t>
+      <c r="B89" s="18" t="inlineStr">
+        <is>
+          <t>Manaus, Brazil; Digital — abstract book held (1 PDF) — extraction pending</t>
         </is>
       </c>
       <c r="C89" s="15" t="inlineStr">
@@ -2712,9 +2712,9 @@
       <c r="A90" s="12" t="n">
         <v>2004</v>
       </c>
-      <c r="B90" s="17" t="inlineStr">
-        <is>
-          <t>Norman, OK; OCR — degraded phone scan — 0 abstracts recovered — flatbed re-scan needed (Carylanne)</t>
+      <c r="B90" s="18" t="inlineStr">
+        <is>
+          <t>Norman, OK; Digital — abstract book held (1 PDF) — extraction pending</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
@@ -2756,14 +2756,14 @@
       <c r="A92" s="12" t="n">
         <v>2006</v>
       </c>
-      <c r="B92" s="16" t="inlineStr">
-        <is>
-          <t>New Orleans, LA; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
-        </is>
-      </c>
-      <c r="C92" s="16" t="inlineStr">
-        <is>
-          <t>New Orleans, LA; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+      <c r="B92" s="18" t="inlineStr">
+        <is>
+          <t>New Orleans, LA; Digital — abstract book held (1 PDF) — extraction pending</t>
+        </is>
+      </c>
+      <c r="C92" s="18" t="inlineStr">
+        <is>
+          <t>New Orleans, LA; Digital — abstract book held (1 PDF) — extraction pending</t>
         </is>
       </c>
       <c r="D92" s="19" t="inlineStr">
@@ -2780,12 +2780,12 @@
       </c>
       <c r="B93" s="20" t="inlineStr">
         <is>
-          <t>St. Louis, MO; Extracted — regex-parsed; Fable re-extraction part-done (229 so far)</t>
+          <t>St. Louis, MO; Extracted — regex-parsed; Fable re-extraction part-done (602 so far)</t>
         </is>
       </c>
       <c r="C93" s="20" t="inlineStr">
         <is>
-          <t>St. Louis, MO (155); Extracted — regex-parsed; Fable re-extraction part-done (229 so far)</t>
+          <t>St. Louis, MO (155); Extracted — regex-parsed; Fable re-extraction part-done (602 so far)</t>
         </is>
       </c>
       <c r="D93" s="19" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="B94" s="20" t="inlineStr">
         <is>
-          <t>Montreal, PQ; Extracted — regex-parsed; Fable re-extraction part-done (684 so far)</t>
+          <t>Montreal, PQ; Extracted — Fable extraction complete (737) — merge pending</t>
         </is>
       </c>
       <c r="C94" s="20" t="inlineStr">
         <is>
-          <t>Montreal, PQ (193); Extracted — regex-parsed; Fable re-extraction part-done (684 so far)</t>
+          <t>Montreal, PQ (193); Extracted — Fable extraction complete (737) — merge pending</t>
         </is>
       </c>
       <c r="D94" s="19" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="B95" s="20" t="inlineStr">
         <is>
-          <t>Portland, OR; Extracted — regex-parsed; Fable re-extraction queued</t>
+          <t>Portland, OR; Extracted — regex-parsed; Fable re-extraction part-done (433 so far)</t>
         </is>
       </c>
       <c r="C95" s="20" t="inlineStr">
         <is>
-          <t>Portland, OR (149); Extracted — regex-parsed; Fable re-extraction queued</t>
+          <t>Portland, OR (149); Extracted — regex-parsed; Fable re-extraction part-done (433 so far)</t>
         </is>
       </c>
       <c r="D95" s="19" t="inlineStr">
@@ -2844,14 +2844,14 @@
       <c r="A96" s="12" t="n">
         <v>2010</v>
       </c>
-      <c r="B96" s="16" t="inlineStr">
-        <is>
-          <t>Providence, RI; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
-        </is>
-      </c>
-      <c r="C96" s="16" t="inlineStr">
-        <is>
-          <t>Providence, RI; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+      <c r="B96" s="18" t="inlineStr">
+        <is>
+          <t>Providence, RI; Digital — abstract book held (1 PDF) — extraction pending</t>
+        </is>
+      </c>
+      <c r="C96" s="18" t="inlineStr">
+        <is>
+          <t>Providence, RI; Digital — abstract book held (1 PDF) — extraction pending</t>
         </is>
       </c>
       <c r="D96" s="16" t="inlineStr">
@@ -2940,14 +2940,14 @@
       <c r="A100" s="12" t="n">
         <v>2014</v>
       </c>
-      <c r="B100" s="16" t="inlineStr">
-        <is>
-          <t>Chattanooga, TN; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
-        </is>
-      </c>
-      <c r="C100" s="16" t="inlineStr">
-        <is>
-          <t>Chattanooga, TN; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+      <c r="B100" s="18" t="inlineStr">
+        <is>
+          <t>Chattanooga, TN; Digital — abstract book held (1 PDF) — extraction pending</t>
+        </is>
+      </c>
+      <c r="C100" s="18" t="inlineStr">
+        <is>
+          <t>Chattanooga, TN; Digital — abstract book held (1 PDF) — extraction pending</t>
         </is>
       </c>
       <c r="D100" s="15" t="inlineStr">
@@ -3018,17 +3018,17 @@
       <c r="A103" s="12" t="n">
         <v>2017</v>
       </c>
-      <c r="B103" s="21" t="inlineStr">
-        <is>
-          <t>Austin, TX; Programme — grid programme only — abstract book needed (Carylanne)</t>
-        </is>
-      </c>
-      <c r="C103" s="21" t="inlineStr">
-        <is>
-          <t>Austin, TX; Programme — grid programme only — abstract book needed (Carylanne)</t>
-        </is>
-      </c>
-      <c r="D103" s="22" t="inlineStr">
+      <c r="B103" s="18" t="inlineStr">
+        <is>
+          <t>Austin, TX; Digital — abstract book held (1 PDF) — extraction pending</t>
+        </is>
+      </c>
+      <c r="C103" s="18" t="inlineStr">
+        <is>
+          <t>Austin, TX; Digital — abstract book held (1 PDF) — extraction pending</t>
+        </is>
+      </c>
+      <c r="D103" s="21" t="inlineStr">
         <is>
           <t>Amsterdam; Schedule — 62 talks ingested, NO abstract bodies; Cat holds a hardcopy but has no scanning capacity; abstract book needed from NEV</t>
         </is>
@@ -3040,14 +3040,14 @@
       <c r="A104" s="12" t="n">
         <v>2018</v>
       </c>
-      <c r="B104" s="16" t="inlineStr">
-        <is>
-          <t>Rochester, NY; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
-        </is>
-      </c>
-      <c r="C104" s="16" t="inlineStr">
-        <is>
-          <t>Rochester, NY; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+      <c r="B104" s="18" t="inlineStr">
+        <is>
+          <t>Rochester, NY; Digital — abstract book held (1 PDF) — extraction pending</t>
+        </is>
+      </c>
+      <c r="C104" s="18" t="inlineStr">
+        <is>
+          <t>Rochester, NY; Digital — abstract book held (1 PDF) — extraction pending</t>
         </is>
       </c>
       <c r="D104" s="15" t="inlineStr">
@@ -3070,14 +3070,14 @@
       <c r="A105" s="12" t="n">
         <v>2019</v>
       </c>
-      <c r="B105" s="21" t="inlineStr">
-        <is>
-          <t>Snowbird, UT; Programme — grid programme only — abstract book needed (Carylanne)</t>
-        </is>
-      </c>
-      <c r="C105" s="21" t="inlineStr">
-        <is>
-          <t>Snowbird, UT; Programme — grid programme only — abstract book needed (Carylanne)</t>
+      <c r="B105" s="18" t="inlineStr">
+        <is>
+          <t>Snowbird, UT; Digital — abstract book held (2 PDFs) — extraction pending</t>
+        </is>
+      </c>
+      <c r="C105" s="18" t="inlineStr">
+        <is>
+          <t>Snowbird, UT; Digital — abstract book held (2 PDFs) — extraction pending</t>
         </is>
       </c>
       <c r="D105" s="15" t="inlineStr">
@@ -3092,14 +3092,14 @@
       <c r="A106" s="12" t="n">
         <v>2020</v>
       </c>
-      <c r="B106" s="16" t="inlineStr">
-        <is>
-          <t>?; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
-        </is>
-      </c>
-      <c r="C106" s="16" t="inlineStr">
-        <is>
-          <t>?; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+      <c r="B106" s="14" t="inlineStr">
+        <is>
+          <t>?; NA — no meeting — virtual BAAM-ZOOM sessions only, no abstract book</t>
+        </is>
+      </c>
+      <c r="C106" s="14" t="inlineStr">
+        <is>
+          <t>?; NA — no meeting — virtual BAAM-ZOOM sessions only, no abstract book</t>
         </is>
       </c>
       <c r="D106" s="13" t="inlineStr">
@@ -3118,17 +3118,17 @@
       <c r="A107" s="12" t="n">
         <v>2021</v>
       </c>
-      <c r="B107" s="22" t="inlineStr">
+      <c r="B107" s="21" t="inlineStr">
         <is>
           <t>Phoenix, AZ; Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="C107" s="22" t="inlineStr">
+      <c r="C107" s="21" t="inlineStr">
         <is>
           <t>Phoenix, AZ (46); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="D107" s="21" t="inlineStr">
+      <c r="D107" s="22" t="inlineStr">
         <is>
           <t>Leiden; Programme — programme only; abstract book needed from NEV</t>
         </is>
@@ -3140,12 +3140,12 @@
       <c r="A108" s="12" t="n">
         <v>2022</v>
       </c>
-      <c r="B108" s="22" t="inlineStr">
+      <c r="B108" s="21" t="inlineStr">
         <is>
           <t>Spokane, WA; Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="C108" s="22" t="inlineStr">
+      <c r="C108" s="21" t="inlineStr">
         <is>
           <t>Spokane, WA (69); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
@@ -3170,14 +3170,14 @@
       <c r="A109" s="12" t="n">
         <v>2023</v>
       </c>
-      <c r="B109" s="22" t="inlineStr">
-        <is>
-          <t>Norfolk, VA; Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
-        </is>
-      </c>
-      <c r="C109" s="22" t="inlineStr">
-        <is>
-          <t>Norfolk, VA (87); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
+      <c r="B109" s="18" t="inlineStr">
+        <is>
+          <t>Norfolk, VA; Digital — abstract book held (1 PDF) — extraction pending</t>
+        </is>
+      </c>
+      <c r="C109" s="18" t="inlineStr">
+        <is>
+          <t>Norfolk, VA; Digital — abstract book held (1 PDF) — extraction pending</t>
         </is>
       </c>
       <c r="D109" s="15" t="inlineStr">
@@ -3192,14 +3192,14 @@
       <c r="A110" s="12" t="n">
         <v>2024</v>
       </c>
-      <c r="B110" s="22" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA; Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
-        </is>
-      </c>
-      <c r="C110" s="22" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA (97); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
+      <c r="B110" s="18" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA; Digital — abstract book held (1 PDF) — extraction pending</t>
+        </is>
+      </c>
+      <c r="C110" s="18" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA; Digital — abstract book held (1 PDF) — extraction pending</t>
         </is>
       </c>
       <c r="D110" s="18" t="inlineStr">
@@ -3218,17 +3218,17 @@
       <c r="A111" s="12" t="n">
         <v>2025</v>
       </c>
-      <c r="B111" s="22" t="inlineStr">
+      <c r="B111" s="21" t="inlineStr">
         <is>
           <t>St. Paul, MN; Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="C111" s="22" t="inlineStr">
+      <c r="C111" s="21" t="inlineStr">
         <is>
           <t>St. Paul, MN (68); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="D111" s="21" t="inlineStr">
+      <c r="D111" s="22" t="inlineStr">
         <is>
           <t>Rotterdam; Programme — agenda only; Cat has no abstract book and is unsure one was produced; NEV/Irene to confirm whether it exists</t>
         </is>
@@ -3240,14 +3240,14 @@
       <c r="A112" s="12" t="n">
         <v>2026</v>
       </c>
-      <c r="B112" s="22" t="inlineStr">
-        <is>
-          <t>New Orleans, LA; Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
-        </is>
-      </c>
-      <c r="C112" s="22" t="inlineStr">
-        <is>
-          <t>New Orleans, LA (61); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
+      <c r="B112" s="18" t="inlineStr">
+        <is>
+          <t>New Orleans, LA; Digital — abstract book held (1 PDF) — extraction pending</t>
+        </is>
+      </c>
+      <c r="C112" s="18" t="inlineStr">
+        <is>
+          <t>New Orleans, LA; Digital — abstract book held (1 PDF) — extraction pending</t>
         </is>
       </c>
       <c r="D112" s="19" t="inlineStr">
@@ -4302,10 +4302,10 @@
         <v>23</v>
       </c>
       <c r="C43" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D43" t="n">
-        <v>52.3</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="44">

--- a/database/conference_coverage_matrix.xlsx
+++ b/database/conference_coverage_matrix.xlsx
@@ -2580,9 +2580,9 @@
       <c r="A84" s="12" t="n">
         <v>1998</v>
       </c>
-      <c r="B84" s="17" t="inlineStr">
-        <is>
-          <t>Guelph, ON; OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
+      <c r="B84" s="15" t="inlineStr">
+        <is>
+          <t>Guelph, ON; Ingested</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
@@ -2690,9 +2690,9 @@
       <c r="A89" s="12" t="n">
         <v>2003</v>
       </c>
-      <c r="B89" s="18" t="inlineStr">
-        <is>
-          <t>Manaus, Brazil; Digital — abstract book held (1 PDF) — extraction pending</t>
+      <c r="B89" s="17" t="inlineStr">
+        <is>
+          <t>Manaus, Brazil; OCR — degraded phone scan — 0 abstracts recovered — flatbed re-scan needed (Carylanne)</t>
         </is>
       </c>
       <c r="C89" s="15" t="inlineStr">
@@ -2712,9 +2712,9 @@
       <c r="A90" s="12" t="n">
         <v>2004</v>
       </c>
-      <c r="B90" s="18" t="inlineStr">
-        <is>
-          <t>Norman, OK; Digital — abstract book held (1 PDF) — extraction pending</t>
+      <c r="B90" s="17" t="inlineStr">
+        <is>
+          <t>Norman, OK; OCR — degraded phone scan — 0 abstracts recovered — flatbed re-scan needed (Carylanne)</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
@@ -2778,14 +2778,14 @@
       <c r="A93" s="12" t="n">
         <v>2007</v>
       </c>
-      <c r="B93" s="20" t="inlineStr">
-        <is>
-          <t>St. Louis, MO; Extracted — regex-parsed; Fable re-extraction part-done (602 so far)</t>
-        </is>
-      </c>
-      <c r="C93" s="20" t="inlineStr">
-        <is>
-          <t>St. Louis, MO (155); Extracted — regex-parsed; Fable re-extraction part-done (602 so far)</t>
+      <c r="B93" s="15" t="inlineStr">
+        <is>
+          <t>St. Louis, MO; Ingested</t>
+        </is>
+      </c>
+      <c r="C93" s="15" t="inlineStr">
+        <is>
+          <t>St. Louis, MO (154); Ingested</t>
         </is>
       </c>
       <c r="D93" s="19" t="inlineStr">
@@ -2800,14 +2800,14 @@
       <c r="A94" s="12" t="n">
         <v>2008</v>
       </c>
-      <c r="B94" s="20" t="inlineStr">
-        <is>
-          <t>Montreal, PQ; Extracted — Fable extraction complete (737) — merge pending</t>
-        </is>
-      </c>
-      <c r="C94" s="20" t="inlineStr">
-        <is>
-          <t>Montreal, PQ (193); Extracted — Fable extraction complete (737) — merge pending</t>
+      <c r="B94" s="15" t="inlineStr">
+        <is>
+          <t>Montreal, PQ; Ingested</t>
+        </is>
+      </c>
+      <c r="C94" s="15" t="inlineStr">
+        <is>
+          <t>Montreal, PQ (205); Ingested</t>
         </is>
       </c>
       <c r="D94" s="19" t="inlineStr">
@@ -2822,14 +2822,14 @@
       <c r="A95" s="12" t="n">
         <v>2009</v>
       </c>
-      <c r="B95" s="20" t="inlineStr">
-        <is>
-          <t>Portland, OR; Extracted — regex-parsed; Fable re-extraction part-done (433 so far)</t>
-        </is>
-      </c>
-      <c r="C95" s="20" t="inlineStr">
-        <is>
-          <t>Portland, OR (149); Extracted — regex-parsed; Fable re-extraction part-done (433 so far)</t>
+      <c r="B95" s="15" t="inlineStr">
+        <is>
+          <t>Portland, OR; Ingested</t>
+        </is>
+      </c>
+      <c r="C95" s="15" t="inlineStr">
+        <is>
+          <t>Portland, OR (169); Ingested</t>
         </is>
       </c>
       <c r="D95" s="19" t="inlineStr">
@@ -2844,14 +2844,14 @@
       <c r="A96" s="12" t="n">
         <v>2010</v>
       </c>
-      <c r="B96" s="18" t="inlineStr">
-        <is>
-          <t>Providence, RI; Digital — abstract book held (1 PDF) — extraction pending</t>
-        </is>
-      </c>
-      <c r="C96" s="18" t="inlineStr">
-        <is>
-          <t>Providence, RI; Digital — abstract book held (1 PDF) — extraction pending</t>
+      <c r="B96" s="20" t="inlineStr">
+        <is>
+          <t>Providence, RI; Extracted — Fable extraction complete (772) — merge pending</t>
+        </is>
+      </c>
+      <c r="C96" s="20" t="inlineStr">
+        <is>
+          <t>Providence, RI; Extracted — Fable extraction complete (772) — merge pending</t>
         </is>
       </c>
       <c r="D96" s="16" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="B100" s="18" t="inlineStr">
         <is>
-          <t>Chattanooga, TN; Digital — abstract book held (1 PDF) — extraction pending</t>
+          <t>Chattanooga, TN; Digital — abstract book held — Fable extraction part-done (254 so far)</t>
         </is>
       </c>
       <c r="C100" s="18" t="inlineStr">
         <is>
-          <t>Chattanooga, TN; Digital — abstract book held (1 PDF) — extraction pending</t>
+          <t>Chattanooga, TN; Digital — abstract book held — Fable extraction part-done (254 so far)</t>
         </is>
       </c>
       <c r="D100" s="15" t="inlineStr">
@@ -3040,14 +3040,14 @@
       <c r="A104" s="12" t="n">
         <v>2018</v>
       </c>
-      <c r="B104" s="18" t="inlineStr">
-        <is>
-          <t>Rochester, NY; Digital — abstract book held (1 PDF) — extraction pending</t>
-        </is>
-      </c>
-      <c r="C104" s="18" t="inlineStr">
-        <is>
-          <t>Rochester, NY; Digital — abstract book held (1 PDF) — extraction pending</t>
+      <c r="B104" s="15" t="inlineStr">
+        <is>
+          <t>Rochester, NY; Ingested</t>
+        </is>
+      </c>
+      <c r="C104" s="15" t="inlineStr">
+        <is>
+          <t>Rochester, NY (31); Ingested</t>
         </is>
       </c>
       <c r="D104" s="15" t="inlineStr">
@@ -3070,14 +3070,14 @@
       <c r="A105" s="12" t="n">
         <v>2019</v>
       </c>
-      <c r="B105" s="18" t="inlineStr">
-        <is>
-          <t>Snowbird, UT; Digital — abstract book held (2 PDFs) — extraction pending</t>
-        </is>
-      </c>
-      <c r="C105" s="18" t="inlineStr">
-        <is>
-          <t>Snowbird, UT; Digital — abstract book held (2 PDFs) — extraction pending</t>
+      <c r="B105" s="15" t="inlineStr">
+        <is>
+          <t>Snowbird, UT; Ingested</t>
+        </is>
+      </c>
+      <c r="C105" s="15" t="inlineStr">
+        <is>
+          <t>Snowbird, UT (183); Ingested</t>
         </is>
       </c>
       <c r="D105" s="15" t="inlineStr">
@@ -3170,14 +3170,14 @@
       <c r="A109" s="12" t="n">
         <v>2023</v>
       </c>
-      <c r="B109" s="18" t="inlineStr">
-        <is>
-          <t>Norfolk, VA; Digital — abstract book held (1 PDF) — extraction pending</t>
-        </is>
-      </c>
-      <c r="C109" s="18" t="inlineStr">
-        <is>
-          <t>Norfolk, VA; Digital — abstract book held (1 PDF) — extraction pending</t>
+      <c r="B109" s="15" t="inlineStr">
+        <is>
+          <t>Norfolk, VA; Ingested</t>
+        </is>
+      </c>
+      <c r="C109" s="15" t="inlineStr">
+        <is>
+          <t>Norfolk, VA (252); Ingested</t>
         </is>
       </c>
       <c r="D109" s="15" t="inlineStr">
@@ -3192,14 +3192,14 @@
       <c r="A110" s="12" t="n">
         <v>2024</v>
       </c>
-      <c r="B110" s="18" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA; Digital — abstract book held (1 PDF) — extraction pending</t>
-        </is>
-      </c>
-      <c r="C110" s="18" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA; Digital — abstract book held (1 PDF) — extraction pending</t>
+      <c r="B110" s="15" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA; Ingested</t>
+        </is>
+      </c>
+      <c r="C110" s="15" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA (257); Ingested</t>
         </is>
       </c>
       <c r="D110" s="18" t="inlineStr">
@@ -3493,19 +3493,19 @@
         <v>1998</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="C10" t="n">
-        <v>61</v>
+        <v>395</v>
       </c>
       <c r="D10" t="n">
-        <v>18</v>
+        <v>233</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -3612,7 +3612,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
         <v>450</v>
       </c>
       <c r="D17" t="n">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E17" t="n">
         <v>36</v>
@@ -3727,19 +3727,19 @@
         <v>2007</v>
       </c>
       <c r="B19" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C19" t="n">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="D19" t="n">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="E19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -3753,19 +3753,19 @@
         <v>2008</v>
       </c>
       <c r="B20" t="n">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="C20" t="n">
-        <v>231</v>
+        <v>312</v>
       </c>
       <c r="D20" t="n">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="E20" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F20" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -3779,19 +3779,19 @@
         <v>2009</v>
       </c>
       <c r="B21" t="n">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="C21" t="n">
-        <v>458</v>
+        <v>510</v>
       </c>
       <c r="D21" t="n">
-        <v>215</v>
+        <v>276</v>
       </c>
       <c r="E21" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F21" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -3938,10 +3938,10 @@
         <v>125</v>
       </c>
       <c r="C27" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D27" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
         <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -3967,7 +3967,7 @@
         <v>441</v>
       </c>
       <c r="D28" t="n">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E28" t="n">
         <v>97</v>
@@ -4013,19 +4013,19 @@
         <v>2018</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G30" t="n">
         <v>75</v>
@@ -4039,19 +4039,19 @@
         <v>2019</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>342</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G31" t="n">
         <v>136</v>
@@ -4135,7 +4135,7 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>89</v>
+        <v>322</v>
       </c>
     </row>
     <row r="35">
@@ -4143,19 +4143,19 @@
         <v>2023</v>
       </c>
       <c r="B35" t="n">
-        <v>87</v>
+        <v>251</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G35" t="n">
         <v>98</v>
@@ -4169,22 +4169,22 @@
         <v>2024</v>
       </c>
       <c r="B36" t="n">
-        <v>97</v>
+        <v>256</v>
       </c>
       <c r="C36" t="n">
-        <v>55</v>
+        <v>226</v>
       </c>
       <c r="D36" t="n">
-        <v>16</v>
+        <v>116</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -4249,25 +4249,25 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>2401</v>
+        <v>2974</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>3756</v>
+        <v>5252</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>2108</v>
+        <v>3102</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>329</v>
+        <v>472</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>731</v>
+        <v>956</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>1517</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="42">
@@ -4299,13 +4299,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C43" t="n">
         <v>43</v>
       </c>
       <c r="D43" t="n">
-        <v>53.5</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="44">

--- a/database/conference_coverage_matrix.xlsx
+++ b/database/conference_coverage_matrix.xlsx
@@ -2785,7 +2785,7 @@
       </c>
       <c r="C93" s="15" t="inlineStr">
         <is>
-          <t>St. Louis, MO (154); Ingested</t>
+          <t>St. Louis, MO (138); Ingested</t>
         </is>
       </c>
       <c r="D93" s="19" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>Montreal, PQ (205); Ingested</t>
+          <t>Montreal, PQ (193); Ingested</t>
         </is>
       </c>
       <c r="D94" s="19" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="C95" s="15" t="inlineStr">
         <is>
-          <t>Portland, OR (169); Ingested</t>
+          <t>Portland, OR (161); Ingested</t>
         </is>
       </c>
       <c r="D95" s="19" t="inlineStr">
@@ -2844,14 +2844,14 @@
       <c r="A96" s="12" t="n">
         <v>2010</v>
       </c>
-      <c r="B96" s="20" t="inlineStr">
-        <is>
-          <t>Providence, RI; Extracted — Fable extraction complete (772) — merge pending</t>
-        </is>
-      </c>
-      <c r="C96" s="20" t="inlineStr">
-        <is>
-          <t>Providence, RI; Extracted — Fable extraction complete (772) — merge pending</t>
+      <c r="B96" s="15" t="inlineStr">
+        <is>
+          <t>Providence, RI; Ingested</t>
+        </is>
+      </c>
+      <c r="C96" s="15" t="inlineStr">
+        <is>
+          <t>Providence, RI (172); Ingested</t>
         </is>
       </c>
       <c r="D96" s="16" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="C98" s="20" t="inlineStr">
         <is>
-          <t>Vancouver, BC (65); Extracted — regex-parsed; Fable re-extraction queued</t>
+          <t>Vancouver, BC (62); Extracted — regex-parsed; Fable re-extraction queued</t>
         </is>
       </c>
       <c r="D98" s="16" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="C101" s="15" t="inlineStr">
         <is>
-          <t>Reno, NV (128); Ingested</t>
+          <t>Reno, NV (118); Ingested</t>
         </is>
       </c>
       <c r="D101" s="18" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="C102" s="15" t="inlineStr">
         <is>
-          <t>New Orleans, LA (251); Ingested</t>
+          <t>New Orleans, LA (233); Ingested</t>
         </is>
       </c>
       <c r="D102" s="15" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="C104" s="15" t="inlineStr">
         <is>
-          <t>Rochester, NY (31); Ingested</t>
+          <t>Rochester, NY (10); Ingested</t>
         </is>
       </c>
       <c r="D104" s="15" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="C105" s="15" t="inlineStr">
         <is>
-          <t>Snowbird, UT (183); Ingested</t>
+          <t>Snowbird, UT (175); Ingested</t>
         </is>
       </c>
       <c r="D105" s="15" t="inlineStr">
@@ -3118,14 +3118,14 @@
       <c r="A107" s="12" t="n">
         <v>2021</v>
       </c>
-      <c r="B107" s="21" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ; Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
-        </is>
-      </c>
-      <c r="C107" s="21" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ (46); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
+      <c r="B107" s="15" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ; Ingested — Oxford Abstracts export (born-digital)</t>
+        </is>
+      </c>
+      <c r="C107" s="15" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ (67); Ingested — Oxford Abstracts export (born-digital)</t>
         </is>
       </c>
       <c r="D107" s="22" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="C108" s="21" t="inlineStr">
         <is>
-          <t>Spokane, WA (69); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
+          <t>Spokane, WA (68); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
       <c r="D108" s="18" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="C109" s="15" t="inlineStr">
         <is>
-          <t>Norfolk, VA (252); Ingested</t>
+          <t>Norfolk, VA (241); Ingested</t>
         </is>
       </c>
       <c r="D109" s="15" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="C110" s="15" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA (257); Ingested</t>
+          <t>Pittsburgh, PA (243); Ingested</t>
         </is>
       </c>
       <c r="D110" s="18" t="inlineStr">
@@ -3493,19 +3493,19 @@
         <v>1998</v>
       </c>
       <c r="B10" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C10" t="n">
-        <v>395</v>
+        <v>334</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>2005</v>
       </c>
       <c r="B17" t="n">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="C17" t="n">
         <v>450</v>
@@ -3727,13 +3727,13 @@
         <v>2007</v>
       </c>
       <c r="B19" t="n">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="C19" t="n">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D19" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -3753,7 +3753,7 @@
         <v>2008</v>
       </c>
       <c r="B20" t="n">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="C20" t="n">
         <v>312</v>
@@ -3779,7 +3779,7 @@
         <v>2009</v>
       </c>
       <c r="B21" t="n">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C21" t="n">
         <v>510</v>
@@ -3805,19 +3805,19 @@
         <v>2010</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>348</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -3857,7 +3857,7 @@
         <v>2012</v>
       </c>
       <c r="B24" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C24" t="n">
         <v>132</v>
@@ -3935,7 +3935,7 @@
         <v>2015</v>
       </c>
       <c r="B27" t="n">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C27" t="n">
         <v>311</v>
@@ -3961,13 +3961,13 @@
         <v>2016</v>
       </c>
       <c r="B28" t="n">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="C28" t="n">
         <v>441</v>
       </c>
       <c r="D28" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E28" t="n">
         <v>97</v>
@@ -4013,13 +4013,13 @@
         <v>2018</v>
       </c>
       <c r="B30" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C30" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D30" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E30" t="n">
         <v>89</v>
@@ -4039,7 +4039,7 @@
         <v>2019</v>
       </c>
       <c r="B31" t="n">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C31" t="n">
         <v>342</v>
@@ -4091,16 +4091,16 @@
         <v>2021</v>
       </c>
       <c r="B33" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4117,7 +4117,7 @@
         <v>2022</v>
       </c>
       <c r="B34" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C34" t="n">
         <v>106</v>
@@ -4143,7 +4143,7 @@
         <v>2023</v>
       </c>
       <c r="B35" t="n">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="C35" t="n">
         <v>229</v>
@@ -4169,7 +4169,7 @@
         <v>2024</v>
       </c>
       <c r="B36" t="n">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="C36" t="n">
         <v>226</v>
@@ -4221,7 +4221,7 @@
         <v>2026</v>
       </c>
       <c r="B38" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C38" t="n">
         <v>21</v>
@@ -4249,19 +4249,19 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>2974</v>
+        <v>3034</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>5252</v>
+        <v>5672</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>3102</v>
+        <v>3288</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>472</v>
+        <v>540</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="G39" s="1" t="n">
         <v>956</v>
@@ -4299,13 +4299,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C43" t="n">
         <v>43</v>
       </c>
       <c r="D43" t="n">
-        <v>69.8</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="44">

--- a/database/conference_coverage_matrix.xlsx
+++ b/database/conference_coverage_matrix.xlsx
@@ -3045,9 +3045,9 @@
           <t>Rochester, NY; Ingested</t>
         </is>
       </c>
-      <c r="C104" s="15" t="inlineStr">
-        <is>
-          <t>Rochester, NY (10); Ingested</t>
+      <c r="C104" s="13" t="inlineStr">
+        <is>
+          <t>Rochester, NY; Missing — AES half absent — the held book covers ASIH/SSAR/HL only (10 elasmo strays in ASIH sessions); ask David Green for the Oxford Abstracts export</t>
         </is>
       </c>
       <c r="D104" s="15" t="inlineStr">
@@ -4299,13 +4299,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C43" t="n">
         <v>43</v>
       </c>
       <c r="D43" t="n">
-        <v>74.40000000000001</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="44">

--- a/database/conference_coverage_matrix.xlsx
+++ b/database/conference_coverage_matrix.xlsx
@@ -4091,7 +4091,7 @@
         <v>2021</v>
       </c>
       <c r="B33" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C33" t="n">
         <v>133</v>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>3034</v>
+        <v>3029</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>5672</v>

--- a/database/conference_coverage_matrix.xlsx
+++ b/database/conference_coverage_matrix.xlsx
@@ -3177,7 +3177,7 @@
       </c>
       <c r="C109" s="15" t="inlineStr">
         <is>
-          <t>Norfolk, VA (241); Ingested</t>
+          <t>Norfolk, VA (154); Ingested</t>
         </is>
       </c>
       <c r="D109" s="15" t="inlineStr">
@@ -4143,7 +4143,7 @@
         <v>2023</v>
       </c>
       <c r="B35" t="n">
-        <v>240</v>
+        <v>155</v>
       </c>
       <c r="C35" t="n">
         <v>229</v>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>3029</v>
+        <v>2944</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>5672</v>

--- a/database/conference_coverage_matrix.xlsx
+++ b/database/conference_coverage_matrix.xlsx
@@ -3199,7 +3199,7 @@
       </c>
       <c r="C110" s="15" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA (243); Ingested</t>
+          <t>Pittsburgh, PA (148); Ingested</t>
         </is>
       </c>
       <c r="D110" s="18" t="inlineStr">
@@ -4169,13 +4169,13 @@
         <v>2024</v>
       </c>
       <c r="B36" t="n">
-        <v>242</v>
+        <v>147</v>
       </c>
       <c r="C36" t="n">
-        <v>226</v>
+        <v>174</v>
       </c>
       <c r="D36" t="n">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -4249,13 +4249,13 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>2944</v>
+        <v>2849</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>5672</v>
+        <v>5620</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>3288</v>
+        <v>3274</v>
       </c>
       <c r="E39" s="1" t="n">
         <v>540</v>

--- a/database/conference_coverage_matrix.xlsx
+++ b/database/conference_coverage_matrix.xlsx
@@ -3045,9 +3045,9 @@
           <t>Rochester, NY; Ingested</t>
         </is>
       </c>
-      <c r="C104" s="13" t="inlineStr">
-        <is>
-          <t>Rochester, NY; Missing — AES half absent — the held book covers ASIH/SSAR/HL only (10 elasmo strays in ASIH sessions); ask David Green for the Oxford Abstracts export</t>
+      <c r="C104" s="14" t="inlineStr">
+        <is>
+          <t>NA — no AES meeting at JMIH — AES met at Sharks International (Joao Pessoa) instead; those abstracts are under SI 2018</t>
         </is>
       </c>
       <c r="D104" s="15" t="inlineStr">
@@ -4302,10 +4302,10 @@
         <v>31</v>
       </c>
       <c r="C43" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D43" t="n">
-        <v>72.09999999999999</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="44">

--- a/database/conference_coverage_matrix.xlsx
+++ b/database/conference_coverage_matrix.xlsx
@@ -8,10 +8,13 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Notes" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conferences" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Conferences'!$A$1:$H$24</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,6 +43,9 @@
     <font>
       <b val="1"/>
       <sz val="13"/>
+    </font>
+    <font>
+      <i val="1"/>
     </font>
   </fonts>
   <fills count="12">
@@ -126,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -138,6 +144,16 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1321,6 +1337,792 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
+    <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>year_from</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>year_to</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>n_needed</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>organisers</t>
+        </is>
+      </c>
+      <c r="G1" s="11" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="H1" s="11" t="inlineStr">
+        <is>
+          <t>contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>ASIH / JMIH</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="n">
+        <v>1913</v>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>n/a — counted under AES</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>Programme officers: Maureen 'Mo' Donnelly (to ~2014), Marty Crump (2015-2019), David M. Green (2020- ). Meeting planned by the MMPC (chairs Ed Heist, then Henry Mushinsky); logistics by Kansas State Conference Management Services. Submissions run on Oxford Abstracts.</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>https://www.asih.org/meetings/recent-meetings (abstract books, 2005 on)</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>david.m.green@mcgill.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>American Elasmobranch Society (AES)</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="n">
+        <v>1983</v>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>AES officers; meets inside JMIH, so the JMIH programme officer holds the abstracts. EXCEPTION 2018: AES met at Sharks International instead.</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>https://elasmo.org/meetings/abstracts/abst&lt;YYYY&gt;/ — full abstracts with bodies for EVERY year 1985-2005 (404 for 1983-84 and 2006+); harvested</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>via JMIH programme officer, david.m.green@mcgill.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>European Elasmobranch Association (EEA)</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="n">
+        <v>1997</v>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="12" t="n">
+        <v>192</v>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>EEA board. Ali Hood (Secretariat, Shark Trust); Cat Gordon (Shark Trust) holds/sources the abstract books. Host national society varies by year (IEG, GRIS, APECE, NEV ...).</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>http://eulasmo.org/ ; host cities per year at http://eulasmo.org/scientific-meetings</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>Cat Gordon / Ali Hood, Shark Trust</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Oceania Chondrichthyan Society (OCS)</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>2005</v>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>OCS council. Brit Finucci (past president, and IUCN SSG Red List Authority Coordinator) is collating the series for us, with council approval. Meetings seen: 2008, 2011, 2012 (Adelaide, joint with ASFB), 2018, 2022 (virtual), 2024 Geelong, 2025 Mooloolaba (20th anniversary).</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>https://www.oceaniasharks.org.au/</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>Brit Finucci</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Sharks International (SI)</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>171</v>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>Rotating local host. 2010 Cairns, 2014 Durban, 2018 Joao Pessoa, 2022 Valencia, 2026 Colombo (Blue Resources Trust).</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>https://www.sharksinternational.org.br/noticia/23-abstract-book/menu_abstract_book.html (2018 book)</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Encuentro Colombiano sobre Condrictios (ECC)</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C7" s="12" t="n">
+        <v>2018</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>Fundacion SQUALUS. I 2008 Bogota, II 2010 Cali, III 2012 Santa Marta, IV 2014 Medellin, V 2016 Bogota, VI 2018 Joao Pessoa (co-located with Sharks International 2018, so check the SI 2018 book first).</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>http://squalus.org/index.php/encuentro-condrictios/ ; https://encuentro.squalus.org</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>squalus@germanm1.sg-host.com (from the site; verify before using)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Simposio Nacional de Tiburones y Rayas (SOMEPEC, Mexico)</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>2004</v>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>Sociedad Mexicana de Peces Cartilaginosos (SOMEPEC). Editions seen: III 2008, IV 2010 (UNAM), V, VI 2014 Mazatlan, VIII 2019 Playa del Carmen (joint with the I Congreso Latinoamericano de Tiburones, Rayas y Quimeras), XI recent.</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>Memorias/resumenes posted on ResearchGate and via facebook.com/Somepec2</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Colloque international requins en Afrique de l'Ouest</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>2011</v>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>2011</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>Commission Sous-Regionale des Peches (CSRP / SRFC). Dakar, Senegal, 25-27 July 2011. One-off as far as we can tell.</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>https://spcsrp.org/</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Gulf and Caribbean Fisheries Institute (GCFI)</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>1948</v>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>GCFI secretariat. Every meeting since 1948 is published in the annual Proceedings, so this is a library request, not an ask of a person.</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gcfi.org/ ; back proceedings in the NOAA Institutional Repository, https://repository.library.noaa.gov/</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Pacific Shark Workshop</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>2011</v>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" s="13" t="inlineStr"/>
+      <c r="G11" s="13" t="inlineStr"/>
+      <c r="H11" s="13" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>ISC Shark Working Group</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>International Scientific Committee for Tuna and Tuna-like Species in the North Pacific Ocean; the Shark Working Group meets within it.</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>https://isc.fra.go.jp/</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>World Congress of Herpetology</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>1989</v>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>101</v>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>World Congress of Herpetology committee. Every 3-5 years.</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>https://www.worldcongressofherpetology.org/</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Indo-Pacific Fish Conference (IPFC)</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n">
+        <v>1981</v>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>Rotating host. IPFC-11 2023 Auckland (joint with ASFB); IPFC-12 2025 Taiwan.</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>https://sfi-cybium.fr/en/indo-pacific-fish-conference</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>International Coral Reef Symposium (ICRS)</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="n">
+        <v>1969</v>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>International Coral Reef Society. ICRS-16 2026 Auckland.</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>https://coralreefs.org/</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>World Fisheries Congress</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>1992</v>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" s="13" t="inlineStr"/>
+      <c r="G16" s="13" t="inlineStr"/>
+      <c r="H16" s="13" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>American Fisheries Society symposia</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>1870</v>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>American Fisheries Society.</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>https://fisheries.org/</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>International Congress on the Biology of Fish</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n">
+        <v>1994</v>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" s="13" t="inlineStr"/>
+      <c r="G18" s="13" t="inlineStr"/>
+      <c r="H18" s="13" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>International Meeting on Mesozoic Fishes</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n">
+        <v>1993</v>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>Meeting conveners vary; 6th meeting edited by Schwarz &amp; Kriwet.</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr"/>
+      <c r="H19" s="13" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>International Congress of Vertebrate Morphology (ICVM)</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="n">
+        <v>1986</v>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="13" t="inlineStr"/>
+      <c r="G20" s="13" t="inlineStr"/>
+      <c r="H20" s="13" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>CIESM Congress (Mediterranean Science Commission)</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="n">
+        <v>1919</v>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>Commission Internationale pour l'Exploration Scientifique de la Mer Mediterranee.</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>https://ciesm.org/</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Albert L. Tester Memorial Symposium</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="n">
+        <v>1976</v>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>University of Hawaii at Manoa.</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr"/>
+      <c r="H22" s="13" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Workshop on Age Determination of Oceanic Pelagic Fishes</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="n">
+        <v>1983</v>
+      </c>
+      <c r="C23" s="12" t="n">
+        <v>1983</v>
+      </c>
+      <c r="D23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" s="13" t="inlineStr"/>
+      <c r="G23" s="13" t="inlineStr"/>
+      <c r="H23" s="13" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Palaeontology / geology meetings (assorted)</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="n">
+        <v>1973</v>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>NOT ONE SERIES — a bucket of many national and international palaeo and geology meetings. Split it before chasing anyone.</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr"/>
+      <c r="H24" s="13" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>frequency: 1 = annual, 2 = biennial, 3 = every three years, 4 = every four years, 0 = one-off / irregular</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>n_needed: corpus records citing that series whose PDF we do NOT hold (scripts/conf_abstracts/conference_lead_candidates.py). It counts abstracts we can already name, so it is a floor, not the size of the series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>A BLANK organisers/website/contact means not found on 2026-09-04, never a guess — a wrong address costs a real email to a real person.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H24"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1333,1934 +2135,1934 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>ASIH/JMIH</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>AES</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>EEA</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>OCS</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="n">
+      <c r="A2" s="16" t="n">
         <v>1916</v>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>New York, NY; Missing</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr"/>
-      <c r="D2" s="14" t="inlineStr"/>
-      <c r="E2" s="14" t="inlineStr"/>
-      <c r="F2" s="14" t="inlineStr"/>
+      <c r="C2" s="18" t="inlineStr"/>
+      <c r="D2" s="18" t="inlineStr"/>
+      <c r="E2" s="18" t="inlineStr"/>
+      <c r="F2" s="18" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="n">
+      <c r="A3" s="16" t="n">
         <v>1917</v>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>Cambridge, MA; Missing</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr"/>
-      <c r="D3" s="14" t="inlineStr"/>
-      <c r="E3" s="14" t="inlineStr"/>
-      <c r="F3" s="14" t="inlineStr"/>
+      <c r="C3" s="18" t="inlineStr"/>
+      <c r="D3" s="18" t="inlineStr"/>
+      <c r="E3" s="18" t="inlineStr"/>
+      <c r="F3" s="18" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="n">
+      <c r="A4" s="16" t="n">
         <v>1918</v>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Brooklyn, NY; Missing</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr"/>
-      <c r="D4" s="14" t="inlineStr"/>
-      <c r="E4" s="14" t="inlineStr"/>
-      <c r="F4" s="14" t="inlineStr"/>
+      <c r="C4" s="18" t="inlineStr"/>
+      <c r="D4" s="18" t="inlineStr"/>
+      <c r="E4" s="18" t="inlineStr"/>
+      <c r="F4" s="18" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="n">
+      <c r="A5" s="16" t="n">
         <v>1919</v>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>?; Missing</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr"/>
-      <c r="D5" s="14" t="inlineStr"/>
-      <c r="E5" s="14" t="inlineStr"/>
-      <c r="F5" s="14" t="inlineStr"/>
+      <c r="C5" s="18" t="inlineStr"/>
+      <c r="D5" s="18" t="inlineStr"/>
+      <c r="E5" s="18" t="inlineStr"/>
+      <c r="F5" s="18" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="n">
+      <c r="A6" s="16" t="n">
         <v>1920</v>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>Washington, DC; Missing</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr"/>
-      <c r="D6" s="14" t="inlineStr"/>
-      <c r="E6" s="14" t="inlineStr"/>
-      <c r="F6" s="14" t="inlineStr"/>
+      <c r="C6" s="18" t="inlineStr"/>
+      <c r="D6" s="18" t="inlineStr"/>
+      <c r="E6" s="18" t="inlineStr"/>
+      <c r="F6" s="18" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="n">
+      <c r="A7" s="16" t="n">
         <v>1921</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>Philadelphia, PA; Missing</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr"/>
-      <c r="D7" s="14" t="inlineStr"/>
-      <c r="E7" s="14" t="inlineStr"/>
-      <c r="F7" s="14" t="inlineStr"/>
+      <c r="C7" s="18" t="inlineStr"/>
+      <c r="D7" s="18" t="inlineStr"/>
+      <c r="E7" s="18" t="inlineStr"/>
+      <c r="F7" s="18" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="n">
+      <c r="A8" s="16" t="n">
         <v>1922</v>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Chicago, IL; Missing</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr"/>
-      <c r="D8" s="14" t="inlineStr"/>
-      <c r="E8" s="14" t="inlineStr"/>
-      <c r="F8" s="14" t="inlineStr"/>
+      <c r="C8" s="18" t="inlineStr"/>
+      <c r="D8" s="18" t="inlineStr"/>
+      <c r="E8" s="18" t="inlineStr"/>
+      <c r="F8" s="18" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="n">
+      <c r="A9" s="16" t="n">
         <v>1923</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>Cambridge, MA; Missing</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr"/>
-      <c r="D9" s="14" t="inlineStr"/>
-      <c r="E9" s="14" t="inlineStr"/>
-      <c r="F9" s="14" t="inlineStr"/>
+      <c r="C9" s="18" t="inlineStr"/>
+      <c r="D9" s="18" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr"/>
+      <c r="F9" s="18" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="n">
+      <c r="A10" s="16" t="n">
         <v>1924</v>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Northhampton, MA; Missing</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr"/>
-      <c r="D10" s="14" t="inlineStr"/>
-      <c r="E10" s="14" t="inlineStr"/>
-      <c r="F10" s="14" t="inlineStr"/>
+      <c r="C10" s="18" t="inlineStr"/>
+      <c r="D10" s="18" t="inlineStr"/>
+      <c r="E10" s="18" t="inlineStr"/>
+      <c r="F10" s="18" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="n">
+      <c r="A11" s="16" t="n">
         <v>1925</v>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>?; Missing</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr"/>
-      <c r="D11" s="14" t="inlineStr"/>
-      <c r="E11" s="14" t="inlineStr"/>
-      <c r="F11" s="14" t="inlineStr"/>
+      <c r="C11" s="18" t="inlineStr"/>
+      <c r="D11" s="18" t="inlineStr"/>
+      <c r="E11" s="18" t="inlineStr"/>
+      <c r="F11" s="18" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="n">
+      <c r="A12" s="16" t="n">
         <v>1926</v>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Philadelphia, PA; Missing</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr"/>
-      <c r="D12" s="14" t="inlineStr"/>
-      <c r="E12" s="14" t="inlineStr"/>
-      <c r="F12" s="14" t="inlineStr"/>
+      <c r="C12" s="18" t="inlineStr"/>
+      <c r="D12" s="18" t="inlineStr"/>
+      <c r="E12" s="18" t="inlineStr"/>
+      <c r="F12" s="18" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="n">
+      <c r="A13" s="16" t="n">
         <v>1927</v>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Philadelphia, PA; Missing</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr"/>
-      <c r="D13" s="14" t="inlineStr"/>
-      <c r="E13" s="14" t="inlineStr"/>
-      <c r="F13" s="14" t="inlineStr"/>
+      <c r="C13" s="18" t="inlineStr"/>
+      <c r="D13" s="18" t="inlineStr"/>
+      <c r="E13" s="18" t="inlineStr"/>
+      <c r="F13" s="18" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="n">
+      <c r="A14" s="16" t="n">
         <v>1928</v>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>Washington, DC; Missing</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr"/>
-      <c r="D14" s="14" t="inlineStr"/>
-      <c r="E14" s="14" t="inlineStr"/>
-      <c r="F14" s="14" t="inlineStr"/>
+      <c r="C14" s="18" t="inlineStr"/>
+      <c r="D14" s="18" t="inlineStr"/>
+      <c r="E14" s="18" t="inlineStr"/>
+      <c r="F14" s="18" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="n">
+      <c r="A15" s="16" t="n">
         <v>1929</v>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>Ann Arbor, MI; Missing</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr"/>
-      <c r="D15" s="14" t="inlineStr"/>
-      <c r="E15" s="14" t="inlineStr"/>
-      <c r="F15" s="14" t="inlineStr"/>
+      <c r="C15" s="18" t="inlineStr"/>
+      <c r="D15" s="18" t="inlineStr"/>
+      <c r="E15" s="18" t="inlineStr"/>
+      <c r="F15" s="18" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="n">
+      <c r="A16" s="16" t="n">
         <v>1930</v>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>New York, NY; Missing</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr"/>
-      <c r="D16" s="14" t="inlineStr"/>
-      <c r="E16" s="14" t="inlineStr"/>
-      <c r="F16" s="14" t="inlineStr"/>
+      <c r="C16" s="18" t="inlineStr"/>
+      <c r="D16" s="18" t="inlineStr"/>
+      <c r="E16" s="18" t="inlineStr"/>
+      <c r="F16" s="18" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="n">
+      <c r="A17" s="16" t="n">
         <v>1931</v>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>Philadelphia, PA; Missing</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr"/>
-      <c r="D17" s="14" t="inlineStr"/>
-      <c r="E17" s="14" t="inlineStr"/>
-      <c r="F17" s="14" t="inlineStr"/>
+      <c r="C17" s="18" t="inlineStr"/>
+      <c r="D17" s="18" t="inlineStr"/>
+      <c r="E17" s="18" t="inlineStr"/>
+      <c r="F17" s="18" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="n">
+      <c r="A18" s="16" t="n">
         <v>1932</v>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>Washington, DC; Missing</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr"/>
-      <c r="D18" s="14" t="inlineStr"/>
-      <c r="E18" s="14" t="inlineStr"/>
-      <c r="F18" s="14" t="inlineStr"/>
+      <c r="C18" s="18" t="inlineStr"/>
+      <c r="D18" s="18" t="inlineStr"/>
+      <c r="E18" s="18" t="inlineStr"/>
+      <c r="F18" s="18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="n">
+      <c r="A19" s="16" t="n">
         <v>1933</v>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>Cambridge, MA; Missing</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr"/>
-      <c r="D19" s="14" t="inlineStr"/>
-      <c r="E19" s="14" t="inlineStr"/>
-      <c r="F19" s="14" t="inlineStr"/>
+      <c r="C19" s="18" t="inlineStr"/>
+      <c r="D19" s="18" t="inlineStr"/>
+      <c r="E19" s="18" t="inlineStr"/>
+      <c r="F19" s="18" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="n">
+      <c r="A20" s="16" t="n">
         <v>1934</v>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>New York, NY; Missing</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr"/>
-      <c r="D20" s="14" t="inlineStr"/>
-      <c r="E20" s="14" t="inlineStr"/>
-      <c r="F20" s="14" t="inlineStr"/>
+      <c r="C20" s="18" t="inlineStr"/>
+      <c r="D20" s="18" t="inlineStr"/>
+      <c r="E20" s="18" t="inlineStr"/>
+      <c r="F20" s="18" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="n">
+      <c r="A21" s="16" t="n">
         <v>1935</v>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>Pittsburgh, PA; Missing</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr"/>
-      <c r="D21" s="14" t="inlineStr"/>
-      <c r="E21" s="14" t="inlineStr"/>
-      <c r="F21" s="14" t="inlineStr"/>
+      <c r="C21" s="18" t="inlineStr"/>
+      <c r="D21" s="18" t="inlineStr"/>
+      <c r="E21" s="18" t="inlineStr"/>
+      <c r="F21" s="18" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="n">
+      <c r="A22" s="16" t="n">
         <v>1936</v>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>Ann Arbor, MI; Missing</t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr"/>
-      <c r="D22" s="14" t="inlineStr"/>
-      <c r="E22" s="14" t="inlineStr"/>
-      <c r="F22" s="14" t="inlineStr"/>
+      <c r="C22" s="18" t="inlineStr"/>
+      <c r="D22" s="18" t="inlineStr"/>
+      <c r="E22" s="18" t="inlineStr"/>
+      <c r="F22" s="18" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="n">
+      <c r="A23" s="16" t="n">
         <v>1937</v>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>Washington, DC; Missing</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr"/>
-      <c r="D23" s="14" t="inlineStr"/>
-      <c r="E23" s="14" t="inlineStr"/>
-      <c r="F23" s="14" t="inlineStr"/>
+      <c r="C23" s="18" t="inlineStr"/>
+      <c r="D23" s="18" t="inlineStr"/>
+      <c r="E23" s="18" t="inlineStr"/>
+      <c r="F23" s="18" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="n">
+      <c r="A24" s="16" t="n">
         <v>1938</v>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>Berkeley, CA; Missing</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr"/>
-      <c r="D24" s="14" t="inlineStr"/>
-      <c r="E24" s="14" t="inlineStr"/>
-      <c r="F24" s="14" t="inlineStr"/>
+      <c r="C24" s="18" t="inlineStr"/>
+      <c r="D24" s="18" t="inlineStr"/>
+      <c r="E24" s="18" t="inlineStr"/>
+      <c r="F24" s="18" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="n">
+      <c r="A25" s="16" t="n">
         <v>1939</v>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>Chicago, IL; Missing</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr"/>
-      <c r="D25" s="14" t="inlineStr"/>
-      <c r="E25" s="14" t="inlineStr"/>
-      <c r="F25" s="14" t="inlineStr"/>
+      <c r="C25" s="18" t="inlineStr"/>
+      <c r="D25" s="18" t="inlineStr"/>
+      <c r="E25" s="18" t="inlineStr"/>
+      <c r="F25" s="18" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="n">
+      <c r="A26" s="16" t="n">
         <v>1940</v>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>Toronto, ON; Missing</t>
         </is>
       </c>
-      <c r="C26" s="14" t="inlineStr"/>
-      <c r="D26" s="14" t="inlineStr"/>
-      <c r="E26" s="14" t="inlineStr"/>
-      <c r="F26" s="14" t="inlineStr"/>
+      <c r="C26" s="18" t="inlineStr"/>
+      <c r="D26" s="18" t="inlineStr"/>
+      <c r="E26" s="18" t="inlineStr"/>
+      <c r="F26" s="18" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="n">
+      <c r="A27" s="16" t="n">
         <v>1941</v>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="17" t="inlineStr">
         <is>
           <t>Gainesville, FL; Missing</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr"/>
-      <c r="D27" s="14" t="inlineStr"/>
-      <c r="E27" s="14" t="inlineStr"/>
-      <c r="F27" s="14" t="inlineStr"/>
+      <c r="C27" s="18" t="inlineStr"/>
+      <c r="D27" s="18" t="inlineStr"/>
+      <c r="E27" s="18" t="inlineStr"/>
+      <c r="F27" s="18" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="n">
+      <c r="A28" s="16" t="n">
         <v>1942</v>
       </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>New York, NY; Missing</t>
         </is>
       </c>
-      <c r="C28" s="14" t="inlineStr"/>
-      <c r="D28" s="14" t="inlineStr"/>
-      <c r="E28" s="14" t="inlineStr"/>
-      <c r="F28" s="14" t="inlineStr"/>
+      <c r="C28" s="18" t="inlineStr"/>
+      <c r="D28" s="18" t="inlineStr"/>
+      <c r="E28" s="18" t="inlineStr"/>
+      <c r="F28" s="18" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="n">
+      <c r="A29" s="16" t="n">
         <v>1943</v>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B29" s="17" t="inlineStr">
         <is>
           <t>?; Missing</t>
         </is>
       </c>
-      <c r="C29" s="14" t="inlineStr"/>
-      <c r="D29" s="14" t="inlineStr"/>
-      <c r="E29" s="14" t="inlineStr"/>
-      <c r="F29" s="14" t="inlineStr"/>
+      <c r="C29" s="18" t="inlineStr"/>
+      <c r="D29" s="18" t="inlineStr"/>
+      <c r="E29" s="18" t="inlineStr"/>
+      <c r="F29" s="18" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="n">
+      <c r="A30" s="16" t="n">
         <v>1944</v>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>?; Missing</t>
         </is>
       </c>
-      <c r="C30" s="14" t="inlineStr"/>
-      <c r="D30" s="14" t="inlineStr"/>
-      <c r="E30" s="14" t="inlineStr"/>
-      <c r="F30" s="14" t="inlineStr"/>
+      <c r="C30" s="18" t="inlineStr"/>
+      <c r="D30" s="18" t="inlineStr"/>
+      <c r="E30" s="18" t="inlineStr"/>
+      <c r="F30" s="18" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="n">
+      <c r="A31" s="16" t="n">
         <v>1945</v>
       </c>
-      <c r="B31" s="13" t="inlineStr">
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>?; Missing</t>
         </is>
       </c>
-      <c r="C31" s="14" t="inlineStr"/>
-      <c r="D31" s="14" t="inlineStr"/>
-      <c r="E31" s="14" t="inlineStr"/>
-      <c r="F31" s="14" t="inlineStr"/>
+      <c r="C31" s="18" t="inlineStr"/>
+      <c r="D31" s="18" t="inlineStr"/>
+      <c r="E31" s="18" t="inlineStr"/>
+      <c r="F31" s="18" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="n">
+      <c r="A32" s="16" t="n">
         <v>1946</v>
       </c>
-      <c r="B32" s="13" t="inlineStr">
+      <c r="B32" s="17" t="inlineStr">
         <is>
           <t>Pittsburgh, PA; Missing</t>
         </is>
       </c>
-      <c r="C32" s="14" t="inlineStr"/>
-      <c r="D32" s="14" t="inlineStr"/>
-      <c r="E32" s="14" t="inlineStr"/>
-      <c r="F32" s="14" t="inlineStr"/>
+      <c r="C32" s="18" t="inlineStr"/>
+      <c r="D32" s="18" t="inlineStr"/>
+      <c r="E32" s="18" t="inlineStr"/>
+      <c r="F32" s="18" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="n">
+      <c r="A33" s="16" t="n">
         <v>1947</v>
       </c>
-      <c r="B33" s="13" t="inlineStr">
+      <c r="B33" s="17" t="inlineStr">
         <is>
           <t>Higgins Lake, MI; Missing</t>
         </is>
       </c>
-      <c r="C33" s="14" t="inlineStr"/>
-      <c r="D33" s="14" t="inlineStr"/>
-      <c r="E33" s="14" t="inlineStr"/>
-      <c r="F33" s="14" t="inlineStr"/>
+      <c r="C33" s="18" t="inlineStr"/>
+      <c r="D33" s="18" t="inlineStr"/>
+      <c r="E33" s="18" t="inlineStr"/>
+      <c r="F33" s="18" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="n">
+      <c r="A34" s="16" t="n">
         <v>1948</v>
       </c>
-      <c r="B34" s="13" t="inlineStr">
+      <c r="B34" s="17" t="inlineStr">
         <is>
           <t>New Orleans, LA; Missing</t>
         </is>
       </c>
-      <c r="C34" s="14" t="inlineStr"/>
-      <c r="D34" s="14" t="inlineStr"/>
-      <c r="E34" s="14" t="inlineStr"/>
-      <c r="F34" s="14" t="inlineStr"/>
+      <c r="C34" s="18" t="inlineStr"/>
+      <c r="D34" s="18" t="inlineStr"/>
+      <c r="E34" s="18" t="inlineStr"/>
+      <c r="F34" s="18" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="n">
+      <c r="A35" s="16" t="n">
         <v>1949</v>
       </c>
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B35" s="17" t="inlineStr">
         <is>
           <t>Washington, DC; Missing</t>
         </is>
       </c>
-      <c r="C35" s="14" t="inlineStr"/>
-      <c r="D35" s="14" t="inlineStr"/>
-      <c r="E35" s="14" t="inlineStr"/>
-      <c r="F35" s="14" t="inlineStr"/>
+      <c r="C35" s="18" t="inlineStr"/>
+      <c r="D35" s="18" t="inlineStr"/>
+      <c r="E35" s="18" t="inlineStr"/>
+      <c r="F35" s="18" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="12" t="n">
+      <c r="A36" s="16" t="n">
         <v>1950</v>
       </c>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="B36" s="17" t="inlineStr">
         <is>
           <t>Salt Lake City, UT; Missing</t>
         </is>
       </c>
-      <c r="C36" s="14" t="inlineStr"/>
-      <c r="D36" s="14" t="inlineStr"/>
-      <c r="E36" s="14" t="inlineStr"/>
-      <c r="F36" s="14" t="inlineStr"/>
+      <c r="C36" s="18" t="inlineStr"/>
+      <c r="D36" s="18" t="inlineStr"/>
+      <c r="E36" s="18" t="inlineStr"/>
+      <c r="F36" s="18" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="12" t="n">
+      <c r="A37" s="16" t="n">
         <v>1951</v>
       </c>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="B37" s="17" t="inlineStr">
         <is>
           <t>Chicago, IL; Missing</t>
         </is>
       </c>
-      <c r="C37" s="14" t="inlineStr"/>
-      <c r="D37" s="14" t="inlineStr"/>
-      <c r="E37" s="14" t="inlineStr"/>
-      <c r="F37" s="14" t="inlineStr"/>
+      <c r="C37" s="18" t="inlineStr"/>
+      <c r="D37" s="18" t="inlineStr"/>
+      <c r="E37" s="18" t="inlineStr"/>
+      <c r="F37" s="18" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="12" t="n">
+      <c r="A38" s="16" t="n">
         <v>1952</v>
       </c>
-      <c r="B38" s="13" t="inlineStr">
+      <c r="B38" s="17" t="inlineStr">
         <is>
           <t>Austin, TX; Missing</t>
         </is>
       </c>
-      <c r="C38" s="14" t="inlineStr"/>
-      <c r="D38" s="14" t="inlineStr"/>
-      <c r="E38" s="14" t="inlineStr"/>
-      <c r="F38" s="14" t="inlineStr"/>
+      <c r="C38" s="18" t="inlineStr"/>
+      <c r="D38" s="18" t="inlineStr"/>
+      <c r="E38" s="18" t="inlineStr"/>
+      <c r="F38" s="18" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="12" t="n">
+      <c r="A39" s="16" t="n">
         <v>1953</v>
       </c>
-      <c r="B39" s="13" t="inlineStr">
+      <c r="B39" s="17" t="inlineStr">
         <is>
           <t>New York, NY; Missing</t>
         </is>
       </c>
-      <c r="C39" s="14" t="inlineStr"/>
-      <c r="D39" s="14" t="inlineStr"/>
-      <c r="E39" s="14" t="inlineStr"/>
-      <c r="F39" s="14" t="inlineStr"/>
+      <c r="C39" s="18" t="inlineStr"/>
+      <c r="D39" s="18" t="inlineStr"/>
+      <c r="E39" s="18" t="inlineStr"/>
+      <c r="F39" s="18" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="12" t="n">
+      <c r="A40" s="16" t="n">
         <v>1954</v>
       </c>
-      <c r="B40" s="13" t="inlineStr">
+      <c r="B40" s="17" t="inlineStr">
         <is>
           <t>Gainesville, FL; Missing</t>
         </is>
       </c>
-      <c r="C40" s="14" t="inlineStr"/>
-      <c r="D40" s="14" t="inlineStr"/>
-      <c r="E40" s="14" t="inlineStr"/>
-      <c r="F40" s="14" t="inlineStr"/>
+      <c r="C40" s="18" t="inlineStr"/>
+      <c r="D40" s="18" t="inlineStr"/>
+      <c r="E40" s="18" t="inlineStr"/>
+      <c r="F40" s="18" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="12" t="n">
+      <c r="A41" s="16" t="n">
         <v>1955</v>
       </c>
-      <c r="B41" s="13" t="inlineStr">
+      <c r="B41" s="17" t="inlineStr">
         <is>
           <t>San Francisco, CA; Missing</t>
         </is>
       </c>
-      <c r="C41" s="14" t="inlineStr"/>
-      <c r="D41" s="14" t="inlineStr"/>
-      <c r="E41" s="14" t="inlineStr"/>
-      <c r="F41" s="14" t="inlineStr"/>
+      <c r="C41" s="18" t="inlineStr"/>
+      <c r="D41" s="18" t="inlineStr"/>
+      <c r="E41" s="18" t="inlineStr"/>
+      <c r="F41" s="18" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="12" t="n">
+      <c r="A42" s="16" t="n">
         <v>1956</v>
       </c>
-      <c r="B42" s="13" t="inlineStr">
+      <c r="B42" s="17" t="inlineStr">
         <is>
           <t>Higgins Lake, MI; Missing</t>
         </is>
       </c>
-      <c r="C42" s="14" t="inlineStr"/>
-      <c r="D42" s="14" t="inlineStr"/>
-      <c r="E42" s="14" t="inlineStr"/>
-      <c r="F42" s="14" t="inlineStr"/>
+      <c r="C42" s="18" t="inlineStr"/>
+      <c r="D42" s="18" t="inlineStr"/>
+      <c r="E42" s="18" t="inlineStr"/>
+      <c r="F42" s="18" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="12" t="n">
+      <c r="A43" s="16" t="n">
         <v>1957</v>
       </c>
-      <c r="B43" s="13" t="inlineStr">
+      <c r="B43" s="17" t="inlineStr">
         <is>
           <t>New Orleans, LA; Missing</t>
         </is>
       </c>
-      <c r="C43" s="14" t="inlineStr"/>
-      <c r="D43" s="14" t="inlineStr"/>
-      <c r="E43" s="14" t="inlineStr"/>
-      <c r="F43" s="14" t="inlineStr"/>
+      <c r="C43" s="18" t="inlineStr"/>
+      <c r="D43" s="18" t="inlineStr"/>
+      <c r="E43" s="18" t="inlineStr"/>
+      <c r="F43" s="18" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="12" t="n">
+      <c r="A44" s="16" t="n">
         <v>1958</v>
       </c>
-      <c r="B44" s="13" t="inlineStr">
+      <c r="B44" s="17" t="inlineStr">
         <is>
           <t>Bloomington, IN; Missing</t>
         </is>
       </c>
-      <c r="C44" s="14" t="inlineStr"/>
-      <c r="D44" s="14" t="inlineStr"/>
-      <c r="E44" s="14" t="inlineStr"/>
-      <c r="F44" s="14" t="inlineStr"/>
+      <c r="C44" s="18" t="inlineStr"/>
+      <c r="D44" s="18" t="inlineStr"/>
+      <c r="E44" s="18" t="inlineStr"/>
+      <c r="F44" s="18" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="12" t="n">
+      <c r="A45" s="16" t="n">
         <v>1959</v>
       </c>
-      <c r="B45" s="13" t="inlineStr">
+      <c r="B45" s="17" t="inlineStr">
         <is>
           <t>San Diego, CA; Missing</t>
         </is>
       </c>
-      <c r="C45" s="14" t="inlineStr"/>
-      <c r="D45" s="14" t="inlineStr"/>
-      <c r="E45" s="14" t="inlineStr"/>
-      <c r="F45" s="14" t="inlineStr"/>
+      <c r="C45" s="18" t="inlineStr"/>
+      <c r="D45" s="18" t="inlineStr"/>
+      <c r="E45" s="18" t="inlineStr"/>
+      <c r="F45" s="18" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="12" t="n">
+      <c r="A46" s="16" t="n">
         <v>1960</v>
       </c>
-      <c r="B46" s="13" t="inlineStr">
+      <c r="B46" s="17" t="inlineStr">
         <is>
           <t>Chicago, IL; Missing</t>
         </is>
       </c>
-      <c r="C46" s="14" t="inlineStr"/>
-      <c r="D46" s="14" t="inlineStr"/>
-      <c r="E46" s="14" t="inlineStr"/>
-      <c r="F46" s="14" t="inlineStr"/>
+      <c r="C46" s="18" t="inlineStr"/>
+      <c r="D46" s="18" t="inlineStr"/>
+      <c r="E46" s="18" t="inlineStr"/>
+      <c r="F46" s="18" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="12" t="n">
+      <c r="A47" s="16" t="n">
         <v>1961</v>
       </c>
-      <c r="B47" s="13" t="inlineStr">
+      <c r="B47" s="17" t="inlineStr">
         <is>
           <t>Austin, TX; Missing</t>
         </is>
       </c>
-      <c r="C47" s="14" t="inlineStr"/>
-      <c r="D47" s="14" t="inlineStr"/>
-      <c r="E47" s="14" t="inlineStr"/>
-      <c r="F47" s="14" t="inlineStr"/>
+      <c r="C47" s="18" t="inlineStr"/>
+      <c r="D47" s="18" t="inlineStr"/>
+      <c r="E47" s="18" t="inlineStr"/>
+      <c r="F47" s="18" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="12" t="n">
+      <c r="A48" s="16" t="n">
         <v>1962</v>
       </c>
-      <c r="B48" s="13" t="inlineStr">
+      <c r="B48" s="17" t="inlineStr">
         <is>
           <t>Washington, DC; Missing</t>
         </is>
       </c>
-      <c r="C48" s="14" t="inlineStr"/>
-      <c r="D48" s="14" t="inlineStr"/>
-      <c r="E48" s="14" t="inlineStr"/>
-      <c r="F48" s="14" t="inlineStr"/>
+      <c r="C48" s="18" t="inlineStr"/>
+      <c r="D48" s="18" t="inlineStr"/>
+      <c r="E48" s="18" t="inlineStr"/>
+      <c r="F48" s="18" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="12" t="n">
+      <c r="A49" s="16" t="n">
         <v>1963</v>
       </c>
-      <c r="B49" s="13" t="inlineStr">
+      <c r="B49" s="17" t="inlineStr">
         <is>
           <t>Vancouver, BC; Missing</t>
         </is>
       </c>
-      <c r="C49" s="14" t="inlineStr"/>
-      <c r="D49" s="14" t="inlineStr"/>
-      <c r="E49" s="14" t="inlineStr"/>
-      <c r="F49" s="14" t="inlineStr"/>
+      <c r="C49" s="18" t="inlineStr"/>
+      <c r="D49" s="18" t="inlineStr"/>
+      <c r="E49" s="18" t="inlineStr"/>
+      <c r="F49" s="18" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="12" t="n">
+      <c r="A50" s="16" t="n">
         <v>1964</v>
       </c>
-      <c r="B50" s="13" t="inlineStr">
+      <c r="B50" s="17" t="inlineStr">
         <is>
           <t>Morehead City, NC; Missing</t>
         </is>
       </c>
-      <c r="C50" s="14" t="inlineStr"/>
-      <c r="D50" s="14" t="inlineStr"/>
-      <c r="E50" s="14" t="inlineStr"/>
-      <c r="F50" s="14" t="inlineStr"/>
+      <c r="C50" s="18" t="inlineStr"/>
+      <c r="D50" s="18" t="inlineStr"/>
+      <c r="E50" s="18" t="inlineStr"/>
+      <c r="F50" s="18" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="12" t="n">
+      <c r="A51" s="16" t="n">
         <v>1965</v>
       </c>
-      <c r="B51" s="13" t="inlineStr">
+      <c r="B51" s="17" t="inlineStr">
         <is>
           <t>Lawrence, KS; Missing</t>
         </is>
       </c>
-      <c r="C51" s="14" t="inlineStr"/>
-      <c r="D51" s="14" t="inlineStr"/>
-      <c r="E51" s="14" t="inlineStr"/>
-      <c r="F51" s="14" t="inlineStr"/>
+      <c r="C51" s="18" t="inlineStr"/>
+      <c r="D51" s="18" t="inlineStr"/>
+      <c r="E51" s="18" t="inlineStr"/>
+      <c r="F51" s="18" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="12" t="n">
+      <c r="A52" s="16" t="n">
         <v>1966</v>
       </c>
-      <c r="B52" s="13" t="inlineStr">
+      <c r="B52" s="17" t="inlineStr">
         <is>
           <t>Miami, FL; Missing</t>
         </is>
       </c>
-      <c r="C52" s="14" t="inlineStr"/>
-      <c r="D52" s="14" t="inlineStr"/>
-      <c r="E52" s="14" t="inlineStr"/>
-      <c r="F52" s="14" t="inlineStr"/>
+      <c r="C52" s="18" t="inlineStr"/>
+      <c r="D52" s="18" t="inlineStr"/>
+      <c r="E52" s="18" t="inlineStr"/>
+      <c r="F52" s="18" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="12" t="n">
+      <c r="A53" s="16" t="n">
         <v>1967</v>
       </c>
-      <c r="B53" s="13" t="inlineStr">
+      <c r="B53" s="17" t="inlineStr">
         <is>
           <t>San Francisco, CA; Missing</t>
         </is>
       </c>
-      <c r="C53" s="14" t="inlineStr"/>
-      <c r="D53" s="14" t="inlineStr"/>
-      <c r="E53" s="14" t="inlineStr"/>
-      <c r="F53" s="14" t="inlineStr"/>
+      <c r="C53" s="18" t="inlineStr"/>
+      <c r="D53" s="18" t="inlineStr"/>
+      <c r="E53" s="18" t="inlineStr"/>
+      <c r="F53" s="18" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="12" t="n">
+      <c r="A54" s="16" t="n">
         <v>1968</v>
       </c>
-      <c r="B54" s="13" t="inlineStr">
+      <c r="B54" s="17" t="inlineStr">
         <is>
           <t>Ann Arbor, MI; Missing</t>
         </is>
       </c>
-      <c r="C54" s="14" t="inlineStr"/>
-      <c r="D54" s="14" t="inlineStr"/>
-      <c r="E54" s="14" t="inlineStr"/>
-      <c r="F54" s="14" t="inlineStr"/>
+      <c r="C54" s="18" t="inlineStr"/>
+      <c r="D54" s="18" t="inlineStr"/>
+      <c r="E54" s="18" t="inlineStr"/>
+      <c r="F54" s="18" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="12" t="n">
+      <c r="A55" s="16" t="n">
         <v>1969</v>
       </c>
-      <c r="B55" s="13" t="inlineStr">
+      <c r="B55" s="17" t="inlineStr">
         <is>
           <t>New York, NY; Missing</t>
         </is>
       </c>
-      <c r="C55" s="14" t="inlineStr"/>
-      <c r="D55" s="14" t="inlineStr"/>
-      <c r="E55" s="14" t="inlineStr"/>
-      <c r="F55" s="14" t="inlineStr"/>
+      <c r="C55" s="18" t="inlineStr"/>
+      <c r="D55" s="18" t="inlineStr"/>
+      <c r="E55" s="18" t="inlineStr"/>
+      <c r="F55" s="18" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="12" t="n">
+      <c r="A56" s="16" t="n">
         <v>1970</v>
       </c>
-      <c r="B56" s="13" t="inlineStr">
+      <c r="B56" s="17" t="inlineStr">
         <is>
           <t>New Orleans, LA; Missing</t>
         </is>
       </c>
-      <c r="C56" s="14" t="inlineStr"/>
-      <c r="D56" s="14" t="inlineStr"/>
-      <c r="E56" s="14" t="inlineStr"/>
-      <c r="F56" s="14" t="inlineStr"/>
+      <c r="C56" s="18" t="inlineStr"/>
+      <c r="D56" s="18" t="inlineStr"/>
+      <c r="E56" s="18" t="inlineStr"/>
+      <c r="F56" s="18" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="12" t="n">
+      <c r="A57" s="16" t="n">
         <v>1971</v>
       </c>
-      <c r="B57" s="13" t="inlineStr">
+      <c r="B57" s="17" t="inlineStr">
         <is>
           <t>Los Angeles, CA; Missing</t>
         </is>
       </c>
-      <c r="C57" s="14" t="inlineStr"/>
-      <c r="D57" s="14" t="inlineStr"/>
-      <c r="E57" s="14" t="inlineStr"/>
-      <c r="F57" s="14" t="inlineStr"/>
+      <c r="C57" s="18" t="inlineStr"/>
+      <c r="D57" s="18" t="inlineStr"/>
+      <c r="E57" s="18" t="inlineStr"/>
+      <c r="F57" s="18" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="12" t="n">
+      <c r="A58" s="16" t="n">
         <v>1972</v>
       </c>
-      <c r="B58" s="13" t="inlineStr">
+      <c r="B58" s="17" t="inlineStr">
         <is>
           <t>Boston, MA; Missing</t>
         </is>
       </c>
-      <c r="C58" s="14" t="inlineStr"/>
-      <c r="D58" s="14" t="inlineStr"/>
-      <c r="E58" s="14" t="inlineStr"/>
-      <c r="F58" s="14" t="inlineStr"/>
+      <c r="C58" s="18" t="inlineStr"/>
+      <c r="D58" s="18" t="inlineStr"/>
+      <c r="E58" s="18" t="inlineStr"/>
+      <c r="F58" s="18" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="12" t="n">
+      <c r="A59" s="16" t="n">
         <v>1973</v>
       </c>
-      <c r="B59" s="13" t="inlineStr">
+      <c r="B59" s="17" t="inlineStr">
         <is>
           <t>San Jose, Costa Rica; Missing</t>
         </is>
       </c>
-      <c r="C59" s="14" t="inlineStr"/>
-      <c r="D59" s="14" t="inlineStr"/>
-      <c r="E59" s="14" t="inlineStr"/>
-      <c r="F59" s="14" t="inlineStr"/>
+      <c r="C59" s="18" t="inlineStr"/>
+      <c r="D59" s="18" t="inlineStr"/>
+      <c r="E59" s="18" t="inlineStr"/>
+      <c r="F59" s="18" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="12" t="n">
+      <c r="A60" s="16" t="n">
         <v>1974</v>
       </c>
-      <c r="B60" s="13" t="inlineStr">
+      <c r="B60" s="17" t="inlineStr">
         <is>
           <t>Ottawa, ON; Missing</t>
         </is>
       </c>
-      <c r="C60" s="14" t="inlineStr"/>
-      <c r="D60" s="14" t="inlineStr"/>
-      <c r="E60" s="14" t="inlineStr"/>
-      <c r="F60" s="14" t="inlineStr"/>
+      <c r="C60" s="18" t="inlineStr"/>
+      <c r="D60" s="18" t="inlineStr"/>
+      <c r="E60" s="18" t="inlineStr"/>
+      <c r="F60" s="18" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="12" t="n">
+      <c r="A61" s="16" t="n">
         <v>1975</v>
       </c>
-      <c r="B61" s="13" t="inlineStr">
+      <c r="B61" s="17" t="inlineStr">
         <is>
           <t>Williamsburg, VA; Missing</t>
         </is>
       </c>
-      <c r="C61" s="14" t="inlineStr"/>
-      <c r="D61" s="14" t="inlineStr"/>
-      <c r="E61" s="14" t="inlineStr"/>
-      <c r="F61" s="14" t="inlineStr"/>
+      <c r="C61" s="18" t="inlineStr"/>
+      <c r="D61" s="18" t="inlineStr"/>
+      <c r="E61" s="18" t="inlineStr"/>
+      <c r="F61" s="18" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="12" t="n">
+      <c r="A62" s="16" t="n">
         <v>1976</v>
       </c>
-      <c r="B62" s="13" t="inlineStr">
+      <c r="B62" s="17" t="inlineStr">
         <is>
           <t>Fairbanks, AK; Missing</t>
         </is>
       </c>
-      <c r="C62" s="14" t="inlineStr"/>
-      <c r="D62" s="14" t="inlineStr"/>
-      <c r="E62" s="14" t="inlineStr"/>
-      <c r="F62" s="14" t="inlineStr"/>
+      <c r="C62" s="18" t="inlineStr"/>
+      <c r="D62" s="18" t="inlineStr"/>
+      <c r="E62" s="18" t="inlineStr"/>
+      <c r="F62" s="18" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="12" t="n">
+      <c r="A63" s="16" t="n">
         <v>1977</v>
       </c>
-      <c r="B63" s="13" t="inlineStr">
+      <c r="B63" s="17" t="inlineStr">
         <is>
           <t>Gainesville, FL; Missing</t>
         </is>
       </c>
-      <c r="C63" s="14" t="inlineStr"/>
-      <c r="D63" s="14" t="inlineStr"/>
-      <c r="E63" s="14" t="inlineStr"/>
-      <c r="F63" s="14" t="inlineStr"/>
+      <c r="C63" s="18" t="inlineStr"/>
+      <c r="D63" s="18" t="inlineStr"/>
+      <c r="E63" s="18" t="inlineStr"/>
+      <c r="F63" s="18" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="12" t="n">
+      <c r="A64" s="16" t="n">
         <v>1978</v>
       </c>
-      <c r="B64" s="13" t="inlineStr">
+      <c r="B64" s="17" t="inlineStr">
         <is>
           <t>Tempe, AZ; Missing</t>
         </is>
       </c>
-      <c r="C64" s="14" t="inlineStr"/>
-      <c r="D64" s="14" t="inlineStr"/>
-      <c r="E64" s="14" t="inlineStr"/>
-      <c r="F64" s="14" t="inlineStr"/>
+      <c r="C64" s="18" t="inlineStr"/>
+      <c r="D64" s="18" t="inlineStr"/>
+      <c r="E64" s="18" t="inlineStr"/>
+      <c r="F64" s="18" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="12" t="n">
+      <c r="A65" s="16" t="n">
         <v>1979</v>
       </c>
-      <c r="B65" s="13" t="inlineStr">
+      <c r="B65" s="17" t="inlineStr">
         <is>
           <t>Orono, ME; Missing</t>
         </is>
       </c>
-      <c r="C65" s="14" t="inlineStr"/>
-      <c r="D65" s="14" t="inlineStr"/>
-      <c r="E65" s="14" t="inlineStr"/>
-      <c r="F65" s="14" t="inlineStr"/>
+      <c r="C65" s="18" t="inlineStr"/>
+      <c r="D65" s="18" t="inlineStr"/>
+      <c r="E65" s="18" t="inlineStr"/>
+      <c r="F65" s="18" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="12" t="n">
+      <c r="A66" s="16" t="n">
         <v>1980</v>
       </c>
-      <c r="B66" s="13" t="inlineStr">
+      <c r="B66" s="17" t="inlineStr">
         <is>
           <t>Fort Worth, TX; Missing</t>
         </is>
       </c>
-      <c r="C66" s="14" t="inlineStr"/>
-      <c r="D66" s="14" t="inlineStr"/>
-      <c r="E66" s="14" t="inlineStr"/>
-      <c r="F66" s="14" t="inlineStr"/>
+      <c r="C66" s="18" t="inlineStr"/>
+      <c r="D66" s="18" t="inlineStr"/>
+      <c r="E66" s="18" t="inlineStr"/>
+      <c r="F66" s="18" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="12" t="n">
+      <c r="A67" s="16" t="n">
         <v>1981</v>
       </c>
-      <c r="B67" s="13" t="inlineStr">
+      <c r="B67" s="17" t="inlineStr">
         <is>
           <t>Corvallis, OR; Missing</t>
         </is>
       </c>
-      <c r="C67" s="14" t="inlineStr"/>
-      <c r="D67" s="14" t="inlineStr"/>
-      <c r="E67" s="14" t="inlineStr"/>
-      <c r="F67" s="14" t="inlineStr"/>
+      <c r="C67" s="18" t="inlineStr"/>
+      <c r="D67" s="18" t="inlineStr"/>
+      <c r="E67" s="18" t="inlineStr"/>
+      <c r="F67" s="18" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="12" t="n">
+      <c r="A68" s="16" t="n">
         <v>1982</v>
       </c>
-      <c r="B68" s="13" t="inlineStr">
+      <c r="B68" s="17" t="inlineStr">
         <is>
           <t>DeKalb, IL; Missing</t>
         </is>
       </c>
-      <c r="C68" s="14" t="inlineStr"/>
-      <c r="D68" s="14" t="inlineStr"/>
-      <c r="E68" s="14" t="inlineStr"/>
-      <c r="F68" s="14" t="inlineStr"/>
+      <c r="C68" s="18" t="inlineStr"/>
+      <c r="D68" s="18" t="inlineStr"/>
+      <c r="E68" s="18" t="inlineStr"/>
+      <c r="F68" s="18" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="12" t="n">
+      <c r="A69" s="16" t="n">
         <v>1983</v>
       </c>
-      <c r="B69" s="13" t="inlineStr">
+      <c r="B69" s="17" t="inlineStr">
         <is>
           <t>Tallahasee, FL; Missing</t>
         </is>
       </c>
-      <c r="C69" s="13" t="inlineStr">
+      <c r="C69" s="17" t="inlineStr">
         <is>
           <t>Tallahasee, FL; Missing</t>
         </is>
       </c>
-      <c r="D69" s="14" t="inlineStr"/>
-      <c r="E69" s="14" t="inlineStr"/>
-      <c r="F69" s="14" t="inlineStr"/>
+      <c r="D69" s="18" t="inlineStr"/>
+      <c r="E69" s="18" t="inlineStr"/>
+      <c r="F69" s="18" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="12" t="n">
+      <c r="A70" s="16" t="n">
         <v>1984</v>
       </c>
-      <c r="B70" s="13" t="inlineStr">
+      <c r="B70" s="17" t="inlineStr">
         <is>
           <t>Norman, OK; Missing</t>
         </is>
       </c>
-      <c r="C70" s="13" t="inlineStr">
+      <c r="C70" s="17" t="inlineStr">
         <is>
           <t>Norman, OK; Missing</t>
         </is>
       </c>
-      <c r="D70" s="14" t="inlineStr"/>
-      <c r="E70" s="14" t="inlineStr"/>
-      <c r="F70" s="14" t="inlineStr"/>
+      <c r="D70" s="18" t="inlineStr"/>
+      <c r="E70" s="18" t="inlineStr"/>
+      <c r="F70" s="18" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="12" t="n">
+      <c r="A71" s="16" t="n">
         <v>1985</v>
       </c>
-      <c r="B71" s="13" t="inlineStr">
+      <c r="B71" s="17" t="inlineStr">
         <is>
           <t>Knoxville, TN; Missing</t>
         </is>
       </c>
-      <c r="C71" s="15" t="inlineStr">
+      <c r="C71" s="19" t="inlineStr">
         <is>
           <t>Knoxville, TN (26); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D71" s="14" t="inlineStr"/>
-      <c r="E71" s="14" t="inlineStr"/>
-      <c r="F71" s="14" t="inlineStr"/>
+      <c r="D71" s="18" t="inlineStr"/>
+      <c r="E71" s="18" t="inlineStr"/>
+      <c r="F71" s="18" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="12" t="n">
+      <c r="A72" s="16" t="n">
         <v>1986</v>
       </c>
-      <c r="B72" s="13" t="inlineStr">
+      <c r="B72" s="17" t="inlineStr">
         <is>
           <t>Victoria, BC; Missing</t>
         </is>
       </c>
-      <c r="C72" s="15" t="inlineStr">
+      <c r="C72" s="19" t="inlineStr">
         <is>
           <t>Victoria, BC (35); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D72" s="14" t="inlineStr"/>
-      <c r="E72" s="14" t="inlineStr"/>
-      <c r="F72" s="14" t="inlineStr"/>
+      <c r="D72" s="18" t="inlineStr"/>
+      <c r="E72" s="18" t="inlineStr"/>
+      <c r="F72" s="18" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="12" t="n">
+      <c r="A73" s="16" t="n">
         <v>1987</v>
       </c>
-      <c r="B73" s="13" t="inlineStr">
+      <c r="B73" s="17" t="inlineStr">
         <is>
           <t>Albany, NY; Missing</t>
         </is>
       </c>
-      <c r="C73" s="15" t="inlineStr">
+      <c r="C73" s="19" t="inlineStr">
         <is>
           <t>Albany, NY (33); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D73" s="14" t="inlineStr"/>
-      <c r="E73" s="14" t="inlineStr"/>
-      <c r="F73" s="14" t="inlineStr"/>
+      <c r="D73" s="18" t="inlineStr"/>
+      <c r="E73" s="18" t="inlineStr"/>
+      <c r="F73" s="18" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="12" t="n">
+      <c r="A74" s="16" t="n">
         <v>1988</v>
       </c>
-      <c r="B74" s="13" t="inlineStr">
+      <c r="B74" s="17" t="inlineStr">
         <is>
           <t>Ann Arbor, MI; Missing</t>
         </is>
       </c>
-      <c r="C74" s="15" t="inlineStr">
+      <c r="C74" s="19" t="inlineStr">
         <is>
           <t>Ann Arbor, MI (34); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D74" s="14" t="inlineStr"/>
-      <c r="E74" s="14" t="inlineStr"/>
-      <c r="F74" s="14" t="inlineStr"/>
+      <c r="D74" s="18" t="inlineStr"/>
+      <c r="E74" s="18" t="inlineStr"/>
+      <c r="F74" s="18" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="12" t="n">
+      <c r="A75" s="16" t="n">
         <v>1989</v>
       </c>
-      <c r="B75" s="13" t="inlineStr">
+      <c r="B75" s="17" t="inlineStr">
         <is>
           <t>San Francisco, CA; Missing</t>
         </is>
       </c>
-      <c r="C75" s="15" t="inlineStr">
+      <c r="C75" s="19" t="inlineStr">
         <is>
           <t>San Francisco, CA (63); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D75" s="14" t="inlineStr"/>
-      <c r="E75" s="14" t="inlineStr"/>
-      <c r="F75" s="14" t="inlineStr"/>
+      <c r="D75" s="18" t="inlineStr"/>
+      <c r="E75" s="18" t="inlineStr"/>
+      <c r="F75" s="18" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="12" t="n">
+      <c r="A76" s="16" t="n">
         <v>1990</v>
       </c>
-      <c r="B76" s="13" t="inlineStr">
+      <c r="B76" s="17" t="inlineStr">
         <is>
           <t>Charleston, SC; Missing</t>
         </is>
       </c>
-      <c r="C76" s="15" t="inlineStr">
+      <c r="C76" s="19" t="inlineStr">
         <is>
           <t>Charleston, SC (47); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D76" s="14" t="inlineStr"/>
-      <c r="E76" s="14" t="inlineStr"/>
-      <c r="F76" s="14" t="inlineStr"/>
+      <c r="D76" s="18" t="inlineStr"/>
+      <c r="E76" s="18" t="inlineStr"/>
+      <c r="F76" s="18" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="12" t="n">
+      <c r="A77" s="16" t="n">
         <v>1991</v>
       </c>
-      <c r="B77" s="13" t="inlineStr">
+      <c r="B77" s="17" t="inlineStr">
         <is>
           <t>New York, NY; Missing</t>
         </is>
       </c>
-      <c r="C77" s="15" t="inlineStr">
+      <c r="C77" s="19" t="inlineStr">
         <is>
           <t>New York, NY (34); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D77" s="14" t="inlineStr"/>
-      <c r="E77" s="14" t="inlineStr"/>
-      <c r="F77" s="14" t="inlineStr"/>
+      <c r="D77" s="18" t="inlineStr"/>
+      <c r="E77" s="18" t="inlineStr"/>
+      <c r="F77" s="18" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="12" t="n">
+      <c r="A78" s="16" t="n">
         <v>1992</v>
       </c>
-      <c r="B78" s="16" t="inlineStr">
+      <c r="B78" s="20" t="inlineStr">
         <is>
           <t>Champaign-Urbana, IL; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C78" s="15" t="inlineStr">
+      <c r="C78" s="19" t="inlineStr">
         <is>
           <t>Champaign-Urbana, IL (41); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D78" s="14" t="inlineStr"/>
-      <c r="E78" s="14" t="inlineStr"/>
-      <c r="F78" s="14" t="inlineStr"/>
+      <c r="D78" s="18" t="inlineStr"/>
+      <c r="E78" s="18" t="inlineStr"/>
+      <c r="F78" s="18" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="12" t="n">
+      <c r="A79" s="16" t="n">
         <v>1993</v>
       </c>
-      <c r="B79" s="16" t="inlineStr">
+      <c r="B79" s="20" t="inlineStr">
         <is>
           <t>Austin, TX; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C79" s="15" t="inlineStr">
+      <c r="C79" s="19" t="inlineStr">
         <is>
           <t>Austin, TX (45); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D79" s="14" t="inlineStr"/>
-      <c r="E79" s="14" t="inlineStr"/>
-      <c r="F79" s="14" t="inlineStr"/>
+      <c r="D79" s="18" t="inlineStr"/>
+      <c r="E79" s="18" t="inlineStr"/>
+      <c r="F79" s="18" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="12" t="n">
+      <c r="A80" s="16" t="n">
         <v>1994</v>
       </c>
-      <c r="B80" s="16" t="inlineStr">
+      <c r="B80" s="20" t="inlineStr">
         <is>
           <t>Los Angeles, CA; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C80" s="15" t="inlineStr">
+      <c r="C80" s="19" t="inlineStr">
         <is>
           <t>Los Angeles, CA (50); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D80" s="14" t="inlineStr"/>
-      <c r="E80" s="14" t="inlineStr"/>
-      <c r="F80" s="14" t="inlineStr"/>
+      <c r="D80" s="18" t="inlineStr"/>
+      <c r="E80" s="18" t="inlineStr"/>
+      <c r="F80" s="18" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="12" t="n">
+      <c r="A81" s="16" t="n">
         <v>1995</v>
       </c>
-      <c r="B81" s="16" t="inlineStr">
+      <c r="B81" s="20" t="inlineStr">
         <is>
           <t>Edmonton, AB; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C81" s="15" t="inlineStr">
+      <c r="C81" s="19" t="inlineStr">
         <is>
           <t>Edmonton, AB (46); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D81" s="14" t="inlineStr"/>
-      <c r="E81" s="14" t="inlineStr"/>
-      <c r="F81" s="14" t="inlineStr"/>
+      <c r="D81" s="18" t="inlineStr"/>
+      <c r="E81" s="18" t="inlineStr"/>
+      <c r="F81" s="18" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="12" t="n">
+      <c r="A82" s="16" t="n">
         <v>1996</v>
       </c>
-      <c r="B82" s="16" t="inlineStr">
+      <c r="B82" s="20" t="inlineStr">
         <is>
           <t>New Orleans, LA; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C82" s="15" t="inlineStr">
+      <c r="C82" s="19" t="inlineStr">
         <is>
           <t>New Orleans, LA (98); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D82" s="14" t="inlineStr"/>
-      <c r="E82" s="14" t="inlineStr"/>
-      <c r="F82" s="14" t="inlineStr"/>
+      <c r="D82" s="18" t="inlineStr"/>
+      <c r="E82" s="18" t="inlineStr"/>
+      <c r="F82" s="18" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="12" t="n">
+      <c r="A83" s="16" t="n">
         <v>1997</v>
       </c>
-      <c r="B83" s="17" t="inlineStr">
+      <c r="B83" s="21" t="inlineStr">
         <is>
           <t>Seattle, WA; OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
         </is>
       </c>
-      <c r="C83" s="15" t="inlineStr">
+      <c r="C83" s="19" t="inlineStr">
         <is>
           <t>Seattle, WA (68); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D83" s="13" t="inlineStr">
+      <c r="D83" s="17" t="inlineStr">
         <is>
           <t>?; Missing — 1st EEA; no known abstract source; host city also unknown</t>
         </is>
       </c>
-      <c r="E83" s="14" t="inlineStr"/>
-      <c r="F83" s="14" t="inlineStr"/>
+      <c r="E83" s="18" t="inlineStr"/>
+      <c r="F83" s="18" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="12" t="n">
+      <c r="A84" s="16" t="n">
         <v>1998</v>
       </c>
-      <c r="B84" s="15" t="inlineStr">
+      <c r="B84" s="19" t="inlineStr">
         <is>
           <t>Guelph, ON; Ingested</t>
         </is>
       </c>
-      <c r="C84" s="15" t="inlineStr">
+      <c r="C84" s="19" t="inlineStr">
         <is>
           <t>Guelph, ON (63); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D84" s="13" t="inlineStr">
+      <c r="D84" s="17" t="inlineStr">
         <is>
           <t>Lisbon; Missing — 2nd EEA; no known abstract source</t>
         </is>
       </c>
-      <c r="E84" s="14" t="inlineStr"/>
-      <c r="F84" s="14" t="inlineStr"/>
+      <c r="E84" s="18" t="inlineStr"/>
+      <c r="F84" s="18" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="12" t="n">
+      <c r="A85" s="16" t="n">
         <v>1999</v>
       </c>
-      <c r="B85" s="17" t="inlineStr">
+      <c r="B85" s="21" t="inlineStr">
         <is>
           <t>University Park, PA; OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
         </is>
       </c>
-      <c r="C85" s="15" t="inlineStr">
+      <c r="C85" s="19" t="inlineStr">
         <is>
           <t>University Park, PA (78); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D85" s="13" t="inlineStr">
+      <c r="D85" s="17" t="inlineStr">
         <is>
           <t>?; Missing — 3rd EEA; no known abstract source; host city also unknown</t>
         </is>
       </c>
-      <c r="E85" s="14" t="inlineStr"/>
-      <c r="F85" s="14" t="inlineStr"/>
+      <c r="E85" s="18" t="inlineStr"/>
+      <c r="F85" s="18" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="12" t="n">
+      <c r="A86" s="16" t="n">
         <v>2000</v>
       </c>
-      <c r="B86" s="17" t="inlineStr">
+      <c r="B86" s="21" t="inlineStr">
         <is>
           <t>La Paz, Mexico; OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
         </is>
       </c>
-      <c r="C86" s="15" t="inlineStr">
+      <c r="C86" s="19" t="inlineStr">
         <is>
           <t>La Paz, Mexico (134); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D86" s="13" t="inlineStr">
+      <c r="D86" s="17" t="inlineStr">
         <is>
           <t>?; Missing — 4th EEA; no known abstract source; host city also unknown</t>
         </is>
       </c>
-      <c r="E86" s="14" t="inlineStr"/>
-      <c r="F86" s="14" t="inlineStr"/>
+      <c r="E86" s="18" t="inlineStr"/>
+      <c r="F86" s="18" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="12" t="n">
+      <c r="A87" s="16" t="n">
         <v>2001</v>
       </c>
-      <c r="B87" s="17" t="inlineStr">
+      <c r="B87" s="21" t="inlineStr">
         <is>
           <t>University Park, PA; OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
         </is>
       </c>
-      <c r="C87" s="15" t="inlineStr">
+      <c r="C87" s="19" t="inlineStr">
         <is>
           <t>University Park, PA (84); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D87" s="13" t="inlineStr">
+      <c r="D87" s="17" t="inlineStr">
         <is>
           <t>?; Missing — 5th EEA; no known abstract source; host city also unknown</t>
         </is>
       </c>
-      <c r="E87" s="14" t="inlineStr"/>
-      <c r="F87" s="14" t="inlineStr"/>
+      <c r="E87" s="18" t="inlineStr"/>
+      <c r="F87" s="18" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="12" t="n">
+      <c r="A88" s="16" t="n">
         <v>2002</v>
       </c>
-      <c r="B88" s="16" t="inlineStr">
+      <c r="B88" s="20" t="inlineStr">
         <is>
           <t>Kansas City, MO; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C88" s="15" t="inlineStr">
+      <c r="C88" s="19" t="inlineStr">
         <is>
           <t>Kansas City, MO (27); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D88" s="18" t="inlineStr">
+      <c r="D88" s="22" t="inlineStr">
         <is>
           <t>Cardiff; Digital — abstract booklet (Word) found by Ali Hood 2026-08-27; queued for extraction</t>
         </is>
       </c>
-      <c r="E88" s="14" t="inlineStr"/>
-      <c r="F88" s="14" t="inlineStr"/>
+      <c r="E88" s="18" t="inlineStr"/>
+      <c r="F88" s="18" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="12" t="n">
+      <c r="A89" s="16" t="n">
         <v>2003</v>
       </c>
-      <c r="B89" s="17" t="inlineStr">
+      <c r="B89" s="21" t="inlineStr">
         <is>
           <t>Manaus, Brazil; OCR — degraded phone scan — 0 abstracts recovered — flatbed re-scan needed (Carylanne)</t>
         </is>
       </c>
-      <c r="C89" s="15" t="inlineStr">
+      <c r="C89" s="19" t="inlineStr">
         <is>
           <t>Manaus, Brazil (82); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D89" s="19" t="inlineStr">
+      <c r="D89" s="23" t="inlineStr">
         <is>
           <t>San Marino; Pending — 7th EEA; Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
-      <c r="E89" s="14" t="inlineStr"/>
-      <c r="F89" s="14" t="inlineStr"/>
+      <c r="E89" s="18" t="inlineStr"/>
+      <c r="F89" s="18" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="12" t="n">
+      <c r="A90" s="16" t="n">
         <v>2004</v>
       </c>
-      <c r="B90" s="17" t="inlineStr">
+      <c r="B90" s="21" t="inlineStr">
         <is>
           <t>Norman, OK; OCR — degraded phone scan — 0 abstracts recovered — flatbed re-scan needed (Carylanne)</t>
         </is>
       </c>
-      <c r="C90" s="15" t="inlineStr">
+      <c r="C90" s="19" t="inlineStr">
         <is>
           <t>Norman, OK (59); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D90" s="15" t="inlineStr">
+      <c r="D90" s="19" t="inlineStr">
         <is>
           <t>London; Ingested — 55 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E90" s="14" t="inlineStr"/>
-      <c r="F90" s="14" t="inlineStr"/>
+      <c r="E90" s="18" t="inlineStr"/>
+      <c r="F90" s="18" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="12" t="n">
+      <c r="A91" s="16" t="n">
         <v>2005</v>
       </c>
-      <c r="B91" s="15" t="inlineStr">
+      <c r="B91" s="19" t="inlineStr">
         <is>
           <t>Tampa, FL; Ingested</t>
         </is>
       </c>
-      <c r="C91" s="15" t="inlineStr">
+      <c r="C91" s="19" t="inlineStr">
         <is>
           <t>Tampa, FL (158); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D91" s="19" t="inlineStr">
+      <c r="D91" s="23" t="inlineStr">
         <is>
           <t>Monaco; Pending — 9th EEA; Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
-      <c r="E91" s="14" t="inlineStr"/>
-      <c r="F91" s="14" t="inlineStr"/>
+      <c r="E91" s="18" t="inlineStr"/>
+      <c r="F91" s="18" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="12" t="n">
+      <c r="A92" s="16" t="n">
         <v>2006</v>
       </c>
-      <c r="B92" s="18" t="inlineStr">
+      <c r="B92" s="22" t="inlineStr">
         <is>
           <t>New Orleans, LA; Digital — abstract book held (1 PDF) — extraction pending</t>
         </is>
       </c>
-      <c r="C92" s="18" t="inlineStr">
+      <c r="C92" s="22" t="inlineStr">
         <is>
           <t>New Orleans, LA; Digital — abstract book held (1 PDF) — extraction pending</t>
         </is>
       </c>
-      <c r="D92" s="19" t="inlineStr">
+      <c r="D92" s="23" t="inlineStr">
         <is>
           <t>Hamburg; Pending — 10th EEA; Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
-      <c r="E92" s="14" t="inlineStr"/>
-      <c r="F92" s="14" t="inlineStr"/>
+      <c r="E92" s="18" t="inlineStr"/>
+      <c r="F92" s="18" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="12" t="n">
+      <c r="A93" s="16" t="n">
         <v>2007</v>
       </c>
-      <c r="B93" s="15" t="inlineStr">
+      <c r="B93" s="19" t="inlineStr">
         <is>
           <t>St. Louis, MO; Ingested</t>
         </is>
       </c>
-      <c r="C93" s="15" t="inlineStr">
+      <c r="C93" s="19" t="inlineStr">
         <is>
           <t>St. Louis, MO (138); Ingested</t>
         </is>
       </c>
-      <c r="D93" s="19" t="inlineStr">
+      <c r="D93" s="23" t="inlineStr">
         <is>
           <t>Brest; Pending — 11th EEA; Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
-      <c r="E93" s="14" t="inlineStr"/>
-      <c r="F93" s="14" t="inlineStr"/>
+      <c r="E93" s="18" t="inlineStr"/>
+      <c r="F93" s="18" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="12" t="n">
+      <c r="A94" s="16" t="n">
         <v>2008</v>
       </c>
-      <c r="B94" s="15" t="inlineStr">
+      <c r="B94" s="19" t="inlineStr">
         <is>
           <t>Montreal, PQ; Ingested</t>
         </is>
       </c>
-      <c r="C94" s="15" t="inlineStr">
+      <c r="C94" s="19" t="inlineStr">
         <is>
           <t>Montreal, PQ (193); Ingested</t>
         </is>
       </c>
-      <c r="D94" s="19" t="inlineStr">
+      <c r="D94" s="23" t="inlineStr">
         <is>
           <t>Lisbon; Pending — 12th EEA; Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
-      <c r="E94" s="14" t="inlineStr"/>
-      <c r="F94" s="14" t="inlineStr"/>
+      <c r="E94" s="18" t="inlineStr"/>
+      <c r="F94" s="18" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="12" t="n">
+      <c r="A95" s="16" t="n">
         <v>2009</v>
       </c>
-      <c r="B95" s="15" t="inlineStr">
+      <c r="B95" s="19" t="inlineStr">
         <is>
           <t>Portland, OR; Ingested</t>
         </is>
       </c>
-      <c r="C95" s="15" t="inlineStr">
+      <c r="C95" s="19" t="inlineStr">
         <is>
           <t>Portland, OR (161); Ingested</t>
         </is>
       </c>
-      <c r="D95" s="19" t="inlineStr">
+      <c r="D95" s="23" t="inlineStr">
         <is>
           <t>Palma de Majorca; Pending — 13th EEA; Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
-      <c r="E95" s="14" t="inlineStr"/>
-      <c r="F95" s="14" t="inlineStr"/>
+      <c r="E95" s="18" t="inlineStr"/>
+      <c r="F95" s="18" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="12" t="n">
+      <c r="A96" s="16" t="n">
         <v>2010</v>
       </c>
-      <c r="B96" s="15" t="inlineStr">
+      <c r="B96" s="19" t="inlineStr">
         <is>
           <t>Providence, RI; Ingested</t>
         </is>
       </c>
-      <c r="C96" s="15" t="inlineStr">
+      <c r="C96" s="19" t="inlineStr">
         <is>
           <t>Providence, RI (172); Ingested</t>
         </is>
       </c>
-      <c r="D96" s="16" t="inlineStr">
+      <c r="D96" s="20" t="inlineStr">
         <is>
           <t>Galway; Hardcopy — Cat holds a hardcopy but has no scanning capacity; digital copy needed from IEG (Ireland)</t>
         </is>
       </c>
-      <c r="E96" s="14" t="inlineStr"/>
-      <c r="F96" s="13" t="inlineStr">
+      <c r="E96" s="18" t="inlineStr"/>
+      <c r="F96" s="17" t="inlineStr">
         <is>
           <t>Cairns; Missing — find source</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="12" t="n">
+      <c r="A97" s="16" t="n">
         <v>2011</v>
       </c>
-      <c r="B97" s="16" t="inlineStr">
+      <c r="B97" s="20" t="inlineStr">
         <is>
           <t>Minneapolis, MN; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C97" s="16" t="inlineStr">
+      <c r="C97" s="20" t="inlineStr">
         <is>
           <t>Minneapolis, MN; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="D97" s="15" t="inlineStr">
+      <c r="D97" s="19" t="inlineStr">
         <is>
           <t>Berlin; Ingested — 58 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E97" s="14" t="inlineStr"/>
-      <c r="F97" s="14" t="inlineStr"/>
+      <c r="E97" s="18" t="inlineStr"/>
+      <c r="F97" s="18" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="12" t="n">
+      <c r="A98" s="16" t="n">
         <v>2012</v>
       </c>
-      <c r="B98" s="20" t="inlineStr">
+      <c r="B98" s="24" t="inlineStr">
         <is>
           <t>Vancouver, BC; Extracted — regex-parsed; Fable re-extraction queued</t>
         </is>
       </c>
-      <c r="C98" s="20" t="inlineStr">
+      <c r="C98" s="24" t="inlineStr">
         <is>
           <t>Vancouver, BC (62); Extracted — regex-parsed; Fable re-extraction queued</t>
         </is>
       </c>
-      <c r="D98" s="16" t="inlineStr">
+      <c r="D98" s="20" t="inlineStr">
         <is>
           <t>Milan; Hardcopy — Cat holds a hardcopy but has no scanning capacity; digital copy needed from GRIS (Italy)</t>
         </is>
       </c>
-      <c r="E98" s="19" t="inlineStr">
+      <c r="E98" s="23" t="inlineStr">
         <is>
           <t>Adelaide; Pending — joint with ASFB; Brit Finucci confirming</t>
         </is>
       </c>
-      <c r="F98" s="14" t="inlineStr"/>
+      <c r="F98" s="18" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="12" t="n">
+      <c r="A99" s="16" t="n">
         <v>2013</v>
       </c>
-      <c r="B99" s="16" t="inlineStr">
+      <c r="B99" s="20" t="inlineStr">
         <is>
           <t>Albuquerque, NM; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C99" s="16" t="inlineStr">
+      <c r="C99" s="20" t="inlineStr">
         <is>
           <t>Albuquerque, NM; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="D99" s="15" t="inlineStr">
+      <c r="D99" s="19" t="inlineStr">
         <is>
           <t>Plymouth; Ingested — 93 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E99" s="14" t="inlineStr"/>
-      <c r="F99" s="14" t="inlineStr"/>
+      <c r="E99" s="18" t="inlineStr"/>
+      <c r="F99" s="18" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="12" t="n">
+      <c r="A100" s="16" t="n">
         <v>2014</v>
       </c>
-      <c r="B100" s="18" t="inlineStr">
+      <c r="B100" s="22" t="inlineStr">
         <is>
           <t>Chattanooga, TN; Digital — abstract book held — Fable extraction part-done (254 so far)</t>
         </is>
       </c>
-      <c r="C100" s="18" t="inlineStr">
+      <c r="C100" s="22" t="inlineStr">
         <is>
           <t>Chattanooga, TN; Digital — abstract book held — Fable extraction part-done (254 so far)</t>
         </is>
       </c>
-      <c r="D100" s="15" t="inlineStr">
+      <c r="D100" s="19" t="inlineStr">
         <is>
           <t>Leeuwarden; Ingested — 61 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E100" s="19" t="inlineStr">
+      <c r="E100" s="23" t="inlineStr">
         <is>
           <t>?; Pending — Brit Finucci collating; year/location to confirm</t>
         </is>
       </c>
-      <c r="F100" s="13" t="inlineStr">
+      <c r="F100" s="17" t="inlineStr">
         <is>
           <t>Durban; Missing — find source</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="12" t="n">
+      <c r="A101" s="16" t="n">
         <v>2015</v>
       </c>
-      <c r="B101" s="15" t="inlineStr">
+      <c r="B101" s="19" t="inlineStr">
         <is>
           <t>Reno, NV; Ingested</t>
         </is>
       </c>
-      <c r="C101" s="15" t="inlineStr">
+      <c r="C101" s="19" t="inlineStr">
         <is>
           <t>Reno, NV (118); Ingested</t>
         </is>
       </c>
-      <c r="D101" s="18" t="inlineStr">
+      <c r="D101" s="22" t="inlineStr">
         <is>
           <t>Peniche; Digital — 19th EEA Book of Abstracts (99pp, born-digital) held by Simon all along; queued for extraction</t>
         </is>
       </c>
-      <c r="E101" s="14" t="inlineStr"/>
-      <c r="F101" s="14" t="inlineStr"/>
+      <c r="E101" s="18" t="inlineStr"/>
+      <c r="F101" s="18" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="12" t="n">
+      <c r="A102" s="16" t="n">
         <v>2016</v>
       </c>
-      <c r="B102" s="15" t="inlineStr">
+      <c r="B102" s="19" t="inlineStr">
         <is>
           <t>New Orleans, LA; Ingested</t>
         </is>
       </c>
-      <c r="C102" s="15" t="inlineStr">
+      <c r="C102" s="19" t="inlineStr">
         <is>
           <t>New Orleans, LA (233); Ingested</t>
         </is>
       </c>
-      <c r="D102" s="15" t="inlineStr">
+      <c r="D102" s="19" t="inlineStr">
         <is>
           <t>Bristol; Ingested — 93 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E102" s="19" t="inlineStr">
+      <c r="E102" s="23" t="inlineStr">
         <is>
           <t>?; Pending — Brit Finucci collating; year/location to confirm</t>
         </is>
       </c>
-      <c r="F102" s="14" t="inlineStr"/>
+      <c r="F102" s="18" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="12" t="n">
+      <c r="A103" s="16" t="n">
         <v>2017</v>
       </c>
-      <c r="B103" s="18" t="inlineStr">
+      <c r="B103" s="22" t="inlineStr">
         <is>
           <t>Austin, TX; Digital — abstract book held (1 PDF) — extraction pending</t>
         </is>
       </c>
-      <c r="C103" s="18" t="inlineStr">
+      <c r="C103" s="22" t="inlineStr">
         <is>
           <t>Austin, TX; Digital — abstract book held (1 PDF) — extraction pending</t>
         </is>
       </c>
-      <c r="D103" s="21" t="inlineStr">
+      <c r="D103" s="25" t="inlineStr">
         <is>
           <t>Amsterdam; Schedule — 62 talks ingested, NO abstract bodies; Cat holds a hardcopy but has no scanning capacity; abstract book needed from NEV</t>
         </is>
       </c>
-      <c r="E103" s="14" t="inlineStr"/>
-      <c r="F103" s="14" t="inlineStr"/>
+      <c r="E103" s="18" t="inlineStr"/>
+      <c r="F103" s="18" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="12" t="n">
+      <c r="A104" s="16" t="n">
         <v>2018</v>
       </c>
-      <c r="B104" s="15" t="inlineStr">
+      <c r="B104" s="19" t="inlineStr">
         <is>
           <t>Rochester, NY; Ingested</t>
         </is>
       </c>
-      <c r="C104" s="14" t="inlineStr">
+      <c r="C104" s="18" t="inlineStr">
         <is>
           <t>NA — no AES meeting at JMIH — AES met at Sharks International (Joao Pessoa) instead; those abstracts are under SI 2018</t>
         </is>
       </c>
-      <c r="D104" s="15" t="inlineStr">
+      <c r="D104" s="19" t="inlineStr">
         <is>
           <t>Peniche; Ingested — 75 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E104" s="19" t="inlineStr">
+      <c r="E104" s="23" t="inlineStr">
         <is>
           <t>North Stradbroke Is.; Pending — Moreton Bay Research Station; Brit Finucci confirming</t>
         </is>
       </c>
-      <c r="F104" s="15" t="inlineStr">
+      <c r="F104" s="19" t="inlineStr">
         <is>
           <t>Joao Pessoa; Ingested</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="12" t="n">
+      <c r="A105" s="16" t="n">
         <v>2019</v>
       </c>
-      <c r="B105" s="15" t="inlineStr">
+      <c r="B105" s="19" t="inlineStr">
         <is>
           <t>Snowbird, UT; Ingested</t>
         </is>
       </c>
-      <c r="C105" s="15" t="inlineStr">
+      <c r="C105" s="19" t="inlineStr">
         <is>
           <t>Snowbird, UT (175); Ingested</t>
         </is>
       </c>
-      <c r="D105" s="15" t="inlineStr">
+      <c r="D105" s="19" t="inlineStr">
         <is>
           <t>Rende; Ingested — 136 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E105" s="14" t="inlineStr"/>
-      <c r="F105" s="14" t="inlineStr"/>
+      <c r="E105" s="18" t="inlineStr"/>
+      <c r="F105" s="18" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="12" t="n">
+      <c r="A106" s="16" t="n">
         <v>2020</v>
       </c>
-      <c r="B106" s="14" t="inlineStr">
+      <c r="B106" s="18" t="inlineStr">
         <is>
           <t>?; NA — no meeting — virtual BAAM-ZOOM sessions only, no abstract book</t>
         </is>
       </c>
-      <c r="C106" s="14" t="inlineStr">
+      <c r="C106" s="18" t="inlineStr">
         <is>
           <t>?; NA — no meeting — virtual BAAM-ZOOM sessions only, no abstract book</t>
         </is>
       </c>
-      <c r="D106" s="13" t="inlineStr">
+      <c r="D106" s="17" t="inlineStr">
         <is>
           <t>?; Missing — unknown whether a meeting was held: Cat thinks it was online for covid but was on maternity leave and is unsure; organiser unknown; abstracts unknown</t>
         </is>
       </c>
-      <c r="E106" s="19" t="inlineStr">
+      <c r="E106" s="23" t="inlineStr">
         <is>
           <t>?; Pending — Brit Finucci collating; year/location to confirm</t>
         </is>
       </c>
-      <c r="F106" s="14" t="inlineStr"/>
+      <c r="F106" s="18" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="12" t="n">
+      <c r="A107" s="16" t="n">
         <v>2021</v>
       </c>
-      <c r="B107" s="15" t="inlineStr">
+      <c r="B107" s="19" t="inlineStr">
         <is>
           <t>Phoenix, AZ; Ingested — Oxford Abstracts export (born-digital)</t>
         </is>
       </c>
-      <c r="C107" s="15" t="inlineStr">
+      <c r="C107" s="19" t="inlineStr">
         <is>
           <t>Phoenix, AZ (67); Ingested — Oxford Abstracts export (born-digital)</t>
         </is>
       </c>
-      <c r="D107" s="22" t="inlineStr">
+      <c r="D107" s="26" t="inlineStr">
         <is>
           <t>Leiden; Programme — programme only; abstract book needed from NEV</t>
         </is>
       </c>
-      <c r="E107" s="14" t="inlineStr"/>
-      <c r="F107" s="14" t="inlineStr"/>
+      <c r="E107" s="18" t="inlineStr"/>
+      <c r="F107" s="18" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="12" t="n">
+      <c r="A108" s="16" t="n">
         <v>2022</v>
       </c>
-      <c r="B108" s="21" t="inlineStr">
+      <c r="B108" s="25" t="inlineStr">
         <is>
           <t>Spokane, WA; Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="C108" s="21" t="inlineStr">
+      <c r="C108" s="25" t="inlineStr">
         <is>
           <t>Spokane, WA (68); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="D108" s="18" t="inlineStr">
+      <c r="D108" s="22" t="inlineStr">
         <is>
           <t>Valencia (=SI2022); Digital — full SI2022 abstract book received 2026-08-27; queued for extraction</t>
         </is>
       </c>
-      <c r="E108" s="19" t="inlineStr">
+      <c r="E108" s="23" t="inlineStr">
         <is>
           <t>?; Pending — Brit Finucci collating; year/location to confirm</t>
         </is>
       </c>
-      <c r="F108" s="18" t="inlineStr">
+      <c r="F108" s="22" t="inlineStr">
         <is>
           <t>Valencia; Digital — full abstract book received 2026-08-27; queued (schedule already ingested)</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="12" t="n">
+      <c r="A109" s="16" t="n">
         <v>2023</v>
       </c>
-      <c r="B109" s="15" t="inlineStr">
+      <c r="B109" s="19" t="inlineStr">
         <is>
           <t>Norfolk, VA; Ingested</t>
         </is>
       </c>
-      <c r="C109" s="15" t="inlineStr">
+      <c r="C109" s="19" t="inlineStr">
         <is>
           <t>Norfolk, VA (154); Ingested</t>
         </is>
       </c>
-      <c r="D109" s="15" t="inlineStr">
+      <c r="D109" s="19" t="inlineStr">
         <is>
           <t>Brighton; Ingested — oral 64 + poster 34 = 98 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E109" s="14" t="inlineStr"/>
-      <c r="F109" s="14" t="inlineStr"/>
+      <c r="E109" s="18" t="inlineStr"/>
+      <c r="F109" s="18" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="12" t="n">
+      <c r="A110" s="16" t="n">
         <v>2024</v>
       </c>
-      <c r="B110" s="15" t="inlineStr">
+      <c r="B110" s="19" t="inlineStr">
         <is>
           <t>Pittsburgh, PA; Ingested</t>
         </is>
       </c>
-      <c r="C110" s="15" t="inlineStr">
+      <c r="C110" s="19" t="inlineStr">
         <is>
           <t>Pittsburgh, PA (148); Ingested</t>
         </is>
       </c>
-      <c r="D110" s="18" t="inlineStr">
+      <c r="D110" s="22" t="inlineStr">
         <is>
           <t>Thessaloniki; Digital — clean abstract book received from Cat 2026-08-27; queued for extraction</t>
         </is>
       </c>
-      <c r="E110" s="19" t="inlineStr">
+      <c r="E110" s="23" t="inlineStr">
         <is>
           <t>Geelong; Pending — Brit Finucci confirming</t>
         </is>
       </c>
-      <c r="F110" s="14" t="inlineStr"/>
+      <c r="F110" s="18" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="12" t="n">
+      <c r="A111" s="16" t="n">
         <v>2025</v>
       </c>
-      <c r="B111" s="21" t="inlineStr">
+      <c r="B111" s="25" t="inlineStr">
         <is>
           <t>St. Paul, MN; Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="C111" s="21" t="inlineStr">
+      <c r="C111" s="25" t="inlineStr">
         <is>
           <t>St. Paul, MN (68); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="D111" s="22" t="inlineStr">
+      <c r="D111" s="26" t="inlineStr">
         <is>
           <t>Rotterdam; Programme — agenda only; Cat has no abstract book and is unsure one was produced; NEV/Irene to confirm whether it exists</t>
         </is>
       </c>
-      <c r="E111" s="14" t="inlineStr"/>
-      <c r="F111" s="14" t="inlineStr"/>
+      <c r="E111" s="18" t="inlineStr"/>
+      <c r="F111" s="18" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="12" t="n">
+      <c r="A112" s="16" t="n">
         <v>2026</v>
       </c>
-      <c r="B112" s="18" t="inlineStr">
+      <c r="B112" s="22" t="inlineStr">
         <is>
           <t>New Orleans, LA; Digital — abstract book held (1 PDF) — extraction pending</t>
         </is>
       </c>
-      <c r="C112" s="18" t="inlineStr">
+      <c r="C112" s="22" t="inlineStr">
         <is>
           <t>New Orleans, LA; Digital — abstract book held (1 PDF) — extraction pending</t>
         </is>
       </c>
-      <c r="D112" s="19" t="inlineStr">
+      <c r="D112" s="23" t="inlineStr">
         <is>
           <t>online; Pending — will be digital (Shark Trust hosting)</t>
         </is>
       </c>
-      <c r="E112" s="19" t="inlineStr">
+      <c r="E112" s="23" t="inlineStr">
         <is>
           <t>?; Pending — Brit Finucci collating; year/location to confirm</t>
         </is>
       </c>
-      <c r="F112" s="15" t="inlineStr">
+      <c r="F112" s="19" t="inlineStr">
         <is>
           <t>Colombo; Ingested</t>
         </is>
@@ -3271,7 +4073,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3284,7 +4086,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>Conference abstract coverage — dashboard</t>
         </is>

--- a/database/conference_coverage_matrix.xlsx
+++ b/database/conference_coverage_matrix.xlsx
@@ -3849,7 +3849,7 @@
       </c>
       <c r="C104" s="18" t="inlineStr">
         <is>
-          <t>NA — no AES meeting at JMIH — AES met at Sharks International (Joao Pessoa) instead; those abstracts are under SI 2018</t>
+          <t>Joao Pessoa (at SI); NA — no AES meeting at JMIH — AES met at Sharks International instead, so those abstracts are under SI 2018</t>
         </is>
       </c>
       <c r="D104" s="19" t="inlineStr">

--- a/database/conference_coverage_matrix.xlsx
+++ b/database/conference_coverage_matrix.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Conferences'!$A$1:$H$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Conferences'!$A$1:$H$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1337,7 +1337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1560,15 +1560,19 @@
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>Rotating local host. 2010 Cairns, 2014 Durban, 2018 Joao Pessoa, 2022 Valencia, 2026 Colombo (Blue Resources Trust).</t>
+          <t>Rotating local host. 2010 Cairns (6-11 June, Rydges Esplanade Resort; host body NOT FOUND). 2014 Durban (2-6 June), hosted by the KwaZulu-Natal Sharks Board; 169 orals + 52 posters, which matches the 170 records we want almost exactly. 2018 Joao Pessoa, UFPB, joint with AES, SBEEL and Fundacion SQUALUS. 2022 Valencia. 2026 Colombo, hosted by Blue Resources Trust.</t>
         </is>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>https://www.sharksinternational.org.br/noticia/23-abstract-book/menu_abstract_book.html (2018 book)</t>
-        </is>
-      </c>
-      <c r="H6" s="13" t="inlineStr"/>
+          <t>https://www.sharksinternational.org.br/noticia/23-abstract-book/menu_abstract_book.html (2018 book, which we hold)</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>sharksinternational2014@gmail.com (2014 organising committee, from the KZN Sharks Board announcement; may be dormant)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -1590,7 +1594,7 @@
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>Fundacion SQUALUS. I 2008 Bogota, II 2010 Cali, III 2012 Santa Marta, IV 2014 Medellin, V 2016 Bogota, VI 2018 Joao Pessoa (co-located with Sharks International 2018, so check the SI 2018 book first).</t>
+          <t>Fundacion SQUALUS. I 2008 Bogota, II 2010 Cali, III 2012 Santa Marta, IV 2014 Medellin, V 2016 Bogota, VI 2018 Joao Pessoa. CONFIRMED 2026-09-04: the VI IS ALREADY HELD — the SI 2018 book is the joint book for four meetings at once (Sharks International, the 34th AES annual meeting, the X SBEEL Reuniao and the VI ECC), and we have its 427 abstracts. So the ask is editions I-V, and the corpus cites only the IV.</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
@@ -1607,11 +1611,11 @@
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>Simposio Nacional de Tiburones y Rayas (SOMEPEC, Mexico)</t>
+          <t>Sociedade Brasileira para o Estudo de Elasmobranquios (SBEEL)</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>2004</v>
+        <v>1997</v>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
@@ -1622,78 +1626,78 @@
         <v>2</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>Sociedad Mexicana de Peces Cartilaginosos (SOMEPEC). Editions seen: III 2008, IV 2010 (UNAM), V, VI 2014 Mazatlan, VIII 2019 Playa del Carmen (joint with the I Congreso Latinoamericano de Tiburones, Rayas y Quimeras), XI recent.</t>
-        </is>
-      </c>
-      <c r="G8" s="13" t="inlineStr">
-        <is>
-          <t>Memorias/resumenes posted on ResearchGate and via facebook.com/Somepec2</t>
-        </is>
-      </c>
+          <t>SBEEL. The X Reuniao was held in 2018 inside the Sharks International book, so at least nine earlier meetings exist. The corpus cites only the II, which is why n_needed is 1 — that number is a floor and badly understates this series.</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr"/>
       <c r="H8" s="13" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>Colloque international requins en Afrique de l'Ouest</t>
+          <t>Simposio Nacional de Tiburones y Rayas (SOMEPEC, Mexico)</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>2011</v>
-      </c>
-      <c r="C9" s="12" t="n">
-        <v>2011</v>
+        <v>2004</v>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>Commission Sous-Regionale des Peches (CSRP / SRFC). Dakar, Senegal, 25-27 July 2011. One-off as far as we can tell.</t>
+          <t>Sociedad Mexicana de Peces Cartilaginosos (SOMEPEC). HARVESTED 2026-09-04 from somepec.org, no request to anyone needed: I 2004 (with the III Semana del Tiburon, UNAM), III 2008, IV 2010 (UNAM), VII 2016, XI 2025 as abstract books, plus the IX 2021 programme. All five books carry a clean text layer. STILL MISSING: II, V, VI 2014 Mazatlan (the edition our corpus cites), VIII 2019 Playa del Carmen (joint with the I Congreso Latinoamericano de Tiburones, Rayas y Quimeras), and X. Ask info@somepec.org for exactly those five.</t>
         </is>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
-          <t>https://spcsrp.org/</t>
-        </is>
-      </c>
-      <c r="H9" s="13" t="inlineStr"/>
+          <t>https://somepec.org/memorias/ ; back volumes under https://somepec.org/wp-content/uploads/ ; scraper scripts/conf_abstracts/scrape_somepec.py</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>info@somepec.org ; +52 55 5034 1708</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Gulf and Caribbean Fisheries Institute (GCFI)</t>
+          <t>Colloque international requins en Afrique de l'Ouest</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>1948</v>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>ongoing</t>
-        </is>
+        <v>2011</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>2011</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>GCFI secretariat. Every meeting since 1948 is published in the annual Proceedings, so this is a library request, not an ask of a person.</t>
+          <t>Commission Sous-Regionale des Peches (CSRP / SRFC), an intergovernmental body for seven West African states. Dakar, Senegal, 25-27 July 2011, on the conservation and sustainable management of shark populations in West Africa. A single meeting, not a series — kept on the list anyway: 48 abstracts is one email and one book, and it is the only West African material in the corpus.</t>
         </is>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>https://www.gcfi.org/ ; back proceedings in the NOAA Institutional Repository, https://repository.library.noaa.gov/</t>
+          <t>https://spcsrp.org/</t>
         </is>
       </c>
       <c r="H10" s="13" t="inlineStr"/>
@@ -1701,65 +1705,65 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>Pacific Shark Workshop</t>
+          <t>Gulf and Caribbean Fisheries Institute (GCFI)</t>
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>2011</v>
-      </c>
-      <c r="C11" s="12" t="n">
-        <v>2012</v>
+        <v>1948</v>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="F11" s="13" t="inlineStr"/>
-      <c r="G11" s="13" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>GCFI secretariat. Every meeting since 1948 is in the annual Proceedings and every PAPER is a free PDF at proceedings.gcfi.org (verified 2026-09-04), so nobody needs asking and nobody should be assigned these. The 31 corpus records were sitting on the needs-library queue and are now acquisition_route=gcfi_proceedings.</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>https://proceedings.gcfi.org/ (per-paper PDFs) ; https://www.gcfi.org/ ; back volumes also in the NOAA Institutional Repository</t>
+        </is>
+      </c>
       <c r="H11" s="13" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>ISC Shark Working Group</t>
+          <t>Pacific Shark Workshop</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>2013</v>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>ongoing</t>
-        </is>
+        <v>2011</v>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>2012</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>International Scientific Committee for Tuna and Tuna-like Species in the North Pacific Ocean; the Shark Working Group meets within it.</t>
-        </is>
-      </c>
-      <c r="G12" s="13" t="inlineStr">
-        <is>
-          <t>https://isc.fra.go.jp/</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F12" s="13" t="inlineStr"/>
+      <c r="G12" s="13" t="inlineStr"/>
       <c r="H12" s="13" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>World Congress of Herpetology</t>
+          <t>ISC Shark Working Group</t>
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>1989</v>
+        <v>2013</v>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
@@ -1767,19 +1771,19 @@
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>World Congress of Herpetology committee. Every 3-5 years.</t>
+          <t>International Scientific Committee for Tuna and Tuna-like Species in the North Pacific Ocean; the Shark Working Group meets within it.</t>
         </is>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
-          <t>https://www.worldcongressofherpetology.org/</t>
+          <t>https://isc.fra.go.jp/</t>
         </is>
       </c>
       <c r="H13" s="13" t="inlineStr"/>
@@ -1787,11 +1791,11 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>Indo-Pacific Fish Conference (IPFC)</t>
+          <t>World Congress of Herpetology</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>1981</v>
+        <v>1989</v>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
@@ -1802,16 +1806,16 @@
         <v>4</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>Rotating host. IPFC-11 2023 Auckland (joint with ASFB); IPFC-12 2025 Taiwan.</t>
+          <t>World Congress of Herpetology committee. Every 3-5 years.</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>https://sfi-cybium.fr/en/indo-pacific-fish-conference</t>
+          <t>https://www.worldcongressofherpetology.org/</t>
         </is>
       </c>
       <c r="H14" s="13" t="inlineStr"/>
@@ -1819,11 +1823,11 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>International Coral Reef Symposium (ICRS)</t>
+          <t>Indo-Pacific Fish Conference (IPFC)</t>
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>1969</v>
+        <v>1981</v>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
@@ -1834,16 +1838,16 @@
         <v>4</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>International Coral Reef Society. ICRS-16 2026 Auckland.</t>
+          <t>Rotating host. IPFC-11 2023 Auckland (joint with ASFB); IPFC-12 2025 Taiwan.</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>https://coralreefs.org/</t>
+          <t>https://sfi-cybium.fr/en/indo-pacific-fish-conference</t>
         </is>
       </c>
       <c r="H15" s="13" t="inlineStr"/>
@@ -1851,11 +1855,11 @@
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>World Fisheries Congress</t>
+          <t>International Coral Reef Symposium (ICRS)</t>
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>1992</v>
+        <v>1969</v>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
@@ -1866,20 +1870,28 @@
         <v>4</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="F16" s="13" t="inlineStr"/>
-      <c r="G16" s="13" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>International Coral Reef Society. ICRS-16 2026 Auckland.</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>https://coralreefs.org/</t>
+        </is>
+      </c>
       <c r="H16" s="13" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>American Fisheries Society symposia</t>
+          <t>World Fisheries Congress</t>
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>1870</v>
+        <v>1992</v>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
@@ -1887,31 +1899,23 @@
         </is>
       </c>
       <c r="D17" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="F17" s="13" t="inlineStr">
-        <is>
-          <t>American Fisheries Society.</t>
-        </is>
-      </c>
-      <c r="G17" s="13" t="inlineStr">
-        <is>
-          <t>https://fisheries.org/</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F17" s="13" t="inlineStr"/>
+      <c r="G17" s="13" t="inlineStr"/>
       <c r="H17" s="13" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>International Congress on the Biology of Fish</t>
+          <t>American Fisheries Society symposia</t>
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>1994</v>
+        <v>1870</v>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
@@ -1919,23 +1923,31 @@
         </is>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="F18" s="13" t="inlineStr"/>
-      <c r="G18" s="13" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>American Fisheries Society.</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>https://fisheries.org/</t>
+        </is>
+      </c>
       <c r="H18" s="13" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>International Meeting on Mesozoic Fishes</t>
+          <t>International Congress on the Biology of Fish</t>
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
@@ -1943,27 +1955,23 @@
         </is>
       </c>
       <c r="D19" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="E19" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="F19" s="13" t="inlineStr">
-        <is>
-          <t>Meeting conveners vary; 6th meeting edited by Schwarz &amp; Kriwet.</t>
-        </is>
-      </c>
+      <c r="F19" s="13" t="inlineStr"/>
       <c r="G19" s="13" t="inlineStr"/>
       <c r="H19" s="13" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>International Congress of Vertebrate Morphology (ICVM)</t>
+          <t>International Meeting on Mesozoic Fishes</t>
         </is>
       </c>
       <c r="B20" s="12" t="n">
-        <v>1986</v>
+        <v>1993</v>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
@@ -1971,23 +1979,27 @@
         </is>
       </c>
       <c r="D20" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="13" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>Meeting conveners vary; 6th meeting edited by Schwarz &amp; Kriwet.</t>
+        </is>
+      </c>
       <c r="G20" s="13" t="inlineStr"/>
       <c r="H20" s="13" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>CIESM Congress (Mediterranean Science Commission)</t>
+          <t>International Congress of Vertebrate Morphology (ICVM)</t>
         </is>
       </c>
       <c r="B21" s="12" t="n">
-        <v>1919</v>
+        <v>1986</v>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
@@ -2000,26 +2012,18 @@
       <c r="E21" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="13" t="inlineStr">
-        <is>
-          <t>Commission Internationale pour l'Exploration Scientifique de la Mer Mediterranee.</t>
-        </is>
-      </c>
-      <c r="G21" s="13" t="inlineStr">
-        <is>
-          <t>https://ciesm.org/</t>
-        </is>
-      </c>
+      <c r="F21" s="13" t="inlineStr"/>
+      <c r="G21" s="13" t="inlineStr"/>
       <c r="H21" s="13" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>Albert L. Tester Memorial Symposium</t>
+          <t>CIESM Congress (Mediterranean Science Commission)</t>
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>1976</v>
+        <v>1919</v>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
@@ -2027,92 +2031,124 @@
         </is>
       </c>
       <c r="D22" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>University of Hawaii at Manoa.</t>
-        </is>
-      </c>
-      <c r="G22" s="13" t="inlineStr"/>
+          <t>Commission Internationale pour l'Exploration Scientifique de la Mer Mediterranee.</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>https://ciesm.org/</t>
+        </is>
+      </c>
       <c r="H22" s="13" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Workshop on Age Determination of Oceanic Pelagic Fishes</t>
+          <t>Albert L. Tester Memorial Symposium</t>
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>1983</v>
-      </c>
-      <c r="C23" s="12" t="n">
-        <v>1983</v>
+        <v>1976</v>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="F23" s="13" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>University of Hawaii at Manoa.</t>
+        </is>
+      </c>
       <c r="G23" s="13" t="inlineStr"/>
       <c r="H23" s="13" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Palaeontology / geology meetings (assorted)</t>
+          <t>Workshop on Age Determination of Oceanic Pelagic Fishes</t>
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>1973</v>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>ongoing</t>
-        </is>
+        <v>1983</v>
+      </c>
+      <c r="C24" s="12" t="n">
+        <v>1983</v>
       </c>
       <c r="D24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>81</v>
-      </c>
-      <c r="F24" s="13" t="inlineStr">
-        <is>
-          <t>NOT ONE SERIES — a bucket of many national and international palaeo and geology meetings. Split it before chasing anyone.</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="F24" s="13" t="inlineStr"/>
       <c r="G24" s="13" t="inlineStr"/>
       <c r="H24" s="13" t="inlineStr"/>
     </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>frequency: 1 = annual, 2 = biennial, 3 = every three years, 4 = every four years, 0 = one-off / irregular</t>
-        </is>
-      </c>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Palaeontology / geology meetings (assorted)</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="n">
+        <v>1973</v>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>NOT ONE SERIES — a bucket of many national and international palaeo and geology meetings. Split it before chasing anyone.</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr"/>
+      <c r="H25" s="13" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>n_needed: corpus records citing that series whose PDF we do NOT hold (scripts/conf_abstracts/conference_lead_candidates.py). It counts abstracts we can already name, so it is a floor, not the size of the series.</t>
+          <t>frequency: 1 = annual, 2 = biennial, 3 = every three years, 4 = every four years, 0 = one-off / irregular</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
+          <t>n_needed: corpus records citing that series whose PDF we do NOT hold (scripts/conf_abstracts/conference_lead_candidates.py). It counts abstracts we can already name, so it is a floor, not the size of the series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
           <t>A BLANK organisers/website/contact means not found on 2026-09-04, never a guess — a wrong address costs a real email to a real person.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H24"/>
+  <autoFilter ref="A1:H25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/database/conference_coverage_matrix.xlsx
+++ b/database/conference_coverage_matrix.xlsx
@@ -1560,7 +1560,7 @@
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>Rotating local host. 2010 Cairns (6-11 June, Rydges Esplanade Resort; host body NOT FOUND). 2014 Durban (2-6 June), hosted by the KwaZulu-Natal Sharks Board; 169 orals + 52 posters, which matches the 170 records we want almost exactly. 2018 Joao Pessoa, UFPB, joint with AES, SBEEL and Fundacion SQUALUS. 2022 Valencia. 2026 Colombo, hosted by Blue Resources Trust.</t>
+          <t>Rotating local host, and the SI 2018 book's executive and scientific committees carry the previous hosts forward, which is the best evidence available for who ran the early ones. 2010 CAIRNS (6-11 June, Rydges Esplanade Resort): no source names the host body. Michelle Heupel (AIMS / James Cook University) is the sole Australian on the 2018 committee, consistent with Simon's recollection of Heupel and Colin Simpfendorfer (also JCU) running it. TREAT AS LIKELY, NOT CONFIRMED. 2014 DURBAN (2-6 June): hosted by the KwaZulu-Natal Sharks Board, 169 orals + 52 posters, which matches the 170 records we want almost exactly. Geremy Cliff (Head of Research at the KZN Sharks Board for ~30 years) sits on the 2018 committee and is the obvious approach; Sabine Wintner (KZNSB / UKZN) is the other senior elasmobranch scientist there. No source names the committee chair. 2018 Joao Pessoa: UFPB, president Ricardo de Souza Rosa, joint with AES, SBEEL and Fundacion SQUALUS. 2022 Valencia. 2026 Colombo, hosted by Blue Resources Trust.</t>
         </is>
       </c>
       <c r="G6" s="13" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>sharksinternational2014@gmail.com (2014 organising committee, from the KZN Sharks Board announcement; may be dormant)</t>
+          <t>sharksinternational2014@gmail.com (2014 organising committee, from the KZN Sharks Board announcement; likely dormant — go via Geremy Cliff or Sabine Wintner at the KZN Sharks Board for 2014, and Michelle Heupel or Colin Simpfendorfer for 2010)</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F112"/>
+  <dimension ref="A1:Y112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2168,6 +2168,25 @@
     <col width="44" customWidth="1" min="4" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
     <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="19" max="19"/>
+    <col width="30" customWidth="1" min="20" max="20"/>
+    <col width="30" customWidth="1" min="21" max="21"/>
+    <col width="30" customWidth="1" min="22" max="22"/>
+    <col width="30" customWidth="1" min="23" max="23"/>
+    <col width="30" customWidth="1" min="24" max="24"/>
+    <col width="30" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2201,6 +2220,101 @@
           <t>SI</t>
         </is>
       </c>
+      <c r="G1" s="15" t="inlineStr">
+        <is>
+          <t>ECC</t>
+        </is>
+      </c>
+      <c r="H1" s="15" t="inlineStr">
+        <is>
+          <t>SBEEL</t>
+        </is>
+      </c>
+      <c r="I1" s="15" t="inlineStr">
+        <is>
+          <t>SOMEPEC</t>
+        </is>
+      </c>
+      <c r="J1" s="15" t="inlineStr">
+        <is>
+          <t>W Africa</t>
+        </is>
+      </c>
+      <c r="K1" s="15" t="inlineStr">
+        <is>
+          <t>GCFI</t>
+        </is>
+      </c>
+      <c r="L1" s="15" t="inlineStr">
+        <is>
+          <t>Pac Shark Wksp</t>
+        </is>
+      </c>
+      <c r="M1" s="15" t="inlineStr">
+        <is>
+          <t>ISC Shark WG</t>
+        </is>
+      </c>
+      <c r="N1" s="15" t="inlineStr">
+        <is>
+          <t>WCH</t>
+        </is>
+      </c>
+      <c r="O1" s="15" t="inlineStr">
+        <is>
+          <t>IPFC</t>
+        </is>
+      </c>
+      <c r="P1" s="15" t="inlineStr">
+        <is>
+          <t>ICRS</t>
+        </is>
+      </c>
+      <c r="Q1" s="15" t="inlineStr">
+        <is>
+          <t>WFC</t>
+        </is>
+      </c>
+      <c r="R1" s="15" t="inlineStr">
+        <is>
+          <t>AFS</t>
+        </is>
+      </c>
+      <c r="S1" s="15" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="T1" s="15" t="inlineStr">
+        <is>
+          <t>Mesozoic Fishes</t>
+        </is>
+      </c>
+      <c r="U1" s="15" t="inlineStr">
+        <is>
+          <t>ICVM</t>
+        </is>
+      </c>
+      <c r="V1" s="15" t="inlineStr">
+        <is>
+          <t>CIESM</t>
+        </is>
+      </c>
+      <c r="W1" s="15" t="inlineStr">
+        <is>
+          <t>Tester Symp</t>
+        </is>
+      </c>
+      <c r="X1" s="15" t="inlineStr">
+        <is>
+          <t>Age Det Wksp</t>
+        </is>
+      </c>
+      <c r="Y1" s="15" t="inlineStr">
+        <is>
+          <t>Palaeo/geol</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="16" t="n">
@@ -2215,6 +2329,25 @@
       <c r="D2" s="18" t="inlineStr"/>
       <c r="E2" s="18" t="inlineStr"/>
       <c r="F2" s="18" t="inlineStr"/>
+      <c r="G2" s="18" t="inlineStr"/>
+      <c r="H2" s="18" t="inlineStr"/>
+      <c r="I2" s="18" t="inlineStr"/>
+      <c r="J2" s="18" t="inlineStr"/>
+      <c r="K2" s="18" t="inlineStr"/>
+      <c r="L2" s="18" t="inlineStr"/>
+      <c r="M2" s="18" t="inlineStr"/>
+      <c r="N2" s="18" t="inlineStr"/>
+      <c r="O2" s="18" t="inlineStr"/>
+      <c r="P2" s="18" t="inlineStr"/>
+      <c r="Q2" s="18" t="inlineStr"/>
+      <c r="R2" s="18" t="inlineStr"/>
+      <c r="S2" s="18" t="inlineStr"/>
+      <c r="T2" s="18" t="inlineStr"/>
+      <c r="U2" s="18" t="inlineStr"/>
+      <c r="V2" s="18" t="inlineStr"/>
+      <c r="W2" s="18" t="inlineStr"/>
+      <c r="X2" s="18" t="inlineStr"/>
+      <c r="Y2" s="18" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="16" t="n">
@@ -2229,6 +2362,25 @@
       <c r="D3" s="18" t="inlineStr"/>
       <c r="E3" s="18" t="inlineStr"/>
       <c r="F3" s="18" t="inlineStr"/>
+      <c r="G3" s="18" t="inlineStr"/>
+      <c r="H3" s="18" t="inlineStr"/>
+      <c r="I3" s="18" t="inlineStr"/>
+      <c r="J3" s="18" t="inlineStr"/>
+      <c r="K3" s="18" t="inlineStr"/>
+      <c r="L3" s="18" t="inlineStr"/>
+      <c r="M3" s="18" t="inlineStr"/>
+      <c r="N3" s="18" t="inlineStr"/>
+      <c r="O3" s="18" t="inlineStr"/>
+      <c r="P3" s="18" t="inlineStr"/>
+      <c r="Q3" s="18" t="inlineStr"/>
+      <c r="R3" s="18" t="inlineStr"/>
+      <c r="S3" s="18" t="inlineStr"/>
+      <c r="T3" s="18" t="inlineStr"/>
+      <c r="U3" s="18" t="inlineStr"/>
+      <c r="V3" s="18" t="inlineStr"/>
+      <c r="W3" s="18" t="inlineStr"/>
+      <c r="X3" s="18" t="inlineStr"/>
+      <c r="Y3" s="18" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="16" t="n">
@@ -2243,6 +2395,25 @@
       <c r="D4" s="18" t="inlineStr"/>
       <c r="E4" s="18" t="inlineStr"/>
       <c r="F4" s="18" t="inlineStr"/>
+      <c r="G4" s="18" t="inlineStr"/>
+      <c r="H4" s="18" t="inlineStr"/>
+      <c r="I4" s="18" t="inlineStr"/>
+      <c r="J4" s="18" t="inlineStr"/>
+      <c r="K4" s="18" t="inlineStr"/>
+      <c r="L4" s="18" t="inlineStr"/>
+      <c r="M4" s="18" t="inlineStr"/>
+      <c r="N4" s="18" t="inlineStr"/>
+      <c r="O4" s="18" t="inlineStr"/>
+      <c r="P4" s="18" t="inlineStr"/>
+      <c r="Q4" s="18" t="inlineStr"/>
+      <c r="R4" s="18" t="inlineStr"/>
+      <c r="S4" s="18" t="inlineStr"/>
+      <c r="T4" s="18" t="inlineStr"/>
+      <c r="U4" s="18" t="inlineStr"/>
+      <c r="V4" s="18" t="inlineStr"/>
+      <c r="W4" s="18" t="inlineStr"/>
+      <c r="X4" s="18" t="inlineStr"/>
+      <c r="Y4" s="18" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="16" t="n">
@@ -2257,6 +2428,25 @@
       <c r="D5" s="18" t="inlineStr"/>
       <c r="E5" s="18" t="inlineStr"/>
       <c r="F5" s="18" t="inlineStr"/>
+      <c r="G5" s="18" t="inlineStr"/>
+      <c r="H5" s="18" t="inlineStr"/>
+      <c r="I5" s="18" t="inlineStr"/>
+      <c r="J5" s="18" t="inlineStr"/>
+      <c r="K5" s="18" t="inlineStr"/>
+      <c r="L5" s="18" t="inlineStr"/>
+      <c r="M5" s="18" t="inlineStr"/>
+      <c r="N5" s="18" t="inlineStr"/>
+      <c r="O5" s="18" t="inlineStr"/>
+      <c r="P5" s="18" t="inlineStr"/>
+      <c r="Q5" s="18" t="inlineStr"/>
+      <c r="R5" s="18" t="inlineStr"/>
+      <c r="S5" s="18" t="inlineStr"/>
+      <c r="T5" s="18" t="inlineStr"/>
+      <c r="U5" s="18" t="inlineStr"/>
+      <c r="V5" s="18" t="inlineStr"/>
+      <c r="W5" s="18" t="inlineStr"/>
+      <c r="X5" s="18" t="inlineStr"/>
+      <c r="Y5" s="18" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="16" t="n">
@@ -2271,6 +2461,25 @@
       <c r="D6" s="18" t="inlineStr"/>
       <c r="E6" s="18" t="inlineStr"/>
       <c r="F6" s="18" t="inlineStr"/>
+      <c r="G6" s="18" t="inlineStr"/>
+      <c r="H6" s="18" t="inlineStr"/>
+      <c r="I6" s="18" t="inlineStr"/>
+      <c r="J6" s="18" t="inlineStr"/>
+      <c r="K6" s="18" t="inlineStr"/>
+      <c r="L6" s="18" t="inlineStr"/>
+      <c r="M6" s="18" t="inlineStr"/>
+      <c r="N6" s="18" t="inlineStr"/>
+      <c r="O6" s="18" t="inlineStr"/>
+      <c r="P6" s="18" t="inlineStr"/>
+      <c r="Q6" s="18" t="inlineStr"/>
+      <c r="R6" s="18" t="inlineStr"/>
+      <c r="S6" s="18" t="inlineStr"/>
+      <c r="T6" s="18" t="inlineStr"/>
+      <c r="U6" s="18" t="inlineStr"/>
+      <c r="V6" s="18" t="inlineStr"/>
+      <c r="W6" s="18" t="inlineStr"/>
+      <c r="X6" s="18" t="inlineStr"/>
+      <c r="Y6" s="18" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="16" t="n">
@@ -2285,6 +2494,25 @@
       <c r="D7" s="18" t="inlineStr"/>
       <c r="E7" s="18" t="inlineStr"/>
       <c r="F7" s="18" t="inlineStr"/>
+      <c r="G7" s="18" t="inlineStr"/>
+      <c r="H7" s="18" t="inlineStr"/>
+      <c r="I7" s="18" t="inlineStr"/>
+      <c r="J7" s="18" t="inlineStr"/>
+      <c r="K7" s="18" t="inlineStr"/>
+      <c r="L7" s="18" t="inlineStr"/>
+      <c r="M7" s="18" t="inlineStr"/>
+      <c r="N7" s="18" t="inlineStr"/>
+      <c r="O7" s="18" t="inlineStr"/>
+      <c r="P7" s="18" t="inlineStr"/>
+      <c r="Q7" s="18" t="inlineStr"/>
+      <c r="R7" s="18" t="inlineStr"/>
+      <c r="S7" s="18" t="inlineStr"/>
+      <c r="T7" s="18" t="inlineStr"/>
+      <c r="U7" s="18" t="inlineStr"/>
+      <c r="V7" s="18" t="inlineStr"/>
+      <c r="W7" s="18" t="inlineStr"/>
+      <c r="X7" s="18" t="inlineStr"/>
+      <c r="Y7" s="18" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="16" t="n">
@@ -2299,6 +2527,25 @@
       <c r="D8" s="18" t="inlineStr"/>
       <c r="E8" s="18" t="inlineStr"/>
       <c r="F8" s="18" t="inlineStr"/>
+      <c r="G8" s="18" t="inlineStr"/>
+      <c r="H8" s="18" t="inlineStr"/>
+      <c r="I8" s="18" t="inlineStr"/>
+      <c r="J8" s="18" t="inlineStr"/>
+      <c r="K8" s="18" t="inlineStr"/>
+      <c r="L8" s="18" t="inlineStr"/>
+      <c r="M8" s="18" t="inlineStr"/>
+      <c r="N8" s="18" t="inlineStr"/>
+      <c r="O8" s="18" t="inlineStr"/>
+      <c r="P8" s="18" t="inlineStr"/>
+      <c r="Q8" s="18" t="inlineStr"/>
+      <c r="R8" s="18" t="inlineStr"/>
+      <c r="S8" s="18" t="inlineStr"/>
+      <c r="T8" s="18" t="inlineStr"/>
+      <c r="U8" s="18" t="inlineStr"/>
+      <c r="V8" s="18" t="inlineStr"/>
+      <c r="W8" s="18" t="inlineStr"/>
+      <c r="X8" s="18" t="inlineStr"/>
+      <c r="Y8" s="18" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="16" t="n">
@@ -2313,6 +2560,25 @@
       <c r="D9" s="18" t="inlineStr"/>
       <c r="E9" s="18" t="inlineStr"/>
       <c r="F9" s="18" t="inlineStr"/>
+      <c r="G9" s="18" t="inlineStr"/>
+      <c r="H9" s="18" t="inlineStr"/>
+      <c r="I9" s="18" t="inlineStr"/>
+      <c r="J9" s="18" t="inlineStr"/>
+      <c r="K9" s="18" t="inlineStr"/>
+      <c r="L9" s="18" t="inlineStr"/>
+      <c r="M9" s="18" t="inlineStr"/>
+      <c r="N9" s="18" t="inlineStr"/>
+      <c r="O9" s="18" t="inlineStr"/>
+      <c r="P9" s="18" t="inlineStr"/>
+      <c r="Q9" s="18" t="inlineStr"/>
+      <c r="R9" s="18" t="inlineStr"/>
+      <c r="S9" s="18" t="inlineStr"/>
+      <c r="T9" s="18" t="inlineStr"/>
+      <c r="U9" s="18" t="inlineStr"/>
+      <c r="V9" s="18" t="inlineStr"/>
+      <c r="W9" s="18" t="inlineStr"/>
+      <c r="X9" s="18" t="inlineStr"/>
+      <c r="Y9" s="18" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="16" t="n">
@@ -2327,6 +2593,25 @@
       <c r="D10" s="18" t="inlineStr"/>
       <c r="E10" s="18" t="inlineStr"/>
       <c r="F10" s="18" t="inlineStr"/>
+      <c r="G10" s="18" t="inlineStr"/>
+      <c r="H10" s="18" t="inlineStr"/>
+      <c r="I10" s="18" t="inlineStr"/>
+      <c r="J10" s="18" t="inlineStr"/>
+      <c r="K10" s="18" t="inlineStr"/>
+      <c r="L10" s="18" t="inlineStr"/>
+      <c r="M10" s="18" t="inlineStr"/>
+      <c r="N10" s="18" t="inlineStr"/>
+      <c r="O10" s="18" t="inlineStr"/>
+      <c r="P10" s="18" t="inlineStr"/>
+      <c r="Q10" s="18" t="inlineStr"/>
+      <c r="R10" s="18" t="inlineStr"/>
+      <c r="S10" s="18" t="inlineStr"/>
+      <c r="T10" s="18" t="inlineStr"/>
+      <c r="U10" s="18" t="inlineStr"/>
+      <c r="V10" s="18" t="inlineStr"/>
+      <c r="W10" s="18" t="inlineStr"/>
+      <c r="X10" s="18" t="inlineStr"/>
+      <c r="Y10" s="18" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="16" t="n">
@@ -2341,6 +2626,25 @@
       <c r="D11" s="18" t="inlineStr"/>
       <c r="E11" s="18" t="inlineStr"/>
       <c r="F11" s="18" t="inlineStr"/>
+      <c r="G11" s="18" t="inlineStr"/>
+      <c r="H11" s="18" t="inlineStr"/>
+      <c r="I11" s="18" t="inlineStr"/>
+      <c r="J11" s="18" t="inlineStr"/>
+      <c r="K11" s="18" t="inlineStr"/>
+      <c r="L11" s="18" t="inlineStr"/>
+      <c r="M11" s="18" t="inlineStr"/>
+      <c r="N11" s="18" t="inlineStr"/>
+      <c r="O11" s="18" t="inlineStr"/>
+      <c r="P11" s="18" t="inlineStr"/>
+      <c r="Q11" s="18" t="inlineStr"/>
+      <c r="R11" s="18" t="inlineStr"/>
+      <c r="S11" s="18" t="inlineStr"/>
+      <c r="T11" s="18" t="inlineStr"/>
+      <c r="U11" s="18" t="inlineStr"/>
+      <c r="V11" s="18" t="inlineStr"/>
+      <c r="W11" s="18" t="inlineStr"/>
+      <c r="X11" s="18" t="inlineStr"/>
+      <c r="Y11" s="18" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="16" t="n">
@@ -2355,6 +2659,25 @@
       <c r="D12" s="18" t="inlineStr"/>
       <c r="E12" s="18" t="inlineStr"/>
       <c r="F12" s="18" t="inlineStr"/>
+      <c r="G12" s="18" t="inlineStr"/>
+      <c r="H12" s="18" t="inlineStr"/>
+      <c r="I12" s="18" t="inlineStr"/>
+      <c r="J12" s="18" t="inlineStr"/>
+      <c r="K12" s="18" t="inlineStr"/>
+      <c r="L12" s="18" t="inlineStr"/>
+      <c r="M12" s="18" t="inlineStr"/>
+      <c r="N12" s="18" t="inlineStr"/>
+      <c r="O12" s="18" t="inlineStr"/>
+      <c r="P12" s="18" t="inlineStr"/>
+      <c r="Q12" s="18" t="inlineStr"/>
+      <c r="R12" s="18" t="inlineStr"/>
+      <c r="S12" s="18" t="inlineStr"/>
+      <c r="T12" s="18" t="inlineStr"/>
+      <c r="U12" s="18" t="inlineStr"/>
+      <c r="V12" s="18" t="inlineStr"/>
+      <c r="W12" s="18" t="inlineStr"/>
+      <c r="X12" s="18" t="inlineStr"/>
+      <c r="Y12" s="18" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="16" t="n">
@@ -2369,6 +2692,25 @@
       <c r="D13" s="18" t="inlineStr"/>
       <c r="E13" s="18" t="inlineStr"/>
       <c r="F13" s="18" t="inlineStr"/>
+      <c r="G13" s="18" t="inlineStr"/>
+      <c r="H13" s="18" t="inlineStr"/>
+      <c r="I13" s="18" t="inlineStr"/>
+      <c r="J13" s="18" t="inlineStr"/>
+      <c r="K13" s="18" t="inlineStr"/>
+      <c r="L13" s="18" t="inlineStr"/>
+      <c r="M13" s="18" t="inlineStr"/>
+      <c r="N13" s="18" t="inlineStr"/>
+      <c r="O13" s="18" t="inlineStr"/>
+      <c r="P13" s="18" t="inlineStr"/>
+      <c r="Q13" s="18" t="inlineStr"/>
+      <c r="R13" s="18" t="inlineStr"/>
+      <c r="S13" s="18" t="inlineStr"/>
+      <c r="T13" s="18" t="inlineStr"/>
+      <c r="U13" s="18" t="inlineStr"/>
+      <c r="V13" s="18" t="inlineStr"/>
+      <c r="W13" s="18" t="inlineStr"/>
+      <c r="X13" s="18" t="inlineStr"/>
+      <c r="Y13" s="18" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="16" t="n">
@@ -2383,6 +2725,25 @@
       <c r="D14" s="18" t="inlineStr"/>
       <c r="E14" s="18" t="inlineStr"/>
       <c r="F14" s="18" t="inlineStr"/>
+      <c r="G14" s="18" t="inlineStr"/>
+      <c r="H14" s="18" t="inlineStr"/>
+      <c r="I14" s="18" t="inlineStr"/>
+      <c r="J14" s="18" t="inlineStr"/>
+      <c r="K14" s="18" t="inlineStr"/>
+      <c r="L14" s="18" t="inlineStr"/>
+      <c r="M14" s="18" t="inlineStr"/>
+      <c r="N14" s="18" t="inlineStr"/>
+      <c r="O14" s="18" t="inlineStr"/>
+      <c r="P14" s="18" t="inlineStr"/>
+      <c r="Q14" s="18" t="inlineStr"/>
+      <c r="R14" s="18" t="inlineStr"/>
+      <c r="S14" s="18" t="inlineStr"/>
+      <c r="T14" s="18" t="inlineStr"/>
+      <c r="U14" s="18" t="inlineStr"/>
+      <c r="V14" s="18" t="inlineStr"/>
+      <c r="W14" s="18" t="inlineStr"/>
+      <c r="X14" s="18" t="inlineStr"/>
+      <c r="Y14" s="18" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="16" t="n">
@@ -2397,6 +2758,25 @@
       <c r="D15" s="18" t="inlineStr"/>
       <c r="E15" s="18" t="inlineStr"/>
       <c r="F15" s="18" t="inlineStr"/>
+      <c r="G15" s="18" t="inlineStr"/>
+      <c r="H15" s="18" t="inlineStr"/>
+      <c r="I15" s="18" t="inlineStr"/>
+      <c r="J15" s="18" t="inlineStr"/>
+      <c r="K15" s="18" t="inlineStr"/>
+      <c r="L15" s="18" t="inlineStr"/>
+      <c r="M15" s="18" t="inlineStr"/>
+      <c r="N15" s="18" t="inlineStr"/>
+      <c r="O15" s="18" t="inlineStr"/>
+      <c r="P15" s="18" t="inlineStr"/>
+      <c r="Q15" s="18" t="inlineStr"/>
+      <c r="R15" s="18" t="inlineStr"/>
+      <c r="S15" s="18" t="inlineStr"/>
+      <c r="T15" s="18" t="inlineStr"/>
+      <c r="U15" s="18" t="inlineStr"/>
+      <c r="V15" s="18" t="inlineStr"/>
+      <c r="W15" s="18" t="inlineStr"/>
+      <c r="X15" s="18" t="inlineStr"/>
+      <c r="Y15" s="18" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="16" t="n">
@@ -2411,6 +2791,25 @@
       <c r="D16" s="18" t="inlineStr"/>
       <c r="E16" s="18" t="inlineStr"/>
       <c r="F16" s="18" t="inlineStr"/>
+      <c r="G16" s="18" t="inlineStr"/>
+      <c r="H16" s="18" t="inlineStr"/>
+      <c r="I16" s="18" t="inlineStr"/>
+      <c r="J16" s="18" t="inlineStr"/>
+      <c r="K16" s="18" t="inlineStr"/>
+      <c r="L16" s="18" t="inlineStr"/>
+      <c r="M16" s="18" t="inlineStr"/>
+      <c r="N16" s="18" t="inlineStr"/>
+      <c r="O16" s="18" t="inlineStr"/>
+      <c r="P16" s="18" t="inlineStr"/>
+      <c r="Q16" s="18" t="inlineStr"/>
+      <c r="R16" s="18" t="inlineStr"/>
+      <c r="S16" s="18" t="inlineStr"/>
+      <c r="T16" s="18" t="inlineStr"/>
+      <c r="U16" s="18" t="inlineStr"/>
+      <c r="V16" s="18" t="inlineStr"/>
+      <c r="W16" s="18" t="inlineStr"/>
+      <c r="X16" s="18" t="inlineStr"/>
+      <c r="Y16" s="18" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="16" t="n">
@@ -2425,6 +2824,25 @@
       <c r="D17" s="18" t="inlineStr"/>
       <c r="E17" s="18" t="inlineStr"/>
       <c r="F17" s="18" t="inlineStr"/>
+      <c r="G17" s="18" t="inlineStr"/>
+      <c r="H17" s="18" t="inlineStr"/>
+      <c r="I17" s="18" t="inlineStr"/>
+      <c r="J17" s="18" t="inlineStr"/>
+      <c r="K17" s="18" t="inlineStr"/>
+      <c r="L17" s="18" t="inlineStr"/>
+      <c r="M17" s="18" t="inlineStr"/>
+      <c r="N17" s="18" t="inlineStr"/>
+      <c r="O17" s="18" t="inlineStr"/>
+      <c r="P17" s="18" t="inlineStr"/>
+      <c r="Q17" s="18" t="inlineStr"/>
+      <c r="R17" s="18" t="inlineStr"/>
+      <c r="S17" s="18" t="inlineStr"/>
+      <c r="T17" s="18" t="inlineStr"/>
+      <c r="U17" s="18" t="inlineStr"/>
+      <c r="V17" s="18" t="inlineStr"/>
+      <c r="W17" s="18" t="inlineStr"/>
+      <c r="X17" s="18" t="inlineStr"/>
+      <c r="Y17" s="18" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="16" t="n">
@@ -2439,6 +2857,25 @@
       <c r="D18" s="18" t="inlineStr"/>
       <c r="E18" s="18" t="inlineStr"/>
       <c r="F18" s="18" t="inlineStr"/>
+      <c r="G18" s="18" t="inlineStr"/>
+      <c r="H18" s="18" t="inlineStr"/>
+      <c r="I18" s="18" t="inlineStr"/>
+      <c r="J18" s="18" t="inlineStr"/>
+      <c r="K18" s="18" t="inlineStr"/>
+      <c r="L18" s="18" t="inlineStr"/>
+      <c r="M18" s="18" t="inlineStr"/>
+      <c r="N18" s="18" t="inlineStr"/>
+      <c r="O18" s="18" t="inlineStr"/>
+      <c r="P18" s="18" t="inlineStr"/>
+      <c r="Q18" s="18" t="inlineStr"/>
+      <c r="R18" s="18" t="inlineStr"/>
+      <c r="S18" s="18" t="inlineStr"/>
+      <c r="T18" s="18" t="inlineStr"/>
+      <c r="U18" s="18" t="inlineStr"/>
+      <c r="V18" s="18" t="inlineStr"/>
+      <c r="W18" s="18" t="inlineStr"/>
+      <c r="X18" s="18" t="inlineStr"/>
+      <c r="Y18" s="18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="16" t="n">
@@ -2453,6 +2890,25 @@
       <c r="D19" s="18" t="inlineStr"/>
       <c r="E19" s="18" t="inlineStr"/>
       <c r="F19" s="18" t="inlineStr"/>
+      <c r="G19" s="18" t="inlineStr"/>
+      <c r="H19" s="18" t="inlineStr"/>
+      <c r="I19" s="18" t="inlineStr"/>
+      <c r="J19" s="18" t="inlineStr"/>
+      <c r="K19" s="18" t="inlineStr"/>
+      <c r="L19" s="18" t="inlineStr"/>
+      <c r="M19" s="18" t="inlineStr"/>
+      <c r="N19" s="18" t="inlineStr"/>
+      <c r="O19" s="18" t="inlineStr"/>
+      <c r="P19" s="18" t="inlineStr"/>
+      <c r="Q19" s="18" t="inlineStr"/>
+      <c r="R19" s="18" t="inlineStr"/>
+      <c r="S19" s="18" t="inlineStr"/>
+      <c r="T19" s="18" t="inlineStr"/>
+      <c r="U19" s="18" t="inlineStr"/>
+      <c r="V19" s="18" t="inlineStr"/>
+      <c r="W19" s="18" t="inlineStr"/>
+      <c r="X19" s="18" t="inlineStr"/>
+      <c r="Y19" s="18" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="16" t="n">
@@ -2467,6 +2923,25 @@
       <c r="D20" s="18" t="inlineStr"/>
       <c r="E20" s="18" t="inlineStr"/>
       <c r="F20" s="18" t="inlineStr"/>
+      <c r="G20" s="18" t="inlineStr"/>
+      <c r="H20" s="18" t="inlineStr"/>
+      <c r="I20" s="18" t="inlineStr"/>
+      <c r="J20" s="18" t="inlineStr"/>
+      <c r="K20" s="18" t="inlineStr"/>
+      <c r="L20" s="18" t="inlineStr"/>
+      <c r="M20" s="18" t="inlineStr"/>
+      <c r="N20" s="18" t="inlineStr"/>
+      <c r="O20" s="18" t="inlineStr"/>
+      <c r="P20" s="18" t="inlineStr"/>
+      <c r="Q20" s="18" t="inlineStr"/>
+      <c r="R20" s="18" t="inlineStr"/>
+      <c r="S20" s="18" t="inlineStr"/>
+      <c r="T20" s="18" t="inlineStr"/>
+      <c r="U20" s="18" t="inlineStr"/>
+      <c r="V20" s="18" t="inlineStr"/>
+      <c r="W20" s="18" t="inlineStr"/>
+      <c r="X20" s="18" t="inlineStr"/>
+      <c r="Y20" s="18" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="16" t="n">
@@ -2481,6 +2956,25 @@
       <c r="D21" s="18" t="inlineStr"/>
       <c r="E21" s="18" t="inlineStr"/>
       <c r="F21" s="18" t="inlineStr"/>
+      <c r="G21" s="18" t="inlineStr"/>
+      <c r="H21" s="18" t="inlineStr"/>
+      <c r="I21" s="18" t="inlineStr"/>
+      <c r="J21" s="18" t="inlineStr"/>
+      <c r="K21" s="18" t="inlineStr"/>
+      <c r="L21" s="18" t="inlineStr"/>
+      <c r="M21" s="18" t="inlineStr"/>
+      <c r="N21" s="18" t="inlineStr"/>
+      <c r="O21" s="18" t="inlineStr"/>
+      <c r="P21" s="18" t="inlineStr"/>
+      <c r="Q21" s="18" t="inlineStr"/>
+      <c r="R21" s="18" t="inlineStr"/>
+      <c r="S21" s="18" t="inlineStr"/>
+      <c r="T21" s="18" t="inlineStr"/>
+      <c r="U21" s="18" t="inlineStr"/>
+      <c r="V21" s="18" t="inlineStr"/>
+      <c r="W21" s="18" t="inlineStr"/>
+      <c r="X21" s="18" t="inlineStr"/>
+      <c r="Y21" s="18" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="16" t="n">
@@ -2495,6 +2989,25 @@
       <c r="D22" s="18" t="inlineStr"/>
       <c r="E22" s="18" t="inlineStr"/>
       <c r="F22" s="18" t="inlineStr"/>
+      <c r="G22" s="18" t="inlineStr"/>
+      <c r="H22" s="18" t="inlineStr"/>
+      <c r="I22" s="18" t="inlineStr"/>
+      <c r="J22" s="18" t="inlineStr"/>
+      <c r="K22" s="18" t="inlineStr"/>
+      <c r="L22" s="18" t="inlineStr"/>
+      <c r="M22" s="18" t="inlineStr"/>
+      <c r="N22" s="18" t="inlineStr"/>
+      <c r="O22" s="18" t="inlineStr"/>
+      <c r="P22" s="18" t="inlineStr"/>
+      <c r="Q22" s="18" t="inlineStr"/>
+      <c r="R22" s="18" t="inlineStr"/>
+      <c r="S22" s="18" t="inlineStr"/>
+      <c r="T22" s="18" t="inlineStr"/>
+      <c r="U22" s="18" t="inlineStr"/>
+      <c r="V22" s="18" t="inlineStr"/>
+      <c r="W22" s="18" t="inlineStr"/>
+      <c r="X22" s="18" t="inlineStr"/>
+      <c r="Y22" s="18" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="16" t="n">
@@ -2509,6 +3022,25 @@
       <c r="D23" s="18" t="inlineStr"/>
       <c r="E23" s="18" t="inlineStr"/>
       <c r="F23" s="18" t="inlineStr"/>
+      <c r="G23" s="18" t="inlineStr"/>
+      <c r="H23" s="18" t="inlineStr"/>
+      <c r="I23" s="18" t="inlineStr"/>
+      <c r="J23" s="18" t="inlineStr"/>
+      <c r="K23" s="18" t="inlineStr"/>
+      <c r="L23" s="18" t="inlineStr"/>
+      <c r="M23" s="18" t="inlineStr"/>
+      <c r="N23" s="18" t="inlineStr"/>
+      <c r="O23" s="18" t="inlineStr"/>
+      <c r="P23" s="18" t="inlineStr"/>
+      <c r="Q23" s="18" t="inlineStr"/>
+      <c r="R23" s="18" t="inlineStr"/>
+      <c r="S23" s="18" t="inlineStr"/>
+      <c r="T23" s="18" t="inlineStr"/>
+      <c r="U23" s="18" t="inlineStr"/>
+      <c r="V23" s="18" t="inlineStr"/>
+      <c r="W23" s="18" t="inlineStr"/>
+      <c r="X23" s="18" t="inlineStr"/>
+      <c r="Y23" s="18" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="16" t="n">
@@ -2523,6 +3055,25 @@
       <c r="D24" s="18" t="inlineStr"/>
       <c r="E24" s="18" t="inlineStr"/>
       <c r="F24" s="18" t="inlineStr"/>
+      <c r="G24" s="18" t="inlineStr"/>
+      <c r="H24" s="18" t="inlineStr"/>
+      <c r="I24" s="18" t="inlineStr"/>
+      <c r="J24" s="18" t="inlineStr"/>
+      <c r="K24" s="18" t="inlineStr"/>
+      <c r="L24" s="18" t="inlineStr"/>
+      <c r="M24" s="18" t="inlineStr"/>
+      <c r="N24" s="18" t="inlineStr"/>
+      <c r="O24" s="18" t="inlineStr"/>
+      <c r="P24" s="18" t="inlineStr"/>
+      <c r="Q24" s="18" t="inlineStr"/>
+      <c r="R24" s="18" t="inlineStr"/>
+      <c r="S24" s="18" t="inlineStr"/>
+      <c r="T24" s="18" t="inlineStr"/>
+      <c r="U24" s="18" t="inlineStr"/>
+      <c r="V24" s="18" t="inlineStr"/>
+      <c r="W24" s="18" t="inlineStr"/>
+      <c r="X24" s="18" t="inlineStr"/>
+      <c r="Y24" s="18" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="16" t="n">
@@ -2537,6 +3088,25 @@
       <c r="D25" s="18" t="inlineStr"/>
       <c r="E25" s="18" t="inlineStr"/>
       <c r="F25" s="18" t="inlineStr"/>
+      <c r="G25" s="18" t="inlineStr"/>
+      <c r="H25" s="18" t="inlineStr"/>
+      <c r="I25" s="18" t="inlineStr"/>
+      <c r="J25" s="18" t="inlineStr"/>
+      <c r="K25" s="18" t="inlineStr"/>
+      <c r="L25" s="18" t="inlineStr"/>
+      <c r="M25" s="18" t="inlineStr"/>
+      <c r="N25" s="18" t="inlineStr"/>
+      <c r="O25" s="18" t="inlineStr"/>
+      <c r="P25" s="18" t="inlineStr"/>
+      <c r="Q25" s="18" t="inlineStr"/>
+      <c r="R25" s="18" t="inlineStr"/>
+      <c r="S25" s="18" t="inlineStr"/>
+      <c r="T25" s="18" t="inlineStr"/>
+      <c r="U25" s="18" t="inlineStr"/>
+      <c r="V25" s="18" t="inlineStr"/>
+      <c r="W25" s="18" t="inlineStr"/>
+      <c r="X25" s="18" t="inlineStr"/>
+      <c r="Y25" s="18" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="16" t="n">
@@ -2551,6 +3121,25 @@
       <c r="D26" s="18" t="inlineStr"/>
       <c r="E26" s="18" t="inlineStr"/>
       <c r="F26" s="18" t="inlineStr"/>
+      <c r="G26" s="18" t="inlineStr"/>
+      <c r="H26" s="18" t="inlineStr"/>
+      <c r="I26" s="18" t="inlineStr"/>
+      <c r="J26" s="18" t="inlineStr"/>
+      <c r="K26" s="18" t="inlineStr"/>
+      <c r="L26" s="18" t="inlineStr"/>
+      <c r="M26" s="18" t="inlineStr"/>
+      <c r="N26" s="18" t="inlineStr"/>
+      <c r="O26" s="18" t="inlineStr"/>
+      <c r="P26" s="18" t="inlineStr"/>
+      <c r="Q26" s="18" t="inlineStr"/>
+      <c r="R26" s="18" t="inlineStr"/>
+      <c r="S26" s="18" t="inlineStr"/>
+      <c r="T26" s="18" t="inlineStr"/>
+      <c r="U26" s="18" t="inlineStr"/>
+      <c r="V26" s="18" t="inlineStr"/>
+      <c r="W26" s="18" t="inlineStr"/>
+      <c r="X26" s="18" t="inlineStr"/>
+      <c r="Y26" s="18" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="16" t="n">
@@ -2565,6 +3154,25 @@
       <c r="D27" s="18" t="inlineStr"/>
       <c r="E27" s="18" t="inlineStr"/>
       <c r="F27" s="18" t="inlineStr"/>
+      <c r="G27" s="18" t="inlineStr"/>
+      <c r="H27" s="18" t="inlineStr"/>
+      <c r="I27" s="18" t="inlineStr"/>
+      <c r="J27" s="18" t="inlineStr"/>
+      <c r="K27" s="18" t="inlineStr"/>
+      <c r="L27" s="18" t="inlineStr"/>
+      <c r="M27" s="18" t="inlineStr"/>
+      <c r="N27" s="18" t="inlineStr"/>
+      <c r="O27" s="18" t="inlineStr"/>
+      <c r="P27" s="18" t="inlineStr"/>
+      <c r="Q27" s="18" t="inlineStr"/>
+      <c r="R27" s="18" t="inlineStr"/>
+      <c r="S27" s="18" t="inlineStr"/>
+      <c r="T27" s="18" t="inlineStr"/>
+      <c r="U27" s="18" t="inlineStr"/>
+      <c r="V27" s="18" t="inlineStr"/>
+      <c r="W27" s="18" t="inlineStr"/>
+      <c r="X27" s="18" t="inlineStr"/>
+      <c r="Y27" s="18" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="16" t="n">
@@ -2579,6 +3187,25 @@
       <c r="D28" s="18" t="inlineStr"/>
       <c r="E28" s="18" t="inlineStr"/>
       <c r="F28" s="18" t="inlineStr"/>
+      <c r="G28" s="18" t="inlineStr"/>
+      <c r="H28" s="18" t="inlineStr"/>
+      <c r="I28" s="18" t="inlineStr"/>
+      <c r="J28" s="18" t="inlineStr"/>
+      <c r="K28" s="18" t="inlineStr"/>
+      <c r="L28" s="18" t="inlineStr"/>
+      <c r="M28" s="18" t="inlineStr"/>
+      <c r="N28" s="18" t="inlineStr"/>
+      <c r="O28" s="18" t="inlineStr"/>
+      <c r="P28" s="18" t="inlineStr"/>
+      <c r="Q28" s="18" t="inlineStr"/>
+      <c r="R28" s="18" t="inlineStr"/>
+      <c r="S28" s="18" t="inlineStr"/>
+      <c r="T28" s="18" t="inlineStr"/>
+      <c r="U28" s="18" t="inlineStr"/>
+      <c r="V28" s="18" t="inlineStr"/>
+      <c r="W28" s="18" t="inlineStr"/>
+      <c r="X28" s="18" t="inlineStr"/>
+      <c r="Y28" s="18" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="16" t="n">
@@ -2593,6 +3220,25 @@
       <c r="D29" s="18" t="inlineStr"/>
       <c r="E29" s="18" t="inlineStr"/>
       <c r="F29" s="18" t="inlineStr"/>
+      <c r="G29" s="18" t="inlineStr"/>
+      <c r="H29" s="18" t="inlineStr"/>
+      <c r="I29" s="18" t="inlineStr"/>
+      <c r="J29" s="18" t="inlineStr"/>
+      <c r="K29" s="18" t="inlineStr"/>
+      <c r="L29" s="18" t="inlineStr"/>
+      <c r="M29" s="18" t="inlineStr"/>
+      <c r="N29" s="18" t="inlineStr"/>
+      <c r="O29" s="18" t="inlineStr"/>
+      <c r="P29" s="18" t="inlineStr"/>
+      <c r="Q29" s="18" t="inlineStr"/>
+      <c r="R29" s="18" t="inlineStr"/>
+      <c r="S29" s="18" t="inlineStr"/>
+      <c r="T29" s="18" t="inlineStr"/>
+      <c r="U29" s="18" t="inlineStr"/>
+      <c r="V29" s="18" t="inlineStr"/>
+      <c r="W29" s="18" t="inlineStr"/>
+      <c r="X29" s="18" t="inlineStr"/>
+      <c r="Y29" s="18" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="16" t="n">
@@ -2607,6 +3253,25 @@
       <c r="D30" s="18" t="inlineStr"/>
       <c r="E30" s="18" t="inlineStr"/>
       <c r="F30" s="18" t="inlineStr"/>
+      <c r="G30" s="18" t="inlineStr"/>
+      <c r="H30" s="18" t="inlineStr"/>
+      <c r="I30" s="18" t="inlineStr"/>
+      <c r="J30" s="18" t="inlineStr"/>
+      <c r="K30" s="18" t="inlineStr"/>
+      <c r="L30" s="18" t="inlineStr"/>
+      <c r="M30" s="18" t="inlineStr"/>
+      <c r="N30" s="18" t="inlineStr"/>
+      <c r="O30" s="18" t="inlineStr"/>
+      <c r="P30" s="18" t="inlineStr"/>
+      <c r="Q30" s="18" t="inlineStr"/>
+      <c r="R30" s="18" t="inlineStr"/>
+      <c r="S30" s="18" t="inlineStr"/>
+      <c r="T30" s="18" t="inlineStr"/>
+      <c r="U30" s="18" t="inlineStr"/>
+      <c r="V30" s="18" t="inlineStr"/>
+      <c r="W30" s="18" t="inlineStr"/>
+      <c r="X30" s="18" t="inlineStr"/>
+      <c r="Y30" s="18" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="16" t="n">
@@ -2621,6 +3286,25 @@
       <c r="D31" s="18" t="inlineStr"/>
       <c r="E31" s="18" t="inlineStr"/>
       <c r="F31" s="18" t="inlineStr"/>
+      <c r="G31" s="18" t="inlineStr"/>
+      <c r="H31" s="18" t="inlineStr"/>
+      <c r="I31" s="18" t="inlineStr"/>
+      <c r="J31" s="18" t="inlineStr"/>
+      <c r="K31" s="18" t="inlineStr"/>
+      <c r="L31" s="18" t="inlineStr"/>
+      <c r="M31" s="18" t="inlineStr"/>
+      <c r="N31" s="18" t="inlineStr"/>
+      <c r="O31" s="18" t="inlineStr"/>
+      <c r="P31" s="18" t="inlineStr"/>
+      <c r="Q31" s="18" t="inlineStr"/>
+      <c r="R31" s="18" t="inlineStr"/>
+      <c r="S31" s="18" t="inlineStr"/>
+      <c r="T31" s="18" t="inlineStr"/>
+      <c r="U31" s="18" t="inlineStr"/>
+      <c r="V31" s="18" t="inlineStr"/>
+      <c r="W31" s="18" t="inlineStr"/>
+      <c r="X31" s="18" t="inlineStr"/>
+      <c r="Y31" s="18" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="16" t="n">
@@ -2635,6 +3319,25 @@
       <c r="D32" s="18" t="inlineStr"/>
       <c r="E32" s="18" t="inlineStr"/>
       <c r="F32" s="18" t="inlineStr"/>
+      <c r="G32" s="18" t="inlineStr"/>
+      <c r="H32" s="18" t="inlineStr"/>
+      <c r="I32" s="18" t="inlineStr"/>
+      <c r="J32" s="18" t="inlineStr"/>
+      <c r="K32" s="18" t="inlineStr"/>
+      <c r="L32" s="18" t="inlineStr"/>
+      <c r="M32" s="18" t="inlineStr"/>
+      <c r="N32" s="18" t="inlineStr"/>
+      <c r="O32" s="18" t="inlineStr"/>
+      <c r="P32" s="18" t="inlineStr"/>
+      <c r="Q32" s="18" t="inlineStr"/>
+      <c r="R32" s="18" t="inlineStr"/>
+      <c r="S32" s="18" t="inlineStr"/>
+      <c r="T32" s="18" t="inlineStr"/>
+      <c r="U32" s="18" t="inlineStr"/>
+      <c r="V32" s="18" t="inlineStr"/>
+      <c r="W32" s="18" t="inlineStr"/>
+      <c r="X32" s="18" t="inlineStr"/>
+      <c r="Y32" s="18" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="16" t="n">
@@ -2649,6 +3352,25 @@
       <c r="D33" s="18" t="inlineStr"/>
       <c r="E33" s="18" t="inlineStr"/>
       <c r="F33" s="18" t="inlineStr"/>
+      <c r="G33" s="18" t="inlineStr"/>
+      <c r="H33" s="18" t="inlineStr"/>
+      <c r="I33" s="18" t="inlineStr"/>
+      <c r="J33" s="18" t="inlineStr"/>
+      <c r="K33" s="18" t="inlineStr"/>
+      <c r="L33" s="18" t="inlineStr"/>
+      <c r="M33" s="18" t="inlineStr"/>
+      <c r="N33" s="18" t="inlineStr"/>
+      <c r="O33" s="18" t="inlineStr"/>
+      <c r="P33" s="18" t="inlineStr"/>
+      <c r="Q33" s="18" t="inlineStr"/>
+      <c r="R33" s="18" t="inlineStr"/>
+      <c r="S33" s="18" t="inlineStr"/>
+      <c r="T33" s="18" t="inlineStr"/>
+      <c r="U33" s="18" t="inlineStr"/>
+      <c r="V33" s="18" t="inlineStr"/>
+      <c r="W33" s="18" t="inlineStr"/>
+      <c r="X33" s="18" t="inlineStr"/>
+      <c r="Y33" s="18" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="16" t="n">
@@ -2663,6 +3385,25 @@
       <c r="D34" s="18" t="inlineStr"/>
       <c r="E34" s="18" t="inlineStr"/>
       <c r="F34" s="18" t="inlineStr"/>
+      <c r="G34" s="18" t="inlineStr"/>
+      <c r="H34" s="18" t="inlineStr"/>
+      <c r="I34" s="18" t="inlineStr"/>
+      <c r="J34" s="18" t="inlineStr"/>
+      <c r="K34" s="18" t="inlineStr"/>
+      <c r="L34" s="18" t="inlineStr"/>
+      <c r="M34" s="18" t="inlineStr"/>
+      <c r="N34" s="18" t="inlineStr"/>
+      <c r="O34" s="18" t="inlineStr"/>
+      <c r="P34" s="18" t="inlineStr"/>
+      <c r="Q34" s="18" t="inlineStr"/>
+      <c r="R34" s="18" t="inlineStr"/>
+      <c r="S34" s="18" t="inlineStr"/>
+      <c r="T34" s="18" t="inlineStr"/>
+      <c r="U34" s="18" t="inlineStr"/>
+      <c r="V34" s="18" t="inlineStr"/>
+      <c r="W34" s="18" t="inlineStr"/>
+      <c r="X34" s="18" t="inlineStr"/>
+      <c r="Y34" s="18" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="16" t="n">
@@ -2677,6 +3418,25 @@
       <c r="D35" s="18" t="inlineStr"/>
       <c r="E35" s="18" t="inlineStr"/>
       <c r="F35" s="18" t="inlineStr"/>
+      <c r="G35" s="18" t="inlineStr"/>
+      <c r="H35" s="18" t="inlineStr"/>
+      <c r="I35" s="18" t="inlineStr"/>
+      <c r="J35" s="18" t="inlineStr"/>
+      <c r="K35" s="18" t="inlineStr"/>
+      <c r="L35" s="18" t="inlineStr"/>
+      <c r="M35" s="18" t="inlineStr"/>
+      <c r="N35" s="18" t="inlineStr"/>
+      <c r="O35" s="18" t="inlineStr"/>
+      <c r="P35" s="18" t="inlineStr"/>
+      <c r="Q35" s="18" t="inlineStr"/>
+      <c r="R35" s="18" t="inlineStr"/>
+      <c r="S35" s="18" t="inlineStr"/>
+      <c r="T35" s="18" t="inlineStr"/>
+      <c r="U35" s="18" t="inlineStr"/>
+      <c r="V35" s="18" t="inlineStr"/>
+      <c r="W35" s="18" t="inlineStr"/>
+      <c r="X35" s="18" t="inlineStr"/>
+      <c r="Y35" s="18" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="16" t="n">
@@ -2691,6 +3451,25 @@
       <c r="D36" s="18" t="inlineStr"/>
       <c r="E36" s="18" t="inlineStr"/>
       <c r="F36" s="18" t="inlineStr"/>
+      <c r="G36" s="18" t="inlineStr"/>
+      <c r="H36" s="18" t="inlineStr"/>
+      <c r="I36" s="18" t="inlineStr"/>
+      <c r="J36" s="18" t="inlineStr"/>
+      <c r="K36" s="18" t="inlineStr"/>
+      <c r="L36" s="18" t="inlineStr"/>
+      <c r="M36" s="18" t="inlineStr"/>
+      <c r="N36" s="18" t="inlineStr"/>
+      <c r="O36" s="18" t="inlineStr"/>
+      <c r="P36" s="18" t="inlineStr"/>
+      <c r="Q36" s="18" t="inlineStr"/>
+      <c r="R36" s="18" t="inlineStr"/>
+      <c r="S36" s="18" t="inlineStr"/>
+      <c r="T36" s="18" t="inlineStr"/>
+      <c r="U36" s="18" t="inlineStr"/>
+      <c r="V36" s="18" t="inlineStr"/>
+      <c r="W36" s="18" t="inlineStr"/>
+      <c r="X36" s="18" t="inlineStr"/>
+      <c r="Y36" s="18" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="16" t="n">
@@ -2705,6 +3484,25 @@
       <c r="D37" s="18" t="inlineStr"/>
       <c r="E37" s="18" t="inlineStr"/>
       <c r="F37" s="18" t="inlineStr"/>
+      <c r="G37" s="18" t="inlineStr"/>
+      <c r="H37" s="18" t="inlineStr"/>
+      <c r="I37" s="18" t="inlineStr"/>
+      <c r="J37" s="18" t="inlineStr"/>
+      <c r="K37" s="18" t="inlineStr"/>
+      <c r="L37" s="18" t="inlineStr"/>
+      <c r="M37" s="18" t="inlineStr"/>
+      <c r="N37" s="18" t="inlineStr"/>
+      <c r="O37" s="18" t="inlineStr"/>
+      <c r="P37" s="18" t="inlineStr"/>
+      <c r="Q37" s="18" t="inlineStr"/>
+      <c r="R37" s="18" t="inlineStr"/>
+      <c r="S37" s="18" t="inlineStr"/>
+      <c r="T37" s="18" t="inlineStr"/>
+      <c r="U37" s="18" t="inlineStr"/>
+      <c r="V37" s="18" t="inlineStr"/>
+      <c r="W37" s="18" t="inlineStr"/>
+      <c r="X37" s="18" t="inlineStr"/>
+      <c r="Y37" s="18" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="16" t="n">
@@ -2719,6 +3517,29 @@
       <c r="D38" s="18" t="inlineStr"/>
       <c r="E38" s="18" t="inlineStr"/>
       <c r="F38" s="18" t="inlineStr"/>
+      <c r="G38" s="18" t="inlineStr"/>
+      <c r="H38" s="18" t="inlineStr"/>
+      <c r="I38" s="18" t="inlineStr"/>
+      <c r="J38" s="18" t="inlineStr"/>
+      <c r="K38" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 1 abstract cited by the corpus</t>
+        </is>
+      </c>
+      <c r="L38" s="18" t="inlineStr"/>
+      <c r="M38" s="18" t="inlineStr"/>
+      <c r="N38" s="18" t="inlineStr"/>
+      <c r="O38" s="18" t="inlineStr"/>
+      <c r="P38" s="18" t="inlineStr"/>
+      <c r="Q38" s="18" t="inlineStr"/>
+      <c r="R38" s="18" t="inlineStr"/>
+      <c r="S38" s="18" t="inlineStr"/>
+      <c r="T38" s="18" t="inlineStr"/>
+      <c r="U38" s="18" t="inlineStr"/>
+      <c r="V38" s="18" t="inlineStr"/>
+      <c r="W38" s="18" t="inlineStr"/>
+      <c r="X38" s="18" t="inlineStr"/>
+      <c r="Y38" s="18" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="16" t="n">
@@ -2733,6 +3554,25 @@
       <c r="D39" s="18" t="inlineStr"/>
       <c r="E39" s="18" t="inlineStr"/>
       <c r="F39" s="18" t="inlineStr"/>
+      <c r="G39" s="18" t="inlineStr"/>
+      <c r="H39" s="18" t="inlineStr"/>
+      <c r="I39" s="18" t="inlineStr"/>
+      <c r="J39" s="18" t="inlineStr"/>
+      <c r="K39" s="18" t="inlineStr"/>
+      <c r="L39" s="18" t="inlineStr"/>
+      <c r="M39" s="18" t="inlineStr"/>
+      <c r="N39" s="18" t="inlineStr"/>
+      <c r="O39" s="18" t="inlineStr"/>
+      <c r="P39" s="18" t="inlineStr"/>
+      <c r="Q39" s="18" t="inlineStr"/>
+      <c r="R39" s="18" t="inlineStr"/>
+      <c r="S39" s="18" t="inlineStr"/>
+      <c r="T39" s="18" t="inlineStr"/>
+      <c r="U39" s="18" t="inlineStr"/>
+      <c r="V39" s="18" t="inlineStr"/>
+      <c r="W39" s="18" t="inlineStr"/>
+      <c r="X39" s="18" t="inlineStr"/>
+      <c r="Y39" s="18" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="16" t="n">
@@ -2747,6 +3587,25 @@
       <c r="D40" s="18" t="inlineStr"/>
       <c r="E40" s="18" t="inlineStr"/>
       <c r="F40" s="18" t="inlineStr"/>
+      <c r="G40" s="18" t="inlineStr"/>
+      <c r="H40" s="18" t="inlineStr"/>
+      <c r="I40" s="18" t="inlineStr"/>
+      <c r="J40" s="18" t="inlineStr"/>
+      <c r="K40" s="18" t="inlineStr"/>
+      <c r="L40" s="18" t="inlineStr"/>
+      <c r="M40" s="18" t="inlineStr"/>
+      <c r="N40" s="18" t="inlineStr"/>
+      <c r="O40" s="18" t="inlineStr"/>
+      <c r="P40" s="18" t="inlineStr"/>
+      <c r="Q40" s="18" t="inlineStr"/>
+      <c r="R40" s="18" t="inlineStr"/>
+      <c r="S40" s="18" t="inlineStr"/>
+      <c r="T40" s="18" t="inlineStr"/>
+      <c r="U40" s="18" t="inlineStr"/>
+      <c r="V40" s="18" t="inlineStr"/>
+      <c r="W40" s="18" t="inlineStr"/>
+      <c r="X40" s="18" t="inlineStr"/>
+      <c r="Y40" s="18" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="16" t="n">
@@ -2761,6 +3620,29 @@
       <c r="D41" s="18" t="inlineStr"/>
       <c r="E41" s="18" t="inlineStr"/>
       <c r="F41" s="18" t="inlineStr"/>
+      <c r="G41" s="18" t="inlineStr"/>
+      <c r="H41" s="18" t="inlineStr"/>
+      <c r="I41" s="18" t="inlineStr"/>
+      <c r="J41" s="18" t="inlineStr"/>
+      <c r="K41" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 1 abstract cited by the corpus</t>
+        </is>
+      </c>
+      <c r="L41" s="18" t="inlineStr"/>
+      <c r="M41" s="18" t="inlineStr"/>
+      <c r="N41" s="18" t="inlineStr"/>
+      <c r="O41" s="18" t="inlineStr"/>
+      <c r="P41" s="18" t="inlineStr"/>
+      <c r="Q41" s="18" t="inlineStr"/>
+      <c r="R41" s="18" t="inlineStr"/>
+      <c r="S41" s="18" t="inlineStr"/>
+      <c r="T41" s="18" t="inlineStr"/>
+      <c r="U41" s="18" t="inlineStr"/>
+      <c r="V41" s="18" t="inlineStr"/>
+      <c r="W41" s="18" t="inlineStr"/>
+      <c r="X41" s="18" t="inlineStr"/>
+      <c r="Y41" s="18" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="16" t="n">
@@ -2775,6 +3657,25 @@
       <c r="D42" s="18" t="inlineStr"/>
       <c r="E42" s="18" t="inlineStr"/>
       <c r="F42" s="18" t="inlineStr"/>
+      <c r="G42" s="18" t="inlineStr"/>
+      <c r="H42" s="18" t="inlineStr"/>
+      <c r="I42" s="18" t="inlineStr"/>
+      <c r="J42" s="18" t="inlineStr"/>
+      <c r="K42" s="18" t="inlineStr"/>
+      <c r="L42" s="18" t="inlineStr"/>
+      <c r="M42" s="18" t="inlineStr"/>
+      <c r="N42" s="18" t="inlineStr"/>
+      <c r="O42" s="18" t="inlineStr"/>
+      <c r="P42" s="18" t="inlineStr"/>
+      <c r="Q42" s="18" t="inlineStr"/>
+      <c r="R42" s="18" t="inlineStr"/>
+      <c r="S42" s="18" t="inlineStr"/>
+      <c r="T42" s="18" t="inlineStr"/>
+      <c r="U42" s="18" t="inlineStr"/>
+      <c r="V42" s="18" t="inlineStr"/>
+      <c r="W42" s="18" t="inlineStr"/>
+      <c r="X42" s="18" t="inlineStr"/>
+      <c r="Y42" s="18" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="16" t="n">
@@ -2789,6 +3690,25 @@
       <c r="D43" s="18" t="inlineStr"/>
       <c r="E43" s="18" t="inlineStr"/>
       <c r="F43" s="18" t="inlineStr"/>
+      <c r="G43" s="18" t="inlineStr"/>
+      <c r="H43" s="18" t="inlineStr"/>
+      <c r="I43" s="18" t="inlineStr"/>
+      <c r="J43" s="18" t="inlineStr"/>
+      <c r="K43" s="18" t="inlineStr"/>
+      <c r="L43" s="18" t="inlineStr"/>
+      <c r="M43" s="18" t="inlineStr"/>
+      <c r="N43" s="18" t="inlineStr"/>
+      <c r="O43" s="18" t="inlineStr"/>
+      <c r="P43" s="18" t="inlineStr"/>
+      <c r="Q43" s="18" t="inlineStr"/>
+      <c r="R43" s="18" t="inlineStr"/>
+      <c r="S43" s="18" t="inlineStr"/>
+      <c r="T43" s="18" t="inlineStr"/>
+      <c r="U43" s="18" t="inlineStr"/>
+      <c r="V43" s="18" t="inlineStr"/>
+      <c r="W43" s="18" t="inlineStr"/>
+      <c r="X43" s="18" t="inlineStr"/>
+      <c r="Y43" s="18" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="16" t="n">
@@ -2803,6 +3723,25 @@
       <c r="D44" s="18" t="inlineStr"/>
       <c r="E44" s="18" t="inlineStr"/>
       <c r="F44" s="18" t="inlineStr"/>
+      <c r="G44" s="18" t="inlineStr"/>
+      <c r="H44" s="18" t="inlineStr"/>
+      <c r="I44" s="18" t="inlineStr"/>
+      <c r="J44" s="18" t="inlineStr"/>
+      <c r="K44" s="18" t="inlineStr"/>
+      <c r="L44" s="18" t="inlineStr"/>
+      <c r="M44" s="18" t="inlineStr"/>
+      <c r="N44" s="18" t="inlineStr"/>
+      <c r="O44" s="18" t="inlineStr"/>
+      <c r="P44" s="18" t="inlineStr"/>
+      <c r="Q44" s="18" t="inlineStr"/>
+      <c r="R44" s="18" t="inlineStr"/>
+      <c r="S44" s="18" t="inlineStr"/>
+      <c r="T44" s="18" t="inlineStr"/>
+      <c r="U44" s="18" t="inlineStr"/>
+      <c r="V44" s="18" t="inlineStr"/>
+      <c r="W44" s="18" t="inlineStr"/>
+      <c r="X44" s="18" t="inlineStr"/>
+      <c r="Y44" s="18" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="16" t="n">
@@ -2817,6 +3756,25 @@
       <c r="D45" s="18" t="inlineStr"/>
       <c r="E45" s="18" t="inlineStr"/>
       <c r="F45" s="18" t="inlineStr"/>
+      <c r="G45" s="18" t="inlineStr"/>
+      <c r="H45" s="18" t="inlineStr"/>
+      <c r="I45" s="18" t="inlineStr"/>
+      <c r="J45" s="18" t="inlineStr"/>
+      <c r="K45" s="18" t="inlineStr"/>
+      <c r="L45" s="18" t="inlineStr"/>
+      <c r="M45" s="18" t="inlineStr"/>
+      <c r="N45" s="18" t="inlineStr"/>
+      <c r="O45" s="18" t="inlineStr"/>
+      <c r="P45" s="18" t="inlineStr"/>
+      <c r="Q45" s="18" t="inlineStr"/>
+      <c r="R45" s="18" t="inlineStr"/>
+      <c r="S45" s="18" t="inlineStr"/>
+      <c r="T45" s="18" t="inlineStr"/>
+      <c r="U45" s="18" t="inlineStr"/>
+      <c r="V45" s="18" t="inlineStr"/>
+      <c r="W45" s="18" t="inlineStr"/>
+      <c r="X45" s="18" t="inlineStr"/>
+      <c r="Y45" s="18" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="16" t="n">
@@ -2831,6 +3789,25 @@
       <c r="D46" s="18" t="inlineStr"/>
       <c r="E46" s="18" t="inlineStr"/>
       <c r="F46" s="18" t="inlineStr"/>
+      <c r="G46" s="18" t="inlineStr"/>
+      <c r="H46" s="18" t="inlineStr"/>
+      <c r="I46" s="18" t="inlineStr"/>
+      <c r="J46" s="18" t="inlineStr"/>
+      <c r="K46" s="18" t="inlineStr"/>
+      <c r="L46" s="18" t="inlineStr"/>
+      <c r="M46" s="18" t="inlineStr"/>
+      <c r="N46" s="18" t="inlineStr"/>
+      <c r="O46" s="18" t="inlineStr"/>
+      <c r="P46" s="18" t="inlineStr"/>
+      <c r="Q46" s="18" t="inlineStr"/>
+      <c r="R46" s="18" t="inlineStr"/>
+      <c r="S46" s="18" t="inlineStr"/>
+      <c r="T46" s="18" t="inlineStr"/>
+      <c r="U46" s="18" t="inlineStr"/>
+      <c r="V46" s="18" t="inlineStr"/>
+      <c r="W46" s="18" t="inlineStr"/>
+      <c r="X46" s="18" t="inlineStr"/>
+      <c r="Y46" s="18" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="16" t="n">
@@ -2845,6 +3822,25 @@
       <c r="D47" s="18" t="inlineStr"/>
       <c r="E47" s="18" t="inlineStr"/>
       <c r="F47" s="18" t="inlineStr"/>
+      <c r="G47" s="18" t="inlineStr"/>
+      <c r="H47" s="18" t="inlineStr"/>
+      <c r="I47" s="18" t="inlineStr"/>
+      <c r="J47" s="18" t="inlineStr"/>
+      <c r="K47" s="18" t="inlineStr"/>
+      <c r="L47" s="18" t="inlineStr"/>
+      <c r="M47" s="18" t="inlineStr"/>
+      <c r="N47" s="18" t="inlineStr"/>
+      <c r="O47" s="18" t="inlineStr"/>
+      <c r="P47" s="18" t="inlineStr"/>
+      <c r="Q47" s="18" t="inlineStr"/>
+      <c r="R47" s="18" t="inlineStr"/>
+      <c r="S47" s="18" t="inlineStr"/>
+      <c r="T47" s="18" t="inlineStr"/>
+      <c r="U47" s="18" t="inlineStr"/>
+      <c r="V47" s="18" t="inlineStr"/>
+      <c r="W47" s="18" t="inlineStr"/>
+      <c r="X47" s="18" t="inlineStr"/>
+      <c r="Y47" s="18" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="16" t="n">
@@ -2859,6 +3855,25 @@
       <c r="D48" s="18" t="inlineStr"/>
       <c r="E48" s="18" t="inlineStr"/>
       <c r="F48" s="18" t="inlineStr"/>
+      <c r="G48" s="18" t="inlineStr"/>
+      <c r="H48" s="18" t="inlineStr"/>
+      <c r="I48" s="18" t="inlineStr"/>
+      <c r="J48" s="18" t="inlineStr"/>
+      <c r="K48" s="18" t="inlineStr"/>
+      <c r="L48" s="18" t="inlineStr"/>
+      <c r="M48" s="18" t="inlineStr"/>
+      <c r="N48" s="18" t="inlineStr"/>
+      <c r="O48" s="18" t="inlineStr"/>
+      <c r="P48" s="18" t="inlineStr"/>
+      <c r="Q48" s="18" t="inlineStr"/>
+      <c r="R48" s="18" t="inlineStr"/>
+      <c r="S48" s="18" t="inlineStr"/>
+      <c r="T48" s="18" t="inlineStr"/>
+      <c r="U48" s="18" t="inlineStr"/>
+      <c r="V48" s="18" t="inlineStr"/>
+      <c r="W48" s="18" t="inlineStr"/>
+      <c r="X48" s="18" t="inlineStr"/>
+      <c r="Y48" s="18" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="16" t="n">
@@ -2873,6 +3888,25 @@
       <c r="D49" s="18" t="inlineStr"/>
       <c r="E49" s="18" t="inlineStr"/>
       <c r="F49" s="18" t="inlineStr"/>
+      <c r="G49" s="18" t="inlineStr"/>
+      <c r="H49" s="18" t="inlineStr"/>
+      <c r="I49" s="18" t="inlineStr"/>
+      <c r="J49" s="18" t="inlineStr"/>
+      <c r="K49" s="18" t="inlineStr"/>
+      <c r="L49" s="18" t="inlineStr"/>
+      <c r="M49" s="18" t="inlineStr"/>
+      <c r="N49" s="18" t="inlineStr"/>
+      <c r="O49" s="18" t="inlineStr"/>
+      <c r="P49" s="18" t="inlineStr"/>
+      <c r="Q49" s="18" t="inlineStr"/>
+      <c r="R49" s="18" t="inlineStr"/>
+      <c r="S49" s="18" t="inlineStr"/>
+      <c r="T49" s="18" t="inlineStr"/>
+      <c r="U49" s="18" t="inlineStr"/>
+      <c r="V49" s="18" t="inlineStr"/>
+      <c r="W49" s="18" t="inlineStr"/>
+      <c r="X49" s="18" t="inlineStr"/>
+      <c r="Y49" s="18" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="16" t="n">
@@ -2887,6 +3921,25 @@
       <c r="D50" s="18" t="inlineStr"/>
       <c r="E50" s="18" t="inlineStr"/>
       <c r="F50" s="18" t="inlineStr"/>
+      <c r="G50" s="18" t="inlineStr"/>
+      <c r="H50" s="18" t="inlineStr"/>
+      <c r="I50" s="18" t="inlineStr"/>
+      <c r="J50" s="18" t="inlineStr"/>
+      <c r="K50" s="18" t="inlineStr"/>
+      <c r="L50" s="18" t="inlineStr"/>
+      <c r="M50" s="18" t="inlineStr"/>
+      <c r="N50" s="18" t="inlineStr"/>
+      <c r="O50" s="18" t="inlineStr"/>
+      <c r="P50" s="18" t="inlineStr"/>
+      <c r="Q50" s="18" t="inlineStr"/>
+      <c r="R50" s="18" t="inlineStr"/>
+      <c r="S50" s="18" t="inlineStr"/>
+      <c r="T50" s="18" t="inlineStr"/>
+      <c r="U50" s="18" t="inlineStr"/>
+      <c r="V50" s="18" t="inlineStr"/>
+      <c r="W50" s="18" t="inlineStr"/>
+      <c r="X50" s="18" t="inlineStr"/>
+      <c r="Y50" s="18" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="16" t="n">
@@ -2901,6 +3954,25 @@
       <c r="D51" s="18" t="inlineStr"/>
       <c r="E51" s="18" t="inlineStr"/>
       <c r="F51" s="18" t="inlineStr"/>
+      <c r="G51" s="18" t="inlineStr"/>
+      <c r="H51" s="18" t="inlineStr"/>
+      <c r="I51" s="18" t="inlineStr"/>
+      <c r="J51" s="18" t="inlineStr"/>
+      <c r="K51" s="18" t="inlineStr"/>
+      <c r="L51" s="18" t="inlineStr"/>
+      <c r="M51" s="18" t="inlineStr"/>
+      <c r="N51" s="18" t="inlineStr"/>
+      <c r="O51" s="18" t="inlineStr"/>
+      <c r="P51" s="18" t="inlineStr"/>
+      <c r="Q51" s="18" t="inlineStr"/>
+      <c r="R51" s="18" t="inlineStr"/>
+      <c r="S51" s="18" t="inlineStr"/>
+      <c r="T51" s="18" t="inlineStr"/>
+      <c r="U51" s="18" t="inlineStr"/>
+      <c r="V51" s="18" t="inlineStr"/>
+      <c r="W51" s="18" t="inlineStr"/>
+      <c r="X51" s="18" t="inlineStr"/>
+      <c r="Y51" s="18" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="16" t="n">
@@ -2915,6 +3987,25 @@
       <c r="D52" s="18" t="inlineStr"/>
       <c r="E52" s="18" t="inlineStr"/>
       <c r="F52" s="18" t="inlineStr"/>
+      <c r="G52" s="18" t="inlineStr"/>
+      <c r="H52" s="18" t="inlineStr"/>
+      <c r="I52" s="18" t="inlineStr"/>
+      <c r="J52" s="18" t="inlineStr"/>
+      <c r="K52" s="18" t="inlineStr"/>
+      <c r="L52" s="18" t="inlineStr"/>
+      <c r="M52" s="18" t="inlineStr"/>
+      <c r="N52" s="18" t="inlineStr"/>
+      <c r="O52" s="18" t="inlineStr"/>
+      <c r="P52" s="18" t="inlineStr"/>
+      <c r="Q52" s="18" t="inlineStr"/>
+      <c r="R52" s="18" t="inlineStr"/>
+      <c r="S52" s="18" t="inlineStr"/>
+      <c r="T52" s="18" t="inlineStr"/>
+      <c r="U52" s="18" t="inlineStr"/>
+      <c r="V52" s="18" t="inlineStr"/>
+      <c r="W52" s="18" t="inlineStr"/>
+      <c r="X52" s="18" t="inlineStr"/>
+      <c r="Y52" s="18" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="16" t="n">
@@ -2929,6 +4020,25 @@
       <c r="D53" s="18" t="inlineStr"/>
       <c r="E53" s="18" t="inlineStr"/>
       <c r="F53" s="18" t="inlineStr"/>
+      <c r="G53" s="18" t="inlineStr"/>
+      <c r="H53" s="18" t="inlineStr"/>
+      <c r="I53" s="18" t="inlineStr"/>
+      <c r="J53" s="18" t="inlineStr"/>
+      <c r="K53" s="18" t="inlineStr"/>
+      <c r="L53" s="18" t="inlineStr"/>
+      <c r="M53" s="18" t="inlineStr"/>
+      <c r="N53" s="18" t="inlineStr"/>
+      <c r="O53" s="18" t="inlineStr"/>
+      <c r="P53" s="18" t="inlineStr"/>
+      <c r="Q53" s="18" t="inlineStr"/>
+      <c r="R53" s="18" t="inlineStr"/>
+      <c r="S53" s="18" t="inlineStr"/>
+      <c r="T53" s="18" t="inlineStr"/>
+      <c r="U53" s="18" t="inlineStr"/>
+      <c r="V53" s="18" t="inlineStr"/>
+      <c r="W53" s="18" t="inlineStr"/>
+      <c r="X53" s="18" t="inlineStr"/>
+      <c r="Y53" s="18" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="16" t="n">
@@ -2943,6 +4053,25 @@
       <c r="D54" s="18" t="inlineStr"/>
       <c r="E54" s="18" t="inlineStr"/>
       <c r="F54" s="18" t="inlineStr"/>
+      <c r="G54" s="18" t="inlineStr"/>
+      <c r="H54" s="18" t="inlineStr"/>
+      <c r="I54" s="18" t="inlineStr"/>
+      <c r="J54" s="18" t="inlineStr"/>
+      <c r="K54" s="18" t="inlineStr"/>
+      <c r="L54" s="18" t="inlineStr"/>
+      <c r="M54" s="18" t="inlineStr"/>
+      <c r="N54" s="18" t="inlineStr"/>
+      <c r="O54" s="18" t="inlineStr"/>
+      <c r="P54" s="18" t="inlineStr"/>
+      <c r="Q54" s="18" t="inlineStr"/>
+      <c r="R54" s="18" t="inlineStr"/>
+      <c r="S54" s="18" t="inlineStr"/>
+      <c r="T54" s="18" t="inlineStr"/>
+      <c r="U54" s="18" t="inlineStr"/>
+      <c r="V54" s="18" t="inlineStr"/>
+      <c r="W54" s="18" t="inlineStr"/>
+      <c r="X54" s="18" t="inlineStr"/>
+      <c r="Y54" s="18" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="16" t="n">
@@ -2957,6 +4086,25 @@
       <c r="D55" s="18" t="inlineStr"/>
       <c r="E55" s="18" t="inlineStr"/>
       <c r="F55" s="18" t="inlineStr"/>
+      <c r="G55" s="18" t="inlineStr"/>
+      <c r="H55" s="18" t="inlineStr"/>
+      <c r="I55" s="18" t="inlineStr"/>
+      <c r="J55" s="18" t="inlineStr"/>
+      <c r="K55" s="18" t="inlineStr"/>
+      <c r="L55" s="18" t="inlineStr"/>
+      <c r="M55" s="18" t="inlineStr"/>
+      <c r="N55" s="18" t="inlineStr"/>
+      <c r="O55" s="18" t="inlineStr"/>
+      <c r="P55" s="18" t="inlineStr"/>
+      <c r="Q55" s="18" t="inlineStr"/>
+      <c r="R55" s="18" t="inlineStr"/>
+      <c r="S55" s="18" t="inlineStr"/>
+      <c r="T55" s="18" t="inlineStr"/>
+      <c r="U55" s="18" t="inlineStr"/>
+      <c r="V55" s="18" t="inlineStr"/>
+      <c r="W55" s="18" t="inlineStr"/>
+      <c r="X55" s="18" t="inlineStr"/>
+      <c r="Y55" s="18" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="16" t="n">
@@ -2971,6 +4119,25 @@
       <c r="D56" s="18" t="inlineStr"/>
       <c r="E56" s="18" t="inlineStr"/>
       <c r="F56" s="18" t="inlineStr"/>
+      <c r="G56" s="18" t="inlineStr"/>
+      <c r="H56" s="18" t="inlineStr"/>
+      <c r="I56" s="18" t="inlineStr"/>
+      <c r="J56" s="18" t="inlineStr"/>
+      <c r="K56" s="18" t="inlineStr"/>
+      <c r="L56" s="18" t="inlineStr"/>
+      <c r="M56" s="18" t="inlineStr"/>
+      <c r="N56" s="18" t="inlineStr"/>
+      <c r="O56" s="18" t="inlineStr"/>
+      <c r="P56" s="18" t="inlineStr"/>
+      <c r="Q56" s="18" t="inlineStr"/>
+      <c r="R56" s="18" t="inlineStr"/>
+      <c r="S56" s="18" t="inlineStr"/>
+      <c r="T56" s="18" t="inlineStr"/>
+      <c r="U56" s="18" t="inlineStr"/>
+      <c r="V56" s="18" t="inlineStr"/>
+      <c r="W56" s="18" t="inlineStr"/>
+      <c r="X56" s="18" t="inlineStr"/>
+      <c r="Y56" s="18" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="16" t="n">
@@ -2985,6 +4152,25 @@
       <c r="D57" s="18" t="inlineStr"/>
       <c r="E57" s="18" t="inlineStr"/>
       <c r="F57" s="18" t="inlineStr"/>
+      <c r="G57" s="18" t="inlineStr"/>
+      <c r="H57" s="18" t="inlineStr"/>
+      <c r="I57" s="18" t="inlineStr"/>
+      <c r="J57" s="18" t="inlineStr"/>
+      <c r="K57" s="18" t="inlineStr"/>
+      <c r="L57" s="18" t="inlineStr"/>
+      <c r="M57" s="18" t="inlineStr"/>
+      <c r="N57" s="18" t="inlineStr"/>
+      <c r="O57" s="18" t="inlineStr"/>
+      <c r="P57" s="18" t="inlineStr"/>
+      <c r="Q57" s="18" t="inlineStr"/>
+      <c r="R57" s="18" t="inlineStr"/>
+      <c r="S57" s="18" t="inlineStr"/>
+      <c r="T57" s="18" t="inlineStr"/>
+      <c r="U57" s="18" t="inlineStr"/>
+      <c r="V57" s="18" t="inlineStr"/>
+      <c r="W57" s="18" t="inlineStr"/>
+      <c r="X57" s="18" t="inlineStr"/>
+      <c r="Y57" s="18" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="16" t="n">
@@ -2999,6 +4185,25 @@
       <c r="D58" s="18" t="inlineStr"/>
       <c r="E58" s="18" t="inlineStr"/>
       <c r="F58" s="18" t="inlineStr"/>
+      <c r="G58" s="18" t="inlineStr"/>
+      <c r="H58" s="18" t="inlineStr"/>
+      <c r="I58" s="18" t="inlineStr"/>
+      <c r="J58" s="18" t="inlineStr"/>
+      <c r="K58" s="18" t="inlineStr"/>
+      <c r="L58" s="18" t="inlineStr"/>
+      <c r="M58" s="18" t="inlineStr"/>
+      <c r="N58" s="18" t="inlineStr"/>
+      <c r="O58" s="18" t="inlineStr"/>
+      <c r="P58" s="18" t="inlineStr"/>
+      <c r="Q58" s="18" t="inlineStr"/>
+      <c r="R58" s="18" t="inlineStr"/>
+      <c r="S58" s="18" t="inlineStr"/>
+      <c r="T58" s="18" t="inlineStr"/>
+      <c r="U58" s="18" t="inlineStr"/>
+      <c r="V58" s="18" t="inlineStr"/>
+      <c r="W58" s="18" t="inlineStr"/>
+      <c r="X58" s="18" t="inlineStr"/>
+      <c r="Y58" s="18" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="16" t="n">
@@ -3013,6 +4218,29 @@
       <c r="D59" s="18" t="inlineStr"/>
       <c r="E59" s="18" t="inlineStr"/>
       <c r="F59" s="18" t="inlineStr"/>
+      <c r="G59" s="18" t="inlineStr"/>
+      <c r="H59" s="18" t="inlineStr"/>
+      <c r="I59" s="18" t="inlineStr"/>
+      <c r="J59" s="18" t="inlineStr"/>
+      <c r="K59" s="18" t="inlineStr"/>
+      <c r="L59" s="18" t="inlineStr"/>
+      <c r="M59" s="18" t="inlineStr"/>
+      <c r="N59" s="18" t="inlineStr"/>
+      <c r="O59" s="18" t="inlineStr"/>
+      <c r="P59" s="18" t="inlineStr"/>
+      <c r="Q59" s="18" t="inlineStr"/>
+      <c r="R59" s="18" t="inlineStr"/>
+      <c r="S59" s="18" t="inlineStr"/>
+      <c r="T59" s="18" t="inlineStr"/>
+      <c r="U59" s="18" t="inlineStr"/>
+      <c r="V59" s="18" t="inlineStr"/>
+      <c r="W59" s="18" t="inlineStr"/>
+      <c r="X59" s="18" t="inlineStr"/>
+      <c r="Y59" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 1 abstract cited by the corpus</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="16" t="n">
@@ -3027,6 +4255,25 @@
       <c r="D60" s="18" t="inlineStr"/>
       <c r="E60" s="18" t="inlineStr"/>
       <c r="F60" s="18" t="inlineStr"/>
+      <c r="G60" s="18" t="inlineStr"/>
+      <c r="H60" s="18" t="inlineStr"/>
+      <c r="I60" s="18" t="inlineStr"/>
+      <c r="J60" s="18" t="inlineStr"/>
+      <c r="K60" s="18" t="inlineStr"/>
+      <c r="L60" s="18" t="inlineStr"/>
+      <c r="M60" s="18" t="inlineStr"/>
+      <c r="N60" s="18" t="inlineStr"/>
+      <c r="O60" s="18" t="inlineStr"/>
+      <c r="P60" s="18" t="inlineStr"/>
+      <c r="Q60" s="18" t="inlineStr"/>
+      <c r="R60" s="18" t="inlineStr"/>
+      <c r="S60" s="18" t="inlineStr"/>
+      <c r="T60" s="18" t="inlineStr"/>
+      <c r="U60" s="18" t="inlineStr"/>
+      <c r="V60" s="18" t="inlineStr"/>
+      <c r="W60" s="18" t="inlineStr"/>
+      <c r="X60" s="18" t="inlineStr"/>
+      <c r="Y60" s="18" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="16" t="n">
@@ -3041,6 +4288,25 @@
       <c r="D61" s="18" t="inlineStr"/>
       <c r="E61" s="18" t="inlineStr"/>
       <c r="F61" s="18" t="inlineStr"/>
+      <c r="G61" s="18" t="inlineStr"/>
+      <c r="H61" s="18" t="inlineStr"/>
+      <c r="I61" s="18" t="inlineStr"/>
+      <c r="J61" s="18" t="inlineStr"/>
+      <c r="K61" s="18" t="inlineStr"/>
+      <c r="L61" s="18" t="inlineStr"/>
+      <c r="M61" s="18" t="inlineStr"/>
+      <c r="N61" s="18" t="inlineStr"/>
+      <c r="O61" s="18" t="inlineStr"/>
+      <c r="P61" s="18" t="inlineStr"/>
+      <c r="Q61" s="18" t="inlineStr"/>
+      <c r="R61" s="18" t="inlineStr"/>
+      <c r="S61" s="18" t="inlineStr"/>
+      <c r="T61" s="18" t="inlineStr"/>
+      <c r="U61" s="18" t="inlineStr"/>
+      <c r="V61" s="18" t="inlineStr"/>
+      <c r="W61" s="18" t="inlineStr"/>
+      <c r="X61" s="18" t="inlineStr"/>
+      <c r="Y61" s="18" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="16" t="n">
@@ -3055,6 +4321,29 @@
       <c r="D62" s="18" t="inlineStr"/>
       <c r="E62" s="18" t="inlineStr"/>
       <c r="F62" s="18" t="inlineStr"/>
+      <c r="G62" s="18" t="inlineStr"/>
+      <c r="H62" s="18" t="inlineStr"/>
+      <c r="I62" s="18" t="inlineStr"/>
+      <c r="J62" s="18" t="inlineStr"/>
+      <c r="K62" s="18" t="inlineStr"/>
+      <c r="L62" s="18" t="inlineStr"/>
+      <c r="M62" s="18" t="inlineStr"/>
+      <c r="N62" s="18" t="inlineStr"/>
+      <c r="O62" s="18" t="inlineStr"/>
+      <c r="P62" s="18" t="inlineStr"/>
+      <c r="Q62" s="18" t="inlineStr"/>
+      <c r="R62" s="18" t="inlineStr"/>
+      <c r="S62" s="18" t="inlineStr"/>
+      <c r="T62" s="18" t="inlineStr"/>
+      <c r="U62" s="18" t="inlineStr"/>
+      <c r="V62" s="18" t="inlineStr"/>
+      <c r="W62" s="18" t="inlineStr"/>
+      <c r="X62" s="18" t="inlineStr"/>
+      <c r="Y62" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 2 abstracts cited by the corpus</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="16" t="n">
@@ -3069,6 +4358,25 @@
       <c r="D63" s="18" t="inlineStr"/>
       <c r="E63" s="18" t="inlineStr"/>
       <c r="F63" s="18" t="inlineStr"/>
+      <c r="G63" s="18" t="inlineStr"/>
+      <c r="H63" s="18" t="inlineStr"/>
+      <c r="I63" s="18" t="inlineStr"/>
+      <c r="J63" s="18" t="inlineStr"/>
+      <c r="K63" s="18" t="inlineStr"/>
+      <c r="L63" s="18" t="inlineStr"/>
+      <c r="M63" s="18" t="inlineStr"/>
+      <c r="N63" s="18" t="inlineStr"/>
+      <c r="O63" s="18" t="inlineStr"/>
+      <c r="P63" s="18" t="inlineStr"/>
+      <c r="Q63" s="18" t="inlineStr"/>
+      <c r="R63" s="18" t="inlineStr"/>
+      <c r="S63" s="18" t="inlineStr"/>
+      <c r="T63" s="18" t="inlineStr"/>
+      <c r="U63" s="18" t="inlineStr"/>
+      <c r="V63" s="18" t="inlineStr"/>
+      <c r="W63" s="18" t="inlineStr"/>
+      <c r="X63" s="18" t="inlineStr"/>
+      <c r="Y63" s="18" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="16" t="n">
@@ -3083,6 +4391,25 @@
       <c r="D64" s="18" t="inlineStr"/>
       <c r="E64" s="18" t="inlineStr"/>
       <c r="F64" s="18" t="inlineStr"/>
+      <c r="G64" s="18" t="inlineStr"/>
+      <c r="H64" s="18" t="inlineStr"/>
+      <c r="I64" s="18" t="inlineStr"/>
+      <c r="J64" s="18" t="inlineStr"/>
+      <c r="K64" s="18" t="inlineStr"/>
+      <c r="L64" s="18" t="inlineStr"/>
+      <c r="M64" s="18" t="inlineStr"/>
+      <c r="N64" s="18" t="inlineStr"/>
+      <c r="O64" s="18" t="inlineStr"/>
+      <c r="P64" s="18" t="inlineStr"/>
+      <c r="Q64" s="18" t="inlineStr"/>
+      <c r="R64" s="18" t="inlineStr"/>
+      <c r="S64" s="18" t="inlineStr"/>
+      <c r="T64" s="18" t="inlineStr"/>
+      <c r="U64" s="18" t="inlineStr"/>
+      <c r="V64" s="18" t="inlineStr"/>
+      <c r="W64" s="18" t="inlineStr"/>
+      <c r="X64" s="18" t="inlineStr"/>
+      <c r="Y64" s="18" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="16" t="n">
@@ -3097,6 +4424,25 @@
       <c r="D65" s="18" t="inlineStr"/>
       <c r="E65" s="18" t="inlineStr"/>
       <c r="F65" s="18" t="inlineStr"/>
+      <c r="G65" s="18" t="inlineStr"/>
+      <c r="H65" s="18" t="inlineStr"/>
+      <c r="I65" s="18" t="inlineStr"/>
+      <c r="J65" s="18" t="inlineStr"/>
+      <c r="K65" s="18" t="inlineStr"/>
+      <c r="L65" s="18" t="inlineStr"/>
+      <c r="M65" s="18" t="inlineStr"/>
+      <c r="N65" s="18" t="inlineStr"/>
+      <c r="O65" s="18" t="inlineStr"/>
+      <c r="P65" s="18" t="inlineStr"/>
+      <c r="Q65" s="18" t="inlineStr"/>
+      <c r="R65" s="18" t="inlineStr"/>
+      <c r="S65" s="18" t="inlineStr"/>
+      <c r="T65" s="18" t="inlineStr"/>
+      <c r="U65" s="18" t="inlineStr"/>
+      <c r="V65" s="18" t="inlineStr"/>
+      <c r="W65" s="18" t="inlineStr"/>
+      <c r="X65" s="18" t="inlineStr"/>
+      <c r="Y65" s="18" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="16" t="n">
@@ -3111,6 +4457,29 @@
       <c r="D66" s="18" t="inlineStr"/>
       <c r="E66" s="18" t="inlineStr"/>
       <c r="F66" s="18" t="inlineStr"/>
+      <c r="G66" s="18" t="inlineStr"/>
+      <c r="H66" s="18" t="inlineStr"/>
+      <c r="I66" s="18" t="inlineStr"/>
+      <c r="J66" s="18" t="inlineStr"/>
+      <c r="K66" s="18" t="inlineStr"/>
+      <c r="L66" s="18" t="inlineStr"/>
+      <c r="M66" s="18" t="inlineStr"/>
+      <c r="N66" s="18" t="inlineStr"/>
+      <c r="O66" s="18" t="inlineStr"/>
+      <c r="P66" s="18" t="inlineStr"/>
+      <c r="Q66" s="18" t="inlineStr"/>
+      <c r="R66" s="18" t="inlineStr"/>
+      <c r="S66" s="18" t="inlineStr"/>
+      <c r="T66" s="18" t="inlineStr"/>
+      <c r="U66" s="18" t="inlineStr"/>
+      <c r="V66" s="18" t="inlineStr"/>
+      <c r="W66" s="18" t="inlineStr"/>
+      <c r="X66" s="18" t="inlineStr"/>
+      <c r="Y66" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 1 abstract cited by the corpus</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="16" t="n">
@@ -3125,6 +4494,25 @@
       <c r="D67" s="18" t="inlineStr"/>
       <c r="E67" s="18" t="inlineStr"/>
       <c r="F67" s="18" t="inlineStr"/>
+      <c r="G67" s="18" t="inlineStr"/>
+      <c r="H67" s="18" t="inlineStr"/>
+      <c r="I67" s="18" t="inlineStr"/>
+      <c r="J67" s="18" t="inlineStr"/>
+      <c r="K67" s="18" t="inlineStr"/>
+      <c r="L67" s="18" t="inlineStr"/>
+      <c r="M67" s="18" t="inlineStr"/>
+      <c r="N67" s="18" t="inlineStr"/>
+      <c r="O67" s="18" t="inlineStr"/>
+      <c r="P67" s="18" t="inlineStr"/>
+      <c r="Q67" s="18" t="inlineStr"/>
+      <c r="R67" s="18" t="inlineStr"/>
+      <c r="S67" s="18" t="inlineStr"/>
+      <c r="T67" s="18" t="inlineStr"/>
+      <c r="U67" s="18" t="inlineStr"/>
+      <c r="V67" s="18" t="inlineStr"/>
+      <c r="W67" s="18" t="inlineStr"/>
+      <c r="X67" s="18" t="inlineStr"/>
+      <c r="Y67" s="18" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="16" t="n">
@@ -3139,6 +4527,25 @@
       <c r="D68" s="18" t="inlineStr"/>
       <c r="E68" s="18" t="inlineStr"/>
       <c r="F68" s="18" t="inlineStr"/>
+      <c r="G68" s="18" t="inlineStr"/>
+      <c r="H68" s="18" t="inlineStr"/>
+      <c r="I68" s="18" t="inlineStr"/>
+      <c r="J68" s="18" t="inlineStr"/>
+      <c r="K68" s="18" t="inlineStr"/>
+      <c r="L68" s="18" t="inlineStr"/>
+      <c r="M68" s="18" t="inlineStr"/>
+      <c r="N68" s="18" t="inlineStr"/>
+      <c r="O68" s="18" t="inlineStr"/>
+      <c r="P68" s="18" t="inlineStr"/>
+      <c r="Q68" s="18" t="inlineStr"/>
+      <c r="R68" s="18" t="inlineStr"/>
+      <c r="S68" s="18" t="inlineStr"/>
+      <c r="T68" s="18" t="inlineStr"/>
+      <c r="U68" s="18" t="inlineStr"/>
+      <c r="V68" s="18" t="inlineStr"/>
+      <c r="W68" s="18" t="inlineStr"/>
+      <c r="X68" s="18" t="inlineStr"/>
+      <c r="Y68" s="18" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="16" t="n">
@@ -3157,6 +4564,29 @@
       <c r="D69" s="18" t="inlineStr"/>
       <c r="E69" s="18" t="inlineStr"/>
       <c r="F69" s="18" t="inlineStr"/>
+      <c r="G69" s="18" t="inlineStr"/>
+      <c r="H69" s="18" t="inlineStr"/>
+      <c r="I69" s="18" t="inlineStr"/>
+      <c r="J69" s="18" t="inlineStr"/>
+      <c r="K69" s="18" t="inlineStr"/>
+      <c r="L69" s="18" t="inlineStr"/>
+      <c r="M69" s="18" t="inlineStr"/>
+      <c r="N69" s="18" t="inlineStr"/>
+      <c r="O69" s="18" t="inlineStr"/>
+      <c r="P69" s="18" t="inlineStr"/>
+      <c r="Q69" s="18" t="inlineStr"/>
+      <c r="R69" s="18" t="inlineStr"/>
+      <c r="S69" s="18" t="inlineStr"/>
+      <c r="T69" s="18" t="inlineStr"/>
+      <c r="U69" s="18" t="inlineStr"/>
+      <c r="V69" s="18" t="inlineStr"/>
+      <c r="W69" s="18" t="inlineStr"/>
+      <c r="X69" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 5 abstracts cited by the corpus</t>
+        </is>
+      </c>
+      <c r="Y69" s="18" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="16" t="n">
@@ -3175,6 +4605,29 @@
       <c r="D70" s="18" t="inlineStr"/>
       <c r="E70" s="18" t="inlineStr"/>
       <c r="F70" s="18" t="inlineStr"/>
+      <c r="G70" s="18" t="inlineStr"/>
+      <c r="H70" s="18" t="inlineStr"/>
+      <c r="I70" s="18" t="inlineStr"/>
+      <c r="J70" s="18" t="inlineStr"/>
+      <c r="K70" s="18" t="inlineStr"/>
+      <c r="L70" s="18" t="inlineStr"/>
+      <c r="M70" s="18" t="inlineStr"/>
+      <c r="N70" s="18" t="inlineStr"/>
+      <c r="O70" s="18" t="inlineStr"/>
+      <c r="P70" s="18" t="inlineStr"/>
+      <c r="Q70" s="18" t="inlineStr"/>
+      <c r="R70" s="18" t="inlineStr"/>
+      <c r="S70" s="18" t="inlineStr"/>
+      <c r="T70" s="18" t="inlineStr"/>
+      <c r="U70" s="18" t="inlineStr"/>
+      <c r="V70" s="18" t="inlineStr"/>
+      <c r="W70" s="18" t="inlineStr"/>
+      <c r="X70" s="18" t="inlineStr"/>
+      <c r="Y70" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 1 abstract cited by the corpus</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="16" t="n">
@@ -3193,6 +4646,25 @@
       <c r="D71" s="18" t="inlineStr"/>
       <c r="E71" s="18" t="inlineStr"/>
       <c r="F71" s="18" t="inlineStr"/>
+      <c r="G71" s="18" t="inlineStr"/>
+      <c r="H71" s="18" t="inlineStr"/>
+      <c r="I71" s="18" t="inlineStr"/>
+      <c r="J71" s="18" t="inlineStr"/>
+      <c r="K71" s="18" t="inlineStr"/>
+      <c r="L71" s="18" t="inlineStr"/>
+      <c r="M71" s="18" t="inlineStr"/>
+      <c r="N71" s="18" t="inlineStr"/>
+      <c r="O71" s="18" t="inlineStr"/>
+      <c r="P71" s="18" t="inlineStr"/>
+      <c r="Q71" s="18" t="inlineStr"/>
+      <c r="R71" s="18" t="inlineStr"/>
+      <c r="S71" s="18" t="inlineStr"/>
+      <c r="T71" s="18" t="inlineStr"/>
+      <c r="U71" s="18" t="inlineStr"/>
+      <c r="V71" s="18" t="inlineStr"/>
+      <c r="W71" s="18" t="inlineStr"/>
+      <c r="X71" s="18" t="inlineStr"/>
+      <c r="Y71" s="18" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="16" t="n">
@@ -3211,6 +4683,33 @@
       <c r="D72" s="18" t="inlineStr"/>
       <c r="E72" s="18" t="inlineStr"/>
       <c r="F72" s="18" t="inlineStr"/>
+      <c r="G72" s="18" t="inlineStr"/>
+      <c r="H72" s="18" t="inlineStr"/>
+      <c r="I72" s="18" t="inlineStr"/>
+      <c r="J72" s="18" t="inlineStr"/>
+      <c r="K72" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 2 abstracts cited by the corpus</t>
+        </is>
+      </c>
+      <c r="L72" s="18" t="inlineStr"/>
+      <c r="M72" s="18" t="inlineStr"/>
+      <c r="N72" s="18" t="inlineStr"/>
+      <c r="O72" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 37 abstracts cited by the corpus</t>
+        </is>
+      </c>
+      <c r="P72" s="18" t="inlineStr"/>
+      <c r="Q72" s="18" t="inlineStr"/>
+      <c r="R72" s="18" t="inlineStr"/>
+      <c r="S72" s="18" t="inlineStr"/>
+      <c r="T72" s="18" t="inlineStr"/>
+      <c r="U72" s="18" t="inlineStr"/>
+      <c r="V72" s="18" t="inlineStr"/>
+      <c r="W72" s="18" t="inlineStr"/>
+      <c r="X72" s="18" t="inlineStr"/>
+      <c r="Y72" s="18" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="16" t="n">
@@ -3229,6 +4728,29 @@
       <c r="D73" s="18" t="inlineStr"/>
       <c r="E73" s="18" t="inlineStr"/>
       <c r="F73" s="18" t="inlineStr"/>
+      <c r="G73" s="18" t="inlineStr"/>
+      <c r="H73" s="18" t="inlineStr"/>
+      <c r="I73" s="18" t="inlineStr"/>
+      <c r="J73" s="18" t="inlineStr"/>
+      <c r="K73" s="18" t="inlineStr"/>
+      <c r="L73" s="18" t="inlineStr"/>
+      <c r="M73" s="18" t="inlineStr"/>
+      <c r="N73" s="18" t="inlineStr"/>
+      <c r="O73" s="18" t="inlineStr"/>
+      <c r="P73" s="18" t="inlineStr"/>
+      <c r="Q73" s="18" t="inlineStr"/>
+      <c r="R73" s="18" t="inlineStr"/>
+      <c r="S73" s="18" t="inlineStr"/>
+      <c r="T73" s="18" t="inlineStr"/>
+      <c r="U73" s="18" t="inlineStr"/>
+      <c r="V73" s="18" t="inlineStr"/>
+      <c r="W73" s="18" t="inlineStr"/>
+      <c r="X73" s="18" t="inlineStr"/>
+      <c r="Y73" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 1 abstract cited by the corpus</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="16" t="n">
@@ -3247,6 +4769,25 @@
       <c r="D74" s="18" t="inlineStr"/>
       <c r="E74" s="18" t="inlineStr"/>
       <c r="F74" s="18" t="inlineStr"/>
+      <c r="G74" s="18" t="inlineStr"/>
+      <c r="H74" s="18" t="inlineStr"/>
+      <c r="I74" s="18" t="inlineStr"/>
+      <c r="J74" s="18" t="inlineStr"/>
+      <c r="K74" s="18" t="inlineStr"/>
+      <c r="L74" s="18" t="inlineStr"/>
+      <c r="M74" s="18" t="inlineStr"/>
+      <c r="N74" s="18" t="inlineStr"/>
+      <c r="O74" s="18" t="inlineStr"/>
+      <c r="P74" s="18" t="inlineStr"/>
+      <c r="Q74" s="18" t="inlineStr"/>
+      <c r="R74" s="18" t="inlineStr"/>
+      <c r="S74" s="18" t="inlineStr"/>
+      <c r="T74" s="18" t="inlineStr"/>
+      <c r="U74" s="18" t="inlineStr"/>
+      <c r="V74" s="18" t="inlineStr"/>
+      <c r="W74" s="18" t="inlineStr"/>
+      <c r="X74" s="18" t="inlineStr"/>
+      <c r="Y74" s="18" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="16" t="n">
@@ -3265,6 +4806,25 @@
       <c r="D75" s="18" t="inlineStr"/>
       <c r="E75" s="18" t="inlineStr"/>
       <c r="F75" s="18" t="inlineStr"/>
+      <c r="G75" s="18" t="inlineStr"/>
+      <c r="H75" s="18" t="inlineStr"/>
+      <c r="I75" s="18" t="inlineStr"/>
+      <c r="J75" s="18" t="inlineStr"/>
+      <c r="K75" s="18" t="inlineStr"/>
+      <c r="L75" s="18" t="inlineStr"/>
+      <c r="M75" s="18" t="inlineStr"/>
+      <c r="N75" s="18" t="inlineStr"/>
+      <c r="O75" s="18" t="inlineStr"/>
+      <c r="P75" s="18" t="inlineStr"/>
+      <c r="Q75" s="18" t="inlineStr"/>
+      <c r="R75" s="18" t="inlineStr"/>
+      <c r="S75" s="18" t="inlineStr"/>
+      <c r="T75" s="18" t="inlineStr"/>
+      <c r="U75" s="18" t="inlineStr"/>
+      <c r="V75" s="18" t="inlineStr"/>
+      <c r="W75" s="18" t="inlineStr"/>
+      <c r="X75" s="18" t="inlineStr"/>
+      <c r="Y75" s="18" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="16" t="n">
@@ -3283,6 +4843,25 @@
       <c r="D76" s="18" t="inlineStr"/>
       <c r="E76" s="18" t="inlineStr"/>
       <c r="F76" s="18" t="inlineStr"/>
+      <c r="G76" s="18" t="inlineStr"/>
+      <c r="H76" s="18" t="inlineStr"/>
+      <c r="I76" s="18" t="inlineStr"/>
+      <c r="J76" s="18" t="inlineStr"/>
+      <c r="K76" s="18" t="inlineStr"/>
+      <c r="L76" s="18" t="inlineStr"/>
+      <c r="M76" s="18" t="inlineStr"/>
+      <c r="N76" s="18" t="inlineStr"/>
+      <c r="O76" s="18" t="inlineStr"/>
+      <c r="P76" s="18" t="inlineStr"/>
+      <c r="Q76" s="18" t="inlineStr"/>
+      <c r="R76" s="18" t="inlineStr"/>
+      <c r="S76" s="18" t="inlineStr"/>
+      <c r="T76" s="18" t="inlineStr"/>
+      <c r="U76" s="18" t="inlineStr"/>
+      <c r="V76" s="18" t="inlineStr"/>
+      <c r="W76" s="18" t="inlineStr"/>
+      <c r="X76" s="18" t="inlineStr"/>
+      <c r="Y76" s="18" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="16" t="n">
@@ -3301,6 +4880,25 @@
       <c r="D77" s="18" t="inlineStr"/>
       <c r="E77" s="18" t="inlineStr"/>
       <c r="F77" s="18" t="inlineStr"/>
+      <c r="G77" s="18" t="inlineStr"/>
+      <c r="H77" s="18" t="inlineStr"/>
+      <c r="I77" s="18" t="inlineStr"/>
+      <c r="J77" s="18" t="inlineStr"/>
+      <c r="K77" s="18" t="inlineStr"/>
+      <c r="L77" s="18" t="inlineStr"/>
+      <c r="M77" s="18" t="inlineStr"/>
+      <c r="N77" s="18" t="inlineStr"/>
+      <c r="O77" s="18" t="inlineStr"/>
+      <c r="P77" s="18" t="inlineStr"/>
+      <c r="Q77" s="18" t="inlineStr"/>
+      <c r="R77" s="18" t="inlineStr"/>
+      <c r="S77" s="18" t="inlineStr"/>
+      <c r="T77" s="18" t="inlineStr"/>
+      <c r="U77" s="18" t="inlineStr"/>
+      <c r="V77" s="18" t="inlineStr"/>
+      <c r="W77" s="18" t="inlineStr"/>
+      <c r="X77" s="18" t="inlineStr"/>
+      <c r="Y77" s="18" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="16" t="n">
@@ -3319,6 +4917,29 @@
       <c r="D78" s="18" t="inlineStr"/>
       <c r="E78" s="18" t="inlineStr"/>
       <c r="F78" s="18" t="inlineStr"/>
+      <c r="G78" s="18" t="inlineStr"/>
+      <c r="H78" s="18" t="inlineStr"/>
+      <c r="I78" s="18" t="inlineStr"/>
+      <c r="J78" s="18" t="inlineStr"/>
+      <c r="K78" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 1 abstract cited by the corpus</t>
+        </is>
+      </c>
+      <c r="L78" s="18" t="inlineStr"/>
+      <c r="M78" s="18" t="inlineStr"/>
+      <c r="N78" s="18" t="inlineStr"/>
+      <c r="O78" s="18" t="inlineStr"/>
+      <c r="P78" s="18" t="inlineStr"/>
+      <c r="Q78" s="18" t="inlineStr"/>
+      <c r="R78" s="18" t="inlineStr"/>
+      <c r="S78" s="18" t="inlineStr"/>
+      <c r="T78" s="18" t="inlineStr"/>
+      <c r="U78" s="18" t="inlineStr"/>
+      <c r="V78" s="18" t="inlineStr"/>
+      <c r="W78" s="18" t="inlineStr"/>
+      <c r="X78" s="18" t="inlineStr"/>
+      <c r="Y78" s="18" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="16" t="n">
@@ -3337,6 +4958,33 @@
       <c r="D79" s="18" t="inlineStr"/>
       <c r="E79" s="18" t="inlineStr"/>
       <c r="F79" s="18" t="inlineStr"/>
+      <c r="G79" s="18" t="inlineStr"/>
+      <c r="H79" s="18" t="inlineStr"/>
+      <c r="I79" s="18" t="inlineStr"/>
+      <c r="J79" s="18" t="inlineStr"/>
+      <c r="K79" s="18" t="inlineStr"/>
+      <c r="L79" s="18" t="inlineStr"/>
+      <c r="M79" s="18" t="inlineStr"/>
+      <c r="N79" s="18" t="inlineStr"/>
+      <c r="O79" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 1 abstract cited by the corpus</t>
+        </is>
+      </c>
+      <c r="P79" s="18" t="inlineStr"/>
+      <c r="Q79" s="18" t="inlineStr"/>
+      <c r="R79" s="18" t="inlineStr"/>
+      <c r="S79" s="18" t="inlineStr"/>
+      <c r="T79" s="18" t="inlineStr"/>
+      <c r="U79" s="18" t="inlineStr"/>
+      <c r="V79" s="18" t="inlineStr"/>
+      <c r="W79" s="18" t="inlineStr"/>
+      <c r="X79" s="18" t="inlineStr"/>
+      <c r="Y79" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 1 abstract cited by the corpus</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="16" t="n">
@@ -3355,6 +5003,29 @@
       <c r="D80" s="18" t="inlineStr"/>
       <c r="E80" s="18" t="inlineStr"/>
       <c r="F80" s="18" t="inlineStr"/>
+      <c r="G80" s="18" t="inlineStr"/>
+      <c r="H80" s="18" t="inlineStr"/>
+      <c r="I80" s="18" t="inlineStr"/>
+      <c r="J80" s="18" t="inlineStr"/>
+      <c r="K80" s="18" t="inlineStr"/>
+      <c r="L80" s="18" t="inlineStr"/>
+      <c r="M80" s="18" t="inlineStr"/>
+      <c r="N80" s="18" t="inlineStr"/>
+      <c r="O80" s="18" t="inlineStr"/>
+      <c r="P80" s="18" t="inlineStr"/>
+      <c r="Q80" s="18" t="inlineStr"/>
+      <c r="R80" s="18" t="inlineStr"/>
+      <c r="S80" s="18" t="inlineStr"/>
+      <c r="T80" s="18" t="inlineStr"/>
+      <c r="U80" s="18" t="inlineStr"/>
+      <c r="V80" s="18" t="inlineStr"/>
+      <c r="W80" s="18" t="inlineStr"/>
+      <c r="X80" s="18" t="inlineStr"/>
+      <c r="Y80" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 2 abstracts cited by the corpus</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="16" t="n">
@@ -3373,6 +5044,25 @@
       <c r="D81" s="18" t="inlineStr"/>
       <c r="E81" s="18" t="inlineStr"/>
       <c r="F81" s="18" t="inlineStr"/>
+      <c r="G81" s="18" t="inlineStr"/>
+      <c r="H81" s="18" t="inlineStr"/>
+      <c r="I81" s="18" t="inlineStr"/>
+      <c r="J81" s="18" t="inlineStr"/>
+      <c r="K81" s="18" t="inlineStr"/>
+      <c r="L81" s="18" t="inlineStr"/>
+      <c r="M81" s="18" t="inlineStr"/>
+      <c r="N81" s="18" t="inlineStr"/>
+      <c r="O81" s="18" t="inlineStr"/>
+      <c r="P81" s="18" t="inlineStr"/>
+      <c r="Q81" s="18" t="inlineStr"/>
+      <c r="R81" s="18" t="inlineStr"/>
+      <c r="S81" s="18" t="inlineStr"/>
+      <c r="T81" s="18" t="inlineStr"/>
+      <c r="U81" s="18" t="inlineStr"/>
+      <c r="V81" s="18" t="inlineStr"/>
+      <c r="W81" s="18" t="inlineStr"/>
+      <c r="X81" s="18" t="inlineStr"/>
+      <c r="Y81" s="18" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="16" t="n">
@@ -3391,6 +5081,25 @@
       <c r="D82" s="18" t="inlineStr"/>
       <c r="E82" s="18" t="inlineStr"/>
       <c r="F82" s="18" t="inlineStr"/>
+      <c r="G82" s="18" t="inlineStr"/>
+      <c r="H82" s="18" t="inlineStr"/>
+      <c r="I82" s="18" t="inlineStr"/>
+      <c r="J82" s="18" t="inlineStr"/>
+      <c r="K82" s="18" t="inlineStr"/>
+      <c r="L82" s="18" t="inlineStr"/>
+      <c r="M82" s="18" t="inlineStr"/>
+      <c r="N82" s="18" t="inlineStr"/>
+      <c r="O82" s="18" t="inlineStr"/>
+      <c r="P82" s="18" t="inlineStr"/>
+      <c r="Q82" s="18" t="inlineStr"/>
+      <c r="R82" s="18" t="inlineStr"/>
+      <c r="S82" s="18" t="inlineStr"/>
+      <c r="T82" s="18" t="inlineStr"/>
+      <c r="U82" s="18" t="inlineStr"/>
+      <c r="V82" s="18" t="inlineStr"/>
+      <c r="W82" s="18" t="inlineStr"/>
+      <c r="X82" s="18" t="inlineStr"/>
+      <c r="Y82" s="18" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="16" t="n">
@@ -3413,6 +5122,37 @@
       </c>
       <c r="E83" s="18" t="inlineStr"/>
       <c r="F83" s="18" t="inlineStr"/>
+      <c r="G83" s="18" t="inlineStr"/>
+      <c r="H83" s="18" t="inlineStr"/>
+      <c r="I83" s="18" t="inlineStr"/>
+      <c r="J83" s="18" t="inlineStr"/>
+      <c r="K83" s="18" t="inlineStr"/>
+      <c r="L83" s="18" t="inlineStr"/>
+      <c r="M83" s="18" t="inlineStr"/>
+      <c r="N83" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 1 abstract cited by the corpus</t>
+        </is>
+      </c>
+      <c r="O83" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 11 abstracts cited by the corpus</t>
+        </is>
+      </c>
+      <c r="P83" s="18" t="inlineStr"/>
+      <c r="Q83" s="18" t="inlineStr"/>
+      <c r="R83" s="18" t="inlineStr"/>
+      <c r="S83" s="18" t="inlineStr"/>
+      <c r="T83" s="18" t="inlineStr"/>
+      <c r="U83" s="18" t="inlineStr"/>
+      <c r="V83" s="18" t="inlineStr"/>
+      <c r="W83" s="18" t="inlineStr"/>
+      <c r="X83" s="18" t="inlineStr"/>
+      <c r="Y83" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 1 abstract cited by the corpus</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="16" t="n">
@@ -3435,6 +5175,25 @@
       </c>
       <c r="E84" s="18" t="inlineStr"/>
       <c r="F84" s="18" t="inlineStr"/>
+      <c r="G84" s="18" t="inlineStr"/>
+      <c r="H84" s="18" t="inlineStr"/>
+      <c r="I84" s="18" t="inlineStr"/>
+      <c r="J84" s="18" t="inlineStr"/>
+      <c r="K84" s="18" t="inlineStr"/>
+      <c r="L84" s="18" t="inlineStr"/>
+      <c r="M84" s="18" t="inlineStr"/>
+      <c r="N84" s="18" t="inlineStr"/>
+      <c r="O84" s="18" t="inlineStr"/>
+      <c r="P84" s="18" t="inlineStr"/>
+      <c r="Q84" s="18" t="inlineStr"/>
+      <c r="R84" s="18" t="inlineStr"/>
+      <c r="S84" s="18" t="inlineStr"/>
+      <c r="T84" s="18" t="inlineStr"/>
+      <c r="U84" s="18" t="inlineStr"/>
+      <c r="V84" s="18" t="inlineStr"/>
+      <c r="W84" s="18" t="inlineStr"/>
+      <c r="X84" s="18" t="inlineStr"/>
+      <c r="Y84" s="18" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="16" t="n">
@@ -3457,6 +5216,25 @@
       </c>
       <c r="E85" s="18" t="inlineStr"/>
       <c r="F85" s="18" t="inlineStr"/>
+      <c r="G85" s="18" t="inlineStr"/>
+      <c r="H85" s="18" t="inlineStr"/>
+      <c r="I85" s="18" t="inlineStr"/>
+      <c r="J85" s="18" t="inlineStr"/>
+      <c r="K85" s="18" t="inlineStr"/>
+      <c r="L85" s="18" t="inlineStr"/>
+      <c r="M85" s="18" t="inlineStr"/>
+      <c r="N85" s="18" t="inlineStr"/>
+      <c r="O85" s="18" t="inlineStr"/>
+      <c r="P85" s="18" t="inlineStr"/>
+      <c r="Q85" s="18" t="inlineStr"/>
+      <c r="R85" s="18" t="inlineStr"/>
+      <c r="S85" s="18" t="inlineStr"/>
+      <c r="T85" s="18" t="inlineStr"/>
+      <c r="U85" s="18" t="inlineStr"/>
+      <c r="V85" s="18" t="inlineStr"/>
+      <c r="W85" s="18" t="inlineStr"/>
+      <c r="X85" s="18" t="inlineStr"/>
+      <c r="Y85" s="18" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="16" t="n">
@@ -3479,6 +5257,29 @@
       </c>
       <c r="E86" s="18" t="inlineStr"/>
       <c r="F86" s="18" t="inlineStr"/>
+      <c r="G86" s="18" t="inlineStr"/>
+      <c r="H86" s="18" t="inlineStr"/>
+      <c r="I86" s="18" t="inlineStr"/>
+      <c r="J86" s="18" t="inlineStr"/>
+      <c r="K86" s="18" t="inlineStr"/>
+      <c r="L86" s="18" t="inlineStr"/>
+      <c r="M86" s="18" t="inlineStr"/>
+      <c r="N86" s="18" t="inlineStr"/>
+      <c r="O86" s="18" t="inlineStr"/>
+      <c r="P86" s="18" t="inlineStr"/>
+      <c r="Q86" s="18" t="inlineStr"/>
+      <c r="R86" s="18" t="inlineStr"/>
+      <c r="S86" s="18" t="inlineStr"/>
+      <c r="T86" s="18" t="inlineStr"/>
+      <c r="U86" s="18" t="inlineStr"/>
+      <c r="V86" s="18" t="inlineStr"/>
+      <c r="W86" s="18" t="inlineStr"/>
+      <c r="X86" s="18" t="inlineStr"/>
+      <c r="Y86" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 3 abstracts cited by the corpus</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="16" t="n">
@@ -3501,6 +5302,29 @@
       </c>
       <c r="E87" s="18" t="inlineStr"/>
       <c r="F87" s="18" t="inlineStr"/>
+      <c r="G87" s="18" t="inlineStr"/>
+      <c r="H87" s="18" t="inlineStr"/>
+      <c r="I87" s="18" t="inlineStr"/>
+      <c r="J87" s="18" t="inlineStr"/>
+      <c r="K87" s="18" t="inlineStr"/>
+      <c r="L87" s="18" t="inlineStr"/>
+      <c r="M87" s="18" t="inlineStr"/>
+      <c r="N87" s="18" t="inlineStr"/>
+      <c r="O87" s="18" t="inlineStr"/>
+      <c r="P87" s="18" t="inlineStr"/>
+      <c r="Q87" s="18" t="inlineStr"/>
+      <c r="R87" s="18" t="inlineStr"/>
+      <c r="S87" s="18" t="inlineStr"/>
+      <c r="T87" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 1 abstract cited by the corpus</t>
+        </is>
+      </c>
+      <c r="U87" s="18" t="inlineStr"/>
+      <c r="V87" s="18" t="inlineStr"/>
+      <c r="W87" s="18" t="inlineStr"/>
+      <c r="X87" s="18" t="inlineStr"/>
+      <c r="Y87" s="18" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="16" t="n">
@@ -3523,6 +5347,33 @@
       </c>
       <c r="E88" s="18" t="inlineStr"/>
       <c r="F88" s="18" t="inlineStr"/>
+      <c r="G88" s="18" t="inlineStr"/>
+      <c r="H88" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 1 abstract cited by the corpus</t>
+        </is>
+      </c>
+      <c r="I88" s="18" t="inlineStr"/>
+      <c r="J88" s="18" t="inlineStr"/>
+      <c r="K88" s="18" t="inlineStr"/>
+      <c r="L88" s="18" t="inlineStr"/>
+      <c r="M88" s="18" t="inlineStr"/>
+      <c r="N88" s="18" t="inlineStr"/>
+      <c r="O88" s="18" t="inlineStr"/>
+      <c r="P88" s="18" t="inlineStr"/>
+      <c r="Q88" s="18" t="inlineStr"/>
+      <c r="R88" s="18" t="inlineStr"/>
+      <c r="S88" s="18" t="inlineStr"/>
+      <c r="T88" s="18" t="inlineStr"/>
+      <c r="U88" s="18" t="inlineStr"/>
+      <c r="V88" s="18" t="inlineStr"/>
+      <c r="W88" s="18" t="inlineStr"/>
+      <c r="X88" s="18" t="inlineStr"/>
+      <c r="Y88" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 7 abstracts cited by the corpus</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="16" t="n">
@@ -3545,6 +5396,29 @@
       </c>
       <c r="E89" s="18" t="inlineStr"/>
       <c r="F89" s="18" t="inlineStr"/>
+      <c r="G89" s="18" t="inlineStr"/>
+      <c r="H89" s="18" t="inlineStr"/>
+      <c r="I89" s="18" t="inlineStr"/>
+      <c r="J89" s="18" t="inlineStr"/>
+      <c r="K89" s="18" t="inlineStr"/>
+      <c r="L89" s="18" t="inlineStr"/>
+      <c r="M89" s="18" t="inlineStr"/>
+      <c r="N89" s="18" t="inlineStr"/>
+      <c r="O89" s="18" t="inlineStr"/>
+      <c r="P89" s="18" t="inlineStr"/>
+      <c r="Q89" s="18" t="inlineStr"/>
+      <c r="R89" s="18" t="inlineStr"/>
+      <c r="S89" s="18" t="inlineStr"/>
+      <c r="T89" s="18" t="inlineStr"/>
+      <c r="U89" s="18" t="inlineStr"/>
+      <c r="V89" s="18" t="inlineStr"/>
+      <c r="W89" s="18" t="inlineStr"/>
+      <c r="X89" s="18" t="inlineStr"/>
+      <c r="Y89" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 4 abstracts cited by the corpus</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="16" t="n">
@@ -3567,6 +5441,41 @@
       </c>
       <c r="E90" s="18" t="inlineStr"/>
       <c r="F90" s="18" t="inlineStr"/>
+      <c r="G90" s="18" t="inlineStr"/>
+      <c r="H90" s="18" t="inlineStr"/>
+      <c r="I90" s="22" t="inlineStr">
+        <is>
+          <t>Digital — 1 PDF held — extraction pending</t>
+        </is>
+      </c>
+      <c r="J90" s="18" t="inlineStr"/>
+      <c r="K90" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 7 abstracts cited by the corpus</t>
+        </is>
+      </c>
+      <c r="L90" s="18" t="inlineStr"/>
+      <c r="M90" s="18" t="inlineStr"/>
+      <c r="N90" s="18" t="inlineStr"/>
+      <c r="O90" s="18" t="inlineStr"/>
+      <c r="P90" s="18" t="inlineStr"/>
+      <c r="Q90" s="18" t="inlineStr"/>
+      <c r="R90" s="18" t="inlineStr"/>
+      <c r="S90" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 4 abstracts cited by the corpus</t>
+        </is>
+      </c>
+      <c r="T90" s="18" t="inlineStr"/>
+      <c r="U90" s="18" t="inlineStr"/>
+      <c r="V90" s="18" t="inlineStr"/>
+      <c r="W90" s="18" t="inlineStr"/>
+      <c r="X90" s="18" t="inlineStr"/>
+      <c r="Y90" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 2 abstracts cited by the corpus</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="16" t="n">
@@ -3589,6 +5498,37 @@
       </c>
       <c r="E91" s="18" t="inlineStr"/>
       <c r="F91" s="18" t="inlineStr"/>
+      <c r="G91" s="18" t="inlineStr"/>
+      <c r="H91" s="18" t="inlineStr"/>
+      <c r="I91" s="18" t="inlineStr"/>
+      <c r="J91" s="18" t="inlineStr"/>
+      <c r="K91" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 1 abstract cited by the corpus</t>
+        </is>
+      </c>
+      <c r="L91" s="18" t="inlineStr"/>
+      <c r="M91" s="18" t="inlineStr"/>
+      <c r="N91" s="18" t="inlineStr"/>
+      <c r="O91" s="18" t="inlineStr"/>
+      <c r="P91" s="18" t="inlineStr"/>
+      <c r="Q91" s="18" t="inlineStr"/>
+      <c r="R91" s="18" t="inlineStr"/>
+      <c r="S91" s="18" t="inlineStr"/>
+      <c r="T91" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 2 abstracts cited by the corpus</t>
+        </is>
+      </c>
+      <c r="U91" s="18" t="inlineStr"/>
+      <c r="V91" s="18" t="inlineStr"/>
+      <c r="W91" s="18" t="inlineStr"/>
+      <c r="X91" s="18" t="inlineStr"/>
+      <c r="Y91" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 2 abstracts cited by the corpus</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="16" t="n">
@@ -3611,6 +5551,33 @@
       </c>
       <c r="E92" s="18" t="inlineStr"/>
       <c r="F92" s="18" t="inlineStr"/>
+      <c r="G92" s="18" t="inlineStr"/>
+      <c r="H92" s="18" t="inlineStr"/>
+      <c r="I92" s="18" t="inlineStr"/>
+      <c r="J92" s="18" t="inlineStr"/>
+      <c r="K92" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 12 abstracts cited by the corpus</t>
+        </is>
+      </c>
+      <c r="L92" s="18" t="inlineStr"/>
+      <c r="M92" s="18" t="inlineStr"/>
+      <c r="N92" s="18" t="inlineStr"/>
+      <c r="O92" s="18" t="inlineStr"/>
+      <c r="P92" s="18" t="inlineStr"/>
+      <c r="Q92" s="18" t="inlineStr"/>
+      <c r="R92" s="18" t="inlineStr"/>
+      <c r="S92" s="18" t="inlineStr"/>
+      <c r="T92" s="18" t="inlineStr"/>
+      <c r="U92" s="18" t="inlineStr"/>
+      <c r="V92" s="18" t="inlineStr"/>
+      <c r="W92" s="18" t="inlineStr"/>
+      <c r="X92" s="18" t="inlineStr"/>
+      <c r="Y92" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 5 abstracts cited by the corpus</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="16" t="n">
@@ -3633,6 +5600,37 @@
       </c>
       <c r="E93" s="18" t="inlineStr"/>
       <c r="F93" s="18" t="inlineStr"/>
+      <c r="G93" s="18" t="inlineStr"/>
+      <c r="H93" s="18" t="inlineStr"/>
+      <c r="I93" s="18" t="inlineStr"/>
+      <c r="J93" s="18" t="inlineStr"/>
+      <c r="K93" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 1 abstract cited by the corpus</t>
+        </is>
+      </c>
+      <c r="L93" s="18" t="inlineStr"/>
+      <c r="M93" s="18" t="inlineStr"/>
+      <c r="N93" s="18" t="inlineStr"/>
+      <c r="O93" s="18" t="inlineStr"/>
+      <c r="P93" s="18" t="inlineStr"/>
+      <c r="Q93" s="18" t="inlineStr"/>
+      <c r="R93" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 6 abstracts cited by the corpus</t>
+        </is>
+      </c>
+      <c r="S93" s="18" t="inlineStr"/>
+      <c r="T93" s="18" t="inlineStr"/>
+      <c r="U93" s="18" t="inlineStr"/>
+      <c r="V93" s="18" t="inlineStr"/>
+      <c r="W93" s="18" t="inlineStr"/>
+      <c r="X93" s="18" t="inlineStr"/>
+      <c r="Y93" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 3 abstracts cited by the corpus</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="16" t="n">
@@ -3655,6 +5653,33 @@
       </c>
       <c r="E94" s="18" t="inlineStr"/>
       <c r="F94" s="18" t="inlineStr"/>
+      <c r="G94" s="18" t="inlineStr"/>
+      <c r="H94" s="18" t="inlineStr"/>
+      <c r="I94" s="22" t="inlineStr">
+        <is>
+          <t>Digital — 1 PDF held — extraction pending</t>
+        </is>
+      </c>
+      <c r="J94" s="18" t="inlineStr"/>
+      <c r="K94" s="18" t="inlineStr"/>
+      <c r="L94" s="18" t="inlineStr"/>
+      <c r="M94" s="18" t="inlineStr"/>
+      <c r="N94" s="18" t="inlineStr"/>
+      <c r="O94" s="18" t="inlineStr"/>
+      <c r="P94" s="18" t="inlineStr"/>
+      <c r="Q94" s="18" t="inlineStr"/>
+      <c r="R94" s="18" t="inlineStr"/>
+      <c r="S94" s="18" t="inlineStr"/>
+      <c r="T94" s="18" t="inlineStr"/>
+      <c r="U94" s="18" t="inlineStr"/>
+      <c r="V94" s="18" t="inlineStr"/>
+      <c r="W94" s="18" t="inlineStr"/>
+      <c r="X94" s="18" t="inlineStr"/>
+      <c r="Y94" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 6 abstracts cited by the corpus</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="16" t="n">
@@ -3677,6 +5702,33 @@
       </c>
       <c r="E95" s="18" t="inlineStr"/>
       <c r="F95" s="18" t="inlineStr"/>
+      <c r="G95" s="18" t="inlineStr"/>
+      <c r="H95" s="18" t="inlineStr"/>
+      <c r="I95" s="18" t="inlineStr"/>
+      <c r="J95" s="18" t="inlineStr"/>
+      <c r="K95" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 3 abstracts cited by the corpus</t>
+        </is>
+      </c>
+      <c r="L95" s="18" t="inlineStr"/>
+      <c r="M95" s="18" t="inlineStr"/>
+      <c r="N95" s="18" t="inlineStr"/>
+      <c r="O95" s="18" t="inlineStr"/>
+      <c r="P95" s="18" t="inlineStr"/>
+      <c r="Q95" s="18" t="inlineStr"/>
+      <c r="R95" s="18" t="inlineStr"/>
+      <c r="S95" s="18" t="inlineStr"/>
+      <c r="T95" s="18" t="inlineStr"/>
+      <c r="U95" s="18" t="inlineStr"/>
+      <c r="V95" s="18" t="inlineStr"/>
+      <c r="W95" s="18" t="inlineStr"/>
+      <c r="X95" s="18" t="inlineStr"/>
+      <c r="Y95" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 3 abstracts cited by the corpus</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="16" t="n">
@@ -3703,6 +5755,45 @@
           <t>Cairns; Missing — find source</t>
         </is>
       </c>
+      <c r="G96" s="18" t="inlineStr"/>
+      <c r="H96" s="18" t="inlineStr"/>
+      <c r="I96" s="22" t="inlineStr">
+        <is>
+          <t>Digital — 1 PDF held — extraction pending</t>
+        </is>
+      </c>
+      <c r="J96" s="18" t="inlineStr"/>
+      <c r="K96" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 2 abstracts cited by the corpus</t>
+        </is>
+      </c>
+      <c r="L96" s="18" t="inlineStr"/>
+      <c r="M96" s="18" t="inlineStr"/>
+      <c r="N96" s="18" t="inlineStr"/>
+      <c r="O96" s="18" t="inlineStr"/>
+      <c r="P96" s="18" t="inlineStr"/>
+      <c r="Q96" s="18" t="inlineStr"/>
+      <c r="R96" s="18" t="inlineStr"/>
+      <c r="S96" s="18" t="inlineStr"/>
+      <c r="T96" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 2 abstracts cited by the corpus</t>
+        </is>
+      </c>
+      <c r="U96" s="18" t="inlineStr"/>
+      <c r="V96" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 1 abstract cited by the corpus</t>
+        </is>
+      </c>
+      <c r="W96" s="18" t="inlineStr"/>
+      <c r="X96" s="18" t="inlineStr"/>
+      <c r="Y96" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 3 abstracts cited by the corpus</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="16" t="n">
@@ -3725,6 +5816,41 @@
       </c>
       <c r="E97" s="18" t="inlineStr"/>
       <c r="F97" s="18" t="inlineStr"/>
+      <c r="G97" s="18" t="inlineStr"/>
+      <c r="H97" s="18" t="inlineStr"/>
+      <c r="I97" s="18" t="inlineStr"/>
+      <c r="J97" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 48 abstracts cited by the corpus</t>
+        </is>
+      </c>
+      <c r="K97" s="18" t="inlineStr"/>
+      <c r="L97" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 12 abstracts cited by the corpus</t>
+        </is>
+      </c>
+      <c r="M97" s="18" t="inlineStr"/>
+      <c r="N97" s="18" t="inlineStr"/>
+      <c r="O97" s="18" t="inlineStr"/>
+      <c r="P97" s="18" t="inlineStr"/>
+      <c r="Q97" s="18" t="inlineStr"/>
+      <c r="R97" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 1 abstract cited by the corpus</t>
+        </is>
+      </c>
+      <c r="S97" s="18" t="inlineStr"/>
+      <c r="T97" s="18" t="inlineStr"/>
+      <c r="U97" s="18" t="inlineStr"/>
+      <c r="V97" s="18" t="inlineStr"/>
+      <c r="W97" s="18" t="inlineStr"/>
+      <c r="X97" s="18" t="inlineStr"/>
+      <c r="Y97" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 9 abstracts cited by the corpus</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="16" t="n">
@@ -3751,6 +5877,49 @@
         </is>
       </c>
       <c r="F98" s="18" t="inlineStr"/>
+      <c r="G98" s="18" t="inlineStr"/>
+      <c r="H98" s="18" t="inlineStr"/>
+      <c r="I98" s="18" t="inlineStr"/>
+      <c r="J98" s="18" t="inlineStr"/>
+      <c r="K98" s="18" t="inlineStr"/>
+      <c r="L98" s="18" t="inlineStr"/>
+      <c r="M98" s="18" t="inlineStr"/>
+      <c r="N98" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 100 abstracts cited by the corpus</t>
+        </is>
+      </c>
+      <c r="O98" s="18" t="inlineStr"/>
+      <c r="P98" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 13 abstracts cited by the corpus</t>
+        </is>
+      </c>
+      <c r="Q98" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 6 abstracts cited by the corpus</t>
+        </is>
+      </c>
+      <c r="R98" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 2 abstracts cited by the corpus</t>
+        </is>
+      </c>
+      <c r="S98" s="18" t="inlineStr"/>
+      <c r="T98" s="18" t="inlineStr"/>
+      <c r="U98" s="18" t="inlineStr"/>
+      <c r="V98" s="18" t="inlineStr"/>
+      <c r="W98" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 3 abstracts cited by the corpus</t>
+        </is>
+      </c>
+      <c r="X98" s="18" t="inlineStr"/>
+      <c r="Y98" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 1 abstract cited by the corpus</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="16" t="n">
@@ -3773,6 +5942,37 @@
       </c>
       <c r="E99" s="18" t="inlineStr"/>
       <c r="F99" s="18" t="inlineStr"/>
+      <c r="G99" s="18" t="inlineStr"/>
+      <c r="H99" s="18" t="inlineStr"/>
+      <c r="I99" s="18" t="inlineStr"/>
+      <c r="J99" s="18" t="inlineStr"/>
+      <c r="K99" s="18" t="inlineStr"/>
+      <c r="L99" s="18" t="inlineStr"/>
+      <c r="M99" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 2 abstracts cited by the corpus</t>
+        </is>
+      </c>
+      <c r="N99" s="18" t="inlineStr"/>
+      <c r="O99" s="18" t="inlineStr"/>
+      <c r="P99" s="18" t="inlineStr"/>
+      <c r="Q99" s="18" t="inlineStr"/>
+      <c r="R99" s="18" t="inlineStr"/>
+      <c r="S99" s="18" t="inlineStr"/>
+      <c r="T99" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 11 abstracts cited by the corpus</t>
+        </is>
+      </c>
+      <c r="U99" s="18" t="inlineStr"/>
+      <c r="V99" s="18" t="inlineStr"/>
+      <c r="W99" s="18" t="inlineStr"/>
+      <c r="X99" s="18" t="inlineStr"/>
+      <c r="Y99" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 2 abstracts cited by the corpus</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="16" t="n">
@@ -3803,6 +6003,41 @@
           <t>Durban; Missing — find source</t>
         </is>
       </c>
+      <c r="G100" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 79 abstracts cited by the corpus</t>
+        </is>
+      </c>
+      <c r="H100" s="18" t="inlineStr"/>
+      <c r="I100" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 44 abstracts cited by the corpus</t>
+        </is>
+      </c>
+      <c r="J100" s="18" t="inlineStr"/>
+      <c r="K100" s="18" t="inlineStr"/>
+      <c r="L100" s="18" t="inlineStr"/>
+      <c r="M100" s="18" t="inlineStr"/>
+      <c r="N100" s="18" t="inlineStr"/>
+      <c r="O100" s="18" t="inlineStr"/>
+      <c r="P100" s="18" t="inlineStr"/>
+      <c r="Q100" s="18" t="inlineStr"/>
+      <c r="R100" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 1 abstract cited by the corpus</t>
+        </is>
+      </c>
+      <c r="S100" s="18" t="inlineStr"/>
+      <c r="T100" s="18" t="inlineStr"/>
+      <c r="U100" s="18" t="inlineStr"/>
+      <c r="V100" s="18" t="inlineStr"/>
+      <c r="W100" s="18" t="inlineStr"/>
+      <c r="X100" s="18" t="inlineStr"/>
+      <c r="Y100" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 1 abstract cited by the corpus</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="16" t="n">
@@ -3825,6 +6060,29 @@
       </c>
       <c r="E101" s="18" t="inlineStr"/>
       <c r="F101" s="18" t="inlineStr"/>
+      <c r="G101" s="18" t="inlineStr"/>
+      <c r="H101" s="18" t="inlineStr"/>
+      <c r="I101" s="18" t="inlineStr"/>
+      <c r="J101" s="18" t="inlineStr"/>
+      <c r="K101" s="18" t="inlineStr"/>
+      <c r="L101" s="18" t="inlineStr"/>
+      <c r="M101" s="18" t="inlineStr"/>
+      <c r="N101" s="18" t="inlineStr"/>
+      <c r="O101" s="18" t="inlineStr"/>
+      <c r="P101" s="18" t="inlineStr"/>
+      <c r="Q101" s="18" t="inlineStr"/>
+      <c r="R101" s="18" t="inlineStr"/>
+      <c r="S101" s="18" t="inlineStr"/>
+      <c r="T101" s="18" t="inlineStr"/>
+      <c r="U101" s="18" t="inlineStr"/>
+      <c r="V101" s="18" t="inlineStr"/>
+      <c r="W101" s="18" t="inlineStr"/>
+      <c r="X101" s="18" t="inlineStr"/>
+      <c r="Y101" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 4 abstracts cited by the corpus</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="16" t="n">
@@ -3851,6 +6109,33 @@
         </is>
       </c>
       <c r="F102" s="18" t="inlineStr"/>
+      <c r="G102" s="18" t="inlineStr"/>
+      <c r="H102" s="18" t="inlineStr"/>
+      <c r="I102" s="22" t="inlineStr">
+        <is>
+          <t>Digital — 1 PDF held — extraction pending</t>
+        </is>
+      </c>
+      <c r="J102" s="18" t="inlineStr"/>
+      <c r="K102" s="18" t="inlineStr"/>
+      <c r="L102" s="18" t="inlineStr"/>
+      <c r="M102" s="18" t="inlineStr"/>
+      <c r="N102" s="18" t="inlineStr"/>
+      <c r="O102" s="18" t="inlineStr"/>
+      <c r="P102" s="18" t="inlineStr"/>
+      <c r="Q102" s="18" t="inlineStr"/>
+      <c r="R102" s="18" t="inlineStr"/>
+      <c r="S102" s="18" t="inlineStr"/>
+      <c r="T102" s="18" t="inlineStr"/>
+      <c r="U102" s="18" t="inlineStr"/>
+      <c r="V102" s="18" t="inlineStr"/>
+      <c r="W102" s="18" t="inlineStr"/>
+      <c r="X102" s="18" t="inlineStr"/>
+      <c r="Y102" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 3 abstracts cited by the corpus</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="16" t="n">
@@ -3873,6 +6158,29 @@
       </c>
       <c r="E103" s="18" t="inlineStr"/>
       <c r="F103" s="18" t="inlineStr"/>
+      <c r="G103" s="18" t="inlineStr"/>
+      <c r="H103" s="18" t="inlineStr"/>
+      <c r="I103" s="18" t="inlineStr"/>
+      <c r="J103" s="18" t="inlineStr"/>
+      <c r="K103" s="18" t="inlineStr"/>
+      <c r="L103" s="18" t="inlineStr"/>
+      <c r="M103" s="18" t="inlineStr"/>
+      <c r="N103" s="18" t="inlineStr"/>
+      <c r="O103" s="18" t="inlineStr"/>
+      <c r="P103" s="18" t="inlineStr"/>
+      <c r="Q103" s="18" t="inlineStr"/>
+      <c r="R103" s="18" t="inlineStr"/>
+      <c r="S103" s="18" t="inlineStr"/>
+      <c r="T103" s="18" t="inlineStr"/>
+      <c r="U103" s="18" t="inlineStr"/>
+      <c r="V103" s="18" t="inlineStr"/>
+      <c r="W103" s="18" t="inlineStr"/>
+      <c r="X103" s="18" t="inlineStr"/>
+      <c r="Y103" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 1 abstract cited by the corpus</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="16" t="n">
@@ -3903,6 +6211,29 @@
           <t>Joao Pessoa; Ingested</t>
         </is>
       </c>
+      <c r="G104" s="18" t="inlineStr"/>
+      <c r="H104" s="18" t="inlineStr"/>
+      <c r="I104" s="18" t="inlineStr"/>
+      <c r="J104" s="18" t="inlineStr"/>
+      <c r="K104" s="18" t="inlineStr"/>
+      <c r="L104" s="18" t="inlineStr"/>
+      <c r="M104" s="18" t="inlineStr"/>
+      <c r="N104" s="18" t="inlineStr"/>
+      <c r="O104" s="18" t="inlineStr"/>
+      <c r="P104" s="18" t="inlineStr"/>
+      <c r="Q104" s="18" t="inlineStr"/>
+      <c r="R104" s="18" t="inlineStr"/>
+      <c r="S104" s="18" t="inlineStr"/>
+      <c r="T104" s="18" t="inlineStr"/>
+      <c r="U104" s="18" t="inlineStr"/>
+      <c r="V104" s="18" t="inlineStr"/>
+      <c r="W104" s="18" t="inlineStr"/>
+      <c r="X104" s="18" t="inlineStr"/>
+      <c r="Y104" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 3 abstracts cited by the corpus</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="16" t="n">
@@ -3925,6 +6256,29 @@
       </c>
       <c r="E105" s="18" t="inlineStr"/>
       <c r="F105" s="18" t="inlineStr"/>
+      <c r="G105" s="18" t="inlineStr"/>
+      <c r="H105" s="18" t="inlineStr"/>
+      <c r="I105" s="18" t="inlineStr"/>
+      <c r="J105" s="18" t="inlineStr"/>
+      <c r="K105" s="18" t="inlineStr"/>
+      <c r="L105" s="18" t="inlineStr"/>
+      <c r="M105" s="18" t="inlineStr"/>
+      <c r="N105" s="18" t="inlineStr"/>
+      <c r="O105" s="18" t="inlineStr"/>
+      <c r="P105" s="18" t="inlineStr"/>
+      <c r="Q105" s="18" t="inlineStr"/>
+      <c r="R105" s="18" t="inlineStr"/>
+      <c r="S105" s="18" t="inlineStr"/>
+      <c r="T105" s="18" t="inlineStr"/>
+      <c r="U105" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 1 abstract cited by the corpus</t>
+        </is>
+      </c>
+      <c r="V105" s="18" t="inlineStr"/>
+      <c r="W105" s="18" t="inlineStr"/>
+      <c r="X105" s="18" t="inlineStr"/>
+      <c r="Y105" s="18" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="16" t="n">
@@ -3951,6 +6305,29 @@
         </is>
       </c>
       <c r="F106" s="18" t="inlineStr"/>
+      <c r="G106" s="18" t="inlineStr"/>
+      <c r="H106" s="18" t="inlineStr"/>
+      <c r="I106" s="18" t="inlineStr"/>
+      <c r="J106" s="18" t="inlineStr"/>
+      <c r="K106" s="18" t="inlineStr"/>
+      <c r="L106" s="18" t="inlineStr"/>
+      <c r="M106" s="18" t="inlineStr"/>
+      <c r="N106" s="18" t="inlineStr"/>
+      <c r="O106" s="18" t="inlineStr"/>
+      <c r="P106" s="18" t="inlineStr"/>
+      <c r="Q106" s="18" t="inlineStr"/>
+      <c r="R106" s="18" t="inlineStr"/>
+      <c r="S106" s="18" t="inlineStr"/>
+      <c r="T106" s="18" t="inlineStr"/>
+      <c r="U106" s="18" t="inlineStr"/>
+      <c r="V106" s="18" t="inlineStr"/>
+      <c r="W106" s="18" t="inlineStr"/>
+      <c r="X106" s="18" t="inlineStr"/>
+      <c r="Y106" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 1 abstract cited by the corpus</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="16" t="n">
@@ -3973,6 +6350,33 @@
       </c>
       <c r="E107" s="18" t="inlineStr"/>
       <c r="F107" s="18" t="inlineStr"/>
+      <c r="G107" s="18" t="inlineStr"/>
+      <c r="H107" s="18" t="inlineStr"/>
+      <c r="I107" s="22" t="inlineStr">
+        <is>
+          <t>Digital — 1 PDF held — extraction pending</t>
+        </is>
+      </c>
+      <c r="J107" s="18" t="inlineStr"/>
+      <c r="K107" s="18" t="inlineStr"/>
+      <c r="L107" s="18" t="inlineStr"/>
+      <c r="M107" s="18" t="inlineStr"/>
+      <c r="N107" s="18" t="inlineStr"/>
+      <c r="O107" s="18" t="inlineStr"/>
+      <c r="P107" s="18" t="inlineStr"/>
+      <c r="Q107" s="18" t="inlineStr"/>
+      <c r="R107" s="18" t="inlineStr"/>
+      <c r="S107" s="18" t="inlineStr"/>
+      <c r="T107" s="18" t="inlineStr"/>
+      <c r="U107" s="18" t="inlineStr"/>
+      <c r="V107" s="18" t="inlineStr"/>
+      <c r="W107" s="18" t="inlineStr"/>
+      <c r="X107" s="18" t="inlineStr"/>
+      <c r="Y107" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 2 abstracts cited by the corpus</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="16" t="n">
@@ -4003,6 +6407,29 @@
           <t>Valencia; Digital — full abstract book received 2026-08-27; queued (schedule already ingested)</t>
         </is>
       </c>
+      <c r="G108" s="18" t="inlineStr"/>
+      <c r="H108" s="18" t="inlineStr"/>
+      <c r="I108" s="18" t="inlineStr"/>
+      <c r="J108" s="18" t="inlineStr"/>
+      <c r="K108" s="18" t="inlineStr"/>
+      <c r="L108" s="18" t="inlineStr"/>
+      <c r="M108" s="18" t="inlineStr"/>
+      <c r="N108" s="18" t="inlineStr"/>
+      <c r="O108" s="18" t="inlineStr"/>
+      <c r="P108" s="18" t="inlineStr"/>
+      <c r="Q108" s="18" t="inlineStr"/>
+      <c r="R108" s="18" t="inlineStr"/>
+      <c r="S108" s="18" t="inlineStr"/>
+      <c r="T108" s="18" t="inlineStr"/>
+      <c r="U108" s="18" t="inlineStr"/>
+      <c r="V108" s="18" t="inlineStr"/>
+      <c r="W108" s="18" t="inlineStr"/>
+      <c r="X108" s="18" t="inlineStr"/>
+      <c r="Y108" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 2 abstracts cited by the corpus</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="16" t="n">
@@ -4025,6 +6452,33 @@
       </c>
       <c r="E109" s="18" t="inlineStr"/>
       <c r="F109" s="18" t="inlineStr"/>
+      <c r="G109" s="18" t="inlineStr"/>
+      <c r="H109" s="18" t="inlineStr"/>
+      <c r="I109" s="18" t="inlineStr"/>
+      <c r="J109" s="18" t="inlineStr"/>
+      <c r="K109" s="18" t="inlineStr"/>
+      <c r="L109" s="18" t="inlineStr"/>
+      <c r="M109" s="18" t="inlineStr"/>
+      <c r="N109" s="18" t="inlineStr"/>
+      <c r="O109" s="18" t="inlineStr"/>
+      <c r="P109" s="18" t="inlineStr"/>
+      <c r="Q109" s="18" t="inlineStr"/>
+      <c r="R109" s="18" t="inlineStr"/>
+      <c r="S109" s="18" t="inlineStr"/>
+      <c r="T109" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 1 abstract cited by the corpus</t>
+        </is>
+      </c>
+      <c r="U109" s="18" t="inlineStr"/>
+      <c r="V109" s="18" t="inlineStr"/>
+      <c r="W109" s="18" t="inlineStr"/>
+      <c r="X109" s="18" t="inlineStr"/>
+      <c r="Y109" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 1 abstract cited by the corpus</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="16" t="n">
@@ -4051,6 +6505,25 @@
         </is>
       </c>
       <c r="F110" s="18" t="inlineStr"/>
+      <c r="G110" s="18" t="inlineStr"/>
+      <c r="H110" s="18" t="inlineStr"/>
+      <c r="I110" s="18" t="inlineStr"/>
+      <c r="J110" s="18" t="inlineStr"/>
+      <c r="K110" s="18" t="inlineStr"/>
+      <c r="L110" s="18" t="inlineStr"/>
+      <c r="M110" s="18" t="inlineStr"/>
+      <c r="N110" s="18" t="inlineStr"/>
+      <c r="O110" s="18" t="inlineStr"/>
+      <c r="P110" s="18" t="inlineStr"/>
+      <c r="Q110" s="18" t="inlineStr"/>
+      <c r="R110" s="18" t="inlineStr"/>
+      <c r="S110" s="18" t="inlineStr"/>
+      <c r="T110" s="18" t="inlineStr"/>
+      <c r="U110" s="18" t="inlineStr"/>
+      <c r="V110" s="18" t="inlineStr"/>
+      <c r="W110" s="18" t="inlineStr"/>
+      <c r="X110" s="18" t="inlineStr"/>
+      <c r="Y110" s="18" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="16" t="n">
@@ -4073,6 +6546,33 @@
       </c>
       <c r="E111" s="18" t="inlineStr"/>
       <c r="F111" s="18" t="inlineStr"/>
+      <c r="G111" s="18" t="inlineStr"/>
+      <c r="H111" s="18" t="inlineStr"/>
+      <c r="I111" s="22" t="inlineStr">
+        <is>
+          <t>Digital — 1 PDF held — extraction pending</t>
+        </is>
+      </c>
+      <c r="J111" s="18" t="inlineStr"/>
+      <c r="K111" s="18" t="inlineStr"/>
+      <c r="L111" s="18" t="inlineStr"/>
+      <c r="M111" s="18" t="inlineStr"/>
+      <c r="N111" s="18" t="inlineStr"/>
+      <c r="O111" s="18" t="inlineStr"/>
+      <c r="P111" s="18" t="inlineStr"/>
+      <c r="Q111" s="18" t="inlineStr"/>
+      <c r="R111" s="18" t="inlineStr"/>
+      <c r="S111" s="18" t="inlineStr"/>
+      <c r="T111" s="18" t="inlineStr"/>
+      <c r="U111" s="18" t="inlineStr"/>
+      <c r="V111" s="18" t="inlineStr"/>
+      <c r="W111" s="18" t="inlineStr"/>
+      <c r="X111" s="18" t="inlineStr"/>
+      <c r="Y111" s="17" t="inlineStr">
+        <is>
+          <t>Missing — 3 abstracts cited by the corpus</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="16" t="n">
@@ -4103,6 +6603,25 @@
           <t>Colombo; Ingested</t>
         </is>
       </c>
+      <c r="G112" s="18" t="inlineStr"/>
+      <c r="H112" s="18" t="inlineStr"/>
+      <c r="I112" s="18" t="inlineStr"/>
+      <c r="J112" s="18" t="inlineStr"/>
+      <c r="K112" s="18" t="inlineStr"/>
+      <c r="L112" s="18" t="inlineStr"/>
+      <c r="M112" s="18" t="inlineStr"/>
+      <c r="N112" s="18" t="inlineStr"/>
+      <c r="O112" s="18" t="inlineStr"/>
+      <c r="P112" s="18" t="inlineStr"/>
+      <c r="Q112" s="18" t="inlineStr"/>
+      <c r="R112" s="18" t="inlineStr"/>
+      <c r="S112" s="18" t="inlineStr"/>
+      <c r="T112" s="18" t="inlineStr"/>
+      <c r="U112" s="18" t="inlineStr"/>
+      <c r="V112" s="18" t="inlineStr"/>
+      <c r="W112" s="18" t="inlineStr"/>
+      <c r="X112" s="18" t="inlineStr"/>
+      <c r="Y112" s="18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/database/conference_coverage_matrix.xlsx
+++ b/database/conference_coverage_matrix.xlsx
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
@@ -3521,11 +3521,7 @@
       <c r="H38" s="18" t="inlineStr"/>
       <c r="I38" s="18" t="inlineStr"/>
       <c r="J38" s="18" t="inlineStr"/>
-      <c r="K38" s="17" t="inlineStr">
-        <is>
-          <t>Missing — 1 abstract cited by the corpus</t>
-        </is>
-      </c>
+      <c r="K38" s="18" t="inlineStr"/>
       <c r="L38" s="18" t="inlineStr"/>
       <c r="M38" s="18" t="inlineStr"/>
       <c r="N38" s="18" t="inlineStr"/>
@@ -3624,11 +3620,7 @@
       <c r="H41" s="18" t="inlineStr"/>
       <c r="I41" s="18" t="inlineStr"/>
       <c r="J41" s="18" t="inlineStr"/>
-      <c r="K41" s="17" t="inlineStr">
-        <is>
-          <t>Missing — 1 abstract cited by the corpus</t>
-        </is>
-      </c>
+      <c r="K41" s="18" t="inlineStr"/>
       <c r="L41" s="18" t="inlineStr"/>
       <c r="M41" s="18" t="inlineStr"/>
       <c r="N41" s="18" t="inlineStr"/>
@@ -4238,7 +4230,7 @@
       <c r="X59" s="18" t="inlineStr"/>
       <c r="Y59" s="17" t="inlineStr">
         <is>
-          <t>Missing — 1 abstract cited by the corpus</t>
+          <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
     </row>
@@ -4341,7 +4333,7 @@
       <c r="X62" s="18" t="inlineStr"/>
       <c r="Y62" s="17" t="inlineStr">
         <is>
-          <t>Missing — 2 abstracts cited by the corpus</t>
+          <t>Missing — 2 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4469,7 @@
       <c r="X66" s="18" t="inlineStr"/>
       <c r="Y66" s="17" t="inlineStr">
         <is>
-          <t>Missing — 1 abstract cited by the corpus</t>
+          <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4575,7 @@
       <c r="W69" s="18" t="inlineStr"/>
       <c r="X69" s="17" t="inlineStr">
         <is>
-          <t>Missing — 5 abstracts cited by the corpus</t>
+          <t>?; Missing — 5 abstracts cited by the corpus</t>
         </is>
       </c>
       <c r="Y69" s="18" t="inlineStr"/>
@@ -4625,7 +4617,7 @@
       <c r="X70" s="18" t="inlineStr"/>
       <c r="Y70" s="17" t="inlineStr">
         <is>
-          <t>Missing — 1 abstract cited by the corpus</t>
+          <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4646,11 @@
       <c r="L71" s="18" t="inlineStr"/>
       <c r="M71" s="18" t="inlineStr"/>
       <c r="N71" s="18" t="inlineStr"/>
-      <c r="O71" s="18" t="inlineStr"/>
+      <c r="O71" s="17" t="inlineStr">
+        <is>
+          <t>Tokyo, Japan; Missing — 37 abstracts cited by the corpus [Published 1986]</t>
+        </is>
+      </c>
       <c r="P71" s="18" t="inlineStr"/>
       <c r="Q71" s="18" t="inlineStr"/>
       <c r="R71" s="18" t="inlineStr"/>
@@ -4687,19 +4683,11 @@
       <c r="H72" s="18" t="inlineStr"/>
       <c r="I72" s="18" t="inlineStr"/>
       <c r="J72" s="18" t="inlineStr"/>
-      <c r="K72" s="17" t="inlineStr">
-        <is>
-          <t>Missing — 2 abstracts cited by the corpus</t>
-        </is>
-      </c>
+      <c r="K72" s="18" t="inlineStr"/>
       <c r="L72" s="18" t="inlineStr"/>
       <c r="M72" s="18" t="inlineStr"/>
       <c r="N72" s="18" t="inlineStr"/>
-      <c r="O72" s="17" t="inlineStr">
-        <is>
-          <t>Missing — 37 abstracts cited by the corpus</t>
-        </is>
-      </c>
+      <c r="O72" s="18" t="inlineStr"/>
       <c r="P72" s="18" t="inlineStr"/>
       <c r="Q72" s="18" t="inlineStr"/>
       <c r="R72" s="18" t="inlineStr"/>
@@ -4748,7 +4736,7 @@
       <c r="X73" s="18" t="inlineStr"/>
       <c r="Y73" s="17" t="inlineStr">
         <is>
-          <t>Missing — 1 abstract cited by the corpus</t>
+          <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
     </row>
@@ -4921,11 +4909,7 @@
       <c r="H78" s="18" t="inlineStr"/>
       <c r="I78" s="18" t="inlineStr"/>
       <c r="J78" s="18" t="inlineStr"/>
-      <c r="K78" s="17" t="inlineStr">
-        <is>
-          <t>Missing — 1 abstract cited by the corpus</t>
-        </is>
-      </c>
+      <c r="K78" s="18" t="inlineStr"/>
       <c r="L78" s="18" t="inlineStr"/>
       <c r="M78" s="18" t="inlineStr"/>
       <c r="N78" s="18" t="inlineStr"/>
@@ -4968,7 +4952,7 @@
       <c r="N79" s="18" t="inlineStr"/>
       <c r="O79" s="17" t="inlineStr">
         <is>
-          <t>Missing — 1 abstract cited by the corpus</t>
+          <t>Bangkok, Thailand; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
       <c r="P79" s="18" t="inlineStr"/>
@@ -4982,7 +4966,7 @@
       <c r="X79" s="18" t="inlineStr"/>
       <c r="Y79" s="17" t="inlineStr">
         <is>
-          <t>Missing — 1 abstract cited by the corpus</t>
+          <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
     </row>
@@ -5023,7 +5007,7 @@
       <c r="X80" s="18" t="inlineStr"/>
       <c r="Y80" s="17" t="inlineStr">
         <is>
-          <t>Missing — 2 abstracts cited by the corpus</t>
+          <t>?; Missing — 2 abstracts cited by the corpus</t>
         </is>
       </c>
     </row>
@@ -5131,12 +5115,12 @@
       <c r="M83" s="18" t="inlineStr"/>
       <c r="N83" s="17" t="inlineStr">
         <is>
-          <t>Missing — 1 abstract cited by the corpus</t>
+          <t>Prague, Czech Republic; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
       <c r="O83" s="17" t="inlineStr">
         <is>
-          <t>Missing — 11 abstracts cited by the corpus</t>
+          <t>Noumea, New Caledonia; Missing — 11 abstracts cited by the corpus [Published 1999, 2002]</t>
         </is>
       </c>
       <c r="P83" s="18" t="inlineStr"/>
@@ -5150,7 +5134,7 @@
       <c r="X83" s="18" t="inlineStr"/>
       <c r="Y83" s="17" t="inlineStr">
         <is>
-          <t>Missing — 1 abstract cited by the corpus</t>
+          <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
     </row>
@@ -5277,7 +5261,7 @@
       <c r="X86" s="18" t="inlineStr"/>
       <c r="Y86" s="17" t="inlineStr">
         <is>
-          <t>Missing — 3 abstracts cited by the corpus</t>
+          <t>Missing — 3 abstracts cited by the corpus [3 distinct meetings]</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5301,7 @@
       <c r="S87" s="18" t="inlineStr"/>
       <c r="T87" s="17" t="inlineStr">
         <is>
-          <t>Missing — 1 abstract cited by the corpus</t>
+          <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
       <c r="U87" s="18" t="inlineStr"/>
@@ -5350,7 +5334,7 @@
       <c r="G88" s="18" t="inlineStr"/>
       <c r="H88" s="17" t="inlineStr">
         <is>
-          <t>Missing — 1 abstract cited by the corpus</t>
+          <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
       <c r="I88" s="18" t="inlineStr"/>
@@ -5371,7 +5355,7 @@
       <c r="X88" s="18" t="inlineStr"/>
       <c r="Y88" s="17" t="inlineStr">
         <is>
-          <t>Missing — 7 abstracts cited by the corpus</t>
+          <t>Missing — 7 abstracts cited by the corpus [6 distinct meetings]</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5400,7 @@
       <c r="X89" s="18" t="inlineStr"/>
       <c r="Y89" s="17" t="inlineStr">
         <is>
-          <t>Missing — 4 abstracts cited by the corpus</t>
+          <t>Missing — 4 abstracts cited by the corpus [4 distinct meetings; Published 2006]</t>
         </is>
       </c>
     </row>
@@ -5445,13 +5429,13 @@
       <c r="H90" s="18" t="inlineStr"/>
       <c r="I90" s="22" t="inlineStr">
         <is>
-          <t>Digital — 1 PDF held — extraction pending</t>
+          <t>Ciudad Universitaria, Mexico City; Digital — 1 PDF held — extraction pending</t>
         </is>
       </c>
       <c r="J90" s="18" t="inlineStr"/>
       <c r="K90" s="17" t="inlineStr">
         <is>
-          <t>Missing — 7 abstracts cited by the corpus</t>
+          <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
       <c r="L90" s="18" t="inlineStr"/>
@@ -5463,7 +5447,7 @@
       <c r="R90" s="18" t="inlineStr"/>
       <c r="S90" s="17" t="inlineStr">
         <is>
-          <t>Missing — 4 abstracts cited by the corpus</t>
+          <t>Manaus, Brazil; Missing — 4 abstracts cited by the corpus</t>
         </is>
       </c>
       <c r="T90" s="18" t="inlineStr"/>
@@ -5473,7 +5457,7 @@
       <c r="X90" s="18" t="inlineStr"/>
       <c r="Y90" s="17" t="inlineStr">
         <is>
-          <t>Missing — 2 abstracts cited by the corpus</t>
+          <t>Missing — 2 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
     </row>
@@ -5502,11 +5486,7 @@
       <c r="H91" s="18" t="inlineStr"/>
       <c r="I91" s="18" t="inlineStr"/>
       <c r="J91" s="18" t="inlineStr"/>
-      <c r="K91" s="17" t="inlineStr">
-        <is>
-          <t>Missing — 1 abstract cited by the corpus</t>
-        </is>
-      </c>
+      <c r="K91" s="18" t="inlineStr"/>
       <c r="L91" s="18" t="inlineStr"/>
       <c r="M91" s="18" t="inlineStr"/>
       <c r="N91" s="18" t="inlineStr"/>
@@ -5517,7 +5497,7 @@
       <c r="S91" s="18" t="inlineStr"/>
       <c r="T91" s="17" t="inlineStr">
         <is>
-          <t>Missing — 2 abstracts cited by the corpus</t>
+          <t>Miraflores de la Sierra, Madrid, Spain; Missing — 2 abstracts cited by the corpus</t>
         </is>
       </c>
       <c r="U91" s="18" t="inlineStr"/>
@@ -5526,7 +5506,7 @@
       <c r="X91" s="18" t="inlineStr"/>
       <c r="Y91" s="17" t="inlineStr">
         <is>
-          <t>Missing — 2 abstracts cited by the corpus</t>
+          <t>Missing — 2 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
     </row>
@@ -5557,7 +5537,7 @@
       <c r="J92" s="18" t="inlineStr"/>
       <c r="K92" s="17" t="inlineStr">
         <is>
-          <t>Missing — 12 abstracts cited by the corpus</t>
+          <t>?; Missing — 10 abstracts cited by the corpus</t>
         </is>
       </c>
       <c r="L92" s="18" t="inlineStr"/>
@@ -5575,7 +5555,7 @@
       <c r="X92" s="18" t="inlineStr"/>
       <c r="Y92" s="17" t="inlineStr">
         <is>
-          <t>Missing — 5 abstracts cited by the corpus</t>
+          <t>Missing — 5 abstracts cited by the corpus [5 distinct meetings; Published 2007]</t>
         </is>
       </c>
     </row>
@@ -5606,7 +5586,7 @@
       <c r="J93" s="18" t="inlineStr"/>
       <c r="K93" s="17" t="inlineStr">
         <is>
-          <t>Missing — 1 abstract cited by the corpus</t>
+          <t>Punta Cana, Dominican Republic; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
       <c r="L93" s="18" t="inlineStr"/>
@@ -5617,7 +5597,7 @@
       <c r="Q93" s="18" t="inlineStr"/>
       <c r="R93" s="17" t="inlineStr">
         <is>
-          <t>Missing — 6 abstracts cited by the corpus</t>
+          <t>?; Missing — 6 abstracts cited by the corpus</t>
         </is>
       </c>
       <c r="S93" s="18" t="inlineStr"/>
@@ -5628,7 +5608,7 @@
       <c r="X93" s="18" t="inlineStr"/>
       <c r="Y93" s="17" t="inlineStr">
         <is>
-          <t>Missing — 3 abstracts cited by the corpus</t>
+          <t>Missing — 3 abstracts cited by the corpus [3 distinct meetings]</t>
         </is>
       </c>
     </row>
@@ -5657,7 +5637,7 @@
       <c r="H94" s="18" t="inlineStr"/>
       <c r="I94" s="22" t="inlineStr">
         <is>
-          <t>Digital — 1 PDF held — extraction pending</t>
+          <t>Ciudad Universitaria, Mexico City; Digital — 1 PDF held — extraction pending</t>
         </is>
       </c>
       <c r="J94" s="18" t="inlineStr"/>
@@ -5677,7 +5657,7 @@
       <c r="X94" s="18" t="inlineStr"/>
       <c r="Y94" s="17" t="inlineStr">
         <is>
-          <t>Missing — 6 abstracts cited by the corpus</t>
+          <t>Missing — 6 abstracts cited by the corpus [6 distinct meetings]</t>
         </is>
       </c>
     </row>
@@ -5708,7 +5688,7 @@
       <c r="J95" s="18" t="inlineStr"/>
       <c r="K95" s="17" t="inlineStr">
         <is>
-          <t>Missing — 3 abstracts cited by the corpus</t>
+          <t>Cumana, Venezuela; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
       <c r="L95" s="18" t="inlineStr"/>
@@ -5719,14 +5699,18 @@
       <c r="Q95" s="18" t="inlineStr"/>
       <c r="R95" s="18" t="inlineStr"/>
       <c r="S95" s="18" t="inlineStr"/>
-      <c r="T95" s="18" t="inlineStr"/>
+      <c r="T95" s="17" t="inlineStr">
+        <is>
+          <t>?; Missing — 2 abstracts cited by the corpus [Published 2010]</t>
+        </is>
+      </c>
       <c r="U95" s="18" t="inlineStr"/>
       <c r="V95" s="18" t="inlineStr"/>
       <c r="W95" s="18" t="inlineStr"/>
       <c r="X95" s="18" t="inlineStr"/>
       <c r="Y95" s="17" t="inlineStr">
         <is>
-          <t>Missing — 3 abstracts cited by the corpus</t>
+          <t>Missing — 3 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
     </row>
@@ -5759,15 +5743,11 @@
       <c r="H96" s="18" t="inlineStr"/>
       <c r="I96" s="22" t="inlineStr">
         <is>
-          <t>Digital — 1 PDF held — extraction pending</t>
+          <t>Ciudad Universitaria, Mexico City; Digital — 1 PDF held — extraction pending</t>
         </is>
       </c>
       <c r="J96" s="18" t="inlineStr"/>
-      <c r="K96" s="17" t="inlineStr">
-        <is>
-          <t>Missing — 2 abstracts cited by the corpus</t>
-        </is>
-      </c>
+      <c r="K96" s="18" t="inlineStr"/>
       <c r="L96" s="18" t="inlineStr"/>
       <c r="M96" s="18" t="inlineStr"/>
       <c r="N96" s="18" t="inlineStr"/>
@@ -5776,22 +5756,18 @@
       <c r="Q96" s="18" t="inlineStr"/>
       <c r="R96" s="18" t="inlineStr"/>
       <c r="S96" s="18" t="inlineStr"/>
-      <c r="T96" s="17" t="inlineStr">
-        <is>
-          <t>Missing — 2 abstracts cited by the corpus</t>
-        </is>
-      </c>
+      <c r="T96" s="18" t="inlineStr"/>
       <c r="U96" s="18" t="inlineStr"/>
       <c r="V96" s="17" t="inlineStr">
         <is>
-          <t>Missing — 1 abstract cited by the corpus</t>
+          <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
       <c r="W96" s="18" t="inlineStr"/>
       <c r="X96" s="18" t="inlineStr"/>
       <c r="Y96" s="17" t="inlineStr">
         <is>
-          <t>Missing — 3 abstracts cited by the corpus</t>
+          <t>Missing — 3 abstracts cited by the corpus [3 distinct meetings]</t>
         </is>
       </c>
     </row>
@@ -5821,13 +5797,13 @@
       <c r="I97" s="18" t="inlineStr"/>
       <c r="J97" s="17" t="inlineStr">
         <is>
-          <t>Missing — 48 abstracts cited by the corpus</t>
+          <t>Dakar, Senegal; Missing — 48 abstracts cited by the corpus</t>
         </is>
       </c>
       <c r="K97" s="18" t="inlineStr"/>
       <c r="L97" s="17" t="inlineStr">
         <is>
-          <t>Missing — 12 abstracts cited by the corpus</t>
+          <t>Vancouver, Canada; Missing — 12 abstracts cited by the corpus [Published 2012]</t>
         </is>
       </c>
       <c r="M97" s="18" t="inlineStr"/>
@@ -5837,7 +5813,7 @@
       <c r="Q97" s="18" t="inlineStr"/>
       <c r="R97" s="17" t="inlineStr">
         <is>
-          <t>Missing — 1 abstract cited by the corpus</t>
+          <t>Seattle, WA; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
       <c r="S97" s="18" t="inlineStr"/>
@@ -5848,7 +5824,7 @@
       <c r="X97" s="18" t="inlineStr"/>
       <c r="Y97" s="17" t="inlineStr">
         <is>
-          <t>Missing — 9 abstracts cited by the corpus</t>
+          <t>Missing — 9 abstracts cited by the corpus [5 distinct meetings]</t>
         </is>
       </c>
     </row>
@@ -5886,23 +5862,23 @@
       <c r="M98" s="18" t="inlineStr"/>
       <c r="N98" s="17" t="inlineStr">
         <is>
-          <t>Missing — 100 abstracts cited by the corpus</t>
+          <t>Vancouver, Canada; Missing — 100 abstracts cited by the corpus [Published 2010, 2015]</t>
         </is>
       </c>
       <c r="O98" s="18" t="inlineStr"/>
       <c r="P98" s="17" t="inlineStr">
         <is>
-          <t>Missing — 13 abstracts cited by the corpus</t>
+          <t>Cairns, Queensland, Australia; Missing — 13 abstracts cited by the corpus</t>
         </is>
       </c>
       <c r="Q98" s="17" t="inlineStr">
         <is>
-          <t>Missing — 6 abstracts cited by the corpus</t>
+          <t>Edinburgh, Scotland; Missing — 6 abstracts cited by the corpus</t>
         </is>
       </c>
       <c r="R98" s="17" t="inlineStr">
         <is>
-          <t>Missing — 2 abstracts cited by the corpus</t>
+          <t>Missing — 2 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
       <c r="S98" s="18" t="inlineStr"/>
@@ -5911,13 +5887,13 @@
       <c r="V98" s="18" t="inlineStr"/>
       <c r="W98" s="17" t="inlineStr">
         <is>
-          <t>Missing — 3 abstracts cited by the corpus</t>
+          <t>Honolulu, HI (U. Hawai'i at Manoa); Missing — 3 abstracts cited by the corpus</t>
         </is>
       </c>
       <c r="X98" s="18" t="inlineStr"/>
       <c r="Y98" s="17" t="inlineStr">
         <is>
-          <t>Missing — 1 abstract cited by the corpus</t>
+          <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
     </row>
@@ -5950,7 +5926,7 @@
       <c r="L99" s="18" t="inlineStr"/>
       <c r="M99" s="17" t="inlineStr">
         <is>
-          <t>Missing — 2 abstracts cited by the corpus</t>
+          <t>Missing — 2 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
       <c r="N99" s="18" t="inlineStr"/>
@@ -5961,7 +5937,7 @@
       <c r="S99" s="18" t="inlineStr"/>
       <c r="T99" s="17" t="inlineStr">
         <is>
-          <t>Missing — 11 abstracts cited by the corpus</t>
+          <t>Vienna, Austria; Missing — 11 abstracts cited by the corpus</t>
         </is>
       </c>
       <c r="U99" s="18" t="inlineStr"/>
@@ -5970,7 +5946,7 @@
       <c r="X99" s="18" t="inlineStr"/>
       <c r="Y99" s="17" t="inlineStr">
         <is>
-          <t>Missing — 2 abstracts cited by the corpus</t>
+          <t>Missing — 2 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
     </row>
@@ -6005,13 +5981,13 @@
       </c>
       <c r="G100" s="17" t="inlineStr">
         <is>
-          <t>Missing — 79 abstracts cited by the corpus</t>
+          <t>?; Missing — 79 abstracts cited by the corpus</t>
         </is>
       </c>
       <c r="H100" s="18" t="inlineStr"/>
       <c r="I100" s="17" t="inlineStr">
         <is>
-          <t>Missing — 44 abstracts cited by the corpus</t>
+          <t>Mazatlan, Sinaloa, Mexico; Missing — 44 abstracts cited by the corpus</t>
         </is>
       </c>
       <c r="J100" s="18" t="inlineStr"/>
@@ -6024,7 +6000,7 @@
       <c r="Q100" s="18" t="inlineStr"/>
       <c r="R100" s="17" t="inlineStr">
         <is>
-          <t>Missing — 1 abstract cited by the corpus</t>
+          <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
       <c r="S100" s="18" t="inlineStr"/>
@@ -6035,7 +6011,7 @@
       <c r="X100" s="18" t="inlineStr"/>
       <c r="Y100" s="17" t="inlineStr">
         <is>
-          <t>Missing — 1 abstract cited by the corpus</t>
+          <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
     </row>
@@ -6080,7 +6056,7 @@
       <c r="X101" s="18" t="inlineStr"/>
       <c r="Y101" s="17" t="inlineStr">
         <is>
-          <t>Missing — 4 abstracts cited by the corpus</t>
+          <t>Missing — 4 abstracts cited by the corpus [3 distinct meetings]</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6089,7 @@
       <c r="H102" s="18" t="inlineStr"/>
       <c r="I102" s="22" t="inlineStr">
         <is>
-          <t>Digital — 1 PDF held — extraction pending</t>
+          <t>Puerto Vallarta, Jalisco, Mexico; Digital — 1 PDF held — extraction pending</t>
         </is>
       </c>
       <c r="J102" s="18" t="inlineStr"/>
@@ -6133,7 +6109,7 @@
       <c r="X102" s="18" t="inlineStr"/>
       <c r="Y102" s="17" t="inlineStr">
         <is>
-          <t>Missing — 3 abstracts cited by the corpus</t>
+          <t>Missing — 3 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6154,7 @@
       <c r="X103" s="18" t="inlineStr"/>
       <c r="Y103" s="17" t="inlineStr">
         <is>
-          <t>Missing — 1 abstract cited by the corpus</t>
+          <t>?; Missing — 1 abstract cited by the corpus [Published 2018]</t>
         </is>
       </c>
     </row>
@@ -6231,7 +6207,7 @@
       <c r="X104" s="18" t="inlineStr"/>
       <c r="Y104" s="17" t="inlineStr">
         <is>
-          <t>Missing — 3 abstracts cited by the corpus</t>
+          <t>Missing — 3 abstracts cited by the corpus [3 distinct meetings]</t>
         </is>
       </c>
     </row>
@@ -6272,7 +6248,7 @@
       <c r="T105" s="18" t="inlineStr"/>
       <c r="U105" s="17" t="inlineStr">
         <is>
-          <t>Missing — 1 abstract cited by the corpus</t>
+          <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
       <c r="V105" s="18" t="inlineStr"/>
@@ -6325,7 +6301,7 @@
       <c r="X106" s="18" t="inlineStr"/>
       <c r="Y106" s="17" t="inlineStr">
         <is>
-          <t>Missing — 1 abstract cited by the corpus</t>
+          <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6330,7 @@
       <c r="H107" s="18" t="inlineStr"/>
       <c r="I107" s="22" t="inlineStr">
         <is>
-          <t>Digital — 1 PDF held — extraction pending</t>
+          <t>Puebla, Mexico; Digital — 1 PDF held — extraction pending</t>
         </is>
       </c>
       <c r="J107" s="18" t="inlineStr"/>
@@ -6374,7 +6350,7 @@
       <c r="X107" s="18" t="inlineStr"/>
       <c r="Y107" s="17" t="inlineStr">
         <is>
-          <t>Missing — 2 abstracts cited by the corpus</t>
+          <t>Missing — 2 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
     </row>
@@ -6382,14 +6358,14 @@
       <c r="A108" s="16" t="n">
         <v>2022</v>
       </c>
-      <c r="B108" s="25" t="inlineStr">
-        <is>
-          <t>Spokane, WA; Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
-        </is>
-      </c>
-      <c r="C108" s="25" t="inlineStr">
-        <is>
-          <t>Spokane, WA (68); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
+      <c r="B108" s="19" t="inlineStr">
+        <is>
+          <t>Spokane, WA; Ingested — Oxford Abstracts export (born-digital)</t>
+        </is>
+      </c>
+      <c r="C108" s="19" t="inlineStr">
+        <is>
+          <t>Spokane, WA (109); Ingested — Oxford Abstracts export (born-digital)</t>
         </is>
       </c>
       <c r="D108" s="22" t="inlineStr">
@@ -6427,7 +6403,7 @@
       <c r="X108" s="18" t="inlineStr"/>
       <c r="Y108" s="17" t="inlineStr">
         <is>
-          <t>Missing — 2 abstracts cited by the corpus</t>
+          <t>?; Missing — 2 abstracts cited by the corpus</t>
         </is>
       </c>
     </row>
@@ -6467,7 +6443,7 @@
       <c r="S109" s="18" t="inlineStr"/>
       <c r="T109" s="17" t="inlineStr">
         <is>
-          <t>Missing — 1 abstract cited by the corpus</t>
+          <t>Stuttgart, Germany; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
       <c r="U109" s="18" t="inlineStr"/>
@@ -6476,7 +6452,7 @@
       <c r="X109" s="18" t="inlineStr"/>
       <c r="Y109" s="17" t="inlineStr">
         <is>
-          <t>Missing — 1 abstract cited by the corpus</t>
+          <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
     </row>
@@ -6529,14 +6505,14 @@
       <c r="A111" s="16" t="n">
         <v>2025</v>
       </c>
-      <c r="B111" s="25" t="inlineStr">
-        <is>
-          <t>St. Paul, MN; Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
-        </is>
-      </c>
-      <c r="C111" s="25" t="inlineStr">
-        <is>
-          <t>St. Paul, MN (68); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
+      <c r="B111" s="19" t="inlineStr">
+        <is>
+          <t>St. Paul, MN; Ingested — Oxford Abstracts export (born-digital)</t>
+        </is>
+      </c>
+      <c r="C111" s="19" t="inlineStr">
+        <is>
+          <t>St. Paul, MN (123); Ingested — Oxford Abstracts export (born-digital)</t>
         </is>
       </c>
       <c r="D111" s="26" t="inlineStr">
@@ -6550,7 +6526,7 @@
       <c r="H111" s="18" t="inlineStr"/>
       <c r="I111" s="22" t="inlineStr">
         <is>
-          <t>Digital — 1 PDF held — extraction pending</t>
+          <t>Ensenada, Baja California, Mexico; Digital — 1 PDF held — extraction pending</t>
         </is>
       </c>
       <c r="J111" s="18" t="inlineStr"/>
@@ -6570,7 +6546,7 @@
       <c r="X111" s="18" t="inlineStr"/>
       <c r="Y111" s="17" t="inlineStr">
         <is>
-          <t>Missing — 3 abstracts cited by the corpus</t>
+          <t>?; Missing — 3 abstracts cited by the corpus</t>
         </is>
       </c>
     </row>
@@ -6578,14 +6554,14 @@
       <c r="A112" s="16" t="n">
         <v>2026</v>
       </c>
-      <c r="B112" s="22" t="inlineStr">
-        <is>
-          <t>New Orleans, LA; Digital — abstract book held (1 PDF) — extraction pending</t>
-        </is>
-      </c>
-      <c r="C112" s="22" t="inlineStr">
-        <is>
-          <t>New Orleans, LA; Digital — abstract book held (1 PDF) — extraction pending</t>
+      <c r="B112" s="24" t="inlineStr">
+        <is>
+          <t>New Orleans, LA; Extracted — regex-parsed; Fable re-extraction queued</t>
+        </is>
+      </c>
+      <c r="C112" s="24" t="inlineStr">
+        <is>
+          <t>New Orleans, LA (235); Extracted — regex-parsed; Fable re-extraction queued</t>
         </is>
       </c>
       <c r="D112" s="23" t="inlineStr">
@@ -7448,19 +7424,19 @@
         <v>2021</v>
       </c>
       <c r="B33" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C33" t="n">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="D33" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E33" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -7474,16 +7450,16 @@
         <v>2022</v>
       </c>
       <c r="B34" t="n">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="C34" t="n">
-        <v>106</v>
+        <v>274</v>
       </c>
       <c r="D34" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E34" t="n">
-        <v>20</v>
+        <v>118</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -7500,16 +7476,16 @@
         <v>2023</v>
       </c>
       <c r="B35" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C35" t="n">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="D35" t="n">
         <v>201</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
         <v>3</v>
@@ -7526,7 +7502,7 @@
         <v>2024</v>
       </c>
       <c r="B36" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C36" t="n">
         <v>174</v>
@@ -7552,19 +7528,19 @@
         <v>2025</v>
       </c>
       <c r="B37" t="n">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="C37" t="n">
-        <v>67</v>
+        <v>241</v>
       </c>
       <c r="D37" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="E37" t="n">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -7578,25 +7554,25 @@
         <v>2026</v>
       </c>
       <c r="B38" t="n">
-        <v>37</v>
+        <v>235</v>
       </c>
       <c r="C38" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D38" t="n">
         <v>10</v>
       </c>
       <c r="E38" t="n">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="F38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="39">
@@ -7606,25 +7582,25 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>2849</v>
+        <v>3142</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>5620</v>
+        <v>5976</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>3274</v>
+        <v>3302</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>540</v>
+        <v>715</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G39" s="1" t="n">
         <v>956</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>1750</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="42">
@@ -7656,13 +7632,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C43" t="n">
         <v>42</v>
       </c>
       <c r="D43" t="n">
-        <v>73.8</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="44">

--- a/database/conference_coverage_matrix.xlsx
+++ b/database/conference_coverage_matrix.xlsx
@@ -5578,7 +5578,11 @@
           <t>Brest; Pending — 11th EEA; Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
-      <c r="E93" s="18" t="inlineStr"/>
+      <c r="E93" s="22" t="inlineStr">
+        <is>
+          <t>Queenscliff, VIC, Australia; Digital — abstract book held, queued for extraction</t>
+        </is>
+      </c>
       <c r="F93" s="18" t="inlineStr"/>
       <c r="G93" s="18" t="inlineStr"/>
       <c r="H93" s="18" t="inlineStr"/>
@@ -5631,7 +5635,11 @@
           <t>Lisbon; Pending — 12th EEA; Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
-      <c r="E94" s="18" t="inlineStr"/>
+      <c r="E94" s="22" t="inlineStr">
+        <is>
+          <t>Sydney, NSW, Australia; Digital — abstract book held, queued for extraction</t>
+        </is>
+      </c>
       <c r="F94" s="18" t="inlineStr"/>
       <c r="G94" s="18" t="inlineStr"/>
       <c r="H94" s="18" t="inlineStr"/>
@@ -5790,7 +5798,11 @@
           <t>Berlin; Ingested — 58 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E97" s="18" t="inlineStr"/>
+      <c r="E97" s="22" t="inlineStr">
+        <is>
+          <t>Gold Coast, QLD, Australia; Digital — abstract book held, queued for extraction</t>
+        </is>
+      </c>
       <c r="F97" s="18" t="inlineStr"/>
       <c r="G97" s="18" t="inlineStr"/>
       <c r="H97" s="18" t="inlineStr"/>
@@ -5847,9 +5859,9 @@
           <t>Milan; Hardcopy — Cat holds a hardcopy but has no scanning capacity; digital copy needed from GRIS (Italy)</t>
         </is>
       </c>
-      <c r="E98" s="23" t="inlineStr">
-        <is>
-          <t>Adelaide; Pending — joint with ASFB; Brit Finucci confirming</t>
+      <c r="E98" s="22" t="inlineStr">
+        <is>
+          <t>Adelaide; Digital — abstract book held, queued for extraction</t>
         </is>
       </c>
       <c r="F98" s="18" t="inlineStr"/>
@@ -5916,7 +5928,11 @@
           <t>Plymouth; Ingested — 93 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E99" s="18" t="inlineStr"/>
+      <c r="E99" s="22" t="inlineStr">
+        <is>
+          <t>Brisbane, QLD, Australia; Digital — abstract book held, queued for extraction</t>
+        </is>
+      </c>
       <c r="F99" s="18" t="inlineStr"/>
       <c r="G99" s="18" t="inlineStr"/>
       <c r="H99" s="18" t="inlineStr"/>
@@ -6034,7 +6050,11 @@
           <t>Peniche; Digital — 19th EEA Book of Abstracts (99pp, born-digital) held by Simon all along; queued for extraction</t>
         </is>
       </c>
-      <c r="E101" s="18" t="inlineStr"/>
+      <c r="E101" s="22" t="inlineStr">
+        <is>
+          <t>Auckland, New Zealand; Digital — abstract book held, queued for extraction</t>
+        </is>
+      </c>
       <c r="F101" s="18" t="inlineStr"/>
       <c r="G101" s="18" t="inlineStr"/>
       <c r="H101" s="18" t="inlineStr"/>
@@ -6079,9 +6099,9 @@
           <t>Bristol; Ingested — 93 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E102" s="23" t="inlineStr">
-        <is>
-          <t>?; Pending — Brit Finucci collating; year/location to confirm</t>
+      <c r="E102" s="19" t="inlineStr">
+        <is>
+          <t>Wrest Point, Tasmania, Australia; Ingested — 222 abstracts, 219 with bodies; joint meeting, elasmo flagged per abstract</t>
         </is>
       </c>
       <c r="F102" s="18" t="inlineStr"/>
@@ -6177,9 +6197,9 @@
           <t>Peniche; Ingested — 75 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E104" s="23" t="inlineStr">
-        <is>
-          <t>North Stradbroke Is.; Pending — Moreton Bay Research Station; Brit Finucci confirming</t>
+      <c r="E104" s="22" t="inlineStr">
+        <is>
+          <t>North Stradbroke Is.; Digital — abstract book held, queued for extraction</t>
         </is>
       </c>
       <c r="F104" s="19" t="inlineStr">
@@ -6230,7 +6250,11 @@
           <t>Rende; Ingested — 136 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E105" s="18" t="inlineStr"/>
+      <c r="E105" s="22" t="inlineStr">
+        <is>
+          <t>Dunedin, New Zealand; Digital — abstract book held, queued for extraction</t>
+        </is>
+      </c>
       <c r="F105" s="18" t="inlineStr"/>
       <c r="G105" s="18" t="inlineStr"/>
       <c r="H105" s="18" t="inlineStr"/>
@@ -6275,9 +6299,9 @@
           <t>?; Missing — unknown whether a meeting was held: Cat thinks it was online for covid but was on maternity leave and is unsure; organiser unknown; abstracts unknown</t>
         </is>
       </c>
-      <c r="E106" s="23" t="inlineStr">
-        <is>
-          <t>?; Pending — Brit Finucci collating; year/location to confirm</t>
+      <c r="E106" s="22" t="inlineStr">
+        <is>
+          <t>Virtual; Digital — abstract book held, queued for extraction</t>
         </is>
       </c>
       <c r="F106" s="18" t="inlineStr"/>
@@ -6373,9 +6397,9 @@
           <t>Valencia (=SI2022); Digital — full SI2022 abstract book received 2026-08-27; queued for extraction</t>
         </is>
       </c>
-      <c r="E108" s="23" t="inlineStr">
-        <is>
-          <t>?; Pending — Brit Finucci collating; year/location to confirm</t>
+      <c r="E108" s="22" t="inlineStr">
+        <is>
+          <t>Virtual; Digital — abstract book held, queued for extraction</t>
         </is>
       </c>
       <c r="F108" s="22" t="inlineStr">
@@ -6475,9 +6499,9 @@
           <t>Thessaloniki; Digital — clean abstract book received from Cat 2026-08-27; queued for extraction</t>
         </is>
       </c>
-      <c r="E110" s="23" t="inlineStr">
-        <is>
-          <t>Geelong; Pending — Brit Finucci confirming</t>
+      <c r="E110" s="22" t="inlineStr">
+        <is>
+          <t>Geelong; Digital — abstract book held, queued for extraction</t>
         </is>
       </c>
       <c r="F110" s="18" t="inlineStr"/>
@@ -6520,7 +6544,11 @@
           <t>Rotterdam; Programme — agenda only; Cat has no abstract book and is unsure one was produced; NEV/Irene to confirm whether it exists</t>
         </is>
       </c>
-      <c r="E111" s="18" t="inlineStr"/>
+      <c r="E111" s="22" t="inlineStr">
+        <is>
+          <t>Sunshine Coast, QLD, Australia; Digital — abstract book held, queued for extraction</t>
+        </is>
+      </c>
       <c r="F111" s="18" t="inlineStr"/>
       <c r="G111" s="18" t="inlineStr"/>
       <c r="H111" s="18" t="inlineStr"/>
@@ -7664,13 +7692,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="46">

--- a/database/conference_coverage_matrix.xlsx
+++ b/database/conference_coverage_matrix.xlsx
@@ -6299,9 +6299,9 @@
           <t>?; Missing — unknown whether a meeting was held: Cat thinks it was online for covid but was on maternity leave and is unsure; organiser unknown; abstracts unknown</t>
         </is>
       </c>
-      <c r="E106" s="22" t="inlineStr">
-        <is>
-          <t>Virtual; Digital — abstract book held, queued for extraction</t>
+      <c r="E106" s="19" t="inlineStr">
+        <is>
+          <t>Virtual; Ingested — 44 abstracts, 44 with bodies</t>
         </is>
       </c>
       <c r="F106" s="18" t="inlineStr"/>
@@ -6397,9 +6397,9 @@
           <t>Valencia (=SI2022); Digital — full SI2022 abstract book received 2026-08-27; queued for extraction</t>
         </is>
       </c>
-      <c r="E108" s="22" t="inlineStr">
-        <is>
-          <t>Virtual; Digital — abstract book held, queued for extraction</t>
+      <c r="E108" s="19" t="inlineStr">
+        <is>
+          <t>Virtual; Ingested — 30 abstracts, 30 with bodies</t>
         </is>
       </c>
       <c r="F108" s="22" t="inlineStr">
@@ -6544,9 +6544,9 @@
           <t>Rotterdam; Programme — agenda only; Cat has no abstract book and is unsure one was produced; NEV/Irene to confirm whether it exists</t>
         </is>
       </c>
-      <c r="E111" s="22" t="inlineStr">
-        <is>
-          <t>Sunshine Coast, QLD, Australia; Digital — abstract book held, queued for extraction</t>
+      <c r="E111" s="19" t="inlineStr">
+        <is>
+          <t>Sunshine Coast, QLD, Australia; Ingested — 92 abstracts, 92 with bodies</t>
         </is>
       </c>
       <c r="F111" s="18" t="inlineStr"/>
@@ -7692,13 +7692,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C45" t="n">
         <v>15</v>
       </c>
       <c r="D45" t="n">
-        <v>6.7</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="46">

--- a/database/conference_coverage_matrix.xlsx
+++ b/database/conference_coverage_matrix.xlsx
@@ -5514,14 +5514,14 @@
       <c r="A92" s="16" t="n">
         <v>2006</v>
       </c>
-      <c r="B92" s="22" t="inlineStr">
-        <is>
-          <t>New Orleans, LA; Digital — abstract book held (1 PDF) — extraction pending</t>
-        </is>
-      </c>
-      <c r="C92" s="22" t="inlineStr">
-        <is>
-          <t>New Orleans, LA; Digital — abstract book held (1 PDF) — extraction pending</t>
+      <c r="B92" s="19" t="inlineStr">
+        <is>
+          <t>New Orleans, LA; Ingested</t>
+        </is>
+      </c>
+      <c r="C92" s="19" t="inlineStr">
+        <is>
+          <t>New Orleans, LA (169); Ingested</t>
         </is>
       </c>
       <c r="D92" s="23" t="inlineStr">
@@ -5578,9 +5578,9 @@
           <t>Brest; Pending — 11th EEA; Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
-      <c r="E93" s="22" t="inlineStr">
-        <is>
-          <t>Queenscliff, VIC, Australia; Digital — abstract book held, queued for extraction</t>
+      <c r="E93" s="19" t="inlineStr">
+        <is>
+          <t>Queenscliff, VIC, Australia; Ingested — 51 abstracts, 51 with bodies</t>
         </is>
       </c>
       <c r="F93" s="18" t="inlineStr"/>
@@ -5635,9 +5635,9 @@
           <t>Lisbon; Pending — 12th EEA; Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
-      <c r="E94" s="22" t="inlineStr">
-        <is>
-          <t>Sydney, NSW, Australia; Digital — abstract book held, queued for extraction</t>
+      <c r="E94" s="19" t="inlineStr">
+        <is>
+          <t>Sydney, NSW, Australia; Ingested — 50 abstracts, 47 with bodies</t>
         </is>
       </c>
       <c r="F94" s="18" t="inlineStr"/>
@@ -5798,9 +5798,9 @@
           <t>Berlin; Ingested — 58 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E97" s="22" t="inlineStr">
-        <is>
-          <t>Gold Coast, QLD, Australia; Digital — abstract book held, queued for extraction</t>
+      <c r="E97" s="19" t="inlineStr">
+        <is>
+          <t>Gold Coast, QLD, Australia; Ingested — 48 abstracts, 48 with bodies</t>
         </is>
       </c>
       <c r="F97" s="18" t="inlineStr"/>
@@ -5846,12 +5846,12 @@
       </c>
       <c r="B98" s="24" t="inlineStr">
         <is>
-          <t>Vancouver, BC; Extracted — regex-parsed; Fable re-extraction queued</t>
+          <t>Vancouver, BC; Extracted — regex-parsed; Fable re-extraction part-done (1078 so far)</t>
         </is>
       </c>
       <c r="C98" s="24" t="inlineStr">
         <is>
-          <t>Vancouver, BC (62); Extracted — regex-parsed; Fable re-extraction queued</t>
+          <t>Vancouver, BC (62); Extracted — regex-parsed; Fable re-extraction part-done (1078 so far)</t>
         </is>
       </c>
       <c r="D98" s="20" t="inlineStr">
@@ -5859,9 +5859,9 @@
           <t>Milan; Hardcopy — Cat holds a hardcopy but has no scanning capacity; digital copy needed from GRIS (Italy)</t>
         </is>
       </c>
-      <c r="E98" s="22" t="inlineStr">
-        <is>
-          <t>Adelaide; Digital — abstract book held, queued for extraction</t>
+      <c r="E98" s="19" t="inlineStr">
+        <is>
+          <t>Adelaide; Ingested — 171 abstracts, 171 with bodies; joint meeting, elasmo flagged per abstract</t>
         </is>
       </c>
       <c r="F98" s="18" t="inlineStr"/>
@@ -5928,9 +5928,9 @@
           <t>Plymouth; Ingested — 93 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E99" s="22" t="inlineStr">
-        <is>
-          <t>Brisbane, QLD, Australia; Digital — abstract book held, queued for extraction</t>
+      <c r="E99" s="19" t="inlineStr">
+        <is>
+          <t>Brisbane, QLD, Australia; Ingested — 34 abstracts, 34 with bodies</t>
         </is>
       </c>
       <c r="F99" s="18" t="inlineStr"/>
@@ -5970,14 +5970,14 @@
       <c r="A100" s="16" t="n">
         <v>2014</v>
       </c>
-      <c r="B100" s="22" t="inlineStr">
-        <is>
-          <t>Chattanooga, TN; Digital — abstract book held — Fable extraction part-done (254 so far)</t>
-        </is>
-      </c>
-      <c r="C100" s="22" t="inlineStr">
-        <is>
-          <t>Chattanooga, TN; Digital — abstract book held — Fable extraction part-done (254 so far)</t>
+      <c r="B100" s="19" t="inlineStr">
+        <is>
+          <t>Chattanooga, TN; Ingested</t>
+        </is>
+      </c>
+      <c r="C100" s="19" t="inlineStr">
+        <is>
+          <t>Chattanooga, TN (92); Ingested</t>
         </is>
       </c>
       <c r="D100" s="19" t="inlineStr">
@@ -6050,9 +6050,9 @@
           <t>Peniche; Digital — 19th EEA Book of Abstracts (99pp, born-digital) held by Simon all along; queued for extraction</t>
         </is>
       </c>
-      <c r="E101" s="22" t="inlineStr">
-        <is>
-          <t>Auckland, New Zealand; Digital — abstract book held, queued for extraction</t>
+      <c r="E101" s="19" t="inlineStr">
+        <is>
+          <t>Auckland, New Zealand; Ingested — 219 abstracts, 217 with bodies; joint meeting, elasmo flagged per abstract</t>
         </is>
       </c>
       <c r="F101" s="18" t="inlineStr"/>
@@ -6137,14 +6137,14 @@
       <c r="A103" s="16" t="n">
         <v>2017</v>
       </c>
-      <c r="B103" s="22" t="inlineStr">
-        <is>
-          <t>Austin, TX; Digital — abstract book held (1 PDF) — extraction pending</t>
-        </is>
-      </c>
-      <c r="C103" s="22" t="inlineStr">
-        <is>
-          <t>Austin, TX; Digital — abstract book held (1 PDF) — extraction pending</t>
+      <c r="B103" s="19" t="inlineStr">
+        <is>
+          <t>Austin, TX; Ingested</t>
+        </is>
+      </c>
+      <c r="C103" s="19" t="inlineStr">
+        <is>
+          <t>Austin, TX (162); Ingested</t>
         </is>
       </c>
       <c r="D103" s="25" t="inlineStr">
@@ -6197,9 +6197,9 @@
           <t>Peniche; Ingested — 75 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E104" s="22" t="inlineStr">
-        <is>
-          <t>North Stradbroke Is.; Digital — abstract book held, queued for extraction</t>
+      <c r="E104" s="19" t="inlineStr">
+        <is>
+          <t>North Stradbroke Is.; Ingested — 40 abstracts, 40 with bodies</t>
         </is>
       </c>
       <c r="F104" s="19" t="inlineStr">
@@ -6250,9 +6250,9 @@
           <t>Rende; Ingested — 136 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E105" s="22" t="inlineStr">
-        <is>
-          <t>Dunedin, New Zealand; Digital — abstract book held, queued for extraction</t>
+      <c r="E105" s="19" t="inlineStr">
+        <is>
+          <t>Dunedin, New Zealand; Ingested — 211 abstracts, 209 with bodies; joint meeting, elasmo flagged per abstract</t>
         </is>
       </c>
       <c r="F105" s="18" t="inlineStr"/>
@@ -6499,9 +6499,9 @@
           <t>Thessaloniki; Digital — clean abstract book received from Cat 2026-08-27; queued for extraction</t>
         </is>
       </c>
-      <c r="E110" s="22" t="inlineStr">
-        <is>
-          <t>Geelong; Digital — abstract book held, queued for extraction</t>
+      <c r="E110" s="19" t="inlineStr">
+        <is>
+          <t>Geelong; Ingested — 63 abstracts, 60 with bodies</t>
         </is>
       </c>
       <c r="F110" s="18" t="inlineStr"/>
@@ -6854,19 +6854,19 @@
         <v>1998</v>
       </c>
       <c r="B10" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>334</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -7036,19 +7036,19 @@
         <v>2005</v>
       </c>
       <c r="B17" t="n">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="C17" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>342</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -7088,19 +7088,19 @@
         <v>2007</v>
       </c>
       <c r="B19" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>422</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>294</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -7114,19 +7114,19 @@
         <v>2008</v>
       </c>
       <c r="B20" t="n">
-        <v>193</v>
+        <v>126</v>
       </c>
       <c r="C20" t="n">
-        <v>312</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>188</v>
+        <v>13</v>
       </c>
       <c r="E20" t="n">
         <v>22</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -7140,19 +7140,19 @@
         <v>2009</v>
       </c>
       <c r="B21" t="n">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="C21" t="n">
-        <v>510</v>
+        <v>23</v>
       </c>
       <c r="D21" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>39</v>
       </c>
       <c r="F21" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -7166,19 +7166,19 @@
         <v>2010</v>
       </c>
       <c r="B22" t="n">
-        <v>167</v>
+        <v>115</v>
       </c>
       <c r="C22" t="n">
-        <v>348</v>
+        <v>38</v>
       </c>
       <c r="D22" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>28</v>
       </c>
       <c r="F22" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -7221,7 +7221,7 @@
         <v>62</v>
       </c>
       <c r="C24" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D24" t="n">
         <v>239</v>
@@ -7270,19 +7270,19 @@
         <v>2014</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G26" t="n">
         <v>61</v>
@@ -7296,19 +7296,19 @@
         <v>2015</v>
       </c>
       <c r="B27" t="n">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="C27" t="n">
-        <v>311</v>
+        <v>76</v>
       </c>
       <c r="D27" t="n">
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>86</v>
@@ -7322,19 +7322,19 @@
         <v>2016</v>
       </c>
       <c r="B28" t="n">
-        <v>231</v>
+        <v>162</v>
       </c>
       <c r="C28" t="n">
-        <v>441</v>
+        <v>137</v>
       </c>
       <c r="D28" t="n">
-        <v>261</v>
+        <v>39</v>
       </c>
       <c r="E28" t="n">
         <v>97</v>
       </c>
       <c r="F28" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G28" t="n">
         <v>93</v>
@@ -7348,19 +7348,19 @@
         <v>2017</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G29" t="n">
         <v>62</v>
@@ -7374,19 +7374,19 @@
         <v>2018</v>
       </c>
       <c r="B30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>291</v>
+        <v>130</v>
       </c>
       <c r="D30" t="n">
-        <v>186</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
         <v>89</v>
       </c>
       <c r="F30" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G30" t="n">
         <v>75</v>
@@ -7400,19 +7400,19 @@
         <v>2019</v>
       </c>
       <c r="B31" t="n">
-        <v>166</v>
+        <v>114</v>
       </c>
       <c r="C31" t="n">
-        <v>342</v>
+        <v>164</v>
       </c>
       <c r="D31" t="n">
-        <v>170</v>
+        <v>5</v>
       </c>
       <c r="E31" t="n">
         <v>74</v>
       </c>
       <c r="F31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G31" t="n">
         <v>136</v>
@@ -7504,19 +7504,19 @@
         <v>2023</v>
       </c>
       <c r="B35" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
         <v>98</v>
@@ -7530,19 +7530,19 @@
         <v>2024</v>
       </c>
       <c r="B36" t="n">
-        <v>148</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>96</v>
@@ -7610,19 +7610,19 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>3142</v>
+        <v>2511</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>5976</v>
+        <v>2624</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>3302</v>
+        <v>839</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>715</v>
+        <v>858</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="G39" s="1" t="n">
         <v>956</v>
@@ -7660,13 +7660,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C43" t="n">
         <v>42</v>
       </c>
       <c r="D43" t="n">
-        <v>78.59999999999999</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="44">
@@ -7692,13 +7692,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C45" t="n">
         <v>15</v>
       </c>
       <c r="D45" t="n">
-        <v>26.7</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="46">

--- a/database/conference_coverage_matrix.xlsx
+++ b/database/conference_coverage_matrix.xlsx
@@ -48,7 +48,7 @@
       <i val="1"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -97,6 +97,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00A2C4C9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="006AA84F"/>
       </patternFill>
     </fill>
@@ -132,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -144,6 +149,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -154,7 +160,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -164,7 +170,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -177,6 +183,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1115,7 +1124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1246,12 +1255,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ingested</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fully extracted and merged into the database. Done.</t>
+          <t>DELIBERATELY incomplete. A general-ichthyology volume where only the pages naming an elasmobranch (and the page after each) were sent for extraction, so its teleost abstracts are NOT in the database. The count is real; the coverage is not comparable to a full ingest. Applies to IPFC 2009 and 2023.</t>
         </is>
       </c>
       <c r="C10" s="10" t="n"/>
@@ -1259,68 +1268,81 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>- 'ASIH/JMIH' = the American joint meeting (ASIH pre-1997, JMIH from 1997). ASIH/JMIH/HL/SSAR/NIA share one source book, collapsed to this column to remove duplicates.</t>
-        </is>
-      </c>
+          <t>Ingested</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fully extracted and merged into the database. Done.</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>- 'AES' (American Elasmobranch Society, founded 1983) kept separate — cell shows elasmo-abstract count where ingested. Pre-1983 = no conference (blank).</t>
+          <t>- 'ASIH/JMIH' = the American joint meeting (ASIH pre-1997, JMIH from 1997). ASIH/JMIH/HL/SSAR/NIA share one source book, collapsed to this column to remove duplicates.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>- Host cities 1916-2025 from github.com/SimonDedman/AESconfLocations; 2026 = New Orleans.</t>
+          <t>- 'AES' (American Elasmobranch Society, founded 1983) kept separate — cell shows elasmo-abstract count where ingested. Pre-1983 = no conference (blank).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>- 'OCR' = degraded 1997-2004 JMIH phone-photo scans (all needs_review); Carylanne's flatbed re-scans would upgrade the non-AES content.</t>
+          <t>- Host cities 1916-2025 from github.com/SimonDedman/AESconfLocations; 2026 = New Orleans.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>- AES 1985-2005: full abstracts harvested from elasmo.org/meetings/abstracts/abst&lt;YYYY&gt;/ (1,305 abstracts, 2026-08-25); JMIH-book copies of the same AES talks were removed. No AES source found for 1983-84 or 2006+ online.</t>
+          <t>- 'OCR' = degraded 1997-2004 JMIH phone-photo scans (all needs_review); Carylanne's flatbed re-scans would upgrade the non-AES content.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>- ASIH/JMIH pre-1992: Carylanne's archive starts 1992 → host city shown but 'Missing'.</t>
+          <t>- AES 1985-2005: full abstracts harvested from elasmo.org/meetings/abstracts/abst&lt;YYYY&gt;/ (1,305 abstracts, 2026-08-25); JMIH-book copies of the same AES talks were removed. No AES source found for 1983-84 or 2006+ online.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>- EEA from Cat Gordon (Shark Trust). 2004-2019 + 2023 ingested via Fable and merged 2026-08-25. Received 2026-08-27: 2002 Cardiff booklet, a clean 2024 Thessaloniki book, and the full SI2022 Valencia abstract book (all queued for extraction). 2025 Rotterdam abstract book is still a corrupt file. Cat holds hardcopies of 2010/2012/2015/2017 but has no scanning capacity, so those are being sought digitally from the host groups; Ali Hood is searching her paperwork for 2003-2009. EEA began in 1997 (2002 Cardiff was the 6th).</t>
+          <t>- ASIH/JMIH pre-1992: Carylanne's archive starts 1992 → host city shown but 'Missing'.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>- OCS (Oceania Chondrichthyan Soc, ~2011+, biennial): Brit Finucci collating, pending council — years/locations TBC.</t>
+          <t>- EEA from Cat Gordon (Shark Trust). 2004-2019 + 2023 ingested via Fable and merged 2026-08-25. Received 2026-08-27: 2002 Cardiff booklet, a clean 2024 Thessaloniki book, and the full SI2022 Valencia abstract book (all queued for extraction). 2025 Rotterdam abstract book is still a corrupt file. Cat holds hardcopies of 2010/2012/2015/2017 but has no scanning capacity, so those are being sought digitally from the host groups; Ali Hood is searching her paperwork for 2003-2009. EEA began in 1997 (2002 Cardiff was the 6th).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>- Blank/unshaded cell = no conference that year for that series.</t>
+          <t>- OCS (Oceania Chondrichthyan Soc, ~2011+, biennial): Brit Finucci collating, pending council — years/locations TBC.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
+        <is>
+          <t>- Blank/unshaded cell = no conference that year for that series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>- Per-society counts &amp; trends: see the Dashboard tab.</t>
         </is>
@@ -1351,797 +1373,797 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>series</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>year_from</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>year_to</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>n_needed</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="12" t="inlineStr">
         <is>
           <t>organisers</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="12" t="inlineStr">
         <is>
           <t>contact</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>ASIH / JMIH</t>
         </is>
       </c>
-      <c r="B2" s="12" t="n">
+      <c r="B2" s="13" t="n">
         <v>1913</v>
       </c>
-      <c r="C2" s="12" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>ongoing</t>
         </is>
       </c>
-      <c r="D2" s="12" t="n">
+      <c r="D2" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>n/a — counted under AES</t>
         </is>
       </c>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>Programme officers: Maureen 'Mo' Donnelly (to ~2014), Marty Crump (2015-2019), David M. Green (2020- ). Meeting planned by the MMPC (chairs Ed Heist, then Henry Mushinsky); logistics by Kansas State Conference Management Services. Submissions run on Oxford Abstracts.</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>https://www.asih.org/meetings/recent-meetings (abstract books, 2005 on)</t>
         </is>
       </c>
-      <c r="H2" s="13" t="inlineStr">
+      <c r="H2" s="14" t="inlineStr">
         <is>
           <t>david.m.green@mcgill.ca</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>American Elasmobranch Society (AES)</t>
         </is>
       </c>
-      <c r="B3" s="12" t="n">
+      <c r="B3" s="13" t="n">
         <v>1985</v>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>ongoing</t>
         </is>
       </c>
-      <c r="D3" s="12" t="n">
+      <c r="D3" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="12" t="n">
+      <c r="E3" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="F3" s="14" t="inlineStr">
         <is>
           <t>AES officers; meets inside JMIH, so the JMIH programme officer holds the abstracts. EXCEPTION 2018: AES met at Sharks International instead.</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>https://elasmo.org/meetings/abstracts/abst&lt;YYYY&gt;/ — full abstracts with bodies for EVERY year 1985-2005 (404 for 1983-84 and 2006+); harvested</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="H3" s="14" t="inlineStr">
         <is>
           <t>via JMIH programme officer, david.m.green@mcgill.ca</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>European Elasmobranch Association (EEA)</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n">
+      <c r="B4" s="13" t="n">
         <v>1997</v>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>ongoing</t>
         </is>
       </c>
-      <c r="D4" s="12" t="n">
+      <c r="D4" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="E4" s="13" t="n">
         <v>192</v>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>EEA board. Ali Hood (Secretariat, Shark Trust); Cat Gordon (Shark Trust) holds/sources the abstract books. Host national society varies by year (IEG, GRIS, APECE, NEV ...).</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>http://eulasmo.org/ ; host cities per year at http://eulasmo.org/scientific-meetings</t>
         </is>
       </c>
-      <c r="H4" s="13" t="inlineStr">
+      <c r="H4" s="14" t="inlineStr">
         <is>
           <t>Cat Gordon / Ali Hood, Shark Trust</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Oceania Chondrichthyan Society (OCS)</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="13" t="n">
         <v>2005</v>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>ongoing</t>
         </is>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="13" t="n">
         <v>33</v>
       </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>OCS council. Brit Finucci (past president, and IUCN SSG Red List Authority Coordinator) is collating the series for us, with council approval. Meetings seen: 2008, 2011, 2012 (Adelaide, joint with ASFB), 2018, 2022 (virtual), 2024 Geelong, 2025 Mooloolaba (20th anniversary).</t>
         </is>
       </c>
-      <c r="G5" s="13" t="inlineStr">
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>https://www.oceaniasharks.org.au/</t>
         </is>
       </c>
-      <c r="H5" s="13" t="inlineStr">
+      <c r="H5" s="14" t="inlineStr">
         <is>
           <t>Brit Finucci</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Sharks International (SI)</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="13" t="n">
         <v>2010</v>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>ongoing</t>
         </is>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="13" t="n">
         <v>171</v>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>Rotating local host, and the SI 2018 book's executive and scientific committees carry the previous hosts forward, which is the best evidence available for who ran the early ones. 2010 CAIRNS (6-11 June, Rydges Esplanade Resort): no source names the host body. Michelle Heupel (AIMS / James Cook University) is the sole Australian on the 2018 committee, consistent with Simon's recollection of Heupel and Colin Simpfendorfer (also JCU) running it. TREAT AS LIKELY, NOT CONFIRMED. 2014 DURBAN (2-6 June): hosted by the KwaZulu-Natal Sharks Board, 169 orals + 52 posters, which matches the 170 records we want almost exactly. Geremy Cliff (Head of Research at the KZN Sharks Board for ~30 years) sits on the 2018 committee and is the obvious approach; Sabine Wintner (KZNSB / UKZN) is the other senior elasmobranch scientist there. No source names the committee chair. 2018 Joao Pessoa: UFPB, president Ricardo de Souza Rosa, joint with AES, SBEEL and Fundacion SQUALUS. 2022 Valencia. 2026 Colombo, hosted by Blue Resources Trust.</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>https://www.sharksinternational.org.br/noticia/23-abstract-book/menu_abstract_book.html (2018 book, which we hold)</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>sharksinternational2014@gmail.com (2014 organising committee, from the KZN Sharks Board announcement; likely dormant — go via Geremy Cliff or Sabine Wintner at the KZN Sharks Board for 2014, and Michelle Heupel or Colin Simpfendorfer for 2010)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Encuentro Colombiano sobre Condrictios (ECC)</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="13" t="n">
         <v>2008</v>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="13" t="n">
         <v>2018</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="13" t="n">
         <v>79</v>
       </c>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>Fundacion SQUALUS. I 2008 Bogota, II 2010 Cali, III 2012 Santa Marta, IV 2014 Medellin, V 2016 Bogota, VI 2018 Joao Pessoa. CONFIRMED 2026-09-04: the VI IS ALREADY HELD — the SI 2018 book is the joint book for four meetings at once (Sharks International, the 34th AES annual meeting, the X SBEEL Reuniao and the VI ECC), and we have its 427 abstracts. So the ask is editions I-V, and the corpus cites only the IV.</t>
         </is>
       </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>http://squalus.org/index.php/encuentro-condrictios/ ; https://encuentro.squalus.org</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>squalus@germanm1.sg-host.com (from the site; verify before using)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Sociedade Brasileira para o Estudo de Elasmobranquios (SBEEL)</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="13" t="n">
         <v>1997</v>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>ongoing</t>
         </is>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="13" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t>SBEEL. The X Reuniao was held in 2018 inside the Sharks International book, so at least nine earlier meetings exist. The corpus cites only the II, which is why n_needed is 1 — that number is a floor and badly understates this series.</t>
         </is>
       </c>
-      <c r="G8" s="13" t="inlineStr"/>
-      <c r="H8" s="13" t="inlineStr"/>
+      <c r="G8" s="14" t="inlineStr"/>
+      <c r="H8" s="14" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Simposio Nacional de Tiburones y Rayas (SOMEPEC, Mexico)</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="13" t="n">
         <v>2004</v>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>ongoing</t>
         </is>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="13" t="n">
         <v>44</v>
       </c>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t>Sociedad Mexicana de Peces Cartilaginosos (SOMEPEC). HARVESTED 2026-09-04 from somepec.org, no request to anyone needed: I 2004 (with the III Semana del Tiburon, UNAM), III 2008, IV 2010 (UNAM), VII 2016, XI 2025 as abstract books, plus the IX 2021 programme. All five books carry a clean text layer. STILL MISSING: II, V, VI 2014 Mazatlan (the edition our corpus cites), VIII 2019 Playa del Carmen (joint with the I Congreso Latinoamericano de Tiburones, Rayas y Quimeras), and X. Ask info@somepec.org for exactly those five.</t>
         </is>
       </c>
-      <c r="G9" s="13" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>https://somepec.org/memorias/ ; back volumes under https://somepec.org/wp-content/uploads/ ; scraper scripts/conf_abstracts/scrape_somepec.py</t>
         </is>
       </c>
-      <c r="H9" s="13" t="inlineStr">
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t>info@somepec.org ; +52 55 5034 1708</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Colloque international requins en Afrique de l'Ouest</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="13" t="n">
         <v>2011</v>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="13" t="n">
         <v>2011</v>
       </c>
-      <c r="D10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="12" t="n">
+      <c r="D10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="13" t="n">
         <v>48</v>
       </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr">
         <is>
           <t>Commission Sous-Regionale des Peches (CSRP / SRFC), an intergovernmental body for seven West African states. Dakar, Senegal, 25-27 July 2011, on the conservation and sustainable management of shark populations in West Africa. A single meeting, not a series — kept on the list anyway: 48 abstracts is one email and one book, and it is the only West African material in the corpus.</t>
         </is>
       </c>
-      <c r="G10" s="13" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>https://spcsrp.org/</t>
         </is>
       </c>
-      <c r="H10" s="13" t="inlineStr"/>
+      <c r="H10" s="14" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Gulf and Caribbean Fisheries Institute (GCFI)</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B11" s="13" t="n">
         <v>1948</v>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>ongoing</t>
         </is>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="F11" s="13" t="inlineStr">
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t>GCFI secretariat. Every meeting since 1948 is in the annual Proceedings and every PAPER is a free PDF at proceedings.gcfi.org (verified 2026-09-04), so nobody needs asking and nobody should be assigned these. The 31 corpus records were sitting on the needs-library queue and are now acquisition_route=gcfi_proceedings.</t>
         </is>
       </c>
-      <c r="G11" s="13" t="inlineStr">
+      <c r="G11" s="14" t="inlineStr">
         <is>
           <t>https://proceedings.gcfi.org/ (per-paper PDFs) ; https://www.gcfi.org/ ; back volumes also in the NOAA Institutional Repository</t>
         </is>
       </c>
-      <c r="H11" s="13" t="inlineStr"/>
+      <c r="H11" s="14" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Pacific Shark Workshop</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n">
+      <c r="B12" s="13" t="n">
         <v>2011</v>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C12" s="13" t="n">
         <v>2012</v>
       </c>
-      <c r="D12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="12" t="n">
+      <c r="D12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="F12" s="13" t="inlineStr"/>
-      <c r="G12" s="13" t="inlineStr"/>
-      <c r="H12" s="13" t="inlineStr"/>
+      <c r="F12" s="14" t="inlineStr"/>
+      <c r="G12" s="14" t="inlineStr"/>
+      <c r="H12" s="14" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>ISC Shark Working Group</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n">
+      <c r="B13" s="13" t="n">
         <v>2013</v>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>ongoing</t>
         </is>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D13" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E13" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="13" t="inlineStr">
+      <c r="F13" s="14" t="inlineStr">
         <is>
           <t>International Scientific Committee for Tuna and Tuna-like Species in the North Pacific Ocean; the Shark Working Group meets within it.</t>
         </is>
       </c>
-      <c r="G13" s="13" t="inlineStr">
+      <c r="G13" s="14" t="inlineStr">
         <is>
           <t>https://isc.fra.go.jp/</t>
         </is>
       </c>
-      <c r="H13" s="13" t="inlineStr"/>
+      <c r="H13" s="14" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>World Congress of Herpetology</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n">
+      <c r="B14" s="13" t="n">
         <v>1989</v>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>ongoing</t>
         </is>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="D14" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="E14" s="13" t="n">
         <v>101</v>
       </c>
-      <c r="F14" s="13" t="inlineStr">
+      <c r="F14" s="14" t="inlineStr">
         <is>
           <t>World Congress of Herpetology committee. Every 3-5 years.</t>
         </is>
       </c>
-      <c r="G14" s="13" t="inlineStr">
+      <c r="G14" s="14" t="inlineStr">
         <is>
           <t>https://www.worldcongressofherpetology.org/</t>
         </is>
       </c>
-      <c r="H14" s="13" t="inlineStr"/>
+      <c r="H14" s="14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Indo-Pacific Fish Conference (IPFC)</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n">
+      <c r="B15" s="13" t="n">
         <v>1981</v>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>ongoing</t>
         </is>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="D15" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="E15" s="13" t="n">
         <v>49</v>
       </c>
-      <c r="F15" s="13" t="inlineStr">
+      <c r="F15" s="14" t="inlineStr">
         <is>
           <t>Rotating host. IPFC-11 2023 Auckland (joint with ASFB); IPFC-12 2025 Taiwan.</t>
         </is>
       </c>
-      <c r="G15" s="13" t="inlineStr">
+      <c r="G15" s="14" t="inlineStr">
         <is>
           <t>https://sfi-cybium.fr/en/indo-pacific-fish-conference</t>
         </is>
       </c>
-      <c r="H15" s="13" t="inlineStr"/>
+      <c r="H15" s="14" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>International Coral Reef Symposium (ICRS)</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n">
+      <c r="B16" s="13" t="n">
         <v>1969</v>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>ongoing</t>
         </is>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="D16" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E16" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="F16" s="13" t="inlineStr">
+      <c r="F16" s="14" t="inlineStr">
         <is>
           <t>International Coral Reef Society. ICRS-16 2026 Auckland.</t>
         </is>
       </c>
-      <c r="G16" s="13" t="inlineStr">
+      <c r="G16" s="14" t="inlineStr">
         <is>
           <t>https://coralreefs.org/</t>
         </is>
       </c>
-      <c r="H16" s="13" t="inlineStr"/>
+      <c r="H16" s="14" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>World Fisheries Congress</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B17" s="13" t="n">
         <v>1992</v>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>ongoing</t>
         </is>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D17" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="F17" s="13" t="inlineStr"/>
-      <c r="G17" s="13" t="inlineStr"/>
-      <c r="H17" s="13" t="inlineStr"/>
+      <c r="F17" s="14" t="inlineStr"/>
+      <c r="G17" s="14" t="inlineStr"/>
+      <c r="H17" s="14" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>American Fisheries Society symposia</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n">
+      <c r="B18" s="13" t="n">
         <v>1871</v>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>ongoing</t>
         </is>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D18" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="E18" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="F18" s="13" t="inlineStr">
+      <c r="F18" s="14" t="inlineStr">
         <is>
           <t>American Fisheries Society.</t>
         </is>
       </c>
-      <c r="G18" s="13" t="inlineStr">
+      <c r="G18" s="14" t="inlineStr">
         <is>
           <t>https://fisheries.org/</t>
         </is>
       </c>
-      <c r="H18" s="13" t="inlineStr"/>
+      <c r="H18" s="14" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>International Congress on the Biology of Fish</t>
         </is>
       </c>
-      <c r="B19" s="12" t="n">
+      <c r="B19" s="13" t="n">
         <v>1994</v>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>ongoing</t>
         </is>
       </c>
-      <c r="D19" s="12" t="n">
+      <c r="D19" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="E19" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="F19" s="13" t="inlineStr"/>
-      <c r="G19" s="13" t="inlineStr"/>
-      <c r="H19" s="13" t="inlineStr"/>
+      <c r="F19" s="14" t="inlineStr"/>
+      <c r="G19" s="14" t="inlineStr"/>
+      <c r="H19" s="14" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>International Meeting on Mesozoic Fishes</t>
         </is>
       </c>
-      <c r="B20" s="12" t="n">
+      <c r="B20" s="13" t="n">
         <v>1993</v>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>ongoing</t>
         </is>
       </c>
-      <c r="D20" s="12" t="n">
+      <c r="D20" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="F20" s="13" t="inlineStr">
+      <c r="F20" s="14" t="inlineStr">
         <is>
           <t>Meeting conveners vary; 6th meeting edited by Schwarz &amp; Kriwet.</t>
         </is>
       </c>
-      <c r="G20" s="13" t="inlineStr"/>
-      <c r="H20" s="13" t="inlineStr"/>
+      <c r="G20" s="14" t="inlineStr"/>
+      <c r="H20" s="14" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>International Congress of Vertebrate Morphology (ICVM)</t>
         </is>
       </c>
-      <c r="B21" s="12" t="n">
+      <c r="B21" s="13" t="n">
         <v>1986</v>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>ongoing</t>
         </is>
       </c>
-      <c r="D21" s="12" t="n">
+      <c r="D21" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="E21" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="13" t="inlineStr"/>
-      <c r="G21" s="13" t="inlineStr"/>
-      <c r="H21" s="13" t="inlineStr"/>
+      <c r="F21" s="14" t="inlineStr"/>
+      <c r="G21" s="14" t="inlineStr"/>
+      <c r="H21" s="14" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>CIESM Congress (Mediterranean Science Commission)</t>
         </is>
       </c>
-      <c r="B22" s="12" t="n">
+      <c r="B22" s="13" t="n">
         <v>1919</v>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>ongoing</t>
         </is>
       </c>
-      <c r="D22" s="12" t="n">
+      <c r="D22" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="13" t="inlineStr">
+      <c r="F22" s="14" t="inlineStr">
         <is>
           <t>Commission Internationale pour l'Exploration Scientifique de la Mer Mediterranee.</t>
         </is>
       </c>
-      <c r="G22" s="13" t="inlineStr">
+      <c r="G22" s="14" t="inlineStr">
         <is>
           <t>https://ciesm.org/</t>
         </is>
       </c>
-      <c r="H22" s="13" t="inlineStr"/>
+      <c r="H22" s="14" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Albert L. Tester Memorial Symposium</t>
         </is>
       </c>
-      <c r="B23" s="12" t="n">
+      <c r="B23" s="13" t="n">
         <v>1976</v>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>ongoing</t>
         </is>
       </c>
-      <c r="D23" s="12" t="n">
+      <c r="D23" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="E23" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F23" s="13" t="inlineStr">
+      <c r="F23" s="14" t="inlineStr">
         <is>
           <t>University of Hawaii at Manoa.</t>
         </is>
       </c>
-      <c r="G23" s="13" t="inlineStr"/>
-      <c r="H23" s="13" t="inlineStr"/>
+      <c r="G23" s="14" t="inlineStr"/>
+      <c r="H23" s="14" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>Workshop on Age Determination of Oceanic Pelagic Fishes</t>
         </is>
       </c>
-      <c r="B24" s="12" t="n">
+      <c r="B24" s="13" t="n">
         <v>1983</v>
       </c>
-      <c r="C24" s="12" t="n">
+      <c r="C24" s="13" t="n">
         <v>1983</v>
       </c>
-      <c r="D24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="12" t="n">
+      <c r="D24" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="F24" s="13" t="inlineStr"/>
-      <c r="G24" s="13" t="inlineStr"/>
-      <c r="H24" s="13" t="inlineStr"/>
+      <c r="F24" s="14" t="inlineStr"/>
+      <c r="G24" s="14" t="inlineStr"/>
+      <c r="H24" s="14" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>Palaeontology / geology meetings (assorted)</t>
         </is>
       </c>
-      <c r="B25" s="12" t="n">
+      <c r="B25" s="13" t="n">
         <v>1973</v>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="13" t="inlineStr">
         <is>
           <t>ongoing</t>
         </is>
       </c>
-      <c r="D25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="12" t="n">
+      <c r="D25" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="13" t="n">
         <v>81</v>
       </c>
-      <c r="F25" s="13" t="inlineStr">
+      <c r="F25" s="14" t="inlineStr">
         <is>
           <t>NOT ONE SERIES — a bucket of many national and international palaeo and geology meetings. Split it before chasing anyone.</t>
         </is>
       </c>
-      <c r="G25" s="13" t="inlineStr"/>
-      <c r="H25" s="13" t="inlineStr"/>
+      <c r="G25" s="14" t="inlineStr"/>
+      <c r="H25" s="14" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>frequency: 1 = annual, 2 = biennial, 3 = every three years, 4 = every four years, 0 = one-off / irregular</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>n_needed: corpus records citing that series whose PDF we do NOT hold (scripts/conf_abstracts/conference_lead_candidates.py). It counts abstracts we can already name, so it is a floor, not the size of the series.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>A BLANK organisers/website/contact means not found on 2026-09-04, never a guess — a wrong address costs a real email to a real person.</t>
         </is>
@@ -2190,4442 +2212,4450 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>ASIH/JMIH</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>AES</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>EEA</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>OCS</t>
         </is>
       </c>
-      <c r="F1" s="15" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G1" s="15" t="inlineStr">
+      <c r="G1" s="16" t="inlineStr">
         <is>
           <t>ECC</t>
         </is>
       </c>
-      <c r="H1" s="15" t="inlineStr">
+      <c r="H1" s="16" t="inlineStr">
         <is>
           <t>SBEEL</t>
         </is>
       </c>
-      <c r="I1" s="15" t="inlineStr">
+      <c r="I1" s="16" t="inlineStr">
         <is>
           <t>SOMEPEC</t>
         </is>
       </c>
-      <c r="J1" s="15" t="inlineStr">
+      <c r="J1" s="16" t="inlineStr">
         <is>
           <t>W Africa</t>
         </is>
       </c>
-      <c r="K1" s="15" t="inlineStr">
+      <c r="K1" s="16" t="inlineStr">
         <is>
           <t>GCFI</t>
         </is>
       </c>
-      <c r="L1" s="15" t="inlineStr">
+      <c r="L1" s="16" t="inlineStr">
         <is>
           <t>Pac Shark Wksp</t>
         </is>
       </c>
-      <c r="M1" s="15" t="inlineStr">
+      <c r="M1" s="16" t="inlineStr">
         <is>
           <t>ISC Shark WG</t>
         </is>
       </c>
-      <c r="N1" s="15" t="inlineStr">
+      <c r="N1" s="16" t="inlineStr">
         <is>
           <t>WCH</t>
         </is>
       </c>
-      <c r="O1" s="15" t="inlineStr">
+      <c r="O1" s="16" t="inlineStr">
         <is>
           <t>IPFC</t>
         </is>
       </c>
-      <c r="P1" s="15" t="inlineStr">
+      <c r="P1" s="16" t="inlineStr">
         <is>
           <t>ICRS</t>
         </is>
       </c>
-      <c r="Q1" s="15" t="inlineStr">
+      <c r="Q1" s="16" t="inlineStr">
         <is>
           <t>WFC</t>
         </is>
       </c>
-      <c r="R1" s="15" t="inlineStr">
+      <c r="R1" s="16" t="inlineStr">
         <is>
           <t>AFS</t>
         </is>
       </c>
-      <c r="S1" s="15" t="inlineStr">
+      <c r="S1" s="16" t="inlineStr">
         <is>
           <t>ICBF</t>
         </is>
       </c>
-      <c r="T1" s="15" t="inlineStr">
+      <c r="T1" s="16" t="inlineStr">
         <is>
           <t>Mesozoic Fishes</t>
         </is>
       </c>
-      <c r="U1" s="15" t="inlineStr">
+      <c r="U1" s="16" t="inlineStr">
         <is>
           <t>ICVM</t>
         </is>
       </c>
-      <c r="V1" s="15" t="inlineStr">
+      <c r="V1" s="16" t="inlineStr">
         <is>
           <t>CIESM</t>
         </is>
       </c>
-      <c r="W1" s="15" t="inlineStr">
+      <c r="W1" s="16" t="inlineStr">
         <is>
           <t>Tester Symp</t>
         </is>
       </c>
-      <c r="X1" s="15" t="inlineStr">
+      <c r="X1" s="16" t="inlineStr">
         <is>
           <t>Age Det Wksp</t>
         </is>
       </c>
-      <c r="Y1" s="15" t="inlineStr">
+      <c r="Y1" s="16" t="inlineStr">
         <is>
           <t>Palaeo/geol</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="n">
+      <c r="A2" s="17" t="n">
         <v>1916</v>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>New York, NY; Missing</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr"/>
-      <c r="D2" s="18" t="inlineStr"/>
-      <c r="E2" s="18" t="inlineStr"/>
-      <c r="F2" s="18" t="inlineStr"/>
-      <c r="G2" s="18" t="inlineStr"/>
-      <c r="H2" s="18" t="inlineStr"/>
-      <c r="I2" s="18" t="inlineStr"/>
-      <c r="J2" s="18" t="inlineStr"/>
-      <c r="K2" s="18" t="inlineStr"/>
-      <c r="L2" s="18" t="inlineStr"/>
-      <c r="M2" s="18" t="inlineStr"/>
-      <c r="N2" s="18" t="inlineStr"/>
-      <c r="O2" s="18" t="inlineStr"/>
-      <c r="P2" s="18" t="inlineStr"/>
-      <c r="Q2" s="18" t="inlineStr"/>
-      <c r="R2" s="18" t="inlineStr"/>
-      <c r="S2" s="18" t="inlineStr"/>
-      <c r="T2" s="18" t="inlineStr"/>
-      <c r="U2" s="18" t="inlineStr"/>
-      <c r="V2" s="18" t="inlineStr"/>
-      <c r="W2" s="18" t="inlineStr"/>
-      <c r="X2" s="18" t="inlineStr"/>
-      <c r="Y2" s="18" t="inlineStr"/>
+      <c r="C2" s="19" t="inlineStr"/>
+      <c r="D2" s="19" t="inlineStr"/>
+      <c r="E2" s="19" t="inlineStr"/>
+      <c r="F2" s="19" t="inlineStr"/>
+      <c r="G2" s="19" t="inlineStr"/>
+      <c r="H2" s="19" t="inlineStr"/>
+      <c r="I2" s="19" t="inlineStr"/>
+      <c r="J2" s="19" t="inlineStr"/>
+      <c r="K2" s="19" t="inlineStr"/>
+      <c r="L2" s="19" t="inlineStr"/>
+      <c r="M2" s="19" t="inlineStr"/>
+      <c r="N2" s="19" t="inlineStr"/>
+      <c r="O2" s="19" t="inlineStr"/>
+      <c r="P2" s="19" t="inlineStr"/>
+      <c r="Q2" s="19" t="inlineStr"/>
+      <c r="R2" s="19" t="inlineStr"/>
+      <c r="S2" s="19" t="inlineStr"/>
+      <c r="T2" s="19" t="inlineStr"/>
+      <c r="U2" s="19" t="inlineStr"/>
+      <c r="V2" s="19" t="inlineStr"/>
+      <c r="W2" s="19" t="inlineStr"/>
+      <c r="X2" s="19" t="inlineStr"/>
+      <c r="Y2" s="19" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="n">
+      <c r="A3" s="17" t="n">
         <v>1917</v>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Cambridge, MA; Missing</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr"/>
-      <c r="D3" s="18" t="inlineStr"/>
-      <c r="E3" s="18" t="inlineStr"/>
-      <c r="F3" s="18" t="inlineStr"/>
-      <c r="G3" s="18" t="inlineStr"/>
-      <c r="H3" s="18" t="inlineStr"/>
-      <c r="I3" s="18" t="inlineStr"/>
-      <c r="J3" s="18" t="inlineStr"/>
-      <c r="K3" s="18" t="inlineStr"/>
-      <c r="L3" s="18" t="inlineStr"/>
-      <c r="M3" s="18" t="inlineStr"/>
-      <c r="N3" s="18" t="inlineStr"/>
-      <c r="O3" s="18" t="inlineStr"/>
-      <c r="P3" s="18" t="inlineStr"/>
-      <c r="Q3" s="18" t="inlineStr"/>
-      <c r="R3" s="18" t="inlineStr"/>
-      <c r="S3" s="18" t="inlineStr"/>
-      <c r="T3" s="18" t="inlineStr"/>
-      <c r="U3" s="18" t="inlineStr"/>
-      <c r="V3" s="18" t="inlineStr"/>
-      <c r="W3" s="18" t="inlineStr"/>
-      <c r="X3" s="18" t="inlineStr"/>
-      <c r="Y3" s="18" t="inlineStr"/>
+      <c r="C3" s="19" t="inlineStr"/>
+      <c r="D3" s="19" t="inlineStr"/>
+      <c r="E3" s="19" t="inlineStr"/>
+      <c r="F3" s="19" t="inlineStr"/>
+      <c r="G3" s="19" t="inlineStr"/>
+      <c r="H3" s="19" t="inlineStr"/>
+      <c r="I3" s="19" t="inlineStr"/>
+      <c r="J3" s="19" t="inlineStr"/>
+      <c r="K3" s="19" t="inlineStr"/>
+      <c r="L3" s="19" t="inlineStr"/>
+      <c r="M3" s="19" t="inlineStr"/>
+      <c r="N3" s="19" t="inlineStr"/>
+      <c r="O3" s="19" t="inlineStr"/>
+      <c r="P3" s="19" t="inlineStr"/>
+      <c r="Q3" s="19" t="inlineStr"/>
+      <c r="R3" s="19" t="inlineStr"/>
+      <c r="S3" s="19" t="inlineStr"/>
+      <c r="T3" s="19" t="inlineStr"/>
+      <c r="U3" s="19" t="inlineStr"/>
+      <c r="V3" s="19" t="inlineStr"/>
+      <c r="W3" s="19" t="inlineStr"/>
+      <c r="X3" s="19" t="inlineStr"/>
+      <c r="Y3" s="19" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="n">
+      <c r="A4" s="17" t="n">
         <v>1918</v>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>Brooklyn, NY; Missing</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr"/>
-      <c r="D4" s="18" t="inlineStr"/>
-      <c r="E4" s="18" t="inlineStr"/>
-      <c r="F4" s="18" t="inlineStr"/>
-      <c r="G4" s="18" t="inlineStr"/>
-      <c r="H4" s="18" t="inlineStr"/>
-      <c r="I4" s="18" t="inlineStr"/>
-      <c r="J4" s="18" t="inlineStr"/>
-      <c r="K4" s="18" t="inlineStr"/>
-      <c r="L4" s="18" t="inlineStr"/>
-      <c r="M4" s="18" t="inlineStr"/>
-      <c r="N4" s="18" t="inlineStr"/>
-      <c r="O4" s="18" t="inlineStr"/>
-      <c r="P4" s="18" t="inlineStr"/>
-      <c r="Q4" s="18" t="inlineStr"/>
-      <c r="R4" s="18" t="inlineStr"/>
-      <c r="S4" s="18" t="inlineStr"/>
-      <c r="T4" s="18" t="inlineStr"/>
-      <c r="U4" s="18" t="inlineStr"/>
-      <c r="V4" s="18" t="inlineStr"/>
-      <c r="W4" s="18" t="inlineStr"/>
-      <c r="X4" s="18" t="inlineStr"/>
-      <c r="Y4" s="18" t="inlineStr"/>
+      <c r="C4" s="19" t="inlineStr"/>
+      <c r="D4" s="19" t="inlineStr"/>
+      <c r="E4" s="19" t="inlineStr"/>
+      <c r="F4" s="19" t="inlineStr"/>
+      <c r="G4" s="19" t="inlineStr"/>
+      <c r="H4" s="19" t="inlineStr"/>
+      <c r="I4" s="19" t="inlineStr"/>
+      <c r="J4" s="19" t="inlineStr"/>
+      <c r="K4" s="19" t="inlineStr"/>
+      <c r="L4" s="19" t="inlineStr"/>
+      <c r="M4" s="19" t="inlineStr"/>
+      <c r="N4" s="19" t="inlineStr"/>
+      <c r="O4" s="19" t="inlineStr"/>
+      <c r="P4" s="19" t="inlineStr"/>
+      <c r="Q4" s="19" t="inlineStr"/>
+      <c r="R4" s="19" t="inlineStr"/>
+      <c r="S4" s="19" t="inlineStr"/>
+      <c r="T4" s="19" t="inlineStr"/>
+      <c r="U4" s="19" t="inlineStr"/>
+      <c r="V4" s="19" t="inlineStr"/>
+      <c r="W4" s="19" t="inlineStr"/>
+      <c r="X4" s="19" t="inlineStr"/>
+      <c r="Y4" s="19" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n">
+      <c r="A5" s="17" t="n">
         <v>1919</v>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>?; Missing</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr"/>
-      <c r="D5" s="18" t="inlineStr"/>
-      <c r="E5" s="18" t="inlineStr"/>
-      <c r="F5" s="18" t="inlineStr"/>
-      <c r="G5" s="18" t="inlineStr"/>
-      <c r="H5" s="18" t="inlineStr"/>
-      <c r="I5" s="18" t="inlineStr"/>
-      <c r="J5" s="18" t="inlineStr"/>
-      <c r="K5" s="18" t="inlineStr"/>
-      <c r="L5" s="18" t="inlineStr"/>
-      <c r="M5" s="18" t="inlineStr"/>
-      <c r="N5" s="18" t="inlineStr"/>
-      <c r="O5" s="18" t="inlineStr"/>
-      <c r="P5" s="18" t="inlineStr"/>
-      <c r="Q5" s="18" t="inlineStr"/>
-      <c r="R5" s="18" t="inlineStr"/>
-      <c r="S5" s="18" t="inlineStr"/>
-      <c r="T5" s="18" t="inlineStr"/>
-      <c r="U5" s="18" t="inlineStr"/>
-      <c r="V5" s="18" t="inlineStr"/>
-      <c r="W5" s="18" t="inlineStr"/>
-      <c r="X5" s="18" t="inlineStr"/>
-      <c r="Y5" s="18" t="inlineStr"/>
+      <c r="C5" s="19" t="inlineStr"/>
+      <c r="D5" s="19" t="inlineStr"/>
+      <c r="E5" s="19" t="inlineStr"/>
+      <c r="F5" s="19" t="inlineStr"/>
+      <c r="G5" s="19" t="inlineStr"/>
+      <c r="H5" s="19" t="inlineStr"/>
+      <c r="I5" s="19" t="inlineStr"/>
+      <c r="J5" s="19" t="inlineStr"/>
+      <c r="K5" s="19" t="inlineStr"/>
+      <c r="L5" s="19" t="inlineStr"/>
+      <c r="M5" s="19" t="inlineStr"/>
+      <c r="N5" s="19" t="inlineStr"/>
+      <c r="O5" s="19" t="inlineStr"/>
+      <c r="P5" s="19" t="inlineStr"/>
+      <c r="Q5" s="19" t="inlineStr"/>
+      <c r="R5" s="19" t="inlineStr"/>
+      <c r="S5" s="19" t="inlineStr"/>
+      <c r="T5" s="19" t="inlineStr"/>
+      <c r="U5" s="19" t="inlineStr"/>
+      <c r="V5" s="19" t="inlineStr"/>
+      <c r="W5" s="19" t="inlineStr"/>
+      <c r="X5" s="19" t="inlineStr"/>
+      <c r="Y5" s="19" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="n">
+      <c r="A6" s="17" t="n">
         <v>1920</v>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>Washington, DC; Missing</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr"/>
-      <c r="D6" s="18" t="inlineStr"/>
-      <c r="E6" s="18" t="inlineStr"/>
-      <c r="F6" s="18" t="inlineStr"/>
-      <c r="G6" s="18" t="inlineStr"/>
-      <c r="H6" s="18" t="inlineStr"/>
-      <c r="I6" s="18" t="inlineStr"/>
-      <c r="J6" s="18" t="inlineStr"/>
-      <c r="K6" s="18" t="inlineStr"/>
-      <c r="L6" s="18" t="inlineStr"/>
-      <c r="M6" s="18" t="inlineStr"/>
-      <c r="N6" s="18" t="inlineStr"/>
-      <c r="O6" s="18" t="inlineStr"/>
-      <c r="P6" s="18" t="inlineStr"/>
-      <c r="Q6" s="18" t="inlineStr"/>
-      <c r="R6" s="18" t="inlineStr"/>
-      <c r="S6" s="18" t="inlineStr"/>
-      <c r="T6" s="18" t="inlineStr"/>
-      <c r="U6" s="18" t="inlineStr"/>
-      <c r="V6" s="18" t="inlineStr"/>
-      <c r="W6" s="18" t="inlineStr"/>
-      <c r="X6" s="18" t="inlineStr"/>
-      <c r="Y6" s="18" t="inlineStr"/>
+      <c r="C6" s="19" t="inlineStr"/>
+      <c r="D6" s="19" t="inlineStr"/>
+      <c r="E6" s="19" t="inlineStr"/>
+      <c r="F6" s="19" t="inlineStr"/>
+      <c r="G6" s="19" t="inlineStr"/>
+      <c r="H6" s="19" t="inlineStr"/>
+      <c r="I6" s="19" t="inlineStr"/>
+      <c r="J6" s="19" t="inlineStr"/>
+      <c r="K6" s="19" t="inlineStr"/>
+      <c r="L6" s="19" t="inlineStr"/>
+      <c r="M6" s="19" t="inlineStr"/>
+      <c r="N6" s="19" t="inlineStr"/>
+      <c r="O6" s="19" t="inlineStr"/>
+      <c r="P6" s="19" t="inlineStr"/>
+      <c r="Q6" s="19" t="inlineStr"/>
+      <c r="R6" s="19" t="inlineStr"/>
+      <c r="S6" s="19" t="inlineStr"/>
+      <c r="T6" s="19" t="inlineStr"/>
+      <c r="U6" s="19" t="inlineStr"/>
+      <c r="V6" s="19" t="inlineStr"/>
+      <c r="W6" s="19" t="inlineStr"/>
+      <c r="X6" s="19" t="inlineStr"/>
+      <c r="Y6" s="19" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="n">
+      <c r="A7" s="17" t="n">
         <v>1921</v>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>Philadelphia, PA; Missing</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr"/>
-      <c r="D7" s="18" t="inlineStr"/>
-      <c r="E7" s="18" t="inlineStr"/>
-      <c r="F7" s="18" t="inlineStr"/>
-      <c r="G7" s="18" t="inlineStr"/>
-      <c r="H7" s="18" t="inlineStr"/>
-      <c r="I7" s="18" t="inlineStr"/>
-      <c r="J7" s="18" t="inlineStr"/>
-      <c r="K7" s="18" t="inlineStr"/>
-      <c r="L7" s="18" t="inlineStr"/>
-      <c r="M7" s="18" t="inlineStr"/>
-      <c r="N7" s="18" t="inlineStr"/>
-      <c r="O7" s="18" t="inlineStr"/>
-      <c r="P7" s="18" t="inlineStr"/>
-      <c r="Q7" s="18" t="inlineStr"/>
-      <c r="R7" s="18" t="inlineStr"/>
-      <c r="S7" s="18" t="inlineStr"/>
-      <c r="T7" s="18" t="inlineStr"/>
-      <c r="U7" s="18" t="inlineStr"/>
-      <c r="V7" s="18" t="inlineStr"/>
-      <c r="W7" s="18" t="inlineStr"/>
-      <c r="X7" s="18" t="inlineStr"/>
-      <c r="Y7" s="18" t="inlineStr"/>
+      <c r="C7" s="19" t="inlineStr"/>
+      <c r="D7" s="19" t="inlineStr"/>
+      <c r="E7" s="19" t="inlineStr"/>
+      <c r="F7" s="19" t="inlineStr"/>
+      <c r="G7" s="19" t="inlineStr"/>
+      <c r="H7" s="19" t="inlineStr"/>
+      <c r="I7" s="19" t="inlineStr"/>
+      <c r="J7" s="19" t="inlineStr"/>
+      <c r="K7" s="19" t="inlineStr"/>
+      <c r="L7" s="19" t="inlineStr"/>
+      <c r="M7" s="19" t="inlineStr"/>
+      <c r="N7" s="19" t="inlineStr"/>
+      <c r="O7" s="19" t="inlineStr"/>
+      <c r="P7" s="19" t="inlineStr"/>
+      <c r="Q7" s="19" t="inlineStr"/>
+      <c r="R7" s="19" t="inlineStr"/>
+      <c r="S7" s="19" t="inlineStr"/>
+      <c r="T7" s="19" t="inlineStr"/>
+      <c r="U7" s="19" t="inlineStr"/>
+      <c r="V7" s="19" t="inlineStr"/>
+      <c r="W7" s="19" t="inlineStr"/>
+      <c r="X7" s="19" t="inlineStr"/>
+      <c r="Y7" s="19" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="n">
+      <c r="A8" s="17" t="n">
         <v>1922</v>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Chicago, IL; Missing</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr"/>
-      <c r="D8" s="18" t="inlineStr"/>
-      <c r="E8" s="18" t="inlineStr"/>
-      <c r="F8" s="18" t="inlineStr"/>
-      <c r="G8" s="18" t="inlineStr"/>
-      <c r="H8" s="18" t="inlineStr"/>
-      <c r="I8" s="18" t="inlineStr"/>
-      <c r="J8" s="18" t="inlineStr"/>
-      <c r="K8" s="18" t="inlineStr"/>
-      <c r="L8" s="18" t="inlineStr"/>
-      <c r="M8" s="18" t="inlineStr"/>
-      <c r="N8" s="18" t="inlineStr"/>
-      <c r="O8" s="18" t="inlineStr"/>
-      <c r="P8" s="18" t="inlineStr"/>
-      <c r="Q8" s="18" t="inlineStr"/>
-      <c r="R8" s="18" t="inlineStr"/>
-      <c r="S8" s="18" t="inlineStr"/>
-      <c r="T8" s="18" t="inlineStr"/>
-      <c r="U8" s="18" t="inlineStr"/>
-      <c r="V8" s="18" t="inlineStr"/>
-      <c r="W8" s="18" t="inlineStr"/>
-      <c r="X8" s="18" t="inlineStr"/>
-      <c r="Y8" s="18" t="inlineStr"/>
+      <c r="C8" s="19" t="inlineStr"/>
+      <c r="D8" s="19" t="inlineStr"/>
+      <c r="E8" s="19" t="inlineStr"/>
+      <c r="F8" s="19" t="inlineStr"/>
+      <c r="G8" s="19" t="inlineStr"/>
+      <c r="H8" s="19" t="inlineStr"/>
+      <c r="I8" s="19" t="inlineStr"/>
+      <c r="J8" s="19" t="inlineStr"/>
+      <c r="K8" s="19" t="inlineStr"/>
+      <c r="L8" s="19" t="inlineStr"/>
+      <c r="M8" s="19" t="inlineStr"/>
+      <c r="N8" s="19" t="inlineStr"/>
+      <c r="O8" s="19" t="inlineStr"/>
+      <c r="P8" s="19" t="inlineStr"/>
+      <c r="Q8" s="19" t="inlineStr"/>
+      <c r="R8" s="19" t="inlineStr"/>
+      <c r="S8" s="19" t="inlineStr"/>
+      <c r="T8" s="19" t="inlineStr"/>
+      <c r="U8" s="19" t="inlineStr"/>
+      <c r="V8" s="19" t="inlineStr"/>
+      <c r="W8" s="19" t="inlineStr"/>
+      <c r="X8" s="19" t="inlineStr"/>
+      <c r="Y8" s="19" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="n">
+      <c r="A9" s="17" t="n">
         <v>1923</v>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>Cambridge, MA; Missing</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr"/>
-      <c r="D9" s="18" t="inlineStr"/>
-      <c r="E9" s="18" t="inlineStr"/>
-      <c r="F9" s="18" t="inlineStr"/>
-      <c r="G9" s="18" t="inlineStr"/>
-      <c r="H9" s="18" t="inlineStr"/>
-      <c r="I9" s="18" t="inlineStr"/>
-      <c r="J9" s="18" t="inlineStr"/>
-      <c r="K9" s="18" t="inlineStr"/>
-      <c r="L9" s="18" t="inlineStr"/>
-      <c r="M9" s="18" t="inlineStr"/>
-      <c r="N9" s="18" t="inlineStr"/>
-      <c r="O9" s="18" t="inlineStr"/>
-      <c r="P9" s="18" t="inlineStr"/>
-      <c r="Q9" s="18" t="inlineStr"/>
-      <c r="R9" s="18" t="inlineStr"/>
-      <c r="S9" s="18" t="inlineStr"/>
-      <c r="T9" s="18" t="inlineStr"/>
-      <c r="U9" s="18" t="inlineStr"/>
-      <c r="V9" s="18" t="inlineStr"/>
-      <c r="W9" s="18" t="inlineStr"/>
-      <c r="X9" s="18" t="inlineStr"/>
-      <c r="Y9" s="18" t="inlineStr"/>
+      <c r="C9" s="19" t="inlineStr"/>
+      <c r="D9" s="19" t="inlineStr"/>
+      <c r="E9" s="19" t="inlineStr"/>
+      <c r="F9" s="19" t="inlineStr"/>
+      <c r="G9" s="19" t="inlineStr"/>
+      <c r="H9" s="19" t="inlineStr"/>
+      <c r="I9" s="19" t="inlineStr"/>
+      <c r="J9" s="19" t="inlineStr"/>
+      <c r="K9" s="19" t="inlineStr"/>
+      <c r="L9" s="19" t="inlineStr"/>
+      <c r="M9" s="19" t="inlineStr"/>
+      <c r="N9" s="19" t="inlineStr"/>
+      <c r="O9" s="19" t="inlineStr"/>
+      <c r="P9" s="19" t="inlineStr"/>
+      <c r="Q9" s="19" t="inlineStr"/>
+      <c r="R9" s="19" t="inlineStr"/>
+      <c r="S9" s="19" t="inlineStr"/>
+      <c r="T9" s="19" t="inlineStr"/>
+      <c r="U9" s="19" t="inlineStr"/>
+      <c r="V9" s="19" t="inlineStr"/>
+      <c r="W9" s="19" t="inlineStr"/>
+      <c r="X9" s="19" t="inlineStr"/>
+      <c r="Y9" s="19" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="n">
+      <c r="A10" s="17" t="n">
         <v>1924</v>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>Northhampton, MA; Missing</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr"/>
-      <c r="D10" s="18" t="inlineStr"/>
-      <c r="E10" s="18" t="inlineStr"/>
-      <c r="F10" s="18" t="inlineStr"/>
-      <c r="G10" s="18" t="inlineStr"/>
-      <c r="H10" s="18" t="inlineStr"/>
-      <c r="I10" s="18" t="inlineStr"/>
-      <c r="J10" s="18" t="inlineStr"/>
-      <c r="K10" s="18" t="inlineStr"/>
-      <c r="L10" s="18" t="inlineStr"/>
-      <c r="M10" s="18" t="inlineStr"/>
-      <c r="N10" s="18" t="inlineStr"/>
-      <c r="O10" s="18" t="inlineStr"/>
-      <c r="P10" s="18" t="inlineStr"/>
-      <c r="Q10" s="18" t="inlineStr"/>
-      <c r="R10" s="18" t="inlineStr"/>
-      <c r="S10" s="18" t="inlineStr"/>
-      <c r="T10" s="18" t="inlineStr"/>
-      <c r="U10" s="18" t="inlineStr"/>
-      <c r="V10" s="18" t="inlineStr"/>
-      <c r="W10" s="18" t="inlineStr"/>
-      <c r="X10" s="18" t="inlineStr"/>
-      <c r="Y10" s="18" t="inlineStr"/>
+      <c r="C10" s="19" t="inlineStr"/>
+      <c r="D10" s="19" t="inlineStr"/>
+      <c r="E10" s="19" t="inlineStr"/>
+      <c r="F10" s="19" t="inlineStr"/>
+      <c r="G10" s="19" t="inlineStr"/>
+      <c r="H10" s="19" t="inlineStr"/>
+      <c r="I10" s="19" t="inlineStr"/>
+      <c r="J10" s="19" t="inlineStr"/>
+      <c r="K10" s="19" t="inlineStr"/>
+      <c r="L10" s="19" t="inlineStr"/>
+      <c r="M10" s="19" t="inlineStr"/>
+      <c r="N10" s="19" t="inlineStr"/>
+      <c r="O10" s="19" t="inlineStr"/>
+      <c r="P10" s="19" t="inlineStr"/>
+      <c r="Q10" s="19" t="inlineStr"/>
+      <c r="R10" s="19" t="inlineStr"/>
+      <c r="S10" s="19" t="inlineStr"/>
+      <c r="T10" s="19" t="inlineStr"/>
+      <c r="U10" s="19" t="inlineStr"/>
+      <c r="V10" s="19" t="inlineStr"/>
+      <c r="W10" s="19" t="inlineStr"/>
+      <c r="X10" s="19" t="inlineStr"/>
+      <c r="Y10" s="19" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="n">
+      <c r="A11" s="17" t="n">
         <v>1925</v>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>?; Missing</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr"/>
-      <c r="D11" s="18" t="inlineStr"/>
-      <c r="E11" s="18" t="inlineStr"/>
-      <c r="F11" s="18" t="inlineStr"/>
-      <c r="G11" s="18" t="inlineStr"/>
-      <c r="H11" s="18" t="inlineStr"/>
-      <c r="I11" s="18" t="inlineStr"/>
-      <c r="J11" s="18" t="inlineStr"/>
-      <c r="K11" s="18" t="inlineStr"/>
-      <c r="L11" s="18" t="inlineStr"/>
-      <c r="M11" s="18" t="inlineStr"/>
-      <c r="N11" s="18" t="inlineStr"/>
-      <c r="O11" s="18" t="inlineStr"/>
-      <c r="P11" s="18" t="inlineStr"/>
-      <c r="Q11" s="18" t="inlineStr"/>
-      <c r="R11" s="18" t="inlineStr"/>
-      <c r="S11" s="18" t="inlineStr"/>
-      <c r="T11" s="18" t="inlineStr"/>
-      <c r="U11" s="18" t="inlineStr"/>
-      <c r="V11" s="18" t="inlineStr"/>
-      <c r="W11" s="18" t="inlineStr"/>
-      <c r="X11" s="18" t="inlineStr"/>
-      <c r="Y11" s="18" t="inlineStr"/>
+      <c r="C11" s="19" t="inlineStr"/>
+      <c r="D11" s="19" t="inlineStr"/>
+      <c r="E11" s="19" t="inlineStr"/>
+      <c r="F11" s="19" t="inlineStr"/>
+      <c r="G11" s="19" t="inlineStr"/>
+      <c r="H11" s="19" t="inlineStr"/>
+      <c r="I11" s="19" t="inlineStr"/>
+      <c r="J11" s="19" t="inlineStr"/>
+      <c r="K11" s="19" t="inlineStr"/>
+      <c r="L11" s="19" t="inlineStr"/>
+      <c r="M11" s="19" t="inlineStr"/>
+      <c r="N11" s="19" t="inlineStr"/>
+      <c r="O11" s="19" t="inlineStr"/>
+      <c r="P11" s="19" t="inlineStr"/>
+      <c r="Q11" s="19" t="inlineStr"/>
+      <c r="R11" s="19" t="inlineStr"/>
+      <c r="S11" s="19" t="inlineStr"/>
+      <c r="T11" s="19" t="inlineStr"/>
+      <c r="U11" s="19" t="inlineStr"/>
+      <c r="V11" s="19" t="inlineStr"/>
+      <c r="W11" s="19" t="inlineStr"/>
+      <c r="X11" s="19" t="inlineStr"/>
+      <c r="Y11" s="19" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="n">
+      <c r="A12" s="17" t="n">
         <v>1926</v>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>Philadelphia, PA; Missing</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr"/>
-      <c r="D12" s="18" t="inlineStr"/>
-      <c r="E12" s="18" t="inlineStr"/>
-      <c r="F12" s="18" t="inlineStr"/>
-      <c r="G12" s="18" t="inlineStr"/>
-      <c r="H12" s="18" t="inlineStr"/>
-      <c r="I12" s="18" t="inlineStr"/>
-      <c r="J12" s="18" t="inlineStr"/>
-      <c r="K12" s="18" t="inlineStr"/>
-      <c r="L12" s="18" t="inlineStr"/>
-      <c r="M12" s="18" t="inlineStr"/>
-      <c r="N12" s="18" t="inlineStr"/>
-      <c r="O12" s="18" t="inlineStr"/>
-      <c r="P12" s="18" t="inlineStr"/>
-      <c r="Q12" s="18" t="inlineStr"/>
-      <c r="R12" s="18" t="inlineStr"/>
-      <c r="S12" s="18" t="inlineStr"/>
-      <c r="T12" s="18" t="inlineStr"/>
-      <c r="U12" s="18" t="inlineStr"/>
-      <c r="V12" s="18" t="inlineStr"/>
-      <c r="W12" s="18" t="inlineStr"/>
-      <c r="X12" s="18" t="inlineStr"/>
-      <c r="Y12" s="18" t="inlineStr"/>
+      <c r="C12" s="19" t="inlineStr"/>
+      <c r="D12" s="19" t="inlineStr"/>
+      <c r="E12" s="19" t="inlineStr"/>
+      <c r="F12" s="19" t="inlineStr"/>
+      <c r="G12" s="19" t="inlineStr"/>
+      <c r="H12" s="19" t="inlineStr"/>
+      <c r="I12" s="19" t="inlineStr"/>
+      <c r="J12" s="19" t="inlineStr"/>
+      <c r="K12" s="19" t="inlineStr"/>
+      <c r="L12" s="19" t="inlineStr"/>
+      <c r="M12" s="19" t="inlineStr"/>
+      <c r="N12" s="19" t="inlineStr"/>
+      <c r="O12" s="19" t="inlineStr"/>
+      <c r="P12" s="19" t="inlineStr"/>
+      <c r="Q12" s="19" t="inlineStr"/>
+      <c r="R12" s="19" t="inlineStr"/>
+      <c r="S12" s="19" t="inlineStr"/>
+      <c r="T12" s="19" t="inlineStr"/>
+      <c r="U12" s="19" t="inlineStr"/>
+      <c r="V12" s="19" t="inlineStr"/>
+      <c r="W12" s="19" t="inlineStr"/>
+      <c r="X12" s="19" t="inlineStr"/>
+      <c r="Y12" s="19" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="n">
+      <c r="A13" s="17" t="n">
         <v>1927</v>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>Philadelphia, PA; Missing</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr"/>
-      <c r="D13" s="18" t="inlineStr"/>
-      <c r="E13" s="18" t="inlineStr"/>
-      <c r="F13" s="18" t="inlineStr"/>
-      <c r="G13" s="18" t="inlineStr"/>
-      <c r="H13" s="18" t="inlineStr"/>
-      <c r="I13" s="18" t="inlineStr"/>
-      <c r="J13" s="18" t="inlineStr"/>
-      <c r="K13" s="18" t="inlineStr"/>
-      <c r="L13" s="18" t="inlineStr"/>
-      <c r="M13" s="18" t="inlineStr"/>
-      <c r="N13" s="18" t="inlineStr"/>
-      <c r="O13" s="18" t="inlineStr"/>
-      <c r="P13" s="18" t="inlineStr"/>
-      <c r="Q13" s="18" t="inlineStr"/>
-      <c r="R13" s="18" t="inlineStr"/>
-      <c r="S13" s="18" t="inlineStr"/>
-      <c r="T13" s="18" t="inlineStr"/>
-      <c r="U13" s="18" t="inlineStr"/>
-      <c r="V13" s="18" t="inlineStr"/>
-      <c r="W13" s="18" t="inlineStr"/>
-      <c r="X13" s="18" t="inlineStr"/>
-      <c r="Y13" s="18" t="inlineStr"/>
+      <c r="C13" s="19" t="inlineStr"/>
+      <c r="D13" s="19" t="inlineStr"/>
+      <c r="E13" s="19" t="inlineStr"/>
+      <c r="F13" s="19" t="inlineStr"/>
+      <c r="G13" s="19" t="inlineStr"/>
+      <c r="H13" s="19" t="inlineStr"/>
+      <c r="I13" s="19" t="inlineStr"/>
+      <c r="J13" s="19" t="inlineStr"/>
+      <c r="K13" s="19" t="inlineStr"/>
+      <c r="L13" s="19" t="inlineStr"/>
+      <c r="M13" s="19" t="inlineStr"/>
+      <c r="N13" s="19" t="inlineStr"/>
+      <c r="O13" s="19" t="inlineStr"/>
+      <c r="P13" s="19" t="inlineStr"/>
+      <c r="Q13" s="19" t="inlineStr"/>
+      <c r="R13" s="19" t="inlineStr"/>
+      <c r="S13" s="19" t="inlineStr"/>
+      <c r="T13" s="19" t="inlineStr"/>
+      <c r="U13" s="19" t="inlineStr"/>
+      <c r="V13" s="19" t="inlineStr"/>
+      <c r="W13" s="19" t="inlineStr"/>
+      <c r="X13" s="19" t="inlineStr"/>
+      <c r="Y13" s="19" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="n">
+      <c r="A14" s="17" t="n">
         <v>1928</v>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>Washington, DC; Missing</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr"/>
-      <c r="D14" s="18" t="inlineStr"/>
-      <c r="E14" s="18" t="inlineStr"/>
-      <c r="F14" s="18" t="inlineStr"/>
-      <c r="G14" s="18" t="inlineStr"/>
-      <c r="H14" s="18" t="inlineStr"/>
-      <c r="I14" s="18" t="inlineStr"/>
-      <c r="J14" s="18" t="inlineStr"/>
-      <c r="K14" s="18" t="inlineStr"/>
-      <c r="L14" s="18" t="inlineStr"/>
-      <c r="M14" s="18" t="inlineStr"/>
-      <c r="N14" s="18" t="inlineStr"/>
-      <c r="O14" s="18" t="inlineStr"/>
-      <c r="P14" s="18" t="inlineStr"/>
-      <c r="Q14" s="18" t="inlineStr"/>
-      <c r="R14" s="18" t="inlineStr"/>
-      <c r="S14" s="18" t="inlineStr"/>
-      <c r="T14" s="18" t="inlineStr"/>
-      <c r="U14" s="18" t="inlineStr"/>
-      <c r="V14" s="18" t="inlineStr"/>
-      <c r="W14" s="18" t="inlineStr"/>
-      <c r="X14" s="18" t="inlineStr"/>
-      <c r="Y14" s="18" t="inlineStr"/>
+      <c r="C14" s="19" t="inlineStr"/>
+      <c r="D14" s="19" t="inlineStr"/>
+      <c r="E14" s="19" t="inlineStr"/>
+      <c r="F14" s="19" t="inlineStr"/>
+      <c r="G14" s="19" t="inlineStr"/>
+      <c r="H14" s="19" t="inlineStr"/>
+      <c r="I14" s="19" t="inlineStr"/>
+      <c r="J14" s="19" t="inlineStr"/>
+      <c r="K14" s="19" t="inlineStr"/>
+      <c r="L14" s="19" t="inlineStr"/>
+      <c r="M14" s="19" t="inlineStr"/>
+      <c r="N14" s="19" t="inlineStr"/>
+      <c r="O14" s="19" t="inlineStr"/>
+      <c r="P14" s="19" t="inlineStr"/>
+      <c r="Q14" s="19" t="inlineStr"/>
+      <c r="R14" s="19" t="inlineStr"/>
+      <c r="S14" s="19" t="inlineStr"/>
+      <c r="T14" s="19" t="inlineStr"/>
+      <c r="U14" s="19" t="inlineStr"/>
+      <c r="V14" s="19" t="inlineStr"/>
+      <c r="W14" s="19" t="inlineStr"/>
+      <c r="X14" s="19" t="inlineStr"/>
+      <c r="Y14" s="19" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="n">
+      <c r="A15" s="17" t="n">
         <v>1929</v>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>Ann Arbor, MI; Missing</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr"/>
-      <c r="D15" s="18" t="inlineStr"/>
-      <c r="E15" s="18" t="inlineStr"/>
-      <c r="F15" s="18" t="inlineStr"/>
-      <c r="G15" s="18" t="inlineStr"/>
-      <c r="H15" s="18" t="inlineStr"/>
-      <c r="I15" s="18" t="inlineStr"/>
-      <c r="J15" s="18" t="inlineStr"/>
-      <c r="K15" s="18" t="inlineStr"/>
-      <c r="L15" s="18" t="inlineStr"/>
-      <c r="M15" s="18" t="inlineStr"/>
-      <c r="N15" s="18" t="inlineStr"/>
-      <c r="O15" s="18" t="inlineStr"/>
-      <c r="P15" s="18" t="inlineStr"/>
-      <c r="Q15" s="18" t="inlineStr"/>
-      <c r="R15" s="18" t="inlineStr"/>
-      <c r="S15" s="18" t="inlineStr"/>
-      <c r="T15" s="18" t="inlineStr"/>
-      <c r="U15" s="18" t="inlineStr"/>
-      <c r="V15" s="18" t="inlineStr"/>
-      <c r="W15" s="18" t="inlineStr"/>
-      <c r="X15" s="18" t="inlineStr"/>
-      <c r="Y15" s="18" t="inlineStr"/>
+      <c r="C15" s="19" t="inlineStr"/>
+      <c r="D15" s="19" t="inlineStr"/>
+      <c r="E15" s="19" t="inlineStr"/>
+      <c r="F15" s="19" t="inlineStr"/>
+      <c r="G15" s="19" t="inlineStr"/>
+      <c r="H15" s="19" t="inlineStr"/>
+      <c r="I15" s="19" t="inlineStr"/>
+      <c r="J15" s="19" t="inlineStr"/>
+      <c r="K15" s="19" t="inlineStr"/>
+      <c r="L15" s="19" t="inlineStr"/>
+      <c r="M15" s="19" t="inlineStr"/>
+      <c r="N15" s="19" t="inlineStr"/>
+      <c r="O15" s="19" t="inlineStr"/>
+      <c r="P15" s="19" t="inlineStr"/>
+      <c r="Q15" s="19" t="inlineStr"/>
+      <c r="R15" s="19" t="inlineStr"/>
+      <c r="S15" s="19" t="inlineStr"/>
+      <c r="T15" s="19" t="inlineStr"/>
+      <c r="U15" s="19" t="inlineStr"/>
+      <c r="V15" s="19" t="inlineStr"/>
+      <c r="W15" s="19" t="inlineStr"/>
+      <c r="X15" s="19" t="inlineStr"/>
+      <c r="Y15" s="19" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="17" t="n">
         <v>1930</v>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>New York, NY; Missing</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr"/>
-      <c r="D16" s="18" t="inlineStr"/>
-      <c r="E16" s="18" t="inlineStr"/>
-      <c r="F16" s="18" t="inlineStr"/>
-      <c r="G16" s="18" t="inlineStr"/>
-      <c r="H16" s="18" t="inlineStr"/>
-      <c r="I16" s="18" t="inlineStr"/>
-      <c r="J16" s="18" t="inlineStr"/>
-      <c r="K16" s="18" t="inlineStr"/>
-      <c r="L16" s="18" t="inlineStr"/>
-      <c r="M16" s="18" t="inlineStr"/>
-      <c r="N16" s="18" t="inlineStr"/>
-      <c r="O16" s="18" t="inlineStr"/>
-      <c r="P16" s="18" t="inlineStr"/>
-      <c r="Q16" s="18" t="inlineStr"/>
-      <c r="R16" s="18" t="inlineStr"/>
-      <c r="S16" s="18" t="inlineStr"/>
-      <c r="T16" s="18" t="inlineStr"/>
-      <c r="U16" s="18" t="inlineStr"/>
-      <c r="V16" s="18" t="inlineStr"/>
-      <c r="W16" s="18" t="inlineStr"/>
-      <c r="X16" s="18" t="inlineStr"/>
-      <c r="Y16" s="18" t="inlineStr"/>
+      <c r="C16" s="19" t="inlineStr"/>
+      <c r="D16" s="19" t="inlineStr"/>
+      <c r="E16" s="19" t="inlineStr"/>
+      <c r="F16" s="19" t="inlineStr"/>
+      <c r="G16" s="19" t="inlineStr"/>
+      <c r="H16" s="19" t="inlineStr"/>
+      <c r="I16" s="19" t="inlineStr"/>
+      <c r="J16" s="19" t="inlineStr"/>
+      <c r="K16" s="19" t="inlineStr"/>
+      <c r="L16" s="19" t="inlineStr"/>
+      <c r="M16" s="19" t="inlineStr"/>
+      <c r="N16" s="19" t="inlineStr"/>
+      <c r="O16" s="19" t="inlineStr"/>
+      <c r="P16" s="19" t="inlineStr"/>
+      <c r="Q16" s="19" t="inlineStr"/>
+      <c r="R16" s="19" t="inlineStr"/>
+      <c r="S16" s="19" t="inlineStr"/>
+      <c r="T16" s="19" t="inlineStr"/>
+      <c r="U16" s="19" t="inlineStr"/>
+      <c r="V16" s="19" t="inlineStr"/>
+      <c r="W16" s="19" t="inlineStr"/>
+      <c r="X16" s="19" t="inlineStr"/>
+      <c r="Y16" s="19" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="17" t="n">
         <v>1931</v>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>Philadelphia, PA; Missing</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr"/>
-      <c r="D17" s="18" t="inlineStr"/>
-      <c r="E17" s="18" t="inlineStr"/>
-      <c r="F17" s="18" t="inlineStr"/>
-      <c r="G17" s="18" t="inlineStr"/>
-      <c r="H17" s="18" t="inlineStr"/>
-      <c r="I17" s="18" t="inlineStr"/>
-      <c r="J17" s="18" t="inlineStr"/>
-      <c r="K17" s="18" t="inlineStr"/>
-      <c r="L17" s="18" t="inlineStr"/>
-      <c r="M17" s="18" t="inlineStr"/>
-      <c r="N17" s="18" t="inlineStr"/>
-      <c r="O17" s="18" t="inlineStr"/>
-      <c r="P17" s="18" t="inlineStr"/>
-      <c r="Q17" s="18" t="inlineStr"/>
-      <c r="R17" s="18" t="inlineStr"/>
-      <c r="S17" s="18" t="inlineStr"/>
-      <c r="T17" s="18" t="inlineStr"/>
-      <c r="U17" s="18" t="inlineStr"/>
-      <c r="V17" s="18" t="inlineStr"/>
-      <c r="W17" s="18" t="inlineStr"/>
-      <c r="X17" s="18" t="inlineStr"/>
-      <c r="Y17" s="18" t="inlineStr"/>
+      <c r="C17" s="19" t="inlineStr"/>
+      <c r="D17" s="19" t="inlineStr"/>
+      <c r="E17" s="19" t="inlineStr"/>
+      <c r="F17" s="19" t="inlineStr"/>
+      <c r="G17" s="19" t="inlineStr"/>
+      <c r="H17" s="19" t="inlineStr"/>
+      <c r="I17" s="19" t="inlineStr"/>
+      <c r="J17" s="19" t="inlineStr"/>
+      <c r="K17" s="19" t="inlineStr"/>
+      <c r="L17" s="19" t="inlineStr"/>
+      <c r="M17" s="19" t="inlineStr"/>
+      <c r="N17" s="19" t="inlineStr"/>
+      <c r="O17" s="19" t="inlineStr"/>
+      <c r="P17" s="19" t="inlineStr"/>
+      <c r="Q17" s="19" t="inlineStr"/>
+      <c r="R17" s="19" t="inlineStr"/>
+      <c r="S17" s="19" t="inlineStr"/>
+      <c r="T17" s="19" t="inlineStr"/>
+      <c r="U17" s="19" t="inlineStr"/>
+      <c r="V17" s="19" t="inlineStr"/>
+      <c r="W17" s="19" t="inlineStr"/>
+      <c r="X17" s="19" t="inlineStr"/>
+      <c r="Y17" s="19" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="n">
+      <c r="A18" s="17" t="n">
         <v>1932</v>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>Washington, DC; Missing</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr"/>
-      <c r="D18" s="18" t="inlineStr"/>
-      <c r="E18" s="18" t="inlineStr"/>
-      <c r="F18" s="18" t="inlineStr"/>
-      <c r="G18" s="18" t="inlineStr"/>
-      <c r="H18" s="18" t="inlineStr"/>
-      <c r="I18" s="18" t="inlineStr"/>
-      <c r="J18" s="18" t="inlineStr"/>
-      <c r="K18" s="18" t="inlineStr"/>
-      <c r="L18" s="18" t="inlineStr"/>
-      <c r="M18" s="18" t="inlineStr"/>
-      <c r="N18" s="18" t="inlineStr"/>
-      <c r="O18" s="18" t="inlineStr"/>
-      <c r="P18" s="18" t="inlineStr"/>
-      <c r="Q18" s="18" t="inlineStr"/>
-      <c r="R18" s="18" t="inlineStr"/>
-      <c r="S18" s="18" t="inlineStr"/>
-      <c r="T18" s="18" t="inlineStr"/>
-      <c r="U18" s="18" t="inlineStr"/>
-      <c r="V18" s="18" t="inlineStr"/>
-      <c r="W18" s="18" t="inlineStr"/>
-      <c r="X18" s="18" t="inlineStr"/>
-      <c r="Y18" s="18" t="inlineStr"/>
+      <c r="C18" s="19" t="inlineStr"/>
+      <c r="D18" s="19" t="inlineStr"/>
+      <c r="E18" s="19" t="inlineStr"/>
+      <c r="F18" s="19" t="inlineStr"/>
+      <c r="G18" s="19" t="inlineStr"/>
+      <c r="H18" s="19" t="inlineStr"/>
+      <c r="I18" s="19" t="inlineStr"/>
+      <c r="J18" s="19" t="inlineStr"/>
+      <c r="K18" s="19" t="inlineStr"/>
+      <c r="L18" s="19" t="inlineStr"/>
+      <c r="M18" s="19" t="inlineStr"/>
+      <c r="N18" s="19" t="inlineStr"/>
+      <c r="O18" s="19" t="inlineStr"/>
+      <c r="P18" s="19" t="inlineStr"/>
+      <c r="Q18" s="19" t="inlineStr"/>
+      <c r="R18" s="19" t="inlineStr"/>
+      <c r="S18" s="19" t="inlineStr"/>
+      <c r="T18" s="19" t="inlineStr"/>
+      <c r="U18" s="19" t="inlineStr"/>
+      <c r="V18" s="19" t="inlineStr"/>
+      <c r="W18" s="19" t="inlineStr"/>
+      <c r="X18" s="19" t="inlineStr"/>
+      <c r="Y18" s="19" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="17" t="n">
         <v>1933</v>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>Cambridge, MA; Missing</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr"/>
-      <c r="D19" s="18" t="inlineStr"/>
-      <c r="E19" s="18" t="inlineStr"/>
-      <c r="F19" s="18" t="inlineStr"/>
-      <c r="G19" s="18" t="inlineStr"/>
-      <c r="H19" s="18" t="inlineStr"/>
-      <c r="I19" s="18" t="inlineStr"/>
-      <c r="J19" s="18" t="inlineStr"/>
-      <c r="K19" s="18" t="inlineStr"/>
-      <c r="L19" s="18" t="inlineStr"/>
-      <c r="M19" s="18" t="inlineStr"/>
-      <c r="N19" s="18" t="inlineStr"/>
-      <c r="O19" s="18" t="inlineStr"/>
-      <c r="P19" s="18" t="inlineStr"/>
-      <c r="Q19" s="18" t="inlineStr"/>
-      <c r="R19" s="18" t="inlineStr"/>
-      <c r="S19" s="18" t="inlineStr"/>
-      <c r="T19" s="18" t="inlineStr"/>
-      <c r="U19" s="18" t="inlineStr"/>
-      <c r="V19" s="18" t="inlineStr"/>
-      <c r="W19" s="18" t="inlineStr"/>
-      <c r="X19" s="18" t="inlineStr"/>
-      <c r="Y19" s="18" t="inlineStr"/>
+      <c r="C19" s="19" t="inlineStr"/>
+      <c r="D19" s="19" t="inlineStr"/>
+      <c r="E19" s="19" t="inlineStr"/>
+      <c r="F19" s="19" t="inlineStr"/>
+      <c r="G19" s="19" t="inlineStr"/>
+      <c r="H19" s="19" t="inlineStr"/>
+      <c r="I19" s="19" t="inlineStr"/>
+      <c r="J19" s="19" t="inlineStr"/>
+      <c r="K19" s="19" t="inlineStr"/>
+      <c r="L19" s="19" t="inlineStr"/>
+      <c r="M19" s="19" t="inlineStr"/>
+      <c r="N19" s="19" t="inlineStr"/>
+      <c r="O19" s="19" t="inlineStr"/>
+      <c r="P19" s="19" t="inlineStr"/>
+      <c r="Q19" s="19" t="inlineStr"/>
+      <c r="R19" s="19" t="inlineStr"/>
+      <c r="S19" s="19" t="inlineStr"/>
+      <c r="T19" s="19" t="inlineStr"/>
+      <c r="U19" s="19" t="inlineStr"/>
+      <c r="V19" s="19" t="inlineStr"/>
+      <c r="W19" s="19" t="inlineStr"/>
+      <c r="X19" s="19" t="inlineStr"/>
+      <c r="Y19" s="19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="n">
+      <c r="A20" s="17" t="n">
         <v>1934</v>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>New York, NY; Missing</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr"/>
-      <c r="D20" s="18" t="inlineStr"/>
-      <c r="E20" s="18" t="inlineStr"/>
-      <c r="F20" s="18" t="inlineStr"/>
-      <c r="G20" s="18" t="inlineStr"/>
-      <c r="H20" s="18" t="inlineStr"/>
-      <c r="I20" s="18" t="inlineStr"/>
-      <c r="J20" s="18" t="inlineStr"/>
-      <c r="K20" s="18" t="inlineStr"/>
-      <c r="L20" s="18" t="inlineStr"/>
-      <c r="M20" s="18" t="inlineStr"/>
-      <c r="N20" s="18" t="inlineStr"/>
-      <c r="O20" s="18" t="inlineStr"/>
-      <c r="P20" s="18" t="inlineStr"/>
-      <c r="Q20" s="18" t="inlineStr"/>
-      <c r="R20" s="18" t="inlineStr"/>
-      <c r="S20" s="18" t="inlineStr"/>
-      <c r="T20" s="18" t="inlineStr"/>
-      <c r="U20" s="18" t="inlineStr"/>
-      <c r="V20" s="18" t="inlineStr"/>
-      <c r="W20" s="18" t="inlineStr"/>
-      <c r="X20" s="18" t="inlineStr"/>
-      <c r="Y20" s="18" t="inlineStr"/>
+      <c r="C20" s="19" t="inlineStr"/>
+      <c r="D20" s="19" t="inlineStr"/>
+      <c r="E20" s="19" t="inlineStr"/>
+      <c r="F20" s="19" t="inlineStr"/>
+      <c r="G20" s="19" t="inlineStr"/>
+      <c r="H20" s="19" t="inlineStr"/>
+      <c r="I20" s="19" t="inlineStr"/>
+      <c r="J20" s="19" t="inlineStr"/>
+      <c r="K20" s="19" t="inlineStr"/>
+      <c r="L20" s="19" t="inlineStr"/>
+      <c r="M20" s="19" t="inlineStr"/>
+      <c r="N20" s="19" t="inlineStr"/>
+      <c r="O20" s="19" t="inlineStr"/>
+      <c r="P20" s="19" t="inlineStr"/>
+      <c r="Q20" s="19" t="inlineStr"/>
+      <c r="R20" s="19" t="inlineStr"/>
+      <c r="S20" s="19" t="inlineStr"/>
+      <c r="T20" s="19" t="inlineStr"/>
+      <c r="U20" s="19" t="inlineStr"/>
+      <c r="V20" s="19" t="inlineStr"/>
+      <c r="W20" s="19" t="inlineStr"/>
+      <c r="X20" s="19" t="inlineStr"/>
+      <c r="Y20" s="19" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="n">
+      <c r="A21" s="17" t="n">
         <v>1935</v>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t>Pittsburgh, PA; Missing</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr"/>
-      <c r="D21" s="18" t="inlineStr"/>
-      <c r="E21" s="18" t="inlineStr"/>
-      <c r="F21" s="18" t="inlineStr"/>
-      <c r="G21" s="18" t="inlineStr"/>
-      <c r="H21" s="18" t="inlineStr"/>
-      <c r="I21" s="18" t="inlineStr"/>
-      <c r="J21" s="18" t="inlineStr"/>
-      <c r="K21" s="18" t="inlineStr"/>
-      <c r="L21" s="18" t="inlineStr"/>
-      <c r="M21" s="18" t="inlineStr"/>
-      <c r="N21" s="18" t="inlineStr"/>
-      <c r="O21" s="18" t="inlineStr"/>
-      <c r="P21" s="18" t="inlineStr"/>
-      <c r="Q21" s="18" t="inlineStr"/>
-      <c r="R21" s="18" t="inlineStr"/>
-      <c r="S21" s="18" t="inlineStr"/>
-      <c r="T21" s="18" t="inlineStr"/>
-      <c r="U21" s="18" t="inlineStr"/>
-      <c r="V21" s="18" t="inlineStr"/>
-      <c r="W21" s="18" t="inlineStr"/>
-      <c r="X21" s="18" t="inlineStr"/>
-      <c r="Y21" s="18" t="inlineStr"/>
+      <c r="C21" s="19" t="inlineStr"/>
+      <c r="D21" s="19" t="inlineStr"/>
+      <c r="E21" s="19" t="inlineStr"/>
+      <c r="F21" s="19" t="inlineStr"/>
+      <c r="G21" s="19" t="inlineStr"/>
+      <c r="H21" s="19" t="inlineStr"/>
+      <c r="I21" s="19" t="inlineStr"/>
+      <c r="J21" s="19" t="inlineStr"/>
+      <c r="K21" s="19" t="inlineStr"/>
+      <c r="L21" s="19" t="inlineStr"/>
+      <c r="M21" s="19" t="inlineStr"/>
+      <c r="N21" s="19" t="inlineStr"/>
+      <c r="O21" s="19" t="inlineStr"/>
+      <c r="P21" s="19" t="inlineStr"/>
+      <c r="Q21" s="19" t="inlineStr"/>
+      <c r="R21" s="19" t="inlineStr"/>
+      <c r="S21" s="19" t="inlineStr"/>
+      <c r="T21" s="19" t="inlineStr"/>
+      <c r="U21" s="19" t="inlineStr"/>
+      <c r="V21" s="19" t="inlineStr"/>
+      <c r="W21" s="19" t="inlineStr"/>
+      <c r="X21" s="19" t="inlineStr"/>
+      <c r="Y21" s="19" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="n">
+      <c r="A22" s="17" t="n">
         <v>1936</v>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>Ann Arbor, MI; Missing</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr"/>
-      <c r="D22" s="18" t="inlineStr"/>
-      <c r="E22" s="18" t="inlineStr"/>
-      <c r="F22" s="18" t="inlineStr"/>
-      <c r="G22" s="18" t="inlineStr"/>
-      <c r="H22" s="18" t="inlineStr"/>
-      <c r="I22" s="18" t="inlineStr"/>
-      <c r="J22" s="18" t="inlineStr"/>
-      <c r="K22" s="18" t="inlineStr"/>
-      <c r="L22" s="18" t="inlineStr"/>
-      <c r="M22" s="18" t="inlineStr"/>
-      <c r="N22" s="18" t="inlineStr"/>
-      <c r="O22" s="18" t="inlineStr"/>
-      <c r="P22" s="18" t="inlineStr"/>
-      <c r="Q22" s="18" t="inlineStr"/>
-      <c r="R22" s="18" t="inlineStr"/>
-      <c r="S22" s="18" t="inlineStr"/>
-      <c r="T22" s="18" t="inlineStr"/>
-      <c r="U22" s="18" t="inlineStr"/>
-      <c r="V22" s="18" t="inlineStr"/>
-      <c r="W22" s="18" t="inlineStr"/>
-      <c r="X22" s="18" t="inlineStr"/>
-      <c r="Y22" s="18" t="inlineStr"/>
+      <c r="C22" s="19" t="inlineStr"/>
+      <c r="D22" s="19" t="inlineStr"/>
+      <c r="E22" s="19" t="inlineStr"/>
+      <c r="F22" s="19" t="inlineStr"/>
+      <c r="G22" s="19" t="inlineStr"/>
+      <c r="H22" s="19" t="inlineStr"/>
+      <c r="I22" s="19" t="inlineStr"/>
+      <c r="J22" s="19" t="inlineStr"/>
+      <c r="K22" s="19" t="inlineStr"/>
+      <c r="L22" s="19" t="inlineStr"/>
+      <c r="M22" s="19" t="inlineStr"/>
+      <c r="N22" s="19" t="inlineStr"/>
+      <c r="O22" s="19" t="inlineStr"/>
+      <c r="P22" s="19" t="inlineStr"/>
+      <c r="Q22" s="19" t="inlineStr"/>
+      <c r="R22" s="19" t="inlineStr"/>
+      <c r="S22" s="19" t="inlineStr"/>
+      <c r="T22" s="19" t="inlineStr"/>
+      <c r="U22" s="19" t="inlineStr"/>
+      <c r="V22" s="19" t="inlineStr"/>
+      <c r="W22" s="19" t="inlineStr"/>
+      <c r="X22" s="19" t="inlineStr"/>
+      <c r="Y22" s="19" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="n">
+      <c r="A23" s="17" t="n">
         <v>1937</v>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>Washington, DC; Missing</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr"/>
-      <c r="D23" s="18" t="inlineStr"/>
-      <c r="E23" s="18" t="inlineStr"/>
-      <c r="F23" s="18" t="inlineStr"/>
-      <c r="G23" s="18" t="inlineStr"/>
-      <c r="H23" s="18" t="inlineStr"/>
-      <c r="I23" s="18" t="inlineStr"/>
-      <c r="J23" s="18" t="inlineStr"/>
-      <c r="K23" s="18" t="inlineStr"/>
-      <c r="L23" s="18" t="inlineStr"/>
-      <c r="M23" s="18" t="inlineStr"/>
-      <c r="N23" s="18" t="inlineStr"/>
-      <c r="O23" s="18" t="inlineStr"/>
-      <c r="P23" s="18" t="inlineStr"/>
-      <c r="Q23" s="18" t="inlineStr"/>
-      <c r="R23" s="18" t="inlineStr"/>
-      <c r="S23" s="18" t="inlineStr"/>
-      <c r="T23" s="18" t="inlineStr"/>
-      <c r="U23" s="18" t="inlineStr"/>
-      <c r="V23" s="18" t="inlineStr"/>
-      <c r="W23" s="18" t="inlineStr"/>
-      <c r="X23" s="18" t="inlineStr"/>
-      <c r="Y23" s="18" t="inlineStr"/>
+      <c r="C23" s="19" t="inlineStr"/>
+      <c r="D23" s="19" t="inlineStr"/>
+      <c r="E23" s="19" t="inlineStr"/>
+      <c r="F23" s="19" t="inlineStr"/>
+      <c r="G23" s="19" t="inlineStr"/>
+      <c r="H23" s="19" t="inlineStr"/>
+      <c r="I23" s="19" t="inlineStr"/>
+      <c r="J23" s="19" t="inlineStr"/>
+      <c r="K23" s="19" t="inlineStr"/>
+      <c r="L23" s="19" t="inlineStr"/>
+      <c r="M23" s="19" t="inlineStr"/>
+      <c r="N23" s="19" t="inlineStr"/>
+      <c r="O23" s="19" t="inlineStr"/>
+      <c r="P23" s="19" t="inlineStr"/>
+      <c r="Q23" s="19" t="inlineStr"/>
+      <c r="R23" s="19" t="inlineStr"/>
+      <c r="S23" s="19" t="inlineStr"/>
+      <c r="T23" s="19" t="inlineStr"/>
+      <c r="U23" s="19" t="inlineStr"/>
+      <c r="V23" s="19" t="inlineStr"/>
+      <c r="W23" s="19" t="inlineStr"/>
+      <c r="X23" s="19" t="inlineStr"/>
+      <c r="Y23" s="19" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="n">
+      <c r="A24" s="17" t="n">
         <v>1938</v>
       </c>
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B24" s="18" t="inlineStr">
         <is>
           <t>Berkeley, CA; Missing</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr"/>
-      <c r="D24" s="18" t="inlineStr"/>
-      <c r="E24" s="18" t="inlineStr"/>
-      <c r="F24" s="18" t="inlineStr"/>
-      <c r="G24" s="18" t="inlineStr"/>
-      <c r="H24" s="18" t="inlineStr"/>
-      <c r="I24" s="18" t="inlineStr"/>
-      <c r="J24" s="18" t="inlineStr"/>
-      <c r="K24" s="18" t="inlineStr"/>
-      <c r="L24" s="18" t="inlineStr"/>
-      <c r="M24" s="18" t="inlineStr"/>
-      <c r="N24" s="18" t="inlineStr"/>
-      <c r="O24" s="18" t="inlineStr"/>
-      <c r="P24" s="18" t="inlineStr"/>
-      <c r="Q24" s="18" t="inlineStr"/>
-      <c r="R24" s="18" t="inlineStr"/>
-      <c r="S24" s="18" t="inlineStr"/>
-      <c r="T24" s="18" t="inlineStr"/>
-      <c r="U24" s="18" t="inlineStr"/>
-      <c r="V24" s="18" t="inlineStr"/>
-      <c r="W24" s="18" t="inlineStr"/>
-      <c r="X24" s="18" t="inlineStr"/>
-      <c r="Y24" s="18" t="inlineStr"/>
+      <c r="C24" s="19" t="inlineStr"/>
+      <c r="D24" s="19" t="inlineStr"/>
+      <c r="E24" s="19" t="inlineStr"/>
+      <c r="F24" s="19" t="inlineStr"/>
+      <c r="G24" s="19" t="inlineStr"/>
+      <c r="H24" s="19" t="inlineStr"/>
+      <c r="I24" s="19" t="inlineStr"/>
+      <c r="J24" s="19" t="inlineStr"/>
+      <c r="K24" s="19" t="inlineStr"/>
+      <c r="L24" s="19" t="inlineStr"/>
+      <c r="M24" s="19" t="inlineStr"/>
+      <c r="N24" s="19" t="inlineStr"/>
+      <c r="O24" s="19" t="inlineStr"/>
+      <c r="P24" s="19" t="inlineStr"/>
+      <c r="Q24" s="19" t="inlineStr"/>
+      <c r="R24" s="19" t="inlineStr"/>
+      <c r="S24" s="19" t="inlineStr"/>
+      <c r="T24" s="19" t="inlineStr"/>
+      <c r="U24" s="19" t="inlineStr"/>
+      <c r="V24" s="19" t="inlineStr"/>
+      <c r="W24" s="19" t="inlineStr"/>
+      <c r="X24" s="19" t="inlineStr"/>
+      <c r="Y24" s="19" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="n">
+      <c r="A25" s="17" t="n">
         <v>1939</v>
       </c>
-      <c r="B25" s="17" t="inlineStr">
+      <c r="B25" s="18" t="inlineStr">
         <is>
           <t>Chicago, IL; Missing</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr"/>
-      <c r="D25" s="18" t="inlineStr"/>
-      <c r="E25" s="18" t="inlineStr"/>
-      <c r="F25" s="18" t="inlineStr"/>
-      <c r="G25" s="18" t="inlineStr"/>
-      <c r="H25" s="18" t="inlineStr"/>
-      <c r="I25" s="18" t="inlineStr"/>
-      <c r="J25" s="18" t="inlineStr"/>
-      <c r="K25" s="18" t="inlineStr"/>
-      <c r="L25" s="18" t="inlineStr"/>
-      <c r="M25" s="18" t="inlineStr"/>
-      <c r="N25" s="18" t="inlineStr"/>
-      <c r="O25" s="18" t="inlineStr"/>
-      <c r="P25" s="18" t="inlineStr"/>
-      <c r="Q25" s="18" t="inlineStr"/>
-      <c r="R25" s="18" t="inlineStr"/>
-      <c r="S25" s="18" t="inlineStr"/>
-      <c r="T25" s="18" t="inlineStr"/>
-      <c r="U25" s="18" t="inlineStr"/>
-      <c r="V25" s="18" t="inlineStr"/>
-      <c r="W25" s="18" t="inlineStr"/>
-      <c r="X25" s="18" t="inlineStr"/>
-      <c r="Y25" s="18" t="inlineStr"/>
+      <c r="C25" s="19" t="inlineStr"/>
+      <c r="D25" s="19" t="inlineStr"/>
+      <c r="E25" s="19" t="inlineStr"/>
+      <c r="F25" s="19" t="inlineStr"/>
+      <c r="G25" s="19" t="inlineStr"/>
+      <c r="H25" s="19" t="inlineStr"/>
+      <c r="I25" s="19" t="inlineStr"/>
+      <c r="J25" s="19" t="inlineStr"/>
+      <c r="K25" s="19" t="inlineStr"/>
+      <c r="L25" s="19" t="inlineStr"/>
+      <c r="M25" s="19" t="inlineStr"/>
+      <c r="N25" s="19" t="inlineStr"/>
+      <c r="O25" s="19" t="inlineStr"/>
+      <c r="P25" s="19" t="inlineStr"/>
+      <c r="Q25" s="19" t="inlineStr"/>
+      <c r="R25" s="19" t="inlineStr"/>
+      <c r="S25" s="19" t="inlineStr"/>
+      <c r="T25" s="19" t="inlineStr"/>
+      <c r="U25" s="19" t="inlineStr"/>
+      <c r="V25" s="19" t="inlineStr"/>
+      <c r="W25" s="19" t="inlineStr"/>
+      <c r="X25" s="19" t="inlineStr"/>
+      <c r="Y25" s="19" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="n">
+      <c r="A26" s="17" t="n">
         <v>1940</v>
       </c>
-      <c r="B26" s="17" t="inlineStr">
+      <c r="B26" s="18" t="inlineStr">
         <is>
           <t>Toronto, ON; Missing</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr"/>
-      <c r="D26" s="18" t="inlineStr"/>
-      <c r="E26" s="18" t="inlineStr"/>
-      <c r="F26" s="18" t="inlineStr"/>
-      <c r="G26" s="18" t="inlineStr"/>
-      <c r="H26" s="18" t="inlineStr"/>
-      <c r="I26" s="18" t="inlineStr"/>
-      <c r="J26" s="18" t="inlineStr"/>
-      <c r="K26" s="18" t="inlineStr"/>
-      <c r="L26" s="18" t="inlineStr"/>
-      <c r="M26" s="18" t="inlineStr"/>
-      <c r="N26" s="18" t="inlineStr"/>
-      <c r="O26" s="18" t="inlineStr"/>
-      <c r="P26" s="18" t="inlineStr"/>
-      <c r="Q26" s="18" t="inlineStr"/>
-      <c r="R26" s="18" t="inlineStr"/>
-      <c r="S26" s="18" t="inlineStr"/>
-      <c r="T26" s="18" t="inlineStr"/>
-      <c r="U26" s="18" t="inlineStr"/>
-      <c r="V26" s="18" t="inlineStr"/>
-      <c r="W26" s="18" t="inlineStr"/>
-      <c r="X26" s="18" t="inlineStr"/>
-      <c r="Y26" s="18" t="inlineStr"/>
+      <c r="C26" s="19" t="inlineStr"/>
+      <c r="D26" s="19" t="inlineStr"/>
+      <c r="E26" s="19" t="inlineStr"/>
+      <c r="F26" s="19" t="inlineStr"/>
+      <c r="G26" s="19" t="inlineStr"/>
+      <c r="H26" s="19" t="inlineStr"/>
+      <c r="I26" s="19" t="inlineStr"/>
+      <c r="J26" s="19" t="inlineStr"/>
+      <c r="K26" s="19" t="inlineStr"/>
+      <c r="L26" s="19" t="inlineStr"/>
+      <c r="M26" s="19" t="inlineStr"/>
+      <c r="N26" s="19" t="inlineStr"/>
+      <c r="O26" s="19" t="inlineStr"/>
+      <c r="P26" s="19" t="inlineStr"/>
+      <c r="Q26" s="19" t="inlineStr"/>
+      <c r="R26" s="19" t="inlineStr"/>
+      <c r="S26" s="19" t="inlineStr"/>
+      <c r="T26" s="19" t="inlineStr"/>
+      <c r="U26" s="19" t="inlineStr"/>
+      <c r="V26" s="19" t="inlineStr"/>
+      <c r="W26" s="19" t="inlineStr"/>
+      <c r="X26" s="19" t="inlineStr"/>
+      <c r="Y26" s="19" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="n">
+      <c r="A27" s="17" t="n">
         <v>1941</v>
       </c>
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B27" s="18" t="inlineStr">
         <is>
           <t>Gainesville, FL; Missing</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr"/>
-      <c r="D27" s="18" t="inlineStr"/>
-      <c r="E27" s="18" t="inlineStr"/>
-      <c r="F27" s="18" t="inlineStr"/>
-      <c r="G27" s="18" t="inlineStr"/>
-      <c r="H27" s="18" t="inlineStr"/>
-      <c r="I27" s="18" t="inlineStr"/>
-      <c r="J27" s="18" t="inlineStr"/>
-      <c r="K27" s="18" t="inlineStr"/>
-      <c r="L27" s="18" t="inlineStr"/>
-      <c r="M27" s="18" t="inlineStr"/>
-      <c r="N27" s="18" t="inlineStr"/>
-      <c r="O27" s="18" t="inlineStr"/>
-      <c r="P27" s="18" t="inlineStr"/>
-      <c r="Q27" s="18" t="inlineStr"/>
-      <c r="R27" s="18" t="inlineStr"/>
-      <c r="S27" s="18" t="inlineStr"/>
-      <c r="T27" s="18" t="inlineStr"/>
-      <c r="U27" s="18" t="inlineStr"/>
-      <c r="V27" s="18" t="inlineStr"/>
-      <c r="W27" s="18" t="inlineStr"/>
-      <c r="X27" s="18" t="inlineStr"/>
-      <c r="Y27" s="18" t="inlineStr"/>
+      <c r="C27" s="19" t="inlineStr"/>
+      <c r="D27" s="19" t="inlineStr"/>
+      <c r="E27" s="19" t="inlineStr"/>
+      <c r="F27" s="19" t="inlineStr"/>
+      <c r="G27" s="19" t="inlineStr"/>
+      <c r="H27" s="19" t="inlineStr"/>
+      <c r="I27" s="19" t="inlineStr"/>
+      <c r="J27" s="19" t="inlineStr"/>
+      <c r="K27" s="19" t="inlineStr"/>
+      <c r="L27" s="19" t="inlineStr"/>
+      <c r="M27" s="19" t="inlineStr"/>
+      <c r="N27" s="19" t="inlineStr"/>
+      <c r="O27" s="19" t="inlineStr"/>
+      <c r="P27" s="19" t="inlineStr"/>
+      <c r="Q27" s="19" t="inlineStr"/>
+      <c r="R27" s="19" t="inlineStr"/>
+      <c r="S27" s="19" t="inlineStr"/>
+      <c r="T27" s="19" t="inlineStr"/>
+      <c r="U27" s="19" t="inlineStr"/>
+      <c r="V27" s="19" t="inlineStr"/>
+      <c r="W27" s="19" t="inlineStr"/>
+      <c r="X27" s="19" t="inlineStr"/>
+      <c r="Y27" s="19" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="n">
+      <c r="A28" s="17" t="n">
         <v>1942</v>
       </c>
-      <c r="B28" s="17" t="inlineStr">
+      <c r="B28" s="18" t="inlineStr">
         <is>
           <t>New York, NY; Missing</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr"/>
-      <c r="D28" s="18" t="inlineStr"/>
-      <c r="E28" s="18" t="inlineStr"/>
-      <c r="F28" s="18" t="inlineStr"/>
-      <c r="G28" s="18" t="inlineStr"/>
-      <c r="H28" s="18" t="inlineStr"/>
-      <c r="I28" s="18" t="inlineStr"/>
-      <c r="J28" s="18" t="inlineStr"/>
-      <c r="K28" s="18" t="inlineStr"/>
-      <c r="L28" s="18" t="inlineStr"/>
-      <c r="M28" s="18" t="inlineStr"/>
-      <c r="N28" s="18" t="inlineStr"/>
-      <c r="O28" s="18" t="inlineStr"/>
-      <c r="P28" s="18" t="inlineStr"/>
-      <c r="Q28" s="18" t="inlineStr"/>
-      <c r="R28" s="18" t="inlineStr"/>
-      <c r="S28" s="18" t="inlineStr"/>
-      <c r="T28" s="18" t="inlineStr"/>
-      <c r="U28" s="18" t="inlineStr"/>
-      <c r="V28" s="18" t="inlineStr"/>
-      <c r="W28" s="18" t="inlineStr"/>
-      <c r="X28" s="18" t="inlineStr"/>
-      <c r="Y28" s="18" t="inlineStr"/>
+      <c r="C28" s="19" t="inlineStr"/>
+      <c r="D28" s="19" t="inlineStr"/>
+      <c r="E28" s="19" t="inlineStr"/>
+      <c r="F28" s="19" t="inlineStr"/>
+      <c r="G28" s="19" t="inlineStr"/>
+      <c r="H28" s="19" t="inlineStr"/>
+      <c r="I28" s="19" t="inlineStr"/>
+      <c r="J28" s="19" t="inlineStr"/>
+      <c r="K28" s="19" t="inlineStr"/>
+      <c r="L28" s="19" t="inlineStr"/>
+      <c r="M28" s="19" t="inlineStr"/>
+      <c r="N28" s="19" t="inlineStr"/>
+      <c r="O28" s="19" t="inlineStr"/>
+      <c r="P28" s="19" t="inlineStr"/>
+      <c r="Q28" s="19" t="inlineStr"/>
+      <c r="R28" s="19" t="inlineStr"/>
+      <c r="S28" s="19" t="inlineStr"/>
+      <c r="T28" s="19" t="inlineStr"/>
+      <c r="U28" s="19" t="inlineStr"/>
+      <c r="V28" s="19" t="inlineStr"/>
+      <c r="W28" s="19" t="inlineStr"/>
+      <c r="X28" s="19" t="inlineStr"/>
+      <c r="Y28" s="19" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="n">
+      <c r="A29" s="17" t="n">
         <v>1943</v>
       </c>
-      <c r="B29" s="17" t="inlineStr">
+      <c r="B29" s="18" t="inlineStr">
         <is>
           <t>?; Missing</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr"/>
-      <c r="D29" s="18" t="inlineStr"/>
-      <c r="E29" s="18" t="inlineStr"/>
-      <c r="F29" s="18" t="inlineStr"/>
-      <c r="G29" s="18" t="inlineStr"/>
-      <c r="H29" s="18" t="inlineStr"/>
-      <c r="I29" s="18" t="inlineStr"/>
-      <c r="J29" s="18" t="inlineStr"/>
-      <c r="K29" s="18" t="inlineStr"/>
-      <c r="L29" s="18" t="inlineStr"/>
-      <c r="M29" s="18" t="inlineStr"/>
-      <c r="N29" s="18" t="inlineStr"/>
-      <c r="O29" s="18" t="inlineStr"/>
-      <c r="P29" s="18" t="inlineStr"/>
-      <c r="Q29" s="18" t="inlineStr"/>
-      <c r="R29" s="18" t="inlineStr"/>
-      <c r="S29" s="18" t="inlineStr"/>
-      <c r="T29" s="18" t="inlineStr"/>
-      <c r="U29" s="18" t="inlineStr"/>
-      <c r="V29" s="18" t="inlineStr"/>
-      <c r="W29" s="18" t="inlineStr"/>
-      <c r="X29" s="18" t="inlineStr"/>
-      <c r="Y29" s="18" t="inlineStr"/>
+      <c r="C29" s="19" t="inlineStr"/>
+      <c r="D29" s="19" t="inlineStr"/>
+      <c r="E29" s="19" t="inlineStr"/>
+      <c r="F29" s="19" t="inlineStr"/>
+      <c r="G29" s="19" t="inlineStr"/>
+      <c r="H29" s="19" t="inlineStr"/>
+      <c r="I29" s="19" t="inlineStr"/>
+      <c r="J29" s="19" t="inlineStr"/>
+      <c r="K29" s="19" t="inlineStr"/>
+      <c r="L29" s="19" t="inlineStr"/>
+      <c r="M29" s="19" t="inlineStr"/>
+      <c r="N29" s="19" t="inlineStr"/>
+      <c r="O29" s="19" t="inlineStr"/>
+      <c r="P29" s="19" t="inlineStr"/>
+      <c r="Q29" s="19" t="inlineStr"/>
+      <c r="R29" s="19" t="inlineStr"/>
+      <c r="S29" s="19" t="inlineStr"/>
+      <c r="T29" s="19" t="inlineStr"/>
+      <c r="U29" s="19" t="inlineStr"/>
+      <c r="V29" s="19" t="inlineStr"/>
+      <c r="W29" s="19" t="inlineStr"/>
+      <c r="X29" s="19" t="inlineStr"/>
+      <c r="Y29" s="19" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="n">
+      <c r="A30" s="17" t="n">
         <v>1944</v>
       </c>
-      <c r="B30" s="17" t="inlineStr">
+      <c r="B30" s="18" t="inlineStr">
         <is>
           <t>?; Missing</t>
         </is>
       </c>
-      <c r="C30" s="18" t="inlineStr"/>
-      <c r="D30" s="18" t="inlineStr"/>
-      <c r="E30" s="18" t="inlineStr"/>
-      <c r="F30" s="18" t="inlineStr"/>
-      <c r="G30" s="18" t="inlineStr"/>
-      <c r="H30" s="18" t="inlineStr"/>
-      <c r="I30" s="18" t="inlineStr"/>
-      <c r="J30" s="18" t="inlineStr"/>
-      <c r="K30" s="18" t="inlineStr"/>
-      <c r="L30" s="18" t="inlineStr"/>
-      <c r="M30" s="18" t="inlineStr"/>
-      <c r="N30" s="18" t="inlineStr"/>
-      <c r="O30" s="18" t="inlineStr"/>
-      <c r="P30" s="18" t="inlineStr"/>
-      <c r="Q30" s="18" t="inlineStr"/>
-      <c r="R30" s="18" t="inlineStr"/>
-      <c r="S30" s="18" t="inlineStr"/>
-      <c r="T30" s="18" t="inlineStr"/>
-      <c r="U30" s="18" t="inlineStr"/>
-      <c r="V30" s="18" t="inlineStr"/>
-      <c r="W30" s="18" t="inlineStr"/>
-      <c r="X30" s="18" t="inlineStr"/>
-      <c r="Y30" s="18" t="inlineStr"/>
+      <c r="C30" s="19" t="inlineStr"/>
+      <c r="D30" s="19" t="inlineStr"/>
+      <c r="E30" s="19" t="inlineStr"/>
+      <c r="F30" s="19" t="inlineStr"/>
+      <c r="G30" s="19" t="inlineStr"/>
+      <c r="H30" s="19" t="inlineStr"/>
+      <c r="I30" s="19" t="inlineStr"/>
+      <c r="J30" s="19" t="inlineStr"/>
+      <c r="K30" s="19" t="inlineStr"/>
+      <c r="L30" s="19" t="inlineStr"/>
+      <c r="M30" s="19" t="inlineStr"/>
+      <c r="N30" s="19" t="inlineStr"/>
+      <c r="O30" s="19" t="inlineStr"/>
+      <c r="P30" s="19" t="inlineStr"/>
+      <c r="Q30" s="19" t="inlineStr"/>
+      <c r="R30" s="19" t="inlineStr"/>
+      <c r="S30" s="19" t="inlineStr"/>
+      <c r="T30" s="19" t="inlineStr"/>
+      <c r="U30" s="19" t="inlineStr"/>
+      <c r="V30" s="19" t="inlineStr"/>
+      <c r="W30" s="19" t="inlineStr"/>
+      <c r="X30" s="19" t="inlineStr"/>
+      <c r="Y30" s="19" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="n">
+      <c r="A31" s="17" t="n">
         <v>1945</v>
       </c>
-      <c r="B31" s="17" t="inlineStr">
+      <c r="B31" s="18" t="inlineStr">
         <is>
           <t>?; Missing</t>
         </is>
       </c>
-      <c r="C31" s="18" t="inlineStr"/>
-      <c r="D31" s="18" t="inlineStr"/>
-      <c r="E31" s="18" t="inlineStr"/>
-      <c r="F31" s="18" t="inlineStr"/>
-      <c r="G31" s="18" t="inlineStr"/>
-      <c r="H31" s="18" t="inlineStr"/>
-      <c r="I31" s="18" t="inlineStr"/>
-      <c r="J31" s="18" t="inlineStr"/>
-      <c r="K31" s="18" t="inlineStr"/>
-      <c r="L31" s="18" t="inlineStr"/>
-      <c r="M31" s="18" t="inlineStr"/>
-      <c r="N31" s="18" t="inlineStr"/>
-      <c r="O31" s="18" t="inlineStr"/>
-      <c r="P31" s="18" t="inlineStr"/>
-      <c r="Q31" s="18" t="inlineStr"/>
-      <c r="R31" s="18" t="inlineStr"/>
-      <c r="S31" s="18" t="inlineStr"/>
-      <c r="T31" s="18" t="inlineStr"/>
-      <c r="U31" s="18" t="inlineStr"/>
-      <c r="V31" s="18" t="inlineStr"/>
-      <c r="W31" s="18" t="inlineStr"/>
-      <c r="X31" s="18" t="inlineStr"/>
-      <c r="Y31" s="18" t="inlineStr"/>
+      <c r="C31" s="19" t="inlineStr"/>
+      <c r="D31" s="19" t="inlineStr"/>
+      <c r="E31" s="19" t="inlineStr"/>
+      <c r="F31" s="19" t="inlineStr"/>
+      <c r="G31" s="19" t="inlineStr"/>
+      <c r="H31" s="19" t="inlineStr"/>
+      <c r="I31" s="19" t="inlineStr"/>
+      <c r="J31" s="19" t="inlineStr"/>
+      <c r="K31" s="19" t="inlineStr"/>
+      <c r="L31" s="19" t="inlineStr"/>
+      <c r="M31" s="19" t="inlineStr"/>
+      <c r="N31" s="19" t="inlineStr"/>
+      <c r="O31" s="19" t="inlineStr"/>
+      <c r="P31" s="19" t="inlineStr"/>
+      <c r="Q31" s="19" t="inlineStr"/>
+      <c r="R31" s="19" t="inlineStr"/>
+      <c r="S31" s="19" t="inlineStr"/>
+      <c r="T31" s="19" t="inlineStr"/>
+      <c r="U31" s="19" t="inlineStr"/>
+      <c r="V31" s="19" t="inlineStr"/>
+      <c r="W31" s="19" t="inlineStr"/>
+      <c r="X31" s="19" t="inlineStr"/>
+      <c r="Y31" s="19" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="n">
+      <c r="A32" s="17" t="n">
         <v>1946</v>
       </c>
-      <c r="B32" s="17" t="inlineStr">
+      <c r="B32" s="18" t="inlineStr">
         <is>
           <t>Pittsburgh, PA; Missing</t>
         </is>
       </c>
-      <c r="C32" s="18" t="inlineStr"/>
-      <c r="D32" s="18" t="inlineStr"/>
-      <c r="E32" s="18" t="inlineStr"/>
-      <c r="F32" s="18" t="inlineStr"/>
-      <c r="G32" s="18" t="inlineStr"/>
-      <c r="H32" s="18" t="inlineStr"/>
-      <c r="I32" s="18" t="inlineStr"/>
-      <c r="J32" s="18" t="inlineStr"/>
-      <c r="K32" s="18" t="inlineStr"/>
-      <c r="L32" s="18" t="inlineStr"/>
-      <c r="M32" s="18" t="inlineStr"/>
-      <c r="N32" s="18" t="inlineStr"/>
-      <c r="O32" s="18" t="inlineStr"/>
-      <c r="P32" s="18" t="inlineStr"/>
-      <c r="Q32" s="18" t="inlineStr"/>
-      <c r="R32" s="18" t="inlineStr"/>
-      <c r="S32" s="18" t="inlineStr"/>
-      <c r="T32" s="18" t="inlineStr"/>
-      <c r="U32" s="18" t="inlineStr"/>
-      <c r="V32" s="18" t="inlineStr"/>
-      <c r="W32" s="18" t="inlineStr"/>
-      <c r="X32" s="18" t="inlineStr"/>
-      <c r="Y32" s="18" t="inlineStr"/>
+      <c r="C32" s="19" t="inlineStr"/>
+      <c r="D32" s="19" t="inlineStr"/>
+      <c r="E32" s="19" t="inlineStr"/>
+      <c r="F32" s="19" t="inlineStr"/>
+      <c r="G32" s="19" t="inlineStr"/>
+      <c r="H32" s="19" t="inlineStr"/>
+      <c r="I32" s="19" t="inlineStr"/>
+      <c r="J32" s="19" t="inlineStr"/>
+      <c r="K32" s="19" t="inlineStr"/>
+      <c r="L32" s="19" t="inlineStr"/>
+      <c r="M32" s="19" t="inlineStr"/>
+      <c r="N32" s="19" t="inlineStr"/>
+      <c r="O32" s="19" t="inlineStr"/>
+      <c r="P32" s="19" t="inlineStr"/>
+      <c r="Q32" s="19" t="inlineStr"/>
+      <c r="R32" s="19" t="inlineStr"/>
+      <c r="S32" s="19" t="inlineStr"/>
+      <c r="T32" s="19" t="inlineStr"/>
+      <c r="U32" s="19" t="inlineStr"/>
+      <c r="V32" s="19" t="inlineStr"/>
+      <c r="W32" s="19" t="inlineStr"/>
+      <c r="X32" s="19" t="inlineStr"/>
+      <c r="Y32" s="19" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="n">
+      <c r="A33" s="17" t="n">
         <v>1947</v>
       </c>
-      <c r="B33" s="17" t="inlineStr">
+      <c r="B33" s="18" t="inlineStr">
         <is>
           <t>Higgins Lake, MI; Missing</t>
         </is>
       </c>
-      <c r="C33" s="18" t="inlineStr"/>
-      <c r="D33" s="18" t="inlineStr"/>
-      <c r="E33" s="18" t="inlineStr"/>
-      <c r="F33" s="18" t="inlineStr"/>
-      <c r="G33" s="18" t="inlineStr"/>
-      <c r="H33" s="18" t="inlineStr"/>
-      <c r="I33" s="18" t="inlineStr"/>
-      <c r="J33" s="18" t="inlineStr"/>
-      <c r="K33" s="18" t="inlineStr"/>
-      <c r="L33" s="18" t="inlineStr"/>
-      <c r="M33" s="18" t="inlineStr"/>
-      <c r="N33" s="18" t="inlineStr"/>
-      <c r="O33" s="18" t="inlineStr"/>
-      <c r="P33" s="18" t="inlineStr"/>
-      <c r="Q33" s="18" t="inlineStr"/>
-      <c r="R33" s="18" t="inlineStr"/>
-      <c r="S33" s="18" t="inlineStr"/>
-      <c r="T33" s="18" t="inlineStr"/>
-      <c r="U33" s="18" t="inlineStr"/>
-      <c r="V33" s="18" t="inlineStr"/>
-      <c r="W33" s="18" t="inlineStr"/>
-      <c r="X33" s="18" t="inlineStr"/>
-      <c r="Y33" s="18" t="inlineStr"/>
+      <c r="C33" s="19" t="inlineStr"/>
+      <c r="D33" s="19" t="inlineStr"/>
+      <c r="E33" s="19" t="inlineStr"/>
+      <c r="F33" s="19" t="inlineStr"/>
+      <c r="G33" s="19" t="inlineStr"/>
+      <c r="H33" s="19" t="inlineStr"/>
+      <c r="I33" s="19" t="inlineStr"/>
+      <c r="J33" s="19" t="inlineStr"/>
+      <c r="K33" s="19" t="inlineStr"/>
+      <c r="L33" s="19" t="inlineStr"/>
+      <c r="M33" s="19" t="inlineStr"/>
+      <c r="N33" s="19" t="inlineStr"/>
+      <c r="O33" s="19" t="inlineStr"/>
+      <c r="P33" s="19" t="inlineStr"/>
+      <c r="Q33" s="19" t="inlineStr"/>
+      <c r="R33" s="19" t="inlineStr"/>
+      <c r="S33" s="19" t="inlineStr"/>
+      <c r="T33" s="19" t="inlineStr"/>
+      <c r="U33" s="19" t="inlineStr"/>
+      <c r="V33" s="19" t="inlineStr"/>
+      <c r="W33" s="19" t="inlineStr"/>
+      <c r="X33" s="19" t="inlineStr"/>
+      <c r="Y33" s="19" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="n">
+      <c r="A34" s="17" t="n">
         <v>1948</v>
       </c>
-      <c r="B34" s="17" t="inlineStr">
+      <c r="B34" s="18" t="inlineStr">
         <is>
           <t>New Orleans, LA; Missing</t>
         </is>
       </c>
-      <c r="C34" s="18" t="inlineStr"/>
-      <c r="D34" s="18" t="inlineStr"/>
-      <c r="E34" s="18" t="inlineStr"/>
-      <c r="F34" s="18" t="inlineStr"/>
-      <c r="G34" s="18" t="inlineStr"/>
-      <c r="H34" s="18" t="inlineStr"/>
-      <c r="I34" s="18" t="inlineStr"/>
-      <c r="J34" s="18" t="inlineStr"/>
-      <c r="K34" s="18" t="inlineStr"/>
-      <c r="L34" s="18" t="inlineStr"/>
-      <c r="M34" s="18" t="inlineStr"/>
-      <c r="N34" s="18" t="inlineStr"/>
-      <c r="O34" s="18" t="inlineStr"/>
-      <c r="P34" s="18" t="inlineStr"/>
-      <c r="Q34" s="18" t="inlineStr"/>
-      <c r="R34" s="18" t="inlineStr"/>
-      <c r="S34" s="18" t="inlineStr"/>
-      <c r="T34" s="18" t="inlineStr"/>
-      <c r="U34" s="18" t="inlineStr"/>
-      <c r="V34" s="18" t="inlineStr"/>
-      <c r="W34" s="18" t="inlineStr"/>
-      <c r="X34" s="18" t="inlineStr"/>
-      <c r="Y34" s="18" t="inlineStr"/>
+      <c r="C34" s="19" t="inlineStr"/>
+      <c r="D34" s="19" t="inlineStr"/>
+      <c r="E34" s="19" t="inlineStr"/>
+      <c r="F34" s="19" t="inlineStr"/>
+      <c r="G34" s="19" t="inlineStr"/>
+      <c r="H34" s="19" t="inlineStr"/>
+      <c r="I34" s="19" t="inlineStr"/>
+      <c r="J34" s="19" t="inlineStr"/>
+      <c r="K34" s="19" t="inlineStr"/>
+      <c r="L34" s="19" t="inlineStr"/>
+      <c r="M34" s="19" t="inlineStr"/>
+      <c r="N34" s="19" t="inlineStr"/>
+      <c r="O34" s="19" t="inlineStr"/>
+      <c r="P34" s="19" t="inlineStr"/>
+      <c r="Q34" s="19" t="inlineStr"/>
+      <c r="R34" s="19" t="inlineStr"/>
+      <c r="S34" s="19" t="inlineStr"/>
+      <c r="T34" s="19" t="inlineStr"/>
+      <c r="U34" s="19" t="inlineStr"/>
+      <c r="V34" s="19" t="inlineStr"/>
+      <c r="W34" s="19" t="inlineStr"/>
+      <c r="X34" s="19" t="inlineStr"/>
+      <c r="Y34" s="19" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="n">
+      <c r="A35" s="17" t="n">
         <v>1949</v>
       </c>
-      <c r="B35" s="17" t="inlineStr">
+      <c r="B35" s="18" t="inlineStr">
         <is>
           <t>Washington, DC; Missing</t>
         </is>
       </c>
-      <c r="C35" s="18" t="inlineStr"/>
-      <c r="D35" s="18" t="inlineStr"/>
-      <c r="E35" s="18" t="inlineStr"/>
-      <c r="F35" s="18" t="inlineStr"/>
-      <c r="G35" s="18" t="inlineStr"/>
-      <c r="H35" s="18" t="inlineStr"/>
-      <c r="I35" s="18" t="inlineStr"/>
-      <c r="J35" s="18" t="inlineStr"/>
-      <c r="K35" s="18" t="inlineStr"/>
-      <c r="L35" s="18" t="inlineStr"/>
-      <c r="M35" s="18" t="inlineStr"/>
-      <c r="N35" s="18" t="inlineStr"/>
-      <c r="O35" s="18" t="inlineStr"/>
-      <c r="P35" s="18" t="inlineStr"/>
-      <c r="Q35" s="18" t="inlineStr"/>
-      <c r="R35" s="18" t="inlineStr"/>
-      <c r="S35" s="18" t="inlineStr"/>
-      <c r="T35" s="18" t="inlineStr"/>
-      <c r="U35" s="18" t="inlineStr"/>
-      <c r="V35" s="18" t="inlineStr"/>
-      <c r="W35" s="18" t="inlineStr"/>
-      <c r="X35" s="18" t="inlineStr"/>
-      <c r="Y35" s="18" t="inlineStr"/>
+      <c r="C35" s="19" t="inlineStr"/>
+      <c r="D35" s="19" t="inlineStr"/>
+      <c r="E35" s="19" t="inlineStr"/>
+      <c r="F35" s="19" t="inlineStr"/>
+      <c r="G35" s="19" t="inlineStr"/>
+      <c r="H35" s="19" t="inlineStr"/>
+      <c r="I35" s="19" t="inlineStr"/>
+      <c r="J35" s="19" t="inlineStr"/>
+      <c r="K35" s="19" t="inlineStr"/>
+      <c r="L35" s="19" t="inlineStr"/>
+      <c r="M35" s="19" t="inlineStr"/>
+      <c r="N35" s="19" t="inlineStr"/>
+      <c r="O35" s="19" t="inlineStr"/>
+      <c r="P35" s="19" t="inlineStr"/>
+      <c r="Q35" s="19" t="inlineStr"/>
+      <c r="R35" s="19" t="inlineStr"/>
+      <c r="S35" s="19" t="inlineStr"/>
+      <c r="T35" s="19" t="inlineStr"/>
+      <c r="U35" s="19" t="inlineStr"/>
+      <c r="V35" s="19" t="inlineStr"/>
+      <c r="W35" s="19" t="inlineStr"/>
+      <c r="X35" s="19" t="inlineStr"/>
+      <c r="Y35" s="19" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="n">
+      <c r="A36" s="17" t="n">
         <v>1950</v>
       </c>
-      <c r="B36" s="17" t="inlineStr">
+      <c r="B36" s="18" t="inlineStr">
         <is>
           <t>Salt Lake City, UT; Missing</t>
         </is>
       </c>
-      <c r="C36" s="18" t="inlineStr"/>
-      <c r="D36" s="18" t="inlineStr"/>
-      <c r="E36" s="18" t="inlineStr"/>
-      <c r="F36" s="18" t="inlineStr"/>
-      <c r="G36" s="18" t="inlineStr"/>
-      <c r="H36" s="18" t="inlineStr"/>
-      <c r="I36" s="18" t="inlineStr"/>
-      <c r="J36" s="18" t="inlineStr"/>
-      <c r="K36" s="18" t="inlineStr"/>
-      <c r="L36" s="18" t="inlineStr"/>
-      <c r="M36" s="18" t="inlineStr"/>
-      <c r="N36" s="18" t="inlineStr"/>
-      <c r="O36" s="18" t="inlineStr"/>
-      <c r="P36" s="18" t="inlineStr"/>
-      <c r="Q36" s="18" t="inlineStr"/>
-      <c r="R36" s="18" t="inlineStr"/>
-      <c r="S36" s="18" t="inlineStr"/>
-      <c r="T36" s="18" t="inlineStr"/>
-      <c r="U36" s="18" t="inlineStr"/>
-      <c r="V36" s="18" t="inlineStr"/>
-      <c r="W36" s="18" t="inlineStr"/>
-      <c r="X36" s="18" t="inlineStr"/>
-      <c r="Y36" s="18" t="inlineStr"/>
+      <c r="C36" s="19" t="inlineStr"/>
+      <c r="D36" s="19" t="inlineStr"/>
+      <c r="E36" s="19" t="inlineStr"/>
+      <c r="F36" s="19" t="inlineStr"/>
+      <c r="G36" s="19" t="inlineStr"/>
+      <c r="H36" s="19" t="inlineStr"/>
+      <c r="I36" s="19" t="inlineStr"/>
+      <c r="J36" s="19" t="inlineStr"/>
+      <c r="K36" s="19" t="inlineStr"/>
+      <c r="L36" s="19" t="inlineStr"/>
+      <c r="M36" s="19" t="inlineStr"/>
+      <c r="N36" s="19" t="inlineStr"/>
+      <c r="O36" s="19" t="inlineStr"/>
+      <c r="P36" s="19" t="inlineStr"/>
+      <c r="Q36" s="19" t="inlineStr"/>
+      <c r="R36" s="19" t="inlineStr"/>
+      <c r="S36" s="19" t="inlineStr"/>
+      <c r="T36" s="19" t="inlineStr"/>
+      <c r="U36" s="19" t="inlineStr"/>
+      <c r="V36" s="19" t="inlineStr"/>
+      <c r="W36" s="19" t="inlineStr"/>
+      <c r="X36" s="19" t="inlineStr"/>
+      <c r="Y36" s="19" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="n">
+      <c r="A37" s="17" t="n">
         <v>1951</v>
       </c>
-      <c r="B37" s="17" t="inlineStr">
+      <c r="B37" s="18" t="inlineStr">
         <is>
           <t>Chicago, IL; Missing</t>
         </is>
       </c>
-      <c r="C37" s="18" t="inlineStr"/>
-      <c r="D37" s="18" t="inlineStr"/>
-      <c r="E37" s="18" t="inlineStr"/>
-      <c r="F37" s="18" t="inlineStr"/>
-      <c r="G37" s="18" t="inlineStr"/>
-      <c r="H37" s="18" t="inlineStr"/>
-      <c r="I37" s="18" t="inlineStr"/>
-      <c r="J37" s="18" t="inlineStr"/>
-      <c r="K37" s="18" t="inlineStr"/>
-      <c r="L37" s="18" t="inlineStr"/>
-      <c r="M37" s="18" t="inlineStr"/>
-      <c r="N37" s="18" t="inlineStr"/>
-      <c r="O37" s="18" t="inlineStr"/>
-      <c r="P37" s="18" t="inlineStr"/>
-      <c r="Q37" s="18" t="inlineStr"/>
-      <c r="R37" s="18" t="inlineStr"/>
-      <c r="S37" s="18" t="inlineStr"/>
-      <c r="T37" s="18" t="inlineStr"/>
-      <c r="U37" s="18" t="inlineStr"/>
-      <c r="V37" s="18" t="inlineStr"/>
-      <c r="W37" s="18" t="inlineStr"/>
-      <c r="X37" s="18" t="inlineStr"/>
-      <c r="Y37" s="18" t="inlineStr"/>
+      <c r="C37" s="19" t="inlineStr"/>
+      <c r="D37" s="19" t="inlineStr"/>
+      <c r="E37" s="19" t="inlineStr"/>
+      <c r="F37" s="19" t="inlineStr"/>
+      <c r="G37" s="19" t="inlineStr"/>
+      <c r="H37" s="19" t="inlineStr"/>
+      <c r="I37" s="19" t="inlineStr"/>
+      <c r="J37" s="19" t="inlineStr"/>
+      <c r="K37" s="19" t="inlineStr"/>
+      <c r="L37" s="19" t="inlineStr"/>
+      <c r="M37" s="19" t="inlineStr"/>
+      <c r="N37" s="19" t="inlineStr"/>
+      <c r="O37" s="19" t="inlineStr"/>
+      <c r="P37" s="19" t="inlineStr"/>
+      <c r="Q37" s="19" t="inlineStr"/>
+      <c r="R37" s="19" t="inlineStr"/>
+      <c r="S37" s="19" t="inlineStr"/>
+      <c r="T37" s="19" t="inlineStr"/>
+      <c r="U37" s="19" t="inlineStr"/>
+      <c r="V37" s="19" t="inlineStr"/>
+      <c r="W37" s="19" t="inlineStr"/>
+      <c r="X37" s="19" t="inlineStr"/>
+      <c r="Y37" s="19" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="n">
+      <c r="A38" s="17" t="n">
         <v>1952</v>
       </c>
-      <c r="B38" s="17" t="inlineStr">
+      <c r="B38" s="18" t="inlineStr">
         <is>
           <t>Austin, TX; Missing</t>
         </is>
       </c>
-      <c r="C38" s="18" t="inlineStr"/>
-      <c r="D38" s="18" t="inlineStr"/>
-      <c r="E38" s="18" t="inlineStr"/>
-      <c r="F38" s="18" t="inlineStr"/>
-      <c r="G38" s="18" t="inlineStr"/>
-      <c r="H38" s="18" t="inlineStr"/>
-      <c r="I38" s="18" t="inlineStr"/>
-      <c r="J38" s="18" t="inlineStr"/>
-      <c r="K38" s="18" t="inlineStr"/>
-      <c r="L38" s="18" t="inlineStr"/>
-      <c r="M38" s="18" t="inlineStr"/>
-      <c r="N38" s="18" t="inlineStr"/>
-      <c r="O38" s="18" t="inlineStr"/>
-      <c r="P38" s="18" t="inlineStr"/>
-      <c r="Q38" s="18" t="inlineStr"/>
-      <c r="R38" s="18" t="inlineStr"/>
-      <c r="S38" s="18" t="inlineStr"/>
-      <c r="T38" s="18" t="inlineStr"/>
-      <c r="U38" s="18" t="inlineStr"/>
-      <c r="V38" s="18" t="inlineStr"/>
-      <c r="W38" s="18" t="inlineStr"/>
-      <c r="X38" s="18" t="inlineStr"/>
-      <c r="Y38" s="18" t="inlineStr"/>
+      <c r="C38" s="19" t="inlineStr"/>
+      <c r="D38" s="19" t="inlineStr"/>
+      <c r="E38" s="19" t="inlineStr"/>
+      <c r="F38" s="19" t="inlineStr"/>
+      <c r="G38" s="19" t="inlineStr"/>
+      <c r="H38" s="19" t="inlineStr"/>
+      <c r="I38" s="19" t="inlineStr"/>
+      <c r="J38" s="19" t="inlineStr"/>
+      <c r="K38" s="19" t="inlineStr"/>
+      <c r="L38" s="19" t="inlineStr"/>
+      <c r="M38" s="19" t="inlineStr"/>
+      <c r="N38" s="19" t="inlineStr"/>
+      <c r="O38" s="19" t="inlineStr"/>
+      <c r="P38" s="19" t="inlineStr"/>
+      <c r="Q38" s="19" t="inlineStr"/>
+      <c r="R38" s="19" t="inlineStr"/>
+      <c r="S38" s="19" t="inlineStr"/>
+      <c r="T38" s="19" t="inlineStr"/>
+      <c r="U38" s="19" t="inlineStr"/>
+      <c r="V38" s="19" t="inlineStr"/>
+      <c r="W38" s="19" t="inlineStr"/>
+      <c r="X38" s="19" t="inlineStr"/>
+      <c r="Y38" s="19" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="n">
+      <c r="A39" s="17" t="n">
         <v>1953</v>
       </c>
-      <c r="B39" s="17" t="inlineStr">
+      <c r="B39" s="18" t="inlineStr">
         <is>
           <t>New York, NY; Missing</t>
         </is>
       </c>
-      <c r="C39" s="18" t="inlineStr"/>
-      <c r="D39" s="18" t="inlineStr"/>
-      <c r="E39" s="18" t="inlineStr"/>
-      <c r="F39" s="18" t="inlineStr"/>
-      <c r="G39" s="18" t="inlineStr"/>
-      <c r="H39" s="18" t="inlineStr"/>
-      <c r="I39" s="18" t="inlineStr"/>
-      <c r="J39" s="18" t="inlineStr"/>
-      <c r="K39" s="18" t="inlineStr"/>
-      <c r="L39" s="18" t="inlineStr"/>
-      <c r="M39" s="18" t="inlineStr"/>
-      <c r="N39" s="18" t="inlineStr"/>
-      <c r="O39" s="18" t="inlineStr"/>
-      <c r="P39" s="18" t="inlineStr"/>
-      <c r="Q39" s="18" t="inlineStr"/>
-      <c r="R39" s="18" t="inlineStr"/>
-      <c r="S39" s="18" t="inlineStr"/>
-      <c r="T39" s="18" t="inlineStr"/>
-      <c r="U39" s="18" t="inlineStr"/>
-      <c r="V39" s="18" t="inlineStr"/>
-      <c r="W39" s="18" t="inlineStr"/>
-      <c r="X39" s="18" t="inlineStr"/>
-      <c r="Y39" s="18" t="inlineStr"/>
+      <c r="C39" s="19" t="inlineStr"/>
+      <c r="D39" s="19" t="inlineStr"/>
+      <c r="E39" s="19" t="inlineStr"/>
+      <c r="F39" s="19" t="inlineStr"/>
+      <c r="G39" s="19" t="inlineStr"/>
+      <c r="H39" s="19" t="inlineStr"/>
+      <c r="I39" s="19" t="inlineStr"/>
+      <c r="J39" s="19" t="inlineStr"/>
+      <c r="K39" s="19" t="inlineStr"/>
+      <c r="L39" s="19" t="inlineStr"/>
+      <c r="M39" s="19" t="inlineStr"/>
+      <c r="N39" s="19" t="inlineStr"/>
+      <c r="O39" s="19" t="inlineStr"/>
+      <c r="P39" s="19" t="inlineStr"/>
+      <c r="Q39" s="19" t="inlineStr"/>
+      <c r="R39" s="19" t="inlineStr"/>
+      <c r="S39" s="19" t="inlineStr"/>
+      <c r="T39" s="19" t="inlineStr"/>
+      <c r="U39" s="19" t="inlineStr"/>
+      <c r="V39" s="19" t="inlineStr"/>
+      <c r="W39" s="19" t="inlineStr"/>
+      <c r="X39" s="19" t="inlineStr"/>
+      <c r="Y39" s="19" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="16" t="n">
+      <c r="A40" s="17" t="n">
         <v>1954</v>
       </c>
-      <c r="B40" s="17" t="inlineStr">
+      <c r="B40" s="18" t="inlineStr">
         <is>
           <t>Gainesville, FL; Missing</t>
         </is>
       </c>
-      <c r="C40" s="18" t="inlineStr"/>
-      <c r="D40" s="18" t="inlineStr"/>
-      <c r="E40" s="18" t="inlineStr"/>
-      <c r="F40" s="18" t="inlineStr"/>
-      <c r="G40" s="18" t="inlineStr"/>
-      <c r="H40" s="18" t="inlineStr"/>
-      <c r="I40" s="18" t="inlineStr"/>
-      <c r="J40" s="18" t="inlineStr"/>
-      <c r="K40" s="18" t="inlineStr"/>
-      <c r="L40" s="18" t="inlineStr"/>
-      <c r="M40" s="18" t="inlineStr"/>
-      <c r="N40" s="18" t="inlineStr"/>
-      <c r="O40" s="18" t="inlineStr"/>
-      <c r="P40" s="18" t="inlineStr"/>
-      <c r="Q40" s="18" t="inlineStr"/>
-      <c r="R40" s="18" t="inlineStr"/>
-      <c r="S40" s="18" t="inlineStr"/>
-      <c r="T40" s="18" t="inlineStr"/>
-      <c r="U40" s="18" t="inlineStr"/>
-      <c r="V40" s="18" t="inlineStr"/>
-      <c r="W40" s="18" t="inlineStr"/>
-      <c r="X40" s="18" t="inlineStr"/>
-      <c r="Y40" s="18" t="inlineStr"/>
+      <c r="C40" s="19" t="inlineStr"/>
+      <c r="D40" s="19" t="inlineStr"/>
+      <c r="E40" s="19" t="inlineStr"/>
+      <c r="F40" s="19" t="inlineStr"/>
+      <c r="G40" s="19" t="inlineStr"/>
+      <c r="H40" s="19" t="inlineStr"/>
+      <c r="I40" s="19" t="inlineStr"/>
+      <c r="J40" s="19" t="inlineStr"/>
+      <c r="K40" s="19" t="inlineStr"/>
+      <c r="L40" s="19" t="inlineStr"/>
+      <c r="M40" s="19" t="inlineStr"/>
+      <c r="N40" s="19" t="inlineStr"/>
+      <c r="O40" s="19" t="inlineStr"/>
+      <c r="P40" s="19" t="inlineStr"/>
+      <c r="Q40" s="19" t="inlineStr"/>
+      <c r="R40" s="19" t="inlineStr"/>
+      <c r="S40" s="19" t="inlineStr"/>
+      <c r="T40" s="19" t="inlineStr"/>
+      <c r="U40" s="19" t="inlineStr"/>
+      <c r="V40" s="19" t="inlineStr"/>
+      <c r="W40" s="19" t="inlineStr"/>
+      <c r="X40" s="19" t="inlineStr"/>
+      <c r="Y40" s="19" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="16" t="n">
+      <c r="A41" s="17" t="n">
         <v>1955</v>
       </c>
-      <c r="B41" s="17" t="inlineStr">
+      <c r="B41" s="18" t="inlineStr">
         <is>
           <t>San Francisco, CA; Missing</t>
         </is>
       </c>
-      <c r="C41" s="18" t="inlineStr"/>
-      <c r="D41" s="18" t="inlineStr"/>
-      <c r="E41" s="18" t="inlineStr"/>
-      <c r="F41" s="18" t="inlineStr"/>
-      <c r="G41" s="18" t="inlineStr"/>
-      <c r="H41" s="18" t="inlineStr"/>
-      <c r="I41" s="18" t="inlineStr"/>
-      <c r="J41" s="18" t="inlineStr"/>
-      <c r="K41" s="18" t="inlineStr"/>
-      <c r="L41" s="18" t="inlineStr"/>
-      <c r="M41" s="18" t="inlineStr"/>
-      <c r="N41" s="18" t="inlineStr"/>
-      <c r="O41" s="18" t="inlineStr"/>
-      <c r="P41" s="18" t="inlineStr"/>
-      <c r="Q41" s="18" t="inlineStr"/>
-      <c r="R41" s="18" t="inlineStr"/>
-      <c r="S41" s="18" t="inlineStr"/>
-      <c r="T41" s="18" t="inlineStr"/>
-      <c r="U41" s="18" t="inlineStr"/>
-      <c r="V41" s="18" t="inlineStr"/>
-      <c r="W41" s="18" t="inlineStr"/>
-      <c r="X41" s="18" t="inlineStr"/>
-      <c r="Y41" s="18" t="inlineStr"/>
+      <c r="C41" s="19" t="inlineStr"/>
+      <c r="D41" s="19" t="inlineStr"/>
+      <c r="E41" s="19" t="inlineStr"/>
+      <c r="F41" s="19" t="inlineStr"/>
+      <c r="G41" s="19" t="inlineStr"/>
+      <c r="H41" s="19" t="inlineStr"/>
+      <c r="I41" s="19" t="inlineStr"/>
+      <c r="J41" s="19" t="inlineStr"/>
+      <c r="K41" s="19" t="inlineStr"/>
+      <c r="L41" s="19" t="inlineStr"/>
+      <c r="M41" s="19" t="inlineStr"/>
+      <c r="N41" s="19" t="inlineStr"/>
+      <c r="O41" s="19" t="inlineStr"/>
+      <c r="P41" s="19" t="inlineStr"/>
+      <c r="Q41" s="19" t="inlineStr"/>
+      <c r="R41" s="19" t="inlineStr"/>
+      <c r="S41" s="19" t="inlineStr"/>
+      <c r="T41" s="19" t="inlineStr"/>
+      <c r="U41" s="19" t="inlineStr"/>
+      <c r="V41" s="19" t="inlineStr"/>
+      <c r="W41" s="19" t="inlineStr"/>
+      <c r="X41" s="19" t="inlineStr"/>
+      <c r="Y41" s="19" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="16" t="n">
+      <c r="A42" s="17" t="n">
         <v>1956</v>
       </c>
-      <c r="B42" s="17" t="inlineStr">
+      <c r="B42" s="18" t="inlineStr">
         <is>
           <t>Higgins Lake, MI; Missing</t>
         </is>
       </c>
-      <c r="C42" s="18" t="inlineStr"/>
-      <c r="D42" s="18" t="inlineStr"/>
-      <c r="E42" s="18" t="inlineStr"/>
-      <c r="F42" s="18" t="inlineStr"/>
-      <c r="G42" s="18" t="inlineStr"/>
-      <c r="H42" s="18" t="inlineStr"/>
-      <c r="I42" s="18" t="inlineStr"/>
-      <c r="J42" s="18" t="inlineStr"/>
-      <c r="K42" s="18" t="inlineStr"/>
-      <c r="L42" s="18" t="inlineStr"/>
-      <c r="M42" s="18" t="inlineStr"/>
-      <c r="N42" s="18" t="inlineStr"/>
-      <c r="O42" s="18" t="inlineStr"/>
-      <c r="P42" s="18" t="inlineStr"/>
-      <c r="Q42" s="18" t="inlineStr"/>
-      <c r="R42" s="18" t="inlineStr"/>
-      <c r="S42" s="18" t="inlineStr"/>
-      <c r="T42" s="18" t="inlineStr"/>
-      <c r="U42" s="18" t="inlineStr"/>
-      <c r="V42" s="18" t="inlineStr"/>
-      <c r="W42" s="18" t="inlineStr"/>
-      <c r="X42" s="18" t="inlineStr"/>
-      <c r="Y42" s="18" t="inlineStr"/>
+      <c r="C42" s="19" t="inlineStr"/>
+      <c r="D42" s="19" t="inlineStr"/>
+      <c r="E42" s="19" t="inlineStr"/>
+      <c r="F42" s="19" t="inlineStr"/>
+      <c r="G42" s="19" t="inlineStr"/>
+      <c r="H42" s="19" t="inlineStr"/>
+      <c r="I42" s="19" t="inlineStr"/>
+      <c r="J42" s="19" t="inlineStr"/>
+      <c r="K42" s="19" t="inlineStr"/>
+      <c r="L42" s="19" t="inlineStr"/>
+      <c r="M42" s="19" t="inlineStr"/>
+      <c r="N42" s="19" t="inlineStr"/>
+      <c r="O42" s="19" t="inlineStr"/>
+      <c r="P42" s="19" t="inlineStr"/>
+      <c r="Q42" s="19" t="inlineStr"/>
+      <c r="R42" s="19" t="inlineStr"/>
+      <c r="S42" s="19" t="inlineStr"/>
+      <c r="T42" s="19" t="inlineStr"/>
+      <c r="U42" s="19" t="inlineStr"/>
+      <c r="V42" s="19" t="inlineStr"/>
+      <c r="W42" s="19" t="inlineStr"/>
+      <c r="X42" s="19" t="inlineStr"/>
+      <c r="Y42" s="19" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="16" t="n">
+      <c r="A43" s="17" t="n">
         <v>1957</v>
       </c>
-      <c r="B43" s="17" t="inlineStr">
+      <c r="B43" s="18" t="inlineStr">
         <is>
           <t>New Orleans, LA; Missing</t>
         </is>
       </c>
-      <c r="C43" s="18" t="inlineStr"/>
-      <c r="D43" s="18" t="inlineStr"/>
-      <c r="E43" s="18" t="inlineStr"/>
-      <c r="F43" s="18" t="inlineStr"/>
-      <c r="G43" s="18" t="inlineStr"/>
-      <c r="H43" s="18" t="inlineStr"/>
-      <c r="I43" s="18" t="inlineStr"/>
-      <c r="J43" s="18" t="inlineStr"/>
-      <c r="K43" s="18" t="inlineStr"/>
-      <c r="L43" s="18" t="inlineStr"/>
-      <c r="M43" s="18" t="inlineStr"/>
-      <c r="N43" s="18" t="inlineStr"/>
-      <c r="O43" s="18" t="inlineStr"/>
-      <c r="P43" s="18" t="inlineStr"/>
-      <c r="Q43" s="18" t="inlineStr"/>
-      <c r="R43" s="18" t="inlineStr"/>
-      <c r="S43" s="18" t="inlineStr"/>
-      <c r="T43" s="18" t="inlineStr"/>
-      <c r="U43" s="18" t="inlineStr"/>
-      <c r="V43" s="18" t="inlineStr"/>
-      <c r="W43" s="18" t="inlineStr"/>
-      <c r="X43" s="18" t="inlineStr"/>
-      <c r="Y43" s="18" t="inlineStr"/>
+      <c r="C43" s="19" t="inlineStr"/>
+      <c r="D43" s="19" t="inlineStr"/>
+      <c r="E43" s="19" t="inlineStr"/>
+      <c r="F43" s="19" t="inlineStr"/>
+      <c r="G43" s="19" t="inlineStr"/>
+      <c r="H43" s="19" t="inlineStr"/>
+      <c r="I43" s="19" t="inlineStr"/>
+      <c r="J43" s="19" t="inlineStr"/>
+      <c r="K43" s="19" t="inlineStr"/>
+      <c r="L43" s="19" t="inlineStr"/>
+      <c r="M43" s="19" t="inlineStr"/>
+      <c r="N43" s="19" t="inlineStr"/>
+      <c r="O43" s="19" t="inlineStr"/>
+      <c r="P43" s="19" t="inlineStr"/>
+      <c r="Q43" s="19" t="inlineStr"/>
+      <c r="R43" s="19" t="inlineStr"/>
+      <c r="S43" s="19" t="inlineStr"/>
+      <c r="T43" s="19" t="inlineStr"/>
+      <c r="U43" s="19" t="inlineStr"/>
+      <c r="V43" s="19" t="inlineStr"/>
+      <c r="W43" s="19" t="inlineStr"/>
+      <c r="X43" s="19" t="inlineStr"/>
+      <c r="Y43" s="19" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="16" t="n">
+      <c r="A44" s="17" t="n">
         <v>1958</v>
       </c>
-      <c r="B44" s="17" t="inlineStr">
+      <c r="B44" s="18" t="inlineStr">
         <is>
           <t>Bloomington, IN; Missing</t>
         </is>
       </c>
-      <c r="C44" s="18" t="inlineStr"/>
-      <c r="D44" s="18" t="inlineStr"/>
-      <c r="E44" s="18" t="inlineStr"/>
-      <c r="F44" s="18" t="inlineStr"/>
-      <c r="G44" s="18" t="inlineStr"/>
-      <c r="H44" s="18" t="inlineStr"/>
-      <c r="I44" s="18" t="inlineStr"/>
-      <c r="J44" s="18" t="inlineStr"/>
-      <c r="K44" s="18" t="inlineStr"/>
-      <c r="L44" s="18" t="inlineStr"/>
-      <c r="M44" s="18" t="inlineStr"/>
-      <c r="N44" s="18" t="inlineStr"/>
-      <c r="O44" s="18" t="inlineStr"/>
-      <c r="P44" s="18" t="inlineStr"/>
-      <c r="Q44" s="18" t="inlineStr"/>
-      <c r="R44" s="18" t="inlineStr"/>
-      <c r="S44" s="18" t="inlineStr"/>
-      <c r="T44" s="18" t="inlineStr"/>
-      <c r="U44" s="18" t="inlineStr"/>
-      <c r="V44" s="18" t="inlineStr"/>
-      <c r="W44" s="18" t="inlineStr"/>
-      <c r="X44" s="18" t="inlineStr"/>
-      <c r="Y44" s="18" t="inlineStr"/>
+      <c r="C44" s="19" t="inlineStr"/>
+      <c r="D44" s="19" t="inlineStr"/>
+      <c r="E44" s="19" t="inlineStr"/>
+      <c r="F44" s="19" t="inlineStr"/>
+      <c r="G44" s="19" t="inlineStr"/>
+      <c r="H44" s="19" t="inlineStr"/>
+      <c r="I44" s="19" t="inlineStr"/>
+      <c r="J44" s="19" t="inlineStr"/>
+      <c r="K44" s="19" t="inlineStr"/>
+      <c r="L44" s="19" t="inlineStr"/>
+      <c r="M44" s="19" t="inlineStr"/>
+      <c r="N44" s="19" t="inlineStr"/>
+      <c r="O44" s="19" t="inlineStr"/>
+      <c r="P44" s="19" t="inlineStr"/>
+      <c r="Q44" s="19" t="inlineStr"/>
+      <c r="R44" s="19" t="inlineStr"/>
+      <c r="S44" s="19" t="inlineStr"/>
+      <c r="T44" s="19" t="inlineStr"/>
+      <c r="U44" s="19" t="inlineStr"/>
+      <c r="V44" s="19" t="inlineStr"/>
+      <c r="W44" s="19" t="inlineStr"/>
+      <c r="X44" s="19" t="inlineStr"/>
+      <c r="Y44" s="19" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="n">
+      <c r="A45" s="17" t="n">
         <v>1959</v>
       </c>
-      <c r="B45" s="17" t="inlineStr">
+      <c r="B45" s="18" t="inlineStr">
         <is>
           <t>San Diego, CA; Missing</t>
         </is>
       </c>
-      <c r="C45" s="18" t="inlineStr"/>
-      <c r="D45" s="18" t="inlineStr"/>
-      <c r="E45" s="18" t="inlineStr"/>
-      <c r="F45" s="18" t="inlineStr"/>
-      <c r="G45" s="18" t="inlineStr"/>
-      <c r="H45" s="18" t="inlineStr"/>
-      <c r="I45" s="18" t="inlineStr"/>
-      <c r="J45" s="18" t="inlineStr"/>
-      <c r="K45" s="18" t="inlineStr"/>
-      <c r="L45" s="18" t="inlineStr"/>
-      <c r="M45" s="18" t="inlineStr"/>
-      <c r="N45" s="18" t="inlineStr"/>
-      <c r="O45" s="18" t="inlineStr"/>
-      <c r="P45" s="18" t="inlineStr"/>
-      <c r="Q45" s="18" t="inlineStr"/>
-      <c r="R45" s="18" t="inlineStr"/>
-      <c r="S45" s="18" t="inlineStr"/>
-      <c r="T45" s="18" t="inlineStr"/>
-      <c r="U45" s="18" t="inlineStr"/>
-      <c r="V45" s="18" t="inlineStr"/>
-      <c r="W45" s="18" t="inlineStr"/>
-      <c r="X45" s="18" t="inlineStr"/>
-      <c r="Y45" s="18" t="inlineStr"/>
+      <c r="C45" s="19" t="inlineStr"/>
+      <c r="D45" s="19" t="inlineStr"/>
+      <c r="E45" s="19" t="inlineStr"/>
+      <c r="F45" s="19" t="inlineStr"/>
+      <c r="G45" s="19" t="inlineStr"/>
+      <c r="H45" s="19" t="inlineStr"/>
+      <c r="I45" s="19" t="inlineStr"/>
+      <c r="J45" s="19" t="inlineStr"/>
+      <c r="K45" s="19" t="inlineStr"/>
+      <c r="L45" s="19" t="inlineStr"/>
+      <c r="M45" s="19" t="inlineStr"/>
+      <c r="N45" s="19" t="inlineStr"/>
+      <c r="O45" s="19" t="inlineStr"/>
+      <c r="P45" s="19" t="inlineStr"/>
+      <c r="Q45" s="19" t="inlineStr"/>
+      <c r="R45" s="19" t="inlineStr"/>
+      <c r="S45" s="19" t="inlineStr"/>
+      <c r="T45" s="19" t="inlineStr"/>
+      <c r="U45" s="19" t="inlineStr"/>
+      <c r="V45" s="19" t="inlineStr"/>
+      <c r="W45" s="19" t="inlineStr"/>
+      <c r="X45" s="19" t="inlineStr"/>
+      <c r="Y45" s="19" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="16" t="n">
+      <c r="A46" s="17" t="n">
         <v>1960</v>
       </c>
-      <c r="B46" s="17" t="inlineStr">
+      <c r="B46" s="18" t="inlineStr">
         <is>
           <t>Chicago, IL; Missing</t>
         </is>
       </c>
-      <c r="C46" s="18" t="inlineStr"/>
-      <c r="D46" s="18" t="inlineStr"/>
-      <c r="E46" s="18" t="inlineStr"/>
-      <c r="F46" s="18" t="inlineStr"/>
-      <c r="G46" s="18" t="inlineStr"/>
-      <c r="H46" s="18" t="inlineStr"/>
-      <c r="I46" s="18" t="inlineStr"/>
-      <c r="J46" s="18" t="inlineStr"/>
-      <c r="K46" s="18" t="inlineStr"/>
-      <c r="L46" s="18" t="inlineStr"/>
-      <c r="M46" s="18" t="inlineStr"/>
-      <c r="N46" s="18" t="inlineStr"/>
-      <c r="O46" s="18" t="inlineStr"/>
-      <c r="P46" s="18" t="inlineStr"/>
-      <c r="Q46" s="18" t="inlineStr"/>
-      <c r="R46" s="18" t="inlineStr"/>
-      <c r="S46" s="18" t="inlineStr"/>
-      <c r="T46" s="18" t="inlineStr"/>
-      <c r="U46" s="18" t="inlineStr"/>
-      <c r="V46" s="18" t="inlineStr"/>
-      <c r="W46" s="18" t="inlineStr"/>
-      <c r="X46" s="18" t="inlineStr"/>
-      <c r="Y46" s="18" t="inlineStr"/>
+      <c r="C46" s="19" t="inlineStr"/>
+      <c r="D46" s="19" t="inlineStr"/>
+      <c r="E46" s="19" t="inlineStr"/>
+      <c r="F46" s="19" t="inlineStr"/>
+      <c r="G46" s="19" t="inlineStr"/>
+      <c r="H46" s="19" t="inlineStr"/>
+      <c r="I46" s="19" t="inlineStr"/>
+      <c r="J46" s="19" t="inlineStr"/>
+      <c r="K46" s="19" t="inlineStr"/>
+      <c r="L46" s="19" t="inlineStr"/>
+      <c r="M46" s="19" t="inlineStr"/>
+      <c r="N46" s="19" t="inlineStr"/>
+      <c r="O46" s="19" t="inlineStr"/>
+      <c r="P46" s="19" t="inlineStr"/>
+      <c r="Q46" s="19" t="inlineStr"/>
+      <c r="R46" s="19" t="inlineStr"/>
+      <c r="S46" s="19" t="inlineStr"/>
+      <c r="T46" s="19" t="inlineStr"/>
+      <c r="U46" s="19" t="inlineStr"/>
+      <c r="V46" s="19" t="inlineStr"/>
+      <c r="W46" s="19" t="inlineStr"/>
+      <c r="X46" s="19" t="inlineStr"/>
+      <c r="Y46" s="19" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="16" t="n">
+      <c r="A47" s="17" t="n">
         <v>1961</v>
       </c>
-      <c r="B47" s="17" t="inlineStr">
+      <c r="B47" s="18" t="inlineStr">
         <is>
           <t>Austin, TX; Missing</t>
         </is>
       </c>
-      <c r="C47" s="18" t="inlineStr"/>
-      <c r="D47" s="18" t="inlineStr"/>
-      <c r="E47" s="18" t="inlineStr"/>
-      <c r="F47" s="18" t="inlineStr"/>
-      <c r="G47" s="18" t="inlineStr"/>
-      <c r="H47" s="18" t="inlineStr"/>
-      <c r="I47" s="18" t="inlineStr"/>
-      <c r="J47" s="18" t="inlineStr"/>
-      <c r="K47" s="18" t="inlineStr"/>
-      <c r="L47" s="18" t="inlineStr"/>
-      <c r="M47" s="18" t="inlineStr"/>
-      <c r="N47" s="18" t="inlineStr"/>
-      <c r="O47" s="18" t="inlineStr"/>
-      <c r="P47" s="18" t="inlineStr"/>
-      <c r="Q47" s="18" t="inlineStr"/>
-      <c r="R47" s="18" t="inlineStr"/>
-      <c r="S47" s="18" t="inlineStr"/>
-      <c r="T47" s="18" t="inlineStr"/>
-      <c r="U47" s="18" t="inlineStr"/>
-      <c r="V47" s="18" t="inlineStr"/>
-      <c r="W47" s="18" t="inlineStr"/>
-      <c r="X47" s="18" t="inlineStr"/>
-      <c r="Y47" s="18" t="inlineStr"/>
+      <c r="C47" s="19" t="inlineStr"/>
+      <c r="D47" s="19" t="inlineStr"/>
+      <c r="E47" s="19" t="inlineStr"/>
+      <c r="F47" s="19" t="inlineStr"/>
+      <c r="G47" s="19" t="inlineStr"/>
+      <c r="H47" s="19" t="inlineStr"/>
+      <c r="I47" s="19" t="inlineStr"/>
+      <c r="J47" s="19" t="inlineStr"/>
+      <c r="K47" s="19" t="inlineStr"/>
+      <c r="L47" s="19" t="inlineStr"/>
+      <c r="M47" s="19" t="inlineStr"/>
+      <c r="N47" s="19" t="inlineStr"/>
+      <c r="O47" s="19" t="inlineStr"/>
+      <c r="P47" s="19" t="inlineStr"/>
+      <c r="Q47" s="19" t="inlineStr"/>
+      <c r="R47" s="19" t="inlineStr"/>
+      <c r="S47" s="19" t="inlineStr"/>
+      <c r="T47" s="19" t="inlineStr"/>
+      <c r="U47" s="19" t="inlineStr"/>
+      <c r="V47" s="19" t="inlineStr"/>
+      <c r="W47" s="19" t="inlineStr"/>
+      <c r="X47" s="19" t="inlineStr"/>
+      <c r="Y47" s="19" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="16" t="n">
+      <c r="A48" s="17" t="n">
         <v>1962</v>
       </c>
-      <c r="B48" s="17" t="inlineStr">
+      <c r="B48" s="18" t="inlineStr">
         <is>
           <t>Washington, DC; Missing</t>
         </is>
       </c>
-      <c r="C48" s="18" t="inlineStr"/>
-      <c r="D48" s="18" t="inlineStr"/>
-      <c r="E48" s="18" t="inlineStr"/>
-      <c r="F48" s="18" t="inlineStr"/>
-      <c r="G48" s="18" t="inlineStr"/>
-      <c r="H48" s="18" t="inlineStr"/>
-      <c r="I48" s="18" t="inlineStr"/>
-      <c r="J48" s="18" t="inlineStr"/>
-      <c r="K48" s="18" t="inlineStr"/>
-      <c r="L48" s="18" t="inlineStr"/>
-      <c r="M48" s="18" t="inlineStr"/>
-      <c r="N48" s="18" t="inlineStr"/>
-      <c r="O48" s="18" t="inlineStr"/>
-      <c r="P48" s="18" t="inlineStr"/>
-      <c r="Q48" s="18" t="inlineStr"/>
-      <c r="R48" s="18" t="inlineStr"/>
-      <c r="S48" s="18" t="inlineStr"/>
-      <c r="T48" s="18" t="inlineStr"/>
-      <c r="U48" s="18" t="inlineStr"/>
-      <c r="V48" s="18" t="inlineStr"/>
-      <c r="W48" s="18" t="inlineStr"/>
-      <c r="X48" s="18" t="inlineStr"/>
-      <c r="Y48" s="18" t="inlineStr"/>
+      <c r="C48" s="19" t="inlineStr"/>
+      <c r="D48" s="19" t="inlineStr"/>
+      <c r="E48" s="19" t="inlineStr"/>
+      <c r="F48" s="19" t="inlineStr"/>
+      <c r="G48" s="19" t="inlineStr"/>
+      <c r="H48" s="19" t="inlineStr"/>
+      <c r="I48" s="19" t="inlineStr"/>
+      <c r="J48" s="19" t="inlineStr"/>
+      <c r="K48" s="19" t="inlineStr"/>
+      <c r="L48" s="19" t="inlineStr"/>
+      <c r="M48" s="19" t="inlineStr"/>
+      <c r="N48" s="19" t="inlineStr"/>
+      <c r="O48" s="19" t="inlineStr"/>
+      <c r="P48" s="19" t="inlineStr"/>
+      <c r="Q48" s="19" t="inlineStr"/>
+      <c r="R48" s="19" t="inlineStr"/>
+      <c r="S48" s="19" t="inlineStr"/>
+      <c r="T48" s="19" t="inlineStr"/>
+      <c r="U48" s="19" t="inlineStr"/>
+      <c r="V48" s="19" t="inlineStr"/>
+      <c r="W48" s="19" t="inlineStr"/>
+      <c r="X48" s="19" t="inlineStr"/>
+      <c r="Y48" s="19" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="16" t="n">
+      <c r="A49" s="17" t="n">
         <v>1963</v>
       </c>
-      <c r="B49" s="17" t="inlineStr">
+      <c r="B49" s="18" t="inlineStr">
         <is>
           <t>Vancouver, BC; Missing</t>
         </is>
       </c>
-      <c r="C49" s="18" t="inlineStr"/>
-      <c r="D49" s="18" t="inlineStr"/>
-      <c r="E49" s="18" t="inlineStr"/>
-      <c r="F49" s="18" t="inlineStr"/>
-      <c r="G49" s="18" t="inlineStr"/>
-      <c r="H49" s="18" t="inlineStr"/>
-      <c r="I49" s="18" t="inlineStr"/>
-      <c r="J49" s="18" t="inlineStr"/>
-      <c r="K49" s="18" t="inlineStr"/>
-      <c r="L49" s="18" t="inlineStr"/>
-      <c r="M49" s="18" t="inlineStr"/>
-      <c r="N49" s="18" t="inlineStr"/>
-      <c r="O49" s="18" t="inlineStr"/>
-      <c r="P49" s="18" t="inlineStr"/>
-      <c r="Q49" s="18" t="inlineStr"/>
-      <c r="R49" s="18" t="inlineStr"/>
-      <c r="S49" s="18" t="inlineStr"/>
-      <c r="T49" s="18" t="inlineStr"/>
-      <c r="U49" s="18" t="inlineStr"/>
-      <c r="V49" s="18" t="inlineStr"/>
-      <c r="W49" s="18" t="inlineStr"/>
-      <c r="X49" s="18" t="inlineStr"/>
-      <c r="Y49" s="18" t="inlineStr"/>
+      <c r="C49" s="19" t="inlineStr"/>
+      <c r="D49" s="19" t="inlineStr"/>
+      <c r="E49" s="19" t="inlineStr"/>
+      <c r="F49" s="19" t="inlineStr"/>
+      <c r="G49" s="19" t="inlineStr"/>
+      <c r="H49" s="19" t="inlineStr"/>
+      <c r="I49" s="19" t="inlineStr"/>
+      <c r="J49" s="19" t="inlineStr"/>
+      <c r="K49" s="19" t="inlineStr"/>
+      <c r="L49" s="19" t="inlineStr"/>
+      <c r="M49" s="19" t="inlineStr"/>
+      <c r="N49" s="19" t="inlineStr"/>
+      <c r="O49" s="19" t="inlineStr"/>
+      <c r="P49" s="19" t="inlineStr"/>
+      <c r="Q49" s="19" t="inlineStr"/>
+      <c r="R49" s="19" t="inlineStr"/>
+      <c r="S49" s="19" t="inlineStr"/>
+      <c r="T49" s="19" t="inlineStr"/>
+      <c r="U49" s="19" t="inlineStr"/>
+      <c r="V49" s="19" t="inlineStr"/>
+      <c r="W49" s="19" t="inlineStr"/>
+      <c r="X49" s="19" t="inlineStr"/>
+      <c r="Y49" s="19" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="16" t="n">
+      <c r="A50" s="17" t="n">
         <v>1964</v>
       </c>
-      <c r="B50" s="17" t="inlineStr">
+      <c r="B50" s="18" t="inlineStr">
         <is>
           <t>Morehead City, NC; Missing</t>
         </is>
       </c>
-      <c r="C50" s="18" t="inlineStr"/>
-      <c r="D50" s="18" t="inlineStr"/>
-      <c r="E50" s="18" t="inlineStr"/>
-      <c r="F50" s="18" t="inlineStr"/>
-      <c r="G50" s="18" t="inlineStr"/>
-      <c r="H50" s="18" t="inlineStr"/>
-      <c r="I50" s="18" t="inlineStr"/>
-      <c r="J50" s="18" t="inlineStr"/>
-      <c r="K50" s="18" t="inlineStr"/>
-      <c r="L50" s="18" t="inlineStr"/>
-      <c r="M50" s="18" t="inlineStr"/>
-      <c r="N50" s="18" t="inlineStr"/>
-      <c r="O50" s="18" t="inlineStr"/>
-      <c r="P50" s="18" t="inlineStr"/>
-      <c r="Q50" s="18" t="inlineStr"/>
-      <c r="R50" s="18" t="inlineStr"/>
-      <c r="S50" s="18" t="inlineStr"/>
-      <c r="T50" s="18" t="inlineStr"/>
-      <c r="U50" s="18" t="inlineStr"/>
-      <c r="V50" s="18" t="inlineStr"/>
-      <c r="W50" s="18" t="inlineStr"/>
-      <c r="X50" s="18" t="inlineStr"/>
-      <c r="Y50" s="18" t="inlineStr"/>
+      <c r="C50" s="19" t="inlineStr"/>
+      <c r="D50" s="19" t="inlineStr"/>
+      <c r="E50" s="19" t="inlineStr"/>
+      <c r="F50" s="19" t="inlineStr"/>
+      <c r="G50" s="19" t="inlineStr"/>
+      <c r="H50" s="19" t="inlineStr"/>
+      <c r="I50" s="19" t="inlineStr"/>
+      <c r="J50" s="19" t="inlineStr"/>
+      <c r="K50" s="19" t="inlineStr"/>
+      <c r="L50" s="19" t="inlineStr"/>
+      <c r="M50" s="19" t="inlineStr"/>
+      <c r="N50" s="19" t="inlineStr"/>
+      <c r="O50" s="19" t="inlineStr"/>
+      <c r="P50" s="19" t="inlineStr"/>
+      <c r="Q50" s="19" t="inlineStr"/>
+      <c r="R50" s="19" t="inlineStr"/>
+      <c r="S50" s="19" t="inlineStr"/>
+      <c r="T50" s="19" t="inlineStr"/>
+      <c r="U50" s="19" t="inlineStr"/>
+      <c r="V50" s="19" t="inlineStr"/>
+      <c r="W50" s="19" t="inlineStr"/>
+      <c r="X50" s="19" t="inlineStr"/>
+      <c r="Y50" s="19" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="16" t="n">
+      <c r="A51" s="17" t="n">
         <v>1965</v>
       </c>
-      <c r="B51" s="17" t="inlineStr">
+      <c r="B51" s="18" t="inlineStr">
         <is>
           <t>Lawrence, KS; Missing</t>
         </is>
       </c>
-      <c r="C51" s="18" t="inlineStr"/>
-      <c r="D51" s="18" t="inlineStr"/>
-      <c r="E51" s="18" t="inlineStr"/>
-      <c r="F51" s="18" t="inlineStr"/>
-      <c r="G51" s="18" t="inlineStr"/>
-      <c r="H51" s="18" t="inlineStr"/>
-      <c r="I51" s="18" t="inlineStr"/>
-      <c r="J51" s="18" t="inlineStr"/>
-      <c r="K51" s="18" t="inlineStr"/>
-      <c r="L51" s="18" t="inlineStr"/>
-      <c r="M51" s="18" t="inlineStr"/>
-      <c r="N51" s="18" t="inlineStr"/>
-      <c r="O51" s="18" t="inlineStr"/>
-      <c r="P51" s="18" t="inlineStr"/>
-      <c r="Q51" s="18" t="inlineStr"/>
-      <c r="R51" s="18" t="inlineStr"/>
-      <c r="S51" s="18" t="inlineStr"/>
-      <c r="T51" s="18" t="inlineStr"/>
-      <c r="U51" s="18" t="inlineStr"/>
-      <c r="V51" s="18" t="inlineStr"/>
-      <c r="W51" s="18" t="inlineStr"/>
-      <c r="X51" s="18" t="inlineStr"/>
-      <c r="Y51" s="18" t="inlineStr"/>
+      <c r="C51" s="19" t="inlineStr"/>
+      <c r="D51" s="19" t="inlineStr"/>
+      <c r="E51" s="19" t="inlineStr"/>
+      <c r="F51" s="19" t="inlineStr"/>
+      <c r="G51" s="19" t="inlineStr"/>
+      <c r="H51" s="19" t="inlineStr"/>
+      <c r="I51" s="19" t="inlineStr"/>
+      <c r="J51" s="19" t="inlineStr"/>
+      <c r="K51" s="19" t="inlineStr"/>
+      <c r="L51" s="19" t="inlineStr"/>
+      <c r="M51" s="19" t="inlineStr"/>
+      <c r="N51" s="19" t="inlineStr"/>
+      <c r="O51" s="19" t="inlineStr"/>
+      <c r="P51" s="19" t="inlineStr"/>
+      <c r="Q51" s="19" t="inlineStr"/>
+      <c r="R51" s="19" t="inlineStr"/>
+      <c r="S51" s="19" t="inlineStr"/>
+      <c r="T51" s="19" t="inlineStr"/>
+      <c r="U51" s="19" t="inlineStr"/>
+      <c r="V51" s="19" t="inlineStr"/>
+      <c r="W51" s="19" t="inlineStr"/>
+      <c r="X51" s="19" t="inlineStr"/>
+      <c r="Y51" s="19" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="16" t="n">
+      <c r="A52" s="17" t="n">
         <v>1966</v>
       </c>
-      <c r="B52" s="17" t="inlineStr">
+      <c r="B52" s="18" t="inlineStr">
         <is>
           <t>Miami, FL; Missing</t>
         </is>
       </c>
-      <c r="C52" s="18" t="inlineStr"/>
-      <c r="D52" s="18" t="inlineStr"/>
-      <c r="E52" s="18" t="inlineStr"/>
-      <c r="F52" s="18" t="inlineStr"/>
-      <c r="G52" s="18" t="inlineStr"/>
-      <c r="H52" s="18" t="inlineStr"/>
-      <c r="I52" s="18" t="inlineStr"/>
-      <c r="J52" s="18" t="inlineStr"/>
-      <c r="K52" s="18" t="inlineStr"/>
-      <c r="L52" s="18" t="inlineStr"/>
-      <c r="M52" s="18" t="inlineStr"/>
-      <c r="N52" s="18" t="inlineStr"/>
-      <c r="O52" s="18" t="inlineStr"/>
-      <c r="P52" s="18" t="inlineStr"/>
-      <c r="Q52" s="18" t="inlineStr"/>
-      <c r="R52" s="18" t="inlineStr"/>
-      <c r="S52" s="18" t="inlineStr"/>
-      <c r="T52" s="18" t="inlineStr"/>
-      <c r="U52" s="18" t="inlineStr"/>
-      <c r="V52" s="18" t="inlineStr"/>
-      <c r="W52" s="18" t="inlineStr"/>
-      <c r="X52" s="18" t="inlineStr"/>
-      <c r="Y52" s="18" t="inlineStr"/>
+      <c r="C52" s="19" t="inlineStr"/>
+      <c r="D52" s="19" t="inlineStr"/>
+      <c r="E52" s="19" t="inlineStr"/>
+      <c r="F52" s="19" t="inlineStr"/>
+      <c r="G52" s="19" t="inlineStr"/>
+      <c r="H52" s="19" t="inlineStr"/>
+      <c r="I52" s="19" t="inlineStr"/>
+      <c r="J52" s="19" t="inlineStr"/>
+      <c r="K52" s="19" t="inlineStr"/>
+      <c r="L52" s="19" t="inlineStr"/>
+      <c r="M52" s="19" t="inlineStr"/>
+      <c r="N52" s="19" t="inlineStr"/>
+      <c r="O52" s="19" t="inlineStr"/>
+      <c r="P52" s="19" t="inlineStr"/>
+      <c r="Q52" s="19" t="inlineStr"/>
+      <c r="R52" s="19" t="inlineStr"/>
+      <c r="S52" s="19" t="inlineStr"/>
+      <c r="T52" s="19" t="inlineStr"/>
+      <c r="U52" s="19" t="inlineStr"/>
+      <c r="V52" s="19" t="inlineStr"/>
+      <c r="W52" s="19" t="inlineStr"/>
+      <c r="X52" s="19" t="inlineStr"/>
+      <c r="Y52" s="19" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="16" t="n">
+      <c r="A53" s="17" t="n">
         <v>1967</v>
       </c>
-      <c r="B53" s="17" t="inlineStr">
+      <c r="B53" s="18" t="inlineStr">
         <is>
           <t>San Francisco, CA; Missing</t>
         </is>
       </c>
-      <c r="C53" s="18" t="inlineStr"/>
-      <c r="D53" s="18" t="inlineStr"/>
-      <c r="E53" s="18" t="inlineStr"/>
-      <c r="F53" s="18" t="inlineStr"/>
-      <c r="G53" s="18" t="inlineStr"/>
-      <c r="H53" s="18" t="inlineStr"/>
-      <c r="I53" s="18" t="inlineStr"/>
-      <c r="J53" s="18" t="inlineStr"/>
-      <c r="K53" s="18" t="inlineStr"/>
-      <c r="L53" s="18" t="inlineStr"/>
-      <c r="M53" s="18" t="inlineStr"/>
-      <c r="N53" s="18" t="inlineStr"/>
-      <c r="O53" s="18" t="inlineStr"/>
-      <c r="P53" s="18" t="inlineStr"/>
-      <c r="Q53" s="18" t="inlineStr"/>
-      <c r="R53" s="18" t="inlineStr"/>
-      <c r="S53" s="18" t="inlineStr"/>
-      <c r="T53" s="18" t="inlineStr"/>
-      <c r="U53" s="18" t="inlineStr"/>
-      <c r="V53" s="18" t="inlineStr"/>
-      <c r="W53" s="18" t="inlineStr"/>
-      <c r="X53" s="18" t="inlineStr"/>
-      <c r="Y53" s="18" t="inlineStr"/>
+      <c r="C53" s="19" t="inlineStr"/>
+      <c r="D53" s="19" t="inlineStr"/>
+      <c r="E53" s="19" t="inlineStr"/>
+      <c r="F53" s="19" t="inlineStr"/>
+      <c r="G53" s="19" t="inlineStr"/>
+      <c r="H53" s="19" t="inlineStr"/>
+      <c r="I53" s="19" t="inlineStr"/>
+      <c r="J53" s="19" t="inlineStr"/>
+      <c r="K53" s="19" t="inlineStr"/>
+      <c r="L53" s="19" t="inlineStr"/>
+      <c r="M53" s="19" t="inlineStr"/>
+      <c r="N53" s="19" t="inlineStr"/>
+      <c r="O53" s="19" t="inlineStr"/>
+      <c r="P53" s="19" t="inlineStr"/>
+      <c r="Q53" s="19" t="inlineStr"/>
+      <c r="R53" s="19" t="inlineStr"/>
+      <c r="S53" s="19" t="inlineStr"/>
+      <c r="T53" s="19" t="inlineStr"/>
+      <c r="U53" s="19" t="inlineStr"/>
+      <c r="V53" s="19" t="inlineStr"/>
+      <c r="W53" s="19" t="inlineStr"/>
+      <c r="X53" s="19" t="inlineStr"/>
+      <c r="Y53" s="19" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="16" t="n">
+      <c r="A54" s="17" t="n">
         <v>1968</v>
       </c>
-      <c r="B54" s="17" t="inlineStr">
+      <c r="B54" s="18" t="inlineStr">
         <is>
           <t>Ann Arbor, MI; Missing</t>
         </is>
       </c>
-      <c r="C54" s="18" t="inlineStr"/>
-      <c r="D54" s="18" t="inlineStr"/>
-      <c r="E54" s="18" t="inlineStr"/>
-      <c r="F54" s="18" t="inlineStr"/>
-      <c r="G54" s="18" t="inlineStr"/>
-      <c r="H54" s="18" t="inlineStr"/>
-      <c r="I54" s="18" t="inlineStr"/>
-      <c r="J54" s="18" t="inlineStr"/>
-      <c r="K54" s="18" t="inlineStr"/>
-      <c r="L54" s="18" t="inlineStr"/>
-      <c r="M54" s="18" t="inlineStr"/>
-      <c r="N54" s="18" t="inlineStr"/>
-      <c r="O54" s="18" t="inlineStr"/>
-      <c r="P54" s="18" t="inlineStr"/>
-      <c r="Q54" s="18" t="inlineStr"/>
-      <c r="R54" s="18" t="inlineStr"/>
-      <c r="S54" s="18" t="inlineStr"/>
-      <c r="T54" s="18" t="inlineStr"/>
-      <c r="U54" s="18" t="inlineStr"/>
-      <c r="V54" s="18" t="inlineStr"/>
-      <c r="W54" s="18" t="inlineStr"/>
-      <c r="X54" s="18" t="inlineStr"/>
-      <c r="Y54" s="18" t="inlineStr"/>
+      <c r="C54" s="19" t="inlineStr"/>
+      <c r="D54" s="19" t="inlineStr"/>
+      <c r="E54" s="19" t="inlineStr"/>
+      <c r="F54" s="19" t="inlineStr"/>
+      <c r="G54" s="19" t="inlineStr"/>
+      <c r="H54" s="19" t="inlineStr"/>
+      <c r="I54" s="19" t="inlineStr"/>
+      <c r="J54" s="19" t="inlineStr"/>
+      <c r="K54" s="19" t="inlineStr"/>
+      <c r="L54" s="19" t="inlineStr"/>
+      <c r="M54" s="19" t="inlineStr"/>
+      <c r="N54" s="19" t="inlineStr"/>
+      <c r="O54" s="19" t="inlineStr"/>
+      <c r="P54" s="19" t="inlineStr"/>
+      <c r="Q54" s="19" t="inlineStr"/>
+      <c r="R54" s="19" t="inlineStr"/>
+      <c r="S54" s="19" t="inlineStr"/>
+      <c r="T54" s="19" t="inlineStr"/>
+      <c r="U54" s="19" t="inlineStr"/>
+      <c r="V54" s="19" t="inlineStr"/>
+      <c r="W54" s="19" t="inlineStr"/>
+      <c r="X54" s="19" t="inlineStr"/>
+      <c r="Y54" s="19" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="16" t="n">
+      <c r="A55" s="17" t="n">
         <v>1969</v>
       </c>
-      <c r="B55" s="17" t="inlineStr">
+      <c r="B55" s="18" t="inlineStr">
         <is>
           <t>New York, NY; Missing</t>
         </is>
       </c>
-      <c r="C55" s="18" t="inlineStr"/>
-      <c r="D55" s="18" t="inlineStr"/>
-      <c r="E55" s="18" t="inlineStr"/>
-      <c r="F55" s="18" t="inlineStr"/>
-      <c r="G55" s="18" t="inlineStr"/>
-      <c r="H55" s="18" t="inlineStr"/>
-      <c r="I55" s="18" t="inlineStr"/>
-      <c r="J55" s="18" t="inlineStr"/>
-      <c r="K55" s="18" t="inlineStr"/>
-      <c r="L55" s="18" t="inlineStr"/>
-      <c r="M55" s="18" t="inlineStr"/>
-      <c r="N55" s="18" t="inlineStr"/>
-      <c r="O55" s="18" t="inlineStr"/>
-      <c r="P55" s="18" t="inlineStr"/>
-      <c r="Q55" s="18" t="inlineStr"/>
-      <c r="R55" s="18" t="inlineStr"/>
-      <c r="S55" s="18" t="inlineStr"/>
-      <c r="T55" s="18" t="inlineStr"/>
-      <c r="U55" s="18" t="inlineStr"/>
-      <c r="V55" s="18" t="inlineStr"/>
-      <c r="W55" s="18" t="inlineStr"/>
-      <c r="X55" s="18" t="inlineStr"/>
-      <c r="Y55" s="18" t="inlineStr"/>
+      <c r="C55" s="19" t="inlineStr"/>
+      <c r="D55" s="19" t="inlineStr"/>
+      <c r="E55" s="19" t="inlineStr"/>
+      <c r="F55" s="19" t="inlineStr"/>
+      <c r="G55" s="19" t="inlineStr"/>
+      <c r="H55" s="19" t="inlineStr"/>
+      <c r="I55" s="19" t="inlineStr"/>
+      <c r="J55" s="19" t="inlineStr"/>
+      <c r="K55" s="19" t="inlineStr"/>
+      <c r="L55" s="19" t="inlineStr"/>
+      <c r="M55" s="19" t="inlineStr"/>
+      <c r="N55" s="19" t="inlineStr"/>
+      <c r="O55" s="19" t="inlineStr"/>
+      <c r="P55" s="19" t="inlineStr"/>
+      <c r="Q55" s="19" t="inlineStr"/>
+      <c r="R55" s="19" t="inlineStr"/>
+      <c r="S55" s="19" t="inlineStr"/>
+      <c r="T55" s="19" t="inlineStr"/>
+      <c r="U55" s="19" t="inlineStr"/>
+      <c r="V55" s="19" t="inlineStr"/>
+      <c r="W55" s="19" t="inlineStr"/>
+      <c r="X55" s="19" t="inlineStr"/>
+      <c r="Y55" s="19" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="16" t="n">
+      <c r="A56" s="17" t="n">
         <v>1970</v>
       </c>
-      <c r="B56" s="17" t="inlineStr">
+      <c r="B56" s="18" t="inlineStr">
         <is>
           <t>New Orleans, LA; Missing</t>
         </is>
       </c>
-      <c r="C56" s="18" t="inlineStr"/>
-      <c r="D56" s="18" t="inlineStr"/>
-      <c r="E56" s="18" t="inlineStr"/>
-      <c r="F56" s="18" t="inlineStr"/>
-      <c r="G56" s="18" t="inlineStr"/>
-      <c r="H56" s="18" t="inlineStr"/>
-      <c r="I56" s="18" t="inlineStr"/>
-      <c r="J56" s="18" t="inlineStr"/>
-      <c r="K56" s="18" t="inlineStr"/>
-      <c r="L56" s="18" t="inlineStr"/>
-      <c r="M56" s="18" t="inlineStr"/>
-      <c r="N56" s="18" t="inlineStr"/>
-      <c r="O56" s="18" t="inlineStr"/>
-      <c r="P56" s="18" t="inlineStr"/>
-      <c r="Q56" s="18" t="inlineStr"/>
-      <c r="R56" s="18" t="inlineStr"/>
-      <c r="S56" s="18" t="inlineStr"/>
-      <c r="T56" s="18" t="inlineStr"/>
-      <c r="U56" s="18" t="inlineStr"/>
-      <c r="V56" s="18" t="inlineStr"/>
-      <c r="W56" s="18" t="inlineStr"/>
-      <c r="X56" s="18" t="inlineStr"/>
-      <c r="Y56" s="18" t="inlineStr"/>
+      <c r="C56" s="19" t="inlineStr"/>
+      <c r="D56" s="19" t="inlineStr"/>
+      <c r="E56" s="19" t="inlineStr"/>
+      <c r="F56" s="19" t="inlineStr"/>
+      <c r="G56" s="19" t="inlineStr"/>
+      <c r="H56" s="19" t="inlineStr"/>
+      <c r="I56" s="19" t="inlineStr"/>
+      <c r="J56" s="19" t="inlineStr"/>
+      <c r="K56" s="19" t="inlineStr"/>
+      <c r="L56" s="19" t="inlineStr"/>
+      <c r="M56" s="19" t="inlineStr"/>
+      <c r="N56" s="19" t="inlineStr"/>
+      <c r="O56" s="19" t="inlineStr"/>
+      <c r="P56" s="19" t="inlineStr"/>
+      <c r="Q56" s="19" t="inlineStr"/>
+      <c r="R56" s="19" t="inlineStr"/>
+      <c r="S56" s="19" t="inlineStr"/>
+      <c r="T56" s="19" t="inlineStr"/>
+      <c r="U56" s="19" t="inlineStr"/>
+      <c r="V56" s="19" t="inlineStr"/>
+      <c r="W56" s="19" t="inlineStr"/>
+      <c r="X56" s="19" t="inlineStr"/>
+      <c r="Y56" s="19" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="16" t="n">
+      <c r="A57" s="17" t="n">
         <v>1971</v>
       </c>
-      <c r="B57" s="17" t="inlineStr">
+      <c r="B57" s="18" t="inlineStr">
         <is>
           <t>Los Angeles, CA; Missing</t>
         </is>
       </c>
-      <c r="C57" s="18" t="inlineStr"/>
-      <c r="D57" s="18" t="inlineStr"/>
-      <c r="E57" s="18" t="inlineStr"/>
-      <c r="F57" s="18" t="inlineStr"/>
-      <c r="G57" s="18" t="inlineStr"/>
-      <c r="H57" s="18" t="inlineStr"/>
-      <c r="I57" s="18" t="inlineStr"/>
-      <c r="J57" s="18" t="inlineStr"/>
-      <c r="K57" s="18" t="inlineStr"/>
-      <c r="L57" s="18" t="inlineStr"/>
-      <c r="M57" s="18" t="inlineStr"/>
-      <c r="N57" s="18" t="inlineStr"/>
-      <c r="O57" s="18" t="inlineStr"/>
-      <c r="P57" s="18" t="inlineStr"/>
-      <c r="Q57" s="18" t="inlineStr"/>
-      <c r="R57" s="18" t="inlineStr"/>
-      <c r="S57" s="18" t="inlineStr"/>
-      <c r="T57" s="18" t="inlineStr"/>
-      <c r="U57" s="18" t="inlineStr"/>
-      <c r="V57" s="18" t="inlineStr"/>
-      <c r="W57" s="18" t="inlineStr"/>
-      <c r="X57" s="18" t="inlineStr"/>
-      <c r="Y57" s="18" t="inlineStr"/>
+      <c r="C57" s="19" t="inlineStr"/>
+      <c r="D57" s="19" t="inlineStr"/>
+      <c r="E57" s="19" t="inlineStr"/>
+      <c r="F57" s="19" t="inlineStr"/>
+      <c r="G57" s="19" t="inlineStr"/>
+      <c r="H57" s="19" t="inlineStr"/>
+      <c r="I57" s="19" t="inlineStr"/>
+      <c r="J57" s="19" t="inlineStr"/>
+      <c r="K57" s="19" t="inlineStr"/>
+      <c r="L57" s="19" t="inlineStr"/>
+      <c r="M57" s="19" t="inlineStr"/>
+      <c r="N57" s="19" t="inlineStr"/>
+      <c r="O57" s="19" t="inlineStr"/>
+      <c r="P57" s="19" t="inlineStr"/>
+      <c r="Q57" s="19" t="inlineStr"/>
+      <c r="R57" s="19" t="inlineStr"/>
+      <c r="S57" s="19" t="inlineStr"/>
+      <c r="T57" s="19" t="inlineStr"/>
+      <c r="U57" s="19" t="inlineStr"/>
+      <c r="V57" s="19" t="inlineStr"/>
+      <c r="W57" s="19" t="inlineStr"/>
+      <c r="X57" s="19" t="inlineStr"/>
+      <c r="Y57" s="19" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="16" t="n">
+      <c r="A58" s="17" t="n">
         <v>1972</v>
       </c>
-      <c r="B58" s="17" t="inlineStr">
+      <c r="B58" s="18" t="inlineStr">
         <is>
           <t>Boston, MA; Missing</t>
         </is>
       </c>
-      <c r="C58" s="18" t="inlineStr"/>
-      <c r="D58" s="18" t="inlineStr"/>
-      <c r="E58" s="18" t="inlineStr"/>
-      <c r="F58" s="18" t="inlineStr"/>
-      <c r="G58" s="18" t="inlineStr"/>
-      <c r="H58" s="18" t="inlineStr"/>
-      <c r="I58" s="18" t="inlineStr"/>
-      <c r="J58" s="18" t="inlineStr"/>
-      <c r="K58" s="18" t="inlineStr"/>
-      <c r="L58" s="18" t="inlineStr"/>
-      <c r="M58" s="18" t="inlineStr"/>
-      <c r="N58" s="18" t="inlineStr"/>
-      <c r="O58" s="18" t="inlineStr"/>
-      <c r="P58" s="18" t="inlineStr"/>
-      <c r="Q58" s="18" t="inlineStr"/>
-      <c r="R58" s="18" t="inlineStr"/>
-      <c r="S58" s="18" t="inlineStr"/>
-      <c r="T58" s="18" t="inlineStr"/>
-      <c r="U58" s="18" t="inlineStr"/>
-      <c r="V58" s="18" t="inlineStr"/>
-      <c r="W58" s="18" t="inlineStr"/>
-      <c r="X58" s="18" t="inlineStr"/>
-      <c r="Y58" s="18" t="inlineStr"/>
+      <c r="C58" s="19" t="inlineStr"/>
+      <c r="D58" s="19" t="inlineStr"/>
+      <c r="E58" s="19" t="inlineStr"/>
+      <c r="F58" s="19" t="inlineStr"/>
+      <c r="G58" s="19" t="inlineStr"/>
+      <c r="H58" s="19" t="inlineStr"/>
+      <c r="I58" s="19" t="inlineStr"/>
+      <c r="J58" s="19" t="inlineStr"/>
+      <c r="K58" s="19" t="inlineStr"/>
+      <c r="L58" s="19" t="inlineStr"/>
+      <c r="M58" s="19" t="inlineStr"/>
+      <c r="N58" s="19" t="inlineStr"/>
+      <c r="O58" s="19" t="inlineStr"/>
+      <c r="P58" s="19" t="inlineStr"/>
+      <c r="Q58" s="19" t="inlineStr"/>
+      <c r="R58" s="19" t="inlineStr"/>
+      <c r="S58" s="19" t="inlineStr"/>
+      <c r="T58" s="19" t="inlineStr"/>
+      <c r="U58" s="19" t="inlineStr"/>
+      <c r="V58" s="19" t="inlineStr"/>
+      <c r="W58" s="19" t="inlineStr"/>
+      <c r="X58" s="19" t="inlineStr"/>
+      <c r="Y58" s="19" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="16" t="n">
+      <c r="A59" s="17" t="n">
         <v>1973</v>
       </c>
-      <c r="B59" s="17" t="inlineStr">
+      <c r="B59" s="18" t="inlineStr">
         <is>
           <t>San Jose, Costa Rica; Missing</t>
         </is>
       </c>
-      <c r="C59" s="18" t="inlineStr"/>
-      <c r="D59" s="18" t="inlineStr"/>
-      <c r="E59" s="18" t="inlineStr"/>
-      <c r="F59" s="18" t="inlineStr"/>
-      <c r="G59" s="18" t="inlineStr"/>
-      <c r="H59" s="18" t="inlineStr"/>
-      <c r="I59" s="18" t="inlineStr"/>
-      <c r="J59" s="18" t="inlineStr"/>
-      <c r="K59" s="18" t="inlineStr"/>
-      <c r="L59" s="18" t="inlineStr"/>
-      <c r="M59" s="18" t="inlineStr"/>
-      <c r="N59" s="18" t="inlineStr"/>
-      <c r="O59" s="18" t="inlineStr"/>
-      <c r="P59" s="18" t="inlineStr"/>
-      <c r="Q59" s="18" t="inlineStr"/>
-      <c r="R59" s="18" t="inlineStr"/>
-      <c r="S59" s="18" t="inlineStr"/>
-      <c r="T59" s="18" t="inlineStr"/>
-      <c r="U59" s="18" t="inlineStr"/>
-      <c r="V59" s="18" t="inlineStr"/>
-      <c r="W59" s="18" t="inlineStr"/>
-      <c r="X59" s="18" t="inlineStr"/>
-      <c r="Y59" s="17" t="inlineStr">
+      <c r="C59" s="19" t="inlineStr"/>
+      <c r="D59" s="19" t="inlineStr"/>
+      <c r="E59" s="19" t="inlineStr"/>
+      <c r="F59" s="19" t="inlineStr"/>
+      <c r="G59" s="19" t="inlineStr"/>
+      <c r="H59" s="19" t="inlineStr"/>
+      <c r="I59" s="19" t="inlineStr"/>
+      <c r="J59" s="19" t="inlineStr"/>
+      <c r="K59" s="19" t="inlineStr"/>
+      <c r="L59" s="19" t="inlineStr"/>
+      <c r="M59" s="19" t="inlineStr"/>
+      <c r="N59" s="19" t="inlineStr"/>
+      <c r="O59" s="19" t="inlineStr"/>
+      <c r="P59" s="19" t="inlineStr"/>
+      <c r="Q59" s="19" t="inlineStr"/>
+      <c r="R59" s="19" t="inlineStr"/>
+      <c r="S59" s="19" t="inlineStr"/>
+      <c r="T59" s="19" t="inlineStr"/>
+      <c r="U59" s="19" t="inlineStr"/>
+      <c r="V59" s="19" t="inlineStr"/>
+      <c r="W59" s="19" t="inlineStr"/>
+      <c r="X59" s="19" t="inlineStr"/>
+      <c r="Y59" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="16" t="n">
+      <c r="A60" s="17" t="n">
         <v>1974</v>
       </c>
-      <c r="B60" s="17" t="inlineStr">
+      <c r="B60" s="18" t="inlineStr">
         <is>
           <t>Ottawa, ON; Missing</t>
         </is>
       </c>
-      <c r="C60" s="18" t="inlineStr"/>
-      <c r="D60" s="18" t="inlineStr"/>
-      <c r="E60" s="18" t="inlineStr"/>
-      <c r="F60" s="18" t="inlineStr"/>
-      <c r="G60" s="18" t="inlineStr"/>
-      <c r="H60" s="18" t="inlineStr"/>
-      <c r="I60" s="18" t="inlineStr"/>
-      <c r="J60" s="18" t="inlineStr"/>
-      <c r="K60" s="18" t="inlineStr"/>
-      <c r="L60" s="18" t="inlineStr"/>
-      <c r="M60" s="18" t="inlineStr"/>
-      <c r="N60" s="18" t="inlineStr"/>
-      <c r="O60" s="18" t="inlineStr"/>
-      <c r="P60" s="18" t="inlineStr"/>
-      <c r="Q60" s="18" t="inlineStr"/>
-      <c r="R60" s="18" t="inlineStr"/>
-      <c r="S60" s="18" t="inlineStr"/>
-      <c r="T60" s="18" t="inlineStr"/>
-      <c r="U60" s="18" t="inlineStr"/>
-      <c r="V60" s="18" t="inlineStr"/>
-      <c r="W60" s="18" t="inlineStr"/>
-      <c r="X60" s="18" t="inlineStr"/>
-      <c r="Y60" s="18" t="inlineStr"/>
+      <c r="C60" s="19" t="inlineStr"/>
+      <c r="D60" s="19" t="inlineStr"/>
+      <c r="E60" s="19" t="inlineStr"/>
+      <c r="F60" s="19" t="inlineStr"/>
+      <c r="G60" s="19" t="inlineStr"/>
+      <c r="H60" s="19" t="inlineStr"/>
+      <c r="I60" s="19" t="inlineStr"/>
+      <c r="J60" s="19" t="inlineStr"/>
+      <c r="K60" s="19" t="inlineStr"/>
+      <c r="L60" s="19" t="inlineStr"/>
+      <c r="M60" s="19" t="inlineStr"/>
+      <c r="N60" s="19" t="inlineStr"/>
+      <c r="O60" s="19" t="inlineStr"/>
+      <c r="P60" s="19" t="inlineStr"/>
+      <c r="Q60" s="19" t="inlineStr"/>
+      <c r="R60" s="19" t="inlineStr"/>
+      <c r="S60" s="19" t="inlineStr"/>
+      <c r="T60" s="19" t="inlineStr"/>
+      <c r="U60" s="19" t="inlineStr"/>
+      <c r="V60" s="19" t="inlineStr"/>
+      <c r="W60" s="19" t="inlineStr"/>
+      <c r="X60" s="19" t="inlineStr"/>
+      <c r="Y60" s="19" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="16" t="n">
+      <c r="A61" s="17" t="n">
         <v>1975</v>
       </c>
-      <c r="B61" s="17" t="inlineStr">
+      <c r="B61" s="18" t="inlineStr">
         <is>
           <t>Williamsburg, VA; Missing</t>
         </is>
       </c>
-      <c r="C61" s="18" t="inlineStr"/>
-      <c r="D61" s="18" t="inlineStr"/>
-      <c r="E61" s="18" t="inlineStr"/>
-      <c r="F61" s="18" t="inlineStr"/>
-      <c r="G61" s="18" t="inlineStr"/>
-      <c r="H61" s="18" t="inlineStr"/>
-      <c r="I61" s="18" t="inlineStr"/>
-      <c r="J61" s="18" t="inlineStr"/>
-      <c r="K61" s="18" t="inlineStr"/>
-      <c r="L61" s="18" t="inlineStr"/>
-      <c r="M61" s="18" t="inlineStr"/>
-      <c r="N61" s="18" t="inlineStr"/>
-      <c r="O61" s="18" t="inlineStr"/>
-      <c r="P61" s="18" t="inlineStr"/>
-      <c r="Q61" s="18" t="inlineStr"/>
-      <c r="R61" s="18" t="inlineStr"/>
-      <c r="S61" s="18" t="inlineStr"/>
-      <c r="T61" s="18" t="inlineStr"/>
-      <c r="U61" s="18" t="inlineStr"/>
-      <c r="V61" s="18" t="inlineStr"/>
-      <c r="W61" s="18" t="inlineStr"/>
-      <c r="X61" s="18" t="inlineStr"/>
-      <c r="Y61" s="18" t="inlineStr"/>
+      <c r="C61" s="19" t="inlineStr"/>
+      <c r="D61" s="19" t="inlineStr"/>
+      <c r="E61" s="19" t="inlineStr"/>
+      <c r="F61" s="19" t="inlineStr"/>
+      <c r="G61" s="19" t="inlineStr"/>
+      <c r="H61" s="19" t="inlineStr"/>
+      <c r="I61" s="19" t="inlineStr"/>
+      <c r="J61" s="19" t="inlineStr"/>
+      <c r="K61" s="19" t="inlineStr"/>
+      <c r="L61" s="19" t="inlineStr"/>
+      <c r="M61" s="19" t="inlineStr"/>
+      <c r="N61" s="19" t="inlineStr"/>
+      <c r="O61" s="19" t="inlineStr"/>
+      <c r="P61" s="19" t="inlineStr"/>
+      <c r="Q61" s="19" t="inlineStr"/>
+      <c r="R61" s="19" t="inlineStr"/>
+      <c r="S61" s="19" t="inlineStr"/>
+      <c r="T61" s="19" t="inlineStr"/>
+      <c r="U61" s="19" t="inlineStr"/>
+      <c r="V61" s="19" t="inlineStr"/>
+      <c r="W61" s="19" t="inlineStr"/>
+      <c r="X61" s="19" t="inlineStr"/>
+      <c r="Y61" s="19" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="16" t="n">
+      <c r="A62" s="17" t="n">
         <v>1976</v>
       </c>
-      <c r="B62" s="17" t="inlineStr">
+      <c r="B62" s="18" t="inlineStr">
         <is>
           <t>Fairbanks, AK; Missing</t>
         </is>
       </c>
-      <c r="C62" s="18" t="inlineStr"/>
-      <c r="D62" s="18" t="inlineStr"/>
-      <c r="E62" s="18" t="inlineStr"/>
-      <c r="F62" s="18" t="inlineStr"/>
-      <c r="G62" s="18" t="inlineStr"/>
-      <c r="H62" s="18" t="inlineStr"/>
-      <c r="I62" s="18" t="inlineStr"/>
-      <c r="J62" s="18" t="inlineStr"/>
-      <c r="K62" s="18" t="inlineStr"/>
-      <c r="L62" s="18" t="inlineStr"/>
-      <c r="M62" s="18" t="inlineStr"/>
-      <c r="N62" s="18" t="inlineStr"/>
-      <c r="O62" s="18" t="inlineStr"/>
-      <c r="P62" s="18" t="inlineStr"/>
-      <c r="Q62" s="18" t="inlineStr"/>
-      <c r="R62" s="18" t="inlineStr"/>
-      <c r="S62" s="18" t="inlineStr"/>
-      <c r="T62" s="18" t="inlineStr"/>
-      <c r="U62" s="18" t="inlineStr"/>
-      <c r="V62" s="18" t="inlineStr"/>
-      <c r="W62" s="18" t="inlineStr"/>
-      <c r="X62" s="18" t="inlineStr"/>
-      <c r="Y62" s="17" t="inlineStr">
+      <c r="C62" s="19" t="inlineStr"/>
+      <c r="D62" s="19" t="inlineStr"/>
+      <c r="E62" s="19" t="inlineStr"/>
+      <c r="F62" s="19" t="inlineStr"/>
+      <c r="G62" s="19" t="inlineStr"/>
+      <c r="H62" s="19" t="inlineStr"/>
+      <c r="I62" s="19" t="inlineStr"/>
+      <c r="J62" s="19" t="inlineStr"/>
+      <c r="K62" s="19" t="inlineStr"/>
+      <c r="L62" s="19" t="inlineStr"/>
+      <c r="M62" s="19" t="inlineStr"/>
+      <c r="N62" s="19" t="inlineStr"/>
+      <c r="O62" s="19" t="inlineStr"/>
+      <c r="P62" s="19" t="inlineStr"/>
+      <c r="Q62" s="19" t="inlineStr"/>
+      <c r="R62" s="19" t="inlineStr"/>
+      <c r="S62" s="19" t="inlineStr"/>
+      <c r="T62" s="19" t="inlineStr"/>
+      <c r="U62" s="19" t="inlineStr"/>
+      <c r="V62" s="19" t="inlineStr"/>
+      <c r="W62" s="19" t="inlineStr"/>
+      <c r="X62" s="19" t="inlineStr"/>
+      <c r="Y62" s="18" t="inlineStr">
         <is>
           <t>Missing — 2 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="16" t="n">
+      <c r="A63" s="17" t="n">
         <v>1977</v>
       </c>
-      <c r="B63" s="17" t="inlineStr">
+      <c r="B63" s="18" t="inlineStr">
         <is>
           <t>Gainesville, FL; Missing</t>
         </is>
       </c>
-      <c r="C63" s="18" t="inlineStr"/>
-      <c r="D63" s="18" t="inlineStr"/>
-      <c r="E63" s="18" t="inlineStr"/>
-      <c r="F63" s="18" t="inlineStr"/>
-      <c r="G63" s="18" t="inlineStr"/>
-      <c r="H63" s="18" t="inlineStr"/>
-      <c r="I63" s="18" t="inlineStr"/>
-      <c r="J63" s="18" t="inlineStr"/>
-      <c r="K63" s="18" t="inlineStr"/>
-      <c r="L63" s="18" t="inlineStr"/>
-      <c r="M63" s="18" t="inlineStr"/>
-      <c r="N63" s="18" t="inlineStr"/>
-      <c r="O63" s="18" t="inlineStr"/>
-      <c r="P63" s="18" t="inlineStr"/>
-      <c r="Q63" s="18" t="inlineStr"/>
-      <c r="R63" s="18" t="inlineStr"/>
-      <c r="S63" s="18" t="inlineStr"/>
-      <c r="T63" s="18" t="inlineStr"/>
-      <c r="U63" s="18" t="inlineStr"/>
-      <c r="V63" s="18" t="inlineStr"/>
-      <c r="W63" s="18" t="inlineStr"/>
-      <c r="X63" s="18" t="inlineStr"/>
-      <c r="Y63" s="18" t="inlineStr"/>
+      <c r="C63" s="19" t="inlineStr"/>
+      <c r="D63" s="19" t="inlineStr"/>
+      <c r="E63" s="19" t="inlineStr"/>
+      <c r="F63" s="19" t="inlineStr"/>
+      <c r="G63" s="19" t="inlineStr"/>
+      <c r="H63" s="19" t="inlineStr"/>
+      <c r="I63" s="19" t="inlineStr"/>
+      <c r="J63" s="19" t="inlineStr"/>
+      <c r="K63" s="19" t="inlineStr"/>
+      <c r="L63" s="19" t="inlineStr"/>
+      <c r="M63" s="19" t="inlineStr"/>
+      <c r="N63" s="19" t="inlineStr"/>
+      <c r="O63" s="19" t="inlineStr"/>
+      <c r="P63" s="19" t="inlineStr"/>
+      <c r="Q63" s="19" t="inlineStr"/>
+      <c r="R63" s="19" t="inlineStr"/>
+      <c r="S63" s="19" t="inlineStr"/>
+      <c r="T63" s="19" t="inlineStr"/>
+      <c r="U63" s="19" t="inlineStr"/>
+      <c r="V63" s="19" t="inlineStr"/>
+      <c r="W63" s="19" t="inlineStr"/>
+      <c r="X63" s="19" t="inlineStr"/>
+      <c r="Y63" s="19" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="16" t="n">
+      <c r="A64" s="17" t="n">
         <v>1978</v>
       </c>
-      <c r="B64" s="17" t="inlineStr">
+      <c r="B64" s="18" t="inlineStr">
         <is>
           <t>Tempe, AZ; Missing</t>
         </is>
       </c>
-      <c r="C64" s="18" t="inlineStr"/>
-      <c r="D64" s="18" t="inlineStr"/>
-      <c r="E64" s="18" t="inlineStr"/>
-      <c r="F64" s="18" t="inlineStr"/>
-      <c r="G64" s="18" t="inlineStr"/>
-      <c r="H64" s="18" t="inlineStr"/>
-      <c r="I64" s="18" t="inlineStr"/>
-      <c r="J64" s="18" t="inlineStr"/>
-      <c r="K64" s="18" t="inlineStr"/>
-      <c r="L64" s="18" t="inlineStr"/>
-      <c r="M64" s="18" t="inlineStr"/>
-      <c r="N64" s="18" t="inlineStr"/>
-      <c r="O64" s="18" t="inlineStr"/>
-      <c r="P64" s="18" t="inlineStr"/>
-      <c r="Q64" s="18" t="inlineStr"/>
-      <c r="R64" s="18" t="inlineStr"/>
-      <c r="S64" s="18" t="inlineStr"/>
-      <c r="T64" s="18" t="inlineStr"/>
-      <c r="U64" s="18" t="inlineStr"/>
-      <c r="V64" s="18" t="inlineStr"/>
-      <c r="W64" s="18" t="inlineStr"/>
-      <c r="X64" s="18" t="inlineStr"/>
-      <c r="Y64" s="18" t="inlineStr"/>
+      <c r="C64" s="19" t="inlineStr"/>
+      <c r="D64" s="19" t="inlineStr"/>
+      <c r="E64" s="19" t="inlineStr"/>
+      <c r="F64" s="19" t="inlineStr"/>
+      <c r="G64" s="19" t="inlineStr"/>
+      <c r="H64" s="19" t="inlineStr"/>
+      <c r="I64" s="19" t="inlineStr"/>
+      <c r="J64" s="19" t="inlineStr"/>
+      <c r="K64" s="19" t="inlineStr"/>
+      <c r="L64" s="19" t="inlineStr"/>
+      <c r="M64" s="19" t="inlineStr"/>
+      <c r="N64" s="19" t="inlineStr"/>
+      <c r="O64" s="19" t="inlineStr"/>
+      <c r="P64" s="19" t="inlineStr"/>
+      <c r="Q64" s="19" t="inlineStr"/>
+      <c r="R64" s="19" t="inlineStr"/>
+      <c r="S64" s="19" t="inlineStr"/>
+      <c r="T64" s="19" t="inlineStr"/>
+      <c r="U64" s="19" t="inlineStr"/>
+      <c r="V64" s="19" t="inlineStr"/>
+      <c r="W64" s="19" t="inlineStr"/>
+      <c r="X64" s="19" t="inlineStr"/>
+      <c r="Y64" s="19" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="16" t="n">
+      <c r="A65" s="17" t="n">
         <v>1979</v>
       </c>
-      <c r="B65" s="17" t="inlineStr">
+      <c r="B65" s="18" t="inlineStr">
         <is>
           <t>Orono, ME; Missing</t>
         </is>
       </c>
-      <c r="C65" s="18" t="inlineStr"/>
-      <c r="D65" s="18" t="inlineStr"/>
-      <c r="E65" s="18" t="inlineStr"/>
-      <c r="F65" s="18" t="inlineStr"/>
-      <c r="G65" s="18" t="inlineStr"/>
-      <c r="H65" s="18" t="inlineStr"/>
-      <c r="I65" s="18" t="inlineStr"/>
-      <c r="J65" s="18" t="inlineStr"/>
-      <c r="K65" s="18" t="inlineStr"/>
-      <c r="L65" s="18" t="inlineStr"/>
-      <c r="M65" s="18" t="inlineStr"/>
-      <c r="N65" s="18" t="inlineStr"/>
-      <c r="O65" s="18" t="inlineStr"/>
-      <c r="P65" s="18" t="inlineStr"/>
-      <c r="Q65" s="18" t="inlineStr"/>
-      <c r="R65" s="18" t="inlineStr"/>
-      <c r="S65" s="18" t="inlineStr"/>
-      <c r="T65" s="18" t="inlineStr"/>
-      <c r="U65" s="18" t="inlineStr"/>
-      <c r="V65" s="18" t="inlineStr"/>
-      <c r="W65" s="18" t="inlineStr"/>
-      <c r="X65" s="18" t="inlineStr"/>
-      <c r="Y65" s="18" t="inlineStr"/>
+      <c r="C65" s="19" t="inlineStr"/>
+      <c r="D65" s="19" t="inlineStr"/>
+      <c r="E65" s="19" t="inlineStr"/>
+      <c r="F65" s="19" t="inlineStr"/>
+      <c r="G65" s="19" t="inlineStr"/>
+      <c r="H65" s="19" t="inlineStr"/>
+      <c r="I65" s="19" t="inlineStr"/>
+      <c r="J65" s="19" t="inlineStr"/>
+      <c r="K65" s="19" t="inlineStr"/>
+      <c r="L65" s="19" t="inlineStr"/>
+      <c r="M65" s="19" t="inlineStr"/>
+      <c r="N65" s="19" t="inlineStr"/>
+      <c r="O65" s="19" t="inlineStr"/>
+      <c r="P65" s="19" t="inlineStr"/>
+      <c r="Q65" s="19" t="inlineStr"/>
+      <c r="R65" s="19" t="inlineStr"/>
+      <c r="S65" s="19" t="inlineStr"/>
+      <c r="T65" s="19" t="inlineStr"/>
+      <c r="U65" s="19" t="inlineStr"/>
+      <c r="V65" s="19" t="inlineStr"/>
+      <c r="W65" s="19" t="inlineStr"/>
+      <c r="X65" s="19" t="inlineStr"/>
+      <c r="Y65" s="19" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="16" t="n">
+      <c r="A66" s="17" t="n">
         <v>1980</v>
       </c>
-      <c r="B66" s="17" t="inlineStr">
+      <c r="B66" s="18" t="inlineStr">
         <is>
           <t>Fort Worth, TX; Missing</t>
         </is>
       </c>
-      <c r="C66" s="18" t="inlineStr"/>
-      <c r="D66" s="18" t="inlineStr"/>
-      <c r="E66" s="18" t="inlineStr"/>
-      <c r="F66" s="18" t="inlineStr"/>
-      <c r="G66" s="18" t="inlineStr"/>
-      <c r="H66" s="18" t="inlineStr"/>
-      <c r="I66" s="18" t="inlineStr"/>
-      <c r="J66" s="18" t="inlineStr"/>
-      <c r="K66" s="18" t="inlineStr"/>
-      <c r="L66" s="18" t="inlineStr"/>
-      <c r="M66" s="18" t="inlineStr"/>
-      <c r="N66" s="18" t="inlineStr"/>
-      <c r="O66" s="18" t="inlineStr"/>
-      <c r="P66" s="18" t="inlineStr"/>
-      <c r="Q66" s="18" t="inlineStr"/>
-      <c r="R66" s="18" t="inlineStr"/>
-      <c r="S66" s="18" t="inlineStr"/>
-      <c r="T66" s="18" t="inlineStr"/>
-      <c r="U66" s="18" t="inlineStr"/>
-      <c r="V66" s="18" t="inlineStr"/>
-      <c r="W66" s="18" t="inlineStr"/>
-      <c r="X66" s="18" t="inlineStr"/>
-      <c r="Y66" s="17" t="inlineStr">
+      <c r="C66" s="19" t="inlineStr"/>
+      <c r="D66" s="19" t="inlineStr"/>
+      <c r="E66" s="19" t="inlineStr"/>
+      <c r="F66" s="19" t="inlineStr"/>
+      <c r="G66" s="19" t="inlineStr"/>
+      <c r="H66" s="19" t="inlineStr"/>
+      <c r="I66" s="19" t="inlineStr"/>
+      <c r="J66" s="19" t="inlineStr"/>
+      <c r="K66" s="19" t="inlineStr"/>
+      <c r="L66" s="19" t="inlineStr"/>
+      <c r="M66" s="19" t="inlineStr"/>
+      <c r="N66" s="19" t="inlineStr"/>
+      <c r="O66" s="19" t="inlineStr"/>
+      <c r="P66" s="19" t="inlineStr"/>
+      <c r="Q66" s="19" t="inlineStr"/>
+      <c r="R66" s="19" t="inlineStr"/>
+      <c r="S66" s="19" t="inlineStr"/>
+      <c r="T66" s="19" t="inlineStr"/>
+      <c r="U66" s="19" t="inlineStr"/>
+      <c r="V66" s="19" t="inlineStr"/>
+      <c r="W66" s="19" t="inlineStr"/>
+      <c r="X66" s="19" t="inlineStr"/>
+      <c r="Y66" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="16" t="n">
+      <c r="A67" s="17" t="n">
         <v>1981</v>
       </c>
-      <c r="B67" s="17" t="inlineStr">
+      <c r="B67" s="18" t="inlineStr">
         <is>
           <t>Corvallis, OR; Missing</t>
         </is>
       </c>
-      <c r="C67" s="18" t="inlineStr"/>
-      <c r="D67" s="18" t="inlineStr"/>
-      <c r="E67" s="18" t="inlineStr"/>
-      <c r="F67" s="18" t="inlineStr"/>
-      <c r="G67" s="18" t="inlineStr"/>
-      <c r="H67" s="18" t="inlineStr"/>
-      <c r="I67" s="18" t="inlineStr"/>
-      <c r="J67" s="18" t="inlineStr"/>
-      <c r="K67" s="18" t="inlineStr"/>
-      <c r="L67" s="18" t="inlineStr"/>
-      <c r="M67" s="18" t="inlineStr"/>
-      <c r="N67" s="18" t="inlineStr"/>
-      <c r="O67" s="18" t="inlineStr"/>
-      <c r="P67" s="18" t="inlineStr"/>
-      <c r="Q67" s="18" t="inlineStr"/>
-      <c r="R67" s="18" t="inlineStr"/>
-      <c r="S67" s="18" t="inlineStr"/>
-      <c r="T67" s="18" t="inlineStr"/>
-      <c r="U67" s="18" t="inlineStr"/>
-      <c r="V67" s="18" t="inlineStr"/>
-      <c r="W67" s="18" t="inlineStr"/>
-      <c r="X67" s="18" t="inlineStr"/>
-      <c r="Y67" s="18" t="inlineStr"/>
+      <c r="C67" s="19" t="inlineStr"/>
+      <c r="D67" s="19" t="inlineStr"/>
+      <c r="E67" s="19" t="inlineStr"/>
+      <c r="F67" s="19" t="inlineStr"/>
+      <c r="G67" s="19" t="inlineStr"/>
+      <c r="H67" s="19" t="inlineStr"/>
+      <c r="I67" s="19" t="inlineStr"/>
+      <c r="J67" s="19" t="inlineStr"/>
+      <c r="K67" s="19" t="inlineStr"/>
+      <c r="L67" s="19" t="inlineStr"/>
+      <c r="M67" s="19" t="inlineStr"/>
+      <c r="N67" s="19" t="inlineStr"/>
+      <c r="O67" s="19" t="inlineStr"/>
+      <c r="P67" s="19" t="inlineStr"/>
+      <c r="Q67" s="19" t="inlineStr"/>
+      <c r="R67" s="19" t="inlineStr"/>
+      <c r="S67" s="19" t="inlineStr"/>
+      <c r="T67" s="19" t="inlineStr"/>
+      <c r="U67" s="19" t="inlineStr"/>
+      <c r="V67" s="19" t="inlineStr"/>
+      <c r="W67" s="19" t="inlineStr"/>
+      <c r="X67" s="19" t="inlineStr"/>
+      <c r="Y67" s="19" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="16" t="n">
+      <c r="A68" s="17" t="n">
         <v>1982</v>
       </c>
-      <c r="B68" s="17" t="inlineStr">
+      <c r="B68" s="18" t="inlineStr">
         <is>
           <t>DeKalb, IL; Missing</t>
         </is>
       </c>
-      <c r="C68" s="18" t="inlineStr"/>
-      <c r="D68" s="18" t="inlineStr"/>
-      <c r="E68" s="18" t="inlineStr"/>
-      <c r="F68" s="18" t="inlineStr"/>
-      <c r="G68" s="18" t="inlineStr"/>
-      <c r="H68" s="18" t="inlineStr"/>
-      <c r="I68" s="18" t="inlineStr"/>
-      <c r="J68" s="18" t="inlineStr"/>
-      <c r="K68" s="18" t="inlineStr"/>
-      <c r="L68" s="18" t="inlineStr"/>
-      <c r="M68" s="18" t="inlineStr"/>
-      <c r="N68" s="18" t="inlineStr"/>
-      <c r="O68" s="18" t="inlineStr"/>
-      <c r="P68" s="18" t="inlineStr"/>
-      <c r="Q68" s="18" t="inlineStr"/>
-      <c r="R68" s="18" t="inlineStr"/>
-      <c r="S68" s="18" t="inlineStr"/>
-      <c r="T68" s="18" t="inlineStr"/>
-      <c r="U68" s="18" t="inlineStr"/>
-      <c r="V68" s="18" t="inlineStr"/>
-      <c r="W68" s="18" t="inlineStr"/>
-      <c r="X68" s="18" t="inlineStr"/>
-      <c r="Y68" s="18" t="inlineStr"/>
+      <c r="C68" s="19" t="inlineStr"/>
+      <c r="D68" s="19" t="inlineStr"/>
+      <c r="E68" s="19" t="inlineStr"/>
+      <c r="F68" s="19" t="inlineStr"/>
+      <c r="G68" s="19" t="inlineStr"/>
+      <c r="H68" s="19" t="inlineStr"/>
+      <c r="I68" s="19" t="inlineStr"/>
+      <c r="J68" s="19" t="inlineStr"/>
+      <c r="K68" s="19" t="inlineStr"/>
+      <c r="L68" s="19" t="inlineStr"/>
+      <c r="M68" s="19" t="inlineStr"/>
+      <c r="N68" s="19" t="inlineStr"/>
+      <c r="O68" s="19" t="inlineStr"/>
+      <c r="P68" s="19" t="inlineStr"/>
+      <c r="Q68" s="19" t="inlineStr"/>
+      <c r="R68" s="19" t="inlineStr"/>
+      <c r="S68" s="19" t="inlineStr"/>
+      <c r="T68" s="19" t="inlineStr"/>
+      <c r="U68" s="19" t="inlineStr"/>
+      <c r="V68" s="19" t="inlineStr"/>
+      <c r="W68" s="19" t="inlineStr"/>
+      <c r="X68" s="19" t="inlineStr"/>
+      <c r="Y68" s="19" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="16" t="n">
+      <c r="A69" s="17" t="n">
         <v>1983</v>
       </c>
-      <c r="B69" s="17" t="inlineStr">
+      <c r="B69" s="18" t="inlineStr">
         <is>
           <t>Tallahasee, FL; Missing</t>
         </is>
       </c>
-      <c r="C69" s="17" t="inlineStr">
+      <c r="C69" s="18" t="inlineStr">
         <is>
           <t>Tallahasee, FL; Missing</t>
         </is>
       </c>
-      <c r="D69" s="18" t="inlineStr"/>
-      <c r="E69" s="18" t="inlineStr"/>
-      <c r="F69" s="18" t="inlineStr"/>
-      <c r="G69" s="18" t="inlineStr"/>
-      <c r="H69" s="18" t="inlineStr"/>
-      <c r="I69" s="18" t="inlineStr"/>
-      <c r="J69" s="18" t="inlineStr"/>
-      <c r="K69" s="18" t="inlineStr"/>
-      <c r="L69" s="18" t="inlineStr"/>
-      <c r="M69" s="18" t="inlineStr"/>
-      <c r="N69" s="18" t="inlineStr"/>
-      <c r="O69" s="18" t="inlineStr"/>
-      <c r="P69" s="18" t="inlineStr"/>
-      <c r="Q69" s="18" t="inlineStr"/>
-      <c r="R69" s="18" t="inlineStr"/>
-      <c r="S69" s="18" t="inlineStr"/>
-      <c r="T69" s="18" t="inlineStr"/>
-      <c r="U69" s="18" t="inlineStr"/>
-      <c r="V69" s="18" t="inlineStr"/>
-      <c r="W69" s="18" t="inlineStr"/>
-      <c r="X69" s="17" t="inlineStr">
+      <c r="D69" s="19" t="inlineStr"/>
+      <c r="E69" s="19" t="inlineStr"/>
+      <c r="F69" s="19" t="inlineStr"/>
+      <c r="G69" s="19" t="inlineStr"/>
+      <c r="H69" s="19" t="inlineStr"/>
+      <c r="I69" s="19" t="inlineStr"/>
+      <c r="J69" s="19" t="inlineStr"/>
+      <c r="K69" s="19" t="inlineStr"/>
+      <c r="L69" s="19" t="inlineStr"/>
+      <c r="M69" s="19" t="inlineStr"/>
+      <c r="N69" s="19" t="inlineStr"/>
+      <c r="O69" s="19" t="inlineStr"/>
+      <c r="P69" s="19" t="inlineStr"/>
+      <c r="Q69" s="19" t="inlineStr"/>
+      <c r="R69" s="19" t="inlineStr"/>
+      <c r="S69" s="19" t="inlineStr"/>
+      <c r="T69" s="19" t="inlineStr"/>
+      <c r="U69" s="19" t="inlineStr"/>
+      <c r="V69" s="19" t="inlineStr"/>
+      <c r="W69" s="19" t="inlineStr"/>
+      <c r="X69" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 5 abstracts cited by the corpus</t>
         </is>
       </c>
-      <c r="Y69" s="18" t="inlineStr"/>
+      <c r="Y69" s="19" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="16" t="n">
+      <c r="A70" s="17" t="n">
         <v>1984</v>
       </c>
-      <c r="B70" s="17" t="inlineStr">
+      <c r="B70" s="18" t="inlineStr">
         <is>
           <t>Norman, OK; Missing</t>
         </is>
       </c>
-      <c r="C70" s="17" t="inlineStr">
+      <c r="C70" s="18" t="inlineStr">
         <is>
           <t>Norman, OK; Missing</t>
         </is>
       </c>
-      <c r="D70" s="18" t="inlineStr"/>
-      <c r="E70" s="18" t="inlineStr"/>
-      <c r="F70" s="18" t="inlineStr"/>
-      <c r="G70" s="18" t="inlineStr"/>
-      <c r="H70" s="18" t="inlineStr"/>
-      <c r="I70" s="18" t="inlineStr"/>
-      <c r="J70" s="18" t="inlineStr"/>
-      <c r="K70" s="18" t="inlineStr"/>
-      <c r="L70" s="18" t="inlineStr"/>
-      <c r="M70" s="18" t="inlineStr"/>
-      <c r="N70" s="18" t="inlineStr"/>
-      <c r="O70" s="18" t="inlineStr"/>
-      <c r="P70" s="18" t="inlineStr"/>
-      <c r="Q70" s="18" t="inlineStr"/>
-      <c r="R70" s="18" t="inlineStr"/>
-      <c r="S70" s="18" t="inlineStr"/>
-      <c r="T70" s="18" t="inlineStr"/>
-      <c r="U70" s="18" t="inlineStr"/>
-      <c r="V70" s="18" t="inlineStr"/>
-      <c r="W70" s="18" t="inlineStr"/>
-      <c r="X70" s="18" t="inlineStr"/>
-      <c r="Y70" s="17" t="inlineStr">
+      <c r="D70" s="19" t="inlineStr"/>
+      <c r="E70" s="19" t="inlineStr"/>
+      <c r="F70" s="19" t="inlineStr"/>
+      <c r="G70" s="19" t="inlineStr"/>
+      <c r="H70" s="19" t="inlineStr"/>
+      <c r="I70" s="19" t="inlineStr"/>
+      <c r="J70" s="19" t="inlineStr"/>
+      <c r="K70" s="19" t="inlineStr"/>
+      <c r="L70" s="19" t="inlineStr"/>
+      <c r="M70" s="19" t="inlineStr"/>
+      <c r="N70" s="19" t="inlineStr"/>
+      <c r="O70" s="19" t="inlineStr"/>
+      <c r="P70" s="19" t="inlineStr"/>
+      <c r="Q70" s="19" t="inlineStr"/>
+      <c r="R70" s="19" t="inlineStr"/>
+      <c r="S70" s="19" t="inlineStr"/>
+      <c r="T70" s="19" t="inlineStr"/>
+      <c r="U70" s="19" t="inlineStr"/>
+      <c r="V70" s="19" t="inlineStr"/>
+      <c r="W70" s="19" t="inlineStr"/>
+      <c r="X70" s="19" t="inlineStr"/>
+      <c r="Y70" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="16" t="n">
+      <c r="A71" s="17" t="n">
         <v>1985</v>
       </c>
-      <c r="B71" s="17" t="inlineStr">
+      <c r="B71" s="18" t="inlineStr">
         <is>
           <t>Knoxville, TN; Missing</t>
         </is>
       </c>
-      <c r="C71" s="19" t="inlineStr">
+      <c r="C71" s="20" t="inlineStr">
         <is>
           <t>Knoxville, TN (26); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D71" s="18" t="inlineStr"/>
-      <c r="E71" s="18" t="inlineStr"/>
-      <c r="F71" s="18" t="inlineStr"/>
-      <c r="G71" s="18" t="inlineStr"/>
-      <c r="H71" s="18" t="inlineStr"/>
-      <c r="I71" s="18" t="inlineStr"/>
-      <c r="J71" s="18" t="inlineStr"/>
-      <c r="K71" s="18" t="inlineStr"/>
-      <c r="L71" s="18" t="inlineStr"/>
-      <c r="M71" s="18" t="inlineStr"/>
-      <c r="N71" s="18" t="inlineStr"/>
-      <c r="O71" s="17" t="inlineStr">
+      <c r="D71" s="19" t="inlineStr"/>
+      <c r="E71" s="19" t="inlineStr"/>
+      <c r="F71" s="19" t="inlineStr"/>
+      <c r="G71" s="19" t="inlineStr"/>
+      <c r="H71" s="19" t="inlineStr"/>
+      <c r="I71" s="19" t="inlineStr"/>
+      <c r="J71" s="19" t="inlineStr"/>
+      <c r="K71" s="19" t="inlineStr"/>
+      <c r="L71" s="19" t="inlineStr"/>
+      <c r="M71" s="19" t="inlineStr"/>
+      <c r="N71" s="19" t="inlineStr"/>
+      <c r="O71" s="18" t="inlineStr">
         <is>
           <t>Tokyo, Japan; Missing — 37 abstracts cited by the corpus [Published 1986]</t>
         </is>
       </c>
-      <c r="P71" s="18" t="inlineStr"/>
-      <c r="Q71" s="18" t="inlineStr"/>
-      <c r="R71" s="18" t="inlineStr"/>
-      <c r="S71" s="18" t="inlineStr"/>
-      <c r="T71" s="18" t="inlineStr"/>
-      <c r="U71" s="18" t="inlineStr"/>
-      <c r="V71" s="18" t="inlineStr"/>
-      <c r="W71" s="18" t="inlineStr"/>
-      <c r="X71" s="18" t="inlineStr"/>
-      <c r="Y71" s="18" t="inlineStr"/>
+      <c r="P71" s="19" t="inlineStr"/>
+      <c r="Q71" s="19" t="inlineStr"/>
+      <c r="R71" s="19" t="inlineStr"/>
+      <c r="S71" s="19" t="inlineStr"/>
+      <c r="T71" s="19" t="inlineStr"/>
+      <c r="U71" s="19" t="inlineStr"/>
+      <c r="V71" s="19" t="inlineStr"/>
+      <c r="W71" s="19" t="inlineStr"/>
+      <c r="X71" s="19" t="inlineStr"/>
+      <c r="Y71" s="19" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="16" t="n">
+      <c r="A72" s="17" t="n">
         <v>1986</v>
       </c>
-      <c r="B72" s="17" t="inlineStr">
+      <c r="B72" s="18" t="inlineStr">
         <is>
           <t>Victoria, BC; Missing</t>
         </is>
       </c>
-      <c r="C72" s="19" t="inlineStr">
+      <c r="C72" s="20" t="inlineStr">
         <is>
           <t>Victoria, BC (35); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D72" s="18" t="inlineStr"/>
-      <c r="E72" s="18" t="inlineStr"/>
-      <c r="F72" s="18" t="inlineStr"/>
-      <c r="G72" s="18" t="inlineStr"/>
-      <c r="H72" s="18" t="inlineStr"/>
-      <c r="I72" s="18" t="inlineStr"/>
-      <c r="J72" s="18" t="inlineStr"/>
-      <c r="K72" s="18" t="inlineStr"/>
-      <c r="L72" s="18" t="inlineStr"/>
-      <c r="M72" s="18" t="inlineStr"/>
-      <c r="N72" s="18" t="inlineStr"/>
-      <c r="O72" s="18" t="inlineStr"/>
-      <c r="P72" s="18" t="inlineStr"/>
-      <c r="Q72" s="18" t="inlineStr"/>
-      <c r="R72" s="18" t="inlineStr"/>
-      <c r="S72" s="18" t="inlineStr"/>
-      <c r="T72" s="18" t="inlineStr"/>
-      <c r="U72" s="18" t="inlineStr"/>
-      <c r="V72" s="18" t="inlineStr"/>
-      <c r="W72" s="18" t="inlineStr"/>
-      <c r="X72" s="18" t="inlineStr"/>
-      <c r="Y72" s="18" t="inlineStr"/>
+      <c r="D72" s="19" t="inlineStr"/>
+      <c r="E72" s="19" t="inlineStr"/>
+      <c r="F72" s="19" t="inlineStr"/>
+      <c r="G72" s="19" t="inlineStr"/>
+      <c r="H72" s="19" t="inlineStr"/>
+      <c r="I72" s="19" t="inlineStr"/>
+      <c r="J72" s="19" t="inlineStr"/>
+      <c r="K72" s="19" t="inlineStr"/>
+      <c r="L72" s="19" t="inlineStr"/>
+      <c r="M72" s="19" t="inlineStr"/>
+      <c r="N72" s="19" t="inlineStr"/>
+      <c r="O72" s="19" t="inlineStr"/>
+      <c r="P72" s="19" t="inlineStr"/>
+      <c r="Q72" s="19" t="inlineStr"/>
+      <c r="R72" s="19" t="inlineStr"/>
+      <c r="S72" s="19" t="inlineStr"/>
+      <c r="T72" s="19" t="inlineStr"/>
+      <c r="U72" s="19" t="inlineStr"/>
+      <c r="V72" s="19" t="inlineStr"/>
+      <c r="W72" s="19" t="inlineStr"/>
+      <c r="X72" s="19" t="inlineStr"/>
+      <c r="Y72" s="19" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="16" t="n">
+      <c r="A73" s="17" t="n">
         <v>1987</v>
       </c>
-      <c r="B73" s="17" t="inlineStr">
+      <c r="B73" s="18" t="inlineStr">
         <is>
           <t>Albany, NY; Missing</t>
         </is>
       </c>
-      <c r="C73" s="19" t="inlineStr">
+      <c r="C73" s="20" t="inlineStr">
         <is>
           <t>Albany, NY (33); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D73" s="18" t="inlineStr"/>
-      <c r="E73" s="18" t="inlineStr"/>
-      <c r="F73" s="18" t="inlineStr"/>
-      <c r="G73" s="18" t="inlineStr"/>
-      <c r="H73" s="18" t="inlineStr"/>
-      <c r="I73" s="18" t="inlineStr"/>
-      <c r="J73" s="18" t="inlineStr"/>
-      <c r="K73" s="18" t="inlineStr"/>
-      <c r="L73" s="18" t="inlineStr"/>
-      <c r="M73" s="18" t="inlineStr"/>
-      <c r="N73" s="18" t="inlineStr"/>
-      <c r="O73" s="18" t="inlineStr"/>
-      <c r="P73" s="18" t="inlineStr"/>
-      <c r="Q73" s="18" t="inlineStr"/>
-      <c r="R73" s="18" t="inlineStr"/>
-      <c r="S73" s="18" t="inlineStr"/>
-      <c r="T73" s="18" t="inlineStr"/>
-      <c r="U73" s="18" t="inlineStr"/>
-      <c r="V73" s="18" t="inlineStr"/>
-      <c r="W73" s="18" t="inlineStr"/>
-      <c r="X73" s="18" t="inlineStr"/>
-      <c r="Y73" s="17" t="inlineStr">
+      <c r="D73" s="19" t="inlineStr"/>
+      <c r="E73" s="19" t="inlineStr"/>
+      <c r="F73" s="19" t="inlineStr"/>
+      <c r="G73" s="19" t="inlineStr"/>
+      <c r="H73" s="19" t="inlineStr"/>
+      <c r="I73" s="19" t="inlineStr"/>
+      <c r="J73" s="19" t="inlineStr"/>
+      <c r="K73" s="19" t="inlineStr"/>
+      <c r="L73" s="19" t="inlineStr"/>
+      <c r="M73" s="19" t="inlineStr"/>
+      <c r="N73" s="19" t="inlineStr"/>
+      <c r="O73" s="19" t="inlineStr"/>
+      <c r="P73" s="19" t="inlineStr"/>
+      <c r="Q73" s="19" t="inlineStr"/>
+      <c r="R73" s="19" t="inlineStr"/>
+      <c r="S73" s="19" t="inlineStr"/>
+      <c r="T73" s="19" t="inlineStr"/>
+      <c r="U73" s="19" t="inlineStr"/>
+      <c r="V73" s="19" t="inlineStr"/>
+      <c r="W73" s="19" t="inlineStr"/>
+      <c r="X73" s="19" t="inlineStr"/>
+      <c r="Y73" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="16" t="n">
+      <c r="A74" s="17" t="n">
         <v>1988</v>
       </c>
-      <c r="B74" s="17" t="inlineStr">
+      <c r="B74" s="18" t="inlineStr">
         <is>
           <t>Ann Arbor, MI; Missing</t>
         </is>
       </c>
-      <c r="C74" s="19" t="inlineStr">
+      <c r="C74" s="20" t="inlineStr">
         <is>
           <t>Ann Arbor, MI (34); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D74" s="18" t="inlineStr"/>
-      <c r="E74" s="18" t="inlineStr"/>
-      <c r="F74" s="18" t="inlineStr"/>
-      <c r="G74" s="18" t="inlineStr"/>
-      <c r="H74" s="18" t="inlineStr"/>
-      <c r="I74" s="18" t="inlineStr"/>
-      <c r="J74" s="18" t="inlineStr"/>
-      <c r="K74" s="18" t="inlineStr"/>
-      <c r="L74" s="18" t="inlineStr"/>
-      <c r="M74" s="18" t="inlineStr"/>
-      <c r="N74" s="18" t="inlineStr"/>
-      <c r="O74" s="18" t="inlineStr"/>
-      <c r="P74" s="18" t="inlineStr"/>
-      <c r="Q74" s="18" t="inlineStr"/>
-      <c r="R74" s="18" t="inlineStr"/>
-      <c r="S74" s="18" t="inlineStr"/>
-      <c r="T74" s="18" t="inlineStr"/>
-      <c r="U74" s="18" t="inlineStr"/>
-      <c r="V74" s="18" t="inlineStr"/>
-      <c r="W74" s="18" t="inlineStr"/>
-      <c r="X74" s="18" t="inlineStr"/>
-      <c r="Y74" s="18" t="inlineStr"/>
+      <c r="D74" s="19" t="inlineStr"/>
+      <c r="E74" s="19" t="inlineStr"/>
+      <c r="F74" s="19" t="inlineStr"/>
+      <c r="G74" s="19" t="inlineStr"/>
+      <c r="H74" s="19" t="inlineStr"/>
+      <c r="I74" s="19" t="inlineStr"/>
+      <c r="J74" s="19" t="inlineStr"/>
+      <c r="K74" s="19" t="inlineStr"/>
+      <c r="L74" s="19" t="inlineStr"/>
+      <c r="M74" s="19" t="inlineStr"/>
+      <c r="N74" s="19" t="inlineStr"/>
+      <c r="O74" s="19" t="inlineStr"/>
+      <c r="P74" s="19" t="inlineStr"/>
+      <c r="Q74" s="19" t="inlineStr"/>
+      <c r="R74" s="19" t="inlineStr"/>
+      <c r="S74" s="19" t="inlineStr"/>
+      <c r="T74" s="19" t="inlineStr"/>
+      <c r="U74" s="19" t="inlineStr"/>
+      <c r="V74" s="19" t="inlineStr"/>
+      <c r="W74" s="19" t="inlineStr"/>
+      <c r="X74" s="19" t="inlineStr"/>
+      <c r="Y74" s="19" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="16" t="n">
+      <c r="A75" s="17" t="n">
         <v>1989</v>
       </c>
-      <c r="B75" s="17" t="inlineStr">
+      <c r="B75" s="18" t="inlineStr">
         <is>
           <t>San Francisco, CA; Missing</t>
         </is>
       </c>
-      <c r="C75" s="19" t="inlineStr">
+      <c r="C75" s="20" t="inlineStr">
         <is>
           <t>San Francisco, CA (63); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D75" s="18" t="inlineStr"/>
-      <c r="E75" s="18" t="inlineStr"/>
-      <c r="F75" s="18" t="inlineStr"/>
-      <c r="G75" s="18" t="inlineStr"/>
-      <c r="H75" s="18" t="inlineStr"/>
-      <c r="I75" s="18" t="inlineStr"/>
-      <c r="J75" s="18" t="inlineStr"/>
-      <c r="K75" s="18" t="inlineStr"/>
-      <c r="L75" s="18" t="inlineStr"/>
-      <c r="M75" s="18" t="inlineStr"/>
-      <c r="N75" s="18" t="inlineStr"/>
-      <c r="O75" s="18" t="inlineStr"/>
-      <c r="P75" s="18" t="inlineStr"/>
-      <c r="Q75" s="18" t="inlineStr"/>
-      <c r="R75" s="18" t="inlineStr"/>
-      <c r="S75" s="18" t="inlineStr"/>
-      <c r="T75" s="18" t="inlineStr"/>
-      <c r="U75" s="18" t="inlineStr"/>
-      <c r="V75" s="18" t="inlineStr"/>
-      <c r="W75" s="18" t="inlineStr"/>
-      <c r="X75" s="18" t="inlineStr"/>
-      <c r="Y75" s="18" t="inlineStr"/>
+      <c r="D75" s="19" t="inlineStr"/>
+      <c r="E75" s="19" t="inlineStr"/>
+      <c r="F75" s="19" t="inlineStr"/>
+      <c r="G75" s="19" t="inlineStr"/>
+      <c r="H75" s="19" t="inlineStr"/>
+      <c r="I75" s="19" t="inlineStr"/>
+      <c r="J75" s="19" t="inlineStr"/>
+      <c r="K75" s="19" t="inlineStr"/>
+      <c r="L75" s="19" t="inlineStr"/>
+      <c r="M75" s="19" t="inlineStr"/>
+      <c r="N75" s="19" t="inlineStr"/>
+      <c r="O75" s="19" t="inlineStr"/>
+      <c r="P75" s="19" t="inlineStr"/>
+      <c r="Q75" s="19" t="inlineStr"/>
+      <c r="R75" s="19" t="inlineStr"/>
+      <c r="S75" s="19" t="inlineStr"/>
+      <c r="T75" s="19" t="inlineStr"/>
+      <c r="U75" s="19" t="inlineStr"/>
+      <c r="V75" s="19" t="inlineStr"/>
+      <c r="W75" s="19" t="inlineStr"/>
+      <c r="X75" s="19" t="inlineStr"/>
+      <c r="Y75" s="19" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="16" t="n">
+      <c r="A76" s="17" t="n">
         <v>1990</v>
       </c>
-      <c r="B76" s="17" t="inlineStr">
+      <c r="B76" s="18" t="inlineStr">
         <is>
           <t>Charleston, SC; Missing</t>
         </is>
       </c>
-      <c r="C76" s="19" t="inlineStr">
+      <c r="C76" s="20" t="inlineStr">
         <is>
           <t>Charleston, SC (47); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D76" s="18" t="inlineStr"/>
-      <c r="E76" s="18" t="inlineStr"/>
-      <c r="F76" s="18" t="inlineStr"/>
-      <c r="G76" s="18" t="inlineStr"/>
-      <c r="H76" s="18" t="inlineStr"/>
-      <c r="I76" s="18" t="inlineStr"/>
-      <c r="J76" s="18" t="inlineStr"/>
-      <c r="K76" s="18" t="inlineStr"/>
-      <c r="L76" s="18" t="inlineStr"/>
-      <c r="M76" s="18" t="inlineStr"/>
-      <c r="N76" s="18" t="inlineStr"/>
-      <c r="O76" s="18" t="inlineStr"/>
-      <c r="P76" s="18" t="inlineStr"/>
-      <c r="Q76" s="18" t="inlineStr"/>
-      <c r="R76" s="18" t="inlineStr"/>
-      <c r="S76" s="18" t="inlineStr"/>
-      <c r="T76" s="18" t="inlineStr"/>
-      <c r="U76" s="18" t="inlineStr"/>
-      <c r="V76" s="18" t="inlineStr"/>
-      <c r="W76" s="18" t="inlineStr"/>
-      <c r="X76" s="18" t="inlineStr"/>
-      <c r="Y76" s="18" t="inlineStr"/>
+      <c r="D76" s="19" t="inlineStr"/>
+      <c r="E76" s="19" t="inlineStr"/>
+      <c r="F76" s="19" t="inlineStr"/>
+      <c r="G76" s="19" t="inlineStr"/>
+      <c r="H76" s="19" t="inlineStr"/>
+      <c r="I76" s="19" t="inlineStr"/>
+      <c r="J76" s="19" t="inlineStr"/>
+      <c r="K76" s="19" t="inlineStr"/>
+      <c r="L76" s="19" t="inlineStr"/>
+      <c r="M76" s="19" t="inlineStr"/>
+      <c r="N76" s="19" t="inlineStr"/>
+      <c r="O76" s="19" t="inlineStr"/>
+      <c r="P76" s="19" t="inlineStr"/>
+      <c r="Q76" s="19" t="inlineStr"/>
+      <c r="R76" s="19" t="inlineStr"/>
+      <c r="S76" s="19" t="inlineStr"/>
+      <c r="T76" s="19" t="inlineStr"/>
+      <c r="U76" s="19" t="inlineStr"/>
+      <c r="V76" s="19" t="inlineStr"/>
+      <c r="W76" s="19" t="inlineStr"/>
+      <c r="X76" s="19" t="inlineStr"/>
+      <c r="Y76" s="19" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="16" t="n">
+      <c r="A77" s="17" t="n">
         <v>1991</v>
       </c>
-      <c r="B77" s="17" t="inlineStr">
+      <c r="B77" s="18" t="inlineStr">
         <is>
           <t>New York, NY; Missing</t>
         </is>
       </c>
-      <c r="C77" s="19" t="inlineStr">
+      <c r="C77" s="20" t="inlineStr">
         <is>
           <t>New York, NY (34); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D77" s="18" t="inlineStr"/>
-      <c r="E77" s="18" t="inlineStr"/>
-      <c r="F77" s="18" t="inlineStr"/>
-      <c r="G77" s="18" t="inlineStr"/>
-      <c r="H77" s="18" t="inlineStr"/>
-      <c r="I77" s="18" t="inlineStr"/>
-      <c r="J77" s="18" t="inlineStr"/>
-      <c r="K77" s="18" t="inlineStr"/>
-      <c r="L77" s="18" t="inlineStr"/>
-      <c r="M77" s="18" t="inlineStr"/>
-      <c r="N77" s="18" t="inlineStr"/>
-      <c r="O77" s="18" t="inlineStr"/>
-      <c r="P77" s="18" t="inlineStr"/>
-      <c r="Q77" s="18" t="inlineStr"/>
-      <c r="R77" s="18" t="inlineStr"/>
-      <c r="S77" s="18" t="inlineStr"/>
-      <c r="T77" s="18" t="inlineStr"/>
-      <c r="U77" s="18" t="inlineStr"/>
-      <c r="V77" s="18" t="inlineStr"/>
-      <c r="W77" s="18" t="inlineStr"/>
-      <c r="X77" s="18" t="inlineStr"/>
-      <c r="Y77" s="18" t="inlineStr"/>
+      <c r="D77" s="19" t="inlineStr"/>
+      <c r="E77" s="19" t="inlineStr"/>
+      <c r="F77" s="19" t="inlineStr"/>
+      <c r="G77" s="19" t="inlineStr"/>
+      <c r="H77" s="19" t="inlineStr"/>
+      <c r="I77" s="19" t="inlineStr"/>
+      <c r="J77" s="19" t="inlineStr"/>
+      <c r="K77" s="19" t="inlineStr"/>
+      <c r="L77" s="19" t="inlineStr"/>
+      <c r="M77" s="19" t="inlineStr"/>
+      <c r="N77" s="19" t="inlineStr"/>
+      <c r="O77" s="19" t="inlineStr"/>
+      <c r="P77" s="19" t="inlineStr"/>
+      <c r="Q77" s="19" t="inlineStr"/>
+      <c r="R77" s="19" t="inlineStr"/>
+      <c r="S77" s="19" t="inlineStr"/>
+      <c r="T77" s="19" t="inlineStr"/>
+      <c r="U77" s="19" t="inlineStr"/>
+      <c r="V77" s="19" t="inlineStr"/>
+      <c r="W77" s="19" t="inlineStr"/>
+      <c r="X77" s="19" t="inlineStr"/>
+      <c r="Y77" s="19" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="16" t="n">
+      <c r="A78" s="17" t="n">
         <v>1992</v>
       </c>
-      <c r="B78" s="20" t="inlineStr">
+      <c r="B78" s="21" t="inlineStr">
         <is>
           <t>Champaign-Urbana, IL; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C78" s="19" t="inlineStr">
+      <c r="C78" s="20" t="inlineStr">
         <is>
           <t>Champaign-Urbana, IL (41); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D78" s="18" t="inlineStr"/>
-      <c r="E78" s="18" t="inlineStr"/>
-      <c r="F78" s="18" t="inlineStr"/>
-      <c r="G78" s="18" t="inlineStr"/>
-      <c r="H78" s="18" t="inlineStr"/>
-      <c r="I78" s="18" t="inlineStr"/>
-      <c r="J78" s="18" t="inlineStr"/>
-      <c r="K78" s="18" t="inlineStr"/>
-      <c r="L78" s="18" t="inlineStr"/>
-      <c r="M78" s="18" t="inlineStr"/>
-      <c r="N78" s="18" t="inlineStr"/>
-      <c r="O78" s="18" t="inlineStr"/>
-      <c r="P78" s="18" t="inlineStr"/>
-      <c r="Q78" s="18" t="inlineStr"/>
-      <c r="R78" s="18" t="inlineStr"/>
-      <c r="S78" s="18" t="inlineStr"/>
-      <c r="T78" s="18" t="inlineStr"/>
-      <c r="U78" s="18" t="inlineStr"/>
-      <c r="V78" s="18" t="inlineStr"/>
-      <c r="W78" s="18" t="inlineStr"/>
-      <c r="X78" s="18" t="inlineStr"/>
-      <c r="Y78" s="18" t="inlineStr"/>
+      <c r="D78" s="19" t="inlineStr"/>
+      <c r="E78" s="19" t="inlineStr"/>
+      <c r="F78" s="19" t="inlineStr"/>
+      <c r="G78" s="19" t="inlineStr"/>
+      <c r="H78" s="19" t="inlineStr"/>
+      <c r="I78" s="19" t="inlineStr"/>
+      <c r="J78" s="19" t="inlineStr"/>
+      <c r="K78" s="19" t="inlineStr"/>
+      <c r="L78" s="19" t="inlineStr"/>
+      <c r="M78" s="19" t="inlineStr"/>
+      <c r="N78" s="19" t="inlineStr"/>
+      <c r="O78" s="19" t="inlineStr"/>
+      <c r="P78" s="19" t="inlineStr"/>
+      <c r="Q78" s="19" t="inlineStr"/>
+      <c r="R78" s="19" t="inlineStr"/>
+      <c r="S78" s="19" t="inlineStr"/>
+      <c r="T78" s="19" t="inlineStr"/>
+      <c r="U78" s="19" t="inlineStr"/>
+      <c r="V78" s="19" t="inlineStr"/>
+      <c r="W78" s="19" t="inlineStr"/>
+      <c r="X78" s="19" t="inlineStr"/>
+      <c r="Y78" s="19" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="16" t="n">
+      <c r="A79" s="17" t="n">
         <v>1993</v>
       </c>
-      <c r="B79" s="20" t="inlineStr">
+      <c r="B79" s="21" t="inlineStr">
         <is>
           <t>Austin, TX; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C79" s="19" t="inlineStr">
+      <c r="C79" s="20" t="inlineStr">
         <is>
           <t>Austin, TX (45); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D79" s="18" t="inlineStr"/>
-      <c r="E79" s="18" t="inlineStr"/>
-      <c r="F79" s="18" t="inlineStr"/>
-      <c r="G79" s="18" t="inlineStr"/>
-      <c r="H79" s="18" t="inlineStr"/>
-      <c r="I79" s="18" t="inlineStr"/>
-      <c r="J79" s="18" t="inlineStr"/>
-      <c r="K79" s="18" t="inlineStr"/>
-      <c r="L79" s="18" t="inlineStr"/>
-      <c r="M79" s="18" t="inlineStr"/>
-      <c r="N79" s="18" t="inlineStr"/>
-      <c r="O79" s="17" t="inlineStr">
+      <c r="D79" s="19" t="inlineStr"/>
+      <c r="E79" s="19" t="inlineStr"/>
+      <c r="F79" s="19" t="inlineStr"/>
+      <c r="G79" s="19" t="inlineStr"/>
+      <c r="H79" s="19" t="inlineStr"/>
+      <c r="I79" s="19" t="inlineStr"/>
+      <c r="J79" s="19" t="inlineStr"/>
+      <c r="K79" s="19" t="inlineStr"/>
+      <c r="L79" s="19" t="inlineStr"/>
+      <c r="M79" s="19" t="inlineStr"/>
+      <c r="N79" s="19" t="inlineStr"/>
+      <c r="O79" s="18" t="inlineStr">
         <is>
           <t>Bangkok, Thailand; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="P79" s="18" t="inlineStr"/>
-      <c r="Q79" s="18" t="inlineStr"/>
-      <c r="R79" s="18" t="inlineStr"/>
-      <c r="S79" s="18" t="inlineStr"/>
-      <c r="T79" s="18" t="inlineStr"/>
-      <c r="U79" s="18" t="inlineStr"/>
-      <c r="V79" s="18" t="inlineStr"/>
-      <c r="W79" s="18" t="inlineStr"/>
-      <c r="X79" s="18" t="inlineStr"/>
-      <c r="Y79" s="17" t="inlineStr">
+      <c r="P79" s="19" t="inlineStr"/>
+      <c r="Q79" s="19" t="inlineStr"/>
+      <c r="R79" s="19" t="inlineStr"/>
+      <c r="S79" s="19" t="inlineStr"/>
+      <c r="T79" s="19" t="inlineStr"/>
+      <c r="U79" s="19" t="inlineStr"/>
+      <c r="V79" s="19" t="inlineStr"/>
+      <c r="W79" s="19" t="inlineStr"/>
+      <c r="X79" s="19" t="inlineStr"/>
+      <c r="Y79" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="16" t="n">
+      <c r="A80" s="17" t="n">
         <v>1994</v>
       </c>
-      <c r="B80" s="20" t="inlineStr">
+      <c r="B80" s="21" t="inlineStr">
         <is>
           <t>Los Angeles, CA; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C80" s="19" t="inlineStr">
+      <c r="C80" s="20" t="inlineStr">
         <is>
           <t>Los Angeles, CA (50); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D80" s="18" t="inlineStr"/>
-      <c r="E80" s="18" t="inlineStr"/>
-      <c r="F80" s="18" t="inlineStr"/>
-      <c r="G80" s="18" t="inlineStr"/>
-      <c r="H80" s="18" t="inlineStr"/>
-      <c r="I80" s="18" t="inlineStr"/>
-      <c r="J80" s="18" t="inlineStr"/>
-      <c r="K80" s="18" t="inlineStr"/>
-      <c r="L80" s="18" t="inlineStr"/>
-      <c r="M80" s="18" t="inlineStr"/>
-      <c r="N80" s="18" t="inlineStr"/>
-      <c r="O80" s="18" t="inlineStr"/>
-      <c r="P80" s="18" t="inlineStr"/>
-      <c r="Q80" s="18" t="inlineStr"/>
-      <c r="R80" s="18" t="inlineStr"/>
-      <c r="S80" s="18" t="inlineStr"/>
-      <c r="T80" s="18" t="inlineStr"/>
-      <c r="U80" s="18" t="inlineStr"/>
-      <c r="V80" s="18" t="inlineStr"/>
-      <c r="W80" s="18" t="inlineStr"/>
-      <c r="X80" s="18" t="inlineStr"/>
-      <c r="Y80" s="17" t="inlineStr">
+      <c r="D80" s="19" t="inlineStr"/>
+      <c r="E80" s="19" t="inlineStr"/>
+      <c r="F80" s="19" t="inlineStr"/>
+      <c r="G80" s="19" t="inlineStr"/>
+      <c r="H80" s="19" t="inlineStr"/>
+      <c r="I80" s="19" t="inlineStr"/>
+      <c r="J80" s="19" t="inlineStr"/>
+      <c r="K80" s="19" t="inlineStr"/>
+      <c r="L80" s="19" t="inlineStr"/>
+      <c r="M80" s="19" t="inlineStr"/>
+      <c r="N80" s="19" t="inlineStr"/>
+      <c r="O80" s="19" t="inlineStr"/>
+      <c r="P80" s="19" t="inlineStr"/>
+      <c r="Q80" s="19" t="inlineStr"/>
+      <c r="R80" s="19" t="inlineStr"/>
+      <c r="S80" s="19" t="inlineStr"/>
+      <c r="T80" s="19" t="inlineStr"/>
+      <c r="U80" s="19" t="inlineStr"/>
+      <c r="V80" s="19" t="inlineStr"/>
+      <c r="W80" s="19" t="inlineStr"/>
+      <c r="X80" s="19" t="inlineStr"/>
+      <c r="Y80" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 2 abstracts cited by the corpus</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="16" t="n">
+      <c r="A81" s="17" t="n">
         <v>1995</v>
       </c>
-      <c r="B81" s="20" t="inlineStr">
+      <c r="B81" s="21" t="inlineStr">
         <is>
           <t>Edmonton, AB; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C81" s="19" t="inlineStr">
+      <c r="C81" s="20" t="inlineStr">
         <is>
           <t>Edmonton, AB (46); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D81" s="18" t="inlineStr"/>
-      <c r="E81" s="18" t="inlineStr"/>
-      <c r="F81" s="18" t="inlineStr"/>
-      <c r="G81" s="18" t="inlineStr"/>
-      <c r="H81" s="18" t="inlineStr"/>
-      <c r="I81" s="18" t="inlineStr"/>
-      <c r="J81" s="18" t="inlineStr"/>
-      <c r="K81" s="18" t="inlineStr"/>
-      <c r="L81" s="18" t="inlineStr"/>
-      <c r="M81" s="18" t="inlineStr"/>
-      <c r="N81" s="18" t="inlineStr"/>
-      <c r="O81" s="18" t="inlineStr"/>
-      <c r="P81" s="18" t="inlineStr"/>
-      <c r="Q81" s="18" t="inlineStr"/>
-      <c r="R81" s="18" t="inlineStr"/>
-      <c r="S81" s="18" t="inlineStr"/>
-      <c r="T81" s="18" t="inlineStr"/>
-      <c r="U81" s="18" t="inlineStr"/>
-      <c r="V81" s="18" t="inlineStr"/>
-      <c r="W81" s="18" t="inlineStr"/>
-      <c r="X81" s="18" t="inlineStr"/>
-      <c r="Y81" s="18" t="inlineStr"/>
+      <c r="D81" s="19" t="inlineStr"/>
+      <c r="E81" s="19" t="inlineStr"/>
+      <c r="F81" s="19" t="inlineStr"/>
+      <c r="G81" s="19" t="inlineStr"/>
+      <c r="H81" s="19" t="inlineStr"/>
+      <c r="I81" s="19" t="inlineStr"/>
+      <c r="J81" s="19" t="inlineStr"/>
+      <c r="K81" s="19" t="inlineStr"/>
+      <c r="L81" s="19" t="inlineStr"/>
+      <c r="M81" s="19" t="inlineStr"/>
+      <c r="N81" s="19" t="inlineStr"/>
+      <c r="O81" s="19" t="inlineStr"/>
+      <c r="P81" s="19" t="inlineStr"/>
+      <c r="Q81" s="19" t="inlineStr"/>
+      <c r="R81" s="19" t="inlineStr"/>
+      <c r="S81" s="19" t="inlineStr"/>
+      <c r="T81" s="19" t="inlineStr"/>
+      <c r="U81" s="19" t="inlineStr"/>
+      <c r="V81" s="19" t="inlineStr"/>
+      <c r="W81" s="19" t="inlineStr"/>
+      <c r="X81" s="19" t="inlineStr"/>
+      <c r="Y81" s="19" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="16" t="n">
+      <c r="A82" s="17" t="n">
         <v>1996</v>
       </c>
-      <c r="B82" s="20" t="inlineStr">
+      <c r="B82" s="21" t="inlineStr">
         <is>
           <t>New Orleans, LA; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C82" s="19" t="inlineStr">
+      <c r="C82" s="20" t="inlineStr">
         <is>
           <t>New Orleans, LA (98); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D82" s="18" t="inlineStr"/>
-      <c r="E82" s="18" t="inlineStr"/>
-      <c r="F82" s="18" t="inlineStr"/>
-      <c r="G82" s="18" t="inlineStr"/>
-      <c r="H82" s="18" t="inlineStr"/>
-      <c r="I82" s="18" t="inlineStr"/>
-      <c r="J82" s="18" t="inlineStr"/>
-      <c r="K82" s="18" t="inlineStr"/>
-      <c r="L82" s="18" t="inlineStr"/>
-      <c r="M82" s="18" t="inlineStr"/>
-      <c r="N82" s="18" t="inlineStr"/>
-      <c r="O82" s="18" t="inlineStr"/>
-      <c r="P82" s="18" t="inlineStr"/>
-      <c r="Q82" s="18" t="inlineStr"/>
-      <c r="R82" s="18" t="inlineStr"/>
-      <c r="S82" s="18" t="inlineStr"/>
-      <c r="T82" s="18" t="inlineStr"/>
-      <c r="U82" s="18" t="inlineStr"/>
-      <c r="V82" s="18" t="inlineStr"/>
-      <c r="W82" s="18" t="inlineStr"/>
-      <c r="X82" s="18" t="inlineStr"/>
-      <c r="Y82" s="18" t="inlineStr"/>
+      <c r="D82" s="19" t="inlineStr"/>
+      <c r="E82" s="19" t="inlineStr"/>
+      <c r="F82" s="19" t="inlineStr"/>
+      <c r="G82" s="19" t="inlineStr"/>
+      <c r="H82" s="19" t="inlineStr"/>
+      <c r="I82" s="19" t="inlineStr"/>
+      <c r="J82" s="19" t="inlineStr"/>
+      <c r="K82" s="19" t="inlineStr"/>
+      <c r="L82" s="19" t="inlineStr"/>
+      <c r="M82" s="19" t="inlineStr"/>
+      <c r="N82" s="19" t="inlineStr"/>
+      <c r="O82" s="19" t="inlineStr"/>
+      <c r="P82" s="19" t="inlineStr"/>
+      <c r="Q82" s="19" t="inlineStr"/>
+      <c r="R82" s="19" t="inlineStr"/>
+      <c r="S82" s="19" t="inlineStr"/>
+      <c r="T82" s="19" t="inlineStr"/>
+      <c r="U82" s="19" t="inlineStr"/>
+      <c r="V82" s="19" t="inlineStr"/>
+      <c r="W82" s="19" t="inlineStr"/>
+      <c r="X82" s="19" t="inlineStr"/>
+      <c r="Y82" s="19" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="16" t="n">
+      <c r="A83" s="17" t="n">
         <v>1997</v>
       </c>
-      <c r="B83" s="21" t="inlineStr">
+      <c r="B83" s="22" t="inlineStr">
         <is>
           <t>Seattle, WA; OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
         </is>
       </c>
-      <c r="C83" s="19" t="inlineStr">
+      <c r="C83" s="20" t="inlineStr">
         <is>
           <t>Seattle, WA (68); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D83" s="17" t="inlineStr">
+      <c r="D83" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1st EEA; no known abstract source; host city also unknown</t>
         </is>
       </c>
-      <c r="E83" s="18" t="inlineStr"/>
-      <c r="F83" s="18" t="inlineStr"/>
-      <c r="G83" s="18" t="inlineStr"/>
-      <c r="H83" s="18" t="inlineStr"/>
-      <c r="I83" s="18" t="inlineStr"/>
-      <c r="J83" s="18" t="inlineStr"/>
-      <c r="K83" s="18" t="inlineStr"/>
-      <c r="L83" s="18" t="inlineStr"/>
-      <c r="M83" s="18" t="inlineStr"/>
-      <c r="N83" s="17" t="inlineStr">
+      <c r="E83" s="19" t="inlineStr"/>
+      <c r="F83" s="19" t="inlineStr"/>
+      <c r="G83" s="19" t="inlineStr"/>
+      <c r="H83" s="19" t="inlineStr"/>
+      <c r="I83" s="19" t="inlineStr"/>
+      <c r="J83" s="19" t="inlineStr"/>
+      <c r="K83" s="19" t="inlineStr"/>
+      <c r="L83" s="19" t="inlineStr"/>
+      <c r="M83" s="19" t="inlineStr"/>
+      <c r="N83" s="18" t="inlineStr">
         <is>
           <t>Prague, Czech Republic; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="O83" s="17" t="inlineStr">
+      <c r="O83" s="18" t="inlineStr">
         <is>
           <t>Noumea, New Caledonia; Missing — 11 abstracts cited by the corpus [Published 1999, 2002]</t>
         </is>
       </c>
-      <c r="P83" s="18" t="inlineStr"/>
-      <c r="Q83" s="18" t="inlineStr"/>
-      <c r="R83" s="18" t="inlineStr"/>
-      <c r="S83" s="18" t="inlineStr"/>
-      <c r="T83" s="18" t="inlineStr"/>
-      <c r="U83" s="18" t="inlineStr"/>
-      <c r="V83" s="18" t="inlineStr"/>
-      <c r="W83" s="18" t="inlineStr"/>
-      <c r="X83" s="18" t="inlineStr"/>
-      <c r="Y83" s="17" t="inlineStr">
+      <c r="P83" s="19" t="inlineStr"/>
+      <c r="Q83" s="19" t="inlineStr"/>
+      <c r="R83" s="19" t="inlineStr"/>
+      <c r="S83" s="19" t="inlineStr"/>
+      <c r="T83" s="19" t="inlineStr"/>
+      <c r="U83" s="19" t="inlineStr"/>
+      <c r="V83" s="19" t="inlineStr"/>
+      <c r="W83" s="19" t="inlineStr"/>
+      <c r="X83" s="19" t="inlineStr"/>
+      <c r="Y83" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="16" t="n">
+      <c r="A84" s="17" t="n">
         <v>1998</v>
       </c>
-      <c r="B84" s="19" t="inlineStr">
+      <c r="B84" s="20" t="inlineStr">
         <is>
           <t>Guelph, ON; Ingested</t>
         </is>
       </c>
-      <c r="C84" s="19" t="inlineStr">
+      <c r="C84" s="20" t="inlineStr">
         <is>
           <t>Guelph, ON (63); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D84" s="17" t="inlineStr">
+      <c r="D84" s="18" t="inlineStr">
         <is>
           <t>Lisbon; Missing — 2nd EEA; no known abstract source</t>
         </is>
       </c>
-      <c r="E84" s="18" t="inlineStr"/>
-      <c r="F84" s="18" t="inlineStr"/>
-      <c r="G84" s="18" t="inlineStr"/>
-      <c r="H84" s="18" t="inlineStr"/>
-      <c r="I84" s="18" t="inlineStr"/>
-      <c r="J84" s="18" t="inlineStr"/>
-      <c r="K84" s="18" t="inlineStr"/>
-      <c r="L84" s="18" t="inlineStr"/>
-      <c r="M84" s="18" t="inlineStr"/>
-      <c r="N84" s="18" t="inlineStr"/>
-      <c r="O84" s="18" t="inlineStr"/>
-      <c r="P84" s="18" t="inlineStr"/>
-      <c r="Q84" s="18" t="inlineStr"/>
-      <c r="R84" s="18" t="inlineStr"/>
-      <c r="S84" s="18" t="inlineStr"/>
-      <c r="T84" s="18" t="inlineStr"/>
-      <c r="U84" s="18" t="inlineStr"/>
-      <c r="V84" s="18" t="inlineStr"/>
-      <c r="W84" s="18" t="inlineStr"/>
-      <c r="X84" s="18" t="inlineStr"/>
-      <c r="Y84" s="18" t="inlineStr"/>
+      <c r="E84" s="19" t="inlineStr"/>
+      <c r="F84" s="19" t="inlineStr"/>
+      <c r="G84" s="19" t="inlineStr"/>
+      <c r="H84" s="19" t="inlineStr"/>
+      <c r="I84" s="19" t="inlineStr"/>
+      <c r="J84" s="19" t="inlineStr"/>
+      <c r="K84" s="19" t="inlineStr"/>
+      <c r="L84" s="19" t="inlineStr"/>
+      <c r="M84" s="19" t="inlineStr"/>
+      <c r="N84" s="19" t="inlineStr"/>
+      <c r="O84" s="19" t="inlineStr"/>
+      <c r="P84" s="19" t="inlineStr"/>
+      <c r="Q84" s="19" t="inlineStr"/>
+      <c r="R84" s="19" t="inlineStr"/>
+      <c r="S84" s="19" t="inlineStr"/>
+      <c r="T84" s="19" t="inlineStr"/>
+      <c r="U84" s="19" t="inlineStr"/>
+      <c r="V84" s="19" t="inlineStr"/>
+      <c r="W84" s="19" t="inlineStr"/>
+      <c r="X84" s="19" t="inlineStr"/>
+      <c r="Y84" s="19" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="16" t="n">
+      <c r="A85" s="17" t="n">
         <v>1999</v>
       </c>
-      <c r="B85" s="21" t="inlineStr">
+      <c r="B85" s="22" t="inlineStr">
         <is>
           <t>University Park, PA; OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
         </is>
       </c>
-      <c r="C85" s="19" t="inlineStr">
+      <c r="C85" s="20" t="inlineStr">
         <is>
           <t>University Park, PA (78); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D85" s="17" t="inlineStr">
+      <c r="D85" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 3rd EEA; no known abstract source; host city also unknown</t>
         </is>
       </c>
-      <c r="E85" s="18" t="inlineStr"/>
-      <c r="F85" s="18" t="inlineStr"/>
-      <c r="G85" s="18" t="inlineStr"/>
-      <c r="H85" s="18" t="inlineStr"/>
-      <c r="I85" s="18" t="inlineStr"/>
-      <c r="J85" s="18" t="inlineStr"/>
-      <c r="K85" s="18" t="inlineStr"/>
-      <c r="L85" s="18" t="inlineStr"/>
-      <c r="M85" s="18" t="inlineStr"/>
-      <c r="N85" s="18" t="inlineStr"/>
-      <c r="O85" s="18" t="inlineStr"/>
-      <c r="P85" s="18" t="inlineStr"/>
-      <c r="Q85" s="18" t="inlineStr"/>
-      <c r="R85" s="18" t="inlineStr"/>
-      <c r="S85" s="18" t="inlineStr"/>
-      <c r="T85" s="18" t="inlineStr"/>
-      <c r="U85" s="18" t="inlineStr"/>
-      <c r="V85" s="18" t="inlineStr"/>
-      <c r="W85" s="18" t="inlineStr"/>
-      <c r="X85" s="18" t="inlineStr"/>
-      <c r="Y85" s="18" t="inlineStr"/>
+      <c r="E85" s="19" t="inlineStr"/>
+      <c r="F85" s="19" t="inlineStr"/>
+      <c r="G85" s="19" t="inlineStr"/>
+      <c r="H85" s="19" t="inlineStr"/>
+      <c r="I85" s="19" t="inlineStr"/>
+      <c r="J85" s="19" t="inlineStr"/>
+      <c r="K85" s="19" t="inlineStr"/>
+      <c r="L85" s="19" t="inlineStr"/>
+      <c r="M85" s="19" t="inlineStr"/>
+      <c r="N85" s="19" t="inlineStr"/>
+      <c r="O85" s="19" t="inlineStr"/>
+      <c r="P85" s="19" t="inlineStr"/>
+      <c r="Q85" s="19" t="inlineStr"/>
+      <c r="R85" s="19" t="inlineStr"/>
+      <c r="S85" s="19" t="inlineStr"/>
+      <c r="T85" s="19" t="inlineStr"/>
+      <c r="U85" s="19" t="inlineStr"/>
+      <c r="V85" s="19" t="inlineStr"/>
+      <c r="W85" s="19" t="inlineStr"/>
+      <c r="X85" s="19" t="inlineStr"/>
+      <c r="Y85" s="19" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="16" t="n">
+      <c r="A86" s="17" t="n">
         <v>2000</v>
       </c>
-      <c r="B86" s="21" t="inlineStr">
+      <c r="B86" s="22" t="inlineStr">
         <is>
           <t>La Paz, Mexico; OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
         </is>
       </c>
-      <c r="C86" s="19" t="inlineStr">
+      <c r="C86" s="20" t="inlineStr">
         <is>
           <t>La Paz, Mexico (134); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D86" s="17" t="inlineStr">
+      <c r="D86" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 4th EEA; no known abstract source; host city also unknown</t>
         </is>
       </c>
-      <c r="E86" s="18" t="inlineStr"/>
-      <c r="F86" s="18" t="inlineStr"/>
-      <c r="G86" s="18" t="inlineStr"/>
-      <c r="H86" s="18" t="inlineStr"/>
-      <c r="I86" s="18" t="inlineStr"/>
-      <c r="J86" s="18" t="inlineStr"/>
-      <c r="K86" s="18" t="inlineStr"/>
-      <c r="L86" s="18" t="inlineStr"/>
-      <c r="M86" s="18" t="inlineStr"/>
-      <c r="N86" s="18" t="inlineStr"/>
-      <c r="O86" s="18" t="inlineStr"/>
-      <c r="P86" s="18" t="inlineStr"/>
-      <c r="Q86" s="18" t="inlineStr"/>
-      <c r="R86" s="18" t="inlineStr"/>
-      <c r="S86" s="18" t="inlineStr"/>
-      <c r="T86" s="18" t="inlineStr"/>
-      <c r="U86" s="18" t="inlineStr"/>
-      <c r="V86" s="18" t="inlineStr"/>
-      <c r="W86" s="18" t="inlineStr"/>
-      <c r="X86" s="18" t="inlineStr"/>
-      <c r="Y86" s="17" t="inlineStr">
+      <c r="E86" s="19" t="inlineStr"/>
+      <c r="F86" s="19" t="inlineStr"/>
+      <c r="G86" s="19" t="inlineStr"/>
+      <c r="H86" s="19" t="inlineStr"/>
+      <c r="I86" s="19" t="inlineStr"/>
+      <c r="J86" s="19" t="inlineStr"/>
+      <c r="K86" s="19" t="inlineStr"/>
+      <c r="L86" s="19" t="inlineStr"/>
+      <c r="M86" s="19" t="inlineStr"/>
+      <c r="N86" s="19" t="inlineStr"/>
+      <c r="O86" s="19" t="inlineStr"/>
+      <c r="P86" s="19" t="inlineStr"/>
+      <c r="Q86" s="19" t="inlineStr"/>
+      <c r="R86" s="19" t="inlineStr"/>
+      <c r="S86" s="19" t="inlineStr"/>
+      <c r="T86" s="19" t="inlineStr"/>
+      <c r="U86" s="19" t="inlineStr"/>
+      <c r="V86" s="19" t="inlineStr"/>
+      <c r="W86" s="19" t="inlineStr"/>
+      <c r="X86" s="19" t="inlineStr"/>
+      <c r="Y86" s="18" t="inlineStr">
         <is>
           <t>Missing — 3 abstracts cited by the corpus [3 distinct meetings]</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="16" t="n">
+      <c r="A87" s="17" t="n">
         <v>2001</v>
       </c>
-      <c r="B87" s="21" t="inlineStr">
+      <c r="B87" s="22" t="inlineStr">
         <is>
           <t>University Park, PA; OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
         </is>
       </c>
-      <c r="C87" s="19" t="inlineStr">
+      <c r="C87" s="20" t="inlineStr">
         <is>
           <t>University Park, PA (84); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D87" s="17" t="inlineStr">
+      <c r="D87" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 5th EEA; no known abstract source; host city also unknown</t>
         </is>
       </c>
-      <c r="E87" s="18" t="inlineStr"/>
-      <c r="F87" s="18" t="inlineStr"/>
-      <c r="G87" s="18" t="inlineStr"/>
-      <c r="H87" s="18" t="inlineStr"/>
-      <c r="I87" s="18" t="inlineStr"/>
-      <c r="J87" s="18" t="inlineStr"/>
-      <c r="K87" s="18" t="inlineStr"/>
-      <c r="L87" s="18" t="inlineStr"/>
-      <c r="M87" s="18" t="inlineStr"/>
-      <c r="N87" s="18" t="inlineStr"/>
-      <c r="O87" s="18" t="inlineStr"/>
-      <c r="P87" s="18" t="inlineStr"/>
-      <c r="Q87" s="18" t="inlineStr"/>
-      <c r="R87" s="18" t="inlineStr"/>
-      <c r="S87" s="18" t="inlineStr"/>
-      <c r="T87" s="17" t="inlineStr">
+      <c r="E87" s="19" t="inlineStr"/>
+      <c r="F87" s="19" t="inlineStr"/>
+      <c r="G87" s="19" t="inlineStr"/>
+      <c r="H87" s="19" t="inlineStr"/>
+      <c r="I87" s="19" t="inlineStr"/>
+      <c r="J87" s="19" t="inlineStr"/>
+      <c r="K87" s="19" t="inlineStr"/>
+      <c r="L87" s="19" t="inlineStr"/>
+      <c r="M87" s="19" t="inlineStr"/>
+      <c r="N87" s="19" t="inlineStr"/>
+      <c r="O87" s="19" t="inlineStr"/>
+      <c r="P87" s="19" t="inlineStr"/>
+      <c r="Q87" s="19" t="inlineStr"/>
+      <c r="R87" s="19" t="inlineStr"/>
+      <c r="S87" s="19" t="inlineStr"/>
+      <c r="T87" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="U87" s="18" t="inlineStr"/>
-      <c r="V87" s="18" t="inlineStr"/>
-      <c r="W87" s="18" t="inlineStr"/>
-      <c r="X87" s="18" t="inlineStr"/>
-      <c r="Y87" s="18" t="inlineStr"/>
+      <c r="U87" s="19" t="inlineStr"/>
+      <c r="V87" s="19" t="inlineStr"/>
+      <c r="W87" s="19" t="inlineStr"/>
+      <c r="X87" s="19" t="inlineStr"/>
+      <c r="Y87" s="19" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="16" t="n">
+      <c r="A88" s="17" t="n">
         <v>2002</v>
       </c>
-      <c r="B88" s="20" t="inlineStr">
+      <c r="B88" s="21" t="inlineStr">
         <is>
           <t>Kansas City, MO; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C88" s="19" t="inlineStr">
+      <c r="C88" s="20" t="inlineStr">
         <is>
           <t>Kansas City, MO (27); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D88" s="22" t="inlineStr">
+      <c r="D88" s="23" t="inlineStr">
         <is>
           <t>Cardiff; Digital — abstract booklet (Word) found by Ali Hood 2026-08-27; queued for extraction</t>
         </is>
       </c>
-      <c r="E88" s="18" t="inlineStr"/>
-      <c r="F88" s="18" t="inlineStr"/>
-      <c r="G88" s="18" t="inlineStr"/>
-      <c r="H88" s="17" t="inlineStr">
+      <c r="E88" s="19" t="inlineStr"/>
+      <c r="F88" s="19" t="inlineStr"/>
+      <c r="G88" s="19" t="inlineStr"/>
+      <c r="H88" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="I88" s="18" t="inlineStr"/>
-      <c r="J88" s="18" t="inlineStr"/>
-      <c r="K88" s="18" t="inlineStr"/>
-      <c r="L88" s="18" t="inlineStr"/>
-      <c r="M88" s="18" t="inlineStr"/>
-      <c r="N88" s="18" t="inlineStr"/>
-      <c r="O88" s="18" t="inlineStr"/>
-      <c r="P88" s="18" t="inlineStr"/>
-      <c r="Q88" s="18" t="inlineStr"/>
-      <c r="R88" s="18" t="inlineStr"/>
-      <c r="S88" s="18" t="inlineStr"/>
-      <c r="T88" s="18" t="inlineStr"/>
-      <c r="U88" s="18" t="inlineStr"/>
-      <c r="V88" s="18" t="inlineStr"/>
-      <c r="W88" s="18" t="inlineStr"/>
-      <c r="X88" s="18" t="inlineStr"/>
-      <c r="Y88" s="17" t="inlineStr">
+      <c r="I88" s="19" t="inlineStr"/>
+      <c r="J88" s="19" t="inlineStr"/>
+      <c r="K88" s="19" t="inlineStr"/>
+      <c r="L88" s="19" t="inlineStr"/>
+      <c r="M88" s="19" t="inlineStr"/>
+      <c r="N88" s="19" t="inlineStr"/>
+      <c r="O88" s="19" t="inlineStr"/>
+      <c r="P88" s="19" t="inlineStr"/>
+      <c r="Q88" s="19" t="inlineStr"/>
+      <c r="R88" s="19" t="inlineStr"/>
+      <c r="S88" s="19" t="inlineStr"/>
+      <c r="T88" s="19" t="inlineStr"/>
+      <c r="U88" s="19" t="inlineStr"/>
+      <c r="V88" s="19" t="inlineStr"/>
+      <c r="W88" s="19" t="inlineStr"/>
+      <c r="X88" s="19" t="inlineStr"/>
+      <c r="Y88" s="18" t="inlineStr">
         <is>
           <t>Missing — 7 abstracts cited by the corpus [6 distinct meetings]</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="16" t="n">
+      <c r="A89" s="17" t="n">
         <v>2003</v>
       </c>
-      <c r="B89" s="21" t="inlineStr">
+      <c r="B89" s="22" t="inlineStr">
         <is>
           <t>Manaus, Brazil; OCR — degraded phone scan — 0 abstracts recovered — flatbed re-scan needed (Carylanne)</t>
         </is>
       </c>
-      <c r="C89" s="19" t="inlineStr">
+      <c r="C89" s="20" t="inlineStr">
         <is>
           <t>Manaus, Brazil (82); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D89" s="23" t="inlineStr">
+      <c r="D89" s="24" t="inlineStr">
         <is>
           <t>San Marino; Pending — 7th EEA; Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
-      <c r="E89" s="18" t="inlineStr"/>
-      <c r="F89" s="18" t="inlineStr"/>
-      <c r="G89" s="18" t="inlineStr"/>
-      <c r="H89" s="18" t="inlineStr"/>
-      <c r="I89" s="18" t="inlineStr"/>
-      <c r="J89" s="18" t="inlineStr"/>
-      <c r="K89" s="18" t="inlineStr"/>
-      <c r="L89" s="18" t="inlineStr"/>
-      <c r="M89" s="18" t="inlineStr"/>
-      <c r="N89" s="18" t="inlineStr"/>
-      <c r="O89" s="18" t="inlineStr"/>
-      <c r="P89" s="18" t="inlineStr"/>
-      <c r="Q89" s="18" t="inlineStr"/>
-      <c r="R89" s="18" t="inlineStr"/>
-      <c r="S89" s="18" t="inlineStr"/>
-      <c r="T89" s="18" t="inlineStr"/>
-      <c r="U89" s="18" t="inlineStr"/>
-      <c r="V89" s="18" t="inlineStr"/>
-      <c r="W89" s="18" t="inlineStr"/>
-      <c r="X89" s="18" t="inlineStr"/>
-      <c r="Y89" s="17" t="inlineStr">
+      <c r="E89" s="19" t="inlineStr"/>
+      <c r="F89" s="19" t="inlineStr"/>
+      <c r="G89" s="19" t="inlineStr"/>
+      <c r="H89" s="19" t="inlineStr"/>
+      <c r="I89" s="19" t="inlineStr"/>
+      <c r="J89" s="19" t="inlineStr"/>
+      <c r="K89" s="19" t="inlineStr"/>
+      <c r="L89" s="19" t="inlineStr"/>
+      <c r="M89" s="19" t="inlineStr"/>
+      <c r="N89" s="19" t="inlineStr"/>
+      <c r="O89" s="19" t="inlineStr"/>
+      <c r="P89" s="19" t="inlineStr"/>
+      <c r="Q89" s="19" t="inlineStr"/>
+      <c r="R89" s="19" t="inlineStr"/>
+      <c r="S89" s="19" t="inlineStr"/>
+      <c r="T89" s="19" t="inlineStr"/>
+      <c r="U89" s="19" t="inlineStr"/>
+      <c r="V89" s="19" t="inlineStr"/>
+      <c r="W89" s="19" t="inlineStr"/>
+      <c r="X89" s="19" t="inlineStr"/>
+      <c r="Y89" s="18" t="inlineStr">
         <is>
           <t>Missing — 4 abstracts cited by the corpus [4 distinct meetings; Published 2006]</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="16" t="n">
+      <c r="A90" s="17" t="n">
         <v>2004</v>
       </c>
       <c r="B90" s="21" t="inlineStr">
         <is>
-          <t>Norman, OK; OCR — degraded phone scan — 0 abstracts recovered — flatbed re-scan needed (Carylanne)</t>
-        </is>
-      </c>
-      <c r="C90" s="19" t="inlineStr">
+          <t>Norman, OK; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+        </is>
+      </c>
+      <c r="C90" s="20" t="inlineStr">
         <is>
           <t>Norman, OK (59); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D90" s="19" t="inlineStr">
+      <c r="D90" s="20" t="inlineStr">
         <is>
           <t>London; Ingested — 55 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E90" s="18" t="inlineStr"/>
-      <c r="F90" s="18" t="inlineStr"/>
-      <c r="G90" s="18" t="inlineStr"/>
-      <c r="H90" s="18" t="inlineStr"/>
-      <c r="I90" s="22" t="inlineStr">
+      <c r="E90" s="19" t="inlineStr"/>
+      <c r="F90" s="19" t="inlineStr"/>
+      <c r="G90" s="19" t="inlineStr"/>
+      <c r="H90" s="19" t="inlineStr"/>
+      <c r="I90" s="23" t="inlineStr">
         <is>
           <t>Ciudad Universitaria, Mexico City; Digital — 1 PDF held — extraction pending</t>
         </is>
       </c>
-      <c r="J90" s="18" t="inlineStr"/>
-      <c r="K90" s="17" t="inlineStr">
+      <c r="J90" s="19" t="inlineStr"/>
+      <c r="K90" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="L90" s="18" t="inlineStr"/>
-      <c r="M90" s="18" t="inlineStr"/>
-      <c r="N90" s="18" t="inlineStr"/>
-      <c r="O90" s="18" t="inlineStr"/>
-      <c r="P90" s="18" t="inlineStr"/>
-      <c r="Q90" s="18" t="inlineStr"/>
-      <c r="R90" s="18" t="inlineStr"/>
-      <c r="S90" s="17" t="inlineStr">
+      <c r="L90" s="19" t="inlineStr"/>
+      <c r="M90" s="19" t="inlineStr"/>
+      <c r="N90" s="19" t="inlineStr"/>
+      <c r="O90" s="19" t="inlineStr"/>
+      <c r="P90" s="19" t="inlineStr"/>
+      <c r="Q90" s="19" t="inlineStr"/>
+      <c r="R90" s="19" t="inlineStr"/>
+      <c r="S90" s="18" t="inlineStr">
         <is>
           <t>Manaus, Brazil; Missing — 4 abstracts cited by the corpus</t>
         </is>
       </c>
-      <c r="T90" s="18" t="inlineStr"/>
-      <c r="U90" s="18" t="inlineStr"/>
-      <c r="V90" s="18" t="inlineStr"/>
-      <c r="W90" s="18" t="inlineStr"/>
-      <c r="X90" s="18" t="inlineStr"/>
-      <c r="Y90" s="17" t="inlineStr">
+      <c r="T90" s="19" t="inlineStr"/>
+      <c r="U90" s="19" t="inlineStr"/>
+      <c r="V90" s="19" t="inlineStr"/>
+      <c r="W90" s="19" t="inlineStr"/>
+      <c r="X90" s="19" t="inlineStr"/>
+      <c r="Y90" s="18" t="inlineStr">
         <is>
           <t>Missing — 2 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="16" t="n">
+      <c r="A91" s="17" t="n">
         <v>2005</v>
       </c>
-      <c r="B91" s="19" t="inlineStr">
+      <c r="B91" s="20" t="inlineStr">
         <is>
           <t>Tampa, FL; Ingested</t>
         </is>
       </c>
-      <c r="C91" s="19" t="inlineStr">
+      <c r="C91" s="20" t="inlineStr">
         <is>
           <t>Tampa, FL (158); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D91" s="23" t="inlineStr">
+      <c r="D91" s="24" t="inlineStr">
         <is>
           <t>Monaco; Pending — 9th EEA; Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
-      <c r="E91" s="18" t="inlineStr"/>
-      <c r="F91" s="18" t="inlineStr"/>
-      <c r="G91" s="18" t="inlineStr"/>
-      <c r="H91" s="18" t="inlineStr"/>
-      <c r="I91" s="18" t="inlineStr"/>
-      <c r="J91" s="18" t="inlineStr"/>
-      <c r="K91" s="18" t="inlineStr"/>
-      <c r="L91" s="18" t="inlineStr"/>
-      <c r="M91" s="18" t="inlineStr"/>
-      <c r="N91" s="18" t="inlineStr"/>
-      <c r="O91" s="18" t="inlineStr"/>
-      <c r="P91" s="18" t="inlineStr"/>
-      <c r="Q91" s="18" t="inlineStr"/>
-      <c r="R91" s="18" t="inlineStr"/>
-      <c r="S91" s="18" t="inlineStr"/>
-      <c r="T91" s="17" t="inlineStr">
+      <c r="E91" s="19" t="inlineStr"/>
+      <c r="F91" s="19" t="inlineStr"/>
+      <c r="G91" s="19" t="inlineStr"/>
+      <c r="H91" s="19" t="inlineStr"/>
+      <c r="I91" s="19" t="inlineStr"/>
+      <c r="J91" s="19" t="inlineStr"/>
+      <c r="K91" s="19" t="inlineStr"/>
+      <c r="L91" s="19" t="inlineStr"/>
+      <c r="M91" s="19" t="inlineStr"/>
+      <c r="N91" s="19" t="inlineStr"/>
+      <c r="O91" s="19" t="inlineStr"/>
+      <c r="P91" s="19" t="inlineStr"/>
+      <c r="Q91" s="19" t="inlineStr"/>
+      <c r="R91" s="19" t="inlineStr"/>
+      <c r="S91" s="19" t="inlineStr"/>
+      <c r="T91" s="18" t="inlineStr">
         <is>
           <t>Miraflores de la Sierra, Madrid, Spain; Missing — 2 abstracts cited by the corpus</t>
         </is>
       </c>
-      <c r="U91" s="18" t="inlineStr"/>
-      <c r="V91" s="18" t="inlineStr"/>
-      <c r="W91" s="18" t="inlineStr"/>
-      <c r="X91" s="18" t="inlineStr"/>
-      <c r="Y91" s="17" t="inlineStr">
+      <c r="U91" s="19" t="inlineStr"/>
+      <c r="V91" s="19" t="inlineStr"/>
+      <c r="W91" s="19" t="inlineStr"/>
+      <c r="X91" s="19" t="inlineStr"/>
+      <c r="Y91" s="18" t="inlineStr">
         <is>
           <t>Missing — 2 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="16" t="n">
+      <c r="A92" s="17" t="n">
         <v>2006</v>
       </c>
-      <c r="B92" s="19" t="inlineStr">
+      <c r="B92" s="20" t="inlineStr">
         <is>
           <t>New Orleans, LA; Ingested</t>
         </is>
       </c>
-      <c r="C92" s="19" t="inlineStr">
+      <c r="C92" s="20" t="inlineStr">
         <is>
           <t>New Orleans, LA (169); Ingested</t>
         </is>
       </c>
-      <c r="D92" s="23" t="inlineStr">
+      <c r="D92" s="24" t="inlineStr">
         <is>
           <t>Hamburg; Pending — 10th EEA; Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
-      <c r="E92" s="18" t="inlineStr"/>
-      <c r="F92" s="18" t="inlineStr"/>
-      <c r="G92" s="18" t="inlineStr"/>
-      <c r="H92" s="18" t="inlineStr"/>
-      <c r="I92" s="18" t="inlineStr"/>
-      <c r="J92" s="18" t="inlineStr"/>
-      <c r="K92" s="17" t="inlineStr">
+      <c r="E92" s="19" t="inlineStr"/>
+      <c r="F92" s="19" t="inlineStr"/>
+      <c r="G92" s="19" t="inlineStr"/>
+      <c r="H92" s="19" t="inlineStr"/>
+      <c r="I92" s="19" t="inlineStr"/>
+      <c r="J92" s="19" t="inlineStr"/>
+      <c r="K92" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 10 abstracts cited by the corpus</t>
         </is>
       </c>
-      <c r="L92" s="18" t="inlineStr"/>
-      <c r="M92" s="18" t="inlineStr"/>
-      <c r="N92" s="18" t="inlineStr"/>
-      <c r="O92" s="18" t="inlineStr"/>
-      <c r="P92" s="18" t="inlineStr"/>
-      <c r="Q92" s="18" t="inlineStr"/>
-      <c r="R92" s="18" t="inlineStr"/>
-      <c r="S92" s="18" t="inlineStr"/>
-      <c r="T92" s="18" t="inlineStr"/>
-      <c r="U92" s="18" t="inlineStr"/>
-      <c r="V92" s="18" t="inlineStr"/>
-      <c r="W92" s="18" t="inlineStr"/>
-      <c r="X92" s="18" t="inlineStr"/>
-      <c r="Y92" s="17" t="inlineStr">
+      <c r="L92" s="19" t="inlineStr"/>
+      <c r="M92" s="19" t="inlineStr"/>
+      <c r="N92" s="19" t="inlineStr"/>
+      <c r="O92" s="19" t="inlineStr"/>
+      <c r="P92" s="19" t="inlineStr"/>
+      <c r="Q92" s="19" t="inlineStr"/>
+      <c r="R92" s="19" t="inlineStr"/>
+      <c r="S92" s="19" t="inlineStr"/>
+      <c r="T92" s="19" t="inlineStr"/>
+      <c r="U92" s="19" t="inlineStr"/>
+      <c r="V92" s="19" t="inlineStr"/>
+      <c r="W92" s="19" t="inlineStr"/>
+      <c r="X92" s="19" t="inlineStr"/>
+      <c r="Y92" s="18" t="inlineStr">
         <is>
           <t>Missing — 5 abstracts cited by the corpus [5 distinct meetings; Published 2007]</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="16" t="n">
+      <c r="A93" s="17" t="n">
         <v>2007</v>
       </c>
-      <c r="B93" s="19" t="inlineStr">
+      <c r="B93" s="20" t="inlineStr">
         <is>
           <t>St. Louis, MO; Ingested</t>
         </is>
       </c>
-      <c r="C93" s="19" t="inlineStr">
+      <c r="C93" s="20" t="inlineStr">
         <is>
           <t>St. Louis, MO (138); Ingested</t>
         </is>
       </c>
-      <c r="D93" s="23" t="inlineStr">
+      <c r="D93" s="24" t="inlineStr">
         <is>
           <t>Brest; Pending — 11th EEA; Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
-      <c r="E93" s="19" t="inlineStr">
+      <c r="E93" s="20" t="inlineStr">
         <is>
           <t>Queenscliff, VIC, Australia; Ingested — 51 abstracts, 51 with bodies</t>
         </is>
       </c>
-      <c r="F93" s="18" t="inlineStr"/>
-      <c r="G93" s="18" t="inlineStr"/>
-      <c r="H93" s="18" t="inlineStr"/>
-      <c r="I93" s="18" t="inlineStr"/>
-      <c r="J93" s="18" t="inlineStr"/>
-      <c r="K93" s="17" t="inlineStr">
+      <c r="F93" s="19" t="inlineStr"/>
+      <c r="G93" s="19" t="inlineStr"/>
+      <c r="H93" s="19" t="inlineStr"/>
+      <c r="I93" s="19" t="inlineStr"/>
+      <c r="J93" s="19" t="inlineStr"/>
+      <c r="K93" s="18" t="inlineStr">
         <is>
           <t>Punta Cana, Dominican Republic; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="L93" s="18" t="inlineStr"/>
-      <c r="M93" s="18" t="inlineStr"/>
-      <c r="N93" s="18" t="inlineStr"/>
-      <c r="O93" s="18" t="inlineStr"/>
-      <c r="P93" s="18" t="inlineStr"/>
-      <c r="Q93" s="18" t="inlineStr"/>
-      <c r="R93" s="17" t="inlineStr">
+      <c r="L93" s="19" t="inlineStr"/>
+      <c r="M93" s="19" t="inlineStr"/>
+      <c r="N93" s="19" t="inlineStr"/>
+      <c r="O93" s="19" t="inlineStr"/>
+      <c r="P93" s="19" t="inlineStr"/>
+      <c r="Q93" s="19" t="inlineStr"/>
+      <c r="R93" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 6 abstracts cited by the corpus</t>
         </is>
       </c>
-      <c r="S93" s="18" t="inlineStr"/>
-      <c r="T93" s="18" t="inlineStr"/>
-      <c r="U93" s="18" t="inlineStr"/>
-      <c r="V93" s="18" t="inlineStr"/>
-      <c r="W93" s="18" t="inlineStr"/>
-      <c r="X93" s="18" t="inlineStr"/>
-      <c r="Y93" s="17" t="inlineStr">
+      <c r="S93" s="19" t="inlineStr"/>
+      <c r="T93" s="19" t="inlineStr"/>
+      <c r="U93" s="19" t="inlineStr"/>
+      <c r="V93" s="19" t="inlineStr"/>
+      <c r="W93" s="19" t="inlineStr"/>
+      <c r="X93" s="19" t="inlineStr"/>
+      <c r="Y93" s="18" t="inlineStr">
         <is>
           <t>Missing — 3 abstracts cited by the corpus [3 distinct meetings]</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="16" t="n">
+      <c r="A94" s="17" t="n">
         <v>2008</v>
       </c>
-      <c r="B94" s="19" t="inlineStr">
+      <c r="B94" s="20" t="inlineStr">
         <is>
           <t>Montreal, PQ; Ingested</t>
         </is>
       </c>
-      <c r="C94" s="19" t="inlineStr">
+      <c r="C94" s="20" t="inlineStr">
         <is>
           <t>Montreal, PQ (193); Ingested</t>
         </is>
       </c>
-      <c r="D94" s="23" t="inlineStr">
+      <c r="D94" s="24" t="inlineStr">
         <is>
           <t>Lisbon; Pending — 12th EEA; Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
-      <c r="E94" s="19" t="inlineStr">
+      <c r="E94" s="20" t="inlineStr">
         <is>
           <t>Sydney, NSW, Australia; Ingested — 50 abstracts, 47 with bodies</t>
         </is>
       </c>
-      <c r="F94" s="18" t="inlineStr"/>
-      <c r="G94" s="18" t="inlineStr"/>
-      <c r="H94" s="18" t="inlineStr"/>
-      <c r="I94" s="22" t="inlineStr">
+      <c r="F94" s="19" t="inlineStr"/>
+      <c r="G94" s="19" t="inlineStr"/>
+      <c r="H94" s="19" t="inlineStr"/>
+      <c r="I94" s="23" t="inlineStr">
         <is>
           <t>Ciudad Universitaria, Mexico City; Digital — 1 PDF held — extraction pending</t>
         </is>
       </c>
-      <c r="J94" s="18" t="inlineStr"/>
-      <c r="K94" s="18" t="inlineStr"/>
-      <c r="L94" s="18" t="inlineStr"/>
-      <c r="M94" s="18" t="inlineStr"/>
-      <c r="N94" s="18" t="inlineStr"/>
-      <c r="O94" s="18" t="inlineStr"/>
-      <c r="P94" s="18" t="inlineStr"/>
-      <c r="Q94" s="18" t="inlineStr"/>
-      <c r="R94" s="18" t="inlineStr"/>
-      <c r="S94" s="18" t="inlineStr"/>
-      <c r="T94" s="18" t="inlineStr"/>
-      <c r="U94" s="18" t="inlineStr"/>
-      <c r="V94" s="18" t="inlineStr"/>
-      <c r="W94" s="18" t="inlineStr"/>
-      <c r="X94" s="18" t="inlineStr"/>
-      <c r="Y94" s="17" t="inlineStr">
+      <c r="J94" s="19" t="inlineStr"/>
+      <c r="K94" s="19" t="inlineStr"/>
+      <c r="L94" s="19" t="inlineStr"/>
+      <c r="M94" s="19" t="inlineStr"/>
+      <c r="N94" s="19" t="inlineStr"/>
+      <c r="O94" s="19" t="inlineStr"/>
+      <c r="P94" s="19" t="inlineStr"/>
+      <c r="Q94" s="19" t="inlineStr"/>
+      <c r="R94" s="19" t="inlineStr"/>
+      <c r="S94" s="19" t="inlineStr"/>
+      <c r="T94" s="19" t="inlineStr"/>
+      <c r="U94" s="19" t="inlineStr"/>
+      <c r="V94" s="19" t="inlineStr"/>
+      <c r="W94" s="19" t="inlineStr"/>
+      <c r="X94" s="19" t="inlineStr"/>
+      <c r="Y94" s="18" t="inlineStr">
         <is>
           <t>Missing — 6 abstracts cited by the corpus [6 distinct meetings]</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="16" t="n">
+      <c r="A95" s="17" t="n">
         <v>2009</v>
       </c>
-      <c r="B95" s="19" t="inlineStr">
+      <c r="B95" s="20" t="inlineStr">
         <is>
           <t>Portland, OR; Ingested</t>
         </is>
       </c>
-      <c r="C95" s="19" t="inlineStr">
+      <c r="C95" s="20" t="inlineStr">
         <is>
           <t>Portland, OR (161); Ingested</t>
         </is>
       </c>
-      <c r="D95" s="23" t="inlineStr">
+      <c r="D95" s="24" t="inlineStr">
         <is>
           <t>Palma de Majorca; Pending — 13th EEA; Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
-      <c r="E95" s="18" t="inlineStr"/>
-      <c r="F95" s="18" t="inlineStr"/>
-      <c r="G95" s="18" t="inlineStr"/>
-      <c r="H95" s="18" t="inlineStr"/>
-      <c r="I95" s="18" t="inlineStr"/>
-      <c r="J95" s="18" t="inlineStr"/>
-      <c r="K95" s="17" t="inlineStr">
+      <c r="E95" s="19" t="inlineStr"/>
+      <c r="F95" s="19" t="inlineStr"/>
+      <c r="G95" s="19" t="inlineStr"/>
+      <c r="H95" s="19" t="inlineStr"/>
+      <c r="I95" s="19" t="inlineStr"/>
+      <c r="J95" s="19" t="inlineStr"/>
+      <c r="K95" s="18" t="inlineStr">
         <is>
           <t>Cumana, Venezuela; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="L95" s="18" t="inlineStr"/>
-      <c r="M95" s="18" t="inlineStr"/>
-      <c r="N95" s="18" t="inlineStr"/>
-      <c r="O95" s="18" t="inlineStr"/>
-      <c r="P95" s="18" t="inlineStr"/>
-      <c r="Q95" s="18" t="inlineStr"/>
-      <c r="R95" s="18" t="inlineStr"/>
-      <c r="S95" s="18" t="inlineStr"/>
-      <c r="T95" s="17" t="inlineStr">
+      <c r="L95" s="19" t="inlineStr"/>
+      <c r="M95" s="19" t="inlineStr"/>
+      <c r="N95" s="19" t="inlineStr"/>
+      <c r="O95" s="25" t="inlineStr">
+        <is>
+          <t>Fremantle, WA, Australia; Partial — 416 abstracts, elasmo-targeted pages only (teleost content not captured)</t>
+        </is>
+      </c>
+      <c r="P95" s="19" t="inlineStr"/>
+      <c r="Q95" s="19" t="inlineStr"/>
+      <c r="R95" s="19" t="inlineStr"/>
+      <c r="S95" s="19" t="inlineStr"/>
+      <c r="T95" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 2 abstracts cited by the corpus [Published 2010]</t>
         </is>
       </c>
-      <c r="U95" s="18" t="inlineStr"/>
-      <c r="V95" s="18" t="inlineStr"/>
-      <c r="W95" s="18" t="inlineStr"/>
-      <c r="X95" s="18" t="inlineStr"/>
-      <c r="Y95" s="17" t="inlineStr">
+      <c r="U95" s="19" t="inlineStr"/>
+      <c r="V95" s="19" t="inlineStr"/>
+      <c r="W95" s="19" t="inlineStr"/>
+      <c r="X95" s="19" t="inlineStr"/>
+      <c r="Y95" s="18" t="inlineStr">
         <is>
           <t>Missing — 3 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="16" t="n">
+      <c r="A96" s="17" t="n">
         <v>2010</v>
       </c>
-      <c r="B96" s="19" t="inlineStr">
+      <c r="B96" s="20" t="inlineStr">
         <is>
           <t>Providence, RI; Ingested</t>
         </is>
       </c>
-      <c r="C96" s="19" t="inlineStr">
+      <c r="C96" s="20" t="inlineStr">
         <is>
           <t>Providence, RI (172); Ingested</t>
         </is>
       </c>
-      <c r="D96" s="20" t="inlineStr">
+      <c r="D96" s="21" t="inlineStr">
         <is>
           <t>Galway; Hardcopy — Cat holds a hardcopy but has no scanning capacity; digital copy needed from IEG (Ireland)</t>
         </is>
       </c>
-      <c r="E96" s="18" t="inlineStr"/>
-      <c r="F96" s="17" t="inlineStr">
+      <c r="E96" s="19" t="inlineStr"/>
+      <c r="F96" s="18" t="inlineStr">
         <is>
           <t>Cairns; Missing — find source</t>
         </is>
       </c>
-      <c r="G96" s="18" t="inlineStr"/>
-      <c r="H96" s="18" t="inlineStr"/>
-      <c r="I96" s="22" t="inlineStr">
+      <c r="G96" s="19" t="inlineStr"/>
+      <c r="H96" s="19" t="inlineStr"/>
+      <c r="I96" s="23" t="inlineStr">
         <is>
           <t>Ciudad Universitaria, Mexico City; Digital — 1 PDF held — extraction pending</t>
         </is>
       </c>
-      <c r="J96" s="18" t="inlineStr"/>
-      <c r="K96" s="18" t="inlineStr"/>
-      <c r="L96" s="18" t="inlineStr"/>
-      <c r="M96" s="18" t="inlineStr"/>
-      <c r="N96" s="18" t="inlineStr"/>
-      <c r="O96" s="18" t="inlineStr"/>
-      <c r="P96" s="18" t="inlineStr"/>
-      <c r="Q96" s="18" t="inlineStr"/>
-      <c r="R96" s="18" t="inlineStr"/>
-      <c r="S96" s="18" t="inlineStr"/>
-      <c r="T96" s="18" t="inlineStr"/>
-      <c r="U96" s="18" t="inlineStr"/>
-      <c r="V96" s="17" t="inlineStr">
+      <c r="J96" s="19" t="inlineStr"/>
+      <c r="K96" s="19" t="inlineStr"/>
+      <c r="L96" s="19" t="inlineStr"/>
+      <c r="M96" s="19" t="inlineStr"/>
+      <c r="N96" s="19" t="inlineStr"/>
+      <c r="O96" s="19" t="inlineStr"/>
+      <c r="P96" s="19" t="inlineStr"/>
+      <c r="Q96" s="19" t="inlineStr"/>
+      <c r="R96" s="19" t="inlineStr"/>
+      <c r="S96" s="19" t="inlineStr"/>
+      <c r="T96" s="19" t="inlineStr"/>
+      <c r="U96" s="19" t="inlineStr"/>
+      <c r="V96" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="W96" s="18" t="inlineStr"/>
-      <c r="X96" s="18" t="inlineStr"/>
-      <c r="Y96" s="17" t="inlineStr">
+      <c r="W96" s="19" t="inlineStr"/>
+      <c r="X96" s="19" t="inlineStr"/>
+      <c r="Y96" s="18" t="inlineStr">
         <is>
           <t>Missing — 3 abstracts cited by the corpus [3 distinct meetings]</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="16" t="n">
+      <c r="A97" s="17" t="n">
         <v>2011</v>
       </c>
-      <c r="B97" s="20" t="inlineStr">
+      <c r="B97" s="21" t="inlineStr">
         <is>
           <t>Minneapolis, MN; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C97" s="20" t="inlineStr">
+      <c r="C97" s="21" t="inlineStr">
         <is>
           <t>Minneapolis, MN; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="D97" s="19" t="inlineStr">
+      <c r="D97" s="20" t="inlineStr">
         <is>
           <t>Berlin; Ingested — 58 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E97" s="19" t="inlineStr">
+      <c r="E97" s="20" t="inlineStr">
         <is>
           <t>Gold Coast, QLD, Australia; Ingested — 48 abstracts, 48 with bodies</t>
         </is>
       </c>
-      <c r="F97" s="18" t="inlineStr"/>
-      <c r="G97" s="18" t="inlineStr"/>
-      <c r="H97" s="18" t="inlineStr"/>
-      <c r="I97" s="18" t="inlineStr"/>
-      <c r="J97" s="17" t="inlineStr">
+      <c r="F97" s="19" t="inlineStr"/>
+      <c r="G97" s="19" t="inlineStr"/>
+      <c r="H97" s="19" t="inlineStr"/>
+      <c r="I97" s="19" t="inlineStr"/>
+      <c r="J97" s="18" t="inlineStr">
         <is>
           <t>Dakar, Senegal; Missing — 48 abstracts cited by the corpus</t>
         </is>
       </c>
-      <c r="K97" s="18" t="inlineStr"/>
-      <c r="L97" s="17" t="inlineStr">
+      <c r="K97" s="19" t="inlineStr"/>
+      <c r="L97" s="18" t="inlineStr">
         <is>
           <t>Vancouver, Canada; Missing — 12 abstracts cited by the corpus [Published 2012]</t>
         </is>
       </c>
-      <c r="M97" s="18" t="inlineStr"/>
-      <c r="N97" s="18" t="inlineStr"/>
-      <c r="O97" s="18" t="inlineStr"/>
-      <c r="P97" s="18" t="inlineStr"/>
-      <c r="Q97" s="18" t="inlineStr"/>
-      <c r="R97" s="17" t="inlineStr">
+      <c r="M97" s="19" t="inlineStr"/>
+      <c r="N97" s="19" t="inlineStr"/>
+      <c r="O97" s="19" t="inlineStr"/>
+      <c r="P97" s="19" t="inlineStr"/>
+      <c r="Q97" s="19" t="inlineStr"/>
+      <c r="R97" s="18" t="inlineStr">
         <is>
           <t>Seattle, WA; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="S97" s="18" t="inlineStr"/>
-      <c r="T97" s="18" t="inlineStr"/>
-      <c r="U97" s="18" t="inlineStr"/>
-      <c r="V97" s="18" t="inlineStr"/>
-      <c r="W97" s="18" t="inlineStr"/>
-      <c r="X97" s="18" t="inlineStr"/>
-      <c r="Y97" s="17" t="inlineStr">
+      <c r="S97" s="19" t="inlineStr"/>
+      <c r="T97" s="19" t="inlineStr"/>
+      <c r="U97" s="19" t="inlineStr"/>
+      <c r="V97" s="19" t="inlineStr"/>
+      <c r="W97" s="19" t="inlineStr"/>
+      <c r="X97" s="19" t="inlineStr"/>
+      <c r="Y97" s="18" t="inlineStr">
         <is>
           <t>Missing — 9 abstracts cited by the corpus [5 distinct meetings]</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="16" t="n">
+      <c r="A98" s="17" t="n">
         <v>2012</v>
       </c>
-      <c r="B98" s="24" t="inlineStr">
+      <c r="B98" s="26" t="inlineStr">
         <is>
           <t>Vancouver, BC; Extracted — regex-parsed; Fable re-extraction part-done (1078 so far)</t>
         </is>
       </c>
-      <c r="C98" s="24" t="inlineStr">
+      <c r="C98" s="26" t="inlineStr">
         <is>
           <t>Vancouver, BC (62); Extracted — regex-parsed; Fable re-extraction part-done (1078 so far)</t>
         </is>
       </c>
-      <c r="D98" s="20" t="inlineStr">
+      <c r="D98" s="21" t="inlineStr">
         <is>
           <t>Milan; Hardcopy — Cat holds a hardcopy but has no scanning capacity; digital copy needed from GRIS (Italy)</t>
         </is>
       </c>
-      <c r="E98" s="19" t="inlineStr">
-        <is>
-          <t>Adelaide; Ingested — 171 abstracts, 171 with bodies; joint meeting, elasmo flagged per abstract</t>
-        </is>
-      </c>
-      <c r="F98" s="18" t="inlineStr"/>
-      <c r="G98" s="18" t="inlineStr"/>
-      <c r="H98" s="18" t="inlineStr"/>
-      <c r="I98" s="18" t="inlineStr"/>
-      <c r="J98" s="18" t="inlineStr"/>
-      <c r="K98" s="18" t="inlineStr"/>
-      <c r="L98" s="18" t="inlineStr"/>
-      <c r="M98" s="18" t="inlineStr"/>
-      <c r="N98" s="17" t="inlineStr">
+      <c r="E98" s="20" t="inlineStr">
+        <is>
+          <t>Adelaide; Ingested — 170 abstracts, 170 with bodies; joint meeting, elasmo flagged per abstract</t>
+        </is>
+      </c>
+      <c r="F98" s="19" t="inlineStr"/>
+      <c r="G98" s="19" t="inlineStr"/>
+      <c r="H98" s="19" t="inlineStr"/>
+      <c r="I98" s="19" t="inlineStr"/>
+      <c r="J98" s="19" t="inlineStr"/>
+      <c r="K98" s="19" t="inlineStr"/>
+      <c r="L98" s="19" t="inlineStr"/>
+      <c r="M98" s="19" t="inlineStr"/>
+      <c r="N98" s="18" t="inlineStr">
         <is>
           <t>Vancouver, Canada; Missing — 100 abstracts cited by the corpus [Published 2010, 2015]</t>
         </is>
       </c>
-      <c r="O98" s="18" t="inlineStr"/>
-      <c r="P98" s="17" t="inlineStr">
+      <c r="O98" s="19" t="inlineStr"/>
+      <c r="P98" s="18" t="inlineStr">
         <is>
           <t>Cairns, Queensland, Australia; Missing — 13 abstracts cited by the corpus</t>
         </is>
       </c>
-      <c r="Q98" s="17" t="inlineStr">
+      <c r="Q98" s="18" t="inlineStr">
         <is>
           <t>Edinburgh, Scotland; Missing — 6 abstracts cited by the corpus</t>
         </is>
       </c>
-      <c r="R98" s="17" t="inlineStr">
+      <c r="R98" s="18" t="inlineStr">
         <is>
           <t>Missing — 2 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
-      <c r="S98" s="18" t="inlineStr"/>
-      <c r="T98" s="18" t="inlineStr"/>
-      <c r="U98" s="18" t="inlineStr"/>
-      <c r="V98" s="18" t="inlineStr"/>
-      <c r="W98" s="17" t="inlineStr">
+      <c r="S98" s="19" t="inlineStr"/>
+      <c r="T98" s="19" t="inlineStr"/>
+      <c r="U98" s="19" t="inlineStr"/>
+      <c r="V98" s="19" t="inlineStr"/>
+      <c r="W98" s="18" t="inlineStr">
         <is>
           <t>Honolulu, HI (U. Hawai'i at Manoa); Missing — 3 abstracts cited by the corpus</t>
         </is>
       </c>
-      <c r="X98" s="18" t="inlineStr"/>
-      <c r="Y98" s="17" t="inlineStr">
+      <c r="X98" s="19" t="inlineStr"/>
+      <c r="Y98" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="16" t="n">
+      <c r="A99" s="17" t="n">
         <v>2013</v>
       </c>
-      <c r="B99" s="20" t="inlineStr">
+      <c r="B99" s="21" t="inlineStr">
         <is>
           <t>Albuquerque, NM; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C99" s="20" t="inlineStr">
+      <c r="C99" s="21" t="inlineStr">
         <is>
           <t>Albuquerque, NM; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="D99" s="19" t="inlineStr">
+      <c r="D99" s="20" t="inlineStr">
         <is>
           <t>Plymouth; Ingested — 93 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E99" s="19" t="inlineStr">
+      <c r="E99" s="20" t="inlineStr">
         <is>
           <t>Brisbane, QLD, Australia; Ingested — 34 abstracts, 34 with bodies</t>
         </is>
       </c>
-      <c r="F99" s="18" t="inlineStr"/>
-      <c r="G99" s="18" t="inlineStr"/>
-      <c r="H99" s="18" t="inlineStr"/>
-      <c r="I99" s="18" t="inlineStr"/>
-      <c r="J99" s="18" t="inlineStr"/>
-      <c r="K99" s="18" t="inlineStr"/>
-      <c r="L99" s="18" t="inlineStr"/>
-      <c r="M99" s="17" t="inlineStr">
+      <c r="F99" s="19" t="inlineStr"/>
+      <c r="G99" s="19" t="inlineStr"/>
+      <c r="H99" s="19" t="inlineStr"/>
+      <c r="I99" s="19" t="inlineStr"/>
+      <c r="J99" s="19" t="inlineStr"/>
+      <c r="K99" s="19" t="inlineStr"/>
+      <c r="L99" s="19" t="inlineStr"/>
+      <c r="M99" s="18" t="inlineStr">
         <is>
           <t>Missing — 2 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
-      <c r="N99" s="18" t="inlineStr"/>
-      <c r="O99" s="18" t="inlineStr"/>
-      <c r="P99" s="18" t="inlineStr"/>
-      <c r="Q99" s="18" t="inlineStr"/>
-      <c r="R99" s="18" t="inlineStr"/>
-      <c r="S99" s="18" t="inlineStr"/>
-      <c r="T99" s="17" t="inlineStr">
+      <c r="N99" s="19" t="inlineStr"/>
+      <c r="O99" s="19" t="inlineStr"/>
+      <c r="P99" s="19" t="inlineStr"/>
+      <c r="Q99" s="19" t="inlineStr"/>
+      <c r="R99" s="19" t="inlineStr"/>
+      <c r="S99" s="19" t="inlineStr"/>
+      <c r="T99" s="18" t="inlineStr">
         <is>
           <t>Vienna, Austria; Missing — 11 abstracts cited by the corpus</t>
         </is>
       </c>
-      <c r="U99" s="18" t="inlineStr"/>
-      <c r="V99" s="18" t="inlineStr"/>
-      <c r="W99" s="18" t="inlineStr"/>
-      <c r="X99" s="18" t="inlineStr"/>
-      <c r="Y99" s="17" t="inlineStr">
+      <c r="U99" s="19" t="inlineStr"/>
+      <c r="V99" s="19" t="inlineStr"/>
+      <c r="W99" s="19" t="inlineStr"/>
+      <c r="X99" s="19" t="inlineStr"/>
+      <c r="Y99" s="18" t="inlineStr">
         <is>
           <t>Missing — 2 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="16" t="n">
+      <c r="A100" s="17" t="n">
         <v>2014</v>
       </c>
-      <c r="B100" s="19" t="inlineStr">
+      <c r="B100" s="20" t="inlineStr">
         <is>
           <t>Chattanooga, TN; Ingested</t>
         </is>
       </c>
-      <c r="C100" s="19" t="inlineStr">
+      <c r="C100" s="20" t="inlineStr">
         <is>
           <t>Chattanooga, TN (92); Ingested</t>
         </is>
       </c>
-      <c r="D100" s="19" t="inlineStr">
+      <c r="D100" s="20" t="inlineStr">
         <is>
           <t>Leeuwarden; Ingested — 61 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E100" s="23" t="inlineStr">
+      <c r="E100" s="24" t="inlineStr">
         <is>
           <t>?; Pending — Brit Finucci collating; year/location to confirm</t>
         </is>
       </c>
-      <c r="F100" s="17" t="inlineStr">
+      <c r="F100" s="18" t="inlineStr">
         <is>
           <t>Durban; Missing — find source</t>
         </is>
       </c>
-      <c r="G100" s="17" t="inlineStr">
+      <c r="G100" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 79 abstracts cited by the corpus</t>
         </is>
       </c>
-      <c r="H100" s="18" t="inlineStr"/>
-      <c r="I100" s="17" t="inlineStr">
+      <c r="H100" s="19" t="inlineStr"/>
+      <c r="I100" s="18" t="inlineStr">
         <is>
           <t>Mazatlan, Sinaloa, Mexico; Missing — 44 abstracts cited by the corpus</t>
         </is>
       </c>
-      <c r="J100" s="18" t="inlineStr"/>
-      <c r="K100" s="18" t="inlineStr"/>
-      <c r="L100" s="18" t="inlineStr"/>
-      <c r="M100" s="18" t="inlineStr"/>
-      <c r="N100" s="18" t="inlineStr"/>
-      <c r="O100" s="18" t="inlineStr"/>
-      <c r="P100" s="18" t="inlineStr"/>
-      <c r="Q100" s="18" t="inlineStr"/>
-      <c r="R100" s="17" t="inlineStr">
+      <c r="J100" s="19" t="inlineStr"/>
+      <c r="K100" s="19" t="inlineStr"/>
+      <c r="L100" s="19" t="inlineStr"/>
+      <c r="M100" s="19" t="inlineStr"/>
+      <c r="N100" s="19" t="inlineStr"/>
+      <c r="O100" s="19" t="inlineStr"/>
+      <c r="P100" s="19" t="inlineStr"/>
+      <c r="Q100" s="19" t="inlineStr"/>
+      <c r="R100" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="S100" s="18" t="inlineStr"/>
-      <c r="T100" s="18" t="inlineStr"/>
-      <c r="U100" s="18" t="inlineStr"/>
-      <c r="V100" s="18" t="inlineStr"/>
-      <c r="W100" s="18" t="inlineStr"/>
-      <c r="X100" s="18" t="inlineStr"/>
-      <c r="Y100" s="17" t="inlineStr">
+      <c r="S100" s="19" t="inlineStr"/>
+      <c r="T100" s="19" t="inlineStr"/>
+      <c r="U100" s="19" t="inlineStr"/>
+      <c r="V100" s="19" t="inlineStr"/>
+      <c r="W100" s="19" t="inlineStr"/>
+      <c r="X100" s="19" t="inlineStr"/>
+      <c r="Y100" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="16" t="n">
+      <c r="A101" s="17" t="n">
         <v>2015</v>
       </c>
-      <c r="B101" s="19" t="inlineStr">
+      <c r="B101" s="20" t="inlineStr">
         <is>
           <t>Reno, NV; Ingested</t>
         </is>
       </c>
-      <c r="C101" s="19" t="inlineStr">
+      <c r="C101" s="20" t="inlineStr">
         <is>
           <t>Reno, NV (118); Ingested</t>
         </is>
       </c>
-      <c r="D101" s="22" t="inlineStr">
+      <c r="D101" s="23" t="inlineStr">
         <is>
           <t>Peniche; Digital — 19th EEA Book of Abstracts (99pp, born-digital) held by Simon all along; queued for extraction</t>
         </is>
       </c>
-      <c r="E101" s="19" t="inlineStr">
+      <c r="E101" s="20" t="inlineStr">
         <is>
           <t>Auckland, New Zealand; Ingested — 219 abstracts, 217 with bodies; joint meeting, elasmo flagged per abstract</t>
         </is>
       </c>
-      <c r="F101" s="18" t="inlineStr"/>
-      <c r="G101" s="18" t="inlineStr"/>
-      <c r="H101" s="18" t="inlineStr"/>
-      <c r="I101" s="18" t="inlineStr"/>
-      <c r="J101" s="18" t="inlineStr"/>
-      <c r="K101" s="18" t="inlineStr"/>
-      <c r="L101" s="18" t="inlineStr"/>
-      <c r="M101" s="18" t="inlineStr"/>
-      <c r="N101" s="18" t="inlineStr"/>
-      <c r="O101" s="18" t="inlineStr"/>
-      <c r="P101" s="18" t="inlineStr"/>
-      <c r="Q101" s="18" t="inlineStr"/>
-      <c r="R101" s="18" t="inlineStr"/>
-      <c r="S101" s="18" t="inlineStr"/>
-      <c r="T101" s="18" t="inlineStr"/>
-      <c r="U101" s="18" t="inlineStr"/>
-      <c r="V101" s="18" t="inlineStr"/>
-      <c r="W101" s="18" t="inlineStr"/>
-      <c r="X101" s="18" t="inlineStr"/>
-      <c r="Y101" s="17" t="inlineStr">
+      <c r="F101" s="19" t="inlineStr"/>
+      <c r="G101" s="19" t="inlineStr"/>
+      <c r="H101" s="19" t="inlineStr"/>
+      <c r="I101" s="19" t="inlineStr"/>
+      <c r="J101" s="19" t="inlineStr"/>
+      <c r="K101" s="19" t="inlineStr"/>
+      <c r="L101" s="19" t="inlineStr"/>
+      <c r="M101" s="19" t="inlineStr"/>
+      <c r="N101" s="19" t="inlineStr"/>
+      <c r="O101" s="19" t="inlineStr"/>
+      <c r="P101" s="19" t="inlineStr"/>
+      <c r="Q101" s="19" t="inlineStr"/>
+      <c r="R101" s="19" t="inlineStr"/>
+      <c r="S101" s="19" t="inlineStr"/>
+      <c r="T101" s="19" t="inlineStr"/>
+      <c r="U101" s="19" t="inlineStr"/>
+      <c r="V101" s="19" t="inlineStr"/>
+      <c r="W101" s="19" t="inlineStr"/>
+      <c r="X101" s="19" t="inlineStr"/>
+      <c r="Y101" s="18" t="inlineStr">
         <is>
           <t>Missing — 4 abstracts cited by the corpus [3 distinct meetings]</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="16" t="n">
+      <c r="A102" s="17" t="n">
         <v>2016</v>
       </c>
-      <c r="B102" s="19" t="inlineStr">
+      <c r="B102" s="20" t="inlineStr">
         <is>
           <t>New Orleans, LA; Ingested</t>
         </is>
       </c>
-      <c r="C102" s="19" t="inlineStr">
+      <c r="C102" s="20" t="inlineStr">
         <is>
           <t>New Orleans, LA (233); Ingested</t>
         </is>
       </c>
-      <c r="D102" s="19" t="inlineStr">
+      <c r="D102" s="20" t="inlineStr">
         <is>
           <t>Bristol; Ingested — 93 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E102" s="19" t="inlineStr">
+      <c r="E102" s="20" t="inlineStr">
         <is>
           <t>Wrest Point, Tasmania, Australia; Ingested — 222 abstracts, 219 with bodies; joint meeting, elasmo flagged per abstract</t>
         </is>
       </c>
-      <c r="F102" s="18" t="inlineStr"/>
-      <c r="G102" s="18" t="inlineStr"/>
-      <c r="H102" s="18" t="inlineStr"/>
-      <c r="I102" s="22" t="inlineStr">
+      <c r="F102" s="19" t="inlineStr"/>
+      <c r="G102" s="19" t="inlineStr"/>
+      <c r="H102" s="19" t="inlineStr"/>
+      <c r="I102" s="23" t="inlineStr">
         <is>
           <t>Puerto Vallarta, Jalisco, Mexico; Digital — 1 PDF held — extraction pending</t>
         </is>
       </c>
-      <c r="J102" s="18" t="inlineStr"/>
-      <c r="K102" s="18" t="inlineStr"/>
-      <c r="L102" s="18" t="inlineStr"/>
-      <c r="M102" s="18" t="inlineStr"/>
-      <c r="N102" s="18" t="inlineStr"/>
-      <c r="O102" s="18" t="inlineStr"/>
-      <c r="P102" s="18" t="inlineStr"/>
-      <c r="Q102" s="18" t="inlineStr"/>
-      <c r="R102" s="18" t="inlineStr"/>
-      <c r="S102" s="18" t="inlineStr"/>
-      <c r="T102" s="18" t="inlineStr"/>
-      <c r="U102" s="18" t="inlineStr"/>
-      <c r="V102" s="18" t="inlineStr"/>
-      <c r="W102" s="18" t="inlineStr"/>
-      <c r="X102" s="18" t="inlineStr"/>
-      <c r="Y102" s="17" t="inlineStr">
+      <c r="J102" s="19" t="inlineStr"/>
+      <c r="K102" s="19" t="inlineStr"/>
+      <c r="L102" s="19" t="inlineStr"/>
+      <c r="M102" s="19" t="inlineStr"/>
+      <c r="N102" s="19" t="inlineStr"/>
+      <c r="O102" s="19" t="inlineStr"/>
+      <c r="P102" s="19" t="inlineStr"/>
+      <c r="Q102" s="19" t="inlineStr"/>
+      <c r="R102" s="19" t="inlineStr"/>
+      <c r="S102" s="19" t="inlineStr"/>
+      <c r="T102" s="19" t="inlineStr"/>
+      <c r="U102" s="19" t="inlineStr"/>
+      <c r="V102" s="19" t="inlineStr"/>
+      <c r="W102" s="19" t="inlineStr"/>
+      <c r="X102" s="19" t="inlineStr"/>
+      <c r="Y102" s="18" t="inlineStr">
         <is>
           <t>Missing — 3 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="16" t="n">
+      <c r="A103" s="17" t="n">
         <v>2017</v>
       </c>
-      <c r="B103" s="19" t="inlineStr">
+      <c r="B103" s="20" t="inlineStr">
         <is>
           <t>Austin, TX; Ingested</t>
         </is>
       </c>
-      <c r="C103" s="19" t="inlineStr">
+      <c r="C103" s="20" t="inlineStr">
         <is>
           <t>Austin, TX (162); Ingested</t>
         </is>
       </c>
-      <c r="D103" s="25" t="inlineStr">
+      <c r="D103" s="27" t="inlineStr">
         <is>
           <t>Amsterdam; Schedule — 62 talks ingested, NO abstract bodies; Cat holds a hardcopy but has no scanning capacity; abstract book needed from NEV</t>
         </is>
       </c>
-      <c r="E103" s="18" t="inlineStr"/>
-      <c r="F103" s="18" t="inlineStr"/>
-      <c r="G103" s="18" t="inlineStr"/>
-      <c r="H103" s="18" t="inlineStr"/>
-      <c r="I103" s="18" t="inlineStr"/>
-      <c r="J103" s="18" t="inlineStr"/>
-      <c r="K103" s="18" t="inlineStr"/>
-      <c r="L103" s="18" t="inlineStr"/>
-      <c r="M103" s="18" t="inlineStr"/>
-      <c r="N103" s="18" t="inlineStr"/>
-      <c r="O103" s="18" t="inlineStr"/>
-      <c r="P103" s="18" t="inlineStr"/>
-      <c r="Q103" s="18" t="inlineStr"/>
-      <c r="R103" s="18" t="inlineStr"/>
-      <c r="S103" s="18" t="inlineStr"/>
-      <c r="T103" s="18" t="inlineStr"/>
-      <c r="U103" s="18" t="inlineStr"/>
-      <c r="V103" s="18" t="inlineStr"/>
-      <c r="W103" s="18" t="inlineStr"/>
-      <c r="X103" s="18" t="inlineStr"/>
-      <c r="Y103" s="17" t="inlineStr">
+      <c r="E103" s="19" t="inlineStr"/>
+      <c r="F103" s="19" t="inlineStr"/>
+      <c r="G103" s="19" t="inlineStr"/>
+      <c r="H103" s="19" t="inlineStr"/>
+      <c r="I103" s="19" t="inlineStr"/>
+      <c r="J103" s="19" t="inlineStr"/>
+      <c r="K103" s="19" t="inlineStr"/>
+      <c r="L103" s="19" t="inlineStr"/>
+      <c r="M103" s="19" t="inlineStr"/>
+      <c r="N103" s="19" t="inlineStr"/>
+      <c r="O103" s="19" t="inlineStr"/>
+      <c r="P103" s="19" t="inlineStr"/>
+      <c r="Q103" s="19" t="inlineStr"/>
+      <c r="R103" s="19" t="inlineStr"/>
+      <c r="S103" s="19" t="inlineStr"/>
+      <c r="T103" s="19" t="inlineStr"/>
+      <c r="U103" s="19" t="inlineStr"/>
+      <c r="V103" s="19" t="inlineStr"/>
+      <c r="W103" s="19" t="inlineStr"/>
+      <c r="X103" s="19" t="inlineStr"/>
+      <c r="Y103" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus [Published 2018]</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="16" t="n">
+      <c r="A104" s="17" t="n">
         <v>2018</v>
       </c>
-      <c r="B104" s="19" t="inlineStr">
+      <c r="B104" s="20" t="inlineStr">
         <is>
           <t>Rochester, NY; Ingested</t>
         </is>
       </c>
-      <c r="C104" s="18" t="inlineStr">
+      <c r="C104" s="19" t="inlineStr">
         <is>
           <t>Joao Pessoa (at SI); NA — no AES meeting at JMIH — AES met at Sharks International instead, so those abstracts are under SI 2018</t>
         </is>
       </c>
-      <c r="D104" s="19" t="inlineStr">
+      <c r="D104" s="20" t="inlineStr">
         <is>
           <t>Peniche; Ingested — 75 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E104" s="19" t="inlineStr">
+      <c r="E104" s="20" t="inlineStr">
         <is>
           <t>North Stradbroke Is.; Ingested — 40 abstracts, 40 with bodies</t>
         </is>
       </c>
-      <c r="F104" s="19" t="inlineStr">
+      <c r="F104" s="20" t="inlineStr">
         <is>
           <t>Joao Pessoa; Ingested</t>
         </is>
       </c>
-      <c r="G104" s="18" t="inlineStr"/>
-      <c r="H104" s="18" t="inlineStr"/>
-      <c r="I104" s="18" t="inlineStr"/>
-      <c r="J104" s="18" t="inlineStr"/>
-      <c r="K104" s="18" t="inlineStr"/>
-      <c r="L104" s="18" t="inlineStr"/>
-      <c r="M104" s="18" t="inlineStr"/>
-      <c r="N104" s="18" t="inlineStr"/>
-      <c r="O104" s="18" t="inlineStr"/>
-      <c r="P104" s="18" t="inlineStr"/>
-      <c r="Q104" s="18" t="inlineStr"/>
-      <c r="R104" s="18" t="inlineStr"/>
-      <c r="S104" s="18" t="inlineStr"/>
-      <c r="T104" s="18" t="inlineStr"/>
-      <c r="U104" s="18" t="inlineStr"/>
-      <c r="V104" s="18" t="inlineStr"/>
-      <c r="W104" s="18" t="inlineStr"/>
-      <c r="X104" s="18" t="inlineStr"/>
-      <c r="Y104" s="17" t="inlineStr">
+      <c r="G104" s="19" t="inlineStr"/>
+      <c r="H104" s="19" t="inlineStr"/>
+      <c r="I104" s="19" t="inlineStr"/>
+      <c r="J104" s="19" t="inlineStr"/>
+      <c r="K104" s="19" t="inlineStr"/>
+      <c r="L104" s="19" t="inlineStr"/>
+      <c r="M104" s="19" t="inlineStr"/>
+      <c r="N104" s="19" t="inlineStr"/>
+      <c r="O104" s="19" t="inlineStr"/>
+      <c r="P104" s="19" t="inlineStr"/>
+      <c r="Q104" s="19" t="inlineStr"/>
+      <c r="R104" s="19" t="inlineStr"/>
+      <c r="S104" s="19" t="inlineStr"/>
+      <c r="T104" s="19" t="inlineStr"/>
+      <c r="U104" s="19" t="inlineStr"/>
+      <c r="V104" s="19" t="inlineStr"/>
+      <c r="W104" s="19" t="inlineStr"/>
+      <c r="X104" s="19" t="inlineStr"/>
+      <c r="Y104" s="18" t="inlineStr">
         <is>
           <t>Missing — 3 abstracts cited by the corpus [3 distinct meetings]</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="16" t="n">
+      <c r="A105" s="17" t="n">
         <v>2019</v>
       </c>
-      <c r="B105" s="19" t="inlineStr">
+      <c r="B105" s="20" t="inlineStr">
         <is>
           <t>Snowbird, UT; Ingested</t>
         </is>
       </c>
-      <c r="C105" s="19" t="inlineStr">
+      <c r="C105" s="20" t="inlineStr">
         <is>
           <t>Snowbird, UT (175); Ingested</t>
         </is>
       </c>
-      <c r="D105" s="19" t="inlineStr">
+      <c r="D105" s="20" t="inlineStr">
         <is>
           <t>Rende; Ingested — 136 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E105" s="19" t="inlineStr">
+      <c r="E105" s="20" t="inlineStr">
         <is>
           <t>Dunedin, New Zealand; Ingested — 211 abstracts, 209 with bodies; joint meeting, elasmo flagged per abstract</t>
         </is>
       </c>
-      <c r="F105" s="18" t="inlineStr"/>
-      <c r="G105" s="18" t="inlineStr"/>
-      <c r="H105" s="18" t="inlineStr"/>
-      <c r="I105" s="18" t="inlineStr"/>
-      <c r="J105" s="18" t="inlineStr"/>
-      <c r="K105" s="18" t="inlineStr"/>
-      <c r="L105" s="18" t="inlineStr"/>
-      <c r="M105" s="18" t="inlineStr"/>
-      <c r="N105" s="18" t="inlineStr"/>
-      <c r="O105" s="18" t="inlineStr"/>
-      <c r="P105" s="18" t="inlineStr"/>
-      <c r="Q105" s="18" t="inlineStr"/>
-      <c r="R105" s="18" t="inlineStr"/>
-      <c r="S105" s="18" t="inlineStr"/>
-      <c r="T105" s="18" t="inlineStr"/>
-      <c r="U105" s="17" t="inlineStr">
+      <c r="F105" s="19" t="inlineStr"/>
+      <c r="G105" s="19" t="inlineStr"/>
+      <c r="H105" s="19" t="inlineStr"/>
+      <c r="I105" s="19" t="inlineStr"/>
+      <c r="J105" s="19" t="inlineStr"/>
+      <c r="K105" s="19" t="inlineStr"/>
+      <c r="L105" s="19" t="inlineStr"/>
+      <c r="M105" s="19" t="inlineStr"/>
+      <c r="N105" s="19" t="inlineStr"/>
+      <c r="O105" s="19" t="inlineStr"/>
+      <c r="P105" s="19" t="inlineStr"/>
+      <c r="Q105" s="19" t="inlineStr"/>
+      <c r="R105" s="19" t="inlineStr"/>
+      <c r="S105" s="19" t="inlineStr"/>
+      <c r="T105" s="19" t="inlineStr"/>
+      <c r="U105" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="V105" s="18" t="inlineStr"/>
-      <c r="W105" s="18" t="inlineStr"/>
-      <c r="X105" s="18" t="inlineStr"/>
-      <c r="Y105" s="18" t="inlineStr"/>
+      <c r="V105" s="19" t="inlineStr"/>
+      <c r="W105" s="19" t="inlineStr"/>
+      <c r="X105" s="19" t="inlineStr"/>
+      <c r="Y105" s="19" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="16" t="n">
+      <c r="A106" s="17" t="n">
         <v>2020</v>
       </c>
-      <c r="B106" s="18" t="inlineStr">
+      <c r="B106" s="19" t="inlineStr">
         <is>
           <t>?; NA — no meeting — virtual BAAM-ZOOM sessions only, no abstract book</t>
         </is>
       </c>
-      <c r="C106" s="18" t="inlineStr">
+      <c r="C106" s="19" t="inlineStr">
         <is>
           <t>?; NA — no meeting — virtual BAAM-ZOOM sessions only, no abstract book</t>
         </is>
       </c>
-      <c r="D106" s="17" t="inlineStr">
+      <c r="D106" s="18" t="inlineStr">
         <is>
           <t>?; Missing — unknown whether a meeting was held: Cat thinks it was online for covid but was on maternity leave and is unsure; organiser unknown; abstracts unknown</t>
         </is>
       </c>
-      <c r="E106" s="19" t="inlineStr">
+      <c r="E106" s="20" t="inlineStr">
         <is>
           <t>Virtual; Ingested — 44 abstracts, 44 with bodies</t>
         </is>
       </c>
-      <c r="F106" s="18" t="inlineStr"/>
-      <c r="G106" s="18" t="inlineStr"/>
-      <c r="H106" s="18" t="inlineStr"/>
-      <c r="I106" s="18" t="inlineStr"/>
-      <c r="J106" s="18" t="inlineStr"/>
-      <c r="K106" s="18" t="inlineStr"/>
-      <c r="L106" s="18" t="inlineStr"/>
-      <c r="M106" s="18" t="inlineStr"/>
-      <c r="N106" s="18" t="inlineStr"/>
-      <c r="O106" s="18" t="inlineStr"/>
-      <c r="P106" s="18" t="inlineStr"/>
-      <c r="Q106" s="18" t="inlineStr"/>
-      <c r="R106" s="18" t="inlineStr"/>
-      <c r="S106" s="18" t="inlineStr"/>
-      <c r="T106" s="18" t="inlineStr"/>
-      <c r="U106" s="18" t="inlineStr"/>
-      <c r="V106" s="18" t="inlineStr"/>
-      <c r="W106" s="18" t="inlineStr"/>
-      <c r="X106" s="18" t="inlineStr"/>
-      <c r="Y106" s="17" t="inlineStr">
+      <c r="F106" s="19" t="inlineStr"/>
+      <c r="G106" s="19" t="inlineStr"/>
+      <c r="H106" s="19" t="inlineStr"/>
+      <c r="I106" s="19" t="inlineStr"/>
+      <c r="J106" s="19" t="inlineStr"/>
+      <c r="K106" s="19" t="inlineStr"/>
+      <c r="L106" s="19" t="inlineStr"/>
+      <c r="M106" s="19" t="inlineStr"/>
+      <c r="N106" s="19" t="inlineStr"/>
+      <c r="O106" s="19" t="inlineStr"/>
+      <c r="P106" s="19" t="inlineStr"/>
+      <c r="Q106" s="19" t="inlineStr"/>
+      <c r="R106" s="19" t="inlineStr"/>
+      <c r="S106" s="19" t="inlineStr"/>
+      <c r="T106" s="19" t="inlineStr"/>
+      <c r="U106" s="19" t="inlineStr"/>
+      <c r="V106" s="19" t="inlineStr"/>
+      <c r="W106" s="19" t="inlineStr"/>
+      <c r="X106" s="19" t="inlineStr"/>
+      <c r="Y106" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="16" t="n">
+      <c r="A107" s="17" t="n">
         <v>2021</v>
       </c>
-      <c r="B107" s="19" t="inlineStr">
+      <c r="B107" s="20" t="inlineStr">
         <is>
           <t>Phoenix, AZ; Ingested — Oxford Abstracts export (born-digital)</t>
         </is>
       </c>
-      <c r="C107" s="19" t="inlineStr">
+      <c r="C107" s="20" t="inlineStr">
         <is>
           <t>Phoenix, AZ (67); Ingested — Oxford Abstracts export (born-digital)</t>
         </is>
       </c>
-      <c r="D107" s="26" t="inlineStr">
+      <c r="D107" s="28" t="inlineStr">
         <is>
           <t>Leiden; Programme — programme only; abstract book needed from NEV</t>
         </is>
       </c>
-      <c r="E107" s="18" t="inlineStr"/>
-      <c r="F107" s="18" t="inlineStr"/>
-      <c r="G107" s="18" t="inlineStr"/>
-      <c r="H107" s="18" t="inlineStr"/>
-      <c r="I107" s="22" t="inlineStr">
+      <c r="E107" s="19" t="inlineStr"/>
+      <c r="F107" s="19" t="inlineStr"/>
+      <c r="G107" s="19" t="inlineStr"/>
+      <c r="H107" s="19" t="inlineStr"/>
+      <c r="I107" s="23" t="inlineStr">
         <is>
           <t>Puebla, Mexico; Digital — 1 PDF held — extraction pending</t>
         </is>
       </c>
-      <c r="J107" s="18" t="inlineStr"/>
-      <c r="K107" s="18" t="inlineStr"/>
-      <c r="L107" s="18" t="inlineStr"/>
-      <c r="M107" s="18" t="inlineStr"/>
-      <c r="N107" s="18" t="inlineStr"/>
-      <c r="O107" s="18" t="inlineStr"/>
-      <c r="P107" s="18" t="inlineStr"/>
-      <c r="Q107" s="18" t="inlineStr"/>
-      <c r="R107" s="18" t="inlineStr"/>
-      <c r="S107" s="18" t="inlineStr"/>
-      <c r="T107" s="18" t="inlineStr"/>
-      <c r="U107" s="18" t="inlineStr"/>
-      <c r="V107" s="18" t="inlineStr"/>
-      <c r="W107" s="18" t="inlineStr"/>
-      <c r="X107" s="18" t="inlineStr"/>
-      <c r="Y107" s="17" t="inlineStr">
+      <c r="J107" s="19" t="inlineStr"/>
+      <c r="K107" s="19" t="inlineStr"/>
+      <c r="L107" s="19" t="inlineStr"/>
+      <c r="M107" s="19" t="inlineStr"/>
+      <c r="N107" s="19" t="inlineStr"/>
+      <c r="O107" s="19" t="inlineStr"/>
+      <c r="P107" s="19" t="inlineStr"/>
+      <c r="Q107" s="19" t="inlineStr"/>
+      <c r="R107" s="19" t="inlineStr"/>
+      <c r="S107" s="19" t="inlineStr"/>
+      <c r="T107" s="19" t="inlineStr"/>
+      <c r="U107" s="19" t="inlineStr"/>
+      <c r="V107" s="19" t="inlineStr"/>
+      <c r="W107" s="19" t="inlineStr"/>
+      <c r="X107" s="19" t="inlineStr"/>
+      <c r="Y107" s="18" t="inlineStr">
         <is>
           <t>Missing — 2 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="16" t="n">
+      <c r="A108" s="17" t="n">
         <v>2022</v>
       </c>
-      <c r="B108" s="19" t="inlineStr">
+      <c r="B108" s="20" t="inlineStr">
         <is>
           <t>Spokane, WA; Ingested — Oxford Abstracts export (born-digital)</t>
         </is>
       </c>
-      <c r="C108" s="19" t="inlineStr">
+      <c r="C108" s="20" t="inlineStr">
         <is>
           <t>Spokane, WA (109); Ingested — Oxford Abstracts export (born-digital)</t>
         </is>
       </c>
-      <c r="D108" s="22" t="inlineStr">
+      <c r="D108" s="23" t="inlineStr">
         <is>
           <t>Valencia (=SI2022); Digital — full SI2022 abstract book received 2026-08-27; queued for extraction</t>
         </is>
       </c>
-      <c r="E108" s="19" t="inlineStr">
+      <c r="E108" s="20" t="inlineStr">
         <is>
           <t>Virtual; Ingested — 30 abstracts, 30 with bodies</t>
         </is>
       </c>
-      <c r="F108" s="22" t="inlineStr">
+      <c r="F108" s="23" t="inlineStr">
         <is>
           <t>Valencia; Digital — full abstract book received 2026-08-27; queued (schedule already ingested)</t>
         </is>
       </c>
-      <c r="G108" s="18" t="inlineStr"/>
-      <c r="H108" s="18" t="inlineStr"/>
-      <c r="I108" s="18" t="inlineStr"/>
-      <c r="J108" s="18" t="inlineStr"/>
-      <c r="K108" s="18" t="inlineStr"/>
-      <c r="L108" s="18" t="inlineStr"/>
-      <c r="M108" s="18" t="inlineStr"/>
-      <c r="N108" s="18" t="inlineStr"/>
-      <c r="O108" s="18" t="inlineStr"/>
-      <c r="P108" s="18" t="inlineStr"/>
-      <c r="Q108" s="18" t="inlineStr"/>
-      <c r="R108" s="18" t="inlineStr"/>
-      <c r="S108" s="18" t="inlineStr"/>
-      <c r="T108" s="18" t="inlineStr"/>
-      <c r="U108" s="18" t="inlineStr"/>
-      <c r="V108" s="18" t="inlineStr"/>
-      <c r="W108" s="18" t="inlineStr"/>
-      <c r="X108" s="18" t="inlineStr"/>
-      <c r="Y108" s="17" t="inlineStr">
+      <c r="G108" s="19" t="inlineStr"/>
+      <c r="H108" s="19" t="inlineStr"/>
+      <c r="I108" s="19" t="inlineStr"/>
+      <c r="J108" s="19" t="inlineStr"/>
+      <c r="K108" s="19" t="inlineStr"/>
+      <c r="L108" s="19" t="inlineStr"/>
+      <c r="M108" s="19" t="inlineStr"/>
+      <c r="N108" s="19" t="inlineStr"/>
+      <c r="O108" s="19" t="inlineStr"/>
+      <c r="P108" s="19" t="inlineStr"/>
+      <c r="Q108" s="19" t="inlineStr"/>
+      <c r="R108" s="19" t="inlineStr"/>
+      <c r="S108" s="19" t="inlineStr"/>
+      <c r="T108" s="19" t="inlineStr"/>
+      <c r="U108" s="19" t="inlineStr"/>
+      <c r="V108" s="19" t="inlineStr"/>
+      <c r="W108" s="19" t="inlineStr"/>
+      <c r="X108" s="19" t="inlineStr"/>
+      <c r="Y108" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 2 abstracts cited by the corpus</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="16" t="n">
+      <c r="A109" s="17" t="n">
         <v>2023</v>
       </c>
-      <c r="B109" s="19" t="inlineStr">
+      <c r="B109" s="20" t="inlineStr">
         <is>
           <t>Norfolk, VA; Ingested</t>
         </is>
       </c>
-      <c r="C109" s="19" t="inlineStr">
+      <c r="C109" s="20" t="inlineStr">
         <is>
           <t>Norfolk, VA (154); Ingested</t>
         </is>
       </c>
-      <c r="D109" s="19" t="inlineStr">
+      <c r="D109" s="20" t="inlineStr">
         <is>
           <t>Brighton; Ingested — oral 64 + poster 34 = 98 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E109" s="18" t="inlineStr"/>
-      <c r="F109" s="18" t="inlineStr"/>
-      <c r="G109" s="18" t="inlineStr"/>
-      <c r="H109" s="18" t="inlineStr"/>
-      <c r="I109" s="18" t="inlineStr"/>
-      <c r="J109" s="18" t="inlineStr"/>
-      <c r="K109" s="18" t="inlineStr"/>
-      <c r="L109" s="18" t="inlineStr"/>
-      <c r="M109" s="18" t="inlineStr"/>
-      <c r="N109" s="18" t="inlineStr"/>
-      <c r="O109" s="18" t="inlineStr"/>
-      <c r="P109" s="18" t="inlineStr"/>
-      <c r="Q109" s="18" t="inlineStr"/>
-      <c r="R109" s="18" t="inlineStr"/>
-      <c r="S109" s="18" t="inlineStr"/>
-      <c r="T109" s="17" t="inlineStr">
+      <c r="E109" s="19" t="inlineStr"/>
+      <c r="F109" s="19" t="inlineStr"/>
+      <c r="G109" s="19" t="inlineStr"/>
+      <c r="H109" s="19" t="inlineStr"/>
+      <c r="I109" s="19" t="inlineStr"/>
+      <c r="J109" s="19" t="inlineStr"/>
+      <c r="K109" s="19" t="inlineStr"/>
+      <c r="L109" s="19" t="inlineStr"/>
+      <c r="M109" s="19" t="inlineStr"/>
+      <c r="N109" s="19" t="inlineStr"/>
+      <c r="O109" s="25" t="inlineStr">
+        <is>
+          <t>Auckland, New Zealand; Partial — 142 abstracts, elasmo-targeted pages only (teleost content not captured)</t>
+        </is>
+      </c>
+      <c r="P109" s="19" t="inlineStr"/>
+      <c r="Q109" s="19" t="inlineStr"/>
+      <c r="R109" s="19" t="inlineStr"/>
+      <c r="S109" s="19" t="inlineStr"/>
+      <c r="T109" s="18" t="inlineStr">
         <is>
           <t>Stuttgart, Germany; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="U109" s="18" t="inlineStr"/>
-      <c r="V109" s="18" t="inlineStr"/>
-      <c r="W109" s="18" t="inlineStr"/>
-      <c r="X109" s="18" t="inlineStr"/>
-      <c r="Y109" s="17" t="inlineStr">
+      <c r="U109" s="19" t="inlineStr"/>
+      <c r="V109" s="19" t="inlineStr"/>
+      <c r="W109" s="19" t="inlineStr"/>
+      <c r="X109" s="19" t="inlineStr"/>
+      <c r="Y109" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="16" t="n">
+      <c r="A110" s="17" t="n">
         <v>2024</v>
       </c>
-      <c r="B110" s="19" t="inlineStr">
+      <c r="B110" s="20" t="inlineStr">
         <is>
           <t>Pittsburgh, PA; Ingested</t>
         </is>
       </c>
-      <c r="C110" s="19" t="inlineStr">
+      <c r="C110" s="20" t="inlineStr">
         <is>
           <t>Pittsburgh, PA (148); Ingested</t>
         </is>
       </c>
-      <c r="D110" s="22" t="inlineStr">
+      <c r="D110" s="23" t="inlineStr">
         <is>
           <t>Thessaloniki; Digital — clean abstract book received from Cat 2026-08-27; queued for extraction</t>
         </is>
       </c>
-      <c r="E110" s="19" t="inlineStr">
+      <c r="E110" s="20" t="inlineStr">
         <is>
           <t>Geelong; Ingested — 63 abstracts, 60 with bodies</t>
         </is>
       </c>
-      <c r="F110" s="18" t="inlineStr"/>
-      <c r="G110" s="18" t="inlineStr"/>
-      <c r="H110" s="18" t="inlineStr"/>
-      <c r="I110" s="18" t="inlineStr"/>
-      <c r="J110" s="18" t="inlineStr"/>
-      <c r="K110" s="18" t="inlineStr"/>
-      <c r="L110" s="18" t="inlineStr"/>
-      <c r="M110" s="18" t="inlineStr"/>
-      <c r="N110" s="18" t="inlineStr"/>
-      <c r="O110" s="18" t="inlineStr"/>
-      <c r="P110" s="18" t="inlineStr"/>
-      <c r="Q110" s="18" t="inlineStr"/>
-      <c r="R110" s="18" t="inlineStr"/>
-      <c r="S110" s="18" t="inlineStr"/>
-      <c r="T110" s="18" t="inlineStr"/>
-      <c r="U110" s="18" t="inlineStr"/>
-      <c r="V110" s="18" t="inlineStr"/>
-      <c r="W110" s="18" t="inlineStr"/>
-      <c r="X110" s="18" t="inlineStr"/>
-      <c r="Y110" s="18" t="inlineStr"/>
+      <c r="F110" s="19" t="inlineStr"/>
+      <c r="G110" s="19" t="inlineStr"/>
+      <c r="H110" s="19" t="inlineStr"/>
+      <c r="I110" s="19" t="inlineStr"/>
+      <c r="J110" s="19" t="inlineStr"/>
+      <c r="K110" s="19" t="inlineStr"/>
+      <c r="L110" s="19" t="inlineStr"/>
+      <c r="M110" s="19" t="inlineStr"/>
+      <c r="N110" s="19" t="inlineStr"/>
+      <c r="O110" s="19" t="inlineStr"/>
+      <c r="P110" s="19" t="inlineStr"/>
+      <c r="Q110" s="19" t="inlineStr"/>
+      <c r="R110" s="19" t="inlineStr"/>
+      <c r="S110" s="19" t="inlineStr"/>
+      <c r="T110" s="19" t="inlineStr"/>
+      <c r="U110" s="19" t="inlineStr"/>
+      <c r="V110" s="19" t="inlineStr"/>
+      <c r="W110" s="19" t="inlineStr"/>
+      <c r="X110" s="19" t="inlineStr"/>
+      <c r="Y110" s="19" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="16" t="n">
+      <c r="A111" s="17" t="n">
         <v>2025</v>
       </c>
-      <c r="B111" s="19" t="inlineStr">
+      <c r="B111" s="20" t="inlineStr">
         <is>
           <t>St. Paul, MN; Ingested — Oxford Abstracts export (born-digital)</t>
         </is>
       </c>
-      <c r="C111" s="19" t="inlineStr">
+      <c r="C111" s="20" t="inlineStr">
         <is>
           <t>St. Paul, MN (123); Ingested — Oxford Abstracts export (born-digital)</t>
         </is>
       </c>
-      <c r="D111" s="26" t="inlineStr">
+      <c r="D111" s="28" t="inlineStr">
         <is>
           <t>Rotterdam; Programme — agenda only; Cat has no abstract book and is unsure one was produced; NEV/Irene to confirm whether it exists</t>
         </is>
       </c>
-      <c r="E111" s="19" t="inlineStr">
+      <c r="E111" s="20" t="inlineStr">
         <is>
           <t>Sunshine Coast, QLD, Australia; Ingested — 92 abstracts, 92 with bodies</t>
         </is>
       </c>
-      <c r="F111" s="18" t="inlineStr"/>
-      <c r="G111" s="18" t="inlineStr"/>
-      <c r="H111" s="18" t="inlineStr"/>
-      <c r="I111" s="22" t="inlineStr">
+      <c r="F111" s="19" t="inlineStr"/>
+      <c r="G111" s="19" t="inlineStr"/>
+      <c r="H111" s="19" t="inlineStr"/>
+      <c r="I111" s="23" t="inlineStr">
         <is>
           <t>Ensenada, Baja California, Mexico; Digital — 1 PDF held — extraction pending</t>
         </is>
       </c>
-      <c r="J111" s="18" t="inlineStr"/>
-      <c r="K111" s="18" t="inlineStr"/>
-      <c r="L111" s="18" t="inlineStr"/>
-      <c r="M111" s="18" t="inlineStr"/>
-      <c r="N111" s="18" t="inlineStr"/>
-      <c r="O111" s="18" t="inlineStr"/>
-      <c r="P111" s="18" t="inlineStr"/>
-      <c r="Q111" s="18" t="inlineStr"/>
-      <c r="R111" s="18" t="inlineStr"/>
-      <c r="S111" s="18" t="inlineStr"/>
-      <c r="T111" s="18" t="inlineStr"/>
-      <c r="U111" s="18" t="inlineStr"/>
-      <c r="V111" s="18" t="inlineStr"/>
-      <c r="W111" s="18" t="inlineStr"/>
-      <c r="X111" s="18" t="inlineStr"/>
-      <c r="Y111" s="17" t="inlineStr">
+      <c r="J111" s="19" t="inlineStr"/>
+      <c r="K111" s="19" t="inlineStr"/>
+      <c r="L111" s="19" t="inlineStr"/>
+      <c r="M111" s="19" t="inlineStr"/>
+      <c r="N111" s="19" t="inlineStr"/>
+      <c r="O111" s="19" t="inlineStr"/>
+      <c r="P111" s="19" t="inlineStr"/>
+      <c r="Q111" s="19" t="inlineStr"/>
+      <c r="R111" s="19" t="inlineStr"/>
+      <c r="S111" s="19" t="inlineStr"/>
+      <c r="T111" s="19" t="inlineStr"/>
+      <c r="U111" s="19" t="inlineStr"/>
+      <c r="V111" s="19" t="inlineStr"/>
+      <c r="W111" s="19" t="inlineStr"/>
+      <c r="X111" s="19" t="inlineStr"/>
+      <c r="Y111" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 3 abstracts cited by the corpus</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="16" t="n">
+      <c r="A112" s="17" t="n">
         <v>2026</v>
       </c>
-      <c r="B112" s="24" t="inlineStr">
+      <c r="B112" s="26" t="inlineStr">
         <is>
           <t>New Orleans, LA; Extracted — regex-parsed; Fable re-extraction queued</t>
         </is>
       </c>
-      <c r="C112" s="24" t="inlineStr">
+      <c r="C112" s="26" t="inlineStr">
         <is>
           <t>New Orleans, LA (235); Extracted — regex-parsed; Fable re-extraction queued</t>
         </is>
       </c>
-      <c r="D112" s="23" t="inlineStr">
+      <c r="D112" s="24" t="inlineStr">
         <is>
           <t>online; Pending — will be digital (Shark Trust hosting)</t>
         </is>
       </c>
-      <c r="E112" s="23" t="inlineStr">
+      <c r="E112" s="24" t="inlineStr">
         <is>
           <t>?; Pending — Brit Finucci collating; year/location to confirm</t>
         </is>
       </c>
-      <c r="F112" s="19" t="inlineStr">
+      <c r="F112" s="20" t="inlineStr">
         <is>
           <t>Colombo; Ingested</t>
         </is>
       </c>
-      <c r="G112" s="18" t="inlineStr"/>
-      <c r="H112" s="18" t="inlineStr"/>
-      <c r="I112" s="18" t="inlineStr"/>
-      <c r="J112" s="18" t="inlineStr"/>
-      <c r="K112" s="18" t="inlineStr"/>
-      <c r="L112" s="18" t="inlineStr"/>
-      <c r="M112" s="18" t="inlineStr"/>
-      <c r="N112" s="18" t="inlineStr"/>
-      <c r="O112" s="18" t="inlineStr"/>
-      <c r="P112" s="18" t="inlineStr"/>
-      <c r="Q112" s="18" t="inlineStr"/>
-      <c r="R112" s="18" t="inlineStr"/>
-      <c r="S112" s="18" t="inlineStr"/>
-      <c r="T112" s="18" t="inlineStr"/>
-      <c r="U112" s="18" t="inlineStr"/>
-      <c r="V112" s="18" t="inlineStr"/>
-      <c r="W112" s="18" t="inlineStr"/>
-      <c r="X112" s="18" t="inlineStr"/>
-      <c r="Y112" s="18" t="inlineStr"/>
+      <c r="G112" s="19" t="inlineStr"/>
+      <c r="H112" s="19" t="inlineStr"/>
+      <c r="I112" s="19" t="inlineStr"/>
+      <c r="J112" s="19" t="inlineStr"/>
+      <c r="K112" s="19" t="inlineStr"/>
+      <c r="L112" s="19" t="inlineStr"/>
+      <c r="M112" s="19" t="inlineStr"/>
+      <c r="N112" s="19" t="inlineStr"/>
+      <c r="O112" s="19" t="inlineStr"/>
+      <c r="P112" s="19" t="inlineStr"/>
+      <c r="Q112" s="19" t="inlineStr"/>
+      <c r="R112" s="19" t="inlineStr"/>
+      <c r="S112" s="19" t="inlineStr"/>
+      <c r="T112" s="19" t="inlineStr"/>
+      <c r="U112" s="19" t="inlineStr"/>
+      <c r="V112" s="19" t="inlineStr"/>
+      <c r="W112" s="19" t="inlineStr"/>
+      <c r="X112" s="19" t="inlineStr"/>
+      <c r="Y112" s="19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6645,7 +6675,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="27" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>Conference abstract coverage — dashboard</t>
         </is>
@@ -6834,7 +6864,7 @@
         <v>345</v>
       </c>
       <c r="D9" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -6854,19 +6884,19 @@
         <v>1998</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>339</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -7022,7 +7052,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
         <v>55</v>
@@ -7036,19 +7066,19 @@
         <v>2005</v>
       </c>
       <c r="B17" t="n">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>461</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>344</v>
       </c>
       <c r="E17" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -7062,19 +7092,19 @@
         <v>2006</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -7088,19 +7118,19 @@
         <v>2007</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>434</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>297</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -7114,19 +7144,19 @@
         <v>2008</v>
       </c>
       <c r="B20" t="n">
-        <v>126</v>
+        <v>193</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D20" t="n">
-        <v>13</v>
+        <v>191</v>
       </c>
       <c r="E20" t="n">
         <v>22</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -7140,19 +7170,19 @@
         <v>2009</v>
       </c>
       <c r="B21" t="n">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="C21" t="n">
-        <v>23</v>
+        <v>518</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="E21" t="n">
         <v>39</v>
       </c>
       <c r="F21" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -7166,19 +7196,19 @@
         <v>2010</v>
       </c>
       <c r="B22" t="n">
-        <v>115</v>
+        <v>167</v>
       </c>
       <c r="C22" t="n">
-        <v>38</v>
+        <v>359</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="E22" t="n">
         <v>28</v>
       </c>
       <c r="F22" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -7270,19 +7300,19 @@
         <v>2014</v>
       </c>
       <c r="B26" t="n">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="C26" t="n">
-        <v>120</v>
+        <v>366</v>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>206</v>
       </c>
       <c r="E26" t="n">
         <v>74</v>
       </c>
       <c r="F26" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G26" t="n">
         <v>61</v>
@@ -7296,19 +7326,19 @@
         <v>2015</v>
       </c>
       <c r="B27" t="n">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="C27" t="n">
-        <v>76</v>
+        <v>317</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G27" t="n">
         <v>86</v>
@@ -7322,19 +7352,19 @@
         <v>2016</v>
       </c>
       <c r="B28" t="n">
-        <v>162</v>
+        <v>231</v>
       </c>
       <c r="C28" t="n">
-        <v>137</v>
+        <v>455</v>
       </c>
       <c r="D28" t="n">
-        <v>39</v>
+        <v>261</v>
       </c>
       <c r="E28" t="n">
         <v>97</v>
       </c>
       <c r="F28" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G28" t="n">
         <v>93</v>
@@ -7348,19 +7378,19 @@
         <v>2017</v>
       </c>
       <c r="B29" t="n">
-        <v>118</v>
+        <v>154</v>
       </c>
       <c r="C29" t="n">
-        <v>127</v>
+        <v>383</v>
       </c>
       <c r="D29" t="n">
-        <v>32</v>
+        <v>240</v>
       </c>
       <c r="E29" t="n">
         <v>75</v>
       </c>
       <c r="F29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G29" t="n">
         <v>62</v>
@@ -7374,19 +7404,19 @@
         <v>2018</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C30" t="n">
-        <v>130</v>
+        <v>303</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>187</v>
       </c>
       <c r="E30" t="n">
         <v>89</v>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G30" t="n">
         <v>75</v>
@@ -7400,19 +7430,19 @@
         <v>2019</v>
       </c>
       <c r="B31" t="n">
-        <v>114</v>
+        <v>166</v>
       </c>
       <c r="C31" t="n">
-        <v>164</v>
+        <v>349</v>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>171</v>
       </c>
       <c r="E31" t="n">
         <v>74</v>
       </c>
       <c r="F31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G31" t="n">
         <v>136</v>
@@ -7452,13 +7482,13 @@
         <v>2021</v>
       </c>
       <c r="B33" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C33" t="n">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="D33" t="n">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="E33" t="n">
         <v>52</v>
@@ -7478,19 +7508,19 @@
         <v>2022</v>
       </c>
       <c r="B34" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C34" t="n">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="D34" t="n">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="E34" t="n">
         <v>118</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -7504,19 +7534,19 @@
         <v>2023</v>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G35" t="n">
         <v>98</v>
@@ -7530,19 +7560,19 @@
         <v>2024</v>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>148</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G36" t="n">
         <v>96</v>
@@ -7556,19 +7586,19 @@
         <v>2025</v>
       </c>
       <c r="B37" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C37" t="n">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="D37" t="n">
-        <v>35</v>
+        <v>108</v>
       </c>
       <c r="E37" t="n">
         <v>113</v>
       </c>
       <c r="F37" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -7585,16 +7615,16 @@
         <v>235</v>
       </c>
       <c r="C38" t="n">
-        <v>20</v>
+        <v>458</v>
       </c>
       <c r="D38" t="n">
-        <v>10</v>
+        <v>287</v>
       </c>
       <c r="E38" t="n">
         <v>46</v>
       </c>
       <c r="F38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -7610,19 +7640,19 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>2511</v>
+        <v>3557</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>2624</v>
+        <v>7811</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>839</v>
+        <v>4525</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>858</v>
+        <v>863</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>94</v>
+        <v>156</v>
       </c>
       <c r="G39" s="1" t="n">
         <v>956</v>

--- a/database/conference_coverage_matrix.xlsx
+++ b/database/conference_coverage_matrix.xlsx
@@ -188,13 +188,13 @@
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -5870,14 +5870,14 @@
       <c r="A98" s="17" t="n">
         <v>2012</v>
       </c>
-      <c r="B98" s="26" t="inlineStr">
-        <is>
-          <t>Vancouver, BC; Extracted — regex-parsed; Fable re-extraction part-done (1078 so far)</t>
-        </is>
-      </c>
-      <c r="C98" s="26" t="inlineStr">
-        <is>
-          <t>Vancouver, BC (62); Extracted — regex-parsed; Fable re-extraction part-done (1078 so far)</t>
+      <c r="B98" s="20" t="inlineStr">
+        <is>
+          <t>Vancouver, BC; Ingested</t>
+        </is>
+      </c>
+      <c r="C98" s="20" t="inlineStr">
+        <is>
+          <t>Vancouver, BC (174); Ingested</t>
         </is>
       </c>
       <c r="D98" s="21" t="inlineStr">
@@ -6173,7 +6173,7 @@
           <t>Austin, TX (162); Ingested</t>
         </is>
       </c>
-      <c r="D103" s="27" t="inlineStr">
+      <c r="D103" s="26" t="inlineStr">
         <is>
           <t>Amsterdam; Schedule — 62 talks ingested, NO abstract bodies; Cat holds a hardcopy but has no scanning capacity; abstract book needed from NEV</t>
         </is>
@@ -6369,7 +6369,7 @@
           <t>Phoenix, AZ (67); Ingested — Oxford Abstracts export (born-digital)</t>
         </is>
       </c>
-      <c r="D107" s="28" t="inlineStr">
+      <c r="D107" s="27" t="inlineStr">
         <is>
           <t>Leiden; Programme — programme only; abstract book needed from NEV</t>
         </is>
@@ -6569,7 +6569,7 @@
           <t>St. Paul, MN (123); Ingested — Oxford Abstracts export (born-digital)</t>
         </is>
       </c>
-      <c r="D111" s="28" t="inlineStr">
+      <c r="D111" s="27" t="inlineStr">
         <is>
           <t>Rotterdam; Programme — agenda only; Cat has no abstract book and is unsure one was produced; NEV/Irene to confirm whether it exists</t>
         </is>
@@ -6612,12 +6612,12 @@
       <c r="A112" s="17" t="n">
         <v>2026</v>
       </c>
-      <c r="B112" s="26" t="inlineStr">
+      <c r="B112" s="28" t="inlineStr">
         <is>
           <t>New Orleans, LA; Extracted — regex-parsed; Fable re-extraction queued</t>
         </is>
       </c>
-      <c r="C112" s="26" t="inlineStr">
+      <c r="C112" s="28" t="inlineStr">
         <is>
           <t>New Orleans, LA (235); Extracted — regex-parsed; Fable re-extraction queued</t>
         </is>
@@ -7072,7 +7072,7 @@
         <v>461</v>
       </c>
       <c r="D17" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E17" t="n">
         <v>36</v>
@@ -7095,10 +7095,10 @@
         <v>169</v>
       </c>
       <c r="C18" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D18" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7248,19 +7248,19 @@
         <v>2012</v>
       </c>
       <c r="B24" t="n">
-        <v>62</v>
+        <v>174</v>
       </c>
       <c r="C24" t="n">
-        <v>135</v>
+        <v>397</v>
       </c>
       <c r="D24" t="n">
-        <v>239</v>
+        <v>879</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -7303,10 +7303,10 @@
         <v>87</v>
       </c>
       <c r="C26" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D26" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E26" t="n">
         <v>74</v>
@@ -7384,7 +7384,7 @@
         <v>383</v>
       </c>
       <c r="D29" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E29" t="n">
         <v>75</v>
@@ -7488,7 +7488,7 @@
         <v>189</v>
       </c>
       <c r="D33" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E33" t="n">
         <v>52</v>
@@ -7540,7 +7540,7 @@
         <v>237</v>
       </c>
       <c r="D35" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -7615,10 +7615,10 @@
         <v>235</v>
       </c>
       <c r="C38" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D38" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E38" t="n">
         <v>46</v>
@@ -7640,19 +7640,19 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>3557</v>
+        <v>3669</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>7811</v>
+        <v>8076</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>4525</v>
+        <v>5173</v>
       </c>
       <c r="E39" s="1" t="n">
         <v>863</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="G39" s="1" t="n">
         <v>956</v>
@@ -7690,13 +7690,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C43" t="n">
         <v>42</v>
       </c>
       <c r="D43" t="n">
-        <v>85.7</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="44">

--- a/database/conference_coverage_matrix.xlsx
+++ b/database/conference_coverage_matrix.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Conferences'!$A$1:$H$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Conferences'!$A$1:$H$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -198,6 +198,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1359,7 +1360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -2148,29 +2149,138 @@
       <c r="G25" s="14" t="inlineStr"/>
       <c r="H25" s="14" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>SVP (Society of Vertebrate Paleontology annual meeting)</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="n">
+        <v>1940</v>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>57</v>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>Society of Vertebrate Paleontology. Annual meeting; abstracts published as a "Supplement to Number 3" (pre-2013 volumes) or "(Suppl. N)" issue of the Journal of Vertebrate Paleontology, one abstract per page, page numbers suffixed "A" (e.g. 29(Suppl. to No.3), 52A). Elasmobranch-relevant abstracts run at least 1988-2020 in this corpus; the series itself runs continuously to the present.</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>https://vertpaleo.org/annual-meeting/</t>
+        </is>
+      </c>
+      <c r="H26" s="14" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>SICB (Society for Integrative and Comparative Biology)</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="n">
+        <v>1991</v>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>38</v>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>Society for Integrative and Comparative Biology (formed 1991 from the American Society of Zoologists). Annual meeting abstracts published as a January Suppl. 1 issue of Integrative and Comparative Biology (formerly American Zoologist for the ASZ-era predecessor, 1961-1996), one abstract per page, pages prefixed "E" (e.g. 54(IS Suppl. 1): E48). 3 more elasmobranch abstracts found under the predecessor title American Zoologist (1978, 1980, 1985), same page-suffix convention but ending "A" not "E".</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>https://sicb.org/meetings/</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>SIBM (Società Italiana di Biologia Marina)</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="n">
+        <v>1969</v>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>Società Italiana di Biologia Marina. Annual congress; short (1-2 page) proceedings notes published in the society journal Biologia Marina Mediterranea (ISSN 1123-4245) alongside the journal's normal full-length articles -- so NOT every Biologia Marina Mediterranea record is a congress note, only the short ones (page span &lt;=2). Elasmobranch-relevant notes seen 1999-2015 in this corpus.</t>
+        </is>
+      </c>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>https://www.sibm.it/</t>
+        </is>
+      </c>
+      <c r="H28" s="14" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>frequency: 1 = annual, 2 = biennial, 3 = every three years, 4 = every four years, 0 = one-off / irregular</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>n_needed: corpus records citing that series whose PDF we do NOT hold (scripts/conf_abstracts/conference_lead_candidates.py). It counts abstracts we can already name, so it is a floor, not the size of the series.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>A BLANK organisers/website/contact means not found on 2026-09-04, never a guess — a wrong address costs a real email to a real person.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H25"/>
+  <autoFilter ref="A1:H28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2181,7 +2291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y112"/>
+  <dimension ref="A1:AB112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2209,6 +2319,9 @@
     <col width="30" customWidth="1" min="23" max="23"/>
     <col width="30" customWidth="1" min="24" max="24"/>
     <col width="30" customWidth="1" min="25" max="25"/>
+    <col width="30" customWidth="1" min="26" max="26"/>
+    <col width="30" customWidth="1" min="27" max="27"/>
+    <col width="30" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2335,6 +2448,21 @@
       <c r="Y1" s="16" t="inlineStr">
         <is>
           <t>Palaeo/geol</t>
+        </is>
+      </c>
+      <c r="Z1" s="16" t="inlineStr">
+        <is>
+          <t>SVP</t>
+        </is>
+      </c>
+      <c r="AA1" s="16" t="inlineStr">
+        <is>
+          <t>SICB</t>
+        </is>
+      </c>
+      <c r="AB1" s="16" t="inlineStr">
+        <is>
+          <t>SIBM</t>
         </is>
       </c>
     </row>
@@ -2370,6 +2498,9 @@
       <c r="W2" s="19" t="inlineStr"/>
       <c r="X2" s="19" t="inlineStr"/>
       <c r="Y2" s="19" t="inlineStr"/>
+      <c r="Z2" s="30" t="n"/>
+      <c r="AA2" s="30" t="n"/>
+      <c r="AB2" s="30" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="17" t="n">
@@ -2403,6 +2534,9 @@
       <c r="W3" s="19" t="inlineStr"/>
       <c r="X3" s="19" t="inlineStr"/>
       <c r="Y3" s="19" t="inlineStr"/>
+      <c r="Z3" s="30" t="n"/>
+      <c r="AA3" s="30" t="n"/>
+      <c r="AB3" s="30" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="17" t="n">
@@ -2436,6 +2570,9 @@
       <c r="W4" s="19" t="inlineStr"/>
       <c r="X4" s="19" t="inlineStr"/>
       <c r="Y4" s="19" t="inlineStr"/>
+      <c r="Z4" s="30" t="n"/>
+      <c r="AA4" s="30" t="n"/>
+      <c r="AB4" s="30" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="17" t="n">
@@ -2469,6 +2606,9 @@
       <c r="W5" s="19" t="inlineStr"/>
       <c r="X5" s="19" t="inlineStr"/>
       <c r="Y5" s="19" t="inlineStr"/>
+      <c r="Z5" s="30" t="n"/>
+      <c r="AA5" s="30" t="n"/>
+      <c r="AB5" s="30" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="17" t="n">
@@ -2502,6 +2642,9 @@
       <c r="W6" s="19" t="inlineStr"/>
       <c r="X6" s="19" t="inlineStr"/>
       <c r="Y6" s="19" t="inlineStr"/>
+      <c r="Z6" s="30" t="n"/>
+      <c r="AA6" s="30" t="n"/>
+      <c r="AB6" s="30" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="17" t="n">
@@ -2535,6 +2678,9 @@
       <c r="W7" s="19" t="inlineStr"/>
       <c r="X7" s="19" t="inlineStr"/>
       <c r="Y7" s="19" t="inlineStr"/>
+      <c r="Z7" s="30" t="n"/>
+      <c r="AA7" s="30" t="n"/>
+      <c r="AB7" s="30" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="17" t="n">
@@ -2568,6 +2714,9 @@
       <c r="W8" s="19" t="inlineStr"/>
       <c r="X8" s="19" t="inlineStr"/>
       <c r="Y8" s="19" t="inlineStr"/>
+      <c r="Z8" s="30" t="n"/>
+      <c r="AA8" s="30" t="n"/>
+      <c r="AB8" s="30" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="17" t="n">
@@ -2601,6 +2750,9 @@
       <c r="W9" s="19" t="inlineStr"/>
       <c r="X9" s="19" t="inlineStr"/>
       <c r="Y9" s="19" t="inlineStr"/>
+      <c r="Z9" s="30" t="n"/>
+      <c r="AA9" s="30" t="n"/>
+      <c r="AB9" s="30" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="17" t="n">
@@ -2634,6 +2786,9 @@
       <c r="W10" s="19" t="inlineStr"/>
       <c r="X10" s="19" t="inlineStr"/>
       <c r="Y10" s="19" t="inlineStr"/>
+      <c r="Z10" s="30" t="n"/>
+      <c r="AA10" s="30" t="n"/>
+      <c r="AB10" s="30" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="17" t="n">
@@ -2667,6 +2822,9 @@
       <c r="W11" s="19" t="inlineStr"/>
       <c r="X11" s="19" t="inlineStr"/>
       <c r="Y11" s="19" t="inlineStr"/>
+      <c r="Z11" s="30" t="n"/>
+      <c r="AA11" s="30" t="n"/>
+      <c r="AB11" s="30" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="17" t="n">
@@ -2700,6 +2858,9 @@
       <c r="W12" s="19" t="inlineStr"/>
       <c r="X12" s="19" t="inlineStr"/>
       <c r="Y12" s="19" t="inlineStr"/>
+      <c r="Z12" s="30" t="n"/>
+      <c r="AA12" s="30" t="n"/>
+      <c r="AB12" s="30" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="17" t="n">
@@ -2733,6 +2894,9 @@
       <c r="W13" s="19" t="inlineStr"/>
       <c r="X13" s="19" t="inlineStr"/>
       <c r="Y13" s="19" t="inlineStr"/>
+      <c r="Z13" s="30" t="n"/>
+      <c r="AA13" s="30" t="n"/>
+      <c r="AB13" s="30" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="17" t="n">
@@ -2766,6 +2930,9 @@
       <c r="W14" s="19" t="inlineStr"/>
       <c r="X14" s="19" t="inlineStr"/>
       <c r="Y14" s="19" t="inlineStr"/>
+      <c r="Z14" s="30" t="n"/>
+      <c r="AA14" s="30" t="n"/>
+      <c r="AB14" s="30" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="17" t="n">
@@ -2799,6 +2966,9 @@
       <c r="W15" s="19" t="inlineStr"/>
       <c r="X15" s="19" t="inlineStr"/>
       <c r="Y15" s="19" t="inlineStr"/>
+      <c r="Z15" s="30" t="n"/>
+      <c r="AA15" s="30" t="n"/>
+      <c r="AB15" s="30" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="n">
@@ -2832,6 +3002,9 @@
       <c r="W16" s="19" t="inlineStr"/>
       <c r="X16" s="19" t="inlineStr"/>
       <c r="Y16" s="19" t="inlineStr"/>
+      <c r="Z16" s="30" t="n"/>
+      <c r="AA16" s="30" t="n"/>
+      <c r="AB16" s="30" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="17" t="n">
@@ -2865,6 +3038,9 @@
       <c r="W17" s="19" t="inlineStr"/>
       <c r="X17" s="19" t="inlineStr"/>
       <c r="Y17" s="19" t="inlineStr"/>
+      <c r="Z17" s="30" t="n"/>
+      <c r="AA17" s="30" t="n"/>
+      <c r="AB17" s="30" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="17" t="n">
@@ -2898,6 +3074,9 @@
       <c r="W18" s="19" t="inlineStr"/>
       <c r="X18" s="19" t="inlineStr"/>
       <c r="Y18" s="19" t="inlineStr"/>
+      <c r="Z18" s="30" t="n"/>
+      <c r="AA18" s="30" t="n"/>
+      <c r="AB18" s="30" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="17" t="n">
@@ -2931,6 +3110,9 @@
       <c r="W19" s="19" t="inlineStr"/>
       <c r="X19" s="19" t="inlineStr"/>
       <c r="Y19" s="19" t="inlineStr"/>
+      <c r="Z19" s="30" t="n"/>
+      <c r="AA19" s="30" t="n"/>
+      <c r="AB19" s="30" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="17" t="n">
@@ -2964,6 +3146,9 @@
       <c r="W20" s="19" t="inlineStr"/>
       <c r="X20" s="19" t="inlineStr"/>
       <c r="Y20" s="19" t="inlineStr"/>
+      <c r="Z20" s="30" t="n"/>
+      <c r="AA20" s="30" t="n"/>
+      <c r="AB20" s="30" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="17" t="n">
@@ -2997,6 +3182,9 @@
       <c r="W21" s="19" t="inlineStr"/>
       <c r="X21" s="19" t="inlineStr"/>
       <c r="Y21" s="19" t="inlineStr"/>
+      <c r="Z21" s="30" t="n"/>
+      <c r="AA21" s="30" t="n"/>
+      <c r="AB21" s="30" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="17" t="n">
@@ -3030,6 +3218,9 @@
       <c r="W22" s="19" t="inlineStr"/>
       <c r="X22" s="19" t="inlineStr"/>
       <c r="Y22" s="19" t="inlineStr"/>
+      <c r="Z22" s="30" t="n"/>
+      <c r="AA22" s="30" t="n"/>
+      <c r="AB22" s="30" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="17" t="n">
@@ -3063,6 +3254,9 @@
       <c r="W23" s="19" t="inlineStr"/>
       <c r="X23" s="19" t="inlineStr"/>
       <c r="Y23" s="19" t="inlineStr"/>
+      <c r="Z23" s="30" t="n"/>
+      <c r="AA23" s="30" t="n"/>
+      <c r="AB23" s="30" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="17" t="n">
@@ -3096,6 +3290,9 @@
       <c r="W24" s="19" t="inlineStr"/>
       <c r="X24" s="19" t="inlineStr"/>
       <c r="Y24" s="19" t="inlineStr"/>
+      <c r="Z24" s="30" t="n"/>
+      <c r="AA24" s="30" t="n"/>
+      <c r="AB24" s="30" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="17" t="n">
@@ -3129,6 +3326,9 @@
       <c r="W25" s="19" t="inlineStr"/>
       <c r="X25" s="19" t="inlineStr"/>
       <c r="Y25" s="19" t="inlineStr"/>
+      <c r="Z25" s="30" t="n"/>
+      <c r="AA25" s="30" t="n"/>
+      <c r="AB25" s="30" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="17" t="n">
@@ -3162,6 +3362,9 @@
       <c r="W26" s="19" t="inlineStr"/>
       <c r="X26" s="19" t="inlineStr"/>
       <c r="Y26" s="19" t="inlineStr"/>
+      <c r="Z26" s="30" t="n"/>
+      <c r="AA26" s="30" t="n"/>
+      <c r="AB26" s="30" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="17" t="n">
@@ -3195,6 +3398,9 @@
       <c r="W27" s="19" t="inlineStr"/>
       <c r="X27" s="19" t="inlineStr"/>
       <c r="Y27" s="19" t="inlineStr"/>
+      <c r="Z27" s="30" t="n"/>
+      <c r="AA27" s="30" t="n"/>
+      <c r="AB27" s="30" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="17" t="n">
@@ -3228,6 +3434,9 @@
       <c r="W28" s="19" t="inlineStr"/>
       <c r="X28" s="19" t="inlineStr"/>
       <c r="Y28" s="19" t="inlineStr"/>
+      <c r="Z28" s="30" t="n"/>
+      <c r="AA28" s="30" t="n"/>
+      <c r="AB28" s="30" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="17" t="n">
@@ -3261,6 +3470,9 @@
       <c r="W29" s="19" t="inlineStr"/>
       <c r="X29" s="19" t="inlineStr"/>
       <c r="Y29" s="19" t="inlineStr"/>
+      <c r="Z29" s="30" t="n"/>
+      <c r="AA29" s="30" t="n"/>
+      <c r="AB29" s="30" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="17" t="n">
@@ -3294,6 +3506,9 @@
       <c r="W30" s="19" t="inlineStr"/>
       <c r="X30" s="19" t="inlineStr"/>
       <c r="Y30" s="19" t="inlineStr"/>
+      <c r="Z30" s="30" t="n"/>
+      <c r="AA30" s="30" t="n"/>
+      <c r="AB30" s="30" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="17" t="n">
@@ -3327,6 +3542,9 @@
       <c r="W31" s="19" t="inlineStr"/>
       <c r="X31" s="19" t="inlineStr"/>
       <c r="Y31" s="19" t="inlineStr"/>
+      <c r="Z31" s="30" t="n"/>
+      <c r="AA31" s="30" t="n"/>
+      <c r="AB31" s="30" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="17" t="n">
@@ -3360,6 +3578,9 @@
       <c r="W32" s="19" t="inlineStr"/>
       <c r="X32" s="19" t="inlineStr"/>
       <c r="Y32" s="19" t="inlineStr"/>
+      <c r="Z32" s="30" t="n"/>
+      <c r="AA32" s="30" t="n"/>
+      <c r="AB32" s="30" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="17" t="n">
@@ -3393,6 +3614,9 @@
       <c r="W33" s="19" t="inlineStr"/>
       <c r="X33" s="19" t="inlineStr"/>
       <c r="Y33" s="19" t="inlineStr"/>
+      <c r="Z33" s="30" t="n"/>
+      <c r="AA33" s="30" t="n"/>
+      <c r="AB33" s="30" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="17" t="n">
@@ -3426,6 +3650,9 @@
       <c r="W34" s="19" t="inlineStr"/>
       <c r="X34" s="19" t="inlineStr"/>
       <c r="Y34" s="19" t="inlineStr"/>
+      <c r="Z34" s="30" t="n"/>
+      <c r="AA34" s="30" t="n"/>
+      <c r="AB34" s="30" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="17" t="n">
@@ -3459,6 +3686,9 @@
       <c r="W35" s="19" t="inlineStr"/>
       <c r="X35" s="19" t="inlineStr"/>
       <c r="Y35" s="19" t="inlineStr"/>
+      <c r="Z35" s="30" t="n"/>
+      <c r="AA35" s="30" t="n"/>
+      <c r="AB35" s="30" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="17" t="n">
@@ -3492,6 +3722,9 @@
       <c r="W36" s="19" t="inlineStr"/>
       <c r="X36" s="19" t="inlineStr"/>
       <c r="Y36" s="19" t="inlineStr"/>
+      <c r="Z36" s="30" t="n"/>
+      <c r="AA36" s="30" t="n"/>
+      <c r="AB36" s="30" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="17" t="n">
@@ -3525,6 +3758,9 @@
       <c r="W37" s="19" t="inlineStr"/>
       <c r="X37" s="19" t="inlineStr"/>
       <c r="Y37" s="19" t="inlineStr"/>
+      <c r="Z37" s="30" t="n"/>
+      <c r="AA37" s="30" t="n"/>
+      <c r="AB37" s="30" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="17" t="n">
@@ -3558,6 +3794,9 @@
       <c r="W38" s="19" t="inlineStr"/>
       <c r="X38" s="19" t="inlineStr"/>
       <c r="Y38" s="19" t="inlineStr"/>
+      <c r="Z38" s="30" t="n"/>
+      <c r="AA38" s="30" t="n"/>
+      <c r="AB38" s="30" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="17" t="n">
@@ -3591,6 +3830,9 @@
       <c r="W39" s="19" t="inlineStr"/>
       <c r="X39" s="19" t="inlineStr"/>
       <c r="Y39" s="19" t="inlineStr"/>
+      <c r="Z39" s="30" t="n"/>
+      <c r="AA39" s="30" t="n"/>
+      <c r="AB39" s="30" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="17" t="n">
@@ -3624,6 +3866,9 @@
       <c r="W40" s="19" t="inlineStr"/>
       <c r="X40" s="19" t="inlineStr"/>
       <c r="Y40" s="19" t="inlineStr"/>
+      <c r="Z40" s="30" t="n"/>
+      <c r="AA40" s="30" t="n"/>
+      <c r="AB40" s="30" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="17" t="n">
@@ -3657,6 +3902,9 @@
       <c r="W41" s="19" t="inlineStr"/>
       <c r="X41" s="19" t="inlineStr"/>
       <c r="Y41" s="19" t="inlineStr"/>
+      <c r="Z41" s="30" t="n"/>
+      <c r="AA41" s="30" t="n"/>
+      <c r="AB41" s="30" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="17" t="n">
@@ -3690,6 +3938,9 @@
       <c r="W42" s="19" t="inlineStr"/>
       <c r="X42" s="19" t="inlineStr"/>
       <c r="Y42" s="19" t="inlineStr"/>
+      <c r="Z42" s="30" t="n"/>
+      <c r="AA42" s="30" t="n"/>
+      <c r="AB42" s="30" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="17" t="n">
@@ -3723,6 +3974,9 @@
       <c r="W43" s="19" t="inlineStr"/>
       <c r="X43" s="19" t="inlineStr"/>
       <c r="Y43" s="19" t="inlineStr"/>
+      <c r="Z43" s="30" t="n"/>
+      <c r="AA43" s="30" t="n"/>
+      <c r="AB43" s="30" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="17" t="n">
@@ -3756,6 +4010,9 @@
       <c r="W44" s="19" t="inlineStr"/>
       <c r="X44" s="19" t="inlineStr"/>
       <c r="Y44" s="19" t="inlineStr"/>
+      <c r="Z44" s="30" t="n"/>
+      <c r="AA44" s="30" t="n"/>
+      <c r="AB44" s="30" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="17" t="n">
@@ -3789,6 +4046,9 @@
       <c r="W45" s="19" t="inlineStr"/>
       <c r="X45" s="19" t="inlineStr"/>
       <c r="Y45" s="19" t="inlineStr"/>
+      <c r="Z45" s="30" t="n"/>
+      <c r="AA45" s="30" t="n"/>
+      <c r="AB45" s="30" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="17" t="n">
@@ -3822,6 +4082,9 @@
       <c r="W46" s="19" t="inlineStr"/>
       <c r="X46" s="19" t="inlineStr"/>
       <c r="Y46" s="19" t="inlineStr"/>
+      <c r="Z46" s="30" t="n"/>
+      <c r="AA46" s="30" t="n"/>
+      <c r="AB46" s="30" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="17" t="n">
@@ -3855,6 +4118,9 @@
       <c r="W47" s="19" t="inlineStr"/>
       <c r="X47" s="19" t="inlineStr"/>
       <c r="Y47" s="19" t="inlineStr"/>
+      <c r="Z47" s="30" t="n"/>
+      <c r="AA47" s="30" t="n"/>
+      <c r="AB47" s="30" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="17" t="n">
@@ -3888,6 +4154,9 @@
       <c r="W48" s="19" t="inlineStr"/>
       <c r="X48" s="19" t="inlineStr"/>
       <c r="Y48" s="19" t="inlineStr"/>
+      <c r="Z48" s="30" t="n"/>
+      <c r="AA48" s="30" t="n"/>
+      <c r="AB48" s="30" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="17" t="n">
@@ -3921,6 +4190,9 @@
       <c r="W49" s="19" t="inlineStr"/>
       <c r="X49" s="19" t="inlineStr"/>
       <c r="Y49" s="19" t="inlineStr"/>
+      <c r="Z49" s="30" t="n"/>
+      <c r="AA49" s="30" t="n"/>
+      <c r="AB49" s="30" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="17" t="n">
@@ -3954,6 +4226,9 @@
       <c r="W50" s="19" t="inlineStr"/>
       <c r="X50" s="19" t="inlineStr"/>
       <c r="Y50" s="19" t="inlineStr"/>
+      <c r="Z50" s="30" t="n"/>
+      <c r="AA50" s="30" t="n"/>
+      <c r="AB50" s="30" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="17" t="n">
@@ -3987,6 +4262,9 @@
       <c r="W51" s="19" t="inlineStr"/>
       <c r="X51" s="19" t="inlineStr"/>
       <c r="Y51" s="19" t="inlineStr"/>
+      <c r="Z51" s="30" t="n"/>
+      <c r="AA51" s="30" t="n"/>
+      <c r="AB51" s="30" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="17" t="n">
@@ -4020,6 +4298,9 @@
       <c r="W52" s="19" t="inlineStr"/>
       <c r="X52" s="19" t="inlineStr"/>
       <c r="Y52" s="19" t="inlineStr"/>
+      <c r="Z52" s="30" t="n"/>
+      <c r="AA52" s="30" t="n"/>
+      <c r="AB52" s="30" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="17" t="n">
@@ -4053,6 +4334,9 @@
       <c r="W53" s="19" t="inlineStr"/>
       <c r="X53" s="19" t="inlineStr"/>
       <c r="Y53" s="19" t="inlineStr"/>
+      <c r="Z53" s="30" t="n"/>
+      <c r="AA53" s="30" t="n"/>
+      <c r="AB53" s="30" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="17" t="n">
@@ -4086,6 +4370,9 @@
       <c r="W54" s="19" t="inlineStr"/>
       <c r="X54" s="19" t="inlineStr"/>
       <c r="Y54" s="19" t="inlineStr"/>
+      <c r="Z54" s="30" t="n"/>
+      <c r="AA54" s="30" t="n"/>
+      <c r="AB54" s="30" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="17" t="n">
@@ -4119,6 +4406,9 @@
       <c r="W55" s="19" t="inlineStr"/>
       <c r="X55" s="19" t="inlineStr"/>
       <c r="Y55" s="19" t="inlineStr"/>
+      <c r="Z55" s="30" t="n"/>
+      <c r="AA55" s="30" t="n"/>
+      <c r="AB55" s="30" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="17" t="n">
@@ -4152,6 +4442,9 @@
       <c r="W56" s="19" t="inlineStr"/>
       <c r="X56" s="19" t="inlineStr"/>
       <c r="Y56" s="19" t="inlineStr"/>
+      <c r="Z56" s="30" t="n"/>
+      <c r="AA56" s="30" t="n"/>
+      <c r="AB56" s="30" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="17" t="n">
@@ -4185,6 +4478,9 @@
       <c r="W57" s="19" t="inlineStr"/>
       <c r="X57" s="19" t="inlineStr"/>
       <c r="Y57" s="19" t="inlineStr"/>
+      <c r="Z57" s="30" t="n"/>
+      <c r="AA57" s="30" t="n"/>
+      <c r="AB57" s="30" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="17" t="n">
@@ -4218,6 +4514,9 @@
       <c r="W58" s="19" t="inlineStr"/>
       <c r="X58" s="19" t="inlineStr"/>
       <c r="Y58" s="19" t="inlineStr"/>
+      <c r="Z58" s="30" t="n"/>
+      <c r="AA58" s="30" t="n"/>
+      <c r="AB58" s="30" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="17" t="n">
@@ -4255,6 +4554,9 @@
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
+      <c r="Z59" s="30" t="n"/>
+      <c r="AA59" s="30" t="n"/>
+      <c r="AB59" s="30" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="17" t="n">
@@ -4288,6 +4590,9 @@
       <c r="W60" s="19" t="inlineStr"/>
       <c r="X60" s="19" t="inlineStr"/>
       <c r="Y60" s="19" t="inlineStr"/>
+      <c r="Z60" s="30" t="n"/>
+      <c r="AA60" s="30" t="n"/>
+      <c r="AB60" s="30" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="17" t="n">
@@ -4321,6 +4626,9 @@
       <c r="W61" s="19" t="inlineStr"/>
       <c r="X61" s="19" t="inlineStr"/>
       <c r="Y61" s="19" t="inlineStr"/>
+      <c r="Z61" s="30" t="n"/>
+      <c r="AA61" s="30" t="n"/>
+      <c r="AB61" s="30" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="17" t="n">
@@ -4358,6 +4666,9 @@
           <t>Missing — 2 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
+      <c r="Z62" s="30" t="n"/>
+      <c r="AA62" s="30" t="n"/>
+      <c r="AB62" s="30" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="17" t="n">
@@ -4391,6 +4702,9 @@
       <c r="W63" s="19" t="inlineStr"/>
       <c r="X63" s="19" t="inlineStr"/>
       <c r="Y63" s="19" t="inlineStr"/>
+      <c r="Z63" s="30" t="n"/>
+      <c r="AA63" s="30" t="n"/>
+      <c r="AB63" s="30" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="17" t="n">
@@ -4424,6 +4738,13 @@
       <c r="W64" s="19" t="inlineStr"/>
       <c r="X64" s="19" t="inlineStr"/>
       <c r="Y64" s="19" t="inlineStr"/>
+      <c r="Z64" s="30" t="n"/>
+      <c r="AA64" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
+      <c r="AB64" s="30" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="17" t="n">
@@ -4457,6 +4778,9 @@
       <c r="W65" s="19" t="inlineStr"/>
       <c r="X65" s="19" t="inlineStr"/>
       <c r="Y65" s="19" t="inlineStr"/>
+      <c r="Z65" s="30" t="n"/>
+      <c r="AA65" s="30" t="n"/>
+      <c r="AB65" s="30" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="17" t="n">
@@ -4494,6 +4818,13 @@
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
+      <c r="Z66" s="30" t="n"/>
+      <c r="AA66" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
+      <c r="AB66" s="30" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="17" t="n">
@@ -4527,6 +4858,9 @@
       <c r="W67" s="19" t="inlineStr"/>
       <c r="X67" s="19" t="inlineStr"/>
       <c r="Y67" s="19" t="inlineStr"/>
+      <c r="Z67" s="30" t="n"/>
+      <c r="AA67" s="30" t="n"/>
+      <c r="AB67" s="30" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="17" t="n">
@@ -4560,6 +4894,9 @@
       <c r="W68" s="19" t="inlineStr"/>
       <c r="X68" s="19" t="inlineStr"/>
       <c r="Y68" s="19" t="inlineStr"/>
+      <c r="Z68" s="30" t="n"/>
+      <c r="AA68" s="30" t="n"/>
+      <c r="AB68" s="30" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="17" t="n">
@@ -4601,6 +4938,9 @@
         </is>
       </c>
       <c r="Y69" s="19" t="inlineStr"/>
+      <c r="Z69" s="30" t="n"/>
+      <c r="AA69" s="30" t="n"/>
+      <c r="AB69" s="30" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="17" t="n">
@@ -4642,6 +4982,9 @@
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
+      <c r="Z70" s="30" t="n"/>
+      <c r="AA70" s="30" t="n"/>
+      <c r="AB70" s="30" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="17" t="n">
@@ -4683,6 +5026,13 @@
       <c r="W71" s="19" t="inlineStr"/>
       <c r="X71" s="19" t="inlineStr"/>
       <c r="Y71" s="19" t="inlineStr"/>
+      <c r="Z71" s="30" t="n"/>
+      <c r="AA71" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
+      <c r="AB71" s="30" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="17" t="n">
@@ -4720,6 +5070,9 @@
       <c r="W72" s="19" t="inlineStr"/>
       <c r="X72" s="19" t="inlineStr"/>
       <c r="Y72" s="19" t="inlineStr"/>
+      <c r="Z72" s="30" t="n"/>
+      <c r="AA72" s="30" t="n"/>
+      <c r="AB72" s="30" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="17" t="n">
@@ -4761,6 +5114,9 @@
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
+      <c r="Z73" s="30" t="n"/>
+      <c r="AA73" s="30" t="n"/>
+      <c r="AB73" s="30" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="17" t="n">
@@ -4798,6 +5154,13 @@
       <c r="W74" s="19" t="inlineStr"/>
       <c r="X74" s="19" t="inlineStr"/>
       <c r="Y74" s="19" t="inlineStr"/>
+      <c r="Z74" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
+      <c r="AA74" s="30" t="n"/>
+      <c r="AB74" s="30" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="17" t="n">
@@ -4835,6 +5198,9 @@
       <c r="W75" s="19" t="inlineStr"/>
       <c r="X75" s="19" t="inlineStr"/>
       <c r="Y75" s="19" t="inlineStr"/>
+      <c r="Z75" s="30" t="n"/>
+      <c r="AA75" s="30" t="n"/>
+      <c r="AB75" s="30" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="17" t="n">
@@ -4872,6 +5238,9 @@
       <c r="W76" s="19" t="inlineStr"/>
       <c r="X76" s="19" t="inlineStr"/>
       <c r="Y76" s="19" t="inlineStr"/>
+      <c r="Z76" s="30" t="n"/>
+      <c r="AA76" s="30" t="n"/>
+      <c r="AB76" s="30" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="17" t="n">
@@ -4909,6 +5278,13 @@
       <c r="W77" s="19" t="inlineStr"/>
       <c r="X77" s="19" t="inlineStr"/>
       <c r="Y77" s="19" t="inlineStr"/>
+      <c r="Z77" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
+      <c r="AA77" s="30" t="n"/>
+      <c r="AB77" s="30" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="17" t="n">
@@ -4946,6 +5322,13 @@
       <c r="W78" s="19" t="inlineStr"/>
       <c r="X78" s="19" t="inlineStr"/>
       <c r="Y78" s="19" t="inlineStr"/>
+      <c r="Z78" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
+      <c r="AA78" s="30" t="n"/>
+      <c r="AB78" s="30" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="17" t="n">
@@ -4991,6 +5374,13 @@
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
+      <c r="Z79" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 2 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
+      <c r="AA79" s="30" t="n"/>
+      <c r="AB79" s="30" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="17" t="n">
@@ -5032,6 +5422,13 @@
           <t>?; Missing — 2 abstracts cited by the corpus</t>
         </is>
       </c>
+      <c r="Z80" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
+      <c r="AA80" s="30" t="n"/>
+      <c r="AB80" s="30" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="17" t="n">
@@ -5069,6 +5466,13 @@
       <c r="W81" s="19" t="inlineStr"/>
       <c r="X81" s="19" t="inlineStr"/>
       <c r="Y81" s="19" t="inlineStr"/>
+      <c r="Z81" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 2 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
+      <c r="AA81" s="30" t="n"/>
+      <c r="AB81" s="30" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="17" t="n">
@@ -5106,6 +5510,13 @@
       <c r="W82" s="19" t="inlineStr"/>
       <c r="X82" s="19" t="inlineStr"/>
       <c r="Y82" s="19" t="inlineStr"/>
+      <c r="Z82" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 2 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
+      <c r="AA82" s="30" t="n"/>
+      <c r="AB82" s="30" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="17" t="n">
@@ -5159,6 +5570,13 @@
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
+      <c r="Z83" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 2 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
+      <c r="AA83" s="30" t="n"/>
+      <c r="AB83" s="30" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="17" t="n">
@@ -5166,7 +5584,7 @@
       </c>
       <c r="B84" s="20" t="inlineStr">
         <is>
-          <t>Guelph, ON; Ingested</t>
+          <t>Guelph, ON; Ingested — Fable-merged 2026-09-17</t>
         </is>
       </c>
       <c r="C84" s="20" t="inlineStr">
@@ -5200,6 +5618,13 @@
       <c r="W84" s="19" t="inlineStr"/>
       <c r="X84" s="19" t="inlineStr"/>
       <c r="Y84" s="19" t="inlineStr"/>
+      <c r="Z84" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 2 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
+      <c r="AA84" s="30" t="n"/>
+      <c r="AB84" s="30" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="17" t="n">
@@ -5241,6 +5666,17 @@
       <c r="W85" s="19" t="inlineStr"/>
       <c r="X85" s="19" t="inlineStr"/>
       <c r="Y85" s="19" t="inlineStr"/>
+      <c r="Z85" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 4 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
+      <c r="AA85" s="30" t="n"/>
+      <c r="AB85" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="17" t="n">
@@ -5286,6 +5722,13 @@
           <t>Missing — 3 abstracts cited by the corpus [3 distinct meetings]</t>
         </is>
       </c>
+      <c r="Z86" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 4 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
+      <c r="AA86" s="30" t="n"/>
+      <c r="AB86" s="30" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="17" t="n">
@@ -5331,6 +5774,9 @@
       <c r="W87" s="19" t="inlineStr"/>
       <c r="X87" s="19" t="inlineStr"/>
       <c r="Y87" s="19" t="inlineStr"/>
+      <c r="Z87" s="30" t="n"/>
+      <c r="AA87" s="30" t="n"/>
+      <c r="AB87" s="30" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="17" t="n">
@@ -5380,6 +5826,13 @@
           <t>Missing — 7 abstracts cited by the corpus [6 distinct meetings]</t>
         </is>
       </c>
+      <c r="Z88" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 4 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
+      <c r="AA88" s="30" t="n"/>
+      <c r="AB88" s="30" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="17" t="n">
@@ -5425,6 +5878,13 @@
           <t>Missing — 4 abstracts cited by the corpus [4 distinct meetings; Published 2006]</t>
         </is>
       </c>
+      <c r="Z89" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 2 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
+      <c r="AA89" s="30" t="n"/>
+      <c r="AB89" s="30" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="17" t="n">
@@ -5449,9 +5909,9 @@
       <c r="F90" s="19" t="inlineStr"/>
       <c r="G90" s="19" t="inlineStr"/>
       <c r="H90" s="19" t="inlineStr"/>
-      <c r="I90" s="23" t="inlineStr">
-        <is>
-          <t>Ciudad Universitaria, Mexico City; Digital — 1 PDF held — extraction pending</t>
+      <c r="I90" s="20" t="inlineStr">
+        <is>
+          <t>Ciudad Universitaria, Mexico City; Ingested — Fable extraction 2026-09-17, 44 abstracts</t>
         </is>
       </c>
       <c r="J90" s="19" t="inlineStr"/>
@@ -5482,6 +5942,9 @@
           <t>Missing — 2 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
+      <c r="Z90" s="30" t="n"/>
+      <c r="AA90" s="30" t="n"/>
+      <c r="AB90" s="30" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="17" t="n">
@@ -5489,7 +5952,7 @@
       </c>
       <c r="B91" s="20" t="inlineStr">
         <is>
-          <t>Tampa, FL; Ingested</t>
+          <t>Tampa, FL; Ingested — Fable-merged 2026-09-17</t>
         </is>
       </c>
       <c r="C91" s="20" t="inlineStr">
@@ -5531,6 +5994,13 @@
           <t>Missing — 2 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
+      <c r="Z91" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
+      <c r="AA91" s="30" t="n"/>
+      <c r="AB91" s="30" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="17" t="n">
@@ -5580,6 +6050,17 @@
           <t>Missing — 5 abstracts cited by the corpus [5 distinct meetings; Published 2007]</t>
         </is>
       </c>
+      <c r="Z92" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 3 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
+      <c r="AA92" s="30" t="n"/>
+      <c r="AB92" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 4 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="17" t="n">
@@ -5637,6 +6118,17 @@
           <t>Missing — 3 abstracts cited by the corpus [3 distinct meetings]</t>
         </is>
       </c>
+      <c r="Z93" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
+      <c r="AA93" s="30" t="n"/>
+      <c r="AB93" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 3 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="17" t="n">
@@ -5665,9 +6157,9 @@
       <c r="F94" s="19" t="inlineStr"/>
       <c r="G94" s="19" t="inlineStr"/>
       <c r="H94" s="19" t="inlineStr"/>
-      <c r="I94" s="23" t="inlineStr">
-        <is>
-          <t>Ciudad Universitaria, Mexico City; Digital — 1 PDF held — extraction pending</t>
+      <c r="I94" s="20" t="inlineStr">
+        <is>
+          <t>Ciudad Universitaria, Mexico City; Ingested — Fable extraction 2026-09-17, 58 abstracts</t>
         </is>
       </c>
       <c r="J94" s="19" t="inlineStr"/>
@@ -5690,6 +6182,17 @@
           <t>Missing — 6 abstracts cited by the corpus [6 distinct meetings]</t>
         </is>
       </c>
+      <c r="Z94" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
+      <c r="AA94" s="30" t="n"/>
+      <c r="AB94" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 2 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="17" t="n">
@@ -5726,7 +6229,7 @@
       <c r="N95" s="19" t="inlineStr"/>
       <c r="O95" s="25" t="inlineStr">
         <is>
-          <t>Fremantle, WA, Australia; Partial — 416 abstracts, elasmo-targeted pages only (teleost content not captured)</t>
+          <t>Fremantle, WA, Australia; Partial — 389 abstracts, elasmo-targeted pages only (teleost content not captured)</t>
         </is>
       </c>
       <c r="P95" s="19" t="inlineStr"/>
@@ -5747,6 +6250,17 @@
           <t>Missing — 3 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
+      <c r="Z95" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 17 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
+      <c r="AA95" s="30" t="n"/>
+      <c r="AB95" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 2 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="17" t="n">
@@ -5775,9 +6289,9 @@
       </c>
       <c r="G96" s="19" t="inlineStr"/>
       <c r="H96" s="19" t="inlineStr"/>
-      <c r="I96" s="23" t="inlineStr">
-        <is>
-          <t>Ciudad Universitaria, Mexico City; Digital — 1 PDF held — extraction pending</t>
+      <c r="I96" s="20" t="inlineStr">
+        <is>
+          <t>Ciudad Universitaria, Mexico City; Ingested — Fable extraction 2026-09-17, 61 abstracts</t>
         </is>
       </c>
       <c r="J96" s="19" t="inlineStr"/>
@@ -5804,6 +6318,13 @@
           <t>Missing — 3 abstracts cited by the corpus [3 distinct meetings]</t>
         </is>
       </c>
+      <c r="Z96" s="30" t="n"/>
+      <c r="AA96" s="30" t="n"/>
+      <c r="AB96" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 4 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="17" t="n">
@@ -5863,6 +6384,17 @@
       <c r="Y97" s="18" t="inlineStr">
         <is>
           <t>Missing — 9 abstracts cited by the corpus [5 distinct meetings]</t>
+        </is>
+      </c>
+      <c r="Z97" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 2 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
+      <c r="AA97" s="30" t="n"/>
+      <c r="AB97" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
     </row>
@@ -5934,6 +6466,21 @@
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
+      <c r="Z98" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 3 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
+      <c r="AA98" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 6 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
+      <c r="AB98" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 2 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="17" t="n">
@@ -5989,6 +6536,17 @@
       <c r="Y99" s="18" t="inlineStr">
         <is>
           <t>Missing — 2 abstracts cited by the corpus [2 distinct meetings]</t>
+        </is>
+      </c>
+      <c r="Z99" s="30" t="n"/>
+      <c r="AA99" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 16 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
+      <c r="AB99" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
     </row>
@@ -6054,6 +6612,17 @@
       <c r="Y100" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
+        </is>
+      </c>
+      <c r="Z100" s="30" t="n"/>
+      <c r="AA100" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 13 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
+      <c r="AB100" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
     </row>
@@ -6105,6 +6674,17 @@
           <t>Missing — 4 abstracts cited by the corpus [3 distinct meetings]</t>
         </is>
       </c>
+      <c r="Z101" s="30" t="n"/>
+      <c r="AA101" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 3 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
+      <c r="AB101" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 3 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="17" t="n">
@@ -6133,9 +6713,9 @@
       <c r="F102" s="19" t="inlineStr"/>
       <c r="G102" s="19" t="inlineStr"/>
       <c r="H102" s="19" t="inlineStr"/>
-      <c r="I102" s="23" t="inlineStr">
-        <is>
-          <t>Puerto Vallarta, Jalisco, Mexico; Digital — 1 PDF held — extraction pending</t>
+      <c r="I102" s="20" t="inlineStr">
+        <is>
+          <t>Puerto Vallarta, Jalisco, Mexico; Ingested — Fable extraction 2026-09-17, 55 abstracts</t>
         </is>
       </c>
       <c r="J102" s="19" t="inlineStr"/>
@@ -6158,6 +6738,9 @@
           <t>Missing — 3 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
+      <c r="Z102" s="30" t="n"/>
+      <c r="AA102" s="30" t="n"/>
+      <c r="AB102" s="30" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="17" t="n">
@@ -6203,6 +6786,9 @@
           <t>?; Missing — 1 abstract cited by the corpus [Published 2018]</t>
         </is>
       </c>
+      <c r="Z103" s="30" t="n"/>
+      <c r="AA103" s="30" t="n"/>
+      <c r="AB103" s="30" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="17" t="n">
@@ -6256,6 +6842,9 @@
           <t>Missing — 3 abstracts cited by the corpus [3 distinct meetings]</t>
         </is>
       </c>
+      <c r="Z104" s="30" t="n"/>
+      <c r="AA104" s="30" t="n"/>
+      <c r="AB104" s="30" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="17" t="n">
@@ -6305,6 +6894,9 @@
       <c r="W105" s="19" t="inlineStr"/>
       <c r="X105" s="19" t="inlineStr"/>
       <c r="Y105" s="19" t="inlineStr"/>
+      <c r="Z105" s="30" t="n"/>
+      <c r="AA105" s="30" t="n"/>
+      <c r="AB105" s="30" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="17" t="n">
@@ -6354,6 +6946,13 @@
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
+      <c r="Z106" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
+        </is>
+      </c>
+      <c r="AA106" s="30" t="n"/>
+      <c r="AB106" s="30" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="17" t="n">
@@ -6403,6 +7002,9 @@
           <t>Missing — 2 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
+      <c r="Z107" s="30" t="n"/>
+      <c r="AA107" s="30" t="n"/>
+      <c r="AB107" s="30" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="17" t="n">
@@ -6456,6 +7058,9 @@
           <t>?; Missing — 2 abstracts cited by the corpus</t>
         </is>
       </c>
+      <c r="Z108" s="30" t="n"/>
+      <c r="AA108" s="30" t="n"/>
+      <c r="AB108" s="30" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="17" t="n">
@@ -6509,6 +7114,9 @@
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
+      <c r="Z109" s="30" t="n"/>
+      <c r="AA109" s="30" t="n"/>
+      <c r="AB109" s="30" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="17" t="n">
@@ -6554,6 +7162,9 @@
       <c r="W110" s="19" t="inlineStr"/>
       <c r="X110" s="19" t="inlineStr"/>
       <c r="Y110" s="19" t="inlineStr"/>
+      <c r="Z110" s="30" t="n"/>
+      <c r="AA110" s="30" t="n"/>
+      <c r="AB110" s="30" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="17" t="n">
@@ -6582,9 +7193,9 @@
       <c r="F111" s="19" t="inlineStr"/>
       <c r="G111" s="19" t="inlineStr"/>
       <c r="H111" s="19" t="inlineStr"/>
-      <c r="I111" s="23" t="inlineStr">
-        <is>
-          <t>Ensenada, Baja California, Mexico; Digital — 1 PDF held — extraction pending</t>
+      <c r="I111" s="20" t="inlineStr">
+        <is>
+          <t>Ensenada, Baja California, Mexico; Ingested — Fable extraction 2026-09-17, 104 abstracts</t>
         </is>
       </c>
       <c r="J111" s="19" t="inlineStr"/>
@@ -6607,6 +7218,9 @@
           <t>?; Missing — 3 abstracts cited by the corpus</t>
         </is>
       </c>
+      <c r="Z111" s="30" t="n"/>
+      <c r="AA111" s="30" t="n"/>
+      <c r="AB111" s="30" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="17" t="n">
@@ -6656,6 +7270,9 @@
       <c r="W112" s="19" t="inlineStr"/>
       <c r="X112" s="19" t="inlineStr"/>
       <c r="Y112" s="19" t="inlineStr"/>
+      <c r="Z112" s="30" t="n"/>
+      <c r="AA112" s="30" t="n"/>
+      <c r="AB112" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/database/conference_coverage_matrix.xlsx
+++ b/database/conference_coverage_matrix.xlsx
@@ -2257,7 +2257,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
@@ -7236,9 +7235,9 @@
           <t>New Orleans, LA (235); Extracted — regex-parsed; Fable re-extraction queued</t>
         </is>
       </c>
-      <c r="D112" s="24" t="inlineStr">
-        <is>
-          <t>online; Pending — will be digital (Shark Trust hosting)</t>
+      <c r="D112" s="20" t="inlineStr">
+        <is>
+          <t>online; Ingested — 83 abstracts (local parser anchored on the booklet's own agenda, 2026-10-07); the agenda lists 84 talks, Kingma's has no abstract printed</t>
         </is>
       </c>
       <c r="E112" s="24" t="inlineStr">
@@ -8244,7 +8243,7 @@
         <v>7</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H38" t="n">
         <v>1000</v>
@@ -8272,7 +8271,7 @@
         <v>161</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>956</v>
+        <v>1039</v>
       </c>
       <c r="H39" s="1" t="n">
         <v>1749</v>
@@ -8323,13 +8322,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C44" t="n">
         <v>30</v>
       </c>
       <c r="D44" t="n">
-        <v>26.7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45">

--- a/database/conference_coverage_matrix.xlsx
+++ b/database/conference_coverage_matrix.xlsx
@@ -5733,9 +5733,9 @@
       <c r="A87" s="17" t="n">
         <v>2001</v>
       </c>
-      <c r="B87" s="22" t="inlineStr">
-        <is>
-          <t>University Park, PA; OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
+      <c r="B87" s="20" t="inlineStr">
+        <is>
+          <t>University Park, PA; Ingested — flatbed rescan (Carylanne, Oct 2026), rules-parsed 2026-10-13, 300 abstracts</t>
         </is>
       </c>
       <c r="C87" s="20" t="inlineStr">

--- a/database/conference_coverage_matrix.xlsx
+++ b/database/conference_coverage_matrix.xlsx
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -198,7 +198,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1743,7 +1742,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
@@ -2005,7 +2004,7 @@
         <v>4</v>
       </c>
       <c r="E20" s="13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
@@ -2139,7 +2138,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
@@ -2497,9 +2496,9 @@
       <c r="W2" s="19" t="inlineStr"/>
       <c r="X2" s="19" t="inlineStr"/>
       <c r="Y2" s="19" t="inlineStr"/>
-      <c r="Z2" s="30" t="n"/>
-      <c r="AA2" s="30" t="n"/>
-      <c r="AB2" s="30" t="n"/>
+      <c r="Z2" s="19" t="inlineStr"/>
+      <c r="AA2" s="19" t="inlineStr"/>
+      <c r="AB2" s="19" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="17" t="n">
@@ -2533,9 +2532,9 @@
       <c r="W3" s="19" t="inlineStr"/>
       <c r="X3" s="19" t="inlineStr"/>
       <c r="Y3" s="19" t="inlineStr"/>
-      <c r="Z3" s="30" t="n"/>
-      <c r="AA3" s="30" t="n"/>
-      <c r="AB3" s="30" t="n"/>
+      <c r="Z3" s="19" t="inlineStr"/>
+      <c r="AA3" s="19" t="inlineStr"/>
+      <c r="AB3" s="19" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="17" t="n">
@@ -2569,9 +2568,9 @@
       <c r="W4" s="19" t="inlineStr"/>
       <c r="X4" s="19" t="inlineStr"/>
       <c r="Y4" s="19" t="inlineStr"/>
-      <c r="Z4" s="30" t="n"/>
-      <c r="AA4" s="30" t="n"/>
-      <c r="AB4" s="30" t="n"/>
+      <c r="Z4" s="19" t="inlineStr"/>
+      <c r="AA4" s="19" t="inlineStr"/>
+      <c r="AB4" s="19" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="17" t="n">
@@ -2605,9 +2604,9 @@
       <c r="W5" s="19" t="inlineStr"/>
       <c r="X5" s="19" t="inlineStr"/>
       <c r="Y5" s="19" t="inlineStr"/>
-      <c r="Z5" s="30" t="n"/>
-      <c r="AA5" s="30" t="n"/>
-      <c r="AB5" s="30" t="n"/>
+      <c r="Z5" s="19" t="inlineStr"/>
+      <c r="AA5" s="19" t="inlineStr"/>
+      <c r="AB5" s="19" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="17" t="n">
@@ -2641,9 +2640,9 @@
       <c r="W6" s="19" t="inlineStr"/>
       <c r="X6" s="19" t="inlineStr"/>
       <c r="Y6" s="19" t="inlineStr"/>
-      <c r="Z6" s="30" t="n"/>
-      <c r="AA6" s="30" t="n"/>
-      <c r="AB6" s="30" t="n"/>
+      <c r="Z6" s="19" t="inlineStr"/>
+      <c r="AA6" s="19" t="inlineStr"/>
+      <c r="AB6" s="19" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="17" t="n">
@@ -2677,9 +2676,9 @@
       <c r="W7" s="19" t="inlineStr"/>
       <c r="X7" s="19" t="inlineStr"/>
       <c r="Y7" s="19" t="inlineStr"/>
-      <c r="Z7" s="30" t="n"/>
-      <c r="AA7" s="30" t="n"/>
-      <c r="AB7" s="30" t="n"/>
+      <c r="Z7" s="19" t="inlineStr"/>
+      <c r="AA7" s="19" t="inlineStr"/>
+      <c r="AB7" s="19" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="17" t="n">
@@ -2713,9 +2712,9 @@
       <c r="W8" s="19" t="inlineStr"/>
       <c r="X8" s="19" t="inlineStr"/>
       <c r="Y8" s="19" t="inlineStr"/>
-      <c r="Z8" s="30" t="n"/>
-      <c r="AA8" s="30" t="n"/>
-      <c r="AB8" s="30" t="n"/>
+      <c r="Z8" s="19" t="inlineStr"/>
+      <c r="AA8" s="19" t="inlineStr"/>
+      <c r="AB8" s="19" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="17" t="n">
@@ -2749,9 +2748,9 @@
       <c r="W9" s="19" t="inlineStr"/>
       <c r="X9" s="19" t="inlineStr"/>
       <c r="Y9" s="19" t="inlineStr"/>
-      <c r="Z9" s="30" t="n"/>
-      <c r="AA9" s="30" t="n"/>
-      <c r="AB9" s="30" t="n"/>
+      <c r="Z9" s="19" t="inlineStr"/>
+      <c r="AA9" s="19" t="inlineStr"/>
+      <c r="AB9" s="19" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="17" t="n">
@@ -2785,9 +2784,9 @@
       <c r="W10" s="19" t="inlineStr"/>
       <c r="X10" s="19" t="inlineStr"/>
       <c r="Y10" s="19" t="inlineStr"/>
-      <c r="Z10" s="30" t="n"/>
-      <c r="AA10" s="30" t="n"/>
-      <c r="AB10" s="30" t="n"/>
+      <c r="Z10" s="19" t="inlineStr"/>
+      <c r="AA10" s="19" t="inlineStr"/>
+      <c r="AB10" s="19" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="17" t="n">
@@ -2821,9 +2820,9 @@
       <c r="W11" s="19" t="inlineStr"/>
       <c r="X11" s="19" t="inlineStr"/>
       <c r="Y11" s="19" t="inlineStr"/>
-      <c r="Z11" s="30" t="n"/>
-      <c r="AA11" s="30" t="n"/>
-      <c r="AB11" s="30" t="n"/>
+      <c r="Z11" s="19" t="inlineStr"/>
+      <c r="AA11" s="19" t="inlineStr"/>
+      <c r="AB11" s="19" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="17" t="n">
@@ -2857,9 +2856,9 @@
       <c r="W12" s="19" t="inlineStr"/>
       <c r="X12" s="19" t="inlineStr"/>
       <c r="Y12" s="19" t="inlineStr"/>
-      <c r="Z12" s="30" t="n"/>
-      <c r="AA12" s="30" t="n"/>
-      <c r="AB12" s="30" t="n"/>
+      <c r="Z12" s="19" t="inlineStr"/>
+      <c r="AA12" s="19" t="inlineStr"/>
+      <c r="AB12" s="19" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="17" t="n">
@@ -2893,9 +2892,9 @@
       <c r="W13" s="19" t="inlineStr"/>
       <c r="X13" s="19" t="inlineStr"/>
       <c r="Y13" s="19" t="inlineStr"/>
-      <c r="Z13" s="30" t="n"/>
-      <c r="AA13" s="30" t="n"/>
-      <c r="AB13" s="30" t="n"/>
+      <c r="Z13" s="19" t="inlineStr"/>
+      <c r="AA13" s="19" t="inlineStr"/>
+      <c r="AB13" s="19" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="17" t="n">
@@ -2929,9 +2928,9 @@
       <c r="W14" s="19" t="inlineStr"/>
       <c r="X14" s="19" t="inlineStr"/>
       <c r="Y14" s="19" t="inlineStr"/>
-      <c r="Z14" s="30" t="n"/>
-      <c r="AA14" s="30" t="n"/>
-      <c r="AB14" s="30" t="n"/>
+      <c r="Z14" s="19" t="inlineStr"/>
+      <c r="AA14" s="19" t="inlineStr"/>
+      <c r="AB14" s="19" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="17" t="n">
@@ -2965,9 +2964,9 @@
       <c r="W15" s="19" t="inlineStr"/>
       <c r="X15" s="19" t="inlineStr"/>
       <c r="Y15" s="19" t="inlineStr"/>
-      <c r="Z15" s="30" t="n"/>
-      <c r="AA15" s="30" t="n"/>
-      <c r="AB15" s="30" t="n"/>
+      <c r="Z15" s="19" t="inlineStr"/>
+      <c r="AA15" s="19" t="inlineStr"/>
+      <c r="AB15" s="19" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="n">
@@ -3001,9 +3000,9 @@
       <c r="W16" s="19" t="inlineStr"/>
       <c r="X16" s="19" t="inlineStr"/>
       <c r="Y16" s="19" t="inlineStr"/>
-      <c r="Z16" s="30" t="n"/>
-      <c r="AA16" s="30" t="n"/>
-      <c r="AB16" s="30" t="n"/>
+      <c r="Z16" s="19" t="inlineStr"/>
+      <c r="AA16" s="19" t="inlineStr"/>
+      <c r="AB16" s="19" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="17" t="n">
@@ -3037,9 +3036,9 @@
       <c r="W17" s="19" t="inlineStr"/>
       <c r="X17" s="19" t="inlineStr"/>
       <c r="Y17" s="19" t="inlineStr"/>
-      <c r="Z17" s="30" t="n"/>
-      <c r="AA17" s="30" t="n"/>
-      <c r="AB17" s="30" t="n"/>
+      <c r="Z17" s="19" t="inlineStr"/>
+      <c r="AA17" s="19" t="inlineStr"/>
+      <c r="AB17" s="19" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="17" t="n">
@@ -3073,9 +3072,9 @@
       <c r="W18" s="19" t="inlineStr"/>
       <c r="X18" s="19" t="inlineStr"/>
       <c r="Y18" s="19" t="inlineStr"/>
-      <c r="Z18" s="30" t="n"/>
-      <c r="AA18" s="30" t="n"/>
-      <c r="AB18" s="30" t="n"/>
+      <c r="Z18" s="19" t="inlineStr"/>
+      <c r="AA18" s="19" t="inlineStr"/>
+      <c r="AB18" s="19" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="17" t="n">
@@ -3109,9 +3108,9 @@
       <c r="W19" s="19" t="inlineStr"/>
       <c r="X19" s="19" t="inlineStr"/>
       <c r="Y19" s="19" t="inlineStr"/>
-      <c r="Z19" s="30" t="n"/>
-      <c r="AA19" s="30" t="n"/>
-      <c r="AB19" s="30" t="n"/>
+      <c r="Z19" s="19" t="inlineStr"/>
+      <c r="AA19" s="19" t="inlineStr"/>
+      <c r="AB19" s="19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="17" t="n">
@@ -3145,9 +3144,9 @@
       <c r="W20" s="19" t="inlineStr"/>
       <c r="X20" s="19" t="inlineStr"/>
       <c r="Y20" s="19" t="inlineStr"/>
-      <c r="Z20" s="30" t="n"/>
-      <c r="AA20" s="30" t="n"/>
-      <c r="AB20" s="30" t="n"/>
+      <c r="Z20" s="19" t="inlineStr"/>
+      <c r="AA20" s="19" t="inlineStr"/>
+      <c r="AB20" s="19" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="17" t="n">
@@ -3181,9 +3180,9 @@
       <c r="W21" s="19" t="inlineStr"/>
       <c r="X21" s="19" t="inlineStr"/>
       <c r="Y21" s="19" t="inlineStr"/>
-      <c r="Z21" s="30" t="n"/>
-      <c r="AA21" s="30" t="n"/>
-      <c r="AB21" s="30" t="n"/>
+      <c r="Z21" s="19" t="inlineStr"/>
+      <c r="AA21" s="19" t="inlineStr"/>
+      <c r="AB21" s="19" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="17" t="n">
@@ -3217,9 +3216,9 @@
       <c r="W22" s="19" t="inlineStr"/>
       <c r="X22" s="19" t="inlineStr"/>
       <c r="Y22" s="19" t="inlineStr"/>
-      <c r="Z22" s="30" t="n"/>
-      <c r="AA22" s="30" t="n"/>
-      <c r="AB22" s="30" t="n"/>
+      <c r="Z22" s="19" t="inlineStr"/>
+      <c r="AA22" s="19" t="inlineStr"/>
+      <c r="AB22" s="19" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="17" t="n">
@@ -3253,9 +3252,9 @@
       <c r="W23" s="19" t="inlineStr"/>
       <c r="X23" s="19" t="inlineStr"/>
       <c r="Y23" s="19" t="inlineStr"/>
-      <c r="Z23" s="30" t="n"/>
-      <c r="AA23" s="30" t="n"/>
-      <c r="AB23" s="30" t="n"/>
+      <c r="Z23" s="19" t="inlineStr"/>
+      <c r="AA23" s="19" t="inlineStr"/>
+      <c r="AB23" s="19" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="17" t="n">
@@ -3289,9 +3288,9 @@
       <c r="W24" s="19" t="inlineStr"/>
       <c r="X24" s="19" t="inlineStr"/>
       <c r="Y24" s="19" t="inlineStr"/>
-      <c r="Z24" s="30" t="n"/>
-      <c r="AA24" s="30" t="n"/>
-      <c r="AB24" s="30" t="n"/>
+      <c r="Z24" s="19" t="inlineStr"/>
+      <c r="AA24" s="19" t="inlineStr"/>
+      <c r="AB24" s="19" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="17" t="n">
@@ -3325,9 +3324,9 @@
       <c r="W25" s="19" t="inlineStr"/>
       <c r="X25" s="19" t="inlineStr"/>
       <c r="Y25" s="19" t="inlineStr"/>
-      <c r="Z25" s="30" t="n"/>
-      <c r="AA25" s="30" t="n"/>
-      <c r="AB25" s="30" t="n"/>
+      <c r="Z25" s="19" t="inlineStr"/>
+      <c r="AA25" s="19" t="inlineStr"/>
+      <c r="AB25" s="19" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="17" t="n">
@@ -3361,9 +3360,9 @@
       <c r="W26" s="19" t="inlineStr"/>
       <c r="X26" s="19" t="inlineStr"/>
       <c r="Y26" s="19" t="inlineStr"/>
-      <c r="Z26" s="30" t="n"/>
-      <c r="AA26" s="30" t="n"/>
-      <c r="AB26" s="30" t="n"/>
+      <c r="Z26" s="19" t="inlineStr"/>
+      <c r="AA26" s="19" t="inlineStr"/>
+      <c r="AB26" s="19" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="17" t="n">
@@ -3397,9 +3396,9 @@
       <c r="W27" s="19" t="inlineStr"/>
       <c r="X27" s="19" t="inlineStr"/>
       <c r="Y27" s="19" t="inlineStr"/>
-      <c r="Z27" s="30" t="n"/>
-      <c r="AA27" s="30" t="n"/>
-      <c r="AB27" s="30" t="n"/>
+      <c r="Z27" s="19" t="inlineStr"/>
+      <c r="AA27" s="19" t="inlineStr"/>
+      <c r="AB27" s="19" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="17" t="n">
@@ -3433,9 +3432,9 @@
       <c r="W28" s="19" t="inlineStr"/>
       <c r="X28" s="19" t="inlineStr"/>
       <c r="Y28" s="19" t="inlineStr"/>
-      <c r="Z28" s="30" t="n"/>
-      <c r="AA28" s="30" t="n"/>
-      <c r="AB28" s="30" t="n"/>
+      <c r="Z28" s="19" t="inlineStr"/>
+      <c r="AA28" s="19" t="inlineStr"/>
+      <c r="AB28" s="19" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="17" t="n">
@@ -3469,9 +3468,9 @@
       <c r="W29" s="19" t="inlineStr"/>
       <c r="X29" s="19" t="inlineStr"/>
       <c r="Y29" s="19" t="inlineStr"/>
-      <c r="Z29" s="30" t="n"/>
-      <c r="AA29" s="30" t="n"/>
-      <c r="AB29" s="30" t="n"/>
+      <c r="Z29" s="19" t="inlineStr"/>
+      <c r="AA29" s="19" t="inlineStr"/>
+      <c r="AB29" s="19" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="17" t="n">
@@ -3505,9 +3504,9 @@
       <c r="W30" s="19" t="inlineStr"/>
       <c r="X30" s="19" t="inlineStr"/>
       <c r="Y30" s="19" t="inlineStr"/>
-      <c r="Z30" s="30" t="n"/>
-      <c r="AA30" s="30" t="n"/>
-      <c r="AB30" s="30" t="n"/>
+      <c r="Z30" s="19" t="inlineStr"/>
+      <c r="AA30" s="19" t="inlineStr"/>
+      <c r="AB30" s="19" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="17" t="n">
@@ -3541,9 +3540,9 @@
       <c r="W31" s="19" t="inlineStr"/>
       <c r="X31" s="19" t="inlineStr"/>
       <c r="Y31" s="19" t="inlineStr"/>
-      <c r="Z31" s="30" t="n"/>
-      <c r="AA31" s="30" t="n"/>
-      <c r="AB31" s="30" t="n"/>
+      <c r="Z31" s="19" t="inlineStr"/>
+      <c r="AA31" s="19" t="inlineStr"/>
+      <c r="AB31" s="19" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="17" t="n">
@@ -3577,9 +3576,9 @@
       <c r="W32" s="19" t="inlineStr"/>
       <c r="X32" s="19" t="inlineStr"/>
       <c r="Y32" s="19" t="inlineStr"/>
-      <c r="Z32" s="30" t="n"/>
-      <c r="AA32" s="30" t="n"/>
-      <c r="AB32" s="30" t="n"/>
+      <c r="Z32" s="19" t="inlineStr"/>
+      <c r="AA32" s="19" t="inlineStr"/>
+      <c r="AB32" s="19" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="17" t="n">
@@ -3613,9 +3612,9 @@
       <c r="W33" s="19" t="inlineStr"/>
       <c r="X33" s="19" t="inlineStr"/>
       <c r="Y33" s="19" t="inlineStr"/>
-      <c r="Z33" s="30" t="n"/>
-      <c r="AA33" s="30" t="n"/>
-      <c r="AB33" s="30" t="n"/>
+      <c r="Z33" s="19" t="inlineStr"/>
+      <c r="AA33" s="19" t="inlineStr"/>
+      <c r="AB33" s="19" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="17" t="n">
@@ -3649,9 +3648,9 @@
       <c r="W34" s="19" t="inlineStr"/>
       <c r="X34" s="19" t="inlineStr"/>
       <c r="Y34" s="19" t="inlineStr"/>
-      <c r="Z34" s="30" t="n"/>
-      <c r="AA34" s="30" t="n"/>
-      <c r="AB34" s="30" t="n"/>
+      <c r="Z34" s="19" t="inlineStr"/>
+      <c r="AA34" s="19" t="inlineStr"/>
+      <c r="AB34" s="19" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="17" t="n">
@@ -3684,10 +3683,14 @@
       <c r="V35" s="19" t="inlineStr"/>
       <c r="W35" s="19" t="inlineStr"/>
       <c r="X35" s="19" t="inlineStr"/>
-      <c r="Y35" s="19" t="inlineStr"/>
-      <c r="Z35" s="30" t="n"/>
-      <c r="AA35" s="30" t="n"/>
-      <c r="AB35" s="30" t="n"/>
+      <c r="Y35" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 1 abstract cited by the corpus</t>
+        </is>
+      </c>
+      <c r="Z35" s="19" t="inlineStr"/>
+      <c r="AA35" s="19" t="inlineStr"/>
+      <c r="AB35" s="19" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="17" t="n">
@@ -3721,9 +3724,9 @@
       <c r="W36" s="19" t="inlineStr"/>
       <c r="X36" s="19" t="inlineStr"/>
       <c r="Y36" s="19" t="inlineStr"/>
-      <c r="Z36" s="30" t="n"/>
-      <c r="AA36" s="30" t="n"/>
-      <c r="AB36" s="30" t="n"/>
+      <c r="Z36" s="19" t="inlineStr"/>
+      <c r="AA36" s="19" t="inlineStr"/>
+      <c r="AB36" s="19" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="17" t="n">
@@ -3757,9 +3760,9 @@
       <c r="W37" s="19" t="inlineStr"/>
       <c r="X37" s="19" t="inlineStr"/>
       <c r="Y37" s="19" t="inlineStr"/>
-      <c r="Z37" s="30" t="n"/>
-      <c r="AA37" s="30" t="n"/>
-      <c r="AB37" s="30" t="n"/>
+      <c r="Z37" s="19" t="inlineStr"/>
+      <c r="AA37" s="19" t="inlineStr"/>
+      <c r="AB37" s="19" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="17" t="n">
@@ -3793,9 +3796,9 @@
       <c r="W38" s="19" t="inlineStr"/>
       <c r="X38" s="19" t="inlineStr"/>
       <c r="Y38" s="19" t="inlineStr"/>
-      <c r="Z38" s="30" t="n"/>
-      <c r="AA38" s="30" t="n"/>
-      <c r="AB38" s="30" t="n"/>
+      <c r="Z38" s="19" t="inlineStr"/>
+      <c r="AA38" s="19" t="inlineStr"/>
+      <c r="AB38" s="19" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="17" t="n">
@@ -3829,9 +3832,9 @@
       <c r="W39" s="19" t="inlineStr"/>
       <c r="X39" s="19" t="inlineStr"/>
       <c r="Y39" s="19" t="inlineStr"/>
-      <c r="Z39" s="30" t="n"/>
-      <c r="AA39" s="30" t="n"/>
-      <c r="AB39" s="30" t="n"/>
+      <c r="Z39" s="19" t="inlineStr"/>
+      <c r="AA39" s="19" t="inlineStr"/>
+      <c r="AB39" s="19" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="17" t="n">
@@ -3865,9 +3868,9 @@
       <c r="W40" s="19" t="inlineStr"/>
       <c r="X40" s="19" t="inlineStr"/>
       <c r="Y40" s="19" t="inlineStr"/>
-      <c r="Z40" s="30" t="n"/>
-      <c r="AA40" s="30" t="n"/>
-      <c r="AB40" s="30" t="n"/>
+      <c r="Z40" s="19" t="inlineStr"/>
+      <c r="AA40" s="19" t="inlineStr"/>
+      <c r="AB40" s="19" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="17" t="n">
@@ -3901,9 +3904,9 @@
       <c r="W41" s="19" t="inlineStr"/>
       <c r="X41" s="19" t="inlineStr"/>
       <c r="Y41" s="19" t="inlineStr"/>
-      <c r="Z41" s="30" t="n"/>
-      <c r="AA41" s="30" t="n"/>
-      <c r="AB41" s="30" t="n"/>
+      <c r="Z41" s="19" t="inlineStr"/>
+      <c r="AA41" s="19" t="inlineStr"/>
+      <c r="AB41" s="19" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="17" t="n">
@@ -3937,9 +3940,9 @@
       <c r="W42" s="19" t="inlineStr"/>
       <c r="X42" s="19" t="inlineStr"/>
       <c r="Y42" s="19" t="inlineStr"/>
-      <c r="Z42" s="30" t="n"/>
-      <c r="AA42" s="30" t="n"/>
-      <c r="AB42" s="30" t="n"/>
+      <c r="Z42" s="19" t="inlineStr"/>
+      <c r="AA42" s="19" t="inlineStr"/>
+      <c r="AB42" s="19" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="17" t="n">
@@ -3973,9 +3976,9 @@
       <c r="W43" s="19" t="inlineStr"/>
       <c r="X43" s="19" t="inlineStr"/>
       <c r="Y43" s="19" t="inlineStr"/>
-      <c r="Z43" s="30" t="n"/>
-      <c r="AA43" s="30" t="n"/>
-      <c r="AB43" s="30" t="n"/>
+      <c r="Z43" s="19" t="inlineStr"/>
+      <c r="AA43" s="19" t="inlineStr"/>
+      <c r="AB43" s="19" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="17" t="n">
@@ -4009,9 +4012,9 @@
       <c r="W44" s="19" t="inlineStr"/>
       <c r="X44" s="19" t="inlineStr"/>
       <c r="Y44" s="19" t="inlineStr"/>
-      <c r="Z44" s="30" t="n"/>
-      <c r="AA44" s="30" t="n"/>
-      <c r="AB44" s="30" t="n"/>
+      <c r="Z44" s="19" t="inlineStr"/>
+      <c r="AA44" s="19" t="inlineStr"/>
+      <c r="AB44" s="19" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="17" t="n">
@@ -4045,9 +4048,9 @@
       <c r="W45" s="19" t="inlineStr"/>
       <c r="X45" s="19" t="inlineStr"/>
       <c r="Y45" s="19" t="inlineStr"/>
-      <c r="Z45" s="30" t="n"/>
-      <c r="AA45" s="30" t="n"/>
-      <c r="AB45" s="30" t="n"/>
+      <c r="Z45" s="19" t="inlineStr"/>
+      <c r="AA45" s="19" t="inlineStr"/>
+      <c r="AB45" s="19" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="17" t="n">
@@ -4081,9 +4084,9 @@
       <c r="W46" s="19" t="inlineStr"/>
       <c r="X46" s="19" t="inlineStr"/>
       <c r="Y46" s="19" t="inlineStr"/>
-      <c r="Z46" s="30" t="n"/>
-      <c r="AA46" s="30" t="n"/>
-      <c r="AB46" s="30" t="n"/>
+      <c r="Z46" s="19" t="inlineStr"/>
+      <c r="AA46" s="19" t="inlineStr"/>
+      <c r="AB46" s="19" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="17" t="n">
@@ -4117,9 +4120,9 @@
       <c r="W47" s="19" t="inlineStr"/>
       <c r="X47" s="19" t="inlineStr"/>
       <c r="Y47" s="19" t="inlineStr"/>
-      <c r="Z47" s="30" t="n"/>
-      <c r="AA47" s="30" t="n"/>
-      <c r="AB47" s="30" t="n"/>
+      <c r="Z47" s="19" t="inlineStr"/>
+      <c r="AA47" s="19" t="inlineStr"/>
+      <c r="AB47" s="19" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="17" t="n">
@@ -4153,9 +4156,9 @@
       <c r="W48" s="19" t="inlineStr"/>
       <c r="X48" s="19" t="inlineStr"/>
       <c r="Y48" s="19" t="inlineStr"/>
-      <c r="Z48" s="30" t="n"/>
-      <c r="AA48" s="30" t="n"/>
-      <c r="AB48" s="30" t="n"/>
+      <c r="Z48" s="19" t="inlineStr"/>
+      <c r="AA48" s="19" t="inlineStr"/>
+      <c r="AB48" s="19" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="17" t="n">
@@ -4189,9 +4192,9 @@
       <c r="W49" s="19" t="inlineStr"/>
       <c r="X49" s="19" t="inlineStr"/>
       <c r="Y49" s="19" t="inlineStr"/>
-      <c r="Z49" s="30" t="n"/>
-      <c r="AA49" s="30" t="n"/>
-      <c r="AB49" s="30" t="n"/>
+      <c r="Z49" s="19" t="inlineStr"/>
+      <c r="AA49" s="19" t="inlineStr"/>
+      <c r="AB49" s="19" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="17" t="n">
@@ -4225,9 +4228,9 @@
       <c r="W50" s="19" t="inlineStr"/>
       <c r="X50" s="19" t="inlineStr"/>
       <c r="Y50" s="19" t="inlineStr"/>
-      <c r="Z50" s="30" t="n"/>
-      <c r="AA50" s="30" t="n"/>
-      <c r="AB50" s="30" t="n"/>
+      <c r="Z50" s="19" t="inlineStr"/>
+      <c r="AA50" s="19" t="inlineStr"/>
+      <c r="AB50" s="19" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="17" t="n">
@@ -4261,9 +4264,9 @@
       <c r="W51" s="19" t="inlineStr"/>
       <c r="X51" s="19" t="inlineStr"/>
       <c r="Y51" s="19" t="inlineStr"/>
-      <c r="Z51" s="30" t="n"/>
-      <c r="AA51" s="30" t="n"/>
-      <c r="AB51" s="30" t="n"/>
+      <c r="Z51" s="19" t="inlineStr"/>
+      <c r="AA51" s="19" t="inlineStr"/>
+      <c r="AB51" s="19" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="17" t="n">
@@ -4297,9 +4300,9 @@
       <c r="W52" s="19" t="inlineStr"/>
       <c r="X52" s="19" t="inlineStr"/>
       <c r="Y52" s="19" t="inlineStr"/>
-      <c r="Z52" s="30" t="n"/>
-      <c r="AA52" s="30" t="n"/>
-      <c r="AB52" s="30" t="n"/>
+      <c r="Z52" s="19" t="inlineStr"/>
+      <c r="AA52" s="19" t="inlineStr"/>
+      <c r="AB52" s="19" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="17" t="n">
@@ -4333,9 +4336,9 @@
       <c r="W53" s="19" t="inlineStr"/>
       <c r="X53" s="19" t="inlineStr"/>
       <c r="Y53" s="19" t="inlineStr"/>
-      <c r="Z53" s="30" t="n"/>
-      <c r="AA53" s="30" t="n"/>
-      <c r="AB53" s="30" t="n"/>
+      <c r="Z53" s="19" t="inlineStr"/>
+      <c r="AA53" s="19" t="inlineStr"/>
+      <c r="AB53" s="19" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="17" t="n">
@@ -4369,9 +4372,9 @@
       <c r="W54" s="19" t="inlineStr"/>
       <c r="X54" s="19" t="inlineStr"/>
       <c r="Y54" s="19" t="inlineStr"/>
-      <c r="Z54" s="30" t="n"/>
-      <c r="AA54" s="30" t="n"/>
-      <c r="AB54" s="30" t="n"/>
+      <c r="Z54" s="19" t="inlineStr"/>
+      <c r="AA54" s="19" t="inlineStr"/>
+      <c r="AB54" s="19" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="17" t="n">
@@ -4405,9 +4408,9 @@
       <c r="W55" s="19" t="inlineStr"/>
       <c r="X55" s="19" t="inlineStr"/>
       <c r="Y55" s="19" t="inlineStr"/>
-      <c r="Z55" s="30" t="n"/>
-      <c r="AA55" s="30" t="n"/>
-      <c r="AB55" s="30" t="n"/>
+      <c r="Z55" s="19" t="inlineStr"/>
+      <c r="AA55" s="19" t="inlineStr"/>
+      <c r="AB55" s="19" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="17" t="n">
@@ -4441,9 +4444,9 @@
       <c r="W56" s="19" t="inlineStr"/>
       <c r="X56" s="19" t="inlineStr"/>
       <c r="Y56" s="19" t="inlineStr"/>
-      <c r="Z56" s="30" t="n"/>
-      <c r="AA56" s="30" t="n"/>
-      <c r="AB56" s="30" t="n"/>
+      <c r="Z56" s="19" t="inlineStr"/>
+      <c r="AA56" s="19" t="inlineStr"/>
+      <c r="AB56" s="19" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="17" t="n">
@@ -4477,9 +4480,9 @@
       <c r="W57" s="19" t="inlineStr"/>
       <c r="X57" s="19" t="inlineStr"/>
       <c r="Y57" s="19" t="inlineStr"/>
-      <c r="Z57" s="30" t="n"/>
-      <c r="AA57" s="30" t="n"/>
-      <c r="AB57" s="30" t="n"/>
+      <c r="Z57" s="19" t="inlineStr"/>
+      <c r="AA57" s="19" t="inlineStr"/>
+      <c r="AB57" s="19" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="17" t="n">
@@ -4513,9 +4516,9 @@
       <c r="W58" s="19" t="inlineStr"/>
       <c r="X58" s="19" t="inlineStr"/>
       <c r="Y58" s="19" t="inlineStr"/>
-      <c r="Z58" s="30" t="n"/>
-      <c r="AA58" s="30" t="n"/>
-      <c r="AB58" s="30" t="n"/>
+      <c r="Z58" s="19" t="inlineStr"/>
+      <c r="AA58" s="19" t="inlineStr"/>
+      <c r="AB58" s="19" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="17" t="n">
@@ -4553,9 +4556,9 @@
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="Z59" s="30" t="n"/>
-      <c r="AA59" s="30" t="n"/>
-      <c r="AB59" s="30" t="n"/>
+      <c r="Z59" s="19" t="inlineStr"/>
+      <c r="AA59" s="19" t="inlineStr"/>
+      <c r="AB59" s="19" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="17" t="n">
@@ -4589,9 +4592,9 @@
       <c r="W60" s="19" t="inlineStr"/>
       <c r="X60" s="19" t="inlineStr"/>
       <c r="Y60" s="19" t="inlineStr"/>
-      <c r="Z60" s="30" t="n"/>
-      <c r="AA60" s="30" t="n"/>
-      <c r="AB60" s="30" t="n"/>
+      <c r="Z60" s="19" t="inlineStr"/>
+      <c r="AA60" s="19" t="inlineStr"/>
+      <c r="AB60" s="19" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="17" t="n">
@@ -4625,9 +4628,9 @@
       <c r="W61" s="19" t="inlineStr"/>
       <c r="X61" s="19" t="inlineStr"/>
       <c r="Y61" s="19" t="inlineStr"/>
-      <c r="Z61" s="30" t="n"/>
-      <c r="AA61" s="30" t="n"/>
-      <c r="AB61" s="30" t="n"/>
+      <c r="Z61" s="19" t="inlineStr"/>
+      <c r="AA61" s="19" t="inlineStr"/>
+      <c r="AB61" s="19" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="17" t="n">
@@ -4665,9 +4668,9 @@
           <t>Missing — 2 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
-      <c r="Z62" s="30" t="n"/>
-      <c r="AA62" s="30" t="n"/>
-      <c r="AB62" s="30" t="n"/>
+      <c r="Z62" s="19" t="inlineStr"/>
+      <c r="AA62" s="19" t="inlineStr"/>
+      <c r="AB62" s="19" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="17" t="n">
@@ -4701,9 +4704,9 @@
       <c r="W63" s="19" t="inlineStr"/>
       <c r="X63" s="19" t="inlineStr"/>
       <c r="Y63" s="19" t="inlineStr"/>
-      <c r="Z63" s="30" t="n"/>
-      <c r="AA63" s="30" t="n"/>
-      <c r="AB63" s="30" t="n"/>
+      <c r="Z63" s="19" t="inlineStr"/>
+      <c r="AA63" s="19" t="inlineStr"/>
+      <c r="AB63" s="19" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="17" t="n">
@@ -4737,13 +4740,13 @@
       <c r="W64" s="19" t="inlineStr"/>
       <c r="X64" s="19" t="inlineStr"/>
       <c r="Y64" s="19" t="inlineStr"/>
-      <c r="Z64" s="30" t="n"/>
+      <c r="Z64" s="19" t="inlineStr"/>
       <c r="AA64" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AB64" s="30" t="n"/>
+      <c r="AB64" s="19" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="17" t="n">
@@ -4777,9 +4780,9 @@
       <c r="W65" s="19" t="inlineStr"/>
       <c r="X65" s="19" t="inlineStr"/>
       <c r="Y65" s="19" t="inlineStr"/>
-      <c r="Z65" s="30" t="n"/>
-      <c r="AA65" s="30" t="n"/>
-      <c r="AB65" s="30" t="n"/>
+      <c r="Z65" s="19" t="inlineStr"/>
+      <c r="AA65" s="19" t="inlineStr"/>
+      <c r="AB65" s="19" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="17" t="n">
@@ -4817,13 +4820,13 @@
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="Z66" s="30" t="n"/>
+      <c r="Z66" s="19" t="inlineStr"/>
       <c r="AA66" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AB66" s="30" t="n"/>
+      <c r="AB66" s="19" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="17" t="n">
@@ -4857,9 +4860,9 @@
       <c r="W67" s="19" t="inlineStr"/>
       <c r="X67" s="19" t="inlineStr"/>
       <c r="Y67" s="19" t="inlineStr"/>
-      <c r="Z67" s="30" t="n"/>
-      <c r="AA67" s="30" t="n"/>
-      <c r="AB67" s="30" t="n"/>
+      <c r="Z67" s="19" t="inlineStr"/>
+      <c r="AA67" s="19" t="inlineStr"/>
+      <c r="AB67" s="19" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="17" t="n">
@@ -4893,9 +4896,9 @@
       <c r="W68" s="19" t="inlineStr"/>
       <c r="X68" s="19" t="inlineStr"/>
       <c r="Y68" s="19" t="inlineStr"/>
-      <c r="Z68" s="30" t="n"/>
-      <c r="AA68" s="30" t="n"/>
-      <c r="AB68" s="30" t="n"/>
+      <c r="Z68" s="19" t="inlineStr"/>
+      <c r="AA68" s="19" t="inlineStr"/>
+      <c r="AB68" s="19" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="17" t="n">
@@ -4937,9 +4940,9 @@
         </is>
       </c>
       <c r="Y69" s="19" t="inlineStr"/>
-      <c r="Z69" s="30" t="n"/>
-      <c r="AA69" s="30" t="n"/>
-      <c r="AB69" s="30" t="n"/>
+      <c r="Z69" s="19" t="inlineStr"/>
+      <c r="AA69" s="19" t="inlineStr"/>
+      <c r="AB69" s="19" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="17" t="n">
@@ -4981,9 +4984,9 @@
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="Z70" s="30" t="n"/>
-      <c r="AA70" s="30" t="n"/>
-      <c r="AB70" s="30" t="n"/>
+      <c r="Z70" s="19" t="inlineStr"/>
+      <c r="AA70" s="19" t="inlineStr"/>
+      <c r="AB70" s="19" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="17" t="n">
@@ -5025,13 +5028,13 @@
       <c r="W71" s="19" t="inlineStr"/>
       <c r="X71" s="19" t="inlineStr"/>
       <c r="Y71" s="19" t="inlineStr"/>
-      <c r="Z71" s="30" t="n"/>
+      <c r="Z71" s="19" t="inlineStr"/>
       <c r="AA71" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AB71" s="30" t="n"/>
+      <c r="AB71" s="19" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="17" t="n">
@@ -5069,9 +5072,9 @@
       <c r="W72" s="19" t="inlineStr"/>
       <c r="X72" s="19" t="inlineStr"/>
       <c r="Y72" s="19" t="inlineStr"/>
-      <c r="Z72" s="30" t="n"/>
-      <c r="AA72" s="30" t="n"/>
-      <c r="AB72" s="30" t="n"/>
+      <c r="Z72" s="19" t="inlineStr"/>
+      <c r="AA72" s="19" t="inlineStr"/>
+      <c r="AB72" s="19" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="17" t="n">
@@ -5113,9 +5116,9 @@
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="Z73" s="30" t="n"/>
-      <c r="AA73" s="30" t="n"/>
-      <c r="AB73" s="30" t="n"/>
+      <c r="Z73" s="19" t="inlineStr"/>
+      <c r="AA73" s="19" t="inlineStr"/>
+      <c r="AB73" s="19" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="17" t="n">
@@ -5158,8 +5161,8 @@
           <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA74" s="30" t="n"/>
-      <c r="AB74" s="30" t="n"/>
+      <c r="AA74" s="19" t="inlineStr"/>
+      <c r="AB74" s="19" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="17" t="n">
@@ -5197,9 +5200,9 @@
       <c r="W75" s="19" t="inlineStr"/>
       <c r="X75" s="19" t="inlineStr"/>
       <c r="Y75" s="19" t="inlineStr"/>
-      <c r="Z75" s="30" t="n"/>
-      <c r="AA75" s="30" t="n"/>
-      <c r="AB75" s="30" t="n"/>
+      <c r="Z75" s="19" t="inlineStr"/>
+      <c r="AA75" s="19" t="inlineStr"/>
+      <c r="AB75" s="19" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="17" t="n">
@@ -5237,9 +5240,9 @@
       <c r="W76" s="19" t="inlineStr"/>
       <c r="X76" s="19" t="inlineStr"/>
       <c r="Y76" s="19" t="inlineStr"/>
-      <c r="Z76" s="30" t="n"/>
-      <c r="AA76" s="30" t="n"/>
-      <c r="AB76" s="30" t="n"/>
+      <c r="Z76" s="19" t="inlineStr"/>
+      <c r="AA76" s="19" t="inlineStr"/>
+      <c r="AB76" s="19" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="17" t="n">
@@ -5282,8 +5285,8 @@
           <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA77" s="30" t="n"/>
-      <c r="AB77" s="30" t="n"/>
+      <c r="AA77" s="19" t="inlineStr"/>
+      <c r="AB77" s="19" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="17" t="n">
@@ -5326,8 +5329,8 @@
           <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA78" s="30" t="n"/>
-      <c r="AB78" s="30" t="n"/>
+      <c r="AA78" s="19" t="inlineStr"/>
+      <c r="AB78" s="19" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="17" t="n">
@@ -5378,8 +5381,8 @@
           <t>?; Missing — 2 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA79" s="30" t="n"/>
-      <c r="AB79" s="30" t="n"/>
+      <c r="AA79" s="19" t="inlineStr"/>
+      <c r="AB79" s="19" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="17" t="n">
@@ -5426,8 +5429,8 @@
           <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA80" s="30" t="n"/>
-      <c r="AB80" s="30" t="n"/>
+      <c r="AA80" s="19" t="inlineStr"/>
+      <c r="AB80" s="19" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="17" t="n">
@@ -5470,8 +5473,8 @@
           <t>?; Missing — 2 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA81" s="30" t="n"/>
-      <c r="AB81" s="30" t="n"/>
+      <c r="AA81" s="19" t="inlineStr"/>
+      <c r="AB81" s="19" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="17" t="n">
@@ -5514,8 +5517,8 @@
           <t>?; Missing — 2 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA82" s="30" t="n"/>
-      <c r="AB82" s="30" t="n"/>
+      <c r="AA82" s="19" t="inlineStr"/>
+      <c r="AB82" s="19" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="17" t="n">
@@ -5574,8 +5577,8 @@
           <t>?; Missing — 2 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA83" s="30" t="n"/>
-      <c r="AB83" s="30" t="n"/>
+      <c r="AA83" s="19" t="inlineStr"/>
+      <c r="AB83" s="19" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="17" t="n">
@@ -5622,8 +5625,8 @@
           <t>?; Missing — 2 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA84" s="30" t="n"/>
-      <c r="AB84" s="30" t="n"/>
+      <c r="AA84" s="19" t="inlineStr"/>
+      <c r="AB84" s="19" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="17" t="n">
@@ -5670,7 +5673,7 @@
           <t>?; Missing — 4 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA85" s="30" t="n"/>
+      <c r="AA85" s="19" t="inlineStr"/>
       <c r="AB85" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
@@ -5726,8 +5729,8 @@
           <t>?; Missing — 4 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA86" s="30" t="n"/>
-      <c r="AB86" s="30" t="n"/>
+      <c r="AA86" s="19" t="inlineStr"/>
+      <c r="AB86" s="19" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="17" t="n">
@@ -5773,9 +5776,9 @@
       <c r="W87" s="19" t="inlineStr"/>
       <c r="X87" s="19" t="inlineStr"/>
       <c r="Y87" s="19" t="inlineStr"/>
-      <c r="Z87" s="30" t="n"/>
-      <c r="AA87" s="30" t="n"/>
-      <c r="AB87" s="30" t="n"/>
+      <c r="Z87" s="19" t="inlineStr"/>
+      <c r="AA87" s="19" t="inlineStr"/>
+      <c r="AB87" s="19" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="17" t="n">
@@ -5806,7 +5809,11 @@
       </c>
       <c r="I88" s="19" t="inlineStr"/>
       <c r="J88" s="19" t="inlineStr"/>
-      <c r="K88" s="19" t="inlineStr"/>
+      <c r="K88" s="18" t="inlineStr">
+        <is>
+          <t>Xel Ha, Mexico; Missing — 1 abstract cited by the corpus [Published 2004]</t>
+        </is>
+      </c>
       <c r="L88" s="19" t="inlineStr"/>
       <c r="M88" s="19" t="inlineStr"/>
       <c r="N88" s="19" t="inlineStr"/>
@@ -5830,8 +5837,8 @@
           <t>?; Missing — 4 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA88" s="30" t="n"/>
-      <c r="AB88" s="30" t="n"/>
+      <c r="AA88" s="19" t="inlineStr"/>
+      <c r="AB88" s="19" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="17" t="n">
@@ -5882,8 +5889,8 @@
           <t>?; Missing — 2 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA89" s="30" t="n"/>
-      <c r="AB89" s="30" t="n"/>
+      <c r="AA89" s="19" t="inlineStr"/>
+      <c r="AB89" s="19" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="17" t="n">
@@ -5941,9 +5948,9 @@
           <t>Missing — 2 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
-      <c r="Z90" s="30" t="n"/>
-      <c r="AA90" s="30" t="n"/>
-      <c r="AB90" s="30" t="n"/>
+      <c r="Z90" s="19" t="inlineStr"/>
+      <c r="AA90" s="19" t="inlineStr"/>
+      <c r="AB90" s="19" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="17" t="n">
@@ -5998,8 +6005,8 @@
           <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA91" s="30" t="n"/>
-      <c r="AB91" s="30" t="n"/>
+      <c r="AA91" s="19" t="inlineStr"/>
+      <c r="AB91" s="19" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="17" t="n">
@@ -6054,7 +6061,7 @@
           <t>?; Missing — 3 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA92" s="30" t="n"/>
+      <c r="AA92" s="19" t="inlineStr"/>
       <c r="AB92" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 4 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
@@ -6122,7 +6129,7 @@
           <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA93" s="30" t="n"/>
+      <c r="AA93" s="19" t="inlineStr"/>
       <c r="AB93" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 3 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
@@ -6186,7 +6193,7 @@
           <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA94" s="30" t="n"/>
+      <c r="AA94" s="19" t="inlineStr"/>
       <c r="AB94" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 2 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
@@ -6254,7 +6261,7 @@
           <t>?; Missing — 17 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA95" s="30" t="n"/>
+      <c r="AA95" s="19" t="inlineStr"/>
       <c r="AB95" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 2 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
@@ -6317,8 +6324,8 @@
           <t>Missing — 3 abstracts cited by the corpus [3 distinct meetings]</t>
         </is>
       </c>
-      <c r="Z96" s="30" t="n"/>
-      <c r="AA96" s="30" t="n"/>
+      <c r="Z96" s="19" t="inlineStr"/>
+      <c r="AA96" s="19" t="inlineStr"/>
       <c r="AB96" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 4 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
@@ -6390,7 +6397,7 @@
           <t>?; Missing — 2 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA97" s="30" t="n"/>
+      <c r="AA97" s="19" t="inlineStr"/>
       <c r="AB97" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
@@ -6525,7 +6532,7 @@
       <c r="S99" s="19" t="inlineStr"/>
       <c r="T99" s="18" t="inlineStr">
         <is>
-          <t>Vienna, Austria; Missing — 11 abstracts cited by the corpus</t>
+          <t>Vienna, Austria; Missing — 10 abstracts cited by the corpus</t>
         </is>
       </c>
       <c r="U99" s="19" t="inlineStr"/>
@@ -6537,7 +6544,7 @@
           <t>Missing — 2 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
-      <c r="Z99" s="30" t="n"/>
+      <c r="Z99" s="19" t="inlineStr"/>
       <c r="AA99" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 16 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
@@ -6613,7 +6620,7 @@
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="Z100" s="30" t="n"/>
+      <c r="Z100" s="19" t="inlineStr"/>
       <c r="AA100" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 13 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
@@ -6670,10 +6677,10 @@
       <c r="X101" s="19" t="inlineStr"/>
       <c r="Y101" s="18" t="inlineStr">
         <is>
-          <t>Missing — 4 abstracts cited by the corpus [3 distinct meetings]</t>
-        </is>
-      </c>
-      <c r="Z101" s="30" t="n"/>
+          <t>Missing — 5 abstracts cited by the corpus [4 distinct meetings]</t>
+        </is>
+      </c>
+      <c r="Z101" s="19" t="inlineStr"/>
       <c r="AA101" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 3 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
@@ -6737,9 +6744,9 @@
           <t>Missing — 3 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
-      <c r="Z102" s="30" t="n"/>
-      <c r="AA102" s="30" t="n"/>
-      <c r="AB102" s="30" t="n"/>
+      <c r="Z102" s="19" t="inlineStr"/>
+      <c r="AA102" s="19" t="inlineStr"/>
+      <c r="AB102" s="19" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="17" t="n">
@@ -6785,9 +6792,9 @@
           <t>?; Missing — 1 abstract cited by the corpus [Published 2018]</t>
         </is>
       </c>
-      <c r="Z103" s="30" t="n"/>
-      <c r="AA103" s="30" t="n"/>
-      <c r="AB103" s="30" t="n"/>
+      <c r="Z103" s="19" t="inlineStr"/>
+      <c r="AA103" s="19" t="inlineStr"/>
+      <c r="AB103" s="19" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="17" t="n">
@@ -6841,9 +6848,9 @@
           <t>Missing — 3 abstracts cited by the corpus [3 distinct meetings]</t>
         </is>
       </c>
-      <c r="Z104" s="30" t="n"/>
-      <c r="AA104" s="30" t="n"/>
-      <c r="AB104" s="30" t="n"/>
+      <c r="Z104" s="19" t="inlineStr"/>
+      <c r="AA104" s="19" t="inlineStr"/>
+      <c r="AB104" s="19" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="17" t="n">
@@ -6893,9 +6900,9 @@
       <c r="W105" s="19" t="inlineStr"/>
       <c r="X105" s="19" t="inlineStr"/>
       <c r="Y105" s="19" t="inlineStr"/>
-      <c r="Z105" s="30" t="n"/>
-      <c r="AA105" s="30" t="n"/>
-      <c r="AB105" s="30" t="n"/>
+      <c r="Z105" s="19" t="inlineStr"/>
+      <c r="AA105" s="19" t="inlineStr"/>
+      <c r="AB105" s="19" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="17" t="n">
@@ -6911,9 +6918,9 @@
           <t>?; NA — no meeting — virtual BAAM-ZOOM sessions only, no abstract book</t>
         </is>
       </c>
-      <c r="D106" s="18" t="inlineStr">
-        <is>
-          <t>?; Missing — unknown whether a meeting was held: Cat thinks it was online for covid but was on maternity leave and is unsure; organiser unknown; abstracts unknown</t>
+      <c r="D106" s="19" t="inlineStr">
+        <is>
+          <t>none; NA — no meeting in 2020 (covid); confirmed by Simon 2026-09-30, not a gap to chase</t>
         </is>
       </c>
       <c r="E106" s="20" t="inlineStr">
@@ -6950,8 +6957,8 @@
           <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA106" s="30" t="n"/>
-      <c r="AB106" s="30" t="n"/>
+      <c r="AA106" s="19" t="inlineStr"/>
+      <c r="AB106" s="19" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="17" t="n">
@@ -7001,9 +7008,9 @@
           <t>Missing — 2 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
-      <c r="Z107" s="30" t="n"/>
-      <c r="AA107" s="30" t="n"/>
-      <c r="AB107" s="30" t="n"/>
+      <c r="Z107" s="19" t="inlineStr"/>
+      <c r="AA107" s="19" t="inlineStr"/>
+      <c r="AB107" s="19" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="17" t="n">
@@ -7057,9 +7064,9 @@
           <t>?; Missing — 2 abstracts cited by the corpus</t>
         </is>
       </c>
-      <c r="Z108" s="30" t="n"/>
-      <c r="AA108" s="30" t="n"/>
-      <c r="AB108" s="30" t="n"/>
+      <c r="Z108" s="19" t="inlineStr"/>
+      <c r="AA108" s="19" t="inlineStr"/>
+      <c r="AB108" s="19" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="17" t="n">
@@ -7113,9 +7120,9 @@
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="Z109" s="30" t="n"/>
-      <c r="AA109" s="30" t="n"/>
-      <c r="AB109" s="30" t="n"/>
+      <c r="Z109" s="19" t="inlineStr"/>
+      <c r="AA109" s="19" t="inlineStr"/>
+      <c r="AB109" s="19" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="17" t="n">
@@ -7161,9 +7168,9 @@
       <c r="W110" s="19" t="inlineStr"/>
       <c r="X110" s="19" t="inlineStr"/>
       <c r="Y110" s="19" t="inlineStr"/>
-      <c r="Z110" s="30" t="n"/>
-      <c r="AA110" s="30" t="n"/>
-      <c r="AB110" s="30" t="n"/>
+      <c r="Z110" s="19" t="inlineStr"/>
+      <c r="AA110" s="19" t="inlineStr"/>
+      <c r="AB110" s="19" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="17" t="n">
@@ -7217,9 +7224,9 @@
           <t>?; Missing — 3 abstracts cited by the corpus</t>
         </is>
       </c>
-      <c r="Z111" s="30" t="n"/>
-      <c r="AA111" s="30" t="n"/>
-      <c r="AB111" s="30" t="n"/>
+      <c r="Z111" s="19" t="inlineStr"/>
+      <c r="AA111" s="19" t="inlineStr"/>
+      <c r="AB111" s="19" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="17" t="n">
@@ -7268,10 +7275,14 @@
       <c r="V112" s="19" t="inlineStr"/>
       <c r="W112" s="19" t="inlineStr"/>
       <c r="X112" s="19" t="inlineStr"/>
-      <c r="Y112" s="19" t="inlineStr"/>
-      <c r="Z112" s="30" t="n"/>
-      <c r="AA112" s="30" t="n"/>
-      <c r="AB112" s="30" t="n"/>
+      <c r="Y112" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 1 abstract cited by the corpus</t>
+        </is>
+      </c>
+      <c r="Z112" s="19" t="inlineStr"/>
+      <c r="AA112" s="19" t="inlineStr"/>
+      <c r="AB112" s="19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7581,10 +7592,10 @@
         <v>84</v>
       </c>
       <c r="C13" t="n">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="D13" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -7870,7 +7881,7 @@
         <v>397</v>
       </c>
       <c r="D24" t="n">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -8259,10 +8270,10 @@
         <v>3669</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>8076</v>
+        <v>8053</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>5173</v>
+        <v>5147</v>
       </c>
       <c r="E39" s="1" t="n">
         <v>863</v>
@@ -8325,10 +8336,10 @@
         <v>9</v>
       </c>
       <c r="C44" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D44" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45">

--- a/database/conference_coverage_matrix.xlsx
+++ b/database/conference_coverage_matrix.xlsx
@@ -7488,10 +7488,10 @@
         <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D9" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -7514,10 +7514,10 @@
         <v>86</v>
       </c>
       <c r="C10" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -7540,7 +7540,7 @@
         <v>78</v>
       </c>
       <c r="C11" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D11" t="n">
         <v>148</v>
@@ -7569,7 +7569,7 @@
         <v>216</v>
       </c>
       <c r="D12" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -7589,10 +7589,10 @@
         <v>2001</v>
       </c>
       <c r="B13" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C13" t="n">
-        <v>176</v>
+        <v>299</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -7748,10 +7748,10 @@
         <v>138</v>
       </c>
       <c r="C19" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D19" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -7774,10 +7774,10 @@
         <v>193</v>
       </c>
       <c r="C20" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D20" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E20" t="n">
         <v>22</v>
@@ -7829,7 +7829,7 @@
         <v>359</v>
       </c>
       <c r="D22" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E22" t="n">
         <v>28</v>
@@ -7881,7 +7881,7 @@
         <v>397</v>
       </c>
       <c r="D24" t="n">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -7933,7 +7933,7 @@
         <v>367</v>
       </c>
       <c r="D26" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E26" t="n">
         <v>74</v>
@@ -7959,7 +7959,7 @@
         <v>317</v>
       </c>
       <c r="D27" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -7982,10 +7982,10 @@
         <v>231</v>
       </c>
       <c r="C28" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D28" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E28" t="n">
         <v>97</v>
@@ -8008,7 +8008,7 @@
         <v>154</v>
       </c>
       <c r="C29" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D29" t="n">
         <v>241</v>
@@ -8063,7 +8063,7 @@
         <v>349</v>
       </c>
       <c r="D31" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E31" t="n">
         <v>74</v>
@@ -8193,7 +8193,7 @@
         <v>183</v>
       </c>
       <c r="D36" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -8242,7 +8242,7 @@
         <v>235</v>
       </c>
       <c r="C38" t="n">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D38" t="n">
         <v>288</v>
@@ -8267,13 +8267,13 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>3669</v>
+        <v>3670</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>8053</v>
+        <v>8185</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>5147</v>
+        <v>5167</v>
       </c>
       <c r="E39" s="1" t="n">
         <v>863</v>

--- a/database/conference_coverage_matrix.xlsx
+++ b/database/conference_coverage_matrix.xlsx
@@ -7488,7 +7488,7 @@
         <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="D9" t="n">
         <v>139</v>
@@ -7514,7 +7514,7 @@
         <v>86</v>
       </c>
       <c r="C10" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D10" t="n">
         <v>217</v>
@@ -7540,7 +7540,7 @@
         <v>78</v>
       </c>
       <c r="C11" t="n">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="D11" t="n">
         <v>148</v>
@@ -7696,7 +7696,7 @@
         <v>179</v>
       </c>
       <c r="C17" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D17" t="n">
         <v>345</v>
@@ -7774,7 +7774,7 @@
         <v>193</v>
       </c>
       <c r="C20" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D20" t="n">
         <v>192</v>
@@ -7956,10 +7956,10 @@
         <v>117</v>
       </c>
       <c r="C27" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D27" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -8270,10 +8270,10 @@
         <v>3670</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>8185</v>
+        <v>8201</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>5167</v>
+        <v>5171</v>
       </c>
       <c r="E39" s="1" t="n">
         <v>863</v>

--- a/database/conference_coverage_matrix.xlsx
+++ b/database/conference_coverage_matrix.xlsx
@@ -8254,7 +8254,7 @@
         <v>7</v>
       </c>
       <c r="G38" t="n">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="H38" t="n">
         <v>1000</v>
@@ -8282,7 +8282,7 @@
         <v>161</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>1039</v>
+        <v>1068</v>
       </c>
       <c r="H39" s="1" t="n">
         <v>1749</v>

--- a/database/conference_coverage_matrix.xlsx
+++ b/database/conference_coverage_matrix.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Conferences'!$A$1:$H$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Conferences'!$A$1:$H$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1359,7 +1359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1645,27 +1645,35 @@
         </is>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8" s="13" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>SBEEL. The X Reuniao was held in 2018 inside the Sharks International book, so at least nine earlier meetings exist. The corpus cites only the II, which is why n_needed is 1 — that number is a floor and badly understates this series.</t>
-        </is>
-      </c>
-      <c r="G8" s="14" t="inlineStr"/>
-      <c r="H8" s="14" t="inlineStr"/>
+          <t>SBEEL (Sociedade Brasileira para o Estudo de Elasmobranquios), founded 1 Aug 1997 at the I Reuniao (Ilheus, BA) from the Grupo de Trabalho sobre Pesca e Pesquisa de Tubaroes e Raias (formed as a society at Rio Grande, RS, 1995). TEN meetings, 1997-2018 (also called 'Encontro'): I 1997 Ilheus BA (74 abstracts), II 2000 Santos SP (98), III 2002 Joao Pessoa PB (71), IV 2004 Recife PE (97), V 2006 Itajai SC (88), VI 2008 Fortaleza CE (96), VII 2011 Rio Grande RS (87), VIII 2014 Recife PE, UFRPE (72), IX 2016 Penedo AL, UFAL, 24-28 Apr (107), X 2018 Joao Pessoa PB, 3-8 Jun, joint with Sharks International (461; HELD as the SI 2018 book). No XI found (searched 2026-10-28). Soares &amp; Petean 2023 (Neotrop. Ichthyol. 21(2):e230027) analysed all ten books: 1,248 SBEEL abstracts; their Tab. S1 (CC BY 4.0) gives every title, first-author institution, and taxa, but NO bodies. Books are print 'Livro/Caderno de Resumos' (V: Itajai, Nova Letra, 123 pp); none found online. Board on the 2021 site: Otto B. F. Gadig (president, UNESP), Ricardo S. Rosa (treasurer, UFPB), Rodrigo R. Barreto (secretary, CEPSUL/ICMBio). Marcela Alvarenga (SciLifeLab, ex-UFRJ) is asking SBEEL for the books (28 Oct 2026). Sister series not yet a column: EBI (Encontro Brasileiro de Ictiologia, SBI, biennial, 326 chondrichthyan abstracts 1991-2019 in the same Tab. S1).</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>sbeel.org.br is DEAD (NXDOMAIN 2026-10-28; spam-hijacked by 2023); Wayback copies 2017-2022 hold history and board only, no abstract books</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>Via Marcela Alvarenga (asking SBEEL, reply ~6 Nov 2026); else Karla D. A. Soares (UFRJ) and Flavia F. Petean, who located all ten books, or Otto Gadig (UNESP). Addresses: Gmail/Contacts, not stored here</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>Simposio Nacional de Tiburones y Rayas (SOMEPEC, Mexico)</t>
+          <t>Encontro Brasileiro de Ictiologia (EBI)</t>
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>2004</v>
+        <v>1983</v>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
@@ -1673,85 +1681,89 @@
         </is>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Sociedad Mexicana de Peces Cartilaginosos (SOMEPEC). HARVESTED 2026-09-04 from somepec.org, no request to anyone needed: I 2004 (with the III Semana del Tiburon, UNAM), III 2008, IV 2010 (UNAM), VII 2016, XI 2025 as abstract books, plus the IX 2021 programme. All five books carry a clean text layer. STILL MISSING: II, V, VI 2014 Mazatlan (the edition our corpus cites), VIII 2019 Playa del Carmen (joint with the I Congreso Latinoamericano de Tiburones, Rayas y Quimeras), and X. Ask info@somepec.org for exactly those five.</t>
+          <t>Sociedade Brasileira de Ictiologia (SBI); official biennial meeting, annual 1983-1992 then biennial from 1993-95. Editions: IX 1991 Maringa PR (UEM/Nupelia), X 1993 Sao Paulo (USP), XI 1995 Campinas (PUCCAMP), XII 1997 Sao Paulo (IO-USP, 24-28 Feb), XIII 1999 SP (city not established), XIV 2001 Sao Leopoldo RS (UNISINOS), XV 2003 Sao Paulo, XVI 2005 Joao Pessoa PB, XVII 2007 Itajai SC (Univali), XVIII 2009 Cuiaba MT (UFMT), XIX 2011 Manaus AM, XX 2013 Maringa PR, XXI 2015 Olinda PE (UFRPE), XXII 2017 Porto Seguro BA (UFSB), XXIII 2019 Belem PA, XXIV 2022 Gramado RS, XXV 2025 Palmas TO (UFT, 26-31 Jan). Chondrichthyans are 1.4-6.6% of each book (326 abstracts 1991-2019, Soares &amp; Petean 2023), so this column counts elasmo abstracts, not the whole book. No corpus record cites EBI yet (2026-10-28).</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>https://somepec.org/memorias/ ; back volumes under https://somepec.org/wp-content/uploads/ ; scraper scripts/conf_abstracts/scrape_somepec.py</t>
+          <t>https://www.sbi.bio.br/ (Boletim SBI archive). Online proceedings: 2015 CD at automacaodeeventos.com.br/ebi2015/cd/ ; 2025 Anais at editorarealize.com.br (ISBN 978-65-5222-033-2)</t>
         </is>
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>info@somepec.org ; +52 55 5034 1708</t>
+          <t>SBI board via sbi.bio.br; or Karla D. A. Soares (UFRJ) and Flavia F. Petean, who located the 1991-2019 books. Addresses: Gmail/Contacts</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>Colloque international requins en Afrique de l'Ouest</t>
+          <t>Simposio Nacional de Tiburones y Rayas (SOMEPEC, Mexico)</t>
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>2011</v>
-      </c>
-      <c r="C10" s="13" t="n">
-        <v>2011</v>
+        <v>2004</v>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
       </c>
       <c r="D10" s="13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Commission Sous-Regionale des Peches (CSRP / SRFC), an intergovernmental body for seven West African states. Dakar, Senegal, 25-27 July 2011, on the conservation and sustainable management of shark populations in West Africa. A single meeting, not a series — kept on the list anyway: 48 abstracts is one email and one book, and it is the only West African material in the corpus.</t>
+          <t>Sociedad Mexicana de Peces Cartilaginosos (SOMEPEC). HARVESTED 2026-09-04 from somepec.org, no request to anyone needed: I 2004 (with the III Semana del Tiburon, UNAM), III 2008, IV 2010 (UNAM), VII 2016, XI 2025 as abstract books, plus the IX 2021 programme. All five books carry a clean text layer. STILL MISSING: II, V, VI 2014 Mazatlan (the edition our corpus cites), VIII 2019 Playa del Carmen (joint with the I Congreso Latinoamericano de Tiburones, Rayas y Quimeras), and X. Ask info@somepec.org for exactly those five.</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>https://spcsrp.org/</t>
-        </is>
-      </c>
-      <c r="H10" s="14" t="inlineStr"/>
+          <t>https://somepec.org/memorias/ ; back volumes under https://somepec.org/wp-content/uploads/ ; scraper scripts/conf_abstracts/scrape_somepec.py</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>info@somepec.org ; +52 55 5034 1708</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Gulf and Caribbean Fisheries Institute (GCFI)</t>
+          <t>Colloque international requins en Afrique de l'Ouest</t>
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>1948</v>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>ongoing</t>
-        </is>
+        <v>2011</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>2011</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>GCFI secretariat. Every meeting since 1948 is in the annual Proceedings and every PAPER is a free PDF at proceedings.gcfi.org (verified 2026-09-04), so nobody needs asking and nobody should be assigned these. The 31 corpus records were sitting on the needs-library queue and are now acquisition_route=gcfi_proceedings.</t>
+          <t>Commission Sous-Regionale des Peches (CSRP / SRFC), an intergovernmental body for seven West African states. Dakar, Senegal, 25-27 July 2011, on the conservation and sustainable management of shark populations in West Africa. A single meeting, not a series — kept on the list anyway: 48 abstracts is one email and one book, and it is the only West African material in the corpus.</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>https://proceedings.gcfi.org/ (per-paper PDFs) ; https://www.gcfi.org/ ; back volumes also in the NOAA Institutional Repository</t>
+          <t>https://spcsrp.org/</t>
         </is>
       </c>
       <c r="H11" s="14" t="inlineStr"/>
@@ -1759,65 +1771,65 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>Pacific Shark Workshop</t>
+          <t>Gulf and Caribbean Fisheries Institute (GCFI)</t>
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>2011</v>
-      </c>
-      <c r="C12" s="13" t="n">
-        <v>2012</v>
+        <v>1948</v>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
       </c>
       <c r="D12" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="F12" s="14" t="inlineStr"/>
-      <c r="G12" s="14" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>GCFI secretariat. Every meeting since 1948 is in the annual Proceedings and every PAPER is a free PDF at proceedings.gcfi.org (verified 2026-09-04), so nobody needs asking and nobody should be assigned these. The 31 corpus records were sitting on the needs-library queue and are now acquisition_route=gcfi_proceedings.</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>https://proceedings.gcfi.org/ (per-paper PDFs) ; https://www.gcfi.org/ ; back volumes also in the NOAA Institutional Repository</t>
+        </is>
+      </c>
       <c r="H12" s="14" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>ISC Shark Working Group</t>
+          <t>Pacific Shark Workshop</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>2013</v>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>ongoing</t>
-        </is>
+        <v>2011</v>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>2012</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="14" t="inlineStr">
-        <is>
-          <t>International Scientific Committee for Tuna and Tuna-like Species in the North Pacific Ocean; the Shark Working Group meets within it.</t>
-        </is>
-      </c>
-      <c r="G13" s="14" t="inlineStr">
-        <is>
-          <t>https://isc.fra.go.jp/</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F13" s="14" t="inlineStr"/>
+      <c r="G13" s="14" t="inlineStr"/>
       <c r="H13" s="14" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>World Congress of Herpetology</t>
+          <t>ISC Shark Working Group</t>
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>1989</v>
+        <v>2013</v>
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
@@ -1825,19 +1837,19 @@
         </is>
       </c>
       <c r="D14" s="13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>World Congress of Herpetology committee. Every 3-5 years.</t>
+          <t>International Scientific Committee for Tuna and Tuna-like Species in the North Pacific Ocean; the Shark Working Group meets within it.</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>https://www.worldcongressofherpetology.org/</t>
+          <t>https://isc.fra.go.jp/</t>
         </is>
       </c>
       <c r="H14" s="14" t="inlineStr"/>
@@ -1845,11 +1857,11 @@
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>Indo-Pacific Fish Conference (IPFC)</t>
+          <t>World Congress of Herpetology</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>1981</v>
+        <v>1989</v>
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
@@ -1860,16 +1872,16 @@
         <v>4</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Rotating host. IPFC-11 2023 Auckland (joint with ASFB); IPFC-12 2025 Taiwan.</t>
+          <t>World Congress of Herpetology committee. Every 3-5 years.</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>https://sfi-cybium.fr/en/indo-pacific-fish-conference</t>
+          <t>https://www.worldcongressofherpetology.org/</t>
         </is>
       </c>
       <c r="H15" s="14" t="inlineStr"/>
@@ -1877,11 +1889,11 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>International Coral Reef Symposium (ICRS)</t>
+          <t>Indo-Pacific Fish Conference (IPFC)</t>
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>1969</v>
+        <v>1981</v>
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
@@ -1892,16 +1904,16 @@
         <v>4</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>International Coral Reef Society. ICRS-16 2026 Auckland.</t>
+          <t>Rotating host. IPFC-11 2023 Auckland (joint with ASFB); IPFC-12 2025 Taiwan.</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>https://coralreefs.org/</t>
+          <t>https://sfi-cybium.fr/en/indo-pacific-fish-conference</t>
         </is>
       </c>
       <c r="H16" s="14" t="inlineStr"/>
@@ -1909,11 +1921,11 @@
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>World Fisheries Congress</t>
+          <t>International Coral Reef Symposium (ICRS)</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>1992</v>
+        <v>1969</v>
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
@@ -1924,20 +1936,28 @@
         <v>4</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="F17" s="14" t="inlineStr"/>
-      <c r="G17" s="14" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>International Coral Reef Society. ICRS-16 2026 Auckland.</t>
+        </is>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>https://coralreefs.org/</t>
+        </is>
+      </c>
       <c r="H17" s="14" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>American Fisheries Society symposia</t>
+          <t>World Fisheries Congress</t>
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>1871</v>
+        <v>1992</v>
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
@@ -1945,31 +1965,23 @@
         </is>
       </c>
       <c r="D18" s="13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="F18" s="14" t="inlineStr">
-        <is>
-          <t>American Fisheries Society.</t>
-        </is>
-      </c>
-      <c r="G18" s="14" t="inlineStr">
-        <is>
-          <t>https://fisheries.org/</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F18" s="14" t="inlineStr"/>
+      <c r="G18" s="14" t="inlineStr"/>
       <c r="H18" s="14" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>International Congress on the Biology of Fish</t>
+          <t>American Fisheries Society symposia</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>1994</v>
+        <v>1871</v>
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
@@ -1977,23 +1989,31 @@
         </is>
       </c>
       <c r="D19" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="F19" s="14" t="inlineStr"/>
-      <c r="G19" s="14" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>American Fisheries Society.</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>https://fisheries.org/</t>
+        </is>
+      </c>
       <c r="H19" s="14" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>International Meeting on Mesozoic Fishes</t>
+          <t>International Congress on the Biology of Fish</t>
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
@@ -2001,27 +2021,23 @@
         </is>
       </c>
       <c r="D20" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="E20" s="13" t="n">
-        <v>16</v>
-      </c>
-      <c r="F20" s="14" t="inlineStr">
-        <is>
-          <t>Meeting conveners vary; 6th meeting edited by Schwarz &amp; Kriwet.</t>
-        </is>
-      </c>
+      <c r="F20" s="14" t="inlineStr"/>
       <c r="G20" s="14" t="inlineStr"/>
       <c r="H20" s="14" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>International Congress of Vertebrate Morphology (ICVM)</t>
+          <t>International Meeting on Mesozoic Fishes</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>1986</v>
+        <v>1993</v>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
@@ -2029,23 +2045,27 @@
         </is>
       </c>
       <c r="D21" s="13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="14" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>Meeting conveners vary; 6th meeting edited by Schwarz &amp; Kriwet.</t>
+        </is>
+      </c>
       <c r="G21" s="14" t="inlineStr"/>
       <c r="H21" s="14" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>CIESM Congress (Mediterranean Science Commission)</t>
+          <t>International Congress of Vertebrate Morphology (ICVM)</t>
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>1919</v>
+        <v>1986</v>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
@@ -2058,26 +2078,18 @@
       <c r="E22" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="14" t="inlineStr">
-        <is>
-          <t>Commission Internationale pour l'Exploration Scientifique de la Mer Mediterranee.</t>
-        </is>
-      </c>
-      <c r="G22" s="14" t="inlineStr">
-        <is>
-          <t>https://ciesm.org/</t>
-        </is>
-      </c>
+      <c r="F22" s="14" t="inlineStr"/>
+      <c r="G22" s="14" t="inlineStr"/>
       <c r="H22" s="14" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>Albert L. Tester Memorial Symposium</t>
+          <t>CIESM Congress (Mediterranean Science Commission)</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>1976</v>
+        <v>1919</v>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
@@ -2085,77 +2097,81 @@
         </is>
       </c>
       <c r="D23" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="13" t="n">
-        <v>3</v>
-      </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>University of Hawaii at Manoa.</t>
-        </is>
-      </c>
-      <c r="G23" s="14" t="inlineStr"/>
+          <t>Commission Internationale pour l'Exploration Scientifique de la Mer Mediterranee.</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>https://ciesm.org/</t>
+        </is>
+      </c>
       <c r="H23" s="14" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>Workshop on Age Determination of Oceanic Pelagic Fishes</t>
+          <t>Albert L. Tester Memorial Symposium</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>1983</v>
-      </c>
-      <c r="C24" s="13" t="n">
-        <v>1983</v>
+        <v>1976</v>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
       </c>
       <c r="D24" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="F24" s="14" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>University of Hawaii at Manoa.</t>
+        </is>
+      </c>
       <c r="G24" s="14" t="inlineStr"/>
       <c r="H24" s="14" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>Palaeontology / geology meetings (assorted)</t>
+          <t>Workshop on Age Determination of Oceanic Pelagic Fishes</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>1973</v>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>ongoing</t>
-        </is>
+        <v>1983</v>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>1983</v>
       </c>
       <c r="D25" s="13" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>92</v>
-      </c>
-      <c r="F25" s="14" t="inlineStr">
-        <is>
-          <t>NOT ONE SERIES — a bucket of many national and international palaeo and geology meetings. Split it before chasing anyone.</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="F25" s="14" t="inlineStr"/>
       <c r="G25" s="14" t="inlineStr"/>
       <c r="H25" s="14" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>SVP (Society of Vertebrate Paleontology annual meeting)</t>
+          <t>Palaeontology / geology meetings (assorted)</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>1940</v>
+        <v>1973</v>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
@@ -2163,35 +2179,27 @@
         </is>
       </c>
       <c r="D26" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>Society of Vertebrate Paleontology. Annual meeting; abstracts published as a "Supplement to Number 3" (pre-2013 volumes) or "(Suppl. N)" issue of the Journal of Vertebrate Paleontology, one abstract per page, page numbers suffixed "A" (e.g. 29(Suppl. to No.3), 52A). Elasmobranch-relevant abstracts run at least 1988-2020 in this corpus; the series itself runs continuously to the present.</t>
-        </is>
-      </c>
-      <c r="G26" s="14" t="inlineStr">
-        <is>
-          <t>https://vertpaleo.org/annual-meeting/</t>
-        </is>
-      </c>
-      <c r="H26" s="14" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
+          <t>NOT ONE SERIES — a bucket of many national and international palaeo and geology meetings. Split it before chasing anyone.</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="inlineStr"/>
+      <c r="H26" s="14" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>SICB (Society for Integrative and Comparative Biology)</t>
+          <t>SVP (Society of Vertebrate Paleontology annual meeting)</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>1991</v>
+        <v>1940</v>
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
@@ -2202,16 +2210,16 @@
         <v>1</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>Society for Integrative and Comparative Biology (formed 1991 from the American Society of Zoologists). Annual meeting abstracts published as a January Suppl. 1 issue of Integrative and Comparative Biology (formerly American Zoologist for the ASZ-era predecessor, 1961-1996), one abstract per page, pages prefixed "E" (e.g. 54(IS Suppl. 1): E48). 3 more elasmobranch abstracts found under the predecessor title American Zoologist (1978, 1980, 1985), same page-suffix convention but ending "A" not "E".</t>
+          <t>Society of Vertebrate Paleontology. Annual meeting; abstracts published as a "Supplement to Number 3" (pre-2013 volumes) or "(Suppl. N)" issue of the Journal of Vertebrate Paleontology, one abstract per page, page numbers suffixed "A" (e.g. 29(Suppl. to No.3), 52A). Elasmobranch-relevant abstracts run at least 1988-2020 in this corpus; the series itself runs continuously to the present.</t>
         </is>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>https://sicb.org/meetings/</t>
+          <t>https://vertpaleo.org/annual-meeting/</t>
         </is>
       </c>
       <c r="H27" s="14" t="inlineStr">
@@ -2223,11 +2231,11 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>SIBM (Società Italiana di Biologia Marina)</t>
+          <t>SICB (Society for Integrative and Comparative Biology)</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>1969</v>
+        <v>1991</v>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
@@ -2238,47 +2246,83 @@
         <v>1</v>
       </c>
       <c r="E28" s="13" t="n">
+        <v>38</v>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>Society for Integrative and Comparative Biology (formed 1991 from the American Society of Zoologists). Annual meeting abstracts published as a January Suppl. 1 issue of Integrative and Comparative Biology (formerly American Zoologist for the ASZ-era predecessor, 1961-1996), one abstract per page, pages prefixed "E" (e.g. 54(IS Suppl. 1): E48). 3 more elasmobranch abstracts found under the predecessor title American Zoologist (1978, 1980, 1985), same page-suffix convention but ending "A" not "E".</t>
+        </is>
+      </c>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>https://sicb.org/meetings/</t>
+        </is>
+      </c>
+      <c r="H28" s="14" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>SIBM (Società Italiana di Biologia Marina)</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="n">
+        <v>1969</v>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>ongoing</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="13" t="n">
         <v>24</v>
       </c>
-      <c r="F28" s="14" t="inlineStr">
+      <c r="F29" s="14" t="inlineStr">
         <is>
           <t>Società Italiana di Biologia Marina. Annual congress; short (1-2 page) proceedings notes published in the society journal Biologia Marina Mediterranea (ISSN 1123-4245) alongside the journal's normal full-length articles -- so NOT every Biologia Marina Mediterranea record is a congress note, only the short ones (page span &lt;=2). Elasmobranch-relevant notes seen 1999-2015 in this corpus.</t>
         </is>
       </c>
-      <c r="G28" s="14" t="inlineStr">
+      <c r="G29" s="14" t="inlineStr">
         <is>
           <t>https://www.sibm.it/</t>
         </is>
       </c>
-      <c r="H28" s="14" t="inlineStr">
+      <c r="H29" s="14" t="inlineStr">
         <is>
           <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>frequency: 1 = annual, 2 = biennial, 3 = every three years, 4 = every four years, 0 = one-off / irregular</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>n_needed: corpus records citing that series whose PDF we do NOT hold (scripts/conf_abstracts/conference_lead_candidates.py). It counts abstracts we can already name, so it is a floor, not the size of the series.</t>
+          <t>frequency: 1 = annual, 2 = biennial, 3 = every three years, 4 = every four years, 0 = one-off / irregular</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
+          <t>n_needed: corpus records citing that series whose PDF we do NOT hold (scripts/conf_abstracts/conference_lead_candidates.py). It counts abstracts we can already name, so it is a floor, not the size of the series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
           <t>A BLANK organisers/website/contact means not found on 2026-09-04, never a guess — a wrong address costs a real email to a real person.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H28"/>
+  <autoFilter ref="A1:H29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2289,7 +2333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB112"/>
+  <dimension ref="A1:AC112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2320,6 +2364,7 @@
     <col width="30" customWidth="1" min="26" max="26"/>
     <col width="30" customWidth="1" min="27" max="27"/>
     <col width="30" customWidth="1" min="28" max="28"/>
+    <col width="30" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2365,100 +2410,105 @@
       </c>
       <c r="I1" s="16" t="inlineStr">
         <is>
+          <t>EBI</t>
+        </is>
+      </c>
+      <c r="J1" s="16" t="inlineStr">
+        <is>
           <t>SOMEPEC</t>
         </is>
       </c>
-      <c r="J1" s="16" t="inlineStr">
+      <c r="K1" s="16" t="inlineStr">
         <is>
           <t>W Africa</t>
         </is>
       </c>
-      <c r="K1" s="16" t="inlineStr">
+      <c r="L1" s="16" t="inlineStr">
         <is>
           <t>GCFI</t>
         </is>
       </c>
-      <c r="L1" s="16" t="inlineStr">
+      <c r="M1" s="16" t="inlineStr">
         <is>
           <t>Pac Shark Wksp</t>
         </is>
       </c>
-      <c r="M1" s="16" t="inlineStr">
+      <c r="N1" s="16" t="inlineStr">
         <is>
           <t>ISC Shark WG</t>
         </is>
       </c>
-      <c r="N1" s="16" t="inlineStr">
+      <c r="O1" s="16" t="inlineStr">
         <is>
           <t>WCH</t>
         </is>
       </c>
-      <c r="O1" s="16" t="inlineStr">
+      <c r="P1" s="16" t="inlineStr">
         <is>
           <t>IPFC</t>
         </is>
       </c>
-      <c r="P1" s="16" t="inlineStr">
+      <c r="Q1" s="16" t="inlineStr">
         <is>
           <t>ICRS</t>
         </is>
       </c>
-      <c r="Q1" s="16" t="inlineStr">
+      <c r="R1" s="16" t="inlineStr">
         <is>
           <t>WFC</t>
         </is>
       </c>
-      <c r="R1" s="16" t="inlineStr">
+      <c r="S1" s="16" t="inlineStr">
         <is>
           <t>AFS</t>
         </is>
       </c>
-      <c r="S1" s="16" t="inlineStr">
+      <c r="T1" s="16" t="inlineStr">
         <is>
           <t>ICBF</t>
         </is>
       </c>
-      <c r="T1" s="16" t="inlineStr">
+      <c r="U1" s="16" t="inlineStr">
         <is>
           <t>Mesozoic Fishes</t>
         </is>
       </c>
-      <c r="U1" s="16" t="inlineStr">
+      <c r="V1" s="16" t="inlineStr">
         <is>
           <t>ICVM</t>
         </is>
       </c>
-      <c r="V1" s="16" t="inlineStr">
+      <c r="W1" s="16" t="inlineStr">
         <is>
           <t>CIESM</t>
         </is>
       </c>
-      <c r="W1" s="16" t="inlineStr">
+      <c r="X1" s="16" t="inlineStr">
         <is>
           <t>Tester Symp</t>
         </is>
       </c>
-      <c r="X1" s="16" t="inlineStr">
+      <c r="Y1" s="16" t="inlineStr">
         <is>
           <t>Age Det Wksp</t>
         </is>
       </c>
-      <c r="Y1" s="16" t="inlineStr">
+      <c r="Z1" s="16" t="inlineStr">
         <is>
           <t>Palaeo/geol</t>
         </is>
       </c>
-      <c r="Z1" s="16" t="inlineStr">
+      <c r="AA1" s="16" t="inlineStr">
         <is>
           <t>SVP</t>
         </is>
       </c>
-      <c r="AA1" s="16" t="inlineStr">
+      <c r="AB1" s="16" t="inlineStr">
         <is>
           <t>SICB</t>
         </is>
       </c>
-      <c r="AB1" s="16" t="inlineStr">
+      <c r="AC1" s="16" t="inlineStr">
         <is>
           <t>SIBM</t>
         </is>
@@ -2499,6 +2549,7 @@
       <c r="Z2" s="19" t="inlineStr"/>
       <c r="AA2" s="19" t="inlineStr"/>
       <c r="AB2" s="19" t="inlineStr"/>
+      <c r="AC2" s="19" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="17" t="n">
@@ -2535,6 +2586,7 @@
       <c r="Z3" s="19" t="inlineStr"/>
       <c r="AA3" s="19" t="inlineStr"/>
       <c r="AB3" s="19" t="inlineStr"/>
+      <c r="AC3" s="19" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="17" t="n">
@@ -2571,6 +2623,7 @@
       <c r="Z4" s="19" t="inlineStr"/>
       <c r="AA4" s="19" t="inlineStr"/>
       <c r="AB4" s="19" t="inlineStr"/>
+      <c r="AC4" s="19" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="17" t="n">
@@ -2607,6 +2660,7 @@
       <c r="Z5" s="19" t="inlineStr"/>
       <c r="AA5" s="19" t="inlineStr"/>
       <c r="AB5" s="19" t="inlineStr"/>
+      <c r="AC5" s="19" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="17" t="n">
@@ -2643,6 +2697,7 @@
       <c r="Z6" s="19" t="inlineStr"/>
       <c r="AA6" s="19" t="inlineStr"/>
       <c r="AB6" s="19" t="inlineStr"/>
+      <c r="AC6" s="19" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="17" t="n">
@@ -2679,6 +2734,7 @@
       <c r="Z7" s="19" t="inlineStr"/>
       <c r="AA7" s="19" t="inlineStr"/>
       <c r="AB7" s="19" t="inlineStr"/>
+      <c r="AC7" s="19" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="17" t="n">
@@ -2715,6 +2771,7 @@
       <c r="Z8" s="19" t="inlineStr"/>
       <c r="AA8" s="19" t="inlineStr"/>
       <c r="AB8" s="19" t="inlineStr"/>
+      <c r="AC8" s="19" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="17" t="n">
@@ -2751,6 +2808,7 @@
       <c r="Z9" s="19" t="inlineStr"/>
       <c r="AA9" s="19" t="inlineStr"/>
       <c r="AB9" s="19" t="inlineStr"/>
+      <c r="AC9" s="19" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="17" t="n">
@@ -2787,6 +2845,7 @@
       <c r="Z10" s="19" t="inlineStr"/>
       <c r="AA10" s="19" t="inlineStr"/>
       <c r="AB10" s="19" t="inlineStr"/>
+      <c r="AC10" s="19" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="17" t="n">
@@ -2823,6 +2882,7 @@
       <c r="Z11" s="19" t="inlineStr"/>
       <c r="AA11" s="19" t="inlineStr"/>
       <c r="AB11" s="19" t="inlineStr"/>
+      <c r="AC11" s="19" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="17" t="n">
@@ -2859,6 +2919,7 @@
       <c r="Z12" s="19" t="inlineStr"/>
       <c r="AA12" s="19" t="inlineStr"/>
       <c r="AB12" s="19" t="inlineStr"/>
+      <c r="AC12" s="19" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="17" t="n">
@@ -2895,6 +2956,7 @@
       <c r="Z13" s="19" t="inlineStr"/>
       <c r="AA13" s="19" t="inlineStr"/>
       <c r="AB13" s="19" t="inlineStr"/>
+      <c r="AC13" s="19" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="17" t="n">
@@ -2931,6 +2993,7 @@
       <c r="Z14" s="19" t="inlineStr"/>
       <c r="AA14" s="19" t="inlineStr"/>
       <c r="AB14" s="19" t="inlineStr"/>
+      <c r="AC14" s="19" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="17" t="n">
@@ -2967,6 +3030,7 @@
       <c r="Z15" s="19" t="inlineStr"/>
       <c r="AA15" s="19" t="inlineStr"/>
       <c r="AB15" s="19" t="inlineStr"/>
+      <c r="AC15" s="19" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="n">
@@ -3003,6 +3067,7 @@
       <c r="Z16" s="19" t="inlineStr"/>
       <c r="AA16" s="19" t="inlineStr"/>
       <c r="AB16" s="19" t="inlineStr"/>
+      <c r="AC16" s="19" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="17" t="n">
@@ -3039,6 +3104,7 @@
       <c r="Z17" s="19" t="inlineStr"/>
       <c r="AA17" s="19" t="inlineStr"/>
       <c r="AB17" s="19" t="inlineStr"/>
+      <c r="AC17" s="19" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="17" t="n">
@@ -3075,6 +3141,7 @@
       <c r="Z18" s="19" t="inlineStr"/>
       <c r="AA18" s="19" t="inlineStr"/>
       <c r="AB18" s="19" t="inlineStr"/>
+      <c r="AC18" s="19" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="17" t="n">
@@ -3111,6 +3178,7 @@
       <c r="Z19" s="19" t="inlineStr"/>
       <c r="AA19" s="19" t="inlineStr"/>
       <c r="AB19" s="19" t="inlineStr"/>
+      <c r="AC19" s="19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="17" t="n">
@@ -3147,6 +3215,7 @@
       <c r="Z20" s="19" t="inlineStr"/>
       <c r="AA20" s="19" t="inlineStr"/>
       <c r="AB20" s="19" t="inlineStr"/>
+      <c r="AC20" s="19" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="17" t="n">
@@ -3183,6 +3252,7 @@
       <c r="Z21" s="19" t="inlineStr"/>
       <c r="AA21" s="19" t="inlineStr"/>
       <c r="AB21" s="19" t="inlineStr"/>
+      <c r="AC21" s="19" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="17" t="n">
@@ -3219,6 +3289,7 @@
       <c r="Z22" s="19" t="inlineStr"/>
       <c r="AA22" s="19" t="inlineStr"/>
       <c r="AB22" s="19" t="inlineStr"/>
+      <c r="AC22" s="19" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="17" t="n">
@@ -3255,6 +3326,7 @@
       <c r="Z23" s="19" t="inlineStr"/>
       <c r="AA23" s="19" t="inlineStr"/>
       <c r="AB23" s="19" t="inlineStr"/>
+      <c r="AC23" s="19" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="17" t="n">
@@ -3291,6 +3363,7 @@
       <c r="Z24" s="19" t="inlineStr"/>
       <c r="AA24" s="19" t="inlineStr"/>
       <c r="AB24" s="19" t="inlineStr"/>
+      <c r="AC24" s="19" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="17" t="n">
@@ -3327,6 +3400,7 @@
       <c r="Z25" s="19" t="inlineStr"/>
       <c r="AA25" s="19" t="inlineStr"/>
       <c r="AB25" s="19" t="inlineStr"/>
+      <c r="AC25" s="19" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="17" t="n">
@@ -3363,6 +3437,7 @@
       <c r="Z26" s="19" t="inlineStr"/>
       <c r="AA26" s="19" t="inlineStr"/>
       <c r="AB26" s="19" t="inlineStr"/>
+      <c r="AC26" s="19" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="17" t="n">
@@ -3399,6 +3474,7 @@
       <c r="Z27" s="19" t="inlineStr"/>
       <c r="AA27" s="19" t="inlineStr"/>
       <c r="AB27" s="19" t="inlineStr"/>
+      <c r="AC27" s="19" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="17" t="n">
@@ -3435,6 +3511,7 @@
       <c r="Z28" s="19" t="inlineStr"/>
       <c r="AA28" s="19" t="inlineStr"/>
       <c r="AB28" s="19" t="inlineStr"/>
+      <c r="AC28" s="19" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="17" t="n">
@@ -3471,6 +3548,7 @@
       <c r="Z29" s="19" t="inlineStr"/>
       <c r="AA29" s="19" t="inlineStr"/>
       <c r="AB29" s="19" t="inlineStr"/>
+      <c r="AC29" s="19" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="17" t="n">
@@ -3507,6 +3585,7 @@
       <c r="Z30" s="19" t="inlineStr"/>
       <c r="AA30" s="19" t="inlineStr"/>
       <c r="AB30" s="19" t="inlineStr"/>
+      <c r="AC30" s="19" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="17" t="n">
@@ -3543,6 +3622,7 @@
       <c r="Z31" s="19" t="inlineStr"/>
       <c r="AA31" s="19" t="inlineStr"/>
       <c r="AB31" s="19" t="inlineStr"/>
+      <c r="AC31" s="19" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="17" t="n">
@@ -3579,6 +3659,7 @@
       <c r="Z32" s="19" t="inlineStr"/>
       <c r="AA32" s="19" t="inlineStr"/>
       <c r="AB32" s="19" t="inlineStr"/>
+      <c r="AC32" s="19" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="17" t="n">
@@ -3615,6 +3696,7 @@
       <c r="Z33" s="19" t="inlineStr"/>
       <c r="AA33" s="19" t="inlineStr"/>
       <c r="AB33" s="19" t="inlineStr"/>
+      <c r="AC33" s="19" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="17" t="n">
@@ -3651,6 +3733,7 @@
       <c r="Z34" s="19" t="inlineStr"/>
       <c r="AA34" s="19" t="inlineStr"/>
       <c r="AB34" s="19" t="inlineStr"/>
+      <c r="AC34" s="19" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="17" t="n">
@@ -3683,14 +3766,15 @@
       <c r="V35" s="19" t="inlineStr"/>
       <c r="W35" s="19" t="inlineStr"/>
       <c r="X35" s="19" t="inlineStr"/>
-      <c r="Y35" s="18" t="inlineStr">
+      <c r="Y35" s="19" t="inlineStr"/>
+      <c r="Z35" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="Z35" s="19" t="inlineStr"/>
       <c r="AA35" s="19" t="inlineStr"/>
       <c r="AB35" s="19" t="inlineStr"/>
+      <c r="AC35" s="19" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="17" t="n">
@@ -3727,6 +3811,7 @@
       <c r="Z36" s="19" t="inlineStr"/>
       <c r="AA36" s="19" t="inlineStr"/>
       <c r="AB36" s="19" t="inlineStr"/>
+      <c r="AC36" s="19" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="17" t="n">
@@ -3763,6 +3848,7 @@
       <c r="Z37" s="19" t="inlineStr"/>
       <c r="AA37" s="19" t="inlineStr"/>
       <c r="AB37" s="19" t="inlineStr"/>
+      <c r="AC37" s="19" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="17" t="n">
@@ -3799,6 +3885,7 @@
       <c r="Z38" s="19" t="inlineStr"/>
       <c r="AA38" s="19" t="inlineStr"/>
       <c r="AB38" s="19" t="inlineStr"/>
+      <c r="AC38" s="19" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="17" t="n">
@@ -3835,6 +3922,7 @@
       <c r="Z39" s="19" t="inlineStr"/>
       <c r="AA39" s="19" t="inlineStr"/>
       <c r="AB39" s="19" t="inlineStr"/>
+      <c r="AC39" s="19" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="17" t="n">
@@ -3871,6 +3959,7 @@
       <c r="Z40" s="19" t="inlineStr"/>
       <c r="AA40" s="19" t="inlineStr"/>
       <c r="AB40" s="19" t="inlineStr"/>
+      <c r="AC40" s="19" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="17" t="n">
@@ -3907,6 +3996,7 @@
       <c r="Z41" s="19" t="inlineStr"/>
       <c r="AA41" s="19" t="inlineStr"/>
       <c r="AB41" s="19" t="inlineStr"/>
+      <c r="AC41" s="19" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="17" t="n">
@@ -3943,6 +4033,7 @@
       <c r="Z42" s="19" t="inlineStr"/>
       <c r="AA42" s="19" t="inlineStr"/>
       <c r="AB42" s="19" t="inlineStr"/>
+      <c r="AC42" s="19" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="17" t="n">
@@ -3979,6 +4070,7 @@
       <c r="Z43" s="19" t="inlineStr"/>
       <c r="AA43" s="19" t="inlineStr"/>
       <c r="AB43" s="19" t="inlineStr"/>
+      <c r="AC43" s="19" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="17" t="n">
@@ -4015,6 +4107,7 @@
       <c r="Z44" s="19" t="inlineStr"/>
       <c r="AA44" s="19" t="inlineStr"/>
       <c r="AB44" s="19" t="inlineStr"/>
+      <c r="AC44" s="19" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="17" t="n">
@@ -4051,6 +4144,7 @@
       <c r="Z45" s="19" t="inlineStr"/>
       <c r="AA45" s="19" t="inlineStr"/>
       <c r="AB45" s="19" t="inlineStr"/>
+      <c r="AC45" s="19" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="17" t="n">
@@ -4087,6 +4181,7 @@
       <c r="Z46" s="19" t="inlineStr"/>
       <c r="AA46" s="19" t="inlineStr"/>
       <c r="AB46" s="19" t="inlineStr"/>
+      <c r="AC46" s="19" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="17" t="n">
@@ -4123,6 +4218,7 @@
       <c r="Z47" s="19" t="inlineStr"/>
       <c r="AA47" s="19" t="inlineStr"/>
       <c r="AB47" s="19" t="inlineStr"/>
+      <c r="AC47" s="19" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="17" t="n">
@@ -4159,6 +4255,7 @@
       <c r="Z48" s="19" t="inlineStr"/>
       <c r="AA48" s="19" t="inlineStr"/>
       <c r="AB48" s="19" t="inlineStr"/>
+      <c r="AC48" s="19" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="17" t="n">
@@ -4195,6 +4292,7 @@
       <c r="Z49" s="19" t="inlineStr"/>
       <c r="AA49" s="19" t="inlineStr"/>
       <c r="AB49" s="19" t="inlineStr"/>
+      <c r="AC49" s="19" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="17" t="n">
@@ -4231,6 +4329,7 @@
       <c r="Z50" s="19" t="inlineStr"/>
       <c r="AA50" s="19" t="inlineStr"/>
       <c r="AB50" s="19" t="inlineStr"/>
+      <c r="AC50" s="19" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="17" t="n">
@@ -4267,6 +4366,7 @@
       <c r="Z51" s="19" t="inlineStr"/>
       <c r="AA51" s="19" t="inlineStr"/>
       <c r="AB51" s="19" t="inlineStr"/>
+      <c r="AC51" s="19" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="17" t="n">
@@ -4303,6 +4403,7 @@
       <c r="Z52" s="19" t="inlineStr"/>
       <c r="AA52" s="19" t="inlineStr"/>
       <c r="AB52" s="19" t="inlineStr"/>
+      <c r="AC52" s="19" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="17" t="n">
@@ -4339,6 +4440,7 @@
       <c r="Z53" s="19" t="inlineStr"/>
       <c r="AA53" s="19" t="inlineStr"/>
       <c r="AB53" s="19" t="inlineStr"/>
+      <c r="AC53" s="19" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="17" t="n">
@@ -4375,6 +4477,7 @@
       <c r="Z54" s="19" t="inlineStr"/>
       <c r="AA54" s="19" t="inlineStr"/>
       <c r="AB54" s="19" t="inlineStr"/>
+      <c r="AC54" s="19" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="17" t="n">
@@ -4411,6 +4514,7 @@
       <c r="Z55" s="19" t="inlineStr"/>
       <c r="AA55" s="19" t="inlineStr"/>
       <c r="AB55" s="19" t="inlineStr"/>
+      <c r="AC55" s="19" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="17" t="n">
@@ -4447,6 +4551,7 @@
       <c r="Z56" s="19" t="inlineStr"/>
       <c r="AA56" s="19" t="inlineStr"/>
       <c r="AB56" s="19" t="inlineStr"/>
+      <c r="AC56" s="19" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="17" t="n">
@@ -4483,6 +4588,7 @@
       <c r="Z57" s="19" t="inlineStr"/>
       <c r="AA57" s="19" t="inlineStr"/>
       <c r="AB57" s="19" t="inlineStr"/>
+      <c r="AC57" s="19" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="17" t="n">
@@ -4519,6 +4625,7 @@
       <c r="Z58" s="19" t="inlineStr"/>
       <c r="AA58" s="19" t="inlineStr"/>
       <c r="AB58" s="19" t="inlineStr"/>
+      <c r="AC58" s="19" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="17" t="n">
@@ -4551,14 +4658,15 @@
       <c r="V59" s="19" t="inlineStr"/>
       <c r="W59" s="19" t="inlineStr"/>
       <c r="X59" s="19" t="inlineStr"/>
-      <c r="Y59" s="18" t="inlineStr">
+      <c r="Y59" s="19" t="inlineStr"/>
+      <c r="Z59" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="Z59" s="19" t="inlineStr"/>
       <c r="AA59" s="19" t="inlineStr"/>
       <c r="AB59" s="19" t="inlineStr"/>
+      <c r="AC59" s="19" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="17" t="n">
@@ -4595,6 +4703,7 @@
       <c r="Z60" s="19" t="inlineStr"/>
       <c r="AA60" s="19" t="inlineStr"/>
       <c r="AB60" s="19" t="inlineStr"/>
+      <c r="AC60" s="19" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="17" t="n">
@@ -4631,6 +4740,7 @@
       <c r="Z61" s="19" t="inlineStr"/>
       <c r="AA61" s="19" t="inlineStr"/>
       <c r="AB61" s="19" t="inlineStr"/>
+      <c r="AC61" s="19" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="17" t="n">
@@ -4663,14 +4773,15 @@
       <c r="V62" s="19" t="inlineStr"/>
       <c r="W62" s="19" t="inlineStr"/>
       <c r="X62" s="19" t="inlineStr"/>
-      <c r="Y62" s="18" t="inlineStr">
+      <c r="Y62" s="19" t="inlineStr"/>
+      <c r="Z62" s="18" t="inlineStr">
         <is>
           <t>Missing — 2 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
-      <c r="Z62" s="19" t="inlineStr"/>
       <c r="AA62" s="19" t="inlineStr"/>
       <c r="AB62" s="19" t="inlineStr"/>
+      <c r="AC62" s="19" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="17" t="n">
@@ -4707,6 +4818,7 @@
       <c r="Z63" s="19" t="inlineStr"/>
       <c r="AA63" s="19" t="inlineStr"/>
       <c r="AB63" s="19" t="inlineStr"/>
+      <c r="AC63" s="19" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="17" t="n">
@@ -4741,12 +4853,13 @@
       <c r="X64" s="19" t="inlineStr"/>
       <c r="Y64" s="19" t="inlineStr"/>
       <c r="Z64" s="19" t="inlineStr"/>
-      <c r="AA64" s="18" t="inlineStr">
+      <c r="AA64" s="19" t="inlineStr"/>
+      <c r="AB64" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AB64" s="19" t="inlineStr"/>
+      <c r="AC64" s="19" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="17" t="n">
@@ -4783,6 +4896,7 @@
       <c r="Z65" s="19" t="inlineStr"/>
       <c r="AA65" s="19" t="inlineStr"/>
       <c r="AB65" s="19" t="inlineStr"/>
+      <c r="AC65" s="19" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="17" t="n">
@@ -4815,18 +4929,19 @@
       <c r="V66" s="19" t="inlineStr"/>
       <c r="W66" s="19" t="inlineStr"/>
       <c r="X66" s="19" t="inlineStr"/>
-      <c r="Y66" s="18" t="inlineStr">
+      <c r="Y66" s="19" t="inlineStr"/>
+      <c r="Z66" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="Z66" s="19" t="inlineStr"/>
-      <c r="AA66" s="18" t="inlineStr">
+      <c r="AA66" s="19" t="inlineStr"/>
+      <c r="AB66" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AB66" s="19" t="inlineStr"/>
+      <c r="AC66" s="19" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="17" t="n">
@@ -4863,6 +4978,7 @@
       <c r="Z67" s="19" t="inlineStr"/>
       <c r="AA67" s="19" t="inlineStr"/>
       <c r="AB67" s="19" t="inlineStr"/>
+      <c r="AC67" s="19" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="17" t="n">
@@ -4899,6 +5015,7 @@
       <c r="Z68" s="19" t="inlineStr"/>
       <c r="AA68" s="19" t="inlineStr"/>
       <c r="AB68" s="19" t="inlineStr"/>
+      <c r="AC68" s="19" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="17" t="n">
@@ -4934,15 +5051,16 @@
       <c r="U69" s="19" t="inlineStr"/>
       <c r="V69" s="19" t="inlineStr"/>
       <c r="W69" s="19" t="inlineStr"/>
-      <c r="X69" s="18" t="inlineStr">
+      <c r="X69" s="19" t="inlineStr"/>
+      <c r="Y69" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 5 abstracts cited by the corpus</t>
         </is>
       </c>
-      <c r="Y69" s="19" t="inlineStr"/>
       <c r="Z69" s="19" t="inlineStr"/>
       <c r="AA69" s="19" t="inlineStr"/>
       <c r="AB69" s="19" t="inlineStr"/>
+      <c r="AC69" s="19" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="17" t="n">
@@ -4979,14 +5097,15 @@
       <c r="V70" s="19" t="inlineStr"/>
       <c r="W70" s="19" t="inlineStr"/>
       <c r="X70" s="19" t="inlineStr"/>
-      <c r="Y70" s="18" t="inlineStr">
+      <c r="Y70" s="19" t="inlineStr"/>
+      <c r="Z70" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="Z70" s="19" t="inlineStr"/>
       <c r="AA70" s="19" t="inlineStr"/>
       <c r="AB70" s="19" t="inlineStr"/>
+      <c r="AC70" s="19" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="17" t="n">
@@ -5013,12 +5132,12 @@
       <c r="L71" s="19" t="inlineStr"/>
       <c r="M71" s="19" t="inlineStr"/>
       <c r="N71" s="19" t="inlineStr"/>
-      <c r="O71" s="18" t="inlineStr">
+      <c r="O71" s="19" t="inlineStr"/>
+      <c r="P71" s="18" t="inlineStr">
         <is>
           <t>Tokyo, Japan; Missing — 37 abstracts cited by the corpus [Published 1986]</t>
         </is>
       </c>
-      <c r="P71" s="19" t="inlineStr"/>
       <c r="Q71" s="19" t="inlineStr"/>
       <c r="R71" s="19" t="inlineStr"/>
       <c r="S71" s="19" t="inlineStr"/>
@@ -5029,12 +5148,13 @@
       <c r="X71" s="19" t="inlineStr"/>
       <c r="Y71" s="19" t="inlineStr"/>
       <c r="Z71" s="19" t="inlineStr"/>
-      <c r="AA71" s="18" t="inlineStr">
+      <c r="AA71" s="19" t="inlineStr"/>
+      <c r="AB71" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AB71" s="19" t="inlineStr"/>
+      <c r="AC71" s="19" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="17" t="n">
@@ -5075,6 +5195,7 @@
       <c r="Z72" s="19" t="inlineStr"/>
       <c r="AA72" s="19" t="inlineStr"/>
       <c r="AB72" s="19" t="inlineStr"/>
+      <c r="AC72" s="19" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="17" t="n">
@@ -5111,14 +5232,15 @@
       <c r="V73" s="19" t="inlineStr"/>
       <c r="W73" s="19" t="inlineStr"/>
       <c r="X73" s="19" t="inlineStr"/>
-      <c r="Y73" s="18" t="inlineStr">
+      <c r="Y73" s="19" t="inlineStr"/>
+      <c r="Z73" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="Z73" s="19" t="inlineStr"/>
       <c r="AA73" s="19" t="inlineStr"/>
       <c r="AB73" s="19" t="inlineStr"/>
+      <c r="AC73" s="19" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="17" t="n">
@@ -5156,13 +5278,14 @@
       <c r="W74" s="19" t="inlineStr"/>
       <c r="X74" s="19" t="inlineStr"/>
       <c r="Y74" s="19" t="inlineStr"/>
-      <c r="Z74" s="18" t="inlineStr">
+      <c r="Z74" s="19" t="inlineStr"/>
+      <c r="AA74" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA74" s="19" t="inlineStr"/>
       <c r="AB74" s="19" t="inlineStr"/>
+      <c r="AC74" s="19" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="17" t="n">
@@ -5203,6 +5326,7 @@
       <c r="Z75" s="19" t="inlineStr"/>
       <c r="AA75" s="19" t="inlineStr"/>
       <c r="AB75" s="19" t="inlineStr"/>
+      <c r="AC75" s="19" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="17" t="n">
@@ -5243,6 +5367,7 @@
       <c r="Z76" s="19" t="inlineStr"/>
       <c r="AA76" s="19" t="inlineStr"/>
       <c r="AB76" s="19" t="inlineStr"/>
+      <c r="AC76" s="19" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="17" t="n">
@@ -5263,7 +5388,11 @@
       <c r="F77" s="19" t="inlineStr"/>
       <c r="G77" s="19" t="inlineStr"/>
       <c r="H77" s="19" t="inlineStr"/>
-      <c r="I77" s="19" t="inlineStr"/>
+      <c r="I77" s="18" t="inlineStr">
+        <is>
+          <t>Maringa, PR, Brazil; Missing — 12 chondrichthyan (of 196) abstracts in the book (Soares &amp; Petean 2023 Table 1), titles only in their Tab. S1</t>
+        </is>
+      </c>
       <c r="J77" s="19" t="inlineStr"/>
       <c r="K77" s="19" t="inlineStr"/>
       <c r="L77" s="19" t="inlineStr"/>
@@ -5280,13 +5409,14 @@
       <c r="W77" s="19" t="inlineStr"/>
       <c r="X77" s="19" t="inlineStr"/>
       <c r="Y77" s="19" t="inlineStr"/>
-      <c r="Z77" s="18" t="inlineStr">
+      <c r="Z77" s="19" t="inlineStr"/>
+      <c r="AA77" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA77" s="19" t="inlineStr"/>
       <c r="AB77" s="19" t="inlineStr"/>
+      <c r="AC77" s="19" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="17" t="n">
@@ -5324,13 +5454,14 @@
       <c r="W78" s="19" t="inlineStr"/>
       <c r="X78" s="19" t="inlineStr"/>
       <c r="Y78" s="19" t="inlineStr"/>
-      <c r="Z78" s="18" t="inlineStr">
+      <c r="Z78" s="19" t="inlineStr"/>
+      <c r="AA78" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA78" s="19" t="inlineStr"/>
       <c r="AB78" s="19" t="inlineStr"/>
+      <c r="AC78" s="19" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="17" t="n">
@@ -5351,18 +5482,22 @@
       <c r="F79" s="19" t="inlineStr"/>
       <c r="G79" s="19" t="inlineStr"/>
       <c r="H79" s="19" t="inlineStr"/>
-      <c r="I79" s="19" t="inlineStr"/>
+      <c r="I79" s="18" t="inlineStr">
+        <is>
+          <t>Sao Paulo, SP, Brazil; Missing — 12 chondrichthyan (of 241) abstracts in the book (Soares &amp; Petean 2023 Table 1), titles only in their Tab. S1</t>
+        </is>
+      </c>
       <c r="J79" s="19" t="inlineStr"/>
       <c r="K79" s="19" t="inlineStr"/>
       <c r="L79" s="19" t="inlineStr"/>
       <c r="M79" s="19" t="inlineStr"/>
       <c r="N79" s="19" t="inlineStr"/>
-      <c r="O79" s="18" t="inlineStr">
+      <c r="O79" s="19" t="inlineStr"/>
+      <c r="P79" s="18" t="inlineStr">
         <is>
           <t>Bangkok, Thailand; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="P79" s="19" t="inlineStr"/>
       <c r="Q79" s="19" t="inlineStr"/>
       <c r="R79" s="19" t="inlineStr"/>
       <c r="S79" s="19" t="inlineStr"/>
@@ -5371,18 +5506,19 @@
       <c r="V79" s="19" t="inlineStr"/>
       <c r="W79" s="19" t="inlineStr"/>
       <c r="X79" s="19" t="inlineStr"/>
-      <c r="Y79" s="18" t="inlineStr">
+      <c r="Y79" s="19" t="inlineStr"/>
+      <c r="Z79" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="Z79" s="18" t="inlineStr">
+      <c r="AA79" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 2 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA79" s="19" t="inlineStr"/>
       <c r="AB79" s="19" t="inlineStr"/>
+      <c r="AC79" s="19" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="17" t="n">
@@ -5419,18 +5555,19 @@
       <c r="V80" s="19" t="inlineStr"/>
       <c r="W80" s="19" t="inlineStr"/>
       <c r="X80" s="19" t="inlineStr"/>
-      <c r="Y80" s="18" t="inlineStr">
+      <c r="Y80" s="19" t="inlineStr"/>
+      <c r="Z80" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 2 abstracts cited by the corpus</t>
         </is>
       </c>
-      <c r="Z80" s="18" t="inlineStr">
+      <c r="AA80" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA80" s="19" t="inlineStr"/>
       <c r="AB80" s="19" t="inlineStr"/>
+      <c r="AC80" s="19" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="17" t="n">
@@ -5451,7 +5588,11 @@
       <c r="F81" s="19" t="inlineStr"/>
       <c r="G81" s="19" t="inlineStr"/>
       <c r="H81" s="19" t="inlineStr"/>
-      <c r="I81" s="19" t="inlineStr"/>
+      <c r="I81" s="18" t="inlineStr">
+        <is>
+          <t>Campinas, SP, Brazil; Missing — 16 chondrichthyan (of 318) abstracts in the book (Soares &amp; Petean 2023 Table 1), titles only in their Tab. S1</t>
+        </is>
+      </c>
       <c r="J81" s="19" t="inlineStr"/>
       <c r="K81" s="19" t="inlineStr"/>
       <c r="L81" s="19" t="inlineStr"/>
@@ -5468,13 +5609,14 @@
       <c r="W81" s="19" t="inlineStr"/>
       <c r="X81" s="19" t="inlineStr"/>
       <c r="Y81" s="19" t="inlineStr"/>
-      <c r="Z81" s="18" t="inlineStr">
+      <c r="Z81" s="19" t="inlineStr"/>
+      <c r="AA81" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 2 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA81" s="19" t="inlineStr"/>
       <c r="AB81" s="19" t="inlineStr"/>
+      <c r="AC81" s="19" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="17" t="n">
@@ -5512,13 +5654,14 @@
       <c r="W82" s="19" t="inlineStr"/>
       <c r="X82" s="19" t="inlineStr"/>
       <c r="Y82" s="19" t="inlineStr"/>
-      <c r="Z82" s="18" t="inlineStr">
+      <c r="Z82" s="19" t="inlineStr"/>
+      <c r="AA82" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 2 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA82" s="19" t="inlineStr"/>
       <c r="AB82" s="19" t="inlineStr"/>
+      <c r="AC82" s="19" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="17" t="n">
@@ -5542,23 +5685,31 @@
       <c r="E83" s="19" t="inlineStr"/>
       <c r="F83" s="19" t="inlineStr"/>
       <c r="G83" s="19" t="inlineStr"/>
-      <c r="H83" s="19" t="inlineStr"/>
-      <c r="I83" s="19" t="inlineStr"/>
+      <c r="H83" s="18" t="inlineStr">
+        <is>
+          <t>Ilheus, BA, Brazil; Missing — 74 abstracts in the book (Soares &amp; Petean 2023 Table 1), titles only in their Tab. S1</t>
+        </is>
+      </c>
+      <c r="I83" s="18" t="inlineStr">
+        <is>
+          <t>Sao Paulo, SP, Brazil; Missing — 7 chondrichthyan (of 399) abstracts in the book (Soares &amp; Petean 2023 Table 1), titles only in their Tab. S1</t>
+        </is>
+      </c>
       <c r="J83" s="19" t="inlineStr"/>
       <c r="K83" s="19" t="inlineStr"/>
       <c r="L83" s="19" t="inlineStr"/>
       <c r="M83" s="19" t="inlineStr"/>
-      <c r="N83" s="18" t="inlineStr">
+      <c r="N83" s="19" t="inlineStr"/>
+      <c r="O83" s="18" t="inlineStr">
         <is>
           <t>Prague, Czech Republic; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="O83" s="18" t="inlineStr">
+      <c r="P83" s="18" t="inlineStr">
         <is>
           <t>Noumea, New Caledonia; Missing — 11 abstracts cited by the corpus [Published 1999, 2002]</t>
         </is>
       </c>
-      <c r="P83" s="19" t="inlineStr"/>
       <c r="Q83" s="19" t="inlineStr"/>
       <c r="R83" s="19" t="inlineStr"/>
       <c r="S83" s="19" t="inlineStr"/>
@@ -5567,18 +5718,19 @@
       <c r="V83" s="19" t="inlineStr"/>
       <c r="W83" s="19" t="inlineStr"/>
       <c r="X83" s="19" t="inlineStr"/>
-      <c r="Y83" s="18" t="inlineStr">
+      <c r="Y83" s="19" t="inlineStr"/>
+      <c r="Z83" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="Z83" s="18" t="inlineStr">
+      <c r="AA83" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 2 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA83" s="19" t="inlineStr"/>
       <c r="AB83" s="19" t="inlineStr"/>
+      <c r="AC83" s="19" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="17" t="n">
@@ -5620,13 +5772,14 @@
       <c r="W84" s="19" t="inlineStr"/>
       <c r="X84" s="19" t="inlineStr"/>
       <c r="Y84" s="19" t="inlineStr"/>
-      <c r="Z84" s="18" t="inlineStr">
+      <c r="Z84" s="19" t="inlineStr"/>
+      <c r="AA84" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 2 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA84" s="19" t="inlineStr"/>
       <c r="AB84" s="19" t="inlineStr"/>
+      <c r="AC84" s="19" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="17" t="n">
@@ -5651,7 +5804,11 @@
       <c r="F85" s="19" t="inlineStr"/>
       <c r="G85" s="19" t="inlineStr"/>
       <c r="H85" s="19" t="inlineStr"/>
-      <c r="I85" s="19" t="inlineStr"/>
+      <c r="I85" s="18" t="inlineStr">
+        <is>
+          <t>?; Missing — 40 chondrichthyan (of 610) abstracts in the book (Soares &amp; Petean 2023 Table 1), titles only in their Tab. S1</t>
+        </is>
+      </c>
       <c r="J85" s="19" t="inlineStr"/>
       <c r="K85" s="19" t="inlineStr"/>
       <c r="L85" s="19" t="inlineStr"/>
@@ -5668,13 +5825,14 @@
       <c r="W85" s="19" t="inlineStr"/>
       <c r="X85" s="19" t="inlineStr"/>
       <c r="Y85" s="19" t="inlineStr"/>
-      <c r="Z85" s="18" t="inlineStr">
+      <c r="Z85" s="19" t="inlineStr"/>
+      <c r="AA85" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 4 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA85" s="19" t="inlineStr"/>
-      <c r="AB85" s="18" t="inlineStr">
+      <c r="AB85" s="19" t="inlineStr"/>
+      <c r="AC85" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
         </is>
@@ -5702,7 +5860,11 @@
       <c r="E86" s="19" t="inlineStr"/>
       <c r="F86" s="19" t="inlineStr"/>
       <c r="G86" s="19" t="inlineStr"/>
-      <c r="H86" s="19" t="inlineStr"/>
+      <c r="H86" s="18" t="inlineStr">
+        <is>
+          <t>Santos, SP, Brazil; Missing — 1 abstract cited by the corpus of 98 in the book (Soares &amp; Petean 2023) [Published 2002]</t>
+        </is>
+      </c>
       <c r="I86" s="19" t="inlineStr"/>
       <c r="J86" s="19" t="inlineStr"/>
       <c r="K86" s="19" t="inlineStr"/>
@@ -5719,18 +5881,19 @@
       <c r="V86" s="19" t="inlineStr"/>
       <c r="W86" s="19" t="inlineStr"/>
       <c r="X86" s="19" t="inlineStr"/>
-      <c r="Y86" s="18" t="inlineStr">
+      <c r="Y86" s="19" t="inlineStr"/>
+      <c r="Z86" s="18" t="inlineStr">
         <is>
           <t>Missing — 3 abstracts cited by the corpus [3 distinct meetings]</t>
         </is>
       </c>
-      <c r="Z86" s="18" t="inlineStr">
+      <c r="AA86" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 4 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA86" s="19" t="inlineStr"/>
       <c r="AB86" s="19" t="inlineStr"/>
+      <c r="AC86" s="19" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="17" t="n">
@@ -5755,7 +5918,11 @@
       <c r="F87" s="19" t="inlineStr"/>
       <c r="G87" s="19" t="inlineStr"/>
       <c r="H87" s="19" t="inlineStr"/>
-      <c r="I87" s="19" t="inlineStr"/>
+      <c r="I87" s="18" t="inlineStr">
+        <is>
+          <t>Sao Leopoldo, RS, Brazil; Missing — 13 chondrichthyan (of 577) abstracts in the book (Soares &amp; Petean 2023 Table 1), titles only in their Tab. S1</t>
+        </is>
+      </c>
       <c r="J87" s="19" t="inlineStr"/>
       <c r="K87" s="19" t="inlineStr"/>
       <c r="L87" s="19" t="inlineStr"/>
@@ -5766,12 +5933,12 @@
       <c r="Q87" s="19" t="inlineStr"/>
       <c r="R87" s="19" t="inlineStr"/>
       <c r="S87" s="19" t="inlineStr"/>
-      <c r="T87" s="18" t="inlineStr">
+      <c r="T87" s="19" t="inlineStr"/>
+      <c r="U87" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="U87" s="19" t="inlineStr"/>
       <c r="V87" s="19" t="inlineStr"/>
       <c r="W87" s="19" t="inlineStr"/>
       <c r="X87" s="19" t="inlineStr"/>
@@ -5779,6 +5946,7 @@
       <c r="Z87" s="19" t="inlineStr"/>
       <c r="AA87" s="19" t="inlineStr"/>
       <c r="AB87" s="19" t="inlineStr"/>
+      <c r="AC87" s="19" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="17" t="n">
@@ -5804,17 +5972,17 @@
       <c r="G88" s="19" t="inlineStr"/>
       <c r="H88" s="18" t="inlineStr">
         <is>
-          <t>?; Missing — 1 abstract cited by the corpus</t>
+          <t>Joao Pessoa, PB, Brazil; Missing — 71 abstracts in the book (Soares &amp; Petean 2023 Table 1), titles only in their Tab. S1</t>
         </is>
       </c>
       <c r="I88" s="19" t="inlineStr"/>
       <c r="J88" s="19" t="inlineStr"/>
-      <c r="K88" s="18" t="inlineStr">
+      <c r="K88" s="19" t="inlineStr"/>
+      <c r="L88" s="18" t="inlineStr">
         <is>
           <t>Xel Ha, Mexico; Missing — 1 abstract cited by the corpus [Published 2004]</t>
         </is>
       </c>
-      <c r="L88" s="19" t="inlineStr"/>
       <c r="M88" s="19" t="inlineStr"/>
       <c r="N88" s="19" t="inlineStr"/>
       <c r="O88" s="19" t="inlineStr"/>
@@ -5827,26 +5995,27 @@
       <c r="V88" s="19" t="inlineStr"/>
       <c r="W88" s="19" t="inlineStr"/>
       <c r="X88" s="19" t="inlineStr"/>
-      <c r="Y88" s="18" t="inlineStr">
+      <c r="Y88" s="19" t="inlineStr"/>
+      <c r="Z88" s="18" t="inlineStr">
         <is>
           <t>Missing — 7 abstracts cited by the corpus [6 distinct meetings]</t>
         </is>
       </c>
-      <c r="Z88" s="18" t="inlineStr">
+      <c r="AA88" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 4 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA88" s="19" t="inlineStr"/>
       <c r="AB88" s="19" t="inlineStr"/>
+      <c r="AC88" s="19" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="17" t="n">
         <v>2003</v>
       </c>
-      <c r="B89" s="22" t="inlineStr">
-        <is>
-          <t>Manaus, Brazil; OCR — degraded phone scan — 0 abstracts recovered — flatbed re-scan needed (Carylanne)</t>
+      <c r="B89" s="20" t="inlineStr">
+        <is>
+          <t>Manaus, Brazil; Ingested — meeting CD-ROM, one born-digital PDF per abstract (Carylanne)</t>
         </is>
       </c>
       <c r="C89" s="20" t="inlineStr">
@@ -5863,7 +6032,11 @@
       <c r="F89" s="19" t="inlineStr"/>
       <c r="G89" s="19" t="inlineStr"/>
       <c r="H89" s="19" t="inlineStr"/>
-      <c r="I89" s="19" t="inlineStr"/>
+      <c r="I89" s="18" t="inlineStr">
+        <is>
+          <t>Sao Paulo, SP, Brazil; Missing — 7 chondrichthyan (of 520) abstracts in the book (Soares &amp; Petean 2023 Table 1), titles only in their Tab. S1</t>
+        </is>
+      </c>
       <c r="J89" s="19" t="inlineStr"/>
       <c r="K89" s="19" t="inlineStr"/>
       <c r="L89" s="19" t="inlineStr"/>
@@ -5879,26 +6052,27 @@
       <c r="V89" s="19" t="inlineStr"/>
       <c r="W89" s="19" t="inlineStr"/>
       <c r="X89" s="19" t="inlineStr"/>
-      <c r="Y89" s="18" t="inlineStr">
+      <c r="Y89" s="19" t="inlineStr"/>
+      <c r="Z89" s="18" t="inlineStr">
         <is>
           <t>Missing — 4 abstracts cited by the corpus [4 distinct meetings; Published 2006]</t>
         </is>
       </c>
-      <c r="Z89" s="18" t="inlineStr">
+      <c r="AA89" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 2 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA89" s="19" t="inlineStr"/>
       <c r="AB89" s="19" t="inlineStr"/>
+      <c r="AC89" s="19" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="17" t="n">
         <v>2004</v>
       </c>
-      <c r="B90" s="21" t="inlineStr">
-        <is>
-          <t>Norman, OK; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+      <c r="B90" s="20" t="inlineStr">
+        <is>
+          <t>Norman, OK; Ingested — meeting CD-ROM, one born-digital PDF per abstract (Carylanne)</t>
         </is>
       </c>
       <c r="C90" s="20" t="inlineStr">
@@ -5914,43 +6088,48 @@
       <c r="E90" s="19" t="inlineStr"/>
       <c r="F90" s="19" t="inlineStr"/>
       <c r="G90" s="19" t="inlineStr"/>
-      <c r="H90" s="19" t="inlineStr"/>
-      <c r="I90" s="20" t="inlineStr">
+      <c r="H90" s="18" t="inlineStr">
+        <is>
+          <t>Recife, PE, Brazil; Missing — 97 abstracts in the book (Soares &amp; Petean 2023 Table 1), titles only in their Tab. S1</t>
+        </is>
+      </c>
+      <c r="I90" s="19" t="inlineStr"/>
+      <c r="J90" s="20" t="inlineStr">
         <is>
           <t>Ciudad Universitaria, Mexico City; Ingested — Fable extraction 2026-09-17, 44 abstracts</t>
         </is>
       </c>
-      <c r="J90" s="19" t="inlineStr"/>
-      <c r="K90" s="18" t="inlineStr">
+      <c r="K90" s="19" t="inlineStr"/>
+      <c r="L90" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="L90" s="19" t="inlineStr"/>
       <c r="M90" s="19" t="inlineStr"/>
       <c r="N90" s="19" t="inlineStr"/>
       <c r="O90" s="19" t="inlineStr"/>
       <c r="P90" s="19" t="inlineStr"/>
       <c r="Q90" s="19" t="inlineStr"/>
       <c r="R90" s="19" t="inlineStr"/>
-      <c r="S90" s="18" t="inlineStr">
+      <c r="S90" s="19" t="inlineStr"/>
+      <c r="T90" s="18" t="inlineStr">
         <is>
           <t>Manaus, Brazil; Missing — 4 abstracts cited by the corpus</t>
         </is>
       </c>
-      <c r="T90" s="19" t="inlineStr"/>
       <c r="U90" s="19" t="inlineStr"/>
       <c r="V90" s="19" t="inlineStr"/>
       <c r="W90" s="19" t="inlineStr"/>
       <c r="X90" s="19" t="inlineStr"/>
-      <c r="Y90" s="18" t="inlineStr">
+      <c r="Y90" s="19" t="inlineStr"/>
+      <c r="Z90" s="18" t="inlineStr">
         <is>
           <t>Missing — 2 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
-      <c r="Z90" s="19" t="inlineStr"/>
       <c r="AA90" s="19" t="inlineStr"/>
       <c r="AB90" s="19" t="inlineStr"/>
+      <c r="AC90" s="19" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="17" t="n">
@@ -5975,7 +6154,11 @@
       <c r="F91" s="19" t="inlineStr"/>
       <c r="G91" s="19" t="inlineStr"/>
       <c r="H91" s="19" t="inlineStr"/>
-      <c r="I91" s="19" t="inlineStr"/>
+      <c r="I91" s="18" t="inlineStr">
+        <is>
+          <t>Joao Pessoa, PB, Brazil; Missing — 35 chondrichthyan (of 780) abstracts in the book (Soares &amp; Petean 2023 Table 1), titles only in their Tab. S1</t>
+        </is>
+      </c>
       <c r="J91" s="19" t="inlineStr"/>
       <c r="K91" s="19" t="inlineStr"/>
       <c r="L91" s="19" t="inlineStr"/>
@@ -5986,27 +6169,28 @@
       <c r="Q91" s="19" t="inlineStr"/>
       <c r="R91" s="19" t="inlineStr"/>
       <c r="S91" s="19" t="inlineStr"/>
-      <c r="T91" s="18" t="inlineStr">
+      <c r="T91" s="19" t="inlineStr"/>
+      <c r="U91" s="18" t="inlineStr">
         <is>
           <t>Miraflores de la Sierra, Madrid, Spain; Missing — 2 abstracts cited by the corpus</t>
         </is>
       </c>
-      <c r="U91" s="19" t="inlineStr"/>
       <c r="V91" s="19" t="inlineStr"/>
       <c r="W91" s="19" t="inlineStr"/>
       <c r="X91" s="19" t="inlineStr"/>
-      <c r="Y91" s="18" t="inlineStr">
+      <c r="Y91" s="19" t="inlineStr"/>
+      <c r="Z91" s="18" t="inlineStr">
         <is>
           <t>Missing — 2 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
-      <c r="Z91" s="18" t="inlineStr">
+      <c r="AA91" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA91" s="19" t="inlineStr"/>
       <c r="AB91" s="19" t="inlineStr"/>
+      <c r="AC91" s="19" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="17" t="n">
@@ -6019,7 +6203,7 @@
       </c>
       <c r="C92" s="20" t="inlineStr">
         <is>
-          <t>New Orleans, LA (169); Ingested</t>
+          <t>New Orleans, LA (168); Ingested</t>
         </is>
       </c>
       <c r="D92" s="24" t="inlineStr">
@@ -6030,15 +6214,19 @@
       <c r="E92" s="19" t="inlineStr"/>
       <c r="F92" s="19" t="inlineStr"/>
       <c r="G92" s="19" t="inlineStr"/>
-      <c r="H92" s="19" t="inlineStr"/>
+      <c r="H92" s="18" t="inlineStr">
+        <is>
+          <t>Itajai, SC, Brazil; Missing — 88 abstracts in the book (Soares &amp; Petean 2023 Table 1), titles only in their Tab. S1</t>
+        </is>
+      </c>
       <c r="I92" s="19" t="inlineStr"/>
       <c r="J92" s="19" t="inlineStr"/>
-      <c r="K92" s="18" t="inlineStr">
+      <c r="K92" s="19" t="inlineStr"/>
+      <c r="L92" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 10 abstracts cited by the corpus</t>
         </is>
       </c>
-      <c r="L92" s="19" t="inlineStr"/>
       <c r="M92" s="19" t="inlineStr"/>
       <c r="N92" s="19" t="inlineStr"/>
       <c r="O92" s="19" t="inlineStr"/>
@@ -6051,18 +6239,19 @@
       <c r="V92" s="19" t="inlineStr"/>
       <c r="W92" s="19" t="inlineStr"/>
       <c r="X92" s="19" t="inlineStr"/>
-      <c r="Y92" s="18" t="inlineStr">
+      <c r="Y92" s="19" t="inlineStr"/>
+      <c r="Z92" s="18" t="inlineStr">
         <is>
           <t>Missing — 5 abstracts cited by the corpus [5 distinct meetings; Published 2007]</t>
         </is>
       </c>
-      <c r="Z92" s="18" t="inlineStr">
+      <c r="AA92" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 3 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA92" s="19" t="inlineStr"/>
-      <c r="AB92" s="18" t="inlineStr">
+      <c r="AB92" s="19" t="inlineStr"/>
+      <c r="AC92" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 4 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
@@ -6079,7 +6268,7 @@
       </c>
       <c r="C93" s="20" t="inlineStr">
         <is>
-          <t>St. Louis, MO (138); Ingested</t>
+          <t>St. Louis, MO (134); Ingested</t>
         </is>
       </c>
       <c r="D93" s="24" t="inlineStr">
@@ -6095,42 +6284,47 @@
       <c r="F93" s="19" t="inlineStr"/>
       <c r="G93" s="19" t="inlineStr"/>
       <c r="H93" s="19" t="inlineStr"/>
-      <c r="I93" s="19" t="inlineStr"/>
+      <c r="I93" s="18" t="inlineStr">
+        <is>
+          <t>Itajai, SC, Brazil; Missing — 34 chondrichthyan (of 1037) abstracts in the book (Soares &amp; Petean 2023 Table 1), titles only in their Tab. S1</t>
+        </is>
+      </c>
       <c r="J93" s="19" t="inlineStr"/>
-      <c r="K93" s="18" t="inlineStr">
+      <c r="K93" s="19" t="inlineStr"/>
+      <c r="L93" s="18" t="inlineStr">
         <is>
           <t>Punta Cana, Dominican Republic; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="L93" s="19" t="inlineStr"/>
       <c r="M93" s="19" t="inlineStr"/>
       <c r="N93" s="19" t="inlineStr"/>
       <c r="O93" s="19" t="inlineStr"/>
       <c r="P93" s="19" t="inlineStr"/>
       <c r="Q93" s="19" t="inlineStr"/>
-      <c r="R93" s="18" t="inlineStr">
+      <c r="R93" s="19" t="inlineStr"/>
+      <c r="S93" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 6 abstracts cited by the corpus</t>
         </is>
       </c>
-      <c r="S93" s="19" t="inlineStr"/>
       <c r="T93" s="19" t="inlineStr"/>
       <c r="U93" s="19" t="inlineStr"/>
       <c r="V93" s="19" t="inlineStr"/>
       <c r="W93" s="19" t="inlineStr"/>
       <c r="X93" s="19" t="inlineStr"/>
-      <c r="Y93" s="18" t="inlineStr">
+      <c r="Y93" s="19" t="inlineStr"/>
+      <c r="Z93" s="18" t="inlineStr">
         <is>
           <t>Missing — 3 abstracts cited by the corpus [3 distinct meetings]</t>
         </is>
       </c>
-      <c r="Z93" s="18" t="inlineStr">
+      <c r="AA93" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA93" s="19" t="inlineStr"/>
-      <c r="AB93" s="18" t="inlineStr">
+      <c r="AB93" s="19" t="inlineStr"/>
+      <c r="AC93" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 3 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
@@ -6162,13 +6356,17 @@
       </c>
       <c r="F94" s="19" t="inlineStr"/>
       <c r="G94" s="19" t="inlineStr"/>
-      <c r="H94" s="19" t="inlineStr"/>
-      <c r="I94" s="20" t="inlineStr">
+      <c r="H94" s="18" t="inlineStr">
+        <is>
+          <t>Fortaleza, CE, Brazil; Missing — 96 abstracts in the book (Soares &amp; Petean 2023 Table 1), titles only in their Tab. S1</t>
+        </is>
+      </c>
+      <c r="I94" s="19" t="inlineStr"/>
+      <c r="J94" s="20" t="inlineStr">
         <is>
           <t>Ciudad Universitaria, Mexico City; Ingested — Fable extraction 2026-09-17, 58 abstracts</t>
         </is>
       </c>
-      <c r="J94" s="19" t="inlineStr"/>
       <c r="K94" s="19" t="inlineStr"/>
       <c r="L94" s="19" t="inlineStr"/>
       <c r="M94" s="19" t="inlineStr"/>
@@ -6183,18 +6381,19 @@
       <c r="V94" s="19" t="inlineStr"/>
       <c r="W94" s="19" t="inlineStr"/>
       <c r="X94" s="19" t="inlineStr"/>
-      <c r="Y94" s="18" t="inlineStr">
+      <c r="Y94" s="19" t="inlineStr"/>
+      <c r="Z94" s="18" t="inlineStr">
         <is>
           <t>Missing — 6 abstracts cited by the corpus [6 distinct meetings]</t>
         </is>
       </c>
-      <c r="Z94" s="18" t="inlineStr">
+      <c r="AA94" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA94" s="19" t="inlineStr"/>
-      <c r="AB94" s="18" t="inlineStr">
+      <c r="AB94" s="19" t="inlineStr"/>
+      <c r="AC94" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 2 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
@@ -6211,7 +6410,7 @@
       </c>
       <c r="C95" s="20" t="inlineStr">
         <is>
-          <t>Portland, OR (161); Ingested</t>
+          <t>Portland, OR (160); Ingested</t>
         </is>
       </c>
       <c r="D95" s="24" t="inlineStr">
@@ -6223,46 +6422,51 @@
       <c r="F95" s="19" t="inlineStr"/>
       <c r="G95" s="19" t="inlineStr"/>
       <c r="H95" s="19" t="inlineStr"/>
-      <c r="I95" s="19" t="inlineStr"/>
+      <c r="I95" s="18" t="inlineStr">
+        <is>
+          <t>Cuiaba, MT, Brazil; Missing — 15 chondrichthyan (of 527) abstracts in the book (Soares &amp; Petean 2023 Table 1), titles only in their Tab. S1</t>
+        </is>
+      </c>
       <c r="J95" s="19" t="inlineStr"/>
-      <c r="K95" s="18" t="inlineStr">
+      <c r="K95" s="19" t="inlineStr"/>
+      <c r="L95" s="18" t="inlineStr">
         <is>
           <t>Cumana, Venezuela; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="L95" s="19" t="inlineStr"/>
       <c r="M95" s="19" t="inlineStr"/>
       <c r="N95" s="19" t="inlineStr"/>
-      <c r="O95" s="25" t="inlineStr">
+      <c r="O95" s="19" t="inlineStr"/>
+      <c r="P95" s="25" t="inlineStr">
         <is>
           <t>Fremantle, WA, Australia; Partial — 389 abstracts, elasmo-targeted pages only (teleost content not captured)</t>
         </is>
       </c>
-      <c r="P95" s="19" t="inlineStr"/>
       <c r="Q95" s="19" t="inlineStr"/>
       <c r="R95" s="19" t="inlineStr"/>
       <c r="S95" s="19" t="inlineStr"/>
-      <c r="T95" s="18" t="inlineStr">
+      <c r="T95" s="19" t="inlineStr"/>
+      <c r="U95" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 2 abstracts cited by the corpus [Published 2010]</t>
         </is>
       </c>
-      <c r="U95" s="19" t="inlineStr"/>
       <c r="V95" s="19" t="inlineStr"/>
       <c r="W95" s="19" t="inlineStr"/>
       <c r="X95" s="19" t="inlineStr"/>
-      <c r="Y95" s="18" t="inlineStr">
+      <c r="Y95" s="19" t="inlineStr"/>
+      <c r="Z95" s="18" t="inlineStr">
         <is>
           <t>Missing — 3 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
-      <c r="Z95" s="18" t="inlineStr">
+      <c r="AA95" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 17 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA95" s="19" t="inlineStr"/>
-      <c r="AB95" s="18" t="inlineStr">
+      <c r="AB95" s="19" t="inlineStr"/>
+      <c r="AC95" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 2 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
@@ -6279,7 +6483,7 @@
       </c>
       <c r="C96" s="20" t="inlineStr">
         <is>
-          <t>Providence, RI (172); Ingested</t>
+          <t>Providence, RI (171); Ingested</t>
         </is>
       </c>
       <c r="D96" s="21" t="inlineStr">
@@ -6295,12 +6499,12 @@
       </c>
       <c r="G96" s="19" t="inlineStr"/>
       <c r="H96" s="19" t="inlineStr"/>
-      <c r="I96" s="20" t="inlineStr">
+      <c r="I96" s="19" t="inlineStr"/>
+      <c r="J96" s="20" t="inlineStr">
         <is>
           <t>Ciudad Universitaria, Mexico City; Ingested — Fable extraction 2026-09-17, 61 abstracts</t>
         </is>
       </c>
-      <c r="J96" s="19" t="inlineStr"/>
       <c r="K96" s="19" t="inlineStr"/>
       <c r="L96" s="19" t="inlineStr"/>
       <c r="M96" s="19" t="inlineStr"/>
@@ -6312,21 +6516,22 @@
       <c r="S96" s="19" t="inlineStr"/>
       <c r="T96" s="19" t="inlineStr"/>
       <c r="U96" s="19" t="inlineStr"/>
-      <c r="V96" s="18" t="inlineStr">
+      <c r="V96" s="19" t="inlineStr"/>
+      <c r="W96" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="W96" s="19" t="inlineStr"/>
       <c r="X96" s="19" t="inlineStr"/>
-      <c r="Y96" s="18" t="inlineStr">
+      <c r="Y96" s="19" t="inlineStr"/>
+      <c r="Z96" s="18" t="inlineStr">
         <is>
           <t>Missing — 3 abstracts cited by the corpus [3 distinct meetings]</t>
         </is>
       </c>
-      <c r="Z96" s="19" t="inlineStr"/>
       <c r="AA96" s="19" t="inlineStr"/>
-      <c r="AB96" s="18" t="inlineStr">
+      <c r="AB96" s="19" t="inlineStr"/>
+      <c r="AC96" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 4 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
@@ -6358,47 +6563,56 @@
       </c>
       <c r="F97" s="19" t="inlineStr"/>
       <c r="G97" s="19" t="inlineStr"/>
-      <c r="H97" s="19" t="inlineStr"/>
-      <c r="I97" s="19" t="inlineStr"/>
-      <c r="J97" s="18" t="inlineStr">
+      <c r="H97" s="18" t="inlineStr">
+        <is>
+          <t>Rio Grande, RS, Brazil; Missing — 87 abstracts in the book (Soares &amp; Petean 2023 Table 1), titles only in their Tab. S1</t>
+        </is>
+      </c>
+      <c r="I97" s="18" t="inlineStr">
+        <is>
+          <t>Manaus, AM, Brazil; Missing — 27 chondrichthyan (of 786) abstracts in the book (Soares &amp; Petean 2023 Table 1), titles only in their Tab. S1</t>
+        </is>
+      </c>
+      <c r="J97" s="19" t="inlineStr"/>
+      <c r="K97" s="18" t="inlineStr">
         <is>
           <t>Dakar, Senegal; Missing — 48 abstracts cited by the corpus</t>
         </is>
       </c>
-      <c r="K97" s="19" t="inlineStr"/>
-      <c r="L97" s="18" t="inlineStr">
+      <c r="L97" s="19" t="inlineStr"/>
+      <c r="M97" s="18" t="inlineStr">
         <is>
           <t>Vancouver, Canada; Missing — 12 abstracts cited by the corpus [Published 2012]</t>
         </is>
       </c>
-      <c r="M97" s="19" t="inlineStr"/>
       <c r="N97" s="19" t="inlineStr"/>
       <c r="O97" s="19" t="inlineStr"/>
       <c r="P97" s="19" t="inlineStr"/>
       <c r="Q97" s="19" t="inlineStr"/>
-      <c r="R97" s="18" t="inlineStr">
+      <c r="R97" s="19" t="inlineStr"/>
+      <c r="S97" s="18" t="inlineStr">
         <is>
           <t>Seattle, WA; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="S97" s="19" t="inlineStr"/>
       <c r="T97" s="19" t="inlineStr"/>
       <c r="U97" s="19" t="inlineStr"/>
       <c r="V97" s="19" t="inlineStr"/>
       <c r="W97" s="19" t="inlineStr"/>
       <c r="X97" s="19" t="inlineStr"/>
-      <c r="Y97" s="18" t="inlineStr">
+      <c r="Y97" s="19" t="inlineStr"/>
+      <c r="Z97" s="18" t="inlineStr">
         <is>
           <t>Missing — 9 abstracts cited by the corpus [5 distinct meetings]</t>
         </is>
       </c>
-      <c r="Z97" s="18" t="inlineStr">
+      <c r="AA97" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 2 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA97" s="19" t="inlineStr"/>
-      <c r="AB97" s="18" t="inlineStr">
+      <c r="AB97" s="19" t="inlineStr"/>
+      <c r="AC97" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
         </is>
@@ -6436,53 +6650,54 @@
       <c r="K98" s="19" t="inlineStr"/>
       <c r="L98" s="19" t="inlineStr"/>
       <c r="M98" s="19" t="inlineStr"/>
-      <c r="N98" s="18" t="inlineStr">
+      <c r="N98" s="19" t="inlineStr"/>
+      <c r="O98" s="18" t="inlineStr">
         <is>
           <t>Vancouver, Canada; Missing — 100 abstracts cited by the corpus [Published 2010, 2015]</t>
         </is>
       </c>
-      <c r="O98" s="19" t="inlineStr"/>
-      <c r="P98" s="18" t="inlineStr">
+      <c r="P98" s="19" t="inlineStr"/>
+      <c r="Q98" s="18" t="inlineStr">
         <is>
           <t>Cairns, Queensland, Australia; Missing — 13 abstracts cited by the corpus</t>
         </is>
       </c>
-      <c r="Q98" s="18" t="inlineStr">
+      <c r="R98" s="18" t="inlineStr">
         <is>
           <t>Edinburgh, Scotland; Missing — 6 abstracts cited by the corpus</t>
         </is>
       </c>
-      <c r="R98" s="18" t="inlineStr">
+      <c r="S98" s="18" t="inlineStr">
         <is>
           <t>Missing — 2 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
-      <c r="S98" s="19" t="inlineStr"/>
       <c r="T98" s="19" t="inlineStr"/>
       <c r="U98" s="19" t="inlineStr"/>
       <c r="V98" s="19" t="inlineStr"/>
-      <c r="W98" s="18" t="inlineStr">
+      <c r="W98" s="19" t="inlineStr"/>
+      <c r="X98" s="18" t="inlineStr">
         <is>
           <t>Honolulu, HI (U. Hawai'i at Manoa); Missing — 3 abstracts cited by the corpus</t>
         </is>
       </c>
-      <c r="X98" s="19" t="inlineStr"/>
-      <c r="Y98" s="18" t="inlineStr">
+      <c r="Y98" s="19" t="inlineStr"/>
+      <c r="Z98" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="Z98" s="18" t="inlineStr">
+      <c r="AA98" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 3 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA98" s="18" t="inlineStr">
+      <c r="AB98" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 6 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AB98" s="18" t="inlineStr">
+      <c r="AC98" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 2 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
@@ -6515,42 +6730,47 @@
       <c r="F99" s="19" t="inlineStr"/>
       <c r="G99" s="19" t="inlineStr"/>
       <c r="H99" s="19" t="inlineStr"/>
-      <c r="I99" s="19" t="inlineStr"/>
+      <c r="I99" s="18" t="inlineStr">
+        <is>
+          <t>Maringa, PR, Brazil; Missing — 28 chondrichthyan (of 1033) abstracts in the book (Soares &amp; Petean 2023 Table 1), titles only in their Tab. S1</t>
+        </is>
+      </c>
       <c r="J99" s="19" t="inlineStr"/>
       <c r="K99" s="19" t="inlineStr"/>
       <c r="L99" s="19" t="inlineStr"/>
-      <c r="M99" s="18" t="inlineStr">
+      <c r="M99" s="19" t="inlineStr"/>
+      <c r="N99" s="18" t="inlineStr">
         <is>
           <t>Missing — 2 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
-      <c r="N99" s="19" t="inlineStr"/>
       <c r="O99" s="19" t="inlineStr"/>
       <c r="P99" s="19" t="inlineStr"/>
       <c r="Q99" s="19" t="inlineStr"/>
       <c r="R99" s="19" t="inlineStr"/>
       <c r="S99" s="19" t="inlineStr"/>
-      <c r="T99" s="18" t="inlineStr">
+      <c r="T99" s="19" t="inlineStr"/>
+      <c r="U99" s="18" t="inlineStr">
         <is>
           <t>Vienna, Austria; Missing — 10 abstracts cited by the corpus</t>
         </is>
       </c>
-      <c r="U99" s="19" t="inlineStr"/>
       <c r="V99" s="19" t="inlineStr"/>
       <c r="W99" s="19" t="inlineStr"/>
       <c r="X99" s="19" t="inlineStr"/>
-      <c r="Y99" s="18" t="inlineStr">
+      <c r="Y99" s="19" t="inlineStr"/>
+      <c r="Z99" s="18" t="inlineStr">
         <is>
           <t>Missing — 2 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
-      <c r="Z99" s="19" t="inlineStr"/>
-      <c r="AA99" s="18" t="inlineStr">
+      <c r="AA99" s="19" t="inlineStr"/>
+      <c r="AB99" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 16 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AB99" s="18" t="inlineStr">
+      <c r="AC99" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
         </is>
@@ -6567,7 +6787,7 @@
       </c>
       <c r="C100" s="20" t="inlineStr">
         <is>
-          <t>Chattanooga, TN (92); Ingested</t>
+          <t>Chattanooga, TN (90); Ingested</t>
         </is>
       </c>
       <c r="D100" s="20" t="inlineStr">
@@ -6590,13 +6810,17 @@
           <t>?; Missing — 79 abstracts cited by the corpus</t>
         </is>
       </c>
-      <c r="H100" s="19" t="inlineStr"/>
-      <c r="I100" s="18" t="inlineStr">
+      <c r="H100" s="18" t="inlineStr">
+        <is>
+          <t>Recife, PE, Brazil (UFRPE); Missing — 72 abstracts in the book (Soares &amp; Petean 2023 Table 1), titles only in their Tab. S1</t>
+        </is>
+      </c>
+      <c r="I100" s="19" t="inlineStr"/>
+      <c r="J100" s="18" t="inlineStr">
         <is>
           <t>Mazatlan, Sinaloa, Mexico; Missing — 44 abstracts cited by the corpus</t>
         </is>
       </c>
-      <c r="J100" s="19" t="inlineStr"/>
       <c r="K100" s="19" t="inlineStr"/>
       <c r="L100" s="19" t="inlineStr"/>
       <c r="M100" s="19" t="inlineStr"/>
@@ -6604,29 +6828,30 @@
       <c r="O100" s="19" t="inlineStr"/>
       <c r="P100" s="19" t="inlineStr"/>
       <c r="Q100" s="19" t="inlineStr"/>
-      <c r="R100" s="18" t="inlineStr">
+      <c r="R100" s="19" t="inlineStr"/>
+      <c r="S100" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="S100" s="19" t="inlineStr"/>
       <c r="T100" s="19" t="inlineStr"/>
       <c r="U100" s="19" t="inlineStr"/>
       <c r="V100" s="19" t="inlineStr"/>
       <c r="W100" s="19" t="inlineStr"/>
       <c r="X100" s="19" t="inlineStr"/>
-      <c r="Y100" s="18" t="inlineStr">
+      <c r="Y100" s="19" t="inlineStr"/>
+      <c r="Z100" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="Z100" s="19" t="inlineStr"/>
-      <c r="AA100" s="18" t="inlineStr">
+      <c r="AA100" s="19" t="inlineStr"/>
+      <c r="AB100" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 13 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AB100" s="18" t="inlineStr">
+      <c r="AC100" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
         </is>
@@ -6643,7 +6868,7 @@
       </c>
       <c r="C101" s="20" t="inlineStr">
         <is>
-          <t>Reno, NV (118); Ingested</t>
+          <t>Reno, NV (116); Ingested</t>
         </is>
       </c>
       <c r="D101" s="23" t="inlineStr">
@@ -6659,7 +6884,11 @@
       <c r="F101" s="19" t="inlineStr"/>
       <c r="G101" s="19" t="inlineStr"/>
       <c r="H101" s="19" t="inlineStr"/>
-      <c r="I101" s="19" t="inlineStr"/>
+      <c r="I101" s="18" t="inlineStr">
+        <is>
+          <t>Olinda, PE, Brazil; Missing — 32 chondrichthyan (of 1169) abstracts in the book (Soares &amp; Petean 2023 Table 1), titles only in their Tab. S1 [online, not harvested: http://www.automacaodeeventos.com.br/ebi2015/cd/index.htm]</t>
+        </is>
+      </c>
       <c r="J101" s="19" t="inlineStr"/>
       <c r="K101" s="19" t="inlineStr"/>
       <c r="L101" s="19" t="inlineStr"/>
@@ -6675,18 +6904,19 @@
       <c r="V101" s="19" t="inlineStr"/>
       <c r="W101" s="19" t="inlineStr"/>
       <c r="X101" s="19" t="inlineStr"/>
-      <c r="Y101" s="18" t="inlineStr">
+      <c r="Y101" s="19" t="inlineStr"/>
+      <c r="Z101" s="18" t="inlineStr">
         <is>
           <t>Missing — 5 abstracts cited by the corpus [4 distinct meetings]</t>
         </is>
       </c>
-      <c r="Z101" s="19" t="inlineStr"/>
-      <c r="AA101" s="18" t="inlineStr">
+      <c r="AA101" s="19" t="inlineStr"/>
+      <c r="AB101" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 3 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AB101" s="18" t="inlineStr">
+      <c r="AC101" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 3 queue rows are abstracts from this meeting (track C 2026-09-17)</t>
         </is>
@@ -6718,13 +6948,17 @@
       </c>
       <c r="F102" s="19" t="inlineStr"/>
       <c r="G102" s="19" t="inlineStr"/>
-      <c r="H102" s="19" t="inlineStr"/>
-      <c r="I102" s="20" t="inlineStr">
+      <c r="H102" s="18" t="inlineStr">
+        <is>
+          <t>Penedo, AL, Brazil (UFAL); Missing — 107 abstracts in the book (Soares &amp; Petean 2023 Table 1), titles only in their Tab. S1</t>
+        </is>
+      </c>
+      <c r="I102" s="19" t="inlineStr"/>
+      <c r="J102" s="20" t="inlineStr">
         <is>
           <t>Puerto Vallarta, Jalisco, Mexico; Ingested — Fable extraction 2026-09-17, 55 abstracts</t>
         </is>
       </c>
-      <c r="J102" s="19" t="inlineStr"/>
       <c r="K102" s="19" t="inlineStr"/>
       <c r="L102" s="19" t="inlineStr"/>
       <c r="M102" s="19" t="inlineStr"/>
@@ -6739,14 +6973,15 @@
       <c r="V102" s="19" t="inlineStr"/>
       <c r="W102" s="19" t="inlineStr"/>
       <c r="X102" s="19" t="inlineStr"/>
-      <c r="Y102" s="18" t="inlineStr">
+      <c r="Y102" s="19" t="inlineStr"/>
+      <c r="Z102" s="18" t="inlineStr">
         <is>
           <t>Missing — 3 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
-      <c r="Z102" s="19" t="inlineStr"/>
       <c r="AA102" s="19" t="inlineStr"/>
       <c r="AB102" s="19" t="inlineStr"/>
+      <c r="AC102" s="19" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="17" t="n">
@@ -6771,7 +7006,11 @@
       <c r="F103" s="19" t="inlineStr"/>
       <c r="G103" s="19" t="inlineStr"/>
       <c r="H103" s="19" t="inlineStr"/>
-      <c r="I103" s="19" t="inlineStr"/>
+      <c r="I103" s="18" t="inlineStr">
+        <is>
+          <t>Porto Seguro, BA, Brazil; Missing — 24 chondrichthyan (of 765) abstracts in the book (Soares &amp; Petean 2023 Table 1), titles only in their Tab. S1</t>
+        </is>
+      </c>
       <c r="J103" s="19" t="inlineStr"/>
       <c r="K103" s="19" t="inlineStr"/>
       <c r="L103" s="19" t="inlineStr"/>
@@ -6787,14 +7026,15 @@
       <c r="V103" s="19" t="inlineStr"/>
       <c r="W103" s="19" t="inlineStr"/>
       <c r="X103" s="19" t="inlineStr"/>
-      <c r="Y103" s="18" t="inlineStr">
+      <c r="Y103" s="19" t="inlineStr"/>
+      <c r="Z103" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus [Published 2018]</t>
         </is>
       </c>
-      <c r="Z103" s="19" t="inlineStr"/>
       <c r="AA103" s="19" t="inlineStr"/>
       <c r="AB103" s="19" t="inlineStr"/>
+      <c r="AC103" s="19" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="17" t="n">
@@ -6826,7 +7066,11 @@
         </is>
       </c>
       <c r="G104" s="19" t="inlineStr"/>
-      <c r="H104" s="19" t="inlineStr"/>
+      <c r="H104" s="20" t="inlineStr">
+        <is>
+          <t>Joao Pessoa, PB, Brazil; Ingested — joint meeting, held as the SI 2018 book (see the SI column)</t>
+        </is>
+      </c>
       <c r="I104" s="19" t="inlineStr"/>
       <c r="J104" s="19" t="inlineStr"/>
       <c r="K104" s="19" t="inlineStr"/>
@@ -6843,14 +7087,15 @@
       <c r="V104" s="19" t="inlineStr"/>
       <c r="W104" s="19" t="inlineStr"/>
       <c r="X104" s="19" t="inlineStr"/>
-      <c r="Y104" s="18" t="inlineStr">
+      <c r="Y104" s="19" t="inlineStr"/>
+      <c r="Z104" s="18" t="inlineStr">
         <is>
           <t>Missing — 3 abstracts cited by the corpus [3 distinct meetings]</t>
         </is>
       </c>
-      <c r="Z104" s="19" t="inlineStr"/>
       <c r="AA104" s="19" t="inlineStr"/>
       <c r="AB104" s="19" t="inlineStr"/>
+      <c r="AC104" s="19" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="17" t="n">
@@ -6879,7 +7124,11 @@
       <c r="F105" s="19" t="inlineStr"/>
       <c r="G105" s="19" t="inlineStr"/>
       <c r="H105" s="19" t="inlineStr"/>
-      <c r="I105" s="19" t="inlineStr"/>
+      <c r="I105" s="18" t="inlineStr">
+        <is>
+          <t>Belem, PA, Brazil; Missing — 29 chondrichthyan (of 1010) abstracts in the book (Soares &amp; Petean 2023 Table 1), titles only in their Tab. S1</t>
+        </is>
+      </c>
       <c r="J105" s="19" t="inlineStr"/>
       <c r="K105" s="19" t="inlineStr"/>
       <c r="L105" s="19" t="inlineStr"/>
@@ -6891,18 +7140,19 @@
       <c r="R105" s="19" t="inlineStr"/>
       <c r="S105" s="19" t="inlineStr"/>
       <c r="T105" s="19" t="inlineStr"/>
-      <c r="U105" s="18" t="inlineStr">
+      <c r="U105" s="19" t="inlineStr"/>
+      <c r="V105" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="V105" s="19" t="inlineStr"/>
       <c r="W105" s="19" t="inlineStr"/>
       <c r="X105" s="19" t="inlineStr"/>
       <c r="Y105" s="19" t="inlineStr"/>
       <c r="Z105" s="19" t="inlineStr"/>
       <c r="AA105" s="19" t="inlineStr"/>
       <c r="AB105" s="19" t="inlineStr"/>
+      <c r="AC105" s="19" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="17" t="n">
@@ -6947,18 +7197,19 @@
       <c r="V106" s="19" t="inlineStr"/>
       <c r="W106" s="19" t="inlineStr"/>
       <c r="X106" s="19" t="inlineStr"/>
-      <c r="Y106" s="18" t="inlineStr">
+      <c r="Y106" s="19" t="inlineStr"/>
+      <c r="Z106" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="Z106" s="18" t="inlineStr">
+      <c r="AA106" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 queue row is an abstract from this meeting (track C 2026-09-17)</t>
         </is>
       </c>
-      <c r="AA106" s="19" t="inlineStr"/>
       <c r="AB106" s="19" t="inlineStr"/>
+      <c r="AC106" s="19" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="17" t="n">
@@ -6983,12 +7234,12 @@
       <c r="F107" s="19" t="inlineStr"/>
       <c r="G107" s="19" t="inlineStr"/>
       <c r="H107" s="19" t="inlineStr"/>
-      <c r="I107" s="23" t="inlineStr">
+      <c r="I107" s="19" t="inlineStr"/>
+      <c r="J107" s="23" t="inlineStr">
         <is>
           <t>Puebla, Mexico; Digital — 1 PDF held — extraction pending</t>
         </is>
       </c>
-      <c r="J107" s="19" t="inlineStr"/>
       <c r="K107" s="19" t="inlineStr"/>
       <c r="L107" s="19" t="inlineStr"/>
       <c r="M107" s="19" t="inlineStr"/>
@@ -7003,14 +7254,15 @@
       <c r="V107" s="19" t="inlineStr"/>
       <c r="W107" s="19" t="inlineStr"/>
       <c r="X107" s="19" t="inlineStr"/>
-      <c r="Y107" s="18" t="inlineStr">
+      <c r="Y107" s="19" t="inlineStr"/>
+      <c r="Z107" s="18" t="inlineStr">
         <is>
           <t>Missing — 2 abstracts cited by the corpus [2 distinct meetings]</t>
         </is>
       </c>
-      <c r="Z107" s="19" t="inlineStr"/>
       <c r="AA107" s="19" t="inlineStr"/>
       <c r="AB107" s="19" t="inlineStr"/>
+      <c r="AC107" s="19" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="17" t="n">
@@ -7043,7 +7295,11 @@
       </c>
       <c r="G108" s="19" t="inlineStr"/>
       <c r="H108" s="19" t="inlineStr"/>
-      <c r="I108" s="19" t="inlineStr"/>
+      <c r="I108" s="18" t="inlineStr">
+        <is>
+          <t>Gramado, RS, Brazil; Missing — meeting held, abstract count unknown</t>
+        </is>
+      </c>
       <c r="J108" s="19" t="inlineStr"/>
       <c r="K108" s="19" t="inlineStr"/>
       <c r="L108" s="19" t="inlineStr"/>
@@ -7059,14 +7315,15 @@
       <c r="V108" s="19" t="inlineStr"/>
       <c r="W108" s="19" t="inlineStr"/>
       <c r="X108" s="19" t="inlineStr"/>
-      <c r="Y108" s="18" t="inlineStr">
+      <c r="Y108" s="19" t="inlineStr"/>
+      <c r="Z108" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 2 abstracts cited by the corpus</t>
         </is>
       </c>
-      <c r="Z108" s="19" t="inlineStr"/>
       <c r="AA108" s="19" t="inlineStr"/>
       <c r="AB108" s="19" t="inlineStr"/>
+      <c r="AC108" s="19" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="17" t="n">
@@ -7079,7 +7336,7 @@
       </c>
       <c r="C109" s="20" t="inlineStr">
         <is>
-          <t>Norfolk, VA (154); Ingested</t>
+          <t>Norfolk, VA (153); Ingested</t>
         </is>
       </c>
       <c r="D109" s="20" t="inlineStr">
@@ -7097,32 +7354,33 @@
       <c r="L109" s="19" t="inlineStr"/>
       <c r="M109" s="19" t="inlineStr"/>
       <c r="N109" s="19" t="inlineStr"/>
-      <c r="O109" s="25" t="inlineStr">
+      <c r="O109" s="19" t="inlineStr"/>
+      <c r="P109" s="25" t="inlineStr">
         <is>
           <t>Auckland, New Zealand; Partial — 142 abstracts, elasmo-targeted pages only (teleost content not captured)</t>
         </is>
       </c>
-      <c r="P109" s="19" t="inlineStr"/>
       <c r="Q109" s="19" t="inlineStr"/>
       <c r="R109" s="19" t="inlineStr"/>
       <c r="S109" s="19" t="inlineStr"/>
-      <c r="T109" s="18" t="inlineStr">
+      <c r="T109" s="19" t="inlineStr"/>
+      <c r="U109" s="18" t="inlineStr">
         <is>
           <t>Stuttgart, Germany; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="U109" s="19" t="inlineStr"/>
       <c r="V109" s="19" t="inlineStr"/>
       <c r="W109" s="19" t="inlineStr"/>
       <c r="X109" s="19" t="inlineStr"/>
-      <c r="Y109" s="18" t="inlineStr">
+      <c r="Y109" s="19" t="inlineStr"/>
+      <c r="Z109" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="Z109" s="19" t="inlineStr"/>
       <c r="AA109" s="19" t="inlineStr"/>
       <c r="AB109" s="19" t="inlineStr"/>
+      <c r="AC109" s="19" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="17" t="n">
@@ -7171,6 +7429,7 @@
       <c r="Z110" s="19" t="inlineStr"/>
       <c r="AA110" s="19" t="inlineStr"/>
       <c r="AB110" s="19" t="inlineStr"/>
+      <c r="AC110" s="19" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="17" t="n">
@@ -7199,12 +7458,16 @@
       <c r="F111" s="19" t="inlineStr"/>
       <c r="G111" s="19" t="inlineStr"/>
       <c r="H111" s="19" t="inlineStr"/>
-      <c r="I111" s="20" t="inlineStr">
+      <c r="I111" s="18" t="inlineStr">
+        <is>
+          <t>Palmas, TO, Brazil; Missing — meeting held, abstract count unknown [online, not harvested: https://editorarealize.com.br/edicao/detalhes/anais-do-ebi---encontro-brasileiro-de-ictiologia (770 papers)]</t>
+        </is>
+      </c>
+      <c r="J111" s="20" t="inlineStr">
         <is>
           <t>Ensenada, Baja California, Mexico; Ingested — Fable extraction 2026-09-17, 104 abstracts</t>
         </is>
       </c>
-      <c r="J111" s="19" t="inlineStr"/>
       <c r="K111" s="19" t="inlineStr"/>
       <c r="L111" s="19" t="inlineStr"/>
       <c r="M111" s="19" t="inlineStr"/>
@@ -7219,14 +7482,15 @@
       <c r="V111" s="19" t="inlineStr"/>
       <c r="W111" s="19" t="inlineStr"/>
       <c r="X111" s="19" t="inlineStr"/>
-      <c r="Y111" s="18" t="inlineStr">
+      <c r="Y111" s="19" t="inlineStr"/>
+      <c r="Z111" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 3 abstracts cited by the corpus</t>
         </is>
       </c>
-      <c r="Z111" s="19" t="inlineStr"/>
       <c r="AA111" s="19" t="inlineStr"/>
       <c r="AB111" s="19" t="inlineStr"/>
+      <c r="AC111" s="19" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="17" t="n">
@@ -7239,7 +7503,7 @@
       </c>
       <c r="C112" s="28" t="inlineStr">
         <is>
-          <t>New Orleans, LA (235); Extracted — regex-parsed; Fable re-extraction queued</t>
+          <t>New Orleans, LA (232); Extracted — regex-parsed; Fable re-extraction queued</t>
         </is>
       </c>
       <c r="D112" s="20" t="inlineStr">
@@ -7275,14 +7539,15 @@
       <c r="V112" s="19" t="inlineStr"/>
       <c r="W112" s="19" t="inlineStr"/>
       <c r="X112" s="19" t="inlineStr"/>
-      <c r="Y112" s="18" t="inlineStr">
+      <c r="Y112" s="19" t="inlineStr"/>
+      <c r="Z112" s="18" t="inlineStr">
         <is>
           <t>?; Missing — 1 abstract cited by the corpus</t>
         </is>
       </c>
-      <c r="Z112" s="19" t="inlineStr"/>
       <c r="AA112" s="19" t="inlineStr"/>
       <c r="AB112" s="19" t="inlineStr"/>
+      <c r="AC112" s="19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7644,16 +7909,16 @@
         <v>82</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -8270,16 +8535,16 @@
         <v>3670</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>8201</v>
+        <v>8242</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>5171</v>
+        <v>5204</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>161</v>
+        <v>201</v>
       </c>
       <c r="G39" s="1" t="n">
         <v>1068</v>

--- a/database/conference_coverage_matrix.xlsx
+++ b/database/conference_coverage_matrix.xlsx
@@ -1688,7 +1688,7 @@
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Sociedade Brasileira de Ictiologia (SBI); official biennial meeting, annual 1983-1992 then biennial from 1993-95. Editions: IX 1991 Maringa PR (UEM/Nupelia), X 1993 Sao Paulo (USP), XI 1995 Campinas (PUCCAMP), XII 1997 Sao Paulo (IO-USP, 24-28 Feb), XIII 1999 SP (city not established), XIV 2001 Sao Leopoldo RS (UNISINOS), XV 2003 Sao Paulo, XVI 2005 Joao Pessoa PB, XVII 2007 Itajai SC (Univali), XVIII 2009 Cuiaba MT (UFMT), XIX 2011 Manaus AM, XX 2013 Maringa PR, XXI 2015 Olinda PE (UFRPE), XXII 2017 Porto Seguro BA (UFSB), XXIII 2019 Belem PA, XXIV 2022 Gramado RS, XXV 2025 Palmas TO (UFT, 26-31 Jan). Chondrichthyans are 1.4-6.6% of each book (326 abstracts 1991-2019, Soares &amp; Petean 2023), so this column counts elasmo abstracts, not the whole book. No corpus record cites EBI yet (2026-10-28).</t>
+          <t>Sociedade Brasileira de Ictiologia (SBI); official biennial meeting, annual 1983-1992 then biennial from 1993-95. Editions: IX 1991 Maringa PR (UEM/Nupelia), X 1993 Sao Paulo (USP), XI 1995 Campinas (PUCCAMP), XII 1997 Sao Paulo (IO-USP, 24-28 Feb), XIII 1999 Sao Paulo SP, XIV 2001 Sao Leopoldo RS (UNISINOS), XV 2003 Sao Paulo, XVI 2005 Joao Pessoa PB, XVII 2007 Itajai SC (Univali), XVIII 2009 Cuiaba MT (UFMT), XIX 2011 Manaus AM, XX 2013 Maringa PR, XXI 2015 Olinda PE (UFRPE), XXII 2017 Porto Seguro BA (UFSB), XXIII 2019 Belem PA, XXIV 2022 Gramado RS, XXV 2025 Palmas TO (UFT, 26-31 Jan). Chondrichthyans are 1.4-6.6% of each book (326 abstracts 1991-2019, Soares &amp; Petean 2023), so this column counts elasmo abstracts, not the whole book. No corpus record cites EBI yet (2026-10-28). 2015 (1,169) and 2025 (770) proceedings HARVESTED 2026-10-28 (fetch_ebi.py, ingest_ebi.py): every abstract, Portuguese kept verbatim, English titles and elasmo abstracts translated (translate_abstracts.py).</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -5806,7 +5806,7 @@
       <c r="H85" s="19" t="inlineStr"/>
       <c r="I85" s="18" t="inlineStr">
         <is>
-          <t>?; Missing — 40 chondrichthyan (of 610) abstracts in the book (Soares &amp; Petean 2023 Table 1), titles only in their Tab. S1</t>
+          <t>Sao Paulo, SP, Brazil; Missing — 40 chondrichthyan (of 610) abstracts in the book (Soares &amp; Petean 2023 Table 1), titles only in their Tab. S1</t>
         </is>
       </c>
       <c r="J85" s="19" t="inlineStr"/>
@@ -6203,7 +6203,7 @@
       </c>
       <c r="C92" s="20" t="inlineStr">
         <is>
-          <t>New Orleans, LA (168); Ingested</t>
+          <t>New Orleans, LA (169); Ingested</t>
         </is>
       </c>
       <c r="D92" s="24" t="inlineStr">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="C101" s="20" t="inlineStr">
         <is>
-          <t>Reno, NV (116); Ingested</t>
+          <t>Reno, NV (115); Ingested</t>
         </is>
       </c>
       <c r="D101" s="23" t="inlineStr">
@@ -6884,9 +6884,9 @@
       <c r="F101" s="19" t="inlineStr"/>
       <c r="G101" s="19" t="inlineStr"/>
       <c r="H101" s="19" t="inlineStr"/>
-      <c r="I101" s="18" t="inlineStr">
-        <is>
-          <t>Olinda, PE, Brazil; Missing — 32 chondrichthyan (of 1169) abstracts in the book (Soares &amp; Petean 2023 Table 1), titles only in their Tab. S1 [online, not harvested: http://www.automacaodeeventos.com.br/ebi2015/cd/index.htm]</t>
+      <c r="I101" s="20" t="inlineStr">
+        <is>
+          <t>Olinda, PE, Brazil; Ingested — 1169 abstracts, 52 chondrichthyan by our lexicon (32 per Soares &amp; Petean 2023)</t>
         </is>
       </c>
       <c r="J101" s="19" t="inlineStr"/>
@@ -7458,9 +7458,9 @@
       <c r="F111" s="19" t="inlineStr"/>
       <c r="G111" s="19" t="inlineStr"/>
       <c r="H111" s="19" t="inlineStr"/>
-      <c r="I111" s="18" t="inlineStr">
-        <is>
-          <t>Palmas, TO, Brazil; Missing — meeting held, abstract count unknown [online, not harvested: https://editorarealize.com.br/edicao/detalhes/anais-do-ebi---encontro-brasileiro-de-ictiologia (770 papers)]</t>
+      <c r="I111" s="20" t="inlineStr">
+        <is>
+          <t>Palmas, TO, Brazil; Ingested — 770 abstracts, 60 chondrichthyan by our lexicon</t>
         </is>
       </c>
       <c r="J111" s="20" t="inlineStr">
@@ -8218,7 +8218,7 @@
         <v>2015</v>
       </c>
       <c r="B27" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C27" t="n">
         <v>318</v>
@@ -8532,7 +8532,7 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>3670</v>
+        <v>3669</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>8242</v>
